--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99E817C-2989-4006-AF97-622F96ADA5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -40,6 +33,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -50,13 +44,14 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该游戏元素的图标名称</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -64,6 +59,7 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -74,19 +70,21 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏元素ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -96,6 +94,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该元素的特性，有百搭，普通，分散，特殊普通，分散百搭
@@ -107,13 +106,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -123,6 +123,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">该特性下的特点描述
@@ -214,35 +215,30 @@
     <t>保险箱</t>
   </si>
   <si>
+    <t>美金</t>
+  </si>
+  <si>
+    <t>绿火车MINI</t>
+  </si>
+  <si>
+    <t>蓝火车MINOR</t>
+  </si>
+  <si>
+    <t>紫火车MAJOR</t>
+  </si>
+  <si>
+    <t>红火车GRAND</t>
+  </si>
+  <si>
     <t>ALL ABOARD</t>
-  </si>
-  <si>
-    <t>美金</t>
-  </si>
-  <si>
-    <t>绿火车MINI</t>
-  </si>
-  <si>
-    <t>蓝火车MINOR</t>
-  </si>
-  <si>
-    <t>紫火车MAJOR</t>
-  </si>
-  <si>
-    <t>红火车GRAND</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,183 +250,52 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -443,194 +308,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -653,251 +332,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -914,69 +351,21 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.799340800195319"/>
+          <bgColor theme="7" tint="0.7993408001953185"/>
         </patternFill>
       </fill>
     </dxf>
@@ -985,6 +374,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1241,20 +633,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="3" width="9.21666666666667" customWidth="1"/>
+    <col min="3" max="3" width="9.25" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:5">
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1286,7 +678,7 @@
       </c>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" ht="16.5" spans="1:5">
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1301,14 +693,14 @@
       </c>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" ht="16.5" spans="1:5">
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" ht="16.5" spans="1:5">
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1325,7 +717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:5">
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -1342,7 +734,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:5">
+    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -1359,7 +751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:5">
+    <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -1376,7 +768,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:5">
+    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -1393,7 +785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:5">
+    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -1410,7 +802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:5">
+    <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -1427,7 +819,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:5">
+    <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -1444,7 +836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:5">
+    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -1461,7 +853,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:5">
+    <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -1478,7 +870,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:5">
+    <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -1495,7 +887,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:5">
+    <row r="16" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
         <v>12</v>
       </c>
@@ -1512,7 +904,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" ht="16.5" spans="1:5">
+    <row r="17" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A17" s="4">
         <v>13</v>
       </c>
@@ -1529,7 +921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:5">
+    <row r="18" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A18" s="4">
         <v>14</v>
       </c>
@@ -1546,7 +938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" ht="16.5" spans="1:5">
+    <row r="19" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A19" s="4">
         <v>15</v>
       </c>
@@ -1563,7 +955,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:5">
+    <row r="20" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A20" s="4">
         <v>16</v>
       </c>
@@ -1580,7 +972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:5">
+    <row r="21" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A21" s="4">
         <v>17</v>
       </c>
@@ -1594,10 +986,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A22" s="4">
         <v>18</v>
       </c>
@@ -1611,10 +1003,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A23" s="4">
         <v>19</v>
       </c>
@@ -1628,10 +1020,10 @@
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A24" s="4">
         <v>20</v>
       </c>
@@ -1645,10 +1037,10 @@
         <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A25" s="4">
         <v>21</v>
       </c>
@@ -1662,10 +1054,10 @@
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A26" s="4">
         <v>22</v>
       </c>
@@ -1679,23 +1071,18 @@
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A4">
+  <phoneticPr fontId="7" type="noConversion"/>
+  <conditionalFormatting sqref="A1:E4">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD($B1,2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:E4">
-    <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -1,31 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A99E817C-2989-4006-AF97-622F96ADA5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -33,7 +40,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -44,14 +50,13 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该游戏元素的图标名称</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -59,7 +64,6 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -70,21 +74,19 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>游戏元素ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -94,7 +96,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>该元素的特性，有百搭，普通，分散，特殊普通，分散百搭
@@ -106,14 +107,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Mr.M:
@@ -123,7 +123,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">该特性下的特点描述
@@ -215,6 +214,9 @@
     <t>保险箱</t>
   </si>
   <si>
+    <t>ALL ABOARD</t>
+  </si>
+  <si>
     <t>美金</t>
   </si>
   <si>
@@ -228,17 +230,19 @@
   </si>
   <si>
     <t>红火车GRAND</t>
-  </si>
-  <si>
-    <t>ALL ABOARD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,52 +254,183 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,8 +443,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -332,9 +653,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -358,14 +921,62 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.7993408001953185"/>
+          <bgColor theme="7" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -375,18 +986,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -633,20 +1234,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="9.25" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -663,7 +1264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -678,7 +1279,7 @@
       </c>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="3" ht="16.5" hidden="1" spans="1:5">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -693,14 +1294,14 @@
       </c>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="4" ht="16.5" hidden="1" spans="1:5">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -717,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -734,7 +1335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -751,7 +1352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -768,7 +1369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -785,7 +1386,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -802,7 +1403,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="11" ht="16.5" spans="1:5">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -819,7 +1420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -836,7 +1437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="13" ht="16.5" spans="1:5">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -853,7 +1454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -870,7 +1471,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="15" ht="16.5" spans="1:5">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -887,7 +1488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="16" ht="16.5" spans="1:5">
       <c r="A16" s="4">
         <v>12</v>
       </c>
@@ -904,7 +1505,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="17" ht="16.5" spans="1:5">
       <c r="A17" s="4">
         <v>13</v>
       </c>
@@ -921,7 +1522,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="18" ht="16.5" spans="1:5">
       <c r="A18" s="4">
         <v>14</v>
       </c>
@@ -938,7 +1539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="19" ht="16.5" spans="1:5">
       <c r="A19" s="4">
         <v>15</v>
       </c>
@@ -955,7 +1556,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="20" ht="16.5" spans="1:5">
       <c r="A20" s="4">
         <v>16</v>
       </c>
@@ -972,7 +1573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="21" ht="16.5" spans="1:5">
       <c r="A21" s="4">
         <v>17</v>
       </c>
@@ -986,10 +1587,10 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:5">
       <c r="A22" s="4">
         <v>18</v>
       </c>
@@ -1003,10 +1604,10 @@
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:5">
       <c r="A23" s="4">
         <v>19</v>
       </c>
@@ -1020,10 +1621,10 @@
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="4">
         <v>20</v>
       </c>
@@ -1037,10 +1638,10 @@
         <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:5">
       <c r="A25" s="4">
         <v>21</v>
       </c>
@@ -1054,10 +1655,10 @@
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="16.5" x14ac:dyDescent="0.15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="4">
         <v>22</v>
       </c>
@@ -1071,11 +1672,10 @@
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="A1:E4">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B1,2)=1</formula>
@@ -1083,6 +1683,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -98,7 +98,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>该元素的特性，有百搭，普通，分散，特殊普通，分散百搭
+          <t>该元素的特性，不通特性对应不同的中奖判断，有百搭，普通，分散，特殊普通，分散百搭
 0 普通：普通元素，可被百搭代替
 1 百搭：连线中，可代替其它普通元素
 2 分散：统计全局数量
@@ -107,40 +107,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Mr.M:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">该特性下的特点描述
-1.只代替普通元素 
-2.对普通元素进行倍率加成 
-3触发奖励游戏
-4.触发免费旋转游戏
-="&lt;config name="""&amp;B2&amp;""" value= """&amp;C2*1&amp;""" export= """&amp;A2&amp;"_"&amp;C2*1&amp;"""/&gt;"
-</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
   <si>
     <t>图标</t>
   </si>
@@ -154,7 +126,13 @@
     <t>类型</t>
   </si>
   <si>
-    <t>描述</t>
+    <t>图案资源</t>
+  </si>
+  <si>
+    <t>消除后变化元素ID</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>int</t>
@@ -172,64 +150,265 @@
     <t>type</t>
   </si>
   <si>
+    <t>postChangeElementId</t>
+  </si>
+  <si>
+    <t>mykd_TB_0.png</t>
+  </si>
+  <si>
+    <t>mykd_TB_1.png</t>
+  </si>
+  <si>
+    <t>mykd_TB_2.png</t>
+  </si>
+  <si>
     <t>J</t>
   </si>
   <si>
+    <t>mykd_TB_3.png</t>
+  </si>
+  <si>
     <t>Q</t>
   </si>
   <si>
+    <t>mykd_TB_4.png</t>
+  </si>
+  <si>
     <t>K</t>
   </si>
   <si>
+    <t>mykd_TB_5.png</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
+    <t>mykd_TB_6.png</t>
+  </si>
+  <si>
     <t>帽子</t>
   </si>
   <si>
+    <t>mykd_TB_7.png</t>
+  </si>
+  <si>
     <t>铃铛</t>
   </si>
   <si>
+    <t>mykd_TB_8.png</t>
+  </si>
+  <si>
     <t>宠物狗</t>
   </si>
   <si>
+    <t>mykd_TB_9.png</t>
+  </si>
+  <si>
     <t>列车员</t>
   </si>
   <si>
+    <t>mykd_TB_10.png</t>
+  </si>
+  <si>
     <t>富豪</t>
   </si>
   <si>
+    <t>mykd_TB_15.png</t>
+  </si>
+  <si>
     <t>百搭wild</t>
   </si>
   <si>
+    <t>mykd_TB_16.png</t>
+  </si>
+  <si>
     <t>百搭wild_X2</t>
   </si>
   <si>
+    <t>mykd_TB_17.png</t>
+  </si>
+  <si>
     <t>百搭wild_X5</t>
   </si>
   <si>
+    <t>mykd_TB_20.png</t>
+  </si>
+  <si>
     <t>金火车</t>
   </si>
   <si>
+    <t>mykd_TB_19.png</t>
+  </si>
+  <si>
     <t>保险箱</t>
   </si>
   <si>
+    <t>mykd_TB_21.png</t>
+  </si>
+  <si>
     <t>ALL ABOARD</t>
   </si>
   <si>
+    <t>mykd_TB_18.png</t>
+  </si>
+  <si>
     <t>美金</t>
   </si>
   <si>
+    <t>mykd_TB_14.png</t>
+  </si>
+  <si>
     <t>绿火车MINI</t>
   </si>
   <si>
+    <t>mykd_TB_13.png</t>
+  </si>
+  <si>
     <t>蓝火车MINOR</t>
   </si>
   <si>
+    <t>mykd_TB_12.png</t>
+  </si>
+  <si>
     <t>紫火车MAJOR</t>
   </si>
   <si>
+    <t>mykd_TB_11.png</t>
+  </si>
+  <si>
     <t>红火车GRAND</t>
+  </si>
+  <si>
+    <t>特殊美金，不统计投资</t>
+  </si>
+  <si>
+    <t>隐藏图案，常规不出现，用于触发免费</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_16.png</t>
+  </si>
+  <si>
+    <t>2条</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_12.png</t>
+  </si>
+  <si>
+    <t>2筒</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_14.png</t>
+  </si>
+  <si>
+    <t>5条</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_10.png</t>
+  </si>
+  <si>
+    <t>5筒</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_8.png</t>
+  </si>
+  <si>
+    <t>八万</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_6.png</t>
+  </si>
+  <si>
+    <t>白板</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_2.png</t>
+  </si>
+  <si>
+    <t>红中</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_4.png</t>
+  </si>
+  <si>
+    <t>发财</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_wild.png</t>
+  </si>
+  <si>
+    <t>Wild</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_hu.png</t>
+  </si>
+  <si>
+    <t>Scatter胡</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_15.png</t>
+  </si>
+  <si>
+    <t>黄金_2条|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_11.png</t>
+  </si>
+  <si>
+    <t>黄金_2筒|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_13.png</t>
+  </si>
+  <si>
+    <t>黄金_5条|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_9.png</t>
+  </si>
+  <si>
+    <t>黄金_5筒|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_7.png</t>
+  </si>
+  <si>
+    <t>黄金_八万|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_5.png</t>
+  </si>
+  <si>
+    <t>黄金_白板|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_1.png</t>
+  </si>
+  <si>
+    <t>黄金_红中|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_3.png</t>
+  </si>
+  <si>
+    <t>黄金_发财|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>空格</t>
+  </si>
+  <si>
+    <t>护符</t>
+  </si>
+  <si>
+    <t>荷鲁斯之眼</t>
+  </si>
+  <si>
+    <t>翅膀</t>
+  </si>
+  <si>
+    <t>艳后</t>
+  </si>
+  <si>
+    <t>夺宝</t>
   </si>
 </sst>
 </file>
@@ -242,7 +421,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,6 +437,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -406,13 +592,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -430,7 +616,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,6 +626,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -771,137 +975,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -918,6 +1122,30 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1240,14 +1468,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
+    <col min="1" max="1" width="10.375"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="5" max="6" width="21.8" customWidth="1"/>
+    <col min="7" max="7" width="24.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
+    <row r="1" ht="16.5" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,47 +1493,64 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:5">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" s="5"/>
-    </row>
-    <row r="3" ht="16.5" hidden="1" spans="1:5">
+      <c r="F2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="5"/>
-    </row>
-    <row r="4" ht="16.5" hidden="1" spans="1:5">
+      <c r="F3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:7">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:5">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:7">
       <c r="A5" s="4">
-        <v>1</v>
+        <f>B5*100+C5</f>
+        <v>10010001</v>
       </c>
       <c r="B5" s="4">
         <v>100100</v>
@@ -1314,13 +1561,18 @@
       <c r="D5" s="5">
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:5">
+    <row r="6" ht="16.5" spans="1:7">
       <c r="A6" s="4">
-        <v>2</v>
+        <f t="shared" ref="A6:A28" si="0">B6*100+C6</f>
+        <v>10010002</v>
       </c>
       <c r="B6" s="4">
         <v>100100</v>
@@ -1331,13 +1583,18 @@
       <c r="D6" s="5">
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:5">
+    <row r="7" ht="16.5" spans="1:7">
       <c r="A7" s="4">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>10010003</v>
       </c>
       <c r="B7" s="4">
         <v>100100</v>
@@ -1349,12 +1606,17 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
+        <v>15</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:7">
       <c r="A8" s="4">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>10010004</v>
       </c>
       <c r="B8" s="4">
         <v>100100</v>
@@ -1366,12 +1628,17 @@
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
+        <v>17</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:7">
       <c r="A9" s="4">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>10010005</v>
       </c>
       <c r="B9" s="4">
         <v>100100</v>
@@ -1383,12 +1650,17 @@
         <v>0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:5">
+        <v>19</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:7">
       <c r="A10" s="4">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>10010006</v>
       </c>
       <c r="B10" s="4">
         <v>100100</v>
@@ -1400,12 +1672,17 @@
         <v>0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:5">
+        <v>21</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:7">
       <c r="A11" s="4">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>10010007</v>
       </c>
       <c r="B11" s="4">
         <v>100100</v>
@@ -1417,12 +1694,17 @@
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:5">
+        <v>23</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:7">
       <c r="A12" s="4">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>10010008</v>
       </c>
       <c r="B12" s="4">
         <v>100100</v>
@@ -1434,12 +1716,17 @@
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:5">
+        <v>25</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:7">
       <c r="A13" s="4">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>10010009</v>
       </c>
       <c r="B13" s="4">
         <v>100100</v>
@@ -1451,12 +1738,17 @@
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:5">
+        <v>27</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:7">
       <c r="A14" s="4">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>10010010</v>
       </c>
       <c r="B14" s="4">
         <v>100100</v>
@@ -1468,12 +1760,17 @@
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:5">
+        <v>29</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:7">
       <c r="A15" s="4">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>10010011</v>
       </c>
       <c r="B15" s="4">
         <v>100100</v>
@@ -1485,12 +1782,17 @@
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:5">
+        <v>31</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:7">
       <c r="A16" s="4">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>10010012</v>
       </c>
       <c r="B16" s="4">
         <v>100100</v>
@@ -1502,12 +1804,17 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:5">
+        <v>33</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:7">
       <c r="A17" s="4">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>10010013</v>
       </c>
       <c r="B17" s="4">
         <v>100100</v>
@@ -1519,12 +1826,17 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:7">
       <c r="A18" s="4">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>10010014</v>
       </c>
       <c r="B18" s="4">
         <v>100100</v>
@@ -1536,12 +1848,17 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:5">
+        <v>37</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:7">
       <c r="A19" s="4">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>10010015</v>
       </c>
       <c r="B19" s="4">
         <v>100100</v>
@@ -1553,12 +1870,17 @@
         <v>2</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:5">
+        <v>39</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:7">
       <c r="A20" s="4">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>10010016</v>
       </c>
       <c r="B20" s="4">
         <v>100100</v>
@@ -1570,12 +1892,17 @@
         <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:5">
+        <v>41</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:7">
       <c r="A21" s="4">
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>10010017</v>
       </c>
       <c r="B21" s="4">
         <v>100100</v>
@@ -1587,12 +1914,17 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:5">
+        <v>43</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:7">
       <c r="A22" s="4">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>10010018</v>
       </c>
       <c r="B22" s="4">
         <v>100100</v>
@@ -1604,12 +1936,17 @@
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:5">
+        <v>45</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:7">
       <c r="A23" s="4">
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>10010019</v>
       </c>
       <c r="B23" s="4">
         <v>100100</v>
@@ -1621,12 +1958,17 @@
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:5">
+        <v>47</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:7">
       <c r="A24" s="4">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>10010020</v>
       </c>
       <c r="B24" s="4">
         <v>100100</v>
@@ -1638,12 +1980,17 @@
         <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:5">
+        <v>49</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:7">
       <c r="A25" s="4">
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>10010021</v>
       </c>
       <c r="B25" s="4">
         <v>100100</v>
@@ -1655,12 +2002,17 @@
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:5">
+        <v>51</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:7">
       <c r="A26" s="4">
-        <v>22</v>
+        <f t="shared" si="0"/>
+        <v>10010022</v>
       </c>
       <c r="B26" s="4">
         <v>100100</v>
@@ -1672,12 +2024,747 @@
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>29</v>
+        <v>53</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:7">
+      <c r="A27" s="6">
+        <f t="shared" si="0"/>
+        <v>10010028</v>
+      </c>
+      <c r="B27" s="6">
+        <v>100100</v>
+      </c>
+      <c r="C27" s="7">
+        <v>28</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:7">
+      <c r="A28" s="6">
+        <f t="shared" si="0"/>
+        <v>10010030</v>
+      </c>
+      <c r="B28" s="6">
+        <v>100100</v>
+      </c>
+      <c r="C28" s="7">
+        <v>30</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:7">
+      <c r="A29" s="8">
+        <f t="shared" ref="A29:A46" si="1">B29*100+C29</f>
+        <v>10070001</v>
+      </c>
+      <c r="B29" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C29" s="9">
+        <v>1</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:7">
+      <c r="A30" s="8">
+        <f t="shared" si="1"/>
+        <v>10070002</v>
+      </c>
+      <c r="B30" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C30" s="9">
+        <v>2</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:7">
+      <c r="A31" s="8">
+        <f t="shared" si="1"/>
+        <v>10070003</v>
+      </c>
+      <c r="B31" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C31" s="9">
+        <v>3</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:7">
+      <c r="A32" s="8">
+        <f t="shared" si="1"/>
+        <v>10070004</v>
+      </c>
+      <c r="B32" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C32" s="9">
+        <v>4</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:7">
+      <c r="A33" s="8">
+        <f t="shared" si="1"/>
+        <v>10070005</v>
+      </c>
+      <c r="B33" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C33" s="9">
+        <v>5</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:7">
+      <c r="A34" s="8">
+        <f t="shared" si="1"/>
+        <v>10070006</v>
+      </c>
+      <c r="B34" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C34" s="9">
+        <v>6</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:7">
+      <c r="A35" s="8">
+        <f t="shared" si="1"/>
+        <v>10070007</v>
+      </c>
+      <c r="B35" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C35" s="9">
+        <v>7</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:7">
+      <c r="A36" s="8">
+        <f t="shared" si="1"/>
+        <v>10070008</v>
+      </c>
+      <c r="B36" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C36" s="9">
+        <v>8</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:7">
+      <c r="A37" s="8">
+        <f t="shared" si="1"/>
+        <v>10070009</v>
+      </c>
+      <c r="B37" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C37" s="9">
+        <v>9</v>
+      </c>
+      <c r="D37" s="9">
+        <v>1</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:7">
+      <c r="A38" s="8">
+        <f t="shared" si="1"/>
+        <v>10070010</v>
+      </c>
+      <c r="B38" s="8">
+        <v>100700</v>
+      </c>
+      <c r="C38" s="9">
+        <v>10</v>
+      </c>
+      <c r="D38" s="9">
+        <v>2</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:7">
+      <c r="A39" s="10">
+        <f t="shared" si="1"/>
+        <v>10070011</v>
+      </c>
+      <c r="B39" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C39" s="11">
+        <v>11</v>
+      </c>
+      <c r="D39" s="11">
+        <v>0</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F39" s="9">
+        <v>9</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:7">
+      <c r="A40" s="10">
+        <f t="shared" si="1"/>
+        <v>10070012</v>
+      </c>
+      <c r="B40" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C40" s="11">
+        <v>12</v>
+      </c>
+      <c r="D40" s="11">
+        <v>0</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" s="9">
+        <v>9</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:7">
+      <c r="A41" s="10">
+        <f t="shared" si="1"/>
+        <v>10070013</v>
+      </c>
+      <c r="B41" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C41" s="11">
+        <v>13</v>
+      </c>
+      <c r="D41" s="11">
+        <v>0</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="9">
+        <v>9</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:7">
+      <c r="A42" s="10">
+        <f t="shared" si="1"/>
+        <v>10070014</v>
+      </c>
+      <c r="B42" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C42" s="11">
+        <v>14</v>
+      </c>
+      <c r="D42" s="11">
+        <v>0</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="9">
+        <v>9</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:7">
+      <c r="A43" s="10">
+        <f t="shared" si="1"/>
+        <v>10070015</v>
+      </c>
+      <c r="B43" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C43" s="11">
+        <v>15</v>
+      </c>
+      <c r="D43" s="11">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F43" s="9">
+        <v>9</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:7">
+      <c r="A44" s="10">
+        <f t="shared" si="1"/>
+        <v>10070016</v>
+      </c>
+      <c r="B44" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C44" s="11">
+        <v>16</v>
+      </c>
+      <c r="D44" s="11">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" s="9">
+        <v>9</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:7">
+      <c r="A45" s="10">
+        <f t="shared" si="1"/>
+        <v>10070017</v>
+      </c>
+      <c r="B45" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C45" s="11">
+        <v>17</v>
+      </c>
+      <c r="D45" s="11">
+        <v>0</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="9">
+        <v>9</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:7">
+      <c r="A46" s="10">
+        <f t="shared" si="1"/>
+        <v>10070018</v>
+      </c>
+      <c r="B46" s="10">
+        <v>100700</v>
+      </c>
+      <c r="C46" s="11">
+        <v>18</v>
+      </c>
+      <c r="D46" s="11">
+        <v>0</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F46" s="9">
+        <v>9</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:7">
+      <c r="A47" s="12">
+        <f t="shared" ref="A47:A59" si="2">B47*100+C47</f>
+        <v>10140001</v>
+      </c>
+      <c r="B47" s="12">
+        <v>101400</v>
+      </c>
+      <c r="C47" s="13">
+        <v>1</v>
+      </c>
+      <c r="D47" s="13">
+        <v>0</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:7">
+      <c r="A48" s="12">
+        <f t="shared" si="2"/>
+        <v>10140102</v>
+      </c>
+      <c r="B48" s="12">
+        <v>101401</v>
+      </c>
+      <c r="C48" s="13">
+        <v>2</v>
+      </c>
+      <c r="D48" s="13">
+        <v>0</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:7">
+      <c r="A49" s="12">
+        <f t="shared" si="2"/>
+        <v>10140203</v>
+      </c>
+      <c r="B49" s="12">
+        <v>101402</v>
+      </c>
+      <c r="C49" s="13">
+        <v>3</v>
+      </c>
+      <c r="D49" s="13">
+        <v>0</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:7">
+      <c r="A50" s="12">
+        <f t="shared" si="2"/>
+        <v>10140304</v>
+      </c>
+      <c r="B50" s="12">
+        <v>101403</v>
+      </c>
+      <c r="C50" s="13">
+        <v>4</v>
+      </c>
+      <c r="D50" s="13">
+        <v>0</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:7">
+      <c r="A51" s="12">
+        <f t="shared" si="2"/>
+        <v>10140405</v>
+      </c>
+      <c r="B51" s="12">
+        <v>101404</v>
+      </c>
+      <c r="C51" s="13">
+        <v>5</v>
+      </c>
+      <c r="D51" s="13">
+        <v>0</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:7">
+      <c r="A52" s="12">
+        <f t="shared" si="2"/>
+        <v>10140506</v>
+      </c>
+      <c r="B52" s="12">
+        <v>101405</v>
+      </c>
+      <c r="C52" s="13">
+        <v>6</v>
+      </c>
+      <c r="D52" s="13">
+        <v>0</v>
+      </c>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:7">
+      <c r="A53" s="12">
+        <f t="shared" si="2"/>
+        <v>10140607</v>
+      </c>
+      <c r="B53" s="12">
+        <v>101406</v>
+      </c>
+      <c r="C53" s="13">
+        <v>7</v>
+      </c>
+      <c r="D53" s="13">
+        <v>0</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:7">
+      <c r="A54" s="12">
+        <f t="shared" si="2"/>
+        <v>10140708</v>
+      </c>
+      <c r="B54" s="12">
+        <v>101407</v>
+      </c>
+      <c r="C54" s="13">
+        <v>8</v>
+      </c>
+      <c r="D54" s="13">
+        <v>0</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:7">
+      <c r="A55" s="12">
+        <f t="shared" si="2"/>
+        <v>10140809</v>
+      </c>
+      <c r="B55" s="12">
+        <v>101408</v>
+      </c>
+      <c r="C55" s="13">
+        <v>9</v>
+      </c>
+      <c r="D55" s="13">
+        <v>0</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:7">
+      <c r="A56" s="12">
+        <f t="shared" si="2"/>
+        <v>10140910</v>
+      </c>
+      <c r="B56" s="12">
+        <v>101409</v>
+      </c>
+      <c r="C56" s="13">
+        <v>10</v>
+      </c>
+      <c r="D56" s="13">
+        <v>0</v>
+      </c>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:7">
+      <c r="A57" s="12">
+        <f t="shared" si="2"/>
+        <v>10141011</v>
+      </c>
+      <c r="B57" s="12">
+        <v>101410</v>
+      </c>
+      <c r="C57" s="13">
+        <v>11</v>
+      </c>
+      <c r="D57" s="13">
+        <v>0</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:7">
+      <c r="A58" s="12">
+        <f t="shared" si="2"/>
+        <v>10141112</v>
+      </c>
+      <c r="B58" s="12">
+        <v>101411</v>
+      </c>
+      <c r="C58" s="13">
+        <v>12</v>
+      </c>
+      <c r="D58" s="13">
+        <v>1</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:7">
+      <c r="A59" s="12">
+        <f t="shared" si="2"/>
+        <v>10141213</v>
+      </c>
+      <c r="B59" s="12">
+        <v>101412</v>
+      </c>
+      <c r="C59" s="13">
+        <v>13</v>
+      </c>
+      <c r="D59" s="13">
+        <v>2</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:E4">
+  <conditionalFormatting sqref="F2">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B2,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
     <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD($B3,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:D4 G1:G4">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>MOD($B1,2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:F1 E2:E3 E4:F4">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
   <si>
     <t>图标</t>
   </si>
@@ -285,6 +285,39 @@
     <t>隐藏图案，常规不出现，用于触发免费</t>
   </si>
   <si>
+    <t>BAR</t>
+  </si>
+  <si>
+    <t>BAR×2</t>
+  </si>
+  <si>
+    <t>BAR×3</t>
+  </si>
+  <si>
+    <t>7图案</t>
+  </si>
+  <si>
+    <t>樱桃</t>
+  </si>
+  <si>
+    <t>Wild</t>
+  </si>
+  <si>
+    <t>Wild-MINI</t>
+  </si>
+  <si>
+    <t>Wild-MINOR</t>
+  </si>
+  <si>
+    <t>Wild-MAJOR</t>
+  </si>
+  <si>
+    <t>Wild-GRAND</t>
+  </si>
+  <si>
+    <t>空元素</t>
+  </si>
+  <si>
     <t>mjhl_zjm_mj_16.png</t>
   </si>
   <si>
@@ -334,9 +367,6 @@
   </si>
   <si>
     <t>mjhl_zjm_wild.png</t>
-  </si>
-  <si>
-    <t>Wild</t>
   </si>
   <si>
     <t>mjhl_zjm_hu.png</t>
@@ -592,8 +622,8 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -605,8 +635,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -616,7 +646,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -626,6 +656,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -981,7 +1017,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1005,16 +1041,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1023,89 +1059,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1136,6 +1172,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -1146,6 +1185,12 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1468,10 +1513,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="10.375"/>
+    <col min="1" max="2" width="12.625"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
     <col min="5" max="6" width="21.8" customWidth="1"/>
     <col min="7" max="7" width="24.1666666666667" customWidth="1"/>
@@ -1571,7 +1616,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:7">
       <c r="A6" s="4">
-        <f t="shared" ref="A6:A28" si="0">B6*100+C6</f>
+        <f t="shared" ref="A6:A30" si="0">B6*100+C6</f>
         <v>10010002</v>
       </c>
       <c r="B6" s="4">
@@ -2077,11 +2122,11 @@
     </row>
     <row r="29" ht="16.5" spans="1:7">
       <c r="A29" s="8">
-        <f t="shared" ref="A29:A46" si="1">B29*100+C29</f>
-        <v>10070001</v>
+        <f t="shared" si="0"/>
+        <v>10030001</v>
       </c>
       <c r="B29" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C29" s="9">
         <v>1</v>
@@ -2089,21 +2134,19 @@
       <c r="D29" s="9">
         <v>0</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="10"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:7">
       <c r="A30" s="8">
-        <f t="shared" si="1"/>
-        <v>10070002</v>
+        <f t="shared" si="0"/>
+        <v>10030002</v>
       </c>
       <c r="B30" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C30" s="9">
         <v>2</v>
@@ -2111,21 +2154,19 @@
       <c r="D30" s="9">
         <v>0</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="9"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="8"/>
       <c r="G30" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:7">
       <c r="A31" s="8">
-        <f t="shared" si="1"/>
-        <v>10070003</v>
+        <f>B31*100+C31</f>
+        <v>10030003</v>
       </c>
       <c r="B31" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C31" s="9">
         <v>3</v>
@@ -2133,21 +2174,19 @@
       <c r="D31" s="9">
         <v>0</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="9"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="8"/>
       <c r="G31" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:7">
       <c r="A32" s="8">
-        <f t="shared" si="1"/>
-        <v>10070004</v>
+        <f>B32*100+C32</f>
+        <v>10030004</v>
       </c>
       <c r="B32" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C32" s="9">
         <v>4</v>
@@ -2155,21 +2194,19 @@
       <c r="D32" s="9">
         <v>0</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F32" s="9"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="8"/>
       <c r="G32" s="9" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:7">
       <c r="A33" s="8">
-        <f t="shared" si="1"/>
-        <v>10070005</v>
+        <f>B33*100+C33</f>
+        <v>10030005</v>
       </c>
       <c r="B33" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C33" s="9">
         <v>5</v>
@@ -2177,21 +2214,19 @@
       <c r="D33" s="9">
         <v>0</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="9"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="8"/>
       <c r="G33" s="9" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:7">
       <c r="A34" s="8">
-        <f t="shared" si="1"/>
-        <v>10070006</v>
+        <f>B34*100+C34</f>
+        <v>10030006</v>
       </c>
       <c r="B34" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C34" s="9">
         <v>6</v>
@@ -2199,65 +2234,59 @@
       <c r="D34" s="9">
         <v>0</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="9"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="8"/>
       <c r="G34" s="9" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:7">
       <c r="A35" s="8">
-        <f t="shared" si="1"/>
-        <v>10070007</v>
+        <f t="shared" ref="A35:A40" si="1">B35*100+C35</f>
+        <v>10030007</v>
       </c>
       <c r="B35" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C35" s="9">
         <v>7</v>
       </c>
       <c r="D35" s="9">
-        <v>0</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F35" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="E35" s="10"/>
+      <c r="F35" s="8"/>
       <c r="G35" s="9" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:7">
       <c r="A36" s="8">
         <f t="shared" si="1"/>
-        <v>10070008</v>
+        <v>10030008</v>
       </c>
       <c r="B36" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C36" s="9">
         <v>8</v>
       </c>
       <c r="D36" s="9">
-        <v>0</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F36" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="E36" s="10"/>
+      <c r="F36" s="8"/>
       <c r="G36" s="9" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:7">
       <c r="A37" s="8">
         <f t="shared" si="1"/>
-        <v>10070009</v>
+        <v>10030009</v>
       </c>
       <c r="B37" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C37" s="9">
         <v>9</v>
@@ -2265,486 +2294,742 @@
       <c r="D37" s="9">
         <v>1</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F37" s="9"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="8"/>
       <c r="G37" s="9" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:7">
       <c r="A38" s="8">
         <f t="shared" si="1"/>
-        <v>10070010</v>
+        <v>10030010</v>
       </c>
       <c r="B38" s="8">
-        <v>100700</v>
+        <v>100300</v>
       </c>
       <c r="C38" s="9">
         <v>10</v>
       </c>
       <c r="D38" s="9">
+        <v>1</v>
+      </c>
+      <c r="E38" s="10"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:7">
+      <c r="A39" s="8">
+        <f t="shared" si="1"/>
+        <v>10030011</v>
+      </c>
+      <c r="B39" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C39" s="9">
+        <v>11</v>
+      </c>
+      <c r="D39" s="9">
+        <v>1</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="16.5" spans="1:7">
+      <c r="A40" s="8">
+        <f t="shared" si="1"/>
+        <v>10030099</v>
+      </c>
+      <c r="B40" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C40" s="9">
+        <v>99</v>
+      </c>
+      <c r="D40" s="9">
+        <v>1</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:7">
+      <c r="A41" s="11">
+        <f t="shared" ref="A41:A58" si="2">B41*100+C41</f>
+        <v>10070001</v>
+      </c>
+      <c r="B41" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C41" s="12">
+        <v>1</v>
+      </c>
+      <c r="D41" s="12">
+        <v>0</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:7">
+      <c r="A42" s="11">
+        <f t="shared" si="2"/>
+        <v>10070002</v>
+      </c>
+      <c r="B42" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C42" s="12">
         <v>2</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="D42" s="12">
+        <v>0</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:7">
+      <c r="A43" s="11">
+        <f t="shared" si="2"/>
+        <v>10070003</v>
+      </c>
+      <c r="B43" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C43" s="12">
+        <v>3</v>
+      </c>
+      <c r="D43" s="12">
+        <v>0</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:7">
+      <c r="A44" s="11">
+        <f t="shared" si="2"/>
+        <v>10070004</v>
+      </c>
+      <c r="B44" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C44" s="12">
+        <v>4</v>
+      </c>
+      <c r="D44" s="12">
+        <v>0</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9" t="s">
+    </row>
+    <row r="45" ht="16.5" spans="1:7">
+      <c r="A45" s="11">
+        <f t="shared" si="2"/>
+        <v>10070005</v>
+      </c>
+      <c r="B45" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C45" s="12">
+        <v>5</v>
+      </c>
+      <c r="D45" s="12">
+        <v>0</v>
+      </c>
+      <c r="E45" s="12" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:7">
-      <c r="A39" s="10">
-        <f t="shared" si="1"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:7">
+      <c r="A46" s="11">
+        <f t="shared" si="2"/>
+        <v>10070006</v>
+      </c>
+      <c r="B46" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C46" s="12">
+        <v>6</v>
+      </c>
+      <c r="D46" s="12">
+        <v>0</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:7">
+      <c r="A47" s="11">
+        <f t="shared" si="2"/>
+        <v>10070007</v>
+      </c>
+      <c r="B47" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C47" s="12">
+        <v>7</v>
+      </c>
+      <c r="D47" s="12">
+        <v>0</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:7">
+      <c r="A48" s="11">
+        <f t="shared" si="2"/>
+        <v>10070008</v>
+      </c>
+      <c r="B48" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C48" s="12">
+        <v>8</v>
+      </c>
+      <c r="D48" s="12">
+        <v>0</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:7">
+      <c r="A49" s="11">
+        <f t="shared" si="2"/>
+        <v>10070009</v>
+      </c>
+      <c r="B49" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C49" s="12">
+        <v>9</v>
+      </c>
+      <c r="D49" s="12">
+        <v>1</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:7">
+      <c r="A50" s="11">
+        <f t="shared" si="2"/>
+        <v>10070010</v>
+      </c>
+      <c r="B50" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C50" s="12">
+        <v>10</v>
+      </c>
+      <c r="D50" s="12">
+        <v>2</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:7">
+      <c r="A51" s="13">
+        <f t="shared" si="2"/>
         <v>10070011</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B51" s="13">
         <v>100700</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C51" s="14">
         <v>11</v>
       </c>
-      <c r="D39" s="11">
-        <v>0</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F39" s="9">
+      <c r="D51" s="14">
+        <v>0</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F51" s="12">
         <v>9</v>
       </c>
-      <c r="G39" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:7">
-      <c r="A40" s="10">
-        <f t="shared" si="1"/>
+      <c r="G51" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:7">
+      <c r="A52" s="13">
+        <f t="shared" si="2"/>
         <v>10070012</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B52" s="13">
         <v>100700</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C52" s="14">
         <v>12</v>
       </c>
-      <c r="D40" s="11">
-        <v>0</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F40" s="9">
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="F52" s="12">
         <v>9</v>
       </c>
-      <c r="G40" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:7">
-      <c r="A41" s="10">
-        <f t="shared" si="1"/>
+      <c r="G52" s="14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:7">
+      <c r="A53" s="13">
+        <f t="shared" si="2"/>
         <v>10070013</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B53" s="13">
         <v>100700</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C53" s="14">
         <v>13</v>
       </c>
-      <c r="D41" s="11">
-        <v>0</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F41" s="9">
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53" s="12">
         <v>9</v>
       </c>
-      <c r="G41" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:7">
-      <c r="A42" s="10">
-        <f t="shared" si="1"/>
+      <c r="G53" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:7">
+      <c r="A54" s="13">
+        <f t="shared" si="2"/>
         <v>10070014</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B54" s="13">
         <v>100700</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C54" s="14">
         <v>14</v>
       </c>
-      <c r="D42" s="11">
-        <v>0</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F42" s="9">
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" s="12">
         <v>9</v>
       </c>
-      <c r="G42" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:7">
-      <c r="A43" s="10">
-        <f t="shared" si="1"/>
+      <c r="G54" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:7">
+      <c r="A55" s="13">
+        <f t="shared" si="2"/>
         <v>10070015</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B55" s="13">
         <v>100700</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C55" s="14">
         <v>15</v>
       </c>
-      <c r="D43" s="11">
-        <v>0</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="F43" s="9">
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="12">
         <v>9</v>
       </c>
-      <c r="G43" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:7">
-      <c r="A44" s="10">
-        <f t="shared" si="1"/>
+      <c r="G55" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:7">
+      <c r="A56" s="13">
+        <f t="shared" si="2"/>
         <v>10070016</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B56" s="13">
         <v>100700</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C56" s="14">
         <v>16</v>
       </c>
-      <c r="D44" s="11">
-        <v>0</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F44" s="9">
+      <c r="D56" s="14">
+        <v>0</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F56" s="12">
         <v>9</v>
       </c>
-      <c r="G44" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:7">
-      <c r="A45" s="10">
-        <f t="shared" si="1"/>
+      <c r="G56" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:7">
+      <c r="A57" s="13">
+        <f t="shared" si="2"/>
         <v>10070017</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B57" s="13">
         <v>100700</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C57" s="14">
         <v>17</v>
       </c>
-      <c r="D45" s="11">
-        <v>0</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F45" s="9">
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F57" s="12">
         <v>9</v>
       </c>
-      <c r="G45" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:7">
-      <c r="A46" s="10">
-        <f t="shared" si="1"/>
+      <c r="G57" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:7">
+      <c r="A58" s="13">
+        <f t="shared" si="2"/>
         <v>10070018</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B58" s="13">
         <v>100700</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C58" s="14">
         <v>18</v>
       </c>
-      <c r="D46" s="11">
-        <v>0</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F46" s="9">
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F58" s="12">
         <v>9</v>
       </c>
-      <c r="G46" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:7">
-      <c r="A47" s="12">
-        <f t="shared" ref="A47:A59" si="2">B47*100+C47</f>
+      <c r="G58" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:7">
+      <c r="A59" s="15">
+        <f t="shared" ref="A59:A71" si="3">B59*100+C59</f>
         <v>10140001</v>
       </c>
-      <c r="B47" s="12">
+      <c r="B59" s="15">
         <v>101400</v>
       </c>
-      <c r="C47" s="13">
+      <c r="C59" s="16">
         <v>1</v>
       </c>
-      <c r="D47" s="13">
-        <v>0</v>
-      </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:7">
-      <c r="A48" s="12">
-        <f t="shared" si="2"/>
+      <c r="D59" s="16">
+        <v>0</v>
+      </c>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:7">
+      <c r="A60" s="15">
+        <f t="shared" si="3"/>
         <v>10140102</v>
       </c>
-      <c r="B48" s="12">
+      <c r="B60" s="15">
         <v>101401</v>
       </c>
-      <c r="C48" s="13">
+      <c r="C60" s="16">
         <v>2</v>
       </c>
-      <c r="D48" s="13">
-        <v>0</v>
-      </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13">
+      <c r="D60" s="16">
+        <v>0</v>
+      </c>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16">
         <v>9</v>
       </c>
     </row>
-    <row r="49" ht="16.5" spans="1:7">
-      <c r="A49" s="12">
-        <f t="shared" si="2"/>
+    <row r="61" ht="16.5" spans="1:7">
+      <c r="A61" s="15">
+        <f t="shared" si="3"/>
         <v>10140203</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B61" s="15">
         <v>101402</v>
       </c>
-      <c r="C49" s="13">
+      <c r="C61" s="16">
         <v>3</v>
       </c>
-      <c r="D49" s="13">
-        <v>0</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13">
+      <c r="D61" s="16">
+        <v>0</v>
+      </c>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16">
         <v>10</v>
       </c>
     </row>
-    <row r="50" ht="16.5" spans="1:7">
-      <c r="A50" s="12">
-        <f t="shared" si="2"/>
+    <row r="62" ht="16.5" spans="1:7">
+      <c r="A62" s="15">
+        <f t="shared" si="3"/>
         <v>10140304</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B62" s="15">
         <v>101403</v>
       </c>
-      <c r="C50" s="13">
+      <c r="C62" s="16">
         <v>4</v>
       </c>
-      <c r="D50" s="13">
-        <v>0</v>
-      </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13" t="s">
+      <c r="D62" s="16">
+        <v>0</v>
+      </c>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="51" ht="16.5" spans="1:7">
-      <c r="A51" s="12">
-        <f t="shared" si="2"/>
+    <row r="63" ht="16.5" spans="1:7">
+      <c r="A63" s="15">
+        <f t="shared" si="3"/>
         <v>10140405</v>
       </c>
-      <c r="B51" s="12">
+      <c r="B63" s="15">
         <v>101404</v>
       </c>
-      <c r="C51" s="13">
+      <c r="C63" s="16">
         <v>5</v>
       </c>
-      <c r="D51" s="13">
-        <v>0</v>
-      </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13" t="s">
+      <c r="D63" s="16">
+        <v>0</v>
+      </c>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="52" ht="16.5" spans="1:7">
-      <c r="A52" s="12">
-        <f t="shared" si="2"/>
+    <row r="64" ht="16.5" spans="1:7">
+      <c r="A64" s="15">
+        <f t="shared" si="3"/>
         <v>10140506</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B64" s="15">
         <v>101405</v>
       </c>
-      <c r="C52" s="13">
+      <c r="C64" s="16">
         <v>6</v>
       </c>
-      <c r="D52" s="13">
-        <v>0</v>
-      </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13" t="s">
+      <c r="D64" s="16">
+        <v>0</v>
+      </c>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="53" ht="16.5" spans="1:7">
-      <c r="A53" s="12">
-        <f t="shared" si="2"/>
+    <row r="65" ht="16.5" spans="1:7">
+      <c r="A65" s="15">
+        <f t="shared" si="3"/>
         <v>10140607</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B65" s="15">
         <v>101406</v>
       </c>
-      <c r="C53" s="13">
+      <c r="C65" s="16">
         <v>7</v>
       </c>
-      <c r="D53" s="13">
-        <v>0</v>
-      </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13" t="s">
+      <c r="D65" s="16">
+        <v>0</v>
+      </c>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="54" ht="16.5" spans="1:7">
-      <c r="A54" s="12">
-        <f t="shared" si="2"/>
+    <row r="66" ht="16.5" spans="1:7">
+      <c r="A66" s="15">
+        <f t="shared" si="3"/>
         <v>10140708</v>
       </c>
-      <c r="B54" s="12">
+      <c r="B66" s="15">
         <v>101407</v>
       </c>
-      <c r="C54" s="13">
+      <c r="C66" s="16">
         <v>8</v>
       </c>
-      <c r="D54" s="13">
-        <v>0</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:7">
-      <c r="A55" s="12">
-        <f t="shared" si="2"/>
+      <c r="D66" s="16">
+        <v>0</v>
+      </c>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:7">
+      <c r="A67" s="15">
+        <f t="shared" si="3"/>
         <v>10140809</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B67" s="15">
         <v>101408</v>
       </c>
-      <c r="C55" s="13">
+      <c r="C67" s="16">
         <v>9</v>
       </c>
-      <c r="D55" s="13">
-        <v>0</v>
-      </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:7">
-      <c r="A56" s="12">
-        <f t="shared" si="2"/>
+      <c r="D67" s="16">
+        <v>0</v>
+      </c>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:7">
+      <c r="A68" s="15">
+        <f t="shared" si="3"/>
         <v>10140910</v>
       </c>
-      <c r="B56" s="12">
+      <c r="B68" s="15">
         <v>101409</v>
       </c>
-      <c r="C56" s="13">
+      <c r="C68" s="16">
         <v>10</v>
       </c>
-      <c r="D56" s="13">
-        <v>0</v>
-      </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="57" ht="16.5" spans="1:7">
-      <c r="A57" s="12">
-        <f t="shared" si="2"/>
+      <c r="D68" s="16">
+        <v>0</v>
+      </c>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:7">
+      <c r="A69" s="15">
+        <f t="shared" si="3"/>
         <v>10141011</v>
       </c>
-      <c r="B57" s="12">
+      <c r="B69" s="15">
         <v>101410</v>
       </c>
-      <c r="C57" s="13">
+      <c r="C69" s="16">
         <v>11</v>
       </c>
-      <c r="D57" s="13">
-        <v>0</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" ht="16.5" spans="1:7">
-      <c r="A58" s="12">
-        <f t="shared" si="2"/>
+      <c r="D69" s="16">
+        <v>0</v>
+      </c>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" spans="1:7">
+      <c r="A70" s="15">
+        <f t="shared" si="3"/>
         <v>10141112</v>
       </c>
-      <c r="B58" s="12">
+      <c r="B70" s="15">
         <v>101411</v>
       </c>
-      <c r="C58" s="13">
+      <c r="C70" s="16">
         <v>12</v>
       </c>
-      <c r="D58" s="13">
+      <c r="D70" s="16">
         <v>1</v>
       </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" ht="16.5" spans="1:7">
-      <c r="A59" s="12">
-        <f t="shared" si="2"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:7">
+      <c r="A71" s="15">
+        <f t="shared" si="3"/>
         <v>10141213</v>
       </c>
-      <c r="B59" s="12">
+      <c r="B71" s="15">
         <v>101412</v>
       </c>
-      <c r="C59" s="13">
+      <c r="C71" s="16">
         <v>13</v>
       </c>
-      <c r="D59" s="13">
+      <c r="D71" s="16">
         <v>2</v>
       </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13" t="s">
-        <v>98</v>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="119">
   <si>
     <t>图标</t>
   </si>
@@ -300,75 +300,78 @@
     <t>樱桃</t>
   </si>
   <si>
+    <t>Wild-倍率</t>
+  </si>
+  <si>
+    <t>Wild-MINI</t>
+  </si>
+  <si>
+    <t>Wild-MINOR</t>
+  </si>
+  <si>
+    <t>Wild-MAJOR</t>
+  </si>
+  <si>
+    <t>Wild-GRAND</t>
+  </si>
+  <si>
+    <t>空元素</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_16.png</t>
+  </si>
+  <si>
+    <t>2条</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_12.png</t>
+  </si>
+  <si>
+    <t>2筒</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_14.png</t>
+  </si>
+  <si>
+    <t>5条</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_10.png</t>
+  </si>
+  <si>
+    <t>5筒</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_8.png</t>
+  </si>
+  <si>
+    <t>八万</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_6.png</t>
+  </si>
+  <si>
+    <t>白板</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_2.png</t>
+  </si>
+  <si>
+    <t>红中</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_4.png</t>
+  </si>
+  <si>
+    <t>发财</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_wild.png</t>
+  </si>
+  <si>
     <t>Wild</t>
   </si>
   <si>
-    <t>Wild-MINI</t>
-  </si>
-  <si>
-    <t>Wild-MINOR</t>
-  </si>
-  <si>
-    <t>Wild-MAJOR</t>
-  </si>
-  <si>
-    <t>Wild-GRAND</t>
-  </si>
-  <si>
-    <t>空元素</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_16.png</t>
-  </si>
-  <si>
-    <t>2条</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_12.png</t>
-  </si>
-  <si>
-    <t>2筒</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_14.png</t>
-  </si>
-  <si>
-    <t>5条</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_10.png</t>
-  </si>
-  <si>
-    <t>5筒</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_8.png</t>
-  </si>
-  <si>
-    <t>八万</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_6.png</t>
-  </si>
-  <si>
-    <t>白板</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_2.png</t>
-  </si>
-  <si>
-    <t>红中</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_4.png</t>
-  </si>
-  <si>
-    <t>发财</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_wild.png</t>
-  </si>
-  <si>
     <t>mjhl_zjm_hu.png</t>
   </si>
   <si>
@@ -421,6 +424,33 @@
   </si>
   <si>
     <t>黄金_发财|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>彩球</t>
+  </si>
+  <si>
+    <t>爆竹</t>
+  </si>
+  <si>
+    <t>舞狮</t>
+  </si>
+  <si>
+    <t>铜钱</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>摇钱树</t>
+  </si>
+  <si>
+    <t>横财神</t>
+  </si>
+  <si>
+    <t>正财神</t>
+  </si>
+  <si>
+    <t>财神jackpot</t>
   </si>
   <si>
     <t>空格</t>
@@ -622,8 +652,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -635,8 +665,8 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1513,12 +1543,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
-    <col min="5" max="6" width="21.8" customWidth="1"/>
+    <col min="5" max="5" width="18.7416666666667" customWidth="1"/>
+    <col min="6" max="6" width="19.1666666666667" customWidth="1"/>
     <col min="7" max="7" width="24.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1616,7 +1647,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:7">
       <c r="A6" s="4">
-        <f t="shared" ref="A6:A30" si="0">B6*100+C6</f>
+        <f t="shared" ref="A6:A34" si="0">B6*100+C6</f>
         <v>10010002</v>
       </c>
       <c r="B6" s="4">
@@ -2162,7 +2193,7 @@
     </row>
     <row r="31" ht="16.5" spans="1:7">
       <c r="A31" s="8">
-        <f>B31*100+C31</f>
+        <f t="shared" si="0"/>
         <v>10030003</v>
       </c>
       <c r="B31" s="8">
@@ -2182,7 +2213,7 @@
     </row>
     <row r="32" ht="16.5" spans="1:7">
       <c r="A32" s="8">
-        <f>B32*100+C32</f>
+        <f t="shared" si="0"/>
         <v>10030004</v>
       </c>
       <c r="B32" s="8">
@@ -2202,7 +2233,7 @@
     </row>
     <row r="33" ht="16.5" spans="1:7">
       <c r="A33" s="8">
-        <f>B33*100+C33</f>
+        <f t="shared" si="0"/>
         <v>10030005</v>
       </c>
       <c r="B33" s="8">
@@ -2222,7 +2253,7 @@
     </row>
     <row r="34" ht="16.5" spans="1:7">
       <c r="A34" s="8">
-        <f>B34*100+C34</f>
+        <f t="shared" si="0"/>
         <v>10030006</v>
       </c>
       <c r="B34" s="8">
@@ -2362,7 +2393,7 @@
     </row>
     <row r="41" ht="16.5" spans="1:7">
       <c r="A41" s="11">
-        <f t="shared" ref="A41:A58" si="2">B41*100+C41</f>
+        <f t="shared" ref="A41:A70" si="2">B41*100+C41</f>
         <v>10070001</v>
       </c>
       <c r="B41" s="11">
@@ -2555,7 +2586,7 @@
       </c>
       <c r="F49" s="12"/>
       <c r="G49" s="12" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:7">
@@ -2573,11 +2604,11 @@
         <v>2</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" ht="16.5" spans="1:7">
@@ -2595,13 +2626,13 @@
         <v>0</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F51" s="12">
         <v>9</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" ht="16.5" spans="1:7">
@@ -2619,13 +2650,13 @@
         <v>0</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F52" s="12">
         <v>9</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:7">
@@ -2643,13 +2674,13 @@
         <v>0</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F53" s="12">
         <v>9</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:7">
@@ -2667,13 +2698,13 @@
         <v>0</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F54" s="12">
         <v>9</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:7">
@@ -2691,13 +2722,13 @@
         <v>0</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F55" s="12">
         <v>9</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:7">
@@ -2715,13 +2746,13 @@
         <v>0</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F56" s="12">
         <v>9</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:7">
@@ -2739,13 +2770,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F57" s="12">
         <v>9</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:7">
@@ -2763,225 +2794,225 @@
         <v>0</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F58" s="12">
         <v>9</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:7">
-      <c r="A59" s="15">
-        <f t="shared" ref="A59:A71" si="3">B59*100+C59</f>
-        <v>10140001</v>
-      </c>
-      <c r="B59" s="15">
-        <v>101400</v>
-      </c>
-      <c r="C59" s="16">
+      <c r="A59" s="8">
+        <f t="shared" si="2"/>
+        <v>10120001</v>
+      </c>
+      <c r="B59" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C59" s="9">
         <v>1</v>
       </c>
-      <c r="D59" s="16">
-        <v>0</v>
-      </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16" t="s">
-        <v>103</v>
+      <c r="D59" s="9">
+        <v>0</v>
+      </c>
+      <c r="E59" s="10"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:7">
-      <c r="A60" s="15">
-        <f t="shared" si="3"/>
-        <v>10140102</v>
-      </c>
-      <c r="B60" s="15">
-        <v>101401</v>
-      </c>
-      <c r="C60" s="16">
+      <c r="A60" s="8">
+        <f t="shared" si="2"/>
+        <v>10120002</v>
+      </c>
+      <c r="B60" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C60" s="9">
         <v>2</v>
       </c>
-      <c r="D60" s="16">
-        <v>0</v>
-      </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16">
+      <c r="D60" s="9">
+        <v>0</v>
+      </c>
+      <c r="E60" s="10"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:7">
+      <c r="A61" s="8">
+        <f t="shared" si="2"/>
+        <v>10120003</v>
+      </c>
+      <c r="B61" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C61" s="9">
+        <v>3</v>
+      </c>
+      <c r="D61" s="9">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:7">
+      <c r="A62" s="8">
+        <f t="shared" si="2"/>
+        <v>10120004</v>
+      </c>
+      <c r="B62" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C62" s="9">
+        <v>4</v>
+      </c>
+      <c r="D62" s="9">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:7">
+      <c r="A63" s="8">
+        <f t="shared" si="2"/>
+        <v>10120005</v>
+      </c>
+      <c r="B63" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C63" s="9">
+        <v>5</v>
+      </c>
+      <c r="D63" s="9">
+        <v>0</v>
+      </c>
+      <c r="E63" s="10"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:7">
+      <c r="A64" s="8">
+        <f t="shared" si="2"/>
+        <v>10120006</v>
+      </c>
+      <c r="B64" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C64" s="9">
+        <v>6</v>
+      </c>
+      <c r="D64" s="9">
+        <v>0</v>
+      </c>
+      <c r="E64" s="10"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:7">
+      <c r="A65" s="8">
+        <f t="shared" si="2"/>
+        <v>10120007</v>
+      </c>
+      <c r="B65" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C65" s="9">
+        <v>7</v>
+      </c>
+      <c r="D65" s="9">
+        <v>1</v>
+      </c>
+      <c r="E65" s="10"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="1:7">
+      <c r="A66" s="8">
+        <f t="shared" si="2"/>
+        <v>10120008</v>
+      </c>
+      <c r="B66" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C66" s="9">
+        <v>8</v>
+      </c>
+      <c r="D66" s="9">
+        <v>1</v>
+      </c>
+      <c r="E66" s="10"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:7">
+      <c r="A67" s="8">
+        <f t="shared" si="2"/>
+        <v>10120009</v>
+      </c>
+      <c r="B67" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C67" s="9">
         <v>9</v>
       </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:7">
-      <c r="A61" s="15">
-        <f t="shared" si="3"/>
-        <v>10140203</v>
-      </c>
-      <c r="B61" s="15">
-        <v>101402</v>
-      </c>
-      <c r="C61" s="16">
-        <v>3</v>
-      </c>
-      <c r="D61" s="16">
-        <v>0</v>
-      </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16">
+      <c r="D67" s="9">
+        <v>1</v>
+      </c>
+      <c r="E67" s="10"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:7">
+      <c r="A68" s="8">
+        <f t="shared" si="2"/>
+        <v>10120010</v>
+      </c>
+      <c r="B68" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C68" s="9">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" ht="16.5" spans="1:7">
-      <c r="A62" s="15">
-        <f t="shared" si="3"/>
-        <v>10140304</v>
-      </c>
-      <c r="B62" s="15">
-        <v>101403</v>
-      </c>
-      <c r="C62" s="16">
-        <v>4</v>
-      </c>
-      <c r="D62" s="16">
-        <v>0</v>
-      </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:7">
-      <c r="A63" s="15">
-        <f t="shared" si="3"/>
-        <v>10140405</v>
-      </c>
-      <c r="B63" s="15">
-        <v>101404</v>
-      </c>
-      <c r="C63" s="16">
-        <v>5</v>
-      </c>
-      <c r="D63" s="16">
-        <v>0</v>
-      </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:7">
-      <c r="A64" s="15">
-        <f t="shared" si="3"/>
-        <v>10140506</v>
-      </c>
-      <c r="B64" s="15">
-        <v>101405</v>
-      </c>
-      <c r="C64" s="16">
-        <v>6</v>
-      </c>
-      <c r="D64" s="16">
-        <v>0</v>
-      </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:7">
-      <c r="A65" s="15">
-        <f t="shared" si="3"/>
-        <v>10140607</v>
-      </c>
-      <c r="B65" s="15">
-        <v>101406</v>
-      </c>
-      <c r="C65" s="16">
-        <v>7</v>
-      </c>
-      <c r="D65" s="16">
-        <v>0</v>
-      </c>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" ht="16.5" spans="1:7">
-      <c r="A66" s="15">
-        <f t="shared" si="3"/>
-        <v>10140708</v>
-      </c>
-      <c r="B66" s="15">
-        <v>101407</v>
-      </c>
-      <c r="C66" s="16">
-        <v>8</v>
-      </c>
-      <c r="D66" s="16">
-        <v>0</v>
-      </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:7">
-      <c r="A67" s="15">
-        <f t="shared" si="3"/>
-        <v>10140809</v>
-      </c>
-      <c r="B67" s="15">
-        <v>101408</v>
-      </c>
-      <c r="C67" s="16">
-        <v>9</v>
-      </c>
-      <c r="D67" s="16">
-        <v>0</v>
-      </c>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:7">
-      <c r="A68" s="15">
-        <f t="shared" si="3"/>
-        <v>10140910</v>
-      </c>
-      <c r="B68" s="15">
-        <v>101409</v>
-      </c>
-      <c r="C68" s="16">
-        <v>10</v>
-      </c>
-      <c r="D68" s="16">
-        <v>0</v>
-      </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16" t="s">
-        <v>106</v>
+      <c r="D68" s="9">
+        <v>1</v>
+      </c>
+      <c r="E68" s="10"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="9" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:7">
       <c r="A69" s="15">
-        <f t="shared" si="3"/>
-        <v>10141011</v>
+        <f t="shared" ref="A69:A81" si="3">B69*100+C69</f>
+        <v>10140001</v>
       </c>
       <c r="B69" s="15">
-        <v>101410</v>
+        <v>101400</v>
       </c>
       <c r="C69" s="16">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D69" s="16">
         <v>0</v>
@@ -2989,47 +3020,247 @@
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
       <c r="G69" s="16" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:7">
       <c r="A70" s="15">
         <f t="shared" si="3"/>
-        <v>10141112</v>
+        <v>10140102</v>
       </c>
       <c r="B70" s="15">
-        <v>101411</v>
+        <v>101401</v>
       </c>
       <c r="C70" s="16">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D70" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="16"/>
       <c r="F70" s="16"/>
-      <c r="G70" s="16" t="s">
-        <v>62</v>
+      <c r="G70" s="16">
+        <v>9</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:7">
       <c r="A71" s="15">
         <f t="shared" si="3"/>
-        <v>10141213</v>
+        <v>10140203</v>
       </c>
       <c r="B71" s="15">
-        <v>101412</v>
+        <v>101402</v>
       </c>
       <c r="C71" s="16">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D71" s="16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E71" s="16"/>
       <c r="F71" s="16"/>
-      <c r="G71" s="16" t="s">
-        <v>108</v>
+      <c r="G71" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:7">
+      <c r="A72" s="15">
+        <f t="shared" si="3"/>
+        <v>10140304</v>
+      </c>
+      <c r="B72" s="15">
+        <v>101403</v>
+      </c>
+      <c r="C72" s="16">
+        <v>4</v>
+      </c>
+      <c r="D72" s="16">
+        <v>0</v>
+      </c>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" spans="1:7">
+      <c r="A73" s="15">
+        <f t="shared" si="3"/>
+        <v>10140405</v>
+      </c>
+      <c r="B73" s="15">
+        <v>101404</v>
+      </c>
+      <c r="C73" s="16">
+        <v>5</v>
+      </c>
+      <c r="D73" s="16">
+        <v>0</v>
+      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:7">
+      <c r="A74" s="15">
+        <f t="shared" si="3"/>
+        <v>10140506</v>
+      </c>
+      <c r="B74" s="15">
+        <v>101405</v>
+      </c>
+      <c r="C74" s="16">
+        <v>6</v>
+      </c>
+      <c r="D74" s="16">
+        <v>0</v>
+      </c>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" spans="1:7">
+      <c r="A75" s="15">
+        <f t="shared" si="3"/>
+        <v>10140607</v>
+      </c>
+      <c r="B75" s="15">
+        <v>101406</v>
+      </c>
+      <c r="C75" s="16">
+        <v>7</v>
+      </c>
+      <c r="D75" s="16">
+        <v>0</v>
+      </c>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:7">
+      <c r="A76" s="15">
+        <f t="shared" si="3"/>
+        <v>10140708</v>
+      </c>
+      <c r="B76" s="15">
+        <v>101407</v>
+      </c>
+      <c r="C76" s="16">
+        <v>8</v>
+      </c>
+      <c r="D76" s="16">
+        <v>0</v>
+      </c>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:7">
+      <c r="A77" s="15">
+        <f t="shared" si="3"/>
+        <v>10140809</v>
+      </c>
+      <c r="B77" s="15">
+        <v>101408</v>
+      </c>
+      <c r="C77" s="16">
+        <v>9</v>
+      </c>
+      <c r="D77" s="16">
+        <v>0</v>
+      </c>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:7">
+      <c r="A78" s="15">
+        <f t="shared" si="3"/>
+        <v>10140910</v>
+      </c>
+      <c r="B78" s="15">
+        <v>101409</v>
+      </c>
+      <c r="C78" s="16">
+        <v>10</v>
+      </c>
+      <c r="D78" s="16">
+        <v>0</v>
+      </c>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:7">
+      <c r="A79" s="15">
+        <f t="shared" si="3"/>
+        <v>10141011</v>
+      </c>
+      <c r="B79" s="15">
+        <v>101410</v>
+      </c>
+      <c r="C79" s="16">
+        <v>11</v>
+      </c>
+      <c r="D79" s="16">
+        <v>0</v>
+      </c>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:7">
+      <c r="A80" s="15">
+        <f t="shared" si="3"/>
+        <v>10141112</v>
+      </c>
+      <c r="B80" s="15">
+        <v>101411</v>
+      </c>
+      <c r="C80" s="16">
+        <v>12</v>
+      </c>
+      <c r="D80" s="16">
+        <v>1</v>
+      </c>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:7">
+      <c r="A81" s="15">
+        <f t="shared" si="3"/>
+        <v>10141213</v>
+      </c>
+      <c r="B81" s="15">
+        <v>101412</v>
+      </c>
+      <c r="C81" s="16">
+        <v>13</v>
+      </c>
+      <c r="D81" s="16">
+        <v>2</v>
+      </c>
+      <c r="E81" s="16"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="16" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="118">
   <si>
     <t>图标</t>
   </si>
@@ -421,6 +421,33 @@
   </si>
   <si>
     <t>黄金_发财|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>彩球</t>
+  </si>
+  <si>
+    <t>爆竹</t>
+  </si>
+  <si>
+    <t>舞狮</t>
+  </si>
+  <si>
+    <t>铜钱</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>摇钱树</t>
+  </si>
+  <si>
+    <t>横财神</t>
+  </si>
+  <si>
+    <t>正财神</t>
+  </si>
+  <si>
+    <t>财神jackpot</t>
   </si>
   <si>
     <t>空格</t>
@@ -624,12 +651,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -637,6 +658,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1513,12 +1540,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
-    <col min="5" max="6" width="21.8" customWidth="1"/>
+    <col min="5" max="5" width="18.7416666666667" customWidth="1"/>
+    <col min="6" max="6" width="19.1666666666667" customWidth="1"/>
     <col min="7" max="7" width="24.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1616,7 +1644,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:7">
       <c r="A6" s="4">
-        <f t="shared" ref="A6:A30" si="0">B6*100+C6</f>
+        <f t="shared" ref="A6:A34" si="0">B6*100+C6</f>
         <v>10010002</v>
       </c>
       <c r="B6" s="4">
@@ -2162,7 +2190,7 @@
     </row>
     <row r="31" ht="16.5" spans="1:7">
       <c r="A31" s="8">
-        <f>B31*100+C31</f>
+        <f t="shared" si="0"/>
         <v>10030003</v>
       </c>
       <c r="B31" s="8">
@@ -2182,7 +2210,7 @@
     </row>
     <row r="32" ht="16.5" spans="1:7">
       <c r="A32" s="8">
-        <f>B32*100+C32</f>
+        <f t="shared" si="0"/>
         <v>10030004</v>
       </c>
       <c r="B32" s="8">
@@ -2202,7 +2230,7 @@
     </row>
     <row r="33" ht="16.5" spans="1:7">
       <c r="A33" s="8">
-        <f>B33*100+C33</f>
+        <f t="shared" si="0"/>
         <v>10030005</v>
       </c>
       <c r="B33" s="8">
@@ -2222,7 +2250,7 @@
     </row>
     <row r="34" ht="16.5" spans="1:7">
       <c r="A34" s="8">
-        <f>B34*100+C34</f>
+        <f t="shared" si="0"/>
         <v>10030006</v>
       </c>
       <c r="B34" s="8">
@@ -2362,7 +2390,7 @@
     </row>
     <row r="41" ht="16.5" spans="1:7">
       <c r="A41" s="11">
-        <f t="shared" ref="A41:A58" si="2">B41*100+C41</f>
+        <f t="shared" ref="A41:A70" si="2">B41*100+C41</f>
         <v>10070001</v>
       </c>
       <c r="B41" s="11">
@@ -2773,215 +2801,215 @@
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:7">
-      <c r="A59" s="15">
-        <f t="shared" ref="A59:A71" si="3">B59*100+C59</f>
-        <v>10140001</v>
-      </c>
-      <c r="B59" s="15">
-        <v>101400</v>
-      </c>
-      <c r="C59" s="16">
+      <c r="A59" s="8">
+        <f t="shared" si="2"/>
+        <v>10120001</v>
+      </c>
+      <c r="B59" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C59" s="9">
         <v>1</v>
       </c>
-      <c r="D59" s="16">
-        <v>0</v>
-      </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16" t="s">
+      <c r="D59" s="9">
+        <v>0</v>
+      </c>
+      <c r="E59" s="10"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="9" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:7">
-      <c r="A60" s="15">
-        <f t="shared" si="3"/>
-        <v>10140102</v>
-      </c>
-      <c r="B60" s="15">
-        <v>101401</v>
-      </c>
-      <c r="C60" s="16">
+      <c r="A60" s="8">
+        <f t="shared" si="2"/>
+        <v>10120002</v>
+      </c>
+      <c r="B60" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C60" s="9">
         <v>2</v>
       </c>
-      <c r="D60" s="16">
-        <v>0</v>
-      </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16">
+      <c r="D60" s="9">
+        <v>0</v>
+      </c>
+      <c r="E60" s="10"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:7">
+      <c r="A61" s="8">
+        <f t="shared" si="2"/>
+        <v>10120003</v>
+      </c>
+      <c r="B61" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C61" s="9">
+        <v>3</v>
+      </c>
+      <c r="D61" s="9">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:7">
+      <c r="A62" s="8">
+        <f t="shared" si="2"/>
+        <v>10120004</v>
+      </c>
+      <c r="B62" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C62" s="9">
+        <v>4</v>
+      </c>
+      <c r="D62" s="9">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:7">
+      <c r="A63" s="8">
+        <f t="shared" si="2"/>
+        <v>10120005</v>
+      </c>
+      <c r="B63" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C63" s="9">
+        <v>5</v>
+      </c>
+      <c r="D63" s="9">
+        <v>0</v>
+      </c>
+      <c r="E63" s="10"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:7">
+      <c r="A64" s="8">
+        <f t="shared" si="2"/>
+        <v>10120006</v>
+      </c>
+      <c r="B64" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C64" s="9">
+        <v>6</v>
+      </c>
+      <c r="D64" s="9">
+        <v>0</v>
+      </c>
+      <c r="E64" s="10"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:7">
+      <c r="A65" s="8">
+        <f t="shared" si="2"/>
+        <v>10120007</v>
+      </c>
+      <c r="B65" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C65" s="9">
+        <v>7</v>
+      </c>
+      <c r="D65" s="9">
+        <v>1</v>
+      </c>
+      <c r="E65" s="10"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="1:7">
+      <c r="A66" s="8">
+        <f t="shared" si="2"/>
+        <v>10120008</v>
+      </c>
+      <c r="B66" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C66" s="9">
+        <v>8</v>
+      </c>
+      <c r="D66" s="9">
+        <v>1</v>
+      </c>
+      <c r="E66" s="10"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:7">
+      <c r="A67" s="8">
+        <f t="shared" si="2"/>
+        <v>10120009</v>
+      </c>
+      <c r="B67" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C67" s="9">
         <v>9</v>
       </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:7">
-      <c r="A61" s="15">
-        <f t="shared" si="3"/>
-        <v>10140203</v>
-      </c>
-      <c r="B61" s="15">
-        <v>101402</v>
-      </c>
-      <c r="C61" s="16">
-        <v>3</v>
-      </c>
-      <c r="D61" s="16">
-        <v>0</v>
-      </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16">
+      <c r="D67" s="9">
+        <v>1</v>
+      </c>
+      <c r="E67" s="10"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:7">
+      <c r="A68" s="8">
+        <f t="shared" si="2"/>
+        <v>10120010</v>
+      </c>
+      <c r="B68" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C68" s="9">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" ht="16.5" spans="1:7">
-      <c r="A62" s="15">
-        <f t="shared" si="3"/>
-        <v>10140304</v>
-      </c>
-      <c r="B62" s="15">
-        <v>101403</v>
-      </c>
-      <c r="C62" s="16">
-        <v>4</v>
-      </c>
-      <c r="D62" s="16">
-        <v>0</v>
-      </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:7">
-      <c r="A63" s="15">
-        <f t="shared" si="3"/>
-        <v>10140405</v>
-      </c>
-      <c r="B63" s="15">
-        <v>101404</v>
-      </c>
-      <c r="C63" s="16">
-        <v>5</v>
-      </c>
-      <c r="D63" s="16">
-        <v>0</v>
-      </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:7">
-      <c r="A64" s="15">
-        <f t="shared" si="3"/>
-        <v>10140506</v>
-      </c>
-      <c r="B64" s="15">
-        <v>101405</v>
-      </c>
-      <c r="C64" s="16">
-        <v>6</v>
-      </c>
-      <c r="D64" s="16">
-        <v>0</v>
-      </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:7">
-      <c r="A65" s="15">
-        <f t="shared" si="3"/>
-        <v>10140607</v>
-      </c>
-      <c r="B65" s="15">
-        <v>101406</v>
-      </c>
-      <c r="C65" s="16">
-        <v>7</v>
-      </c>
-      <c r="D65" s="16">
-        <v>0</v>
-      </c>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" ht="16.5" spans="1:7">
-      <c r="A66" s="15">
-        <f t="shared" si="3"/>
-        <v>10140708</v>
-      </c>
-      <c r="B66" s="15">
-        <v>101407</v>
-      </c>
-      <c r="C66" s="16">
-        <v>8</v>
-      </c>
-      <c r="D66" s="16">
-        <v>0</v>
-      </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:7">
-      <c r="A67" s="15">
-        <f t="shared" si="3"/>
-        <v>10140809</v>
-      </c>
-      <c r="B67" s="15">
-        <v>101408</v>
-      </c>
-      <c r="C67" s="16">
-        <v>9</v>
-      </c>
-      <c r="D67" s="16">
-        <v>0</v>
-      </c>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:7">
-      <c r="A68" s="15">
-        <f t="shared" si="3"/>
-        <v>10140910</v>
-      </c>
-      <c r="B68" s="15">
-        <v>101409</v>
-      </c>
-      <c r="C68" s="16">
-        <v>10</v>
-      </c>
-      <c r="D68" s="16">
-        <v>0</v>
-      </c>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16" t="s">
-        <v>106</v>
+      <c r="D68" s="9">
+        <v>1</v>
+      </c>
+      <c r="E68" s="10"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:7">
       <c r="A69" s="15">
-        <f t="shared" si="3"/>
-        <v>10141011</v>
+        <f t="shared" ref="A69:A81" si="3">B69*100+C69</f>
+        <v>10140001</v>
       </c>
       <c r="B69" s="15">
-        <v>101410</v>
+        <v>101400</v>
       </c>
       <c r="C69" s="16">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D69" s="16">
         <v>0</v>
@@ -2989,47 +3017,247 @@
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
       <c r="G69" s="16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:7">
       <c r="A70" s="15">
         <f t="shared" si="3"/>
-        <v>10141112</v>
+        <v>10140102</v>
       </c>
       <c r="B70" s="15">
-        <v>101411</v>
+        <v>101401</v>
       </c>
       <c r="C70" s="16">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D70" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="16"/>
       <c r="F70" s="16"/>
-      <c r="G70" s="16" t="s">
-        <v>62</v>
+      <c r="G70" s="16">
+        <v>9</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:7">
       <c r="A71" s="15">
         <f t="shared" si="3"/>
-        <v>10141213</v>
+        <v>10140203</v>
       </c>
       <c r="B71" s="15">
-        <v>101412</v>
+        <v>101402</v>
       </c>
       <c r="C71" s="16">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D71" s="16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E71" s="16"/>
       <c r="F71" s="16"/>
-      <c r="G71" s="16" t="s">
-        <v>108</v>
+      <c r="G71" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:7">
+      <c r="A72" s="15">
+        <f t="shared" si="3"/>
+        <v>10140304</v>
+      </c>
+      <c r="B72" s="15">
+        <v>101403</v>
+      </c>
+      <c r="C72" s="16">
+        <v>4</v>
+      </c>
+      <c r="D72" s="16">
+        <v>0</v>
+      </c>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" spans="1:7">
+      <c r="A73" s="15">
+        <f t="shared" si="3"/>
+        <v>10140405</v>
+      </c>
+      <c r="B73" s="15">
+        <v>101404</v>
+      </c>
+      <c r="C73" s="16">
+        <v>5</v>
+      </c>
+      <c r="D73" s="16">
+        <v>0</v>
+      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:7">
+      <c r="A74" s="15">
+        <f t="shared" si="3"/>
+        <v>10140506</v>
+      </c>
+      <c r="B74" s="15">
+        <v>101405</v>
+      </c>
+      <c r="C74" s="16">
+        <v>6</v>
+      </c>
+      <c r="D74" s="16">
+        <v>0</v>
+      </c>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" spans="1:7">
+      <c r="A75" s="15">
+        <f t="shared" si="3"/>
+        <v>10140607</v>
+      </c>
+      <c r="B75" s="15">
+        <v>101406</v>
+      </c>
+      <c r="C75" s="16">
+        <v>7</v>
+      </c>
+      <c r="D75" s="16">
+        <v>0</v>
+      </c>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:7">
+      <c r="A76" s="15">
+        <f t="shared" si="3"/>
+        <v>10140708</v>
+      </c>
+      <c r="B76" s="15">
+        <v>101407</v>
+      </c>
+      <c r="C76" s="16">
+        <v>8</v>
+      </c>
+      <c r="D76" s="16">
+        <v>0</v>
+      </c>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:7">
+      <c r="A77" s="15">
+        <f t="shared" si="3"/>
+        <v>10140809</v>
+      </c>
+      <c r="B77" s="15">
+        <v>101408</v>
+      </c>
+      <c r="C77" s="16">
+        <v>9</v>
+      </c>
+      <c r="D77" s="16">
+        <v>0</v>
+      </c>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:7">
+      <c r="A78" s="15">
+        <f t="shared" si="3"/>
+        <v>10140910</v>
+      </c>
+      <c r="B78" s="15">
+        <v>101409</v>
+      </c>
+      <c r="C78" s="16">
+        <v>10</v>
+      </c>
+      <c r="D78" s="16">
+        <v>0</v>
+      </c>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:7">
+      <c r="A79" s="15">
+        <f t="shared" si="3"/>
+        <v>10141011</v>
+      </c>
+      <c r="B79" s="15">
+        <v>101410</v>
+      </c>
+      <c r="C79" s="16">
+        <v>11</v>
+      </c>
+      <c r="D79" s="16">
+        <v>0</v>
+      </c>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:7">
+      <c r="A80" s="15">
+        <f t="shared" si="3"/>
+        <v>10141112</v>
+      </c>
+      <c r="B80" s="15">
+        <v>101411</v>
+      </c>
+      <c r="C80" s="16">
+        <v>12</v>
+      </c>
+      <c r="D80" s="16">
+        <v>1</v>
+      </c>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:7">
+      <c r="A81" s="15">
+        <f t="shared" si="3"/>
+        <v>10141213</v>
+      </c>
+      <c r="B81" s="15">
+        <v>101412</v>
+      </c>
+      <c r="C81" s="16">
+        <v>13</v>
+      </c>
+      <c r="D81" s="16">
+        <v>2</v>
+      </c>
+      <c r="E81" s="16"/>
+      <c r="F81" s="16"/>
+      <c r="G81" s="16" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="158">
   <si>
     <t>图标</t>
   </si>
@@ -135,6 +135,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>出现权重</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -300,75 +303,144 @@
     <t>樱桃</t>
   </si>
   <si>
+    <t>Wild-MINI</t>
+  </si>
+  <si>
+    <t>Wild-MINOR</t>
+  </si>
+  <si>
+    <t>Wild-MAJOR</t>
+  </si>
+  <si>
+    <t>Wild-GRAND</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>Wild-倍率6</t>
+  </si>
+  <si>
+    <t>SpecialGird</t>
+  </si>
+  <si>
+    <t>Wild-倍率9</t>
+  </si>
+  <si>
+    <t>Wild-倍率12</t>
+  </si>
+  <si>
+    <t>Wild-倍率15</t>
+  </si>
+  <si>
+    <t>BaseElementReward</t>
+  </si>
+  <si>
+    <t>Wild-倍率21</t>
+  </si>
+  <si>
+    <t>Wild-倍率24</t>
+  </si>
+  <si>
+    <t>Wild-倍率32</t>
+  </si>
+  <si>
+    <t>Wild-倍率38</t>
+  </si>
+  <si>
+    <t>Wild-倍率49</t>
+  </si>
+  <si>
+    <t>Wild-倍率58</t>
+  </si>
+  <si>
+    <t>Wild-倍率68</t>
+  </si>
+  <si>
+    <t>Wild-倍率79</t>
+  </si>
+  <si>
+    <t>Wild-倍率85</t>
+  </si>
+  <si>
+    <t>Wild-倍率96</t>
+  </si>
+  <si>
+    <t>Wild-倍率105</t>
+  </si>
+  <si>
+    <t>Wild-倍率110</t>
+  </si>
+  <si>
+    <t>Wild-倍率125</t>
+  </si>
+  <si>
+    <t>Wild-倍率138</t>
+  </si>
+  <si>
+    <t>Wild-倍率150</t>
+  </si>
+  <si>
+    <t>Wild-倍率210</t>
+  </si>
+  <si>
+    <t>空元素</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_16.png</t>
+  </si>
+  <si>
+    <t>2条</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_12.png</t>
+  </si>
+  <si>
+    <t>2筒</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_14.png</t>
+  </si>
+  <si>
+    <t>5条</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_10.png</t>
+  </si>
+  <si>
+    <t>5筒</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_8.png</t>
+  </si>
+  <si>
+    <t>八万</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_6.png</t>
+  </si>
+  <si>
+    <t>白板</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_2.png</t>
+  </si>
+  <si>
+    <t>红中</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_mj_4.png</t>
+  </si>
+  <si>
+    <t>发财</t>
+  </si>
+  <si>
+    <t>mjhl_zjm_wild.png</t>
+  </si>
+  <si>
     <t>Wild</t>
   </si>
   <si>
-    <t>Wild-MINI</t>
-  </si>
-  <si>
-    <t>Wild-MINOR</t>
-  </si>
-  <si>
-    <t>Wild-MAJOR</t>
-  </si>
-  <si>
-    <t>Wild-GRAND</t>
-  </si>
-  <si>
-    <t>空元素</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_16.png</t>
-  </si>
-  <si>
-    <t>2条</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_12.png</t>
-  </si>
-  <si>
-    <t>2筒</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_14.png</t>
-  </si>
-  <si>
-    <t>5条</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_10.png</t>
-  </si>
-  <si>
-    <t>5筒</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_8.png</t>
-  </si>
-  <si>
-    <t>八万</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_6.png</t>
-  </si>
-  <si>
-    <t>白板</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_2.png</t>
-  </si>
-  <si>
-    <t>红中</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_mj_4.png</t>
-  </si>
-  <si>
-    <t>发财</t>
-  </si>
-  <si>
-    <t>mjhl_zjm_wild.png</t>
-  </si>
-  <si>
     <t>mjhl_zjm_hu.png</t>
   </si>
   <si>
@@ -441,13 +513,61 @@
     <t>摇钱树</t>
   </si>
   <si>
-    <t>横财神</t>
-  </si>
-  <si>
-    <t>正财神</t>
-  </si>
-  <si>
     <t>财神jackpot</t>
+  </si>
+  <si>
+    <t>横财神第1行</t>
+  </si>
+  <si>
+    <t>横财神第2行</t>
+  </si>
+  <si>
+    <t>横财神第3行</t>
+  </si>
+  <si>
+    <t>横财神第2列</t>
+  </si>
+  <si>
+    <t>横财神第3列</t>
+  </si>
+  <si>
+    <t>横财神第4列</t>
+  </si>
+  <si>
+    <t>横财神第1行-第2次</t>
+  </si>
+  <si>
+    <t>横财神第2行-第2次</t>
+  </si>
+  <si>
+    <t>横财神第3行-第2次</t>
+  </si>
+  <si>
+    <t>横财神第2列-第2次</t>
+  </si>
+  <si>
+    <t>横财神第3列-第2次</t>
+  </si>
+  <si>
+    <t>横财神第4列-第2次</t>
+  </si>
+  <si>
+    <t>横财神第1行-第3次</t>
+  </si>
+  <si>
+    <t>横财神第2行-第3次</t>
+  </si>
+  <si>
+    <t>横财神第3行-第3次</t>
+  </si>
+  <si>
+    <t>横财神第2列-第3次</t>
+  </si>
+  <si>
+    <t>横财神第3列-第3次</t>
+  </si>
+  <si>
+    <t>横财神第4列-第3次</t>
   </si>
   <si>
     <t>空格</t>
@@ -649,13 +769,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1168,7 +1288,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1207,6 +1327,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1540,8 +1663,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:M116"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
@@ -1550,7 +1673,7 @@
     <col min="7" max="7" width="24.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:7">
+    <row r="1" ht="16.5" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1572,42 +1695,45 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" ht="16.5" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="5"/>
     </row>
     <row r="3" ht="16.5" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="5"/>
     </row>
@@ -1620,7 +1746,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" ht="16.5" spans="1:7">
+    <row r="5" ht="16.5" spans="1:12">
       <c r="A5" s="4">
         <f>B5*100+C5</f>
         <v>10010001</v>
@@ -1635,16 +1761,19 @@
         <v>0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:7">
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:12">
       <c r="A6" s="4">
-        <f t="shared" ref="A6:A34" si="0">B6*100+C6</f>
+        <f t="shared" ref="A6:A46" si="0">B6*100+C6</f>
         <v>10010002</v>
       </c>
       <c r="B6" s="4">
@@ -1657,14 +1786,17 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:7">
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:12">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>10010003</v>
@@ -1679,14 +1811,17 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:7">
+        <v>17</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:12">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>10010004</v>
@@ -1701,14 +1836,17 @@
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:7">
+        <v>19</v>
+      </c>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:12">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>10010005</v>
@@ -1723,14 +1861,17 @@
         <v>0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:7">
+        <v>21</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:12">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>10010006</v>
@@ -1745,14 +1886,17 @@
         <v>0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:7">
+        <v>23</v>
+      </c>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:12">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>10010007</v>
@@ -1767,14 +1911,17 @@
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:7">
+        <v>25</v>
+      </c>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:12">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>10010008</v>
@@ -1789,14 +1936,17 @@
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:12">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>10010009</v>
@@ -1811,14 +1961,17 @@
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:12">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10010010</v>
@@ -1833,14 +1986,17 @@
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:12">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>10010011</v>
@@ -1855,14 +2011,17 @@
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:7">
+        <v>33</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:12">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>10010012</v>
@@ -1877,14 +2036,17 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:7">
+        <v>35</v>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:12">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>10010013</v>
@@ -1899,14 +2061,17 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:7">
+        <v>37</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:12">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>10010014</v>
@@ -1921,14 +2086,17 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:7">
+        <v>39</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:12">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>10010015</v>
@@ -1943,14 +2111,17 @@
         <v>2</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:7">
+        <v>41</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:12">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>10010016</v>
@@ -1965,14 +2136,17 @@
         <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:7">
+        <v>43</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:12">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>10010017</v>
@@ -1987,14 +2161,17 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:7">
+        <v>45</v>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:12">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>10010018</v>
@@ -2009,14 +2186,17 @@
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:7">
+        <v>47</v>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:12">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>10010019</v>
@@ -2031,14 +2211,17 @@
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:7">
+        <v>49</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:12">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>10010020</v>
@@ -2053,14 +2236,17 @@
         <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:7">
+        <v>51</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:12">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>10010021</v>
@@ -2075,14 +2261,17 @@
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:7">
+        <v>53</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:12">
       <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>10010022</v>
@@ -2097,14 +2286,17 @@
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:7">
+        <v>55</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:12">
       <c r="A27" s="6">
         <f t="shared" si="0"/>
         <v>10010028</v>
@@ -2119,14 +2311,17 @@
         <v>2</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:7">
+        <v>56</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:12">
       <c r="A28" s="6">
         <f t="shared" si="0"/>
         <v>10010030</v>
@@ -2141,14 +2336,17 @@
         <v>2</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:7">
+        <v>57</v>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:12">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>10030001</v>
@@ -2165,10 +2363,13 @@
       <c r="E29" s="10"/>
       <c r="F29" s="8"/>
       <c r="G29" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:7">
+        <v>58</v>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:12">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
         <v>10030002</v>
@@ -2185,10 +2386,13 @@
       <c r="E30" s="10"/>
       <c r="F30" s="8"/>
       <c r="G30" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:7">
+        <v>59</v>
+      </c>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:12">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
         <v>10030003</v>
@@ -2205,10 +2409,13 @@
       <c r="E31" s="10"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:7">
+        <v>60</v>
+      </c>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:12">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
         <v>10030004</v>
@@ -2225,10 +2432,13 @@
       <c r="E32" s="10"/>
       <c r="F32" s="8"/>
       <c r="G32" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:7">
+        <v>27</v>
+      </c>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:12">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
         <v>10030005</v>
@@ -2245,10 +2455,13 @@
       <c r="E33" s="10"/>
       <c r="F33" s="8"/>
       <c r="G33" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:7">
+        <v>61</v>
+      </c>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:12">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
         <v>10030006</v>
@@ -2265,12 +2478,15 @@
       <c r="E34" s="10"/>
       <c r="F34" s="8"/>
       <c r="G34" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:7">
+        <v>62</v>
+      </c>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+    </row>
+    <row r="35" ht="16.5" spans="1:12">
       <c r="A35" s="8">
-        <f t="shared" ref="A35:A40" si="1">B35*100+C35</f>
+        <f t="shared" si="0"/>
         <v>10030007</v>
       </c>
       <c r="B35" s="8">
@@ -2285,12 +2501,15 @@
       <c r="E35" s="10"/>
       <c r="F35" s="8"/>
       <c r="G35" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:7">
+        <v>63</v>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+    </row>
+    <row r="36" ht="16.5" spans="1:12">
       <c r="A36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10030008</v>
       </c>
       <c r="B36" s="8">
@@ -2305,12 +2524,15 @@
       <c r="E36" s="10"/>
       <c r="F36" s="8"/>
       <c r="G36" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:7">
+        <v>64</v>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+    </row>
+    <row r="37" ht="16.5" spans="1:12">
       <c r="A37" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10030009</v>
       </c>
       <c r="B37" s="8">
@@ -2325,12 +2547,15 @@
       <c r="E37" s="10"/>
       <c r="F37" s="8"/>
       <c r="G37" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:7">
+        <v>65</v>
+      </c>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+    </row>
+    <row r="38" ht="16.5" spans="1:12">
       <c r="A38" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10030010</v>
       </c>
       <c r="B38" s="8">
@@ -2345,19 +2570,24 @@
       <c r="E38" s="10"/>
       <c r="F38" s="8"/>
       <c r="G38" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:7">
+        <v>66</v>
+      </c>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" ht="16.5" spans="1:13">
       <c r="A39" s="8">
-        <f t="shared" si="1"/>
-        <v>10030011</v>
+        <f t="shared" si="0"/>
+        <v>10030021</v>
       </c>
       <c r="B39" s="8">
         <v>100300</v>
       </c>
       <c r="C39" s="9">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D39" s="9">
         <v>1</v>
@@ -2365,19 +2595,39 @@
       <c r="E39" s="10"/>
       <c r="F39" s="8"/>
       <c r="G39" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" ht="16.5" spans="1:7">
+        <v>68</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,C39,H39)</f>
+        <v>21_1</v>
+      </c>
+      <c r="J39">
+        <v>6</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,C39,K39,J39)</f>
+        <v>21_1_6</v>
+      </c>
+      <c r="M39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="16.5" spans="1:13">
       <c r="A40" s="8">
-        <f t="shared" si="1"/>
-        <v>10030099</v>
+        <f t="shared" si="0"/>
+        <v>10030022</v>
       </c>
       <c r="B40" s="8">
         <v>100300</v>
       </c>
       <c r="C40" s="9">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="D40" s="9">
         <v>1</v>
@@ -2385,880 +2635,2088 @@
       <c r="E40" s="10"/>
       <c r="F40" s="8"/>
       <c r="G40" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:7">
-      <c r="A41" s="11">
-        <f t="shared" ref="A41:A70" si="2">B41*100+C41</f>
-        <v>10070001</v>
-      </c>
-      <c r="B41" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C41" s="12">
-        <v>1</v>
-      </c>
-      <c r="D41" s="12">
-        <v>0</v>
-      </c>
-      <c r="E41" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" ref="I40:I58" si="1">_xlfn.TEXTJOIN("_",TRUE,C40,H40)</f>
+        <v>22_1</v>
+      </c>
+      <c r="J40" s="13">
+        <v>9</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" ref="L40:L58" si="2">_xlfn.TEXTJOIN("_",TRUE,C40,K40,J40)</f>
+        <v>22_1_9</v>
+      </c>
+      <c r="M40" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,I39:I58)</f>
+        <v>21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A41" s="8">
+        <f t="shared" si="0"/>
+        <v>10030023</v>
+      </c>
+      <c r="B41" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C41" s="9">
+        <v>23</v>
+      </c>
+      <c r="D41" s="9">
+        <v>1</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="1"/>
+        <v>23_1</v>
+      </c>
+      <c r="J41" s="13">
+        <v>12</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="2"/>
+        <v>23_1_12</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A42" s="8">
+        <f t="shared" si="0"/>
+        <v>10030024</v>
+      </c>
+      <c r="B42" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C42" s="9">
+        <v>24</v>
+      </c>
+      <c r="D42" s="9">
+        <v>1</v>
+      </c>
+      <c r="E42" s="10"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="1"/>
+        <v>24_1</v>
+      </c>
+      <c r="J42" s="13">
+        <v>15</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="2"/>
+        <v>24_1_15</v>
+      </c>
+      <c r="M42" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A43" s="8">
+        <f t="shared" si="0"/>
+        <v>10030025</v>
+      </c>
+      <c r="B43" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C43" s="9">
+        <v>25</v>
+      </c>
+      <c r="D43" s="9">
+        <v>1</v>
+      </c>
+      <c r="E43" s="10"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="1"/>
+        <v>25_1</v>
+      </c>
+      <c r="J43" s="13">
+        <v>21</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="2"/>
+        <v>25_1_21</v>
+      </c>
+      <c r="M43" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,L39:L58)</f>
+        <v>21_1_6|22_1_9|23_1_12|24_1_15|25_1_21|26_1_24|27_1_32|28_1_38|29_1_49|30_1_58|31_1_68|32_1_79|33_1_85|34_1_96|35_1_105|36_1_110|37_1_125|38_1_138|39_1_150|40_1_210</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A44" s="8">
+        <f t="shared" si="0"/>
+        <v>10030026</v>
+      </c>
+      <c r="B44" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C44" s="9">
+        <v>26</v>
+      </c>
+      <c r="D44" s="9">
+        <v>1</v>
+      </c>
+      <c r="E44" s="10"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="1"/>
+        <v>26_1</v>
+      </c>
+      <c r="J44" s="13">
+        <v>24</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="2"/>
+        <v>26_1_24</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A45" s="8">
+        <f t="shared" si="0"/>
+        <v>10030027</v>
+      </c>
+      <c r="B45" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C45" s="9">
+        <v>27</v>
+      </c>
+      <c r="D45" s="9">
+        <v>1</v>
+      </c>
+      <c r="E45" s="10"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="1"/>
+        <v>27_1</v>
+      </c>
+      <c r="J45" s="13">
+        <v>32</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45" t="str">
+        <f t="shared" si="2"/>
+        <v>27_1_32</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A46" s="8">
+        <f t="shared" si="0"/>
+        <v>10030028</v>
+      </c>
+      <c r="B46" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C46" s="9">
+        <v>28</v>
+      </c>
+      <c r="D46" s="9">
+        <v>1</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="1"/>
+        <v>28_1</v>
+      </c>
+      <c r="J46" s="13">
+        <v>38</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="2"/>
+        <v>28_1_38</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A47" s="8">
+        <f t="shared" ref="A47:A59" si="3">B47*100+C47</f>
+        <v>10030029</v>
+      </c>
+      <c r="B47" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C47" s="9">
+        <v>29</v>
+      </c>
+      <c r="D47" s="9">
+        <v>1</v>
+      </c>
+      <c r="E47" s="10"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="1"/>
+        <v>29_1</v>
+      </c>
+      <c r="J47" s="13">
+        <v>49</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="2"/>
+        <v>29_1_49</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A48" s="8">
+        <f t="shared" si="3"/>
+        <v>10030030</v>
+      </c>
+      <c r="B48" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C48" s="9">
+        <v>30</v>
+      </c>
+      <c r="D48" s="9">
+        <v>1</v>
+      </c>
+      <c r="E48" s="10"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="1"/>
+        <v>30_1</v>
+      </c>
+      <c r="J48" s="13">
+        <v>58</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="2"/>
+        <v>30_1_58</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A49" s="8">
+        <f t="shared" si="3"/>
+        <v>10030031</v>
+      </c>
+      <c r="B49" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C49" s="9">
+        <v>31</v>
+      </c>
+      <c r="D49" s="9">
+        <v>1</v>
+      </c>
+      <c r="E49" s="10"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="1"/>
+        <v>31_1</v>
+      </c>
+      <c r="J49" s="13">
         <v>68</v>
       </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:7">
-      <c r="A42" s="11">
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49" t="str">
         <f t="shared" si="2"/>
-        <v>10070002</v>
-      </c>
-      <c r="B42" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C42" s="12">
-        <v>2</v>
-      </c>
-      <c r="D42" s="12">
-        <v>0</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:7">
-      <c r="A43" s="11">
+        <v>31_1_68</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A50" s="8">
+        <f t="shared" si="3"/>
+        <v>10030032</v>
+      </c>
+      <c r="B50" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C50" s="9">
+        <v>32</v>
+      </c>
+      <c r="D50" s="9">
+        <v>1</v>
+      </c>
+      <c r="E50" s="10"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="1"/>
+        <v>32_1</v>
+      </c>
+      <c r="J50" s="13">
+        <v>79</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50" t="str">
         <f t="shared" si="2"/>
-        <v>10070003</v>
-      </c>
-      <c r="B43" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C43" s="12">
-        <v>3</v>
-      </c>
-      <c r="D43" s="12">
-        <v>0</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:7">
-      <c r="A44" s="11">
+        <v>32_1_79</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A51" s="8">
+        <f t="shared" si="3"/>
+        <v>10030033</v>
+      </c>
+      <c r="B51" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C51" s="9">
+        <v>33</v>
+      </c>
+      <c r="D51" s="9">
+        <v>1</v>
+      </c>
+      <c r="E51" s="10"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="1"/>
+        <v>33_1</v>
+      </c>
+      <c r="J51" s="13">
+        <v>85</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51" t="str">
         <f t="shared" si="2"/>
-        <v>10070004</v>
-      </c>
-      <c r="B44" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C44" s="12">
-        <v>4</v>
-      </c>
-      <c r="D44" s="12">
-        <v>0</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:7">
-      <c r="A45" s="11">
+        <v>33_1_85</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A52" s="8">
+        <f t="shared" si="3"/>
+        <v>10030034</v>
+      </c>
+      <c r="B52" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C52" s="9">
+        <v>34</v>
+      </c>
+      <c r="D52" s="9">
+        <v>1</v>
+      </c>
+      <c r="E52" s="10"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="1"/>
+        <v>34_1</v>
+      </c>
+      <c r="J52" s="13">
+        <v>96</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52" t="str">
         <f t="shared" si="2"/>
-        <v>10070005</v>
-      </c>
-      <c r="B45" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C45" s="12">
-        <v>5</v>
-      </c>
-      <c r="D45" s="12">
-        <v>0</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:7">
-      <c r="A46" s="11">
+        <v>34_1_96</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A53" s="8">
+        <f t="shared" si="3"/>
+        <v>10030035</v>
+      </c>
+      <c r="B53" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C53" s="9">
+        <v>35</v>
+      </c>
+      <c r="D53" s="9">
+        <v>1</v>
+      </c>
+      <c r="E53" s="10"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="1"/>
+        <v>35_1</v>
+      </c>
+      <c r="J53" s="13">
+        <v>105</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53" t="str">
         <f t="shared" si="2"/>
-        <v>10070006</v>
-      </c>
-      <c r="B46" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C46" s="12">
-        <v>6</v>
-      </c>
-      <c r="D46" s="12">
-        <v>0</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:7">
-      <c r="A47" s="11">
+        <v>35_1_105</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A54" s="8">
+        <f t="shared" si="3"/>
+        <v>10030036</v>
+      </c>
+      <c r="B54" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C54" s="9">
+        <v>36</v>
+      </c>
+      <c r="D54" s="9">
+        <v>1</v>
+      </c>
+      <c r="E54" s="10"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="1"/>
+        <v>36_1</v>
+      </c>
+      <c r="J54" s="13">
+        <v>110</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54" t="str">
         <f t="shared" si="2"/>
-        <v>10070007</v>
-      </c>
-      <c r="B47" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C47" s="12">
-        <v>7</v>
-      </c>
-      <c r="D47" s="12">
-        <v>0</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:7">
-      <c r="A48" s="11">
+        <v>36_1_110</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A55" s="8">
+        <f t="shared" si="3"/>
+        <v>10030037</v>
+      </c>
+      <c r="B55" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C55" s="9">
+        <v>37</v>
+      </c>
+      <c r="D55" s="9">
+        <v>1</v>
+      </c>
+      <c r="E55" s="10"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="1"/>
+        <v>37_1</v>
+      </c>
+      <c r="J55" s="13">
+        <v>125</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55" t="str">
         <f t="shared" si="2"/>
-        <v>10070008</v>
-      </c>
-      <c r="B48" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C48" s="12">
-        <v>8</v>
-      </c>
-      <c r="D48" s="12">
-        <v>0</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:7">
-      <c r="A49" s="11">
+        <v>37_1_125</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A56" s="8">
+        <f t="shared" si="3"/>
+        <v>10030038</v>
+      </c>
+      <c r="B56" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C56" s="9">
+        <v>38</v>
+      </c>
+      <c r="D56" s="9">
+        <v>1</v>
+      </c>
+      <c r="E56" s="10"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="1"/>
+        <v>38_1</v>
+      </c>
+      <c r="J56" s="13">
+        <v>138</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56" t="str">
         <f t="shared" si="2"/>
-        <v>10070009</v>
-      </c>
-      <c r="B49" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C49" s="12">
-        <v>9</v>
-      </c>
-      <c r="D49" s="12">
-        <v>1</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:7">
-      <c r="A50" s="11">
+        <v>38_1_138</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A57" s="8">
+        <f t="shared" si="3"/>
+        <v>10030039</v>
+      </c>
+      <c r="B57" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C57" s="9">
+        <v>39</v>
+      </c>
+      <c r="D57" s="9">
+        <v>1</v>
+      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="1"/>
+        <v>39_1</v>
+      </c>
+      <c r="J57" s="13">
+        <v>150</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57" t="str">
         <f t="shared" si="2"/>
-        <v>10070010</v>
-      </c>
-      <c r="B50" s="11">
-        <v>100700</v>
-      </c>
-      <c r="C50" s="12">
-        <v>10</v>
-      </c>
-      <c r="D50" s="12">
-        <v>2</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:7">
-      <c r="A51" s="13">
+        <v>39_1_150</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A58" s="8">
+        <f t="shared" si="3"/>
+        <v>10030040</v>
+      </c>
+      <c r="B58" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C58" s="9">
+        <v>40</v>
+      </c>
+      <c r="D58" s="9">
+        <v>1</v>
+      </c>
+      <c r="E58" s="10"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="1"/>
+        <v>40_1</v>
+      </c>
+      <c r="J58" s="13">
+        <v>210</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58" t="str">
         <f t="shared" si="2"/>
-        <v>10070011</v>
-      </c>
-      <c r="B51" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C51" s="14">
-        <v>11</v>
-      </c>
-      <c r="D51" s="14">
-        <v>0</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F51" s="12">
-        <v>9</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:7">
-      <c r="A52" s="13">
-        <f t="shared" si="2"/>
-        <v>10070012</v>
-      </c>
-      <c r="B52" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C52" s="14">
-        <v>12</v>
-      </c>
-      <c r="D52" s="14">
-        <v>0</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F52" s="12">
-        <v>9</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" ht="16.5" spans="1:7">
-      <c r="A53" s="13">
-        <f t="shared" si="2"/>
-        <v>10070013</v>
-      </c>
-      <c r="B53" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C53" s="14">
-        <v>13</v>
-      </c>
-      <c r="D53" s="14">
-        <v>0</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="F53" s="12">
-        <v>9</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="54" ht="16.5" spans="1:7">
-      <c r="A54" s="13">
-        <f t="shared" si="2"/>
-        <v>10070014</v>
-      </c>
-      <c r="B54" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C54" s="14">
-        <v>14</v>
-      </c>
-      <c r="D54" s="14">
-        <v>0</v>
-      </c>
-      <c r="E54" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F54" s="12">
-        <v>9</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:7">
-      <c r="A55" s="13">
-        <f t="shared" si="2"/>
-        <v>10070015</v>
-      </c>
-      <c r="B55" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C55" s="14">
-        <v>15</v>
-      </c>
-      <c r="D55" s="14">
-        <v>0</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F55" s="12">
-        <v>9</v>
-      </c>
-      <c r="G55" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:7">
-      <c r="A56" s="13">
-        <f t="shared" si="2"/>
-        <v>10070016</v>
-      </c>
-      <c r="B56" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C56" s="14">
-        <v>16</v>
-      </c>
-      <c r="D56" s="14">
-        <v>0</v>
-      </c>
-      <c r="E56" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="F56" s="12">
-        <v>9</v>
-      </c>
-      <c r="G56" s="14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="57" ht="16.5" spans="1:7">
-      <c r="A57" s="13">
-        <f t="shared" si="2"/>
-        <v>10070017</v>
-      </c>
-      <c r="B57" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C57" s="14">
-        <v>17</v>
-      </c>
-      <c r="D57" s="14">
-        <v>0</v>
-      </c>
-      <c r="E57" s="14" t="s">
+        <v>40_1_210</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A59" s="8">
+        <f t="shared" si="3"/>
+        <v>10030099</v>
+      </c>
+      <c r="B59" s="8">
+        <v>100300</v>
+      </c>
+      <c r="C59" s="9">
         <v>99</v>
       </c>
-      <c r="F57" s="12">
-        <v>9</v>
-      </c>
-      <c r="G57" s="14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" ht="16.5" spans="1:7">
-      <c r="A58" s="13">
-        <f t="shared" si="2"/>
-        <v>10070018</v>
-      </c>
-      <c r="B58" s="13">
-        <v>100700</v>
-      </c>
-      <c r="C58" s="14">
-        <v>18</v>
-      </c>
-      <c r="D58" s="14">
-        <v>0</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F58" s="12">
-        <v>9</v>
-      </c>
-      <c r="G58" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="59" ht="16.5" spans="1:7">
-      <c r="A59" s="8">
-        <f t="shared" si="2"/>
-        <v>10120001</v>
-      </c>
-      <c r="B59" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C59" s="9">
-        <v>1</v>
-      </c>
       <c r="D59" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="8"/>
       <c r="G59" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+    </row>
+    <row r="60" ht="16.5" spans="1:12">
+      <c r="A60" s="11">
+        <f t="shared" ref="A60:A89" si="4">B60*100+C60</f>
+        <v>10070001</v>
+      </c>
+      <c r="B60" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C60" s="12">
+        <v>1</v>
+      </c>
+      <c r="D60" s="12">
+        <v>0</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+    </row>
+    <row r="61" ht="16.5" spans="1:12">
+      <c r="A61" s="11">
+        <f t="shared" si="4"/>
+        <v>10070002</v>
+      </c>
+      <c r="B61" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C61" s="12">
+        <v>2</v>
+      </c>
+      <c r="D61" s="12">
+        <v>0</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+    </row>
+    <row r="62" ht="16.5" spans="1:12">
+      <c r="A62" s="11">
+        <f t="shared" si="4"/>
+        <v>10070003</v>
+      </c>
+      <c r="B62" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C62" s="12">
+        <v>3</v>
+      </c>
+      <c r="D62" s="12">
+        <v>0</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+    </row>
+    <row r="63" ht="16.5" spans="1:12">
+      <c r="A63" s="11">
+        <f t="shared" si="4"/>
+        <v>10070004</v>
+      </c>
+      <c r="B63" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C63" s="12">
+        <v>4</v>
+      </c>
+      <c r="D63" s="12">
+        <v>0</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+    </row>
+    <row r="64" ht="16.5" spans="1:12">
+      <c r="A64" s="11">
+        <f t="shared" si="4"/>
+        <v>10070005</v>
+      </c>
+      <c r="B64" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C64" s="12">
+        <v>5</v>
+      </c>
+      <c r="D64" s="12">
+        <v>0</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
+      <c r="L64" s="13"/>
+    </row>
+    <row r="65" ht="16.5" spans="1:12">
+      <c r="A65" s="11">
+        <f t="shared" si="4"/>
+        <v>10070006</v>
+      </c>
+      <c r="B65" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C65" s="12">
+        <v>6</v>
+      </c>
+      <c r="D65" s="12">
+        <v>0</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+    </row>
+    <row r="66" ht="16.5" spans="1:12">
+      <c r="A66" s="11">
+        <f t="shared" si="4"/>
+        <v>10070007</v>
+      </c>
+      <c r="B66" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C66" s="12">
+        <v>7</v>
+      </c>
+      <c r="D66" s="12">
+        <v>0</v>
+      </c>
+      <c r="E66" s="12" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:7">
-      <c r="A60" s="8">
-        <f t="shared" si="2"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+    </row>
+    <row r="67" ht="16.5" spans="1:12">
+      <c r="A67" s="11">
+        <f t="shared" si="4"/>
+        <v>10070008</v>
+      </c>
+      <c r="B67" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C67" s="12">
+        <v>8</v>
+      </c>
+      <c r="D67" s="12">
+        <v>0</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
+      <c r="L67" s="13"/>
+    </row>
+    <row r="68" ht="16.5" spans="1:12">
+      <c r="A68" s="11">
+        <f t="shared" si="4"/>
+        <v>10070009</v>
+      </c>
+      <c r="B68" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C68" s="12">
+        <v>9</v>
+      </c>
+      <c r="D68" s="12">
+        <v>1</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+    </row>
+    <row r="69" ht="16.5" spans="1:12">
+      <c r="A69" s="11">
+        <f t="shared" si="4"/>
+        <v>10070010</v>
+      </c>
+      <c r="B69" s="11">
+        <v>100700</v>
+      </c>
+      <c r="C69" s="12">
+        <v>10</v>
+      </c>
+      <c r="D69" s="12">
+        <v>2</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+    </row>
+    <row r="70" ht="16.5" spans="1:12">
+      <c r="A70" s="14">
+        <f t="shared" si="4"/>
+        <v>10070011</v>
+      </c>
+      <c r="B70" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C70" s="15">
+        <v>11</v>
+      </c>
+      <c r="D70" s="15">
+        <v>0</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F70" s="12">
+        <v>9</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
+    </row>
+    <row r="71" ht="16.5" spans="1:12">
+      <c r="A71" s="14">
+        <f t="shared" si="4"/>
+        <v>10070012</v>
+      </c>
+      <c r="B71" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C71" s="15">
+        <v>12</v>
+      </c>
+      <c r="D71" s="15">
+        <v>0</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F71" s="12">
+        <v>9</v>
+      </c>
+      <c r="G71" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="J71" s="13"/>
+      <c r="K71" s="13"/>
+      <c r="L71" s="13"/>
+    </row>
+    <row r="72" ht="16.5" spans="1:12">
+      <c r="A72" s="14">
+        <f t="shared" si="4"/>
+        <v>10070013</v>
+      </c>
+      <c r="B72" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C72" s="15">
+        <v>13</v>
+      </c>
+      <c r="D72" s="15">
+        <v>0</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F72" s="12">
+        <v>9</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="J72" s="13"/>
+      <c r="K72" s="13"/>
+      <c r="L72" s="13"/>
+    </row>
+    <row r="73" ht="16.5" spans="1:12">
+      <c r="A73" s="14">
+        <f t="shared" si="4"/>
+        <v>10070014</v>
+      </c>
+      <c r="B73" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C73" s="15">
+        <v>14</v>
+      </c>
+      <c r="D73" s="15">
+        <v>0</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F73" s="12">
+        <v>9</v>
+      </c>
+      <c r="G73" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="J73" s="13"/>
+      <c r="K73" s="13"/>
+      <c r="L73" s="13"/>
+    </row>
+    <row r="74" ht="16.5" spans="1:12">
+      <c r="A74" s="14">
+        <f t="shared" si="4"/>
+        <v>10070015</v>
+      </c>
+      <c r="B74" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C74" s="15">
+        <v>15</v>
+      </c>
+      <c r="D74" s="15">
+        <v>0</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F74" s="12">
+        <v>9</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="J74" s="13"/>
+      <c r="K74" s="13"/>
+      <c r="L74" s="13"/>
+    </row>
+    <row r="75" ht="16.5" spans="1:12">
+      <c r="A75" s="14">
+        <f t="shared" si="4"/>
+        <v>10070016</v>
+      </c>
+      <c r="B75" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C75" s="15">
+        <v>16</v>
+      </c>
+      <c r="D75" s="15">
+        <v>0</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F75" s="12">
+        <v>9</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="J75" s="13"/>
+      <c r="K75" s="13"/>
+      <c r="L75" s="13"/>
+    </row>
+    <row r="76" ht="16.5" spans="1:12">
+      <c r="A76" s="14">
+        <f t="shared" si="4"/>
+        <v>10070017</v>
+      </c>
+      <c r="B76" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C76" s="15">
+        <v>17</v>
+      </c>
+      <c r="D76" s="15">
+        <v>0</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F76" s="12">
+        <v>9</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="J76" s="13"/>
+      <c r="K76" s="13"/>
+      <c r="L76" s="13"/>
+    </row>
+    <row r="77" ht="16.5" spans="1:12">
+      <c r="A77" s="14">
+        <f t="shared" si="4"/>
+        <v>10070018</v>
+      </c>
+      <c r="B77" s="14">
+        <v>100700</v>
+      </c>
+      <c r="C77" s="15">
+        <v>18</v>
+      </c>
+      <c r="D77" s="15">
+        <v>0</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F77" s="12">
+        <v>9</v>
+      </c>
+      <c r="G77" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="J77" s="13"/>
+      <c r="K77" s="13"/>
+      <c r="L77" s="13"/>
+    </row>
+    <row r="78" ht="16.5" spans="1:12">
+      <c r="A78" s="8">
+        <f t="shared" si="4"/>
+        <v>10120001</v>
+      </c>
+      <c r="B78" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C78" s="9">
+        <v>1</v>
+      </c>
+      <c r="D78" s="9">
+        <v>0</v>
+      </c>
+      <c r="E78" s="10"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J78" s="13"/>
+      <c r="K78" s="13"/>
+      <c r="L78" s="13"/>
+    </row>
+    <row r="79" ht="16.5" spans="1:12">
+      <c r="A79" s="8">
+        <f t="shared" si="4"/>
         <v>10120002</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B79" s="8">
         <v>101200</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C79" s="9">
         <v>2</v>
       </c>
-      <c r="D60" s="9">
-        <v>0</v>
-      </c>
-      <c r="E60" s="10"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:7">
-      <c r="A61" s="8">
-        <f t="shared" si="2"/>
+      <c r="D79" s="9">
+        <v>0</v>
+      </c>
+      <c r="E79" s="10"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="J79" s="13"/>
+      <c r="K79" s="13"/>
+      <c r="L79" s="13"/>
+    </row>
+    <row r="80" ht="16.5" spans="1:12">
+      <c r="A80" s="8">
+        <f t="shared" si="4"/>
         <v>10120003</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B80" s="8">
         <v>101200</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C80" s="9">
         <v>3</v>
       </c>
-      <c r="D61" s="9">
-        <v>0</v>
-      </c>
-      <c r="E61" s="10"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" ht="16.5" spans="1:7">
-      <c r="A62" s="8">
-        <f t="shared" si="2"/>
+      <c r="D80" s="9">
+        <v>0</v>
+      </c>
+      <c r="E80" s="10"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="J80" s="13"/>
+      <c r="K80" s="13"/>
+      <c r="L80" s="13"/>
+    </row>
+    <row r="81" ht="16.5" spans="1:12">
+      <c r="A81" s="8">
+        <f t="shared" si="4"/>
         <v>10120004</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B81" s="8">
         <v>101200</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C81" s="9">
         <v>4</v>
       </c>
-      <c r="D62" s="9">
-        <v>0</v>
-      </c>
-      <c r="E62" s="10"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:7">
-      <c r="A63" s="8">
-        <f t="shared" si="2"/>
+      <c r="D81" s="9">
+        <v>0</v>
+      </c>
+      <c r="E81" s="10"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="J81" s="13"/>
+      <c r="K81" s="13"/>
+      <c r="L81" s="13"/>
+    </row>
+    <row r="82" ht="16.5" spans="1:12">
+      <c r="A82" s="8">
+        <f t="shared" si="4"/>
         <v>10120005</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B82" s="8">
         <v>101200</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C82" s="9">
         <v>5</v>
       </c>
-      <c r="D63" s="9">
-        <v>0</v>
-      </c>
-      <c r="E63" s="10"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:7">
-      <c r="A64" s="8">
-        <f t="shared" si="2"/>
+      <c r="D82" s="9">
+        <v>0</v>
+      </c>
+      <c r="E82" s="10"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="J82" s="13"/>
+      <c r="K82" s="13"/>
+      <c r="L82" s="13"/>
+    </row>
+    <row r="83" ht="16.5" spans="1:12">
+      <c r="A83" s="8">
+        <f t="shared" si="4"/>
         <v>10120006</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B83" s="8">
         <v>101200</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C83" s="9">
         <v>6</v>
       </c>
-      <c r="D64" s="9">
-        <v>0</v>
-      </c>
-      <c r="E64" s="10"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="9" t="s">
+      <c r="D83" s="9">
+        <v>0</v>
+      </c>
+      <c r="E83" s="10"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="J83" s="13"/>
+      <c r="K83" s="13"/>
+      <c r="L83" s="13"/>
+    </row>
+    <row r="84" ht="16.5" spans="1:12">
+      <c r="A84" s="8">
+        <f t="shared" ref="A84:A103" si="5">B84*100+C84</f>
+        <v>10120009</v>
+      </c>
+      <c r="B84" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C84" s="9">
+        <v>9</v>
+      </c>
+      <c r="D84" s="9">
+        <v>2</v>
+      </c>
+      <c r="E84" s="10"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="J84" s="13"/>
+      <c r="K84" s="13"/>
+      <c r="L84" s="13"/>
+    </row>
+    <row r="85" ht="16.5" spans="1:12">
+      <c r="A85" s="8">
+        <f t="shared" si="5"/>
+        <v>10120010</v>
+      </c>
+      <c r="B85" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C85" s="9">
+        <v>10</v>
+      </c>
+      <c r="D85" s="9">
+        <v>1</v>
+      </c>
+      <c r="E85" s="10"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="9" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:7">
-      <c r="A65" s="8">
-        <f t="shared" si="2"/>
-        <v>10120007</v>
-      </c>
-      <c r="B65" s="8">
+      <c r="J85" s="13"/>
+      <c r="K85" s="13"/>
+      <c r="L85" s="13"/>
+    </row>
+    <row r="86" ht="16.5" spans="1:12">
+      <c r="A86" s="8">
+        <f t="shared" si="5"/>
+        <v>10120011</v>
+      </c>
+      <c r="B86" s="8">
         <v>101200</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C86" s="9">
+        <v>11</v>
+      </c>
+      <c r="D86" s="9">
+        <v>2</v>
+      </c>
+      <c r="E86" s="10"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J86" s="13"/>
+      <c r="K86" s="13"/>
+      <c r="L86" s="13"/>
+    </row>
+    <row r="87" ht="16.5" spans="1:12">
+      <c r="A87" s="8">
+        <f t="shared" si="5"/>
+        <v>10120012</v>
+      </c>
+      <c r="B87" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C87" s="9">
+        <v>12</v>
+      </c>
+      <c r="D87" s="9">
+        <v>2</v>
+      </c>
+      <c r="E87" s="10"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="J87" s="13"/>
+      <c r="K87" s="13"/>
+      <c r="L87" s="13"/>
+    </row>
+    <row r="88" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A88" s="8">
+        <f t="shared" si="5"/>
+        <v>10120013</v>
+      </c>
+      <c r="B88" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C88" s="9">
+        <v>13</v>
+      </c>
+      <c r="D88" s="9">
+        <v>2</v>
+      </c>
+      <c r="E88" s="10"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="J88" s="13"/>
+      <c r="K88" s="13"/>
+      <c r="L88" s="13"/>
+    </row>
+    <row r="89" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A89" s="8">
+        <f t="shared" si="5"/>
+        <v>10120014</v>
+      </c>
+      <c r="B89" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C89" s="9">
+        <v>14</v>
+      </c>
+      <c r="D89" s="9">
+        <v>2</v>
+      </c>
+      <c r="E89" s="10"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="J89" s="13"/>
+      <c r="K89" s="13"/>
+      <c r="L89" s="13"/>
+    </row>
+    <row r="90" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A90" s="8">
+        <f t="shared" si="5"/>
+        <v>10120015</v>
+      </c>
+      <c r="B90" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C90" s="9">
+        <v>15</v>
+      </c>
+      <c r="D90" s="9">
+        <v>2</v>
+      </c>
+      <c r="E90" s="10"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="J90" s="13"/>
+      <c r="K90" s="13"/>
+      <c r="L90" s="13"/>
+    </row>
+    <row r="91" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A91" s="8">
+        <f t="shared" si="5"/>
+        <v>10120016</v>
+      </c>
+      <c r="B91" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C91" s="9">
+        <v>16</v>
+      </c>
+      <c r="D91" s="9">
+        <v>2</v>
+      </c>
+      <c r="E91" s="10"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="J91" s="13"/>
+      <c r="K91" s="13"/>
+      <c r="L91" s="13"/>
+    </row>
+    <row r="92" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A92" s="8">
+        <f t="shared" si="5"/>
+        <v>10120021</v>
+      </c>
+      <c r="B92" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C92" s="9">
+        <v>21</v>
+      </c>
+      <c r="D92" s="9">
+        <v>2</v>
+      </c>
+      <c r="E92" s="10"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="J92" s="13"/>
+      <c r="K92" s="13"/>
+      <c r="L92" s="13"/>
+    </row>
+    <row r="93" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A93" s="8">
+        <f t="shared" si="5"/>
+        <v>10120022</v>
+      </c>
+      <c r="B93" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C93" s="9">
+        <v>22</v>
+      </c>
+      <c r="D93" s="9">
+        <v>2</v>
+      </c>
+      <c r="E93" s="10"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="J93" s="13"/>
+      <c r="K93" s="13"/>
+      <c r="L93" s="13"/>
+    </row>
+    <row r="94" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A94" s="8">
+        <f t="shared" si="5"/>
+        <v>10120023</v>
+      </c>
+      <c r="B94" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C94" s="9">
+        <v>23</v>
+      </c>
+      <c r="D94" s="9">
+        <v>2</v>
+      </c>
+      <c r="E94" s="10"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="J94" s="13"/>
+      <c r="K94" s="13"/>
+      <c r="L94" s="13"/>
+    </row>
+    <row r="95" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A95" s="8">
+        <f t="shared" si="5"/>
+        <v>10120024</v>
+      </c>
+      <c r="B95" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C95" s="9">
+        <v>24</v>
+      </c>
+      <c r="D95" s="9">
+        <v>2</v>
+      </c>
+      <c r="E95" s="10"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="J95" s="13"/>
+      <c r="K95" s="13"/>
+      <c r="L95" s="13"/>
+    </row>
+    <row r="96" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A96" s="8">
+        <f t="shared" si="5"/>
+        <v>10120025</v>
+      </c>
+      <c r="B96" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C96" s="9">
+        <v>25</v>
+      </c>
+      <c r="D96" s="9">
+        <v>2</v>
+      </c>
+      <c r="E96" s="10"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J96" s="13"/>
+      <c r="K96" s="13"/>
+      <c r="L96" s="13"/>
+    </row>
+    <row r="97" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A97" s="8">
+        <f t="shared" si="5"/>
+        <v>10120026</v>
+      </c>
+      <c r="B97" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C97" s="9">
+        <v>26</v>
+      </c>
+      <c r="D97" s="9">
+        <v>2</v>
+      </c>
+      <c r="E97" s="10"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="J97" s="13"/>
+      <c r="K97" s="13"/>
+      <c r="L97" s="13"/>
+    </row>
+    <row r="98" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A98" s="8">
+        <f t="shared" si="5"/>
+        <v>10120031</v>
+      </c>
+      <c r="B98" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C98" s="9">
+        <v>31</v>
+      </c>
+      <c r="D98" s="9">
+        <v>2</v>
+      </c>
+      <c r="E98" s="10"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J98" s="13"/>
+      <c r="K98" s="13"/>
+      <c r="L98" s="13"/>
+    </row>
+    <row r="99" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A99" s="8">
+        <f t="shared" si="5"/>
+        <v>10120032</v>
+      </c>
+      <c r="B99" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C99" s="9">
+        <v>32</v>
+      </c>
+      <c r="D99" s="9">
+        <v>2</v>
+      </c>
+      <c r="E99" s="10"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="J99" s="13"/>
+      <c r="K99" s="13"/>
+      <c r="L99" s="13"/>
+    </row>
+    <row r="100" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A100" s="8">
+        <f t="shared" si="5"/>
+        <v>10120033</v>
+      </c>
+      <c r="B100" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C100" s="9">
+        <v>33</v>
+      </c>
+      <c r="D100" s="9">
+        <v>2</v>
+      </c>
+      <c r="E100" s="10"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="J100" s="13"/>
+      <c r="K100" s="13"/>
+      <c r="L100" s="13"/>
+    </row>
+    <row r="101" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A101" s="8">
+        <f t="shared" si="5"/>
+        <v>10120034</v>
+      </c>
+      <c r="B101" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C101" s="9">
+        <v>34</v>
+      </c>
+      <c r="D101" s="9">
+        <v>2</v>
+      </c>
+      <c r="E101" s="10"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J101" s="13"/>
+      <c r="K101" s="13"/>
+      <c r="L101" s="13"/>
+    </row>
+    <row r="102" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A102" s="8">
+        <f t="shared" si="5"/>
+        <v>10120035</v>
+      </c>
+      <c r="B102" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C102" s="9">
+        <v>35</v>
+      </c>
+      <c r="D102" s="9">
+        <v>2</v>
+      </c>
+      <c r="E102" s="10"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="J102" s="13"/>
+      <c r="K102" s="13"/>
+      <c r="L102" s="13"/>
+    </row>
+    <row r="103" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A103" s="8">
+        <f t="shared" si="5"/>
+        <v>10120036</v>
+      </c>
+      <c r="B103" s="8">
+        <v>101200</v>
+      </c>
+      <c r="C103" s="9">
+        <v>36</v>
+      </c>
+      <c r="D103" s="9">
+        <v>2</v>
+      </c>
+      <c r="E103" s="10"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J103" s="13"/>
+      <c r="K103" s="13"/>
+      <c r="L103" s="13"/>
+    </row>
+    <row r="104" ht="16.5" spans="1:12">
+      <c r="A104" s="16">
+        <f t="shared" ref="A104:A116" si="6">B104*100+C104</f>
+        <v>10140001</v>
+      </c>
+      <c r="B104" s="16">
+        <v>101400</v>
+      </c>
+      <c r="C104" s="17">
+        <v>1</v>
+      </c>
+      <c r="D104" s="17">
+        <v>0</v>
+      </c>
+      <c r="E104" s="17"/>
+      <c r="F104" s="17"/>
+      <c r="G104" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="J104" s="13"/>
+      <c r="K104" s="13"/>
+      <c r="L104" s="13"/>
+    </row>
+    <row r="105" ht="16.5" spans="1:12">
+      <c r="A105" s="16">
+        <f t="shared" si="6"/>
+        <v>10140102</v>
+      </c>
+      <c r="B105" s="16">
+        <v>101401</v>
+      </c>
+      <c r="C105" s="17">
+        <v>2</v>
+      </c>
+      <c r="D105" s="17">
+        <v>0</v>
+      </c>
+      <c r="E105" s="17"/>
+      <c r="F105" s="17"/>
+      <c r="G105" s="17">
+        <v>9</v>
+      </c>
+      <c r="J105" s="13"/>
+      <c r="K105" s="13"/>
+      <c r="L105" s="13"/>
+    </row>
+    <row r="106" ht="16.5" spans="1:12">
+      <c r="A106" s="16">
+        <f t="shared" si="6"/>
+        <v>10140203</v>
+      </c>
+      <c r="B106" s="16">
+        <v>101402</v>
+      </c>
+      <c r="C106" s="17">
+        <v>3</v>
+      </c>
+      <c r="D106" s="17">
+        <v>0</v>
+      </c>
+      <c r="E106" s="17"/>
+      <c r="F106" s="17"/>
+      <c r="G106" s="17">
+        <v>10</v>
+      </c>
+      <c r="J106" s="13"/>
+      <c r="K106" s="13"/>
+      <c r="L106" s="13"/>
+    </row>
+    <row r="107" ht="16.5" spans="1:12">
+      <c r="A107" s="16">
+        <f t="shared" si="6"/>
+        <v>10140304</v>
+      </c>
+      <c r="B107" s="16">
+        <v>101403</v>
+      </c>
+      <c r="C107" s="17">
+        <v>4</v>
+      </c>
+      <c r="D107" s="17">
+        <v>0</v>
+      </c>
+      <c r="E107" s="17"/>
+      <c r="F107" s="17"/>
+      <c r="G107" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="13"/>
+      <c r="K107" s="13"/>
+      <c r="L107" s="13"/>
+    </row>
+    <row r="108" ht="16.5" spans="1:12">
+      <c r="A108" s="16">
+        <f t="shared" si="6"/>
+        <v>10140405</v>
+      </c>
+      <c r="B108" s="16">
+        <v>101404</v>
+      </c>
+      <c r="C108" s="17">
+        <v>5</v>
+      </c>
+      <c r="D108" s="17">
+        <v>0</v>
+      </c>
+      <c r="E108" s="17"/>
+      <c r="F108" s="17"/>
+      <c r="G108" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J108" s="13"/>
+      <c r="K108" s="13"/>
+      <c r="L108" s="13"/>
+    </row>
+    <row r="109" ht="16.5" spans="1:12">
+      <c r="A109" s="16">
+        <f t="shared" si="6"/>
+        <v>10140506</v>
+      </c>
+      <c r="B109" s="16">
+        <v>101405</v>
+      </c>
+      <c r="C109" s="17">
+        <v>6</v>
+      </c>
+      <c r="D109" s="17">
+        <v>0</v>
+      </c>
+      <c r="E109" s="17"/>
+      <c r="F109" s="17"/>
+      <c r="G109" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J109" s="13"/>
+      <c r="K109" s="13"/>
+      <c r="L109" s="13"/>
+    </row>
+    <row r="110" ht="16.5" spans="1:12">
+      <c r="A110" s="16">
+        <f t="shared" si="6"/>
+        <v>10140607</v>
+      </c>
+      <c r="B110" s="16">
+        <v>101406</v>
+      </c>
+      <c r="C110" s="17">
         <v>7</v>
       </c>
-      <c r="D65" s="9">
-        <v>1</v>
-      </c>
-      <c r="E65" s="10"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="66" ht="16.5" spans="1:7">
-      <c r="A66" s="8">
-        <f t="shared" si="2"/>
-        <v>10120008</v>
-      </c>
-      <c r="B66" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C66" s="9">
+      <c r="D110" s="17">
+        <v>0</v>
+      </c>
+      <c r="E110" s="17"/>
+      <c r="F110" s="17"/>
+      <c r="G110" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J110" s="13"/>
+      <c r="K110" s="13"/>
+      <c r="L110" s="13"/>
+    </row>
+    <row r="111" ht="16.5" spans="1:12">
+      <c r="A111" s="16">
+        <f t="shared" si="6"/>
+        <v>10140708</v>
+      </c>
+      <c r="B111" s="16">
+        <v>101407</v>
+      </c>
+      <c r="C111" s="17">
         <v>8</v>
       </c>
-      <c r="D66" s="9">
-        <v>1</v>
-      </c>
-      <c r="E66" s="10"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:7">
-      <c r="A67" s="8">
-        <f t="shared" si="2"/>
-        <v>10120009</v>
-      </c>
-      <c r="B67" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C67" s="9">
+      <c r="D111" s="17">
+        <v>0</v>
+      </c>
+      <c r="E111" s="17"/>
+      <c r="F111" s="17"/>
+      <c r="G111" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="J111" s="13"/>
+      <c r="K111" s="13"/>
+      <c r="L111" s="13"/>
+    </row>
+    <row r="112" ht="16.5" spans="1:12">
+      <c r="A112" s="16">
+        <f t="shared" si="6"/>
+        <v>10140809</v>
+      </c>
+      <c r="B112" s="16">
+        <v>101408</v>
+      </c>
+      <c r="C112" s="17">
         <v>9</v>
       </c>
-      <c r="D67" s="9">
-        <v>1</v>
-      </c>
-      <c r="E67" s="10"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:7">
-      <c r="A68" s="8">
-        <f t="shared" si="2"/>
-        <v>10120010</v>
-      </c>
-      <c r="B68" s="8">
-        <v>101200</v>
-      </c>
-      <c r="C68" s="9">
+      <c r="D112" s="17">
+        <v>0</v>
+      </c>
+      <c r="E112" s="17"/>
+      <c r="F112" s="17"/>
+      <c r="G112" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="J112" s="13"/>
+      <c r="K112" s="13"/>
+      <c r="L112" s="13"/>
+    </row>
+    <row r="113" ht="16.5" spans="1:12">
+      <c r="A113" s="16">
+        <f t="shared" si="6"/>
+        <v>10140910</v>
+      </c>
+      <c r="B113" s="16">
+        <v>101409</v>
+      </c>
+      <c r="C113" s="17">
         <v>10</v>
       </c>
-      <c r="D68" s="9">
-        <v>1</v>
-      </c>
-      <c r="E68" s="10"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" ht="16.5" spans="1:7">
-      <c r="A69" s="15">
-        <f t="shared" ref="A69:A81" si="3">B69*100+C69</f>
-        <v>10140001</v>
-      </c>
-      <c r="B69" s="15">
-        <v>101400</v>
-      </c>
-      <c r="C69" s="16">
-        <v>1</v>
-      </c>
-      <c r="D69" s="16">
-        <v>0</v>
-      </c>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="70" ht="16.5" spans="1:7">
-      <c r="A70" s="15">
-        <f t="shared" si="3"/>
-        <v>10140102</v>
-      </c>
-      <c r="B70" s="15">
-        <v>101401</v>
-      </c>
-      <c r="C70" s="16">
+      <c r="D113" s="17">
+        <v>0</v>
+      </c>
+      <c r="E113" s="17"/>
+      <c r="F113" s="17"/>
+      <c r="G113" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="J113" s="13"/>
+      <c r="K113" s="13"/>
+      <c r="L113" s="13"/>
+    </row>
+    <row r="114" ht="16.5" spans="1:12">
+      <c r="A114" s="16">
+        <f t="shared" si="6"/>
+        <v>10141011</v>
+      </c>
+      <c r="B114" s="16">
+        <v>101410</v>
+      </c>
+      <c r="C114" s="17">
+        <v>11</v>
+      </c>
+      <c r="D114" s="17">
+        <v>0</v>
+      </c>
+      <c r="E114" s="17"/>
+      <c r="F114" s="17"/>
+      <c r="G114" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="J114" s="13"/>
+      <c r="K114" s="13"/>
+      <c r="L114" s="13"/>
+    </row>
+    <row r="115" ht="16.5" spans="1:12">
+      <c r="A115" s="16">
+        <f t="shared" si="6"/>
+        <v>10141112</v>
+      </c>
+      <c r="B115" s="16">
+        <v>101411</v>
+      </c>
+      <c r="C115" s="17">
+        <v>12</v>
+      </c>
+      <c r="D115" s="17">
+        <v>1</v>
+      </c>
+      <c r="E115" s="17"/>
+      <c r="F115" s="17"/>
+      <c r="G115" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="J115" s="13"/>
+      <c r="K115" s="13"/>
+      <c r="L115" s="13"/>
+    </row>
+    <row r="116" ht="16.5" spans="1:12">
+      <c r="A116" s="16">
+        <f t="shared" si="6"/>
+        <v>10141213</v>
+      </c>
+      <c r="B116" s="16">
+        <v>101412</v>
+      </c>
+      <c r="C116" s="17">
+        <v>13</v>
+      </c>
+      <c r="D116" s="17">
         <v>2</v>
       </c>
-      <c r="D70" s="16">
-        <v>0</v>
-      </c>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" ht="16.5" spans="1:7">
-      <c r="A71" s="15">
-        <f t="shared" si="3"/>
-        <v>10140203</v>
-      </c>
-      <c r="B71" s="15">
-        <v>101402</v>
-      </c>
-      <c r="C71" s="16">
-        <v>3</v>
-      </c>
-      <c r="D71" s="16">
-        <v>0</v>
-      </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" ht="16.5" spans="1:7">
-      <c r="A72" s="15">
-        <f t="shared" si="3"/>
-        <v>10140304</v>
-      </c>
-      <c r="B72" s="15">
-        <v>101403</v>
-      </c>
-      <c r="C72" s="16">
-        <v>4</v>
-      </c>
-      <c r="D72" s="16">
-        <v>0</v>
-      </c>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" ht="16.5" spans="1:7">
-      <c r="A73" s="15">
-        <f t="shared" si="3"/>
-        <v>10140405</v>
-      </c>
-      <c r="B73" s="15">
-        <v>101404</v>
-      </c>
-      <c r="C73" s="16">
-        <v>5</v>
-      </c>
-      <c r="D73" s="16">
-        <v>0</v>
-      </c>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="74" ht="16.5" spans="1:7">
-      <c r="A74" s="15">
-        <f t="shared" si="3"/>
-        <v>10140506</v>
-      </c>
-      <c r="B74" s="15">
-        <v>101405</v>
-      </c>
-      <c r="C74" s="16">
-        <v>6</v>
-      </c>
-      <c r="D74" s="16">
-        <v>0</v>
-      </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75" ht="16.5" spans="1:7">
-      <c r="A75" s="15">
-        <f t="shared" si="3"/>
-        <v>10140607</v>
-      </c>
-      <c r="B75" s="15">
-        <v>101406</v>
-      </c>
-      <c r="C75" s="16">
-        <v>7</v>
-      </c>
-      <c r="D75" s="16">
-        <v>0</v>
-      </c>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" ht="16.5" spans="1:7">
-      <c r="A76" s="15">
-        <f t="shared" si="3"/>
-        <v>10140708</v>
-      </c>
-      <c r="B76" s="15">
-        <v>101407</v>
-      </c>
-      <c r="C76" s="16">
-        <v>8</v>
-      </c>
-      <c r="D76" s="16">
-        <v>0</v>
-      </c>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="77" ht="16.5" spans="1:7">
-      <c r="A77" s="15">
-        <f t="shared" si="3"/>
-        <v>10140809</v>
-      </c>
-      <c r="B77" s="15">
-        <v>101408</v>
-      </c>
-      <c r="C77" s="16">
-        <v>9</v>
-      </c>
-      <c r="D77" s="16">
-        <v>0</v>
-      </c>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="78" ht="16.5" spans="1:7">
-      <c r="A78" s="15">
-        <f t="shared" si="3"/>
-        <v>10140910</v>
-      </c>
-      <c r="B78" s="15">
-        <v>101409</v>
-      </c>
-      <c r="C78" s="16">
-        <v>10</v>
-      </c>
-      <c r="D78" s="16">
-        <v>0</v>
-      </c>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="79" ht="16.5" spans="1:7">
-      <c r="A79" s="15">
-        <f t="shared" si="3"/>
-        <v>10141011</v>
-      </c>
-      <c r="B79" s="15">
-        <v>101410</v>
-      </c>
-      <c r="C79" s="16">
-        <v>11</v>
-      </c>
-      <c r="D79" s="16">
-        <v>0</v>
-      </c>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="80" ht="16.5" spans="1:7">
-      <c r="A80" s="15">
-        <f t="shared" si="3"/>
-        <v>10141112</v>
-      </c>
-      <c r="B80" s="15">
-        <v>101411</v>
-      </c>
-      <c r="C80" s="16">
-        <v>12</v>
-      </c>
-      <c r="D80" s="16">
-        <v>1</v>
-      </c>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="81" ht="16.5" spans="1:7">
-      <c r="A81" s="15">
-        <f t="shared" si="3"/>
-        <v>10141213</v>
-      </c>
-      <c r="B81" s="15">
-        <v>101412</v>
-      </c>
-      <c r="C81" s="16">
-        <v>13</v>
-      </c>
-      <c r="D81" s="16">
-        <v>2</v>
-      </c>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16" t="s">
-        <v>117</v>
-      </c>
+      <c r="E116" s="17"/>
+      <c r="F116" s="17"/>
+      <c r="G116" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="J116" s="13"/>
+      <c r="K116" s="13"/>
+      <c r="L116" s="13"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2">

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="160">
   <si>
     <t>图标</t>
   </si>
@@ -132,6 +132,9 @@
     <t>消除后变化元素ID</t>
   </si>
   <si>
+    <t>图标上显示多语言ID</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -154,6 +157,9 @@
   </si>
   <si>
     <t>postChangeElementId</t>
+  </si>
+  <si>
+    <t>languageID</t>
   </si>
   <si>
     <t>mykd_TB_0.png</t>
@@ -769,13 +775,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1663,17 +1669,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
     <col min="5" max="5" width="18.7416666666667" customWidth="1"/>
-    <col min="6" max="6" width="19.1666666666667" customWidth="1"/>
-    <col min="7" max="7" width="24.1666666666667" customWidth="1"/>
+    <col min="6" max="7" width="19.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="24.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="16.5" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1695,49 +1701,58 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:7">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:7">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:8">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
@@ -1745,8 +1760,9 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:12">
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:13">
       <c r="A5" s="4">
         <f>B5*100+C5</f>
         <v>10010001</v>
@@ -1761,17 +1777,18 @@
         <v>0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="5">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5">
         <v>9</v>
       </c>
-      <c r="J5" s="13"/>
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
-    </row>
-    <row r="6" ht="16.5" spans="1:12">
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:13">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A46" si="0">B6*100+C6</f>
         <v>10010002</v>
@@ -1786,17 +1803,18 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="5">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5">
         <v>10</v>
       </c>
-      <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:12">
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:13">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>10010003</v>
@@ -1811,17 +1829,18 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="13"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:12">
+      <c r="M7" s="13"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:13">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>10010004</v>
@@ -1836,17 +1855,18 @@
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="13"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:12">
+      <c r="M8" s="13"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:13">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>10010005</v>
@@ -1861,17 +1881,18 @@
         <v>0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="13"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:12">
+      <c r="M9" s="13"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:13">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>10010006</v>
@@ -1886,17 +1907,18 @@
         <v>0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="13"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:12">
+      <c r="M10" s="13"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:13">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>10010007</v>
@@ -1911,17 +1933,18 @@
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" s="13"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:12">
+      <c r="M11" s="13"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:13">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>10010008</v>
@@ -1936,17 +1959,18 @@
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="13"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:12">
+      <c r="M12" s="13"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:13">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>10010009</v>
@@ -1961,17 +1985,18 @@
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="13"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:12">
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:13">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10010010</v>
@@ -1986,17 +2011,18 @@
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="13"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:12">
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:13">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>10010011</v>
@@ -2011,17 +2037,18 @@
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="13"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:12">
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:13">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>10010012</v>
@@ -2036,17 +2063,18 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="13"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:12">
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:13">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>10010013</v>
@@ -2061,17 +2089,18 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="13"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:12">
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:13">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>10010014</v>
@@ -2086,17 +2115,18 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="13"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:12">
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:13">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>10010015</v>
@@ -2111,17 +2141,18 @@
         <v>2</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J19" s="13"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:12">
+      <c r="M19" s="13"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:13">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>10010016</v>
@@ -2136,17 +2167,18 @@
         <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="13"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:12">
+      <c r="M20" s="13"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:13">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>10010017</v>
@@ -2161,17 +2193,18 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="13"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:12">
+      <c r="M21" s="13"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:13">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>10010018</v>
@@ -2186,17 +2219,18 @@
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J22" s="13"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:12">
+      <c r="M22" s="13"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:13">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>10010019</v>
@@ -2211,17 +2245,18 @@
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J23" s="13"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:12">
+      <c r="M23" s="13"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:13">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>10010020</v>
@@ -2236,17 +2271,18 @@
         <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J24" s="13"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:12">
+      <c r="M24" s="13"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:13">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>10010021</v>
@@ -2261,17 +2297,18 @@
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="13"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:12">
+      <c r="M25" s="13"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:13">
       <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>10010022</v>
@@ -2286,17 +2323,18 @@
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="J26" s="13"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:12">
+      <c r="M26" s="13"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:13">
       <c r="A27" s="6">
         <f t="shared" si="0"/>
         <v>10010028</v>
@@ -2311,17 +2349,18 @@
         <v>2</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F27" s="7"/>
-      <c r="G27" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J27" s="13"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:12">
+      <c r="M27" s="13"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:13">
       <c r="A28" s="6">
         <f t="shared" si="0"/>
         <v>10010030</v>
@@ -2336,17 +2375,18 @@
         <v>2</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F28" s="7"/>
-      <c r="G28" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J28" s="13"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:12">
+      <c r="M28" s="13"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:13">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>10030001</v>
@@ -2362,14 +2402,15 @@
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="8"/>
-      <c r="G29" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J29" s="13"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:12">
+      <c r="M29" s="13"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:13">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
         <v>10030002</v>
@@ -2385,14 +2426,15 @@
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="8"/>
-      <c r="G30" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J30" s="13"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="9" t="s">
+        <v>61</v>
+      </c>
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:12">
+      <c r="M30" s="13"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:13">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
         <v>10030003</v>
@@ -2408,14 +2450,15 @@
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="8"/>
-      <c r="G31" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J31" s="13"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:12">
+      <c r="M31" s="13"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:13">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
         <v>10030004</v>
@@ -2431,14 +2474,15 @@
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="8"/>
-      <c r="G32" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J32" s="13"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="9" t="s">
+        <v>29</v>
+      </c>
       <c r="K32" s="13"/>
       <c r="L32" s="13"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:12">
+      <c r="M32" s="13"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:13">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
         <v>10030005</v>
@@ -2454,14 +2498,15 @@
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="8"/>
-      <c r="G33" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J33" s="13"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="K33" s="13"/>
       <c r="L33" s="13"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:12">
+      <c r="M33" s="13"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:13">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
         <v>10030006</v>
@@ -2477,14 +2522,15 @@
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="8"/>
-      <c r="G34" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J34" s="13"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="9" t="s">
+        <v>64</v>
+      </c>
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
-    </row>
-    <row r="35" ht="16.5" spans="1:12">
+      <c r="M34" s="13"/>
+    </row>
+    <row r="35" ht="16.5" spans="1:13">
       <c r="A35" s="8">
         <f t="shared" si="0"/>
         <v>10030007</v>
@@ -2500,14 +2546,15 @@
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J35" s="13"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="K35" s="13"/>
       <c r="L35" s="13"/>
-    </row>
-    <row r="36" ht="16.5" spans="1:12">
+      <c r="M35" s="13"/>
+    </row>
+    <row r="36" ht="16.5" spans="1:13">
       <c r="A36" s="8">
         <f t="shared" si="0"/>
         <v>10030008</v>
@@ -2523,14 +2570,15 @@
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="8"/>
-      <c r="G36" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="13"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
-    </row>
-    <row r="37" ht="16.5" spans="1:12">
+      <c r="M36" s="13"/>
+    </row>
+    <row r="37" ht="16.5" spans="1:13">
       <c r="A37" s="8">
         <f t="shared" si="0"/>
         <v>10030009</v>
@@ -2546,14 +2594,15 @@
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="8"/>
-      <c r="G37" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J37" s="13"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="9" t="s">
+        <v>67</v>
+      </c>
       <c r="K37" s="13"/>
       <c r="L37" s="13"/>
-    </row>
-    <row r="38" ht="16.5" spans="1:12">
+      <c r="M37" s="13"/>
+    </row>
+    <row r="38" ht="16.5" spans="1:13">
       <c r="A38" s="8">
         <f t="shared" si="0"/>
         <v>10030010</v>
@@ -2569,16 +2618,17 @@
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="8"/>
-      <c r="G38" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="L38" s="13"/>
-    </row>
-    <row r="39" ht="16.5" spans="1:13">
+      <c r="G38" s="8"/>
+      <c r="H38" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="M38" s="13"/>
+    </row>
+    <row r="39" ht="16.5" spans="1:14">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
         <v>10030021</v>
@@ -2594,31 +2644,34 @@
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="8"/>
-      <c r="G39" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,C39,H39)</f>
+      <c r="G39" s="8">
+        <v>100300021</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,C39,I39)</f>
         <v>21_1</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>6</v>
       </c>
-      <c r="K39">
-        <v>1</v>
-      </c>
-      <c r="L39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,C39,K39,J39)</f>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,C39,L39,K39)</f>
         <v>21_1_6</v>
       </c>
-      <c r="M39" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="16.5" spans="1:14">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
         <v>10030022</v>
@@ -2634,32 +2687,35 @@
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="8"/>
-      <c r="G40" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40" t="str">
-        <f t="shared" ref="I40:I58" si="1">_xlfn.TEXTJOIN("_",TRUE,C40,H40)</f>
+      <c r="G40" s="8">
+        <v>100300022</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" ref="J40:J58" si="1">_xlfn.TEXTJOIN("_",TRUE,C40,I40)</f>
         <v>22_1</v>
       </c>
-      <c r="J40" s="13">
+      <c r="K40" s="13">
         <v>9</v>
       </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="L40" t="str">
-        <f t="shared" ref="L40:L58" si="2">_xlfn.TEXTJOIN("_",TRUE,C40,K40,J40)</f>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40" t="str">
+        <f t="shared" ref="M40:M58" si="2">_xlfn.TEXTJOIN("_",TRUE,C40,L40,K40)</f>
         <v>22_1_9</v>
       </c>
-      <c r="M40" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,I39:I58)</f>
+      <c r="N40" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,J39:J58)</f>
         <v>21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="16.5" spans="1:12">
+    <row r="41" customFormat="1" ht="16.5" spans="1:13">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
         <v>10030023</v>
@@ -2675,28 +2731,31 @@
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="8"/>
-      <c r="G41" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41" t="str">
+      <c r="G41" s="8">
+        <v>100300023</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41" t="str">
         <f t="shared" si="1"/>
         <v>23_1</v>
       </c>
-      <c r="J41" s="13">
+      <c r="K41" s="13">
         <v>12</v>
       </c>
-      <c r="K41">
-        <v>1</v>
-      </c>
-      <c r="L41" t="str">
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41" t="str">
         <f t="shared" si="2"/>
         <v>23_1_12</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="16.5" spans="1:13">
+    <row r="42" customFormat="1" ht="16.5" spans="1:14">
       <c r="A42" s="8">
         <f t="shared" si="0"/>
         <v>10030024</v>
@@ -2712,31 +2771,34 @@
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="8"/>
-      <c r="G42" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H42">
-        <v>1</v>
-      </c>
-      <c r="I42" t="str">
+      <c r="G42" s="8">
+        <v>100300024</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42" t="str">
         <f t="shared" si="1"/>
         <v>24_1</v>
       </c>
-      <c r="J42" s="13">
+      <c r="K42" s="13">
         <v>15</v>
       </c>
-      <c r="K42">
-        <v>1</v>
-      </c>
-      <c r="L42" t="str">
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42" t="str">
         <f t="shared" si="2"/>
         <v>24_1_15</v>
       </c>
-      <c r="M42" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N42" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="16.5" spans="1:14">
       <c r="A43" s="8">
         <f t="shared" si="0"/>
         <v>10030025</v>
@@ -2752,32 +2814,35 @@
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="8"/>
-      <c r="G43" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43" t="str">
+      <c r="G43" s="8">
+        <v>100300025</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43" t="str">
         <f t="shared" si="1"/>
         <v>25_1</v>
       </c>
-      <c r="J43" s="13">
+      <c r="K43" s="13">
         <v>21</v>
       </c>
-      <c r="K43">
-        <v>1</v>
-      </c>
-      <c r="L43" t="str">
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43" t="str">
         <f t="shared" si="2"/>
         <v>25_1_21</v>
       </c>
-      <c r="M43" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,L39:L58)</f>
+      <c r="N43" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,M39:M58)</f>
         <v>21_1_6|22_1_9|23_1_12|24_1_15|25_1_21|26_1_24|27_1_32|28_1_38|29_1_49|30_1_58|31_1_68|32_1_79|33_1_85|34_1_96|35_1_105|36_1_110|37_1_125|38_1_138|39_1_150|40_1_210</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="16.5" spans="1:12">
+    <row r="44" customFormat="1" ht="16.5" spans="1:13">
       <c r="A44" s="8">
         <f t="shared" si="0"/>
         <v>10030026</v>
@@ -2793,28 +2858,31 @@
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="8"/>
-      <c r="G44" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44" t="str">
+      <c r="G44" s="8">
+        <v>100300026</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44" t="str">
         <f t="shared" si="1"/>
         <v>26_1</v>
       </c>
-      <c r="J44" s="13">
+      <c r="K44" s="13">
         <v>24</v>
       </c>
-      <c r="K44">
-        <v>1</v>
-      </c>
-      <c r="L44" t="str">
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44" t="str">
         <f t="shared" si="2"/>
         <v>26_1_24</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:12">
+    <row r="45" customFormat="1" ht="16.5" spans="1:13">
       <c r="A45" s="8">
         <f t="shared" si="0"/>
         <v>10030027</v>
@@ -2830,28 +2898,31 @@
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="8"/>
-      <c r="G45" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45" t="str">
+      <c r="G45" s="8">
+        <v>100300027</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45" t="str">
         <f t="shared" si="1"/>
         <v>27_1</v>
       </c>
-      <c r="J45" s="13">
+      <c r="K45" s="13">
         <v>32</v>
       </c>
-      <c r="K45">
-        <v>1</v>
-      </c>
-      <c r="L45" t="str">
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45" t="str">
         <f t="shared" si="2"/>
         <v>27_1_32</v>
       </c>
     </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:12">
+    <row r="46" customFormat="1" ht="16.5" spans="1:13">
       <c r="A46" s="8">
         <f t="shared" si="0"/>
         <v>10030028</v>
@@ -2867,28 +2938,31 @@
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="8"/>
-      <c r="G46" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46" t="str">
+      <c r="G46" s="8">
+        <v>100300028</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46" t="str">
         <f t="shared" si="1"/>
         <v>28_1</v>
       </c>
-      <c r="J46" s="13">
+      <c r="K46" s="13">
         <v>38</v>
       </c>
-      <c r="K46">
-        <v>1</v>
-      </c>
-      <c r="L46" t="str">
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46" t="str">
         <f t="shared" si="2"/>
         <v>28_1_38</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:12">
+    <row r="47" customFormat="1" ht="16.5" spans="1:13">
       <c r="A47" s="8">
         <f t="shared" ref="A47:A59" si="3">B47*100+C47</f>
         <v>10030029</v>
@@ -2904,28 +2978,31 @@
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="8"/>
-      <c r="G47" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47" t="str">
+      <c r="G47" s="8">
+        <v>100300029</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47" t="str">
         <f t="shared" si="1"/>
         <v>29_1</v>
       </c>
-      <c r="J47" s="13">
+      <c r="K47" s="13">
         <v>49</v>
       </c>
-      <c r="K47">
-        <v>1</v>
-      </c>
-      <c r="L47" t="str">
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47" t="str">
         <f t="shared" si="2"/>
         <v>29_1_49</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="16.5" spans="1:12">
+    <row r="48" customFormat="1" ht="16.5" spans="1:13">
       <c r="A48" s="8">
         <f t="shared" si="3"/>
         <v>10030030</v>
@@ -2941,28 +3018,31 @@
       </c>
       <c r="E48" s="10"/>
       <c r="F48" s="8"/>
-      <c r="G48" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48" t="str">
+      <c r="G48" s="8">
+        <v>100300030</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48" t="str">
         <f t="shared" si="1"/>
         <v>30_1</v>
       </c>
-      <c r="J48" s="13">
+      <c r="K48" s="13">
         <v>58</v>
       </c>
-      <c r="K48">
-        <v>1</v>
-      </c>
-      <c r="L48" t="str">
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48" t="str">
         <f t="shared" si="2"/>
         <v>30_1_58</v>
       </c>
     </row>
-    <row r="49" customFormat="1" ht="16.5" spans="1:12">
+    <row r="49" customFormat="1" ht="16.5" spans="1:13">
       <c r="A49" s="8">
         <f t="shared" si="3"/>
         <v>10030031</v>
@@ -2978,28 +3058,31 @@
       </c>
       <c r="E49" s="10"/>
       <c r="F49" s="8"/>
-      <c r="G49" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49" t="str">
+      <c r="G49" s="8">
+        <v>100300031</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49" t="str">
         <f t="shared" si="1"/>
         <v>31_1</v>
       </c>
-      <c r="J49" s="13">
+      <c r="K49" s="13">
         <v>68</v>
       </c>
-      <c r="K49">
-        <v>1</v>
-      </c>
-      <c r="L49" t="str">
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49" t="str">
         <f t="shared" si="2"/>
         <v>31_1_68</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="16.5" spans="1:12">
+    <row r="50" customFormat="1" ht="16.5" spans="1:13">
       <c r="A50" s="8">
         <f t="shared" si="3"/>
         <v>10030032</v>
@@ -3015,28 +3098,31 @@
       </c>
       <c r="E50" s="10"/>
       <c r="F50" s="8"/>
-      <c r="G50" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50" t="str">
+      <c r="G50" s="8">
+        <v>100300032</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50" t="str">
         <f t="shared" si="1"/>
         <v>32_1</v>
       </c>
-      <c r="J50" s="13">
+      <c r="K50" s="13">
         <v>79</v>
       </c>
-      <c r="K50">
-        <v>1</v>
-      </c>
-      <c r="L50" t="str">
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="M50" t="str">
         <f t="shared" si="2"/>
         <v>32_1_79</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="16.5" spans="1:12">
+    <row r="51" customFormat="1" ht="16.5" spans="1:13">
       <c r="A51" s="8">
         <f t="shared" si="3"/>
         <v>10030033</v>
@@ -3052,28 +3138,31 @@
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="8"/>
-      <c r="G51" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H51">
-        <v>1</v>
-      </c>
-      <c r="I51" t="str">
+      <c r="G51" s="8">
+        <v>100300033</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51" t="str">
         <f t="shared" si="1"/>
         <v>33_1</v>
       </c>
-      <c r="J51" s="13">
+      <c r="K51" s="13">
         <v>85</v>
       </c>
-      <c r="K51">
-        <v>1</v>
-      </c>
-      <c r="L51" t="str">
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51" t="str">
         <f t="shared" si="2"/>
         <v>33_1_85</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="16.5" spans="1:12">
+    <row r="52" customFormat="1" ht="16.5" spans="1:13">
       <c r="A52" s="8">
         <f t="shared" si="3"/>
         <v>10030034</v>
@@ -3089,28 +3178,31 @@
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="8"/>
-      <c r="G52" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H52">
-        <v>1</v>
-      </c>
-      <c r="I52" t="str">
+      <c r="G52" s="8">
+        <v>100300034</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52" t="str">
         <f t="shared" si="1"/>
         <v>34_1</v>
       </c>
-      <c r="J52" s="13">
+      <c r="K52" s="13">
         <v>96</v>
       </c>
-      <c r="K52">
-        <v>1</v>
-      </c>
-      <c r="L52" t="str">
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52" t="str">
         <f t="shared" si="2"/>
         <v>34_1_96</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="16.5" spans="1:12">
+    <row r="53" customFormat="1" ht="16.5" spans="1:13">
       <c r="A53" s="8">
         <f t="shared" si="3"/>
         <v>10030035</v>
@@ -3126,28 +3218,31 @@
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="8"/>
-      <c r="G53" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H53">
-        <v>1</v>
-      </c>
-      <c r="I53" t="str">
+      <c r="G53" s="8">
+        <v>100300035</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53" t="str">
         <f t="shared" si="1"/>
         <v>35_1</v>
       </c>
-      <c r="J53" s="13">
+      <c r="K53" s="13">
         <v>105</v>
       </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53" t="str">
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53" t="str">
         <f t="shared" si="2"/>
         <v>35_1_105</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="16.5" spans="1:12">
+    <row r="54" customFormat="1" ht="16.5" spans="1:13">
       <c r="A54" s="8">
         <f t="shared" si="3"/>
         <v>10030036</v>
@@ -3163,28 +3258,31 @@
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="8"/>
-      <c r="G54" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H54">
-        <v>1</v>
-      </c>
-      <c r="I54" t="str">
+      <c r="G54" s="8">
+        <v>100300036</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54" t="str">
         <f t="shared" si="1"/>
         <v>36_1</v>
       </c>
-      <c r="J54" s="13">
+      <c r="K54" s="13">
         <v>110</v>
       </c>
-      <c r="K54">
-        <v>1</v>
-      </c>
-      <c r="L54" t="str">
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54" t="str">
         <f t="shared" si="2"/>
         <v>36_1_110</v>
       </c>
     </row>
-    <row r="55" customFormat="1" ht="16.5" spans="1:12">
+    <row r="55" customFormat="1" ht="16.5" spans="1:13">
       <c r="A55" s="8">
         <f t="shared" si="3"/>
         <v>10030037</v>
@@ -3200,28 +3298,31 @@
       </c>
       <c r="E55" s="10"/>
       <c r="F55" s="8"/>
-      <c r="G55" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="I55" t="str">
+      <c r="G55" s="8">
+        <v>100300037</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55" t="str">
         <f t="shared" si="1"/>
         <v>37_1</v>
       </c>
-      <c r="J55" s="13">
+      <c r="K55" s="13">
         <v>125</v>
       </c>
-      <c r="K55">
-        <v>1</v>
-      </c>
-      <c r="L55" t="str">
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55" t="str">
         <f t="shared" si="2"/>
         <v>37_1_125</v>
       </c>
     </row>
-    <row r="56" customFormat="1" ht="16.5" spans="1:12">
+    <row r="56" customFormat="1" ht="16.5" spans="1:13">
       <c r="A56" s="8">
         <f t="shared" si="3"/>
         <v>10030038</v>
@@ -3237,28 +3338,31 @@
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="8"/>
-      <c r="G56" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
-      <c r="I56" t="str">
+      <c r="G56" s="8">
+        <v>100300038</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56" t="str">
         <f t="shared" si="1"/>
         <v>38_1</v>
       </c>
-      <c r="J56" s="13">
+      <c r="K56" s="13">
         <v>138</v>
       </c>
-      <c r="K56">
-        <v>1</v>
-      </c>
-      <c r="L56" t="str">
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56" t="str">
         <f t="shared" si="2"/>
         <v>38_1_138</v>
       </c>
     </row>
-    <row r="57" customFormat="1" ht="16.5" spans="1:12">
+    <row r="57" customFormat="1" ht="16.5" spans="1:13">
       <c r="A57" s="8">
         <f t="shared" si="3"/>
         <v>10030039</v>
@@ -3274,28 +3378,31 @@
       </c>
       <c r="E57" s="10"/>
       <c r="F57" s="8"/>
-      <c r="G57" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H57">
-        <v>1</v>
-      </c>
-      <c r="I57" t="str">
+      <c r="G57" s="8">
+        <v>100300039</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57" t="str">
         <f t="shared" si="1"/>
         <v>39_1</v>
       </c>
-      <c r="J57" s="13">
+      <c r="K57" s="13">
         <v>150</v>
       </c>
-      <c r="K57">
-        <v>1</v>
-      </c>
-      <c r="L57" t="str">
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57" t="str">
         <f t="shared" si="2"/>
         <v>39_1_150</v>
       </c>
     </row>
-    <row r="58" customFormat="1" ht="16.5" spans="1:12">
+    <row r="58" customFormat="1" ht="16.5" spans="1:13">
       <c r="A58" s="8">
         <f t="shared" si="3"/>
         <v>10030040</v>
@@ -3311,28 +3418,31 @@
       </c>
       <c r="E58" s="10"/>
       <c r="F58" s="8"/>
-      <c r="G58" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H58">
-        <v>1</v>
-      </c>
-      <c r="I58" t="str">
+      <c r="G58" s="8">
+        <v>100300040</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58" t="str">
         <f t="shared" si="1"/>
         <v>40_1</v>
       </c>
-      <c r="J58" s="13">
+      <c r="K58" s="13">
         <v>210</v>
       </c>
-      <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="L58" t="str">
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58" t="str">
         <f t="shared" si="2"/>
         <v>40_1_210</v>
       </c>
     </row>
-    <row r="59" customFormat="1" ht="16.5" spans="1:12">
+    <row r="59" customFormat="1" ht="16.5" spans="1:13">
       <c r="A59" s="8">
         <f t="shared" si="3"/>
         <v>10030099</v>
@@ -3348,14 +3458,15 @@
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="8"/>
-      <c r="G59" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="J59" s="13"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="9" t="s">
+        <v>92</v>
+      </c>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
-    </row>
-    <row r="60" ht="16.5" spans="1:12">
+      <c r="M59" s="13"/>
+    </row>
+    <row r="60" ht="16.5" spans="1:13">
       <c r="A60" s="11">
         <f t="shared" ref="A60:A89" si="4">B60*100+C60</f>
         <v>10070001</v>
@@ -3370,17 +3481,18 @@
         <v>0</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F60" s="12"/>
-      <c r="G60" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="J60" s="13"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12" t="s">
+        <v>94</v>
+      </c>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
-    </row>
-    <row r="61" ht="16.5" spans="1:12">
+      <c r="M60" s="13"/>
+    </row>
+    <row r="61" ht="16.5" spans="1:13">
       <c r="A61" s="11">
         <f t="shared" si="4"/>
         <v>10070002</v>
@@ -3395,17 +3507,18 @@
         <v>0</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F61" s="12"/>
-      <c r="G61" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J61" s="13"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
-    </row>
-    <row r="62" ht="16.5" spans="1:12">
+      <c r="M61" s="13"/>
+    </row>
+    <row r="62" ht="16.5" spans="1:13">
       <c r="A62" s="11">
         <f t="shared" si="4"/>
         <v>10070003</v>
@@ -3420,17 +3533,18 @@
         <v>0</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F62" s="12"/>
-      <c r="G62" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J62" s="13"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
-    </row>
-    <row r="63" ht="16.5" spans="1:12">
+      <c r="M62" s="13"/>
+    </row>
+    <row r="63" ht="16.5" spans="1:13">
       <c r="A63" s="11">
         <f t="shared" si="4"/>
         <v>10070004</v>
@@ -3445,17 +3559,18 @@
         <v>0</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F63" s="12"/>
-      <c r="G63" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="J63" s="13"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
-    </row>
-    <row r="64" ht="16.5" spans="1:12">
+      <c r="M63" s="13"/>
+    </row>
+    <row r="64" ht="16.5" spans="1:13">
       <c r="A64" s="11">
         <f t="shared" si="4"/>
         <v>10070005</v>
@@ -3470,17 +3585,18 @@
         <v>0</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F64" s="12"/>
-      <c r="G64" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="J64" s="13"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
-    </row>
-    <row r="65" ht="16.5" spans="1:12">
+      <c r="M64" s="13"/>
+    </row>
+    <row r="65" ht="16.5" spans="1:13">
       <c r="A65" s="11">
         <f t="shared" si="4"/>
         <v>10070006</v>
@@ -3495,17 +3611,18 @@
         <v>0</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F65" s="12"/>
-      <c r="G65" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J65" s="13"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="K65" s="13"/>
       <c r="L65" s="13"/>
-    </row>
-    <row r="66" ht="16.5" spans="1:12">
+      <c r="M65" s="13"/>
+    </row>
+    <row r="66" ht="16.5" spans="1:13">
       <c r="A66" s="11">
         <f t="shared" si="4"/>
         <v>10070007</v>
@@ -3520,17 +3637,18 @@
         <v>0</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F66" s="12"/>
-      <c r="G66" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J66" s="13"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12" t="s">
+        <v>106</v>
+      </c>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
-    </row>
-    <row r="67" ht="16.5" spans="1:12">
+      <c r="M66" s="13"/>
+    </row>
+    <row r="67" ht="16.5" spans="1:13">
       <c r="A67" s="11">
         <f t="shared" si="4"/>
         <v>10070008</v>
@@ -3545,17 +3663,18 @@
         <v>0</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F67" s="12"/>
-      <c r="G67" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="J67" s="13"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
-    </row>
-    <row r="68" ht="16.5" spans="1:12">
+      <c r="M67" s="13"/>
+    </row>
+    <row r="68" ht="16.5" spans="1:13">
       <c r="A68" s="11">
         <f t="shared" si="4"/>
         <v>10070009</v>
@@ -3570,17 +3689,18 @@
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F68" s="12"/>
-      <c r="G68" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J68" s="13"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
-    </row>
-    <row r="69" ht="16.5" spans="1:12">
+      <c r="M68" s="13"/>
+    </row>
+    <row r="69" ht="16.5" spans="1:13">
       <c r="A69" s="11">
         <f t="shared" si="4"/>
         <v>10070010</v>
@@ -3595,17 +3715,18 @@
         <v>2</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F69" s="12"/>
-      <c r="G69" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="J69" s="13"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="K69" s="13"/>
       <c r="L69" s="13"/>
-    </row>
-    <row r="70" ht="16.5" spans="1:12">
+      <c r="M69" s="13"/>
+    </row>
+    <row r="70" ht="16.5" spans="1:13">
       <c r="A70" s="14">
         <f t="shared" si="4"/>
         <v>10070011</v>
@@ -3620,19 +3741,20 @@
         <v>0</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F70" s="12">
         <v>9</v>
       </c>
-      <c r="G70" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="J70" s="13"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="15" t="s">
+        <v>114</v>
+      </c>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
-    </row>
-    <row r="71" ht="16.5" spans="1:12">
+      <c r="M70" s="13"/>
+    </row>
+    <row r="71" ht="16.5" spans="1:13">
       <c r="A71" s="14">
         <f t="shared" si="4"/>
         <v>10070012</v>
@@ -3647,19 +3769,20 @@
         <v>0</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F71" s="12">
         <v>9</v>
       </c>
-      <c r="G71" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="J71" s="13"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
-    </row>
-    <row r="72" ht="16.5" spans="1:12">
+      <c r="M71" s="13"/>
+    </row>
+    <row r="72" ht="16.5" spans="1:13">
       <c r="A72" s="14">
         <f t="shared" si="4"/>
         <v>10070013</v>
@@ -3674,19 +3797,20 @@
         <v>0</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F72" s="12">
         <v>9</v>
       </c>
-      <c r="G72" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="J72" s="13"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
-    </row>
-    <row r="73" ht="16.5" spans="1:12">
+      <c r="M72" s="13"/>
+    </row>
+    <row r="73" ht="16.5" spans="1:13">
       <c r="A73" s="14">
         <f t="shared" si="4"/>
         <v>10070014</v>
@@ -3701,19 +3825,20 @@
         <v>0</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F73" s="12">
         <v>9</v>
       </c>
-      <c r="G73" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="J73" s="13"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="K73" s="13"/>
       <c r="L73" s="13"/>
-    </row>
-    <row r="74" ht="16.5" spans="1:12">
+      <c r="M73" s="13"/>
+    </row>
+    <row r="74" ht="16.5" spans="1:13">
       <c r="A74" s="14">
         <f t="shared" si="4"/>
         <v>10070015</v>
@@ -3728,19 +3853,20 @@
         <v>0</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F74" s="12">
         <v>9</v>
       </c>
-      <c r="G74" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="J74" s="13"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="15" t="s">
+        <v>122</v>
+      </c>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
-    </row>
-    <row r="75" ht="16.5" spans="1:12">
+      <c r="M74" s="13"/>
+    </row>
+    <row r="75" ht="16.5" spans="1:13">
       <c r="A75" s="14">
         <f t="shared" si="4"/>
         <v>10070016</v>
@@ -3755,19 +3881,20 @@
         <v>0</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F75" s="12">
         <v>9</v>
       </c>
-      <c r="G75" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="J75" s="13"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
-    </row>
-    <row r="76" ht="16.5" spans="1:12">
+      <c r="M75" s="13"/>
+    </row>
+    <row r="76" ht="16.5" spans="1:13">
       <c r="A76" s="14">
         <f t="shared" si="4"/>
         <v>10070017</v>
@@ -3782,19 +3909,20 @@
         <v>0</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F76" s="12">
         <v>9</v>
       </c>
-      <c r="G76" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="J76" s="13"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="15" t="s">
+        <v>126</v>
+      </c>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
-    </row>
-    <row r="77" ht="16.5" spans="1:12">
+      <c r="M76" s="13"/>
+    </row>
+    <row r="77" ht="16.5" spans="1:13">
       <c r="A77" s="14">
         <f t="shared" si="4"/>
         <v>10070018</v>
@@ -3809,19 +3937,20 @@
         <v>0</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F77" s="12">
         <v>9</v>
       </c>
-      <c r="G77" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="J77" s="13"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
-    </row>
-    <row r="78" ht="16.5" spans="1:12">
+      <c r="M77" s="13"/>
+    </row>
+    <row r="78" ht="16.5" spans="1:13">
       <c r="A78" s="8">
         <f t="shared" si="4"/>
         <v>10120001</v>
@@ -3837,14 +3966,15 @@
       </c>
       <c r="E78" s="10"/>
       <c r="F78" s="8"/>
-      <c r="G78" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="J78" s="13"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="9" t="s">
+        <v>129</v>
+      </c>
       <c r="K78" s="13"/>
       <c r="L78" s="13"/>
-    </row>
-    <row r="79" ht="16.5" spans="1:12">
+      <c r="M78" s="13"/>
+    </row>
+    <row r="79" ht="16.5" spans="1:13">
       <c r="A79" s="8">
         <f t="shared" si="4"/>
         <v>10120002</v>
@@ -3860,14 +3990,15 @@
       </c>
       <c r="E79" s="10"/>
       <c r="F79" s="8"/>
-      <c r="G79" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="J79" s="13"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="9" t="s">
+        <v>130</v>
+      </c>
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
-    </row>
-    <row r="80" ht="16.5" spans="1:12">
+      <c r="M79" s="13"/>
+    </row>
+    <row r="80" ht="16.5" spans="1:13">
       <c r="A80" s="8">
         <f t="shared" si="4"/>
         <v>10120003</v>
@@ -3883,14 +4014,15 @@
       </c>
       <c r="E80" s="10"/>
       <c r="F80" s="8"/>
-      <c r="G80" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J80" s="13"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="9" t="s">
+        <v>131</v>
+      </c>
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
-    </row>
-    <row r="81" ht="16.5" spans="1:12">
+      <c r="M80" s="13"/>
+    </row>
+    <row r="81" ht="16.5" spans="1:13">
       <c r="A81" s="8">
         <f t="shared" si="4"/>
         <v>10120004</v>
@@ -3906,14 +4038,15 @@
       </c>
       <c r="E81" s="10"/>
       <c r="F81" s="8"/>
-      <c r="G81" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="J81" s="13"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="9" t="s">
+        <v>132</v>
+      </c>
       <c r="K81" s="13"/>
       <c r="L81" s="13"/>
-    </row>
-    <row r="82" ht="16.5" spans="1:12">
+      <c r="M81" s="13"/>
+    </row>
+    <row r="82" ht="16.5" spans="1:13">
       <c r="A82" s="8">
         <f t="shared" si="4"/>
         <v>10120005</v>
@@ -3929,14 +4062,15 @@
       </c>
       <c r="E82" s="10"/>
       <c r="F82" s="8"/>
-      <c r="G82" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="J82" s="13"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="9" t="s">
+        <v>133</v>
+      </c>
       <c r="K82" s="13"/>
       <c r="L82" s="13"/>
-    </row>
-    <row r="83" ht="16.5" spans="1:12">
+      <c r="M82" s="13"/>
+    </row>
+    <row r="83" ht="16.5" spans="1:13">
       <c r="A83" s="8">
         <f t="shared" si="4"/>
         <v>10120006</v>
@@ -3952,14 +4086,15 @@
       </c>
       <c r="E83" s="10"/>
       <c r="F83" s="8"/>
-      <c r="G83" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="J83" s="13"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="9" t="s">
+        <v>134</v>
+      </c>
       <c r="K83" s="13"/>
       <c r="L83" s="13"/>
-    </row>
-    <row r="84" ht="16.5" spans="1:12">
+      <c r="M83" s="13"/>
+    </row>
+    <row r="84" ht="16.5" spans="1:13">
       <c r="A84" s="8">
         <f t="shared" ref="A84:A103" si="5">B84*100+C84</f>
         <v>10120009</v>
@@ -3975,14 +4110,15 @@
       </c>
       <c r="E84" s="10"/>
       <c r="F84" s="8"/>
-      <c r="G84" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="J84" s="13"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
-    </row>
-    <row r="85" ht="16.5" spans="1:12">
+      <c r="M84" s="13"/>
+    </row>
+    <row r="85" ht="16.5" spans="1:13">
       <c r="A85" s="8">
         <f t="shared" si="5"/>
         <v>10120010</v>
@@ -3998,14 +4134,15 @@
       </c>
       <c r="E85" s="10"/>
       <c r="F85" s="8"/>
-      <c r="G85" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J85" s="13"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="9" t="s">
+        <v>110</v>
+      </c>
       <c r="K85" s="13"/>
       <c r="L85" s="13"/>
-    </row>
-    <row r="86" ht="16.5" spans="1:12">
+      <c r="M85" s="13"/>
+    </row>
+    <row r="86" ht="16.5" spans="1:13">
       <c r="A86" s="8">
         <f t="shared" si="5"/>
         <v>10120011</v>
@@ -4021,14 +4158,15 @@
       </c>
       <c r="E86" s="10"/>
       <c r="F86" s="8"/>
-      <c r="G86" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J86" s="13"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="K86" s="13"/>
       <c r="L86" s="13"/>
-    </row>
-    <row r="87" ht="16.5" spans="1:12">
+      <c r="M86" s="13"/>
+    </row>
+    <row r="87" ht="16.5" spans="1:13">
       <c r="A87" s="8">
         <f t="shared" si="5"/>
         <v>10120012</v>
@@ -4044,14 +4182,15 @@
       </c>
       <c r="E87" s="10"/>
       <c r="F87" s="8"/>
-      <c r="G87" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="J87" s="13"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="9" t="s">
+        <v>137</v>
+      </c>
       <c r="K87" s="13"/>
       <c r="L87" s="13"/>
-    </row>
-    <row r="88" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M87" s="13"/>
+    </row>
+    <row r="88" customFormat="1" ht="16.5" spans="1:13">
       <c r="A88" s="8">
         <f t="shared" si="5"/>
         <v>10120013</v>
@@ -4067,14 +4206,15 @@
       </c>
       <c r="E88" s="10"/>
       <c r="F88" s="8"/>
-      <c r="G88" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="J88" s="13"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="9" t="s">
+        <v>138</v>
+      </c>
       <c r="K88" s="13"/>
       <c r="L88" s="13"/>
-    </row>
-    <row r="89" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M88" s="13"/>
+    </row>
+    <row r="89" customFormat="1" ht="16.5" spans="1:13">
       <c r="A89" s="8">
         <f t="shared" si="5"/>
         <v>10120014</v>
@@ -4090,14 +4230,15 @@
       </c>
       <c r="E89" s="10"/>
       <c r="F89" s="8"/>
-      <c r="G89" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="J89" s="13"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="9" t="s">
+        <v>139</v>
+      </c>
       <c r="K89" s="13"/>
       <c r="L89" s="13"/>
-    </row>
-    <row r="90" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M89" s="13"/>
+    </row>
+    <row r="90" customFormat="1" ht="16.5" spans="1:13">
       <c r="A90" s="8">
         <f t="shared" si="5"/>
         <v>10120015</v>
@@ -4113,14 +4254,15 @@
       </c>
       <c r="E90" s="10"/>
       <c r="F90" s="8"/>
-      <c r="G90" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="J90" s="13"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="9" t="s">
+        <v>140</v>
+      </c>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
-    </row>
-    <row r="91" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M90" s="13"/>
+    </row>
+    <row r="91" customFormat="1" ht="16.5" spans="1:13">
       <c r="A91" s="8">
         <f t="shared" si="5"/>
         <v>10120016</v>
@@ -4136,14 +4278,15 @@
       </c>
       <c r="E91" s="10"/>
       <c r="F91" s="8"/>
-      <c r="G91" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="J91" s="13"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="9" t="s">
+        <v>141</v>
+      </c>
       <c r="K91" s="13"/>
       <c r="L91" s="13"/>
-    </row>
-    <row r="92" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M91" s="13"/>
+    </row>
+    <row r="92" customFormat="1" ht="16.5" spans="1:13">
       <c r="A92" s="8">
         <f t="shared" si="5"/>
         <v>10120021</v>
@@ -4159,14 +4302,15 @@
       </c>
       <c r="E92" s="10"/>
       <c r="F92" s="8"/>
-      <c r="G92" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="J92" s="13"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="K92" s="13"/>
       <c r="L92" s="13"/>
-    </row>
-    <row r="93" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M92" s="13"/>
+    </row>
+    <row r="93" customFormat="1" ht="16.5" spans="1:13">
       <c r="A93" s="8">
         <f t="shared" si="5"/>
         <v>10120022</v>
@@ -4182,14 +4326,15 @@
       </c>
       <c r="E93" s="10"/>
       <c r="F93" s="8"/>
-      <c r="G93" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="J93" s="13"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="9" t="s">
+        <v>143</v>
+      </c>
       <c r="K93" s="13"/>
       <c r="L93" s="13"/>
-    </row>
-    <row r="94" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M93" s="13"/>
+    </row>
+    <row r="94" customFormat="1" ht="16.5" spans="1:13">
       <c r="A94" s="8">
         <f t="shared" si="5"/>
         <v>10120023</v>
@@ -4205,14 +4350,15 @@
       </c>
       <c r="E94" s="10"/>
       <c r="F94" s="8"/>
-      <c r="G94" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="J94" s="13"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="K94" s="13"/>
       <c r="L94" s="13"/>
-    </row>
-    <row r="95" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M94" s="13"/>
+    </row>
+    <row r="95" customFormat="1" ht="16.5" spans="1:13">
       <c r="A95" s="8">
         <f t="shared" si="5"/>
         <v>10120024</v>
@@ -4228,14 +4374,15 @@
       </c>
       <c r="E95" s="10"/>
       <c r="F95" s="8"/>
-      <c r="G95" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="J95" s="13"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="9" t="s">
+        <v>145</v>
+      </c>
       <c r="K95" s="13"/>
       <c r="L95" s="13"/>
-    </row>
-    <row r="96" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M95" s="13"/>
+    </row>
+    <row r="96" customFormat="1" ht="16.5" spans="1:13">
       <c r="A96" s="8">
         <f t="shared" si="5"/>
         <v>10120025</v>
@@ -4251,14 +4398,15 @@
       </c>
       <c r="E96" s="10"/>
       <c r="F96" s="8"/>
-      <c r="G96" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J96" s="13"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="9" t="s">
+        <v>146</v>
+      </c>
       <c r="K96" s="13"/>
       <c r="L96" s="13"/>
-    </row>
-    <row r="97" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M96" s="13"/>
+    </row>
+    <row r="97" customFormat="1" ht="16.5" spans="1:13">
       <c r="A97" s="8">
         <f t="shared" si="5"/>
         <v>10120026</v>
@@ -4274,14 +4422,15 @@
       </c>
       <c r="E97" s="10"/>
       <c r="F97" s="8"/>
-      <c r="G97" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="J97" s="13"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="9" t="s">
+        <v>147</v>
+      </c>
       <c r="K97" s="13"/>
       <c r="L97" s="13"/>
-    </row>
-    <row r="98" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M97" s="13"/>
+    </row>
+    <row r="98" customFormat="1" ht="16.5" spans="1:13">
       <c r="A98" s="8">
         <f t="shared" si="5"/>
         <v>10120031</v>
@@ -4297,14 +4446,15 @@
       </c>
       <c r="E98" s="10"/>
       <c r="F98" s="8"/>
-      <c r="G98" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J98" s="13"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="9" t="s">
+        <v>148</v>
+      </c>
       <c r="K98" s="13"/>
       <c r="L98" s="13"/>
-    </row>
-    <row r="99" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M98" s="13"/>
+    </row>
+    <row r="99" customFormat="1" ht="16.5" spans="1:13">
       <c r="A99" s="8">
         <f t="shared" si="5"/>
         <v>10120032</v>
@@ -4320,14 +4470,15 @@
       </c>
       <c r="E99" s="10"/>
       <c r="F99" s="8"/>
-      <c r="G99" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="J99" s="13"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="9" t="s">
+        <v>149</v>
+      </c>
       <c r="K99" s="13"/>
       <c r="L99" s="13"/>
-    </row>
-    <row r="100" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M99" s="13"/>
+    </row>
+    <row r="100" customFormat="1" ht="16.5" spans="1:13">
       <c r="A100" s="8">
         <f t="shared" si="5"/>
         <v>10120033</v>
@@ -4343,14 +4494,15 @@
       </c>
       <c r="E100" s="10"/>
       <c r="F100" s="8"/>
-      <c r="G100" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="J100" s="13"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="9" t="s">
+        <v>150</v>
+      </c>
       <c r="K100" s="13"/>
       <c r="L100" s="13"/>
-    </row>
-    <row r="101" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M100" s="13"/>
+    </row>
+    <row r="101" customFormat="1" ht="16.5" spans="1:13">
       <c r="A101" s="8">
         <f t="shared" si="5"/>
         <v>10120034</v>
@@ -4366,14 +4518,15 @@
       </c>
       <c r="E101" s="10"/>
       <c r="F101" s="8"/>
-      <c r="G101" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="J101" s="13"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="9" t="s">
+        <v>151</v>
+      </c>
       <c r="K101" s="13"/>
       <c r="L101" s="13"/>
-    </row>
-    <row r="102" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M101" s="13"/>
+    </row>
+    <row r="102" customFormat="1" ht="16.5" spans="1:13">
       <c r="A102" s="8">
         <f t="shared" si="5"/>
         <v>10120035</v>
@@ -4389,14 +4542,15 @@
       </c>
       <c r="E102" s="10"/>
       <c r="F102" s="8"/>
-      <c r="G102" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="J102" s="13"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="9" t="s">
+        <v>152</v>
+      </c>
       <c r="K102" s="13"/>
       <c r="L102" s="13"/>
-    </row>
-    <row r="103" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M102" s="13"/>
+    </row>
+    <row r="103" customFormat="1" ht="16.5" spans="1:13">
       <c r="A103" s="8">
         <f t="shared" si="5"/>
         <v>10120036</v>
@@ -4412,14 +4566,15 @@
       </c>
       <c r="E103" s="10"/>
       <c r="F103" s="8"/>
-      <c r="G103" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J103" s="13"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="9" t="s">
+        <v>153</v>
+      </c>
       <c r="K103" s="13"/>
       <c r="L103" s="13"/>
-    </row>
-    <row r="104" ht="16.5" spans="1:12">
+      <c r="M103" s="13"/>
+    </row>
+    <row r="104" ht="16.5" spans="1:13">
       <c r="A104" s="16">
         <f t="shared" ref="A104:A116" si="6">B104*100+C104</f>
         <v>10140001</v>
@@ -4435,14 +4590,15 @@
       </c>
       <c r="E104" s="17"/>
       <c r="F104" s="17"/>
-      <c r="G104" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="J104" s="13"/>
+      <c r="G104" s="17"/>
+      <c r="H104" s="17" t="s">
+        <v>154</v>
+      </c>
       <c r="K104" s="13"/>
       <c r="L104" s="13"/>
-    </row>
-    <row r="105" ht="16.5" spans="1:12">
+      <c r="M104" s="13"/>
+    </row>
+    <row r="105" ht="16.5" spans="1:13">
       <c r="A105" s="16">
         <f t="shared" si="6"/>
         <v>10140102</v>
@@ -4458,14 +4614,15 @@
       </c>
       <c r="E105" s="17"/>
       <c r="F105" s="17"/>
-      <c r="G105" s="17">
+      <c r="G105" s="17"/>
+      <c r="H105" s="17">
         <v>9</v>
       </c>
-      <c r="J105" s="13"/>
       <c r="K105" s="13"/>
       <c r="L105" s="13"/>
-    </row>
-    <row r="106" ht="16.5" spans="1:12">
+      <c r="M105" s="13"/>
+    </row>
+    <row r="106" ht="16.5" spans="1:13">
       <c r="A106" s="16">
         <f t="shared" si="6"/>
         <v>10140203</v>
@@ -4481,14 +4638,15 @@
       </c>
       <c r="E106" s="17"/>
       <c r="F106" s="17"/>
-      <c r="G106" s="17">
+      <c r="G106" s="17"/>
+      <c r="H106" s="17">
         <v>10</v>
       </c>
-      <c r="J106" s="13"/>
       <c r="K106" s="13"/>
       <c r="L106" s="13"/>
-    </row>
-    <row r="107" ht="16.5" spans="1:12">
+      <c r="M106" s="13"/>
+    </row>
+    <row r="107" ht="16.5" spans="1:13">
       <c r="A107" s="16">
         <f t="shared" si="6"/>
         <v>10140304</v>
@@ -4504,14 +4662,15 @@
       </c>
       <c r="E107" s="17"/>
       <c r="F107" s="17"/>
-      <c r="G107" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J107" s="13"/>
+      <c r="G107" s="17"/>
+      <c r="H107" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="K107" s="13"/>
       <c r="L107" s="13"/>
-    </row>
-    <row r="108" ht="16.5" spans="1:12">
+      <c r="M107" s="13"/>
+    </row>
+    <row r="108" ht="16.5" spans="1:13">
       <c r="A108" s="16">
         <f t="shared" si="6"/>
         <v>10140405</v>
@@ -4527,14 +4686,15 @@
       </c>
       <c r="E108" s="17"/>
       <c r="F108" s="17"/>
-      <c r="G108" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J108" s="13"/>
+      <c r="G108" s="17"/>
+      <c r="H108" s="17" t="s">
+        <v>21</v>
+      </c>
       <c r="K108" s="13"/>
       <c r="L108" s="13"/>
-    </row>
-    <row r="109" ht="16.5" spans="1:12">
+      <c r="M108" s="13"/>
+    </row>
+    <row r="109" ht="16.5" spans="1:13">
       <c r="A109" s="16">
         <f t="shared" si="6"/>
         <v>10140506</v>
@@ -4550,14 +4710,15 @@
       </c>
       <c r="E109" s="17"/>
       <c r="F109" s="17"/>
-      <c r="G109" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="J109" s="13"/>
+      <c r="G109" s="17"/>
+      <c r="H109" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="K109" s="13"/>
       <c r="L109" s="13"/>
-    </row>
-    <row r="110" ht="16.5" spans="1:12">
+      <c r="M109" s="13"/>
+    </row>
+    <row r="110" ht="16.5" spans="1:13">
       <c r="A110" s="16">
         <f t="shared" si="6"/>
         <v>10140607</v>
@@ -4573,14 +4734,15 @@
       </c>
       <c r="E110" s="17"/>
       <c r="F110" s="17"/>
-      <c r="G110" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J110" s="13"/>
+      <c r="G110" s="17"/>
+      <c r="H110" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="K110" s="13"/>
       <c r="L110" s="13"/>
-    </row>
-    <row r="111" ht="16.5" spans="1:12">
+      <c r="M110" s="13"/>
+    </row>
+    <row r="111" ht="16.5" spans="1:13">
       <c r="A111" s="16">
         <f t="shared" si="6"/>
         <v>10140708</v>
@@ -4596,14 +4758,15 @@
       </c>
       <c r="E111" s="17"/>
       <c r="F111" s="17"/>
-      <c r="G111" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="J111" s="13"/>
+      <c r="G111" s="17"/>
+      <c r="H111" s="17" t="s">
+        <v>155</v>
+      </c>
       <c r="K111" s="13"/>
       <c r="L111" s="13"/>
-    </row>
-    <row r="112" ht="16.5" spans="1:12">
+      <c r="M111" s="13"/>
+    </row>
+    <row r="112" ht="16.5" spans="1:13">
       <c r="A112" s="16">
         <f t="shared" si="6"/>
         <v>10140809</v>
@@ -4619,14 +4782,15 @@
       </c>
       <c r="E112" s="17"/>
       <c r="F112" s="17"/>
-      <c r="G112" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="J112" s="13"/>
+      <c r="G112" s="17"/>
+      <c r="H112" s="17" t="s">
+        <v>156</v>
+      </c>
       <c r="K112" s="13"/>
       <c r="L112" s="13"/>
-    </row>
-    <row r="113" ht="16.5" spans="1:12">
+      <c r="M112" s="13"/>
+    </row>
+    <row r="113" ht="16.5" spans="1:13">
       <c r="A113" s="16">
         <f t="shared" si="6"/>
         <v>10140910</v>
@@ -4642,14 +4806,15 @@
       </c>
       <c r="E113" s="17"/>
       <c r="F113" s="17"/>
-      <c r="G113" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J113" s="13"/>
+      <c r="G113" s="17"/>
+      <c r="H113" s="17" t="s">
+        <v>157</v>
+      </c>
       <c r="K113" s="13"/>
       <c r="L113" s="13"/>
-    </row>
-    <row r="114" ht="16.5" spans="1:12">
+      <c r="M113" s="13"/>
+    </row>
+    <row r="114" ht="16.5" spans="1:13">
       <c r="A114" s="16">
         <f t="shared" si="6"/>
         <v>10141011</v>
@@ -4665,14 +4830,15 @@
       </c>
       <c r="E114" s="17"/>
       <c r="F114" s="17"/>
-      <c r="G114" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="J114" s="13"/>
+      <c r="G114" s="17"/>
+      <c r="H114" s="17" t="s">
+        <v>158</v>
+      </c>
       <c r="K114" s="13"/>
       <c r="L114" s="13"/>
-    </row>
-    <row r="115" ht="16.5" spans="1:12">
+      <c r="M114" s="13"/>
+    </row>
+    <row r="115" ht="16.5" spans="1:13">
       <c r="A115" s="16">
         <f t="shared" si="6"/>
         <v>10141112</v>
@@ -4688,14 +4854,15 @@
       </c>
       <c r="E115" s="17"/>
       <c r="F115" s="17"/>
-      <c r="G115" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="J115" s="13"/>
+      <c r="G115" s="17"/>
+      <c r="H115" s="17" t="s">
+        <v>110</v>
+      </c>
       <c r="K115" s="13"/>
       <c r="L115" s="13"/>
-    </row>
-    <row r="116" ht="16.5" spans="1:12">
+      <c r="M115" s="13"/>
+    </row>
+    <row r="116" ht="16.5" spans="1:13">
       <c r="A116" s="16">
         <f t="shared" si="6"/>
         <v>10141213</v>
@@ -4711,30 +4878,31 @@
       </c>
       <c r="E116" s="17"/>
       <c r="F116" s="17"/>
-      <c r="G116" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="J116" s="13"/>
+      <c r="G116" s="17"/>
+      <c r="H116" s="17" t="s">
+        <v>159</v>
+      </c>
       <c r="K116" s="13"/>
       <c r="L116" s="13"/>
+      <c r="M116" s="13"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F2:G2">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD($B2,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="F3:G3">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B3,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:D4 G1:G4">
+  <conditionalFormatting sqref="A1:D4 H1:H4">
     <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:F1 E2:E3 E4:F4">
+  <conditionalFormatting sqref="E1:G1 E2:E3 E4:G4">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="160">
   <si>
     <t>图标</t>
   </si>
@@ -132,6 +132,9 @@
     <t>消除后变化元素ID</t>
   </si>
   <si>
+    <t>图标上显示多语言ID</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -154,6 +157,9 @@
   </si>
   <si>
     <t>postChangeElementId</t>
+  </si>
+  <si>
+    <t>languageID</t>
   </si>
   <si>
     <t>mykd_TB_0.png</t>
@@ -769,12 +775,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -782,12 +782,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1663,17 +1669,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
     <col min="5" max="5" width="18.7416666666667" customWidth="1"/>
-    <col min="6" max="6" width="19.1666666666667" customWidth="1"/>
-    <col min="7" max="7" width="24.1666666666667" customWidth="1"/>
+    <col min="6" max="7" width="19.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="24.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="16.5" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1695,49 +1701,58 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:7">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:7">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:8">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
@@ -1745,8 +1760,9 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:12">
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:13">
       <c r="A5" s="4">
         <f>B5*100+C5</f>
         <v>10010001</v>
@@ -1761,17 +1777,18 @@
         <v>0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="5">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5">
         <v>9</v>
       </c>
-      <c r="J5" s="13"/>
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
-    </row>
-    <row r="6" ht="16.5" spans="1:12">
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:13">
       <c r="A6" s="4">
         <f t="shared" ref="A6:A46" si="0">B6*100+C6</f>
         <v>10010002</v>
@@ -1786,17 +1803,18 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="5">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5">
         <v>10</v>
       </c>
-      <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:12">
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:13">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>10010003</v>
@@ -1811,17 +1829,18 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="13"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:12">
+      <c r="M7" s="13"/>
+    </row>
+    <row r="8" ht="16.5" spans="1:13">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>10010004</v>
@@ -1836,17 +1855,18 @@
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="13"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:12">
+      <c r="M8" s="13"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:13">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>10010005</v>
@@ -1861,17 +1881,18 @@
         <v>0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="13"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:12">
+      <c r="M9" s="13"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:13">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>10010006</v>
@@ -1886,17 +1907,18 @@
         <v>0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="13"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:12">
+      <c r="M10" s="13"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:13">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>10010007</v>
@@ -1911,17 +1933,18 @@
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" s="13"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:12">
+      <c r="M11" s="13"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:13">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>10010008</v>
@@ -1936,17 +1959,18 @@
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="13"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:12">
+      <c r="M12" s="13"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:13">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>10010009</v>
@@ -1961,17 +1985,18 @@
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="13"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:12">
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:13">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10010010</v>
@@ -1986,17 +2011,18 @@
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="13"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:12">
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:13">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>10010011</v>
@@ -2011,17 +2037,18 @@
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="13"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:12">
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:13">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>10010012</v>
@@ -2036,17 +2063,18 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="13"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:12">
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:13">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>10010013</v>
@@ -2061,17 +2089,18 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="13"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:12">
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:13">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>10010014</v>
@@ -2086,17 +2115,18 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="13"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:12">
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:13">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>10010015</v>
@@ -2111,17 +2141,18 @@
         <v>2</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J19" s="13"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:12">
+      <c r="M19" s="13"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:13">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>10010016</v>
@@ -2136,17 +2167,18 @@
         <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="13"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:12">
+      <c r="M20" s="13"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:13">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>10010017</v>
@@ -2161,17 +2193,18 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="13"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:12">
+      <c r="M21" s="13"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:13">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>10010018</v>
@@ -2186,17 +2219,18 @@
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J22" s="13"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:12">
+      <c r="M22" s="13"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:13">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>10010019</v>
@@ -2211,17 +2245,18 @@
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J23" s="13"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:12">
+      <c r="M23" s="13"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:13">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>10010020</v>
@@ -2236,17 +2271,18 @@
         <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J24" s="13"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:12">
+      <c r="M24" s="13"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:13">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>10010021</v>
@@ -2261,17 +2297,18 @@
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="13"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:12">
+      <c r="M25" s="13"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:13">
       <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>10010022</v>
@@ -2286,17 +2323,18 @@
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="J26" s="13"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:12">
+      <c r="M26" s="13"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:13">
       <c r="A27" s="6">
         <f t="shared" si="0"/>
         <v>10010028</v>
@@ -2311,17 +2349,18 @@
         <v>2</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F27" s="7"/>
-      <c r="G27" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J27" s="13"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:12">
+      <c r="M27" s="13"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:13">
       <c r="A28" s="6">
         <f t="shared" si="0"/>
         <v>10010030</v>
@@ -2336,17 +2375,18 @@
         <v>2</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F28" s="7"/>
-      <c r="G28" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J28" s="13"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:12">
+      <c r="M28" s="13"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:13">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>10030001</v>
@@ -2362,14 +2402,15 @@
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="8"/>
-      <c r="G29" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J29" s="13"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="9" t="s">
+        <v>60</v>
+      </c>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:12">
+      <c r="M29" s="13"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:13">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
         <v>10030002</v>
@@ -2385,14 +2426,15 @@
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="8"/>
-      <c r="G30" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J30" s="13"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="9" t="s">
+        <v>61</v>
+      </c>
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:12">
+      <c r="M30" s="13"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:13">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
         <v>10030003</v>
@@ -2408,14 +2450,15 @@
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="8"/>
-      <c r="G31" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J31" s="13"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="9" t="s">
+        <v>62</v>
+      </c>
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:12">
+      <c r="M31" s="13"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:13">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
         <v>10030004</v>
@@ -2431,14 +2474,15 @@
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="8"/>
-      <c r="G32" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J32" s="13"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="9" t="s">
+        <v>29</v>
+      </c>
       <c r="K32" s="13"/>
       <c r="L32" s="13"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:12">
+      <c r="M32" s="13"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:13">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
         <v>10030005</v>
@@ -2454,14 +2498,15 @@
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="8"/>
-      <c r="G33" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J33" s="13"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="K33" s="13"/>
       <c r="L33" s="13"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:12">
+      <c r="M33" s="13"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:13">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
         <v>10030006</v>
@@ -2477,14 +2522,15 @@
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="8"/>
-      <c r="G34" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J34" s="13"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="9" t="s">
+        <v>64</v>
+      </c>
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
-    </row>
-    <row r="35" ht="16.5" spans="1:12">
+      <c r="M34" s="13"/>
+    </row>
+    <row r="35" ht="16.5" spans="1:13">
       <c r="A35" s="8">
         <f t="shared" si="0"/>
         <v>10030007</v>
@@ -2500,14 +2546,17 @@
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J35" s="13"/>
+      <c r="G35" s="8">
+        <v>100300107</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="K35" s="13"/>
       <c r="L35" s="13"/>
-    </row>
-    <row r="36" ht="16.5" spans="1:12">
+      <c r="M35" s="13"/>
+    </row>
+    <row r="36" ht="16.5" spans="1:13">
       <c r="A36" s="8">
         <f t="shared" si="0"/>
         <v>10030008</v>
@@ -2523,14 +2572,17 @@
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="8"/>
-      <c r="G36" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="13"/>
+      <c r="G36" s="8">
+        <v>100300108</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
-    </row>
-    <row r="37" ht="16.5" spans="1:12">
+      <c r="M36" s="13"/>
+    </row>
+    <row r="37" ht="16.5" spans="1:13">
       <c r="A37" s="8">
         <f t="shared" si="0"/>
         <v>10030009</v>
@@ -2546,14 +2598,17 @@
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="8"/>
-      <c r="G37" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J37" s="13"/>
+      <c r="G37" s="8">
+        <v>100300109</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>67</v>
+      </c>
       <c r="K37" s="13"/>
       <c r="L37" s="13"/>
-    </row>
-    <row r="38" ht="16.5" spans="1:12">
+      <c r="M37" s="13"/>
+    </row>
+    <row r="38" ht="16.5" spans="1:13">
       <c r="A38" s="8">
         <f t="shared" si="0"/>
         <v>10030010</v>
@@ -2569,16 +2624,19 @@
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="8"/>
-      <c r="G38" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="L38" s="13"/>
-    </row>
-    <row r="39" ht="16.5" spans="1:13">
+      <c r="G38" s="8">
+        <v>100300110</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="M38" s="13"/>
+    </row>
+    <row r="39" ht="16.5" spans="1:14">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
         <v>10030021</v>
@@ -2594,31 +2652,34 @@
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="8"/>
-      <c r="G39" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,C39,H39)</f>
+      <c r="G39" s="8">
+        <v>100300021</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,C39,I39)</f>
         <v>21_1</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>6</v>
       </c>
-      <c r="K39">
-        <v>1</v>
-      </c>
-      <c r="L39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,C39,K39,J39)</f>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,C39,L39,K39)</f>
         <v>21_1_6</v>
       </c>
-      <c r="M39" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="16.5" spans="1:14">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
         <v>10030022</v>
@@ -2634,32 +2695,35 @@
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="8"/>
-      <c r="G40" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
-      <c r="I40" t="str">
-        <f t="shared" ref="I40:I58" si="1">_xlfn.TEXTJOIN("_",TRUE,C40,H40)</f>
+      <c r="G40" s="8">
+        <v>100300022</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" ref="J40:J58" si="1">_xlfn.TEXTJOIN("_",TRUE,C40,I40)</f>
         <v>22_1</v>
       </c>
-      <c r="J40" s="13">
+      <c r="K40" s="13">
         <v>9</v>
       </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="L40" t="str">
-        <f t="shared" ref="L40:L58" si="2">_xlfn.TEXTJOIN("_",TRUE,C40,K40,J40)</f>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40" t="str">
+        <f t="shared" ref="M40:M58" si="2">_xlfn.TEXTJOIN("_",TRUE,C40,L40,K40)</f>
         <v>22_1_9</v>
       </c>
-      <c r="M40" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,I39:I58)</f>
+      <c r="N40" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,J39:J58)</f>
         <v>21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="16.5" spans="1:12">
+    <row r="41" customFormat="1" ht="16.5" spans="1:13">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
         <v>10030023</v>
@@ -2675,28 +2739,31 @@
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="8"/>
-      <c r="G41" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H41">
-        <v>1</v>
-      </c>
-      <c r="I41" t="str">
+      <c r="G41" s="8">
+        <v>100300023</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41" t="str">
         <f t="shared" si="1"/>
         <v>23_1</v>
       </c>
-      <c r="J41" s="13">
+      <c r="K41" s="13">
         <v>12</v>
       </c>
-      <c r="K41">
-        <v>1</v>
-      </c>
-      <c r="L41" t="str">
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41" t="str">
         <f t="shared" si="2"/>
         <v>23_1_12</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="16.5" spans="1:13">
+    <row r="42" customFormat="1" ht="16.5" spans="1:14">
       <c r="A42" s="8">
         <f t="shared" si="0"/>
         <v>10030024</v>
@@ -2712,31 +2779,34 @@
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="8"/>
-      <c r="G42" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H42">
-        <v>1</v>
-      </c>
-      <c r="I42" t="str">
+      <c r="G42" s="8">
+        <v>100300024</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42" t="str">
         <f t="shared" si="1"/>
         <v>24_1</v>
       </c>
-      <c r="J42" s="13">
+      <c r="K42" s="13">
         <v>15</v>
       </c>
-      <c r="K42">
-        <v>1</v>
-      </c>
-      <c r="L42" t="str">
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42" t="str">
         <f t="shared" si="2"/>
         <v>24_1_15</v>
       </c>
-      <c r="M42" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N42" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="16.5" spans="1:14">
       <c r="A43" s="8">
         <f t="shared" si="0"/>
         <v>10030025</v>
@@ -2752,32 +2822,35 @@
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="8"/>
-      <c r="G43" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43" t="str">
+      <c r="G43" s="8">
+        <v>100300025</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43" t="str">
         <f t="shared" si="1"/>
         <v>25_1</v>
       </c>
-      <c r="J43" s="13">
+      <c r="K43" s="13">
         <v>21</v>
       </c>
-      <c r="K43">
-        <v>1</v>
-      </c>
-      <c r="L43" t="str">
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="M43" t="str">
         <f t="shared" si="2"/>
         <v>25_1_21</v>
       </c>
-      <c r="M43" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,L39:L58)</f>
+      <c r="N43" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,M39:M58)</f>
         <v>21_1_6|22_1_9|23_1_12|24_1_15|25_1_21|26_1_24|27_1_32|28_1_38|29_1_49|30_1_58|31_1_68|32_1_79|33_1_85|34_1_96|35_1_105|36_1_110|37_1_125|38_1_138|39_1_150|40_1_210</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="16.5" spans="1:12">
+    <row r="44" customFormat="1" ht="16.5" spans="1:13">
       <c r="A44" s="8">
         <f t="shared" si="0"/>
         <v>10030026</v>
@@ -2793,28 +2866,31 @@
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="8"/>
-      <c r="G44" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44" t="str">
+      <c r="G44" s="8">
+        <v>100300026</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44" t="str">
         <f t="shared" si="1"/>
         <v>26_1</v>
       </c>
-      <c r="J44" s="13">
+      <c r="K44" s="13">
         <v>24</v>
       </c>
-      <c r="K44">
-        <v>1</v>
-      </c>
-      <c r="L44" t="str">
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44" t="str">
         <f t="shared" si="2"/>
         <v>26_1_24</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:12">
+    <row r="45" customFormat="1" ht="16.5" spans="1:13">
       <c r="A45" s="8">
         <f t="shared" si="0"/>
         <v>10030027</v>
@@ -2830,28 +2906,31 @@
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="8"/>
-      <c r="G45" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H45">
-        <v>1</v>
-      </c>
-      <c r="I45" t="str">
+      <c r="G45" s="8">
+        <v>100300027</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45" t="str">
         <f t="shared" si="1"/>
         <v>27_1</v>
       </c>
-      <c r="J45" s="13">
+      <c r="K45" s="13">
         <v>32</v>
       </c>
-      <c r="K45">
-        <v>1</v>
-      </c>
-      <c r="L45" t="str">
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45" t="str">
         <f t="shared" si="2"/>
         <v>27_1_32</v>
       </c>
     </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:12">
+    <row r="46" customFormat="1" ht="16.5" spans="1:13">
       <c r="A46" s="8">
         <f t="shared" si="0"/>
         <v>10030028</v>
@@ -2867,28 +2946,31 @@
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="8"/>
-      <c r="G46" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H46">
-        <v>1</v>
-      </c>
-      <c r="I46" t="str">
+      <c r="G46" s="8">
+        <v>100300028</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46" t="str">
         <f t="shared" si="1"/>
         <v>28_1</v>
       </c>
-      <c r="J46" s="13">
+      <c r="K46" s="13">
         <v>38</v>
       </c>
-      <c r="K46">
-        <v>1</v>
-      </c>
-      <c r="L46" t="str">
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46" t="str">
         <f t="shared" si="2"/>
         <v>28_1_38</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:12">
+    <row r="47" customFormat="1" ht="16.5" spans="1:13">
       <c r="A47" s="8">
         <f t="shared" ref="A47:A59" si="3">B47*100+C47</f>
         <v>10030029</v>
@@ -2904,28 +2986,31 @@
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="8"/>
-      <c r="G47" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47" t="str">
+      <c r="G47" s="8">
+        <v>100300029</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47" t="str">
         <f t="shared" si="1"/>
         <v>29_1</v>
       </c>
-      <c r="J47" s="13">
+      <c r="K47" s="13">
         <v>49</v>
       </c>
-      <c r="K47">
-        <v>1</v>
-      </c>
-      <c r="L47" t="str">
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47" t="str">
         <f t="shared" si="2"/>
         <v>29_1_49</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="16.5" spans="1:12">
+    <row r="48" customFormat="1" ht="16.5" spans="1:13">
       <c r="A48" s="8">
         <f t="shared" si="3"/>
         <v>10030030</v>
@@ -2941,28 +3026,31 @@
       </c>
       <c r="E48" s="10"/>
       <c r="F48" s="8"/>
-      <c r="G48" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H48">
-        <v>1</v>
-      </c>
-      <c r="I48" t="str">
+      <c r="G48" s="8">
+        <v>100300030</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48" t="str">
         <f t="shared" si="1"/>
         <v>30_1</v>
       </c>
-      <c r="J48" s="13">
+      <c r="K48" s="13">
         <v>58</v>
       </c>
-      <c r="K48">
-        <v>1</v>
-      </c>
-      <c r="L48" t="str">
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48" t="str">
         <f t="shared" si="2"/>
         <v>30_1_58</v>
       </c>
     </row>
-    <row r="49" customFormat="1" ht="16.5" spans="1:12">
+    <row r="49" customFormat="1" ht="16.5" spans="1:13">
       <c r="A49" s="8">
         <f t="shared" si="3"/>
         <v>10030031</v>
@@ -2978,28 +3066,31 @@
       </c>
       <c r="E49" s="10"/>
       <c r="F49" s="8"/>
-      <c r="G49" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49" t="str">
+      <c r="G49" s="8">
+        <v>100300031</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49" t="str">
         <f t="shared" si="1"/>
         <v>31_1</v>
       </c>
-      <c r="J49" s="13">
+      <c r="K49" s="13">
         <v>68</v>
       </c>
-      <c r="K49">
-        <v>1</v>
-      </c>
-      <c r="L49" t="str">
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49" t="str">
         <f t="shared" si="2"/>
         <v>31_1_68</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="16.5" spans="1:12">
+    <row r="50" customFormat="1" ht="16.5" spans="1:13">
       <c r="A50" s="8">
         <f t="shared" si="3"/>
         <v>10030032</v>
@@ -3015,28 +3106,31 @@
       </c>
       <c r="E50" s="10"/>
       <c r="F50" s="8"/>
-      <c r="G50" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50" t="str">
+      <c r="G50" s="8">
+        <v>100300032</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50" t="str">
         <f t="shared" si="1"/>
         <v>32_1</v>
       </c>
-      <c r="J50" s="13">
+      <c r="K50" s="13">
         <v>79</v>
       </c>
-      <c r="K50">
-        <v>1</v>
-      </c>
-      <c r="L50" t="str">
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="M50" t="str">
         <f t="shared" si="2"/>
         <v>32_1_79</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="16.5" spans="1:12">
+    <row r="51" customFormat="1" ht="16.5" spans="1:13">
       <c r="A51" s="8">
         <f t="shared" si="3"/>
         <v>10030033</v>
@@ -3052,28 +3146,31 @@
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="8"/>
-      <c r="G51" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H51">
-        <v>1</v>
-      </c>
-      <c r="I51" t="str">
+      <c r="G51" s="8">
+        <v>100300033</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51" t="str">
         <f t="shared" si="1"/>
         <v>33_1</v>
       </c>
-      <c r="J51" s="13">
+      <c r="K51" s="13">
         <v>85</v>
       </c>
-      <c r="K51">
-        <v>1</v>
-      </c>
-      <c r="L51" t="str">
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51" t="str">
         <f t="shared" si="2"/>
         <v>33_1_85</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="16.5" spans="1:12">
+    <row r="52" customFormat="1" ht="16.5" spans="1:13">
       <c r="A52" s="8">
         <f t="shared" si="3"/>
         <v>10030034</v>
@@ -3089,28 +3186,31 @@
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="8"/>
-      <c r="G52" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H52">
-        <v>1</v>
-      </c>
-      <c r="I52" t="str">
+      <c r="G52" s="8">
+        <v>100300034</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52" t="str">
         <f t="shared" si="1"/>
         <v>34_1</v>
       </c>
-      <c r="J52" s="13">
+      <c r="K52" s="13">
         <v>96</v>
       </c>
-      <c r="K52">
-        <v>1</v>
-      </c>
-      <c r="L52" t="str">
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52" t="str">
         <f t="shared" si="2"/>
         <v>34_1_96</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="16.5" spans="1:12">
+    <row r="53" customFormat="1" ht="16.5" spans="1:13">
       <c r="A53" s="8">
         <f t="shared" si="3"/>
         <v>10030035</v>
@@ -3126,28 +3226,31 @@
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="8"/>
-      <c r="G53" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H53">
-        <v>1</v>
-      </c>
-      <c r="I53" t="str">
+      <c r="G53" s="8">
+        <v>100300035</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53" t="str">
         <f t="shared" si="1"/>
         <v>35_1</v>
       </c>
-      <c r="J53" s="13">
+      <c r="K53" s="13">
         <v>105</v>
       </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53" t="str">
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53" t="str">
         <f t="shared" si="2"/>
         <v>35_1_105</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="16.5" spans="1:12">
+    <row r="54" customFormat="1" ht="16.5" spans="1:13">
       <c r="A54" s="8">
         <f t="shared" si="3"/>
         <v>10030036</v>
@@ -3163,28 +3266,31 @@
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="8"/>
-      <c r="G54" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H54">
-        <v>1</v>
-      </c>
-      <c r="I54" t="str">
+      <c r="G54" s="8">
+        <v>100300036</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54" t="str">
         <f t="shared" si="1"/>
         <v>36_1</v>
       </c>
-      <c r="J54" s="13">
+      <c r="K54" s="13">
         <v>110</v>
       </c>
-      <c r="K54">
-        <v>1</v>
-      </c>
-      <c r="L54" t="str">
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54" t="str">
         <f t="shared" si="2"/>
         <v>36_1_110</v>
       </c>
     </row>
-    <row r="55" customFormat="1" ht="16.5" spans="1:12">
+    <row r="55" customFormat="1" ht="16.5" spans="1:13">
       <c r="A55" s="8">
         <f t="shared" si="3"/>
         <v>10030037</v>
@@ -3200,28 +3306,31 @@
       </c>
       <c r="E55" s="10"/>
       <c r="F55" s="8"/>
-      <c r="G55" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="I55" t="str">
+      <c r="G55" s="8">
+        <v>100300037</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55" t="str">
         <f t="shared" si="1"/>
         <v>37_1</v>
       </c>
-      <c r="J55" s="13">
+      <c r="K55" s="13">
         <v>125</v>
       </c>
-      <c r="K55">
-        <v>1</v>
-      </c>
-      <c r="L55" t="str">
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55" t="str">
         <f t="shared" si="2"/>
         <v>37_1_125</v>
       </c>
     </row>
-    <row r="56" customFormat="1" ht="16.5" spans="1:12">
+    <row r="56" customFormat="1" ht="16.5" spans="1:13">
       <c r="A56" s="8">
         <f t="shared" si="3"/>
         <v>10030038</v>
@@ -3237,28 +3346,31 @@
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="8"/>
-      <c r="G56" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
-      <c r="I56" t="str">
+      <c r="G56" s="8">
+        <v>100300038</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56" t="str">
         <f t="shared" si="1"/>
         <v>38_1</v>
       </c>
-      <c r="J56" s="13">
+      <c r="K56" s="13">
         <v>138</v>
       </c>
-      <c r="K56">
-        <v>1</v>
-      </c>
-      <c r="L56" t="str">
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56" t="str">
         <f t="shared" si="2"/>
         <v>38_1_138</v>
       </c>
     </row>
-    <row r="57" customFormat="1" ht="16.5" spans="1:12">
+    <row r="57" customFormat="1" ht="16.5" spans="1:13">
       <c r="A57" s="8">
         <f t="shared" si="3"/>
         <v>10030039</v>
@@ -3274,28 +3386,31 @@
       </c>
       <c r="E57" s="10"/>
       <c r="F57" s="8"/>
-      <c r="G57" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H57">
-        <v>1</v>
-      </c>
-      <c r="I57" t="str">
+      <c r="G57" s="8">
+        <v>100300039</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57" t="str">
         <f t="shared" si="1"/>
         <v>39_1</v>
       </c>
-      <c r="J57" s="13">
+      <c r="K57" s="13">
         <v>150</v>
       </c>
-      <c r="K57">
-        <v>1</v>
-      </c>
-      <c r="L57" t="str">
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57" t="str">
         <f t="shared" si="2"/>
         <v>39_1_150</v>
       </c>
     </row>
-    <row r="58" customFormat="1" ht="16.5" spans="1:12">
+    <row r="58" customFormat="1" ht="16.5" spans="1:13">
       <c r="A58" s="8">
         <f t="shared" si="3"/>
         <v>10030040</v>
@@ -3311,28 +3426,31 @@
       </c>
       <c r="E58" s="10"/>
       <c r="F58" s="8"/>
-      <c r="G58" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H58">
-        <v>1</v>
-      </c>
-      <c r="I58" t="str">
+      <c r="G58" s="8">
+        <v>100300040</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58" t="str">
         <f t="shared" si="1"/>
         <v>40_1</v>
       </c>
-      <c r="J58" s="13">
+      <c r="K58" s="13">
         <v>210</v>
       </c>
-      <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="L58" t="str">
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58" t="str">
         <f t="shared" si="2"/>
         <v>40_1_210</v>
       </c>
     </row>
-    <row r="59" customFormat="1" ht="16.5" spans="1:12">
+    <row r="59" customFormat="1" ht="16.5" spans="1:13">
       <c r="A59" s="8">
         <f t="shared" si="3"/>
         <v>10030099</v>
@@ -3348,14 +3466,15 @@
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="8"/>
-      <c r="G59" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="J59" s="13"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="9" t="s">
+        <v>92</v>
+      </c>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
-    </row>
-    <row r="60" ht="16.5" spans="1:12">
+      <c r="M59" s="13"/>
+    </row>
+    <row r="60" ht="16.5" spans="1:13">
       <c r="A60" s="11">
         <f t="shared" ref="A60:A89" si="4">B60*100+C60</f>
         <v>10070001</v>
@@ -3370,17 +3489,18 @@
         <v>0</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F60" s="12"/>
-      <c r="G60" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="J60" s="13"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12" t="s">
+        <v>94</v>
+      </c>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
-    </row>
-    <row r="61" ht="16.5" spans="1:12">
+      <c r="M60" s="13"/>
+    </row>
+    <row r="61" ht="16.5" spans="1:13">
       <c r="A61" s="11">
         <f t="shared" si="4"/>
         <v>10070002</v>
@@ -3395,17 +3515,18 @@
         <v>0</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F61" s="12"/>
-      <c r="G61" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J61" s="13"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12" t="s">
+        <v>96</v>
+      </c>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
-    </row>
-    <row r="62" ht="16.5" spans="1:12">
+      <c r="M61" s="13"/>
+    </row>
+    <row r="62" ht="16.5" spans="1:13">
       <c r="A62" s="11">
         <f t="shared" si="4"/>
         <v>10070003</v>
@@ -3420,17 +3541,18 @@
         <v>0</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F62" s="12"/>
-      <c r="G62" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J62" s="13"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
-    </row>
-    <row r="63" ht="16.5" spans="1:12">
+      <c r="M62" s="13"/>
+    </row>
+    <row r="63" ht="16.5" spans="1:13">
       <c r="A63" s="11">
         <f t="shared" si="4"/>
         <v>10070004</v>
@@ -3445,17 +3567,18 @@
         <v>0</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F63" s="12"/>
-      <c r="G63" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="J63" s="13"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12" t="s">
+        <v>100</v>
+      </c>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
-    </row>
-    <row r="64" ht="16.5" spans="1:12">
+      <c r="M63" s="13"/>
+    </row>
+    <row r="64" ht="16.5" spans="1:13">
       <c r="A64" s="11">
         <f t="shared" si="4"/>
         <v>10070005</v>
@@ -3470,17 +3593,18 @@
         <v>0</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F64" s="12"/>
-      <c r="G64" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="J64" s="13"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12" t="s">
+        <v>102</v>
+      </c>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
-    </row>
-    <row r="65" ht="16.5" spans="1:12">
+      <c r="M64" s="13"/>
+    </row>
+    <row r="65" ht="16.5" spans="1:13">
       <c r="A65" s="11">
         <f t="shared" si="4"/>
         <v>10070006</v>
@@ -3495,17 +3619,18 @@
         <v>0</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F65" s="12"/>
-      <c r="G65" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J65" s="13"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="K65" s="13"/>
       <c r="L65" s="13"/>
-    </row>
-    <row r="66" ht="16.5" spans="1:12">
+      <c r="M65" s="13"/>
+    </row>
+    <row r="66" ht="16.5" spans="1:13">
       <c r="A66" s="11">
         <f t="shared" si="4"/>
         <v>10070007</v>
@@ -3520,17 +3645,18 @@
         <v>0</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F66" s="12"/>
-      <c r="G66" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J66" s="13"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12" t="s">
+        <v>106</v>
+      </c>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
-    </row>
-    <row r="67" ht="16.5" spans="1:12">
+      <c r="M66" s="13"/>
+    </row>
+    <row r="67" ht="16.5" spans="1:13">
       <c r="A67" s="11">
         <f t="shared" si="4"/>
         <v>10070008</v>
@@ -3545,17 +3671,18 @@
         <v>0</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F67" s="12"/>
-      <c r="G67" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="J67" s="13"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
-    </row>
-    <row r="68" ht="16.5" spans="1:12">
+      <c r="M67" s="13"/>
+    </row>
+    <row r="68" ht="16.5" spans="1:13">
       <c r="A68" s="11">
         <f t="shared" si="4"/>
         <v>10070009</v>
@@ -3570,17 +3697,18 @@
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F68" s="12"/>
-      <c r="G68" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J68" s="13"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
-    </row>
-    <row r="69" ht="16.5" spans="1:12">
+      <c r="M68" s="13"/>
+    </row>
+    <row r="69" ht="16.5" spans="1:13">
       <c r="A69" s="11">
         <f t="shared" si="4"/>
         <v>10070010</v>
@@ -3595,17 +3723,18 @@
         <v>2</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F69" s="12"/>
-      <c r="G69" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="J69" s="13"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="K69" s="13"/>
       <c r="L69" s="13"/>
-    </row>
-    <row r="70" ht="16.5" spans="1:12">
+      <c r="M69" s="13"/>
+    </row>
+    <row r="70" ht="16.5" spans="1:13">
       <c r="A70" s="14">
         <f t="shared" si="4"/>
         <v>10070011</v>
@@ -3620,19 +3749,20 @@
         <v>0</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F70" s="12">
         <v>9</v>
       </c>
-      <c r="G70" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="J70" s="13"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="15" t="s">
+        <v>114</v>
+      </c>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
-    </row>
-    <row r="71" ht="16.5" spans="1:12">
+      <c r="M70" s="13"/>
+    </row>
+    <row r="71" ht="16.5" spans="1:13">
       <c r="A71" s="14">
         <f t="shared" si="4"/>
         <v>10070012</v>
@@ -3647,19 +3777,20 @@
         <v>0</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F71" s="12">
         <v>9</v>
       </c>
-      <c r="G71" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="J71" s="13"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
-    </row>
-    <row r="72" ht="16.5" spans="1:12">
+      <c r="M71" s="13"/>
+    </row>
+    <row r="72" ht="16.5" spans="1:13">
       <c r="A72" s="14">
         <f t="shared" si="4"/>
         <v>10070013</v>
@@ -3674,19 +3805,20 @@
         <v>0</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F72" s="12">
         <v>9</v>
       </c>
-      <c r="G72" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="J72" s="13"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
-    </row>
-    <row r="73" ht="16.5" spans="1:12">
+      <c r="M72" s="13"/>
+    </row>
+    <row r="73" ht="16.5" spans="1:13">
       <c r="A73" s="14">
         <f t="shared" si="4"/>
         <v>10070014</v>
@@ -3701,19 +3833,20 @@
         <v>0</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F73" s="12">
         <v>9</v>
       </c>
-      <c r="G73" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="J73" s="13"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="15" t="s">
+        <v>120</v>
+      </c>
       <c r="K73" s="13"/>
       <c r="L73" s="13"/>
-    </row>
-    <row r="74" ht="16.5" spans="1:12">
+      <c r="M73" s="13"/>
+    </row>
+    <row r="74" ht="16.5" spans="1:13">
       <c r="A74" s="14">
         <f t="shared" si="4"/>
         <v>10070015</v>
@@ -3728,19 +3861,20 @@
         <v>0</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F74" s="12">
         <v>9</v>
       </c>
-      <c r="G74" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="J74" s="13"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="15" t="s">
+        <v>122</v>
+      </c>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
-    </row>
-    <row r="75" ht="16.5" spans="1:12">
+      <c r="M74" s="13"/>
+    </row>
+    <row r="75" ht="16.5" spans="1:13">
       <c r="A75" s="14">
         <f t="shared" si="4"/>
         <v>10070016</v>
@@ -3755,19 +3889,20 @@
         <v>0</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F75" s="12">
         <v>9</v>
       </c>
-      <c r="G75" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="J75" s="13"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
-    </row>
-    <row r="76" ht="16.5" spans="1:12">
+      <c r="M75" s="13"/>
+    </row>
+    <row r="76" ht="16.5" spans="1:13">
       <c r="A76" s="14">
         <f t="shared" si="4"/>
         <v>10070017</v>
@@ -3782,19 +3917,20 @@
         <v>0</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F76" s="12">
         <v>9</v>
       </c>
-      <c r="G76" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="J76" s="13"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="15" t="s">
+        <v>126</v>
+      </c>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
-    </row>
-    <row r="77" ht="16.5" spans="1:12">
+      <c r="M76" s="13"/>
+    </row>
+    <row r="77" ht="16.5" spans="1:13">
       <c r="A77" s="14">
         <f t="shared" si="4"/>
         <v>10070018</v>
@@ -3809,19 +3945,20 @@
         <v>0</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F77" s="12">
         <v>9</v>
       </c>
-      <c r="G77" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="J77" s="13"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
-    </row>
-    <row r="78" ht="16.5" spans="1:12">
+      <c r="M77" s="13"/>
+    </row>
+    <row r="78" ht="16.5" spans="1:13">
       <c r="A78" s="8">
         <f t="shared" si="4"/>
         <v>10120001</v>
@@ -3837,14 +3974,15 @@
       </c>
       <c r="E78" s="10"/>
       <c r="F78" s="8"/>
-      <c r="G78" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="J78" s="13"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="9" t="s">
+        <v>129</v>
+      </c>
       <c r="K78" s="13"/>
       <c r="L78" s="13"/>
-    </row>
-    <row r="79" ht="16.5" spans="1:12">
+      <c r="M78" s="13"/>
+    </row>
+    <row r="79" ht="16.5" spans="1:13">
       <c r="A79" s="8">
         <f t="shared" si="4"/>
         <v>10120002</v>
@@ -3860,14 +3998,15 @@
       </c>
       <c r="E79" s="10"/>
       <c r="F79" s="8"/>
-      <c r="G79" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="J79" s="13"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="9" t="s">
+        <v>130</v>
+      </c>
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
-    </row>
-    <row r="80" ht="16.5" spans="1:12">
+      <c r="M79" s="13"/>
+    </row>
+    <row r="80" ht="16.5" spans="1:13">
       <c r="A80" s="8">
         <f t="shared" si="4"/>
         <v>10120003</v>
@@ -3883,14 +4022,15 @@
       </c>
       <c r="E80" s="10"/>
       <c r="F80" s="8"/>
-      <c r="G80" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J80" s="13"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="9" t="s">
+        <v>131</v>
+      </c>
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
-    </row>
-    <row r="81" ht="16.5" spans="1:12">
+      <c r="M80" s="13"/>
+    </row>
+    <row r="81" ht="16.5" spans="1:13">
       <c r="A81" s="8">
         <f t="shared" si="4"/>
         <v>10120004</v>
@@ -3906,14 +4046,15 @@
       </c>
       <c r="E81" s="10"/>
       <c r="F81" s="8"/>
-      <c r="G81" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="J81" s="13"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="9" t="s">
+        <v>132</v>
+      </c>
       <c r="K81" s="13"/>
       <c r="L81" s="13"/>
-    </row>
-    <row r="82" ht="16.5" spans="1:12">
+      <c r="M81" s="13"/>
+    </row>
+    <row r="82" ht="16.5" spans="1:13">
       <c r="A82" s="8">
         <f t="shared" si="4"/>
         <v>10120005</v>
@@ -3929,14 +4070,15 @@
       </c>
       <c r="E82" s="10"/>
       <c r="F82" s="8"/>
-      <c r="G82" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="J82" s="13"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="9" t="s">
+        <v>133</v>
+      </c>
       <c r="K82" s="13"/>
       <c r="L82" s="13"/>
-    </row>
-    <row r="83" ht="16.5" spans="1:12">
+      <c r="M82" s="13"/>
+    </row>
+    <row r="83" ht="16.5" spans="1:13">
       <c r="A83" s="8">
         <f t="shared" si="4"/>
         <v>10120006</v>
@@ -3952,14 +4094,15 @@
       </c>
       <c r="E83" s="10"/>
       <c r="F83" s="8"/>
-      <c r="G83" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="J83" s="13"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="9" t="s">
+        <v>134</v>
+      </c>
       <c r="K83" s="13"/>
       <c r="L83" s="13"/>
-    </row>
-    <row r="84" ht="16.5" spans="1:12">
+      <c r="M83" s="13"/>
+    </row>
+    <row r="84" ht="16.5" spans="1:13">
       <c r="A84" s="8">
         <f t="shared" ref="A84:A103" si="5">B84*100+C84</f>
         <v>10120009</v>
@@ -3975,14 +4118,15 @@
       </c>
       <c r="E84" s="10"/>
       <c r="F84" s="8"/>
-      <c r="G84" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="J84" s="13"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
-    </row>
-    <row r="85" ht="16.5" spans="1:12">
+      <c r="M84" s="13"/>
+    </row>
+    <row r="85" ht="16.5" spans="1:13">
       <c r="A85" s="8">
         <f t="shared" si="5"/>
         <v>10120010</v>
@@ -3998,14 +4142,15 @@
       </c>
       <c r="E85" s="10"/>
       <c r="F85" s="8"/>
-      <c r="G85" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J85" s="13"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="9" t="s">
+        <v>110</v>
+      </c>
       <c r="K85" s="13"/>
       <c r="L85" s="13"/>
-    </row>
-    <row r="86" ht="16.5" spans="1:12">
+      <c r="M85" s="13"/>
+    </row>
+    <row r="86" ht="16.5" spans="1:13">
       <c r="A86" s="8">
         <f t="shared" si="5"/>
         <v>10120011</v>
@@ -4021,14 +4166,15 @@
       </c>
       <c r="E86" s="10"/>
       <c r="F86" s="8"/>
-      <c r="G86" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="J86" s="13"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="K86" s="13"/>
       <c r="L86" s="13"/>
-    </row>
-    <row r="87" ht="16.5" spans="1:12">
+      <c r="M86" s="13"/>
+    </row>
+    <row r="87" ht="16.5" spans="1:13">
       <c r="A87" s="8">
         <f t="shared" si="5"/>
         <v>10120012</v>
@@ -4044,14 +4190,15 @@
       </c>
       <c r="E87" s="10"/>
       <c r="F87" s="8"/>
-      <c r="G87" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="J87" s="13"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="9" t="s">
+        <v>137</v>
+      </c>
       <c r="K87" s="13"/>
       <c r="L87" s="13"/>
-    </row>
-    <row r="88" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M87" s="13"/>
+    </row>
+    <row r="88" customFormat="1" ht="16.5" spans="1:13">
       <c r="A88" s="8">
         <f t="shared" si="5"/>
         <v>10120013</v>
@@ -4067,14 +4214,15 @@
       </c>
       <c r="E88" s="10"/>
       <c r="F88" s="8"/>
-      <c r="G88" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="J88" s="13"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="9" t="s">
+        <v>138</v>
+      </c>
       <c r="K88" s="13"/>
       <c r="L88" s="13"/>
-    </row>
-    <row r="89" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M88" s="13"/>
+    </row>
+    <row r="89" customFormat="1" ht="16.5" spans="1:13">
       <c r="A89" s="8">
         <f t="shared" si="5"/>
         <v>10120014</v>
@@ -4090,14 +4238,15 @@
       </c>
       <c r="E89" s="10"/>
       <c r="F89" s="8"/>
-      <c r="G89" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="J89" s="13"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="9" t="s">
+        <v>139</v>
+      </c>
       <c r="K89" s="13"/>
       <c r="L89" s="13"/>
-    </row>
-    <row r="90" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M89" s="13"/>
+    </row>
+    <row r="90" customFormat="1" ht="16.5" spans="1:13">
       <c r="A90" s="8">
         <f t="shared" si="5"/>
         <v>10120015</v>
@@ -4113,14 +4262,15 @@
       </c>
       <c r="E90" s="10"/>
       <c r="F90" s="8"/>
-      <c r="G90" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="J90" s="13"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="9" t="s">
+        <v>140</v>
+      </c>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
-    </row>
-    <row r="91" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M90" s="13"/>
+    </row>
+    <row r="91" customFormat="1" ht="16.5" spans="1:13">
       <c r="A91" s="8">
         <f t="shared" si="5"/>
         <v>10120016</v>
@@ -4136,14 +4286,15 @@
       </c>
       <c r="E91" s="10"/>
       <c r="F91" s="8"/>
-      <c r="G91" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="J91" s="13"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="9" t="s">
+        <v>141</v>
+      </c>
       <c r="K91" s="13"/>
       <c r="L91" s="13"/>
-    </row>
-    <row r="92" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M91" s="13"/>
+    </row>
+    <row r="92" customFormat="1" ht="16.5" spans="1:13">
       <c r="A92" s="8">
         <f t="shared" si="5"/>
         <v>10120021</v>
@@ -4159,14 +4310,15 @@
       </c>
       <c r="E92" s="10"/>
       <c r="F92" s="8"/>
-      <c r="G92" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="J92" s="13"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="K92" s="13"/>
       <c r="L92" s="13"/>
-    </row>
-    <row r="93" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M92" s="13"/>
+    </row>
+    <row r="93" customFormat="1" ht="16.5" spans="1:13">
       <c r="A93" s="8">
         <f t="shared" si="5"/>
         <v>10120022</v>
@@ -4182,14 +4334,15 @@
       </c>
       <c r="E93" s="10"/>
       <c r="F93" s="8"/>
-      <c r="G93" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="J93" s="13"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="9" t="s">
+        <v>143</v>
+      </c>
       <c r="K93" s="13"/>
       <c r="L93" s="13"/>
-    </row>
-    <row r="94" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M93" s="13"/>
+    </row>
+    <row r="94" customFormat="1" ht="16.5" spans="1:13">
       <c r="A94" s="8">
         <f t="shared" si="5"/>
         <v>10120023</v>
@@ -4205,14 +4358,15 @@
       </c>
       <c r="E94" s="10"/>
       <c r="F94" s="8"/>
-      <c r="G94" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="J94" s="13"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="K94" s="13"/>
       <c r="L94" s="13"/>
-    </row>
-    <row r="95" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M94" s="13"/>
+    </row>
+    <row r="95" customFormat="1" ht="16.5" spans="1:13">
       <c r="A95" s="8">
         <f t="shared" si="5"/>
         <v>10120024</v>
@@ -4228,14 +4382,15 @@
       </c>
       <c r="E95" s="10"/>
       <c r="F95" s="8"/>
-      <c r="G95" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="J95" s="13"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="9" t="s">
+        <v>145</v>
+      </c>
       <c r="K95" s="13"/>
       <c r="L95" s="13"/>
-    </row>
-    <row r="96" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M95" s="13"/>
+    </row>
+    <row r="96" customFormat="1" ht="16.5" spans="1:13">
       <c r="A96" s="8">
         <f t="shared" si="5"/>
         <v>10120025</v>
@@ -4251,14 +4406,15 @@
       </c>
       <c r="E96" s="10"/>
       <c r="F96" s="8"/>
-      <c r="G96" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="J96" s="13"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="9" t="s">
+        <v>146</v>
+      </c>
       <c r="K96" s="13"/>
       <c r="L96" s="13"/>
-    </row>
-    <row r="97" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M96" s="13"/>
+    </row>
+    <row r="97" customFormat="1" ht="16.5" spans="1:13">
       <c r="A97" s="8">
         <f t="shared" si="5"/>
         <v>10120026</v>
@@ -4274,14 +4430,15 @@
       </c>
       <c r="E97" s="10"/>
       <c r="F97" s="8"/>
-      <c r="G97" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="J97" s="13"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="9" t="s">
+        <v>147</v>
+      </c>
       <c r="K97" s="13"/>
       <c r="L97" s="13"/>
-    </row>
-    <row r="98" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M97" s="13"/>
+    </row>
+    <row r="98" customFormat="1" ht="16.5" spans="1:13">
       <c r="A98" s="8">
         <f t="shared" si="5"/>
         <v>10120031</v>
@@ -4297,14 +4454,15 @@
       </c>
       <c r="E98" s="10"/>
       <c r="F98" s="8"/>
-      <c r="G98" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J98" s="13"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="9" t="s">
+        <v>148</v>
+      </c>
       <c r="K98" s="13"/>
       <c r="L98" s="13"/>
-    </row>
-    <row r="99" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M98" s="13"/>
+    </row>
+    <row r="99" customFormat="1" ht="16.5" spans="1:13">
       <c r="A99" s="8">
         <f t="shared" si="5"/>
         <v>10120032</v>
@@ -4320,14 +4478,15 @@
       </c>
       <c r="E99" s="10"/>
       <c r="F99" s="8"/>
-      <c r="G99" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="J99" s="13"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="9" t="s">
+        <v>149</v>
+      </c>
       <c r="K99" s="13"/>
       <c r="L99" s="13"/>
-    </row>
-    <row r="100" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M99" s="13"/>
+    </row>
+    <row r="100" customFormat="1" ht="16.5" spans="1:13">
       <c r="A100" s="8">
         <f t="shared" si="5"/>
         <v>10120033</v>
@@ -4343,14 +4502,15 @@
       </c>
       <c r="E100" s="10"/>
       <c r="F100" s="8"/>
-      <c r="G100" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="J100" s="13"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="9" t="s">
+        <v>150</v>
+      </c>
       <c r="K100" s="13"/>
       <c r="L100" s="13"/>
-    </row>
-    <row r="101" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M100" s="13"/>
+    </row>
+    <row r="101" customFormat="1" ht="16.5" spans="1:13">
       <c r="A101" s="8">
         <f t="shared" si="5"/>
         <v>10120034</v>
@@ -4366,14 +4526,15 @@
       </c>
       <c r="E101" s="10"/>
       <c r="F101" s="8"/>
-      <c r="G101" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="J101" s="13"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="9" t="s">
+        <v>151</v>
+      </c>
       <c r="K101" s="13"/>
       <c r="L101" s="13"/>
-    </row>
-    <row r="102" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M101" s="13"/>
+    </row>
+    <row r="102" customFormat="1" ht="16.5" spans="1:13">
       <c r="A102" s="8">
         <f t="shared" si="5"/>
         <v>10120035</v>
@@ -4389,14 +4550,15 @@
       </c>
       <c r="E102" s="10"/>
       <c r="F102" s="8"/>
-      <c r="G102" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="J102" s="13"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="9" t="s">
+        <v>152</v>
+      </c>
       <c r="K102" s="13"/>
       <c r="L102" s="13"/>
-    </row>
-    <row r="103" customFormat="1" ht="16.5" spans="1:12">
+      <c r="M102" s="13"/>
+    </row>
+    <row r="103" customFormat="1" ht="16.5" spans="1:13">
       <c r="A103" s="8">
         <f t="shared" si="5"/>
         <v>10120036</v>
@@ -4412,14 +4574,15 @@
       </c>
       <c r="E103" s="10"/>
       <c r="F103" s="8"/>
-      <c r="G103" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J103" s="13"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="9" t="s">
+        <v>153</v>
+      </c>
       <c r="K103" s="13"/>
       <c r="L103" s="13"/>
-    </row>
-    <row r="104" ht="16.5" spans="1:12">
+      <c r="M103" s="13"/>
+    </row>
+    <row r="104" ht="16.5" spans="1:13">
       <c r="A104" s="16">
         <f t="shared" ref="A104:A116" si="6">B104*100+C104</f>
         <v>10140001</v>
@@ -4435,20 +4598,21 @@
       </c>
       <c r="E104" s="17"/>
       <c r="F104" s="17"/>
-      <c r="G104" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="J104" s="13"/>
+      <c r="G104" s="17"/>
+      <c r="H104" s="17" t="s">
+        <v>154</v>
+      </c>
       <c r="K104" s="13"/>
       <c r="L104" s="13"/>
-    </row>
-    <row r="105" ht="16.5" spans="1:12">
+      <c r="M104" s="13"/>
+    </row>
+    <row r="105" ht="16.5" spans="1:13">
       <c r="A105" s="16">
         <f t="shared" si="6"/>
-        <v>10140102</v>
+        <v>10140002</v>
       </c>
       <c r="B105" s="16">
-        <v>101401</v>
+        <v>101400</v>
       </c>
       <c r="C105" s="17">
         <v>2</v>
@@ -4458,20 +4622,21 @@
       </c>
       <c r="E105" s="17"/>
       <c r="F105" s="17"/>
-      <c r="G105" s="17">
+      <c r="G105" s="17"/>
+      <c r="H105" s="17">
         <v>9</v>
       </c>
-      <c r="J105" s="13"/>
       <c r="K105" s="13"/>
       <c r="L105" s="13"/>
-    </row>
-    <row r="106" ht="16.5" spans="1:12">
+      <c r="M105" s="13"/>
+    </row>
+    <row r="106" ht="16.5" spans="1:13">
       <c r="A106" s="16">
         <f t="shared" si="6"/>
-        <v>10140203</v>
+        <v>10140003</v>
       </c>
       <c r="B106" s="16">
-        <v>101402</v>
+        <v>101400</v>
       </c>
       <c r="C106" s="17">
         <v>3</v>
@@ -4481,20 +4646,21 @@
       </c>
       <c r="E106" s="17"/>
       <c r="F106" s="17"/>
-      <c r="G106" s="17">
+      <c r="G106" s="17"/>
+      <c r="H106" s="17">
         <v>10</v>
       </c>
-      <c r="J106" s="13"/>
       <c r="K106" s="13"/>
       <c r="L106" s="13"/>
-    </row>
-    <row r="107" ht="16.5" spans="1:12">
+      <c r="M106" s="13"/>
+    </row>
+    <row r="107" ht="16.5" spans="1:13">
       <c r="A107" s="16">
         <f t="shared" si="6"/>
-        <v>10140304</v>
+        <v>10140004</v>
       </c>
       <c r="B107" s="16">
-        <v>101403</v>
+        <v>101400</v>
       </c>
       <c r="C107" s="17">
         <v>4</v>
@@ -4504,20 +4670,21 @@
       </c>
       <c r="E107" s="17"/>
       <c r="F107" s="17"/>
-      <c r="G107" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J107" s="13"/>
+      <c r="G107" s="17"/>
+      <c r="H107" s="17" t="s">
+        <v>19</v>
+      </c>
       <c r="K107" s="13"/>
       <c r="L107" s="13"/>
-    </row>
-    <row r="108" ht="16.5" spans="1:12">
+      <c r="M107" s="13"/>
+    </row>
+    <row r="108" ht="16.5" spans="1:13">
       <c r="A108" s="16">
         <f t="shared" si="6"/>
-        <v>10140405</v>
+        <v>10140005</v>
       </c>
       <c r="B108" s="16">
-        <v>101404</v>
+        <v>101400</v>
       </c>
       <c r="C108" s="17">
         <v>5</v>
@@ -4527,20 +4694,21 @@
       </c>
       <c r="E108" s="17"/>
       <c r="F108" s="17"/>
-      <c r="G108" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J108" s="13"/>
+      <c r="G108" s="17"/>
+      <c r="H108" s="17" t="s">
+        <v>21</v>
+      </c>
       <c r="K108" s="13"/>
       <c r="L108" s="13"/>
-    </row>
-    <row r="109" ht="16.5" spans="1:12">
+      <c r="M108" s="13"/>
+    </row>
+    <row r="109" ht="16.5" spans="1:13">
       <c r="A109" s="16">
         <f t="shared" si="6"/>
-        <v>10140506</v>
+        <v>10140006</v>
       </c>
       <c r="B109" s="16">
-        <v>101405</v>
+        <v>101400</v>
       </c>
       <c r="C109" s="17">
         <v>6</v>
@@ -4550,20 +4718,21 @@
       </c>
       <c r="E109" s="17"/>
       <c r="F109" s="17"/>
-      <c r="G109" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="J109" s="13"/>
+      <c r="G109" s="17"/>
+      <c r="H109" s="17" t="s">
+        <v>23</v>
+      </c>
       <c r="K109" s="13"/>
       <c r="L109" s="13"/>
-    </row>
-    <row r="110" ht="16.5" spans="1:12">
+      <c r="M109" s="13"/>
+    </row>
+    <row r="110" ht="16.5" spans="1:13">
       <c r="A110" s="16">
         <f t="shared" si="6"/>
-        <v>10140607</v>
+        <v>10140007</v>
       </c>
       <c r="B110" s="16">
-        <v>101406</v>
+        <v>101400</v>
       </c>
       <c r="C110" s="17">
         <v>7</v>
@@ -4573,20 +4742,21 @@
       </c>
       <c r="E110" s="17"/>
       <c r="F110" s="17"/>
-      <c r="G110" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J110" s="13"/>
+      <c r="G110" s="17"/>
+      <c r="H110" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="K110" s="13"/>
       <c r="L110" s="13"/>
-    </row>
-    <row r="111" ht="16.5" spans="1:12">
+      <c r="M110" s="13"/>
+    </row>
+    <row r="111" ht="16.5" spans="1:13">
       <c r="A111" s="16">
         <f t="shared" si="6"/>
-        <v>10140708</v>
+        <v>10140008</v>
       </c>
       <c r="B111" s="16">
-        <v>101407</v>
+        <v>101400</v>
       </c>
       <c r="C111" s="17">
         <v>8</v>
@@ -4596,20 +4766,21 @@
       </c>
       <c r="E111" s="17"/>
       <c r="F111" s="17"/>
-      <c r="G111" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="J111" s="13"/>
+      <c r="G111" s="17"/>
+      <c r="H111" s="17" t="s">
+        <v>155</v>
+      </c>
       <c r="K111" s="13"/>
       <c r="L111" s="13"/>
-    </row>
-    <row r="112" ht="16.5" spans="1:12">
+      <c r="M111" s="13"/>
+    </row>
+    <row r="112" ht="16.5" spans="1:13">
       <c r="A112" s="16">
         <f t="shared" si="6"/>
-        <v>10140809</v>
+        <v>10140009</v>
       </c>
       <c r="B112" s="16">
-        <v>101408</v>
+        <v>101400</v>
       </c>
       <c r="C112" s="17">
         <v>9</v>
@@ -4619,20 +4790,21 @@
       </c>
       <c r="E112" s="17"/>
       <c r="F112" s="17"/>
-      <c r="G112" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="J112" s="13"/>
+      <c r="G112" s="17"/>
+      <c r="H112" s="17" t="s">
+        <v>156</v>
+      </c>
       <c r="K112" s="13"/>
       <c r="L112" s="13"/>
-    </row>
-    <row r="113" ht="16.5" spans="1:12">
+      <c r="M112" s="13"/>
+    </row>
+    <row r="113" ht="16.5" spans="1:13">
       <c r="A113" s="16">
         <f t="shared" si="6"/>
-        <v>10140910</v>
+        <v>10140010</v>
       </c>
       <c r="B113" s="16">
-        <v>101409</v>
+        <v>101400</v>
       </c>
       <c r="C113" s="17">
         <v>10</v>
@@ -4642,20 +4814,21 @@
       </c>
       <c r="E113" s="17"/>
       <c r="F113" s="17"/>
-      <c r="G113" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J113" s="13"/>
+      <c r="G113" s="17"/>
+      <c r="H113" s="17" t="s">
+        <v>157</v>
+      </c>
       <c r="K113" s="13"/>
       <c r="L113" s="13"/>
-    </row>
-    <row r="114" ht="16.5" spans="1:12">
+      <c r="M113" s="13"/>
+    </row>
+    <row r="114" ht="16.5" spans="1:13">
       <c r="A114" s="16">
         <f t="shared" si="6"/>
-        <v>10141011</v>
+        <v>10140011</v>
       </c>
       <c r="B114" s="16">
-        <v>101410</v>
+        <v>101400</v>
       </c>
       <c r="C114" s="17">
         <v>11</v>
@@ -4665,20 +4838,21 @@
       </c>
       <c r="E114" s="17"/>
       <c r="F114" s="17"/>
-      <c r="G114" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="J114" s="13"/>
+      <c r="G114" s="17"/>
+      <c r="H114" s="17" t="s">
+        <v>158</v>
+      </c>
       <c r="K114" s="13"/>
       <c r="L114" s="13"/>
-    </row>
-    <row r="115" ht="16.5" spans="1:12">
+      <c r="M114" s="13"/>
+    </row>
+    <row r="115" ht="16.5" spans="1:13">
       <c r="A115" s="16">
         <f t="shared" si="6"/>
-        <v>10141112</v>
+        <v>10140012</v>
       </c>
       <c r="B115" s="16">
-        <v>101411</v>
+        <v>101400</v>
       </c>
       <c r="C115" s="17">
         <v>12</v>
@@ -4688,20 +4862,21 @@
       </c>
       <c r="E115" s="17"/>
       <c r="F115" s="17"/>
-      <c r="G115" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="J115" s="13"/>
+      <c r="G115" s="17"/>
+      <c r="H115" s="17" t="s">
+        <v>110</v>
+      </c>
       <c r="K115" s="13"/>
       <c r="L115" s="13"/>
-    </row>
-    <row r="116" ht="16.5" spans="1:12">
+      <c r="M115" s="13"/>
+    </row>
+    <row r="116" ht="16.5" spans="1:13">
       <c r="A116" s="16">
         <f t="shared" si="6"/>
-        <v>10141213</v>
+        <v>10140013</v>
       </c>
       <c r="B116" s="16">
-        <v>101412</v>
+        <v>101400</v>
       </c>
       <c r="C116" s="17">
         <v>13</v>
@@ -4711,30 +4886,31 @@
       </c>
       <c r="E116" s="17"/>
       <c r="F116" s="17"/>
-      <c r="G116" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="J116" s="13"/>
+      <c r="G116" s="17"/>
+      <c r="H116" s="17" t="s">
+        <v>159</v>
+      </c>
       <c r="K116" s="13"/>
       <c r="L116" s="13"/>
+      <c r="M116" s="13"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2">
+  <conditionalFormatting sqref="F2:G2">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>MOD($B2,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="F3:G3">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B3,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:D4 G1:G4">
+  <conditionalFormatting sqref="A1:D4 H1:H4">
     <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:F1 E2:E3 E4:F4">
+  <conditionalFormatting sqref="E1:G1 E2:E3 E4:G4">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>MOD($B1,2)=1</formula>
     </cfRule>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="157">
   <si>
     <t>图标</t>
   </si>
@@ -321,15 +321,9 @@
     <t>Wild-GRAND</t>
   </si>
   <si>
-    <t>数量</t>
-  </si>
-  <si>
     <t>Wild-倍率6</t>
   </si>
   <si>
-    <t>SpecialGird</t>
-  </si>
-  <si>
     <t>Wild-倍率9</t>
   </si>
   <si>
@@ -337,9 +331,6 @@
   </si>
   <si>
     <t>Wild-倍率15</t>
-  </si>
-  <si>
-    <t>BaseElementReward</t>
   </si>
   <si>
     <t>Wild-倍率21</t>
@@ -1669,7 +1660,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -2631,12 +2622,10 @@
         <v>68</v>
       </c>
       <c r="K38" s="13"/>
-      <c r="L38" s="13" t="s">
-        <v>69</v>
-      </c>
+      <c r="L38" s="13"/>
       <c r="M38" s="13"/>
     </row>
-    <row r="39" ht="16.5" spans="1:14">
+    <row r="39" ht="16.5" spans="1:8">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
         <v>10030021</v>
@@ -2656,30 +2645,10 @@
         <v>100300021</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="J39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,C39,I39)</f>
-        <v>21_1</v>
-      </c>
-      <c r="K39">
-        <v>6</v>
-      </c>
-      <c r="L39">
-        <v>1</v>
-      </c>
-      <c r="M39" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,C39,L39,K39)</f>
-        <v>21_1_6</v>
-      </c>
-      <c r="N39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" ht="16.5" spans="1:14">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="16.5" spans="1:11">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
         <v>10030022</v>
@@ -2699,31 +2668,13 @@
         <v>100300022</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-      <c r="J40" t="str">
-        <f t="shared" ref="J40:J58" si="1">_xlfn.TEXTJOIN("_",TRUE,C40,I40)</f>
-        <v>22_1</v>
-      </c>
-      <c r="K40" s="13">
-        <v>9</v>
-      </c>
-      <c r="L40">
-        <v>1</v>
-      </c>
-      <c r="M40" t="str">
-        <f t="shared" ref="M40:M58" si="2">_xlfn.TEXTJOIN("_",TRUE,C40,L40,K40)</f>
-        <v>22_1_9</v>
-      </c>
-      <c r="N40" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,J39:J58)</f>
-        <v>21_1|22_1|23_1|24_1|25_1|26_1|27_1|28_1|29_1|30_1|31_1|32_1|33_1|34_1|35_1|36_1|37_1|38_1|39_1|40_1</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" ht="16.5" spans="1:13">
+        <v>70</v>
+      </c>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40" s="13"/>
+    </row>
+    <row r="41" customFormat="1" ht="16.5" spans="1:11">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
         <v>10030023</v>
@@ -2743,27 +2694,13 @@
         <v>100300023</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41" t="str">
-        <f t="shared" si="1"/>
-        <v>23_1</v>
-      </c>
-      <c r="K41" s="13">
-        <v>12</v>
-      </c>
-      <c r="L41">
-        <v>1</v>
-      </c>
-      <c r="M41" t="str">
-        <f t="shared" si="2"/>
-        <v>23_1_12</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" ht="16.5" spans="1:14">
+        <v>71</v>
+      </c>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41" s="13"/>
+    </row>
+    <row r="42" customFormat="1" ht="16.5" spans="1:11">
       <c r="A42" s="8">
         <f t="shared" si="0"/>
         <v>10030024</v>
@@ -2783,30 +2720,13 @@
         <v>100300024</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-      <c r="J42" t="str">
-        <f t="shared" si="1"/>
-        <v>24_1</v>
-      </c>
-      <c r="K42" s="13">
-        <v>15</v>
-      </c>
-      <c r="L42">
-        <v>1</v>
-      </c>
-      <c r="M42" t="str">
-        <f t="shared" si="2"/>
-        <v>24_1_15</v>
-      </c>
-      <c r="N42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" ht="16.5" spans="1:14">
+        <v>72</v>
+      </c>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42" s="13"/>
+    </row>
+    <row r="43" customFormat="1" ht="16.5" spans="1:11">
       <c r="A43" s="8">
         <f t="shared" si="0"/>
         <v>10030025</v>
@@ -2826,31 +2746,13 @@
         <v>100300025</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="J43" t="str">
-        <f t="shared" si="1"/>
-        <v>25_1</v>
-      </c>
-      <c r="K43" s="13">
-        <v>21</v>
-      </c>
-      <c r="L43">
-        <v>1</v>
-      </c>
-      <c r="M43" t="str">
-        <f t="shared" si="2"/>
-        <v>25_1_21</v>
-      </c>
-      <c r="N43" t="str">
-        <f>_xlfn.TEXTJOIN("|",TRUE,M39:M58)</f>
-        <v>21_1_6|22_1_9|23_1_12|24_1_15|25_1_21|26_1_24|27_1_32|28_1_38|29_1_49|30_1_58|31_1_68|32_1_79|33_1_85|34_1_96|35_1_105|36_1_110|37_1_125|38_1_138|39_1_150|40_1_210</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" ht="16.5" spans="1:13">
+        <v>73</v>
+      </c>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43" s="13"/>
+    </row>
+    <row r="44" customFormat="1" ht="16.5" spans="1:11">
       <c r="A44" s="8">
         <f t="shared" si="0"/>
         <v>10030026</v>
@@ -2870,27 +2772,13 @@
         <v>100300026</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="J44" t="str">
-        <f t="shared" si="1"/>
-        <v>26_1</v>
-      </c>
-      <c r="K44" s="13">
-        <v>24</v>
-      </c>
-      <c r="L44">
-        <v>1</v>
-      </c>
-      <c r="M44" t="str">
-        <f t="shared" si="2"/>
-        <v>26_1_24</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:13">
+        <v>74</v>
+      </c>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44" s="13"/>
+    </row>
+    <row r="45" customFormat="1" ht="16.5" spans="1:11">
       <c r="A45" s="8">
         <f t="shared" si="0"/>
         <v>10030027</v>
@@ -2910,27 +2798,13 @@
         <v>100300027</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-      <c r="J45" t="str">
-        <f t="shared" si="1"/>
-        <v>27_1</v>
-      </c>
-      <c r="K45" s="13">
-        <v>32</v>
-      </c>
-      <c r="L45">
-        <v>1</v>
-      </c>
-      <c r="M45" t="str">
-        <f t="shared" si="2"/>
-        <v>27_1_32</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:13">
+        <v>75</v>
+      </c>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45" s="13"/>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:11">
       <c r="A46" s="8">
         <f t="shared" si="0"/>
         <v>10030028</v>
@@ -2950,29 +2824,15 @@
         <v>100300028</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I46">
-        <v>1</v>
-      </c>
-      <c r="J46" t="str">
-        <f t="shared" si="1"/>
-        <v>28_1</v>
-      </c>
-      <c r="K46" s="13">
-        <v>38</v>
-      </c>
-      <c r="L46">
-        <v>1</v>
-      </c>
-      <c r="M46" t="str">
-        <f t="shared" si="2"/>
-        <v>28_1_38</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:13">
+        <v>76</v>
+      </c>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46" s="13"/>
+    </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:11">
       <c r="A47" s="8">
-        <f t="shared" ref="A47:A59" si="3">B47*100+C47</f>
+        <f t="shared" ref="A47:A59" si="1">B47*100+C47</f>
         <v>10030029</v>
       </c>
       <c r="B47" s="8">
@@ -2990,29 +2850,15 @@
         <v>100300029</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="J47" t="str">
+        <v>77</v>
+      </c>
+      <c r="I47"/>
+      <c r="J47"/>
+      <c r="K47" s="13"/>
+    </row>
+    <row r="48" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A48" s="8">
         <f t="shared" si="1"/>
-        <v>29_1</v>
-      </c>
-      <c r="K47" s="13">
-        <v>49</v>
-      </c>
-      <c r="L47">
-        <v>1</v>
-      </c>
-      <c r="M47" t="str">
-        <f t="shared" si="2"/>
-        <v>29_1_49</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A48" s="8">
-        <f t="shared" si="3"/>
         <v>10030030</v>
       </c>
       <c r="B48" s="8">
@@ -3030,29 +2876,15 @@
         <v>100300030</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-      <c r="J48" t="str">
+        <v>78</v>
+      </c>
+      <c r="I48"/>
+      <c r="J48"/>
+      <c r="K48" s="13"/>
+    </row>
+    <row r="49" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A49" s="8">
         <f t="shared" si="1"/>
-        <v>30_1</v>
-      </c>
-      <c r="K48" s="13">
-        <v>58</v>
-      </c>
-      <c r="L48">
-        <v>1</v>
-      </c>
-      <c r="M48" t="str">
-        <f t="shared" si="2"/>
-        <v>30_1_58</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A49" s="8">
-        <f t="shared" si="3"/>
         <v>10030031</v>
       </c>
       <c r="B49" s="8">
@@ -3070,29 +2902,15 @@
         <v>100300031</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
-      </c>
-      <c r="J49" t="str">
+        <v>79</v>
+      </c>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49" s="13"/>
+    </row>
+    <row r="50" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A50" s="8">
         <f t="shared" si="1"/>
-        <v>31_1</v>
-      </c>
-      <c r="K49" s="13">
-        <v>68</v>
-      </c>
-      <c r="L49">
-        <v>1</v>
-      </c>
-      <c r="M49" t="str">
-        <f t="shared" si="2"/>
-        <v>31_1_68</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A50" s="8">
-        <f t="shared" si="3"/>
         <v>10030032</v>
       </c>
       <c r="B50" s="8">
@@ -3110,29 +2928,15 @@
         <v>100300032</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-      <c r="J50" t="str">
+        <v>80</v>
+      </c>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50" s="13"/>
+    </row>
+    <row r="51" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A51" s="8">
         <f t="shared" si="1"/>
-        <v>32_1</v>
-      </c>
-      <c r="K50" s="13">
-        <v>79</v>
-      </c>
-      <c r="L50">
-        <v>1</v>
-      </c>
-      <c r="M50" t="str">
-        <f t="shared" si="2"/>
-        <v>32_1_79</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A51" s="8">
-        <f t="shared" si="3"/>
         <v>10030033</v>
       </c>
       <c r="B51" s="8">
@@ -3150,29 +2954,15 @@
         <v>100300033</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I51">
-        <v>1</v>
-      </c>
-      <c r="J51" t="str">
+        <v>81</v>
+      </c>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51" s="13"/>
+    </row>
+    <row r="52" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A52" s="8">
         <f t="shared" si="1"/>
-        <v>33_1</v>
-      </c>
-      <c r="K51" s="13">
-        <v>85</v>
-      </c>
-      <c r="L51">
-        <v>1</v>
-      </c>
-      <c r="M51" t="str">
-        <f t="shared" si="2"/>
-        <v>33_1_85</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A52" s="8">
-        <f t="shared" si="3"/>
         <v>10030034</v>
       </c>
       <c r="B52" s="8">
@@ -3190,29 +2980,15 @@
         <v>100300034</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="I52">
-        <v>1</v>
-      </c>
-      <c r="J52" t="str">
+        <v>82</v>
+      </c>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52" s="13"/>
+    </row>
+    <row r="53" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A53" s="8">
         <f t="shared" si="1"/>
-        <v>34_1</v>
-      </c>
-      <c r="K52" s="13">
-        <v>96</v>
-      </c>
-      <c r="L52">
-        <v>1</v>
-      </c>
-      <c r="M52" t="str">
-        <f t="shared" si="2"/>
-        <v>34_1_96</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A53" s="8">
-        <f t="shared" si="3"/>
         <v>10030035</v>
       </c>
       <c r="B53" s="8">
@@ -3230,29 +3006,15 @@
         <v>100300035</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
-      <c r="J53" t="str">
+        <v>83</v>
+      </c>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53" s="13"/>
+    </row>
+    <row r="54" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A54" s="8">
         <f t="shared" si="1"/>
-        <v>35_1</v>
-      </c>
-      <c r="K53" s="13">
-        <v>105</v>
-      </c>
-      <c r="L53">
-        <v>1</v>
-      </c>
-      <c r="M53" t="str">
-        <f t="shared" si="2"/>
-        <v>35_1_105</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A54" s="8">
-        <f t="shared" si="3"/>
         <v>10030036</v>
       </c>
       <c r="B54" s="8">
@@ -3270,29 +3032,15 @@
         <v>100300036</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I54">
-        <v>1</v>
-      </c>
-      <c r="J54" t="str">
+        <v>84</v>
+      </c>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54" s="13"/>
+    </row>
+    <row r="55" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A55" s="8">
         <f t="shared" si="1"/>
-        <v>36_1</v>
-      </c>
-      <c r="K54" s="13">
-        <v>110</v>
-      </c>
-      <c r="L54">
-        <v>1</v>
-      </c>
-      <c r="M54" t="str">
-        <f t="shared" si="2"/>
-        <v>36_1_110</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A55" s="8">
-        <f t="shared" si="3"/>
         <v>10030037</v>
       </c>
       <c r="B55" s="8">
@@ -3310,29 +3058,15 @@
         <v>100300037</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="I55">
-        <v>1</v>
-      </c>
-      <c r="J55" t="str">
+        <v>85</v>
+      </c>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55" s="13"/>
+    </row>
+    <row r="56" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A56" s="8">
         <f t="shared" si="1"/>
-        <v>37_1</v>
-      </c>
-      <c r="K55" s="13">
-        <v>125</v>
-      </c>
-      <c r="L55">
-        <v>1</v>
-      </c>
-      <c r="M55" t="str">
-        <f t="shared" si="2"/>
-        <v>37_1_125</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A56" s="8">
-        <f t="shared" si="3"/>
         <v>10030038</v>
       </c>
       <c r="B56" s="8">
@@ -3350,29 +3084,15 @@
         <v>100300038</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="I56">
-        <v>1</v>
-      </c>
-      <c r="J56" t="str">
+        <v>86</v>
+      </c>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56" s="13"/>
+    </row>
+    <row r="57" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A57" s="8">
         <f t="shared" si="1"/>
-        <v>38_1</v>
-      </c>
-      <c r="K56" s="13">
-        <v>138</v>
-      </c>
-      <c r="L56">
-        <v>1</v>
-      </c>
-      <c r="M56" t="str">
-        <f t="shared" si="2"/>
-        <v>38_1_138</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A57" s="8">
-        <f t="shared" si="3"/>
         <v>10030039</v>
       </c>
       <c r="B57" s="8">
@@ -3390,29 +3110,15 @@
         <v>100300039</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I57">
-        <v>1</v>
-      </c>
-      <c r="J57" t="str">
+        <v>87</v>
+      </c>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A58" s="8">
         <f t="shared" si="1"/>
-        <v>39_1</v>
-      </c>
-      <c r="K57" s="13">
-        <v>150</v>
-      </c>
-      <c r="L57">
-        <v>1</v>
-      </c>
-      <c r="M57" t="str">
-        <f t="shared" si="2"/>
-        <v>39_1_150</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A58" s="8">
-        <f t="shared" si="3"/>
         <v>10030040</v>
       </c>
       <c r="B58" s="8">
@@ -3430,29 +3136,15 @@
         <v>100300040</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="I58">
-        <v>1</v>
-      </c>
-      <c r="J58" t="str">
-        <f t="shared" si="1"/>
-        <v>40_1</v>
-      </c>
-      <c r="K58" s="13">
-        <v>210</v>
-      </c>
-      <c r="L58">
-        <v>1</v>
-      </c>
-      <c r="M58" t="str">
-        <f t="shared" si="2"/>
-        <v>40_1_210</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58" s="13"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:13">
       <c r="A59" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>10030099</v>
       </c>
       <c r="B59" s="8">
@@ -3468,7 +3160,7 @@
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
       <c r="H59" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
@@ -3476,7 +3168,7 @@
     </row>
     <row r="60" ht="16.5" spans="1:13">
       <c r="A60" s="11">
-        <f t="shared" ref="A60:A89" si="4">B60*100+C60</f>
+        <f t="shared" ref="A60:A89" si="2">B60*100+C60</f>
         <v>10070001</v>
       </c>
       <c r="B60" s="11">
@@ -3489,12 +3181,12 @@
         <v>0</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="12"/>
       <c r="H60" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
@@ -3502,7 +3194,7 @@
     </row>
     <row r="61" ht="16.5" spans="1:13">
       <c r="A61" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070002</v>
       </c>
       <c r="B61" s="11">
@@ -3515,12 +3207,12 @@
         <v>0</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="12"/>
       <c r="H61" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
@@ -3528,7 +3220,7 @@
     </row>
     <row r="62" ht="16.5" spans="1:13">
       <c r="A62" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070003</v>
       </c>
       <c r="B62" s="11">
@@ -3541,12 +3233,12 @@
         <v>0</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="12"/>
       <c r="H62" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
@@ -3554,7 +3246,7 @@
     </row>
     <row r="63" ht="16.5" spans="1:13">
       <c r="A63" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070004</v>
       </c>
       <c r="B63" s="11">
@@ -3567,12 +3259,12 @@
         <v>0</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F63" s="12"/>
       <c r="G63" s="12"/>
       <c r="H63" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
@@ -3580,7 +3272,7 @@
     </row>
     <row r="64" ht="16.5" spans="1:13">
       <c r="A64" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070005</v>
       </c>
       <c r="B64" s="11">
@@ -3593,12 +3285,12 @@
         <v>0</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F64" s="12"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
@@ -3606,7 +3298,7 @@
     </row>
     <row r="65" ht="16.5" spans="1:13">
       <c r="A65" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070006</v>
       </c>
       <c r="B65" s="11">
@@ -3619,12 +3311,12 @@
         <v>0</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F65" s="12"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K65" s="13"/>
       <c r="L65" s="13"/>
@@ -3632,7 +3324,7 @@
     </row>
     <row r="66" ht="16.5" spans="1:13">
       <c r="A66" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070007</v>
       </c>
       <c r="B66" s="11">
@@ -3645,12 +3337,12 @@
         <v>0</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F66" s="12"/>
       <c r="G66" s="12"/>
       <c r="H66" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
@@ -3658,7 +3350,7 @@
     </row>
     <row r="67" ht="16.5" spans="1:13">
       <c r="A67" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070008</v>
       </c>
       <c r="B67" s="11">
@@ -3671,12 +3363,12 @@
         <v>0</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
@@ -3684,7 +3376,7 @@
     </row>
     <row r="68" ht="16.5" spans="1:13">
       <c r="A68" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070009</v>
       </c>
       <c r="B68" s="11">
@@ -3697,12 +3389,12 @@
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
@@ -3710,7 +3402,7 @@
     </row>
     <row r="69" ht="16.5" spans="1:13">
       <c r="A69" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070010</v>
       </c>
       <c r="B69" s="11">
@@ -3723,12 +3415,12 @@
         <v>2</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K69" s="13"/>
       <c r="L69" s="13"/>
@@ -3736,7 +3428,7 @@
     </row>
     <row r="70" ht="16.5" spans="1:13">
       <c r="A70" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070011</v>
       </c>
       <c r="B70" s="14">
@@ -3749,14 +3441,14 @@
         <v>0</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F70" s="12">
         <v>9</v>
       </c>
       <c r="G70" s="12"/>
       <c r="H70" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
@@ -3764,7 +3456,7 @@
     </row>
     <row r="71" ht="16.5" spans="1:13">
       <c r="A71" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070012</v>
       </c>
       <c r="B71" s="14">
@@ -3777,14 +3469,14 @@
         <v>0</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F71" s="12">
         <v>9</v>
       </c>
       <c r="G71" s="12"/>
       <c r="H71" s="15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
@@ -3792,7 +3484,7 @@
     </row>
     <row r="72" ht="16.5" spans="1:13">
       <c r="A72" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070013</v>
       </c>
       <c r="B72" s="14">
@@ -3805,14 +3497,14 @@
         <v>0</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F72" s="12">
         <v>9</v>
       </c>
       <c r="G72" s="12"/>
       <c r="H72" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
@@ -3820,7 +3512,7 @@
     </row>
     <row r="73" ht="16.5" spans="1:13">
       <c r="A73" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070014</v>
       </c>
       <c r="B73" s="14">
@@ -3833,14 +3525,14 @@
         <v>0</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F73" s="12">
         <v>9</v>
       </c>
       <c r="G73" s="12"/>
       <c r="H73" s="15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K73" s="13"/>
       <c r="L73" s="13"/>
@@ -3848,7 +3540,7 @@
     </row>
     <row r="74" ht="16.5" spans="1:13">
       <c r="A74" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070015</v>
       </c>
       <c r="B74" s="14">
@@ -3861,14 +3553,14 @@
         <v>0</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F74" s="12">
         <v>9</v>
       </c>
       <c r="G74" s="12"/>
       <c r="H74" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
@@ -3876,7 +3568,7 @@
     </row>
     <row r="75" ht="16.5" spans="1:13">
       <c r="A75" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070016</v>
       </c>
       <c r="B75" s="14">
@@ -3889,14 +3581,14 @@
         <v>0</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F75" s="12">
         <v>9</v>
       </c>
       <c r="G75" s="12"/>
       <c r="H75" s="15" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
@@ -3904,7 +3596,7 @@
     </row>
     <row r="76" ht="16.5" spans="1:13">
       <c r="A76" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070017</v>
       </c>
       <c r="B76" s="14">
@@ -3917,14 +3609,14 @@
         <v>0</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F76" s="12">
         <v>9</v>
       </c>
       <c r="G76" s="12"/>
       <c r="H76" s="15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
@@ -3932,7 +3624,7 @@
     </row>
     <row r="77" ht="16.5" spans="1:13">
       <c r="A77" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10070018</v>
       </c>
       <c r="B77" s="14">
@@ -3945,14 +3637,14 @@
         <v>0</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F77" s="12">
         <v>9</v>
       </c>
       <c r="G77" s="12"/>
       <c r="H77" s="15" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
@@ -3960,7 +3652,7 @@
     </row>
     <row r="78" ht="16.5" spans="1:13">
       <c r="A78" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10120001</v>
       </c>
       <c r="B78" s="8">
@@ -3976,7 +3668,7 @@
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="H78" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K78" s="13"/>
       <c r="L78" s="13"/>
@@ -3984,7 +3676,7 @@
     </row>
     <row r="79" ht="16.5" spans="1:13">
       <c r="A79" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10120002</v>
       </c>
       <c r="B79" s="8">
@@ -4000,7 +3692,7 @@
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
       <c r="H79" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
@@ -4008,7 +3700,7 @@
     </row>
     <row r="80" ht="16.5" spans="1:13">
       <c r="A80" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10120003</v>
       </c>
       <c r="B80" s="8">
@@ -4024,7 +3716,7 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
       <c r="H80" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
@@ -4032,7 +3724,7 @@
     </row>
     <row r="81" ht="16.5" spans="1:13">
       <c r="A81" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10120004</v>
       </c>
       <c r="B81" s="8">
@@ -4048,7 +3740,7 @@
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
       <c r="H81" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K81" s="13"/>
       <c r="L81" s="13"/>
@@ -4056,7 +3748,7 @@
     </row>
     <row r="82" ht="16.5" spans="1:13">
       <c r="A82" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10120005</v>
       </c>
       <c r="B82" s="8">
@@ -4072,7 +3764,7 @@
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
       <c r="H82" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K82" s="13"/>
       <c r="L82" s="13"/>
@@ -4080,7 +3772,7 @@
     </row>
     <row r="83" ht="16.5" spans="1:13">
       <c r="A83" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10120006</v>
       </c>
       <c r="B83" s="8">
@@ -4096,7 +3788,7 @@
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
       <c r="H83" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K83" s="13"/>
       <c r="L83" s="13"/>
@@ -4104,7 +3796,7 @@
     </row>
     <row r="84" ht="16.5" spans="1:13">
       <c r="A84" s="8">
-        <f t="shared" ref="A84:A103" si="5">B84*100+C84</f>
+        <f t="shared" ref="A84:A103" si="3">B84*100+C84</f>
         <v>10120009</v>
       </c>
       <c r="B84" s="8">
@@ -4120,7 +3812,7 @@
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
       <c r="H84" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
@@ -4128,7 +3820,7 @@
     </row>
     <row r="85" ht="16.5" spans="1:13">
       <c r="A85" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120010</v>
       </c>
       <c r="B85" s="8">
@@ -4144,7 +3836,7 @@
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
       <c r="H85" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K85" s="13"/>
       <c r="L85" s="13"/>
@@ -4152,7 +3844,7 @@
     </row>
     <row r="86" ht="16.5" spans="1:13">
       <c r="A86" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120011</v>
       </c>
       <c r="B86" s="8">
@@ -4168,7 +3860,7 @@
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
       <c r="H86" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K86" s="13"/>
       <c r="L86" s="13"/>
@@ -4176,7 +3868,7 @@
     </row>
     <row r="87" ht="16.5" spans="1:13">
       <c r="A87" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120012</v>
       </c>
       <c r="B87" s="8">
@@ -4192,7 +3884,7 @@
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
       <c r="H87" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K87" s="13"/>
       <c r="L87" s="13"/>
@@ -4200,7 +3892,7 @@
     </row>
     <row r="88" customFormat="1" ht="16.5" spans="1:13">
       <c r="A88" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120013</v>
       </c>
       <c r="B88" s="8">
@@ -4216,7 +3908,7 @@
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
       <c r="H88" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K88" s="13"/>
       <c r="L88" s="13"/>
@@ -4224,7 +3916,7 @@
     </row>
     <row r="89" customFormat="1" ht="16.5" spans="1:13">
       <c r="A89" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120014</v>
       </c>
       <c r="B89" s="8">
@@ -4240,7 +3932,7 @@
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
       <c r="H89" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K89" s="13"/>
       <c r="L89" s="13"/>
@@ -4248,7 +3940,7 @@
     </row>
     <row r="90" customFormat="1" ht="16.5" spans="1:13">
       <c r="A90" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120015</v>
       </c>
       <c r="B90" s="8">
@@ -4264,7 +3956,7 @@
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
       <c r="H90" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
@@ -4272,7 +3964,7 @@
     </row>
     <row r="91" customFormat="1" ht="16.5" spans="1:13">
       <c r="A91" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120016</v>
       </c>
       <c r="B91" s="8">
@@ -4288,7 +3980,7 @@
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
       <c r="H91" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K91" s="13"/>
       <c r="L91" s="13"/>
@@ -4296,7 +3988,7 @@
     </row>
     <row r="92" customFormat="1" ht="16.5" spans="1:13">
       <c r="A92" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120021</v>
       </c>
       <c r="B92" s="8">
@@ -4312,7 +4004,7 @@
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
       <c r="H92" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K92" s="13"/>
       <c r="L92" s="13"/>
@@ -4320,7 +4012,7 @@
     </row>
     <row r="93" customFormat="1" ht="16.5" spans="1:13">
       <c r="A93" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120022</v>
       </c>
       <c r="B93" s="8">
@@ -4336,7 +4028,7 @@
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
       <c r="H93" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K93" s="13"/>
       <c r="L93" s="13"/>
@@ -4344,7 +4036,7 @@
     </row>
     <row r="94" customFormat="1" ht="16.5" spans="1:13">
       <c r="A94" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120023</v>
       </c>
       <c r="B94" s="8">
@@ -4360,7 +4052,7 @@
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
       <c r="H94" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K94" s="13"/>
       <c r="L94" s="13"/>
@@ -4368,7 +4060,7 @@
     </row>
     <row r="95" customFormat="1" ht="16.5" spans="1:13">
       <c r="A95" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120024</v>
       </c>
       <c r="B95" s="8">
@@ -4384,7 +4076,7 @@
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
       <c r="H95" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K95" s="13"/>
       <c r="L95" s="13"/>
@@ -4392,7 +4084,7 @@
     </row>
     <row r="96" customFormat="1" ht="16.5" spans="1:13">
       <c r="A96" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120025</v>
       </c>
       <c r="B96" s="8">
@@ -4408,7 +4100,7 @@
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
       <c r="H96" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K96" s="13"/>
       <c r="L96" s="13"/>
@@ -4416,7 +4108,7 @@
     </row>
     <row r="97" customFormat="1" ht="16.5" spans="1:13">
       <c r="A97" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120026</v>
       </c>
       <c r="B97" s="8">
@@ -4432,7 +4124,7 @@
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
       <c r="H97" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K97" s="13"/>
       <c r="L97" s="13"/>
@@ -4440,7 +4132,7 @@
     </row>
     <row r="98" customFormat="1" ht="16.5" spans="1:13">
       <c r="A98" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120031</v>
       </c>
       <c r="B98" s="8">
@@ -4456,7 +4148,7 @@
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
       <c r="H98" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K98" s="13"/>
       <c r="L98" s="13"/>
@@ -4464,7 +4156,7 @@
     </row>
     <row r="99" customFormat="1" ht="16.5" spans="1:13">
       <c r="A99" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120032</v>
       </c>
       <c r="B99" s="8">
@@ -4480,7 +4172,7 @@
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
       <c r="H99" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K99" s="13"/>
       <c r="L99" s="13"/>
@@ -4488,7 +4180,7 @@
     </row>
     <row r="100" customFormat="1" ht="16.5" spans="1:13">
       <c r="A100" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120033</v>
       </c>
       <c r="B100" s="8">
@@ -4504,7 +4196,7 @@
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
       <c r="H100" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K100" s="13"/>
       <c r="L100" s="13"/>
@@ -4512,7 +4204,7 @@
     </row>
     <row r="101" customFormat="1" ht="16.5" spans="1:13">
       <c r="A101" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120034</v>
       </c>
       <c r="B101" s="8">
@@ -4528,7 +4220,7 @@
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
       <c r="H101" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K101" s="13"/>
       <c r="L101" s="13"/>
@@ -4536,7 +4228,7 @@
     </row>
     <row r="102" customFormat="1" ht="16.5" spans="1:13">
       <c r="A102" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120035</v>
       </c>
       <c r="B102" s="8">
@@ -4552,7 +4244,7 @@
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
       <c r="H102" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K102" s="13"/>
       <c r="L102" s="13"/>
@@ -4560,7 +4252,7 @@
     </row>
     <row r="103" customFormat="1" ht="16.5" spans="1:13">
       <c r="A103" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>10120036</v>
       </c>
       <c r="B103" s="8">
@@ -4576,7 +4268,7 @@
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
       <c r="H103" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K103" s="13"/>
       <c r="L103" s="13"/>
@@ -4584,7 +4276,7 @@
     </row>
     <row r="104" ht="16.5" spans="1:13">
       <c r="A104" s="16">
-        <f t="shared" ref="A104:A116" si="6">B104*100+C104</f>
+        <f t="shared" ref="A104:A116" si="4">B104*100+C104</f>
         <v>10140001</v>
       </c>
       <c r="B104" s="16">
@@ -4600,7 +4292,7 @@
       <c r="F104" s="17"/>
       <c r="G104" s="17"/>
       <c r="H104" s="17" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K104" s="13"/>
       <c r="L104" s="13"/>
@@ -4608,7 +4300,7 @@
     </row>
     <row r="105" ht="16.5" spans="1:13">
       <c r="A105" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140002</v>
       </c>
       <c r="B105" s="16">
@@ -4632,7 +4324,7 @@
     </row>
     <row r="106" ht="16.5" spans="1:13">
       <c r="A106" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140003</v>
       </c>
       <c r="B106" s="16">
@@ -4656,7 +4348,7 @@
     </row>
     <row r="107" ht="16.5" spans="1:13">
       <c r="A107" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140004</v>
       </c>
       <c r="B107" s="16">
@@ -4680,7 +4372,7 @@
     </row>
     <row r="108" ht="16.5" spans="1:13">
       <c r="A108" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140005</v>
       </c>
       <c r="B108" s="16">
@@ -4704,7 +4396,7 @@
     </row>
     <row r="109" ht="16.5" spans="1:13">
       <c r="A109" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140006</v>
       </c>
       <c r="B109" s="16">
@@ -4728,7 +4420,7 @@
     </row>
     <row r="110" ht="16.5" spans="1:13">
       <c r="A110" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140007</v>
       </c>
       <c r="B110" s="16">
@@ -4752,7 +4444,7 @@
     </row>
     <row r="111" ht="16.5" spans="1:13">
       <c r="A111" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140008</v>
       </c>
       <c r="B111" s="16">
@@ -4768,7 +4460,7 @@
       <c r="F111" s="17"/>
       <c r="G111" s="17"/>
       <c r="H111" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K111" s="13"/>
       <c r="L111" s="13"/>
@@ -4776,7 +4468,7 @@
     </row>
     <row r="112" ht="16.5" spans="1:13">
       <c r="A112" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140009</v>
       </c>
       <c r="B112" s="16">
@@ -4792,7 +4484,7 @@
       <c r="F112" s="17"/>
       <c r="G112" s="17"/>
       <c r="H112" s="17" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K112" s="13"/>
       <c r="L112" s="13"/>
@@ -4800,7 +4492,7 @@
     </row>
     <row r="113" ht="16.5" spans="1:13">
       <c r="A113" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140010</v>
       </c>
       <c r="B113" s="16">
@@ -4816,7 +4508,7 @@
       <c r="F113" s="17"/>
       <c r="G113" s="17"/>
       <c r="H113" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K113" s="13"/>
       <c r="L113" s="13"/>
@@ -4824,7 +4516,7 @@
     </row>
     <row r="114" ht="16.5" spans="1:13">
       <c r="A114" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140011</v>
       </c>
       <c r="B114" s="16">
@@ -4840,7 +4532,7 @@
       <c r="F114" s="17"/>
       <c r="G114" s="17"/>
       <c r="H114" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K114" s="13"/>
       <c r="L114" s="13"/>
@@ -4848,7 +4540,7 @@
     </row>
     <row r="115" ht="16.5" spans="1:13">
       <c r="A115" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140012</v>
       </c>
       <c r="B115" s="16">
@@ -4864,7 +4556,7 @@
       <c r="F115" s="17"/>
       <c r="G115" s="17"/>
       <c r="H115" s="17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K115" s="13"/>
       <c r="L115" s="13"/>
@@ -4872,7 +4564,7 @@
     </row>
     <row r="116" ht="16.5" spans="1:13">
       <c r="A116" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10140013</v>
       </c>
       <c r="B116" s="16">
@@ -4888,7 +4580,7 @@
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
       <c r="H116" s="17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K116" s="13"/>
       <c r="L116" s="13"/>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="188">
   <si>
     <t>图标</t>
   </si>
@@ -294,21 +294,42 @@
     <t>隐藏图案，常规不出现，用于触发免费</t>
   </si>
   <si>
+    <t>cjmx_zjm_icon_12.png</t>
+  </si>
+  <si>
     <t>BAR</t>
   </si>
   <si>
+    <t>cjmx_zjm_icon_13.png</t>
+  </si>
+  <si>
     <t>BAR×2</t>
   </si>
   <si>
+    <t>cjmx_zjm_icon_14.png</t>
+  </si>
+  <si>
     <t>BAR×3</t>
   </si>
   <si>
+    <t>cjmx_zjm_icon_7.png</t>
+  </si>
+  <si>
+    <t>cjmx_zjm_icon_9.png</t>
+  </si>
+  <si>
     <t>7图案</t>
   </si>
   <si>
+    <t>cjmx_zjm_icon_8.png</t>
+  </si>
+  <si>
     <t>樱桃</t>
   </si>
   <si>
+    <t>cjmx_zjm_icon_10.png</t>
+  </si>
+  <si>
     <t>Wild-MINI</t>
   </si>
   <si>
@@ -321,6 +342,9 @@
     <t>Wild-GRAND</t>
   </si>
   <si>
+    <t>cjmx_zjm_icon_11.png</t>
+  </si>
+  <si>
     <t>Wild-倍率6</t>
   </si>
   <si>
@@ -492,27 +516,54 @@
     <t>黄金_发财|消除后变为Wild百搭</t>
   </si>
   <si>
-    <t>彩球</t>
-  </si>
-  <si>
-    <t>爆竹</t>
-  </si>
-  <si>
-    <t>舞狮</t>
-  </si>
-  <si>
-    <t>铜钱</t>
-  </si>
-  <si>
-    <t>聚宝盆</t>
-  </si>
-  <si>
-    <t>摇钱树</t>
+    <t>cs_zjm_tb_1.png</t>
+  </si>
+  <si>
+    <t>彩球 - 红包</t>
+  </si>
+  <si>
+    <t>cs_zjm_tb_2.png</t>
+  </si>
+  <si>
+    <t>爆竹 - 玉如意</t>
+  </si>
+  <si>
+    <t>cs_zjm_tb_3.png</t>
+  </si>
+  <si>
+    <t>舞狮 - 福袋</t>
+  </si>
+  <si>
+    <t>cs_zjm_tb_4.png</t>
+  </si>
+  <si>
+    <t>铜钱 - 灯笼</t>
+  </si>
+  <si>
+    <t>cs_zjm_tb_5.png</t>
+  </si>
+  <si>
+    <t>聚宝盆 - 舞狮</t>
+  </si>
+  <si>
+    <t>cs_zjm_tb_6.png</t>
+  </si>
+  <si>
+    <t>摇钱树 - 聚宝盆</t>
+  </si>
+  <si>
+    <t>cs_zjm_tb_9.png</t>
   </si>
   <si>
     <t>财神jackpot</t>
   </si>
   <si>
+    <t>cs_zjm_tb_10.png</t>
+  </si>
+  <si>
+    <t>cs_zjm_tb_7.png</t>
+  </si>
+  <si>
     <t>横财神第1行</t>
   </si>
   <si>
@@ -522,6 +573,9 @@
     <t>横财神第3行</t>
   </si>
   <si>
+    <t>cs_zjm_tb_8.png</t>
+  </si>
+  <si>
     <t>横财神第2列</t>
   </si>
   <si>
@@ -567,19 +621,58 @@
     <t>横财神第4列-第3次</t>
   </si>
   <si>
+    <t>ajyh_zjm_icon_13.png</t>
+  </si>
+  <si>
     <t>空格</t>
   </si>
   <si>
+    <t>ajyh_zjm_icon_6.png</t>
+  </si>
+  <si>
+    <t>ajyh_zjm_icon_5.png</t>
+  </si>
+  <si>
+    <t>ajyh_zjm_icon_4.png</t>
+  </si>
+  <si>
+    <t>ajyh_zjm_icon_3.png</t>
+  </si>
+  <si>
+    <t>ajyh_zjm_icon_2.png</t>
+  </si>
+  <si>
+    <t>ajyh_zjm_icon_1.png</t>
+  </si>
+  <si>
+    <t>ajyh_zjm_icon_7.png</t>
+  </si>
+  <si>
     <t>护符</t>
   </si>
   <si>
+    <t>ajyh_zjm_icon_8.png</t>
+  </si>
+  <si>
     <t>荷鲁斯之眼</t>
   </si>
   <si>
+    <t>ajyh_zjm_icon_9.png</t>
+  </si>
+  <si>
     <t>翅膀</t>
   </si>
   <si>
+    <t>ajyh_zjm_icon_10.png</t>
+  </si>
+  <si>
     <t>艳后</t>
+  </si>
+  <si>
+    <t>ajyh_zjm_icon_11.png</t>
+  </si>
+  <si>
+    <t>ajyh_zjm_icon_12.png</t>
   </si>
   <si>
     <t>夺宝</t>
@@ -774,12 +867,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2391,11 +2484,13 @@
       <c r="D29" s="9">
         <v>0</v>
       </c>
-      <c r="E29" s="10"/>
+      <c r="E29" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
       <c r="H29" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
@@ -2415,11 +2510,13 @@
       <c r="D30" s="9">
         <v>0</v>
       </c>
-      <c r="E30" s="10"/>
+      <c r="E30" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
       <c r="H30" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
@@ -2439,11 +2536,13 @@
       <c r="D31" s="9">
         <v>0</v>
       </c>
-      <c r="E31" s="10"/>
+      <c r="E31" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
       <c r="H31" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
@@ -2463,7 +2562,9 @@
       <c r="D32" s="9">
         <v>0</v>
       </c>
-      <c r="E32" s="10"/>
+      <c r="E32" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
       <c r="H32" s="9" t="s">
@@ -2487,11 +2588,13 @@
       <c r="D33" s="9">
         <v>0</v>
       </c>
-      <c r="E33" s="10"/>
+      <c r="E33" s="10" t="s">
+        <v>67</v>
+      </c>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K33" s="13"/>
       <c r="L33" s="13"/>
@@ -2511,11 +2614,13 @@
       <c r="D34" s="9">
         <v>0</v>
       </c>
-      <c r="E34" s="10"/>
+      <c r="E34" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
       <c r="H34" s="9" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
@@ -2535,13 +2640,15 @@
       <c r="D35" s="9">
         <v>1</v>
       </c>
-      <c r="E35" s="10"/>
+      <c r="E35" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8">
         <v>100300107</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K35" s="13"/>
       <c r="L35" s="13"/>
@@ -2561,13 +2668,15 @@
       <c r="D36" s="9">
         <v>1</v>
       </c>
-      <c r="E36" s="10"/>
+      <c r="E36" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8">
         <v>100300108</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
@@ -2587,13 +2696,15 @@
       <c r="D37" s="9">
         <v>1</v>
       </c>
-      <c r="E37" s="10"/>
+      <c r="E37" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8">
         <v>100300109</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K37" s="13"/>
       <c r="L37" s="13"/>
@@ -2613,13 +2724,15 @@
       <c r="D38" s="9">
         <v>1</v>
       </c>
-      <c r="E38" s="10"/>
+      <c r="E38" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8">
         <v>100300110</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K38" s="13"/>
       <c r="L38" s="13"/>
@@ -2639,13 +2752,15 @@
       <c r="D39" s="9">
         <v>1</v>
       </c>
-      <c r="E39" s="10"/>
+      <c r="E39" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F39" s="8"/>
       <c r="G39" s="8">
         <v>100300021</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" customFormat="1" ht="16.5" spans="1:11">
@@ -2662,13 +2777,15 @@
       <c r="D40" s="9">
         <v>1</v>
       </c>
-      <c r="E40" s="10"/>
+      <c r="E40" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8">
         <v>100300022</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I40"/>
       <c r="J40"/>
@@ -2688,13 +2805,15 @@
       <c r="D41" s="9">
         <v>1</v>
       </c>
-      <c r="E41" s="10"/>
+      <c r="E41" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8">
         <v>100300023</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I41"/>
       <c r="J41"/>
@@ -2714,13 +2833,15 @@
       <c r="D42" s="9">
         <v>1</v>
       </c>
-      <c r="E42" s="10"/>
+      <c r="E42" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8">
         <v>100300024</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I42"/>
       <c r="J42"/>
@@ -2740,13 +2861,15 @@
       <c r="D43" s="9">
         <v>1</v>
       </c>
-      <c r="E43" s="10"/>
+      <c r="E43" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F43" s="8"/>
       <c r="G43" s="8">
         <v>100300025</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I43"/>
       <c r="J43"/>
@@ -2766,13 +2889,15 @@
       <c r="D44" s="9">
         <v>1</v>
       </c>
-      <c r="E44" s="10"/>
+      <c r="E44" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8">
         <v>100300026</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I44"/>
       <c r="J44"/>
@@ -2792,13 +2917,15 @@
       <c r="D45" s="9">
         <v>1</v>
       </c>
-      <c r="E45" s="10"/>
+      <c r="E45" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F45" s="8"/>
       <c r="G45" s="8">
         <v>100300027</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
@@ -2818,13 +2945,15 @@
       <c r="D46" s="9">
         <v>1</v>
       </c>
-      <c r="E46" s="10"/>
+      <c r="E46" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8">
         <v>100300028</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
@@ -2844,13 +2973,15 @@
       <c r="D47" s="9">
         <v>1</v>
       </c>
-      <c r="E47" s="10"/>
+      <c r="E47" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8">
         <v>100300029</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
@@ -2870,13 +3001,15 @@
       <c r="D48" s="9">
         <v>1</v>
       </c>
-      <c r="E48" s="10"/>
+      <c r="E48" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8">
         <v>100300030</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I48"/>
       <c r="J48"/>
@@ -2896,13 +3029,15 @@
       <c r="D49" s="9">
         <v>1</v>
       </c>
-      <c r="E49" s="10"/>
+      <c r="E49" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8">
         <v>100300031</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
@@ -2922,13 +3057,15 @@
       <c r="D50" s="9">
         <v>1</v>
       </c>
-      <c r="E50" s="10"/>
+      <c r="E50" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8">
         <v>100300032</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I50"/>
       <c r="J50"/>
@@ -2948,13 +3085,15 @@
       <c r="D51" s="9">
         <v>1</v>
       </c>
-      <c r="E51" s="10"/>
+      <c r="E51" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8">
         <v>100300033</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I51"/>
       <c r="J51"/>
@@ -2974,13 +3113,15 @@
       <c r="D52" s="9">
         <v>1</v>
       </c>
-      <c r="E52" s="10"/>
+      <c r="E52" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8">
         <v>100300034</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
@@ -3000,13 +3141,15 @@
       <c r="D53" s="9">
         <v>1</v>
       </c>
-      <c r="E53" s="10"/>
+      <c r="E53" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F53" s="8"/>
       <c r="G53" s="8">
         <v>100300035</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I53"/>
       <c r="J53"/>
@@ -3026,13 +3169,15 @@
       <c r="D54" s="9">
         <v>1</v>
       </c>
-      <c r="E54" s="10"/>
+      <c r="E54" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8">
         <v>100300036</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I54"/>
       <c r="J54"/>
@@ -3052,13 +3197,15 @@
       <c r="D55" s="9">
         <v>1</v>
       </c>
-      <c r="E55" s="10"/>
+      <c r="E55" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8">
         <v>100300037</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I55"/>
       <c r="J55"/>
@@ -3078,13 +3225,15 @@
       <c r="D56" s="9">
         <v>1</v>
       </c>
-      <c r="E56" s="10"/>
+      <c r="E56" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8">
         <v>100300038</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="I56"/>
       <c r="J56"/>
@@ -3104,13 +3253,15 @@
       <c r="D57" s="9">
         <v>1</v>
       </c>
-      <c r="E57" s="10"/>
+      <c r="E57" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F57" s="8"/>
       <c r="G57" s="8">
         <v>100300039</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I57"/>
       <c r="J57"/>
@@ -3130,13 +3281,15 @@
       <c r="D58" s="9">
         <v>1</v>
       </c>
-      <c r="E58" s="10"/>
+      <c r="E58" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8">
         <v>100300040</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I58"/>
       <c r="J58"/>
@@ -3160,7 +3313,7 @@
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
       <c r="H59" s="9" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
@@ -3181,12 +3334,12 @@
         <v>0</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="12"/>
       <c r="H60" s="12" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
@@ -3207,12 +3360,12 @@
         <v>0</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="12"/>
       <c r="H61" s="12" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
@@ -3233,12 +3386,12 @@
         <v>0</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="12"/>
       <c r="H62" s="12" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
@@ -3259,12 +3412,12 @@
         <v>0</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F63" s="12"/>
       <c r="G63" s="12"/>
       <c r="H63" s="12" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
@@ -3285,12 +3438,12 @@
         <v>0</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F64" s="12"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
@@ -3311,12 +3464,12 @@
         <v>0</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F65" s="12"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K65" s="13"/>
       <c r="L65" s="13"/>
@@ -3337,12 +3490,12 @@
         <v>0</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F66" s="12"/>
       <c r="G66" s="12"/>
       <c r="H66" s="12" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
@@ -3363,12 +3516,12 @@
         <v>0</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
@@ -3389,12 +3542,12 @@
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
@@ -3415,12 +3568,12 @@
         <v>2</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="K69" s="13"/>
       <c r="L69" s="13"/>
@@ -3441,14 +3594,14 @@
         <v>0</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F70" s="12">
         <v>9</v>
       </c>
       <c r="G70" s="12"/>
       <c r="H70" s="15" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
@@ -3469,14 +3622,14 @@
         <v>0</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F71" s="12">
         <v>9</v>
       </c>
       <c r="G71" s="12"/>
       <c r="H71" s="15" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
@@ -3497,14 +3650,14 @@
         <v>0</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F72" s="12">
         <v>9</v>
       </c>
       <c r="G72" s="12"/>
       <c r="H72" s="15" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
@@ -3525,14 +3678,14 @@
         <v>0</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F73" s="12">
         <v>9</v>
       </c>
       <c r="G73" s="12"/>
       <c r="H73" s="15" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="K73" s="13"/>
       <c r="L73" s="13"/>
@@ -3553,14 +3706,14 @@
         <v>0</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F74" s="12">
         <v>9</v>
       </c>
       <c r="G74" s="12"/>
       <c r="H74" s="15" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
@@ -3581,14 +3734,14 @@
         <v>0</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F75" s="12">
         <v>9</v>
       </c>
       <c r="G75" s="12"/>
       <c r="H75" s="15" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
@@ -3609,14 +3762,14 @@
         <v>0</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F76" s="12">
         <v>9</v>
       </c>
       <c r="G76" s="12"/>
       <c r="H76" s="15" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
@@ -3637,14 +3790,14 @@
         <v>0</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F77" s="12">
         <v>9</v>
       </c>
       <c r="G77" s="12"/>
       <c r="H77" s="15" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
@@ -3664,11 +3817,13 @@
       <c r="D78" s="9">
         <v>0</v>
       </c>
-      <c r="E78" s="10"/>
+      <c r="E78" s="10" t="s">
+        <v>134</v>
+      </c>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="H78" s="9" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K78" s="13"/>
       <c r="L78" s="13"/>
@@ -3688,11 +3843,13 @@
       <c r="D79" s="9">
         <v>0</v>
       </c>
-      <c r="E79" s="10"/>
+      <c r="E79" s="10" t="s">
+        <v>136</v>
+      </c>
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
       <c r="H79" s="9" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
@@ -3712,11 +3869,13 @@
       <c r="D80" s="9">
         <v>0</v>
       </c>
-      <c r="E80" s="10"/>
+      <c r="E80" s="10" t="s">
+        <v>138</v>
+      </c>
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
       <c r="H80" s="9" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
@@ -3736,11 +3895,13 @@
       <c r="D81" s="9">
         <v>0</v>
       </c>
-      <c r="E81" s="10"/>
+      <c r="E81" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
       <c r="H81" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="K81" s="13"/>
       <c r="L81" s="13"/>
@@ -3760,11 +3921,13 @@
       <c r="D82" s="9">
         <v>0</v>
       </c>
-      <c r="E82" s="10"/>
+      <c r="E82" s="10" t="s">
+        <v>142</v>
+      </c>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
       <c r="H82" s="9" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="K82" s="13"/>
       <c r="L82" s="13"/>
@@ -3784,11 +3947,13 @@
       <c r="D83" s="9">
         <v>0</v>
       </c>
-      <c r="E83" s="10"/>
+      <c r="E83" s="10" t="s">
+        <v>144</v>
+      </c>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
       <c r="H83" s="9" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="K83" s="13"/>
       <c r="L83" s="13"/>
@@ -3808,11 +3973,13 @@
       <c r="D84" s="9">
         <v>2</v>
       </c>
-      <c r="E84" s="10"/>
+      <c r="E84" s="10" t="s">
+        <v>146</v>
+      </c>
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
       <c r="H84" s="9" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
@@ -3832,11 +3999,13 @@
       <c r="D85" s="9">
         <v>1</v>
       </c>
-      <c r="E85" s="10"/>
+      <c r="E85" s="10" t="s">
+        <v>148</v>
+      </c>
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
       <c r="H85" s="9" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K85" s="13"/>
       <c r="L85" s="13"/>
@@ -3856,11 +4025,13 @@
       <c r="D86" s="9">
         <v>2</v>
       </c>
-      <c r="E86" s="10"/>
+      <c r="E86" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
       <c r="H86" s="9" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="K86" s="13"/>
       <c r="L86" s="13"/>
@@ -3880,11 +4051,13 @@
       <c r="D87" s="9">
         <v>2</v>
       </c>
-      <c r="E87" s="10"/>
+      <c r="E87" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
       <c r="H87" s="9" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="K87" s="13"/>
       <c r="L87" s="13"/>
@@ -3904,11 +4077,13 @@
       <c r="D88" s="9">
         <v>2</v>
       </c>
-      <c r="E88" s="10"/>
+      <c r="E88" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
       <c r="H88" s="9" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="K88" s="13"/>
       <c r="L88" s="13"/>
@@ -3928,11 +4103,13 @@
       <c r="D89" s="9">
         <v>2</v>
       </c>
-      <c r="E89" s="10"/>
+      <c r="E89" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
       <c r="H89" s="9" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="K89" s="13"/>
       <c r="L89" s="13"/>
@@ -3952,11 +4129,13 @@
       <c r="D90" s="9">
         <v>2</v>
       </c>
-      <c r="E90" s="10"/>
+      <c r="E90" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
       <c r="H90" s="9" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
@@ -3976,11 +4155,13 @@
       <c r="D91" s="9">
         <v>2</v>
       </c>
-      <c r="E91" s="10"/>
+      <c r="E91" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
       <c r="H91" s="9" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="K91" s="13"/>
       <c r="L91" s="13"/>
@@ -4000,11 +4181,13 @@
       <c r="D92" s="9">
         <v>2</v>
       </c>
-      <c r="E92" s="10"/>
+      <c r="E92" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
       <c r="H92" s="9" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K92" s="13"/>
       <c r="L92" s="13"/>
@@ -4024,11 +4207,13 @@
       <c r="D93" s="9">
         <v>2</v>
       </c>
-      <c r="E93" s="10"/>
+      <c r="E93" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
       <c r="H93" s="9" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="K93" s="13"/>
       <c r="L93" s="13"/>
@@ -4048,11 +4233,13 @@
       <c r="D94" s="9">
         <v>2</v>
       </c>
-      <c r="E94" s="10"/>
+      <c r="E94" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
       <c r="H94" s="9" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="K94" s="13"/>
       <c r="L94" s="13"/>
@@ -4072,11 +4259,13 @@
       <c r="D95" s="9">
         <v>2</v>
       </c>
-      <c r="E95" s="10"/>
+      <c r="E95" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
       <c r="H95" s="9" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="K95" s="13"/>
       <c r="L95" s="13"/>
@@ -4096,11 +4285,13 @@
       <c r="D96" s="9">
         <v>2</v>
       </c>
-      <c r="E96" s="10"/>
+      <c r="E96" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
       <c r="H96" s="9" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="K96" s="13"/>
       <c r="L96" s="13"/>
@@ -4120,11 +4311,13 @@
       <c r="D97" s="9">
         <v>2</v>
       </c>
-      <c r="E97" s="10"/>
+      <c r="E97" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
       <c r="H97" s="9" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="K97" s="13"/>
       <c r="L97" s="13"/>
@@ -4144,11 +4337,13 @@
       <c r="D98" s="9">
         <v>2</v>
       </c>
-      <c r="E98" s="10"/>
+      <c r="E98" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
       <c r="H98" s="9" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="K98" s="13"/>
       <c r="L98" s="13"/>
@@ -4168,11 +4363,13 @@
       <c r="D99" s="9">
         <v>2</v>
       </c>
-      <c r="E99" s="10"/>
+      <c r="E99" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
       <c r="H99" s="9" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="K99" s="13"/>
       <c r="L99" s="13"/>
@@ -4192,11 +4389,13 @@
       <c r="D100" s="9">
         <v>2</v>
       </c>
-      <c r="E100" s="10"/>
+      <c r="E100" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
       <c r="H100" s="9" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="K100" s="13"/>
       <c r="L100" s="13"/>
@@ -4216,11 +4415,13 @@
       <c r="D101" s="9">
         <v>2</v>
       </c>
-      <c r="E101" s="10"/>
+      <c r="E101" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
       <c r="H101" s="9" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="K101" s="13"/>
       <c r="L101" s="13"/>
@@ -4240,11 +4441,13 @@
       <c r="D102" s="9">
         <v>2</v>
       </c>
-      <c r="E102" s="10"/>
+      <c r="E102" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
       <c r="H102" s="9" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="K102" s="13"/>
       <c r="L102" s="13"/>
@@ -4264,11 +4467,13 @@
       <c r="D103" s="9">
         <v>2</v>
       </c>
-      <c r="E103" s="10"/>
+      <c r="E103" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
       <c r="H103" s="9" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="K103" s="13"/>
       <c r="L103" s="13"/>
@@ -4288,11 +4493,13 @@
       <c r="D104" s="17">
         <v>0</v>
       </c>
-      <c r="E104" s="17"/>
+      <c r="E104" s="17" t="s">
+        <v>169</v>
+      </c>
       <c r="F104" s="17"/>
       <c r="G104" s="17"/>
       <c r="H104" s="17" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="K104" s="13"/>
       <c r="L104" s="13"/>
@@ -4312,7 +4519,9 @@
       <c r="D105" s="17">
         <v>0</v>
       </c>
-      <c r="E105" s="17"/>
+      <c r="E105" s="17" t="s">
+        <v>171</v>
+      </c>
       <c r="F105" s="17"/>
       <c r="G105" s="17"/>
       <c r="H105" s="17">
@@ -4336,7 +4545,9 @@
       <c r="D106" s="17">
         <v>0</v>
       </c>
-      <c r="E106" s="17"/>
+      <c r="E106" s="17" t="s">
+        <v>172</v>
+      </c>
       <c r="F106" s="17"/>
       <c r="G106" s="17"/>
       <c r="H106" s="17">
@@ -4360,7 +4571,9 @@
       <c r="D107" s="17">
         <v>0</v>
       </c>
-      <c r="E107" s="17"/>
+      <c r="E107" s="17" t="s">
+        <v>173</v>
+      </c>
       <c r="F107" s="17"/>
       <c r="G107" s="17"/>
       <c r="H107" s="17" t="s">
@@ -4384,7 +4597,9 @@
       <c r="D108" s="17">
         <v>0</v>
       </c>
-      <c r="E108" s="17"/>
+      <c r="E108" s="17" t="s">
+        <v>174</v>
+      </c>
       <c r="F108" s="17"/>
       <c r="G108" s="17"/>
       <c r="H108" s="17" t="s">
@@ -4408,7 +4623,9 @@
       <c r="D109" s="17">
         <v>0</v>
       </c>
-      <c r="E109" s="17"/>
+      <c r="E109" s="17" t="s">
+        <v>175</v>
+      </c>
       <c r="F109" s="17"/>
       <c r="G109" s="17"/>
       <c r="H109" s="17" t="s">
@@ -4432,7 +4649,9 @@
       <c r="D110" s="17">
         <v>0</v>
       </c>
-      <c r="E110" s="17"/>
+      <c r="E110" s="17" t="s">
+        <v>176</v>
+      </c>
       <c r="F110" s="17"/>
       <c r="G110" s="17"/>
       <c r="H110" s="17" t="s">
@@ -4456,11 +4675,13 @@
       <c r="D111" s="17">
         <v>0</v>
       </c>
-      <c r="E111" s="17"/>
+      <c r="E111" s="17" t="s">
+        <v>177</v>
+      </c>
       <c r="F111" s="17"/>
       <c r="G111" s="17"/>
       <c r="H111" s="17" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="K111" s="13"/>
       <c r="L111" s="13"/>
@@ -4480,11 +4701,13 @@
       <c r="D112" s="17">
         <v>0</v>
       </c>
-      <c r="E112" s="17"/>
+      <c r="E112" s="17" t="s">
+        <v>179</v>
+      </c>
       <c r="F112" s="17"/>
       <c r="G112" s="17"/>
       <c r="H112" s="17" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="K112" s="13"/>
       <c r="L112" s="13"/>
@@ -4504,11 +4727,13 @@
       <c r="D113" s="17">
         <v>0</v>
       </c>
-      <c r="E113" s="17"/>
+      <c r="E113" s="17" t="s">
+        <v>181</v>
+      </c>
       <c r="F113" s="17"/>
       <c r="G113" s="17"/>
       <c r="H113" s="17" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="K113" s="13"/>
       <c r="L113" s="13"/>
@@ -4528,11 +4753,13 @@
       <c r="D114" s="17">
         <v>0</v>
       </c>
-      <c r="E114" s="17"/>
+      <c r="E114" s="17" t="s">
+        <v>183</v>
+      </c>
       <c r="F114" s="17"/>
       <c r="G114" s="17"/>
       <c r="H114" s="17" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="K114" s="13"/>
       <c r="L114" s="13"/>
@@ -4552,11 +4779,13 @@
       <c r="D115" s="17">
         <v>1</v>
       </c>
-      <c r="E115" s="17"/>
+      <c r="E115" s="17" t="s">
+        <v>185</v>
+      </c>
       <c r="F115" s="17"/>
       <c r="G115" s="17"/>
       <c r="H115" s="17" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K115" s="13"/>
       <c r="L115" s="13"/>
@@ -4576,11 +4805,13 @@
       <c r="D116" s="17">
         <v>2</v>
       </c>
-      <c r="E116" s="17"/>
+      <c r="E116" s="17" t="s">
+        <v>186</v>
+      </c>
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
       <c r="H116" s="17" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="K116" s="13"/>
       <c r="L116" s="13"/>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -3307,7 +3307,7 @@
         <v>99</v>
       </c>
       <c r="D59" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="8"/>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="187">
   <si>
     <t>图标</t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>出现权重</t>
   </si>
   <si>
     <t>int</t>
@@ -861,12 +858,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -878,6 +869,12 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1761,9 +1758,10 @@
     <col min="5" max="5" width="18.7416666666667" customWidth="1"/>
     <col min="6" max="7" width="19.1666666666667" customWidth="1"/>
     <col min="8" max="8" width="24.1666666666667" customWidth="1"/>
+    <col min="10" max="11" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:9">
+    <row r="1" ht="16.5" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1788,51 +1786,48 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" ht="16.5" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="5"/>
     </row>
     <row r="3" ht="16.5" spans="1:8">
       <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H3" s="5"/>
     </row>
@@ -1861,13 +1856,14 @@
         <v>0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
         <v>9</v>
       </c>
+      <c r="I5" s="13"/>
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
@@ -1887,13 +1883,14 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
         <v>10</v>
       </c>
+      <c r="I6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
@@ -1913,13 +1910,14 @@
         <v>0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>19</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I7" s="13"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
@@ -1939,13 +1937,14 @@
         <v>0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>21</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
@@ -1965,13 +1964,14 @@
         <v>0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>23</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
       <c r="M9" s="13"/>
@@ -1991,13 +1991,14 @@
         <v>0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>25</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
@@ -2017,13 +2018,14 @@
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I11" s="13"/>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="M11" s="13"/>
@@ -2043,13 +2045,14 @@
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>29</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I12" s="13"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
       <c r="M12" s="13"/>
@@ -2069,13 +2072,14 @@
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="I13" s="13"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
@@ -2095,13 +2099,14 @@
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>33</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="I14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
@@ -2121,13 +2126,14 @@
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>35</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
@@ -2147,13 +2153,14 @@
         <v>1</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>37</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
       <c r="M16" s="13"/>
@@ -2173,13 +2180,14 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>39</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="I17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
       <c r="M17" s="13"/>
@@ -2199,13 +2207,14 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>41</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
@@ -2225,13 +2234,14 @@
         <v>2</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="I19" s="13"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
@@ -2251,13 +2261,14 @@
         <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>45</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
@@ -2277,13 +2288,14 @@
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="I21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
@@ -2303,13 +2315,14 @@
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I22" s="13"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
       <c r="M22" s="13"/>
@@ -2329,13 +2342,14 @@
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="I23" s="13"/>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
       <c r="M23" s="13"/>
@@ -2355,13 +2369,14 @@
         <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5" t="s">
-        <v>53</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="I24" s="13"/>
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
@@ -2381,13 +2396,14 @@
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>55</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="I25" s="13"/>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
@@ -2407,13 +2423,14 @@
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>57</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="I26" s="13"/>
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
       <c r="M26" s="13"/>
@@ -2433,13 +2450,14 @@
         <v>2</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7" t="s">
-        <v>58</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="I27" s="13"/>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
       <c r="M27" s="13"/>
@@ -2459,13 +2477,14 @@
         <v>2</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="I28" s="13"/>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
       <c r="M28" s="13"/>
@@ -2485,13 +2504,14 @@
         <v>0</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
       <c r="H29" s="9" t="s">
-        <v>61</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="I29" s="13"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
@@ -2511,13 +2531,14 @@
         <v>0</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
       <c r="H30" s="9" t="s">
-        <v>63</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I30" s="13"/>
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
       <c r="M30" s="13"/>
@@ -2537,13 +2558,14 @@
         <v>0</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
       <c r="H31" s="9" t="s">
-        <v>65</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="I31" s="13"/>
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
@@ -2563,13 +2585,14 @@
         <v>0</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
       <c r="H32" s="9" t="s">
-        <v>29</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I32" s="13"/>
       <c r="K32" s="13"/>
       <c r="L32" s="13"/>
       <c r="M32" s="13"/>
@@ -2589,13 +2612,14 @@
         <v>0</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="9" t="s">
-        <v>68</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="I33" s="13"/>
       <c r="K33" s="13"/>
       <c r="L33" s="13"/>
       <c r="M33" s="13"/>
@@ -2615,13 +2639,14 @@
         <v>0</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
       <c r="H34" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I34" s="13"/>
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
       <c r="M34" s="13"/>
@@ -2641,15 +2666,16 @@
         <v>1</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8">
         <v>100300107</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="I35" s="13"/>
       <c r="K35" s="13"/>
       <c r="L35" s="13"/>
       <c r="M35" s="13"/>
@@ -2669,15 +2695,16 @@
         <v>1</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8">
         <v>100300108</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>73</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I36" s="13"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
       <c r="M36" s="13"/>
@@ -2697,15 +2724,16 @@
         <v>1</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8">
         <v>100300109</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>74</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="13"/>
       <c r="M37" s="13"/>
@@ -2725,15 +2753,16 @@
         <v>1</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8">
         <v>100300110</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>75</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="I38" s="13"/>
       <c r="K38" s="13"/>
       <c r="L38" s="13"/>
       <c r="M38" s="13"/>
@@ -2753,17 +2782,17 @@
         <v>1</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="8">
         <v>100300021</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" ht="16.5" spans="1:11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" ht="16.5" spans="1:9">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
         <v>10030022</v>
@@ -2778,20 +2807,18 @@
         <v>1</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8">
         <v>100300022</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I40"/>
-      <c r="J40"/>
-      <c r="K40" s="13"/>
-    </row>
-    <row r="41" customFormat="1" ht="16.5" spans="1:11">
+        <v>77</v>
+      </c>
+      <c r="I40" s="13"/>
+    </row>
+    <row r="41" customFormat="1" ht="16.5" spans="1:9">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
         <v>10030023</v>
@@ -2806,20 +2833,18 @@
         <v>1</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8">
         <v>100300023</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I41"/>
-      <c r="J41"/>
-      <c r="K41" s="13"/>
-    </row>
-    <row r="42" customFormat="1" ht="16.5" spans="1:11">
+        <v>78</v>
+      </c>
+      <c r="I41" s="13"/>
+    </row>
+    <row r="42" customFormat="1" ht="16.5" spans="1:9">
       <c r="A42" s="8">
         <f t="shared" si="0"/>
         <v>10030024</v>
@@ -2834,20 +2859,18 @@
         <v>1</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8">
         <v>100300024</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I42"/>
-      <c r="J42"/>
-      <c r="K42" s="13"/>
-    </row>
-    <row r="43" customFormat="1" ht="16.5" spans="1:11">
+        <v>79</v>
+      </c>
+      <c r="I42" s="13"/>
+    </row>
+    <row r="43" customFormat="1" ht="16.5" spans="1:9">
       <c r="A43" s="8">
         <f t="shared" si="0"/>
         <v>10030025</v>
@@ -2862,20 +2885,18 @@
         <v>1</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F43" s="8"/>
       <c r="G43" s="8">
         <v>100300025</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="I43"/>
-      <c r="J43"/>
-      <c r="K43" s="13"/>
-    </row>
-    <row r="44" customFormat="1" ht="16.5" spans="1:11">
+        <v>80</v>
+      </c>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" customFormat="1" ht="16.5" spans="1:9">
       <c r="A44" s="8">
         <f t="shared" si="0"/>
         <v>10030026</v>
@@ -2890,20 +2911,18 @@
         <v>1</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8">
         <v>100300026</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I44"/>
-      <c r="J44"/>
-      <c r="K44" s="13"/>
-    </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:11">
+        <v>81</v>
+      </c>
+      <c r="I44" s="13"/>
+    </row>
+    <row r="45" customFormat="1" ht="16.5" spans="1:9">
       <c r="A45" s="8">
         <f t="shared" si="0"/>
         <v>10030027</v>
@@ -2918,20 +2937,18 @@
         <v>1</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="8">
         <v>100300027</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45" s="13"/>
-    </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:11">
+        <v>82</v>
+      </c>
+      <c r="I45" s="13"/>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:9">
       <c r="A46" s="8">
         <f t="shared" si="0"/>
         <v>10030028</v>
@@ -2946,20 +2963,18 @@
         <v>1</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8">
         <v>100300028</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I46"/>
-      <c r="J46"/>
-      <c r="K46" s="13"/>
-    </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:11">
+        <v>83</v>
+      </c>
+      <c r="I46" s="13"/>
+    </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:9">
       <c r="A47" s="8">
         <f t="shared" ref="A47:A59" si="1">B47*100+C47</f>
         <v>10030029</v>
@@ -2974,20 +2989,18 @@
         <v>1</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8">
         <v>100300029</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="I47"/>
-      <c r="J47"/>
-      <c r="K47" s="13"/>
-    </row>
-    <row r="48" customFormat="1" ht="16.5" spans="1:11">
+        <v>84</v>
+      </c>
+      <c r="I47" s="13"/>
+    </row>
+    <row r="48" customFormat="1" ht="16.5" spans="1:9">
       <c r="A48" s="8">
         <f t="shared" si="1"/>
         <v>10030030</v>
@@ -3002,20 +3015,18 @@
         <v>1</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8">
         <v>100300030</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I48"/>
-      <c r="J48"/>
-      <c r="K48" s="13"/>
-    </row>
-    <row r="49" customFormat="1" ht="16.5" spans="1:11">
+        <v>85</v>
+      </c>
+      <c r="I48" s="13"/>
+    </row>
+    <row r="49" customFormat="1" ht="16.5" spans="1:9">
       <c r="A49" s="8">
         <f t="shared" si="1"/>
         <v>10030031</v>
@@ -3030,20 +3041,18 @@
         <v>1</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8">
         <v>100300031</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I49"/>
-      <c r="J49"/>
-      <c r="K49" s="13"/>
-    </row>
-    <row r="50" customFormat="1" ht="16.5" spans="1:11">
+        <v>86</v>
+      </c>
+      <c r="I49" s="13"/>
+    </row>
+    <row r="50" customFormat="1" ht="16.5" spans="1:9">
       <c r="A50" s="8">
         <f t="shared" si="1"/>
         <v>10030032</v>
@@ -3058,20 +3067,18 @@
         <v>1</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8">
         <v>100300032</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="I50"/>
-      <c r="J50"/>
-      <c r="K50" s="13"/>
-    </row>
-    <row r="51" customFormat="1" ht="16.5" spans="1:11">
+        <v>87</v>
+      </c>
+      <c r="I50" s="13"/>
+    </row>
+    <row r="51" customFormat="1" ht="16.5" spans="1:9">
       <c r="A51" s="8">
         <f t="shared" si="1"/>
         <v>10030033</v>
@@ -3086,20 +3093,18 @@
         <v>1</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8">
         <v>100300033</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="I51"/>
-      <c r="J51"/>
-      <c r="K51" s="13"/>
-    </row>
-    <row r="52" customFormat="1" ht="16.5" spans="1:11">
+        <v>88</v>
+      </c>
+      <c r="I51" s="13"/>
+    </row>
+    <row r="52" customFormat="1" ht="16.5" spans="1:9">
       <c r="A52" s="8">
         <f t="shared" si="1"/>
         <v>10030034</v>
@@ -3114,20 +3119,18 @@
         <v>1</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8">
         <v>100300034</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I52"/>
-      <c r="J52"/>
-      <c r="K52" s="13"/>
-    </row>
-    <row r="53" customFormat="1" ht="16.5" spans="1:11">
+        <v>89</v>
+      </c>
+      <c r="I52" s="13"/>
+    </row>
+    <row r="53" customFormat="1" ht="16.5" spans="1:9">
       <c r="A53" s="8">
         <f t="shared" si="1"/>
         <v>10030035</v>
@@ -3142,20 +3145,18 @@
         <v>1</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="8">
         <v>100300035</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53" s="13"/>
-    </row>
-    <row r="54" customFormat="1" ht="16.5" spans="1:11">
+        <v>90</v>
+      </c>
+      <c r="I53" s="13"/>
+    </row>
+    <row r="54" customFormat="1" ht="16.5" spans="1:9">
       <c r="A54" s="8">
         <f t="shared" si="1"/>
         <v>10030036</v>
@@ -3170,20 +3171,18 @@
         <v>1</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8">
         <v>100300036</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="K54" s="13"/>
-    </row>
-    <row r="55" customFormat="1" ht="16.5" spans="1:11">
+        <v>91</v>
+      </c>
+      <c r="I54" s="13"/>
+    </row>
+    <row r="55" customFormat="1" ht="16.5" spans="1:9">
       <c r="A55" s="8">
         <f t="shared" si="1"/>
         <v>10030037</v>
@@ -3198,20 +3197,18 @@
         <v>1</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8">
         <v>100300037</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="I55"/>
-      <c r="J55"/>
-      <c r="K55" s="13"/>
-    </row>
-    <row r="56" customFormat="1" ht="16.5" spans="1:11">
+        <v>92</v>
+      </c>
+      <c r="I55" s="13"/>
+    </row>
+    <row r="56" customFormat="1" ht="16.5" spans="1:9">
       <c r="A56" s="8">
         <f t="shared" si="1"/>
         <v>10030038</v>
@@ -3226,20 +3223,18 @@
         <v>1</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8">
         <v>100300038</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="I56"/>
-      <c r="J56"/>
-      <c r="K56" s="13"/>
-    </row>
-    <row r="57" customFormat="1" ht="16.5" spans="1:11">
+        <v>93</v>
+      </c>
+      <c r="I56" s="13"/>
+    </row>
+    <row r="57" customFormat="1" ht="16.5" spans="1:9">
       <c r="A57" s="8">
         <f t="shared" si="1"/>
         <v>10030039</v>
@@ -3254,20 +3249,18 @@
         <v>1</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F57" s="8"/>
       <c r="G57" s="8">
         <v>100300039</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I57"/>
-      <c r="J57"/>
-      <c r="K57" s="13"/>
-    </row>
-    <row r="58" customFormat="1" ht="16.5" spans="1:11">
+        <v>94</v>
+      </c>
+      <c r="I57" s="13"/>
+    </row>
+    <row r="58" customFormat="1" ht="16.5" spans="1:9">
       <c r="A58" s="8">
         <f t="shared" si="1"/>
         <v>10030040</v>
@@ -3282,18 +3275,16 @@
         <v>1</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8">
         <v>100300040</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="I58"/>
-      <c r="J58"/>
-      <c r="K58" s="13"/>
+        <v>95</v>
+      </c>
+      <c r="I58" s="13"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:13">
       <c r="A59" s="8">
@@ -3313,8 +3304,9 @@
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
       <c r="H59" s="9" t="s">
-        <v>97</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="I59" s="13"/>
       <c r="K59" s="13"/>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
@@ -3334,13 +3326,14 @@
         <v>0</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="12"/>
       <c r="H60" s="12" t="s">
-        <v>99</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I60" s="13"/>
       <c r="K60" s="13"/>
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
@@ -3360,13 +3353,14 @@
         <v>0</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="12"/>
       <c r="H61" s="12" t="s">
-        <v>101</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I61" s="13"/>
       <c r="K61" s="13"/>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
@@ -3386,13 +3380,14 @@
         <v>0</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="12"/>
       <c r="H62" s="12" t="s">
-        <v>103</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I62" s="13"/>
       <c r="K62" s="13"/>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
@@ -3412,13 +3407,14 @@
         <v>0</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F63" s="12"/>
       <c r="G63" s="12"/>
       <c r="H63" s="12" t="s">
-        <v>105</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="I63" s="13"/>
       <c r="K63" s="13"/>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
@@ -3438,13 +3434,14 @@
         <v>0</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F64" s="12"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12" t="s">
-        <v>107</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="I64" s="13"/>
       <c r="K64" s="13"/>
       <c r="L64" s="13"/>
       <c r="M64" s="13"/>
@@ -3464,13 +3461,14 @@
         <v>0</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F65" s="12"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="I65" s="13"/>
       <c r="K65" s="13"/>
       <c r="L65" s="13"/>
       <c r="M65" s="13"/>
@@ -3490,13 +3488,14 @@
         <v>0</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F66" s="12"/>
       <c r="G66" s="12"/>
       <c r="H66" s="12" t="s">
-        <v>111</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="I66" s="13"/>
       <c r="K66" s="13"/>
       <c r="L66" s="13"/>
       <c r="M66" s="13"/>
@@ -3516,13 +3515,14 @@
         <v>0</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12" t="s">
-        <v>113</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="I67" s="13"/>
       <c r="K67" s="13"/>
       <c r="L67" s="13"/>
       <c r="M67" s="13"/>
@@ -3542,13 +3542,14 @@
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F68" s="12"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12" t="s">
-        <v>115</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="I68" s="13"/>
       <c r="K68" s="13"/>
       <c r="L68" s="13"/>
       <c r="M68" s="13"/>
@@ -3568,13 +3569,14 @@
         <v>2</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12" t="s">
-        <v>117</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="I69" s="13"/>
       <c r="K69" s="13"/>
       <c r="L69" s="13"/>
       <c r="M69" s="13"/>
@@ -3594,15 +3596,16 @@
         <v>0</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F70" s="12">
         <v>9</v>
       </c>
       <c r="G70" s="12"/>
       <c r="H70" s="15" t="s">
-        <v>119</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="I70" s="13"/>
       <c r="K70" s="13"/>
       <c r="L70" s="13"/>
       <c r="M70" s="13"/>
@@ -3622,15 +3625,16 @@
         <v>0</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F71" s="12">
         <v>9</v>
       </c>
       <c r="G71" s="12"/>
       <c r="H71" s="15" t="s">
-        <v>121</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="I71" s="13"/>
       <c r="K71" s="13"/>
       <c r="L71" s="13"/>
       <c r="M71" s="13"/>
@@ -3650,15 +3654,16 @@
         <v>0</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F72" s="12">
         <v>9</v>
       </c>
       <c r="G72" s="12"/>
       <c r="H72" s="15" t="s">
-        <v>123</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="I72" s="13"/>
       <c r="K72" s="13"/>
       <c r="L72" s="13"/>
       <c r="M72" s="13"/>
@@ -3678,15 +3683,16 @@
         <v>0</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F73" s="12">
         <v>9</v>
       </c>
       <c r="G73" s="12"/>
       <c r="H73" s="15" t="s">
-        <v>125</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="I73" s="13"/>
       <c r="K73" s="13"/>
       <c r="L73" s="13"/>
       <c r="M73" s="13"/>
@@ -3706,15 +3712,16 @@
         <v>0</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F74" s="12">
         <v>9</v>
       </c>
       <c r="G74" s="12"/>
       <c r="H74" s="15" t="s">
-        <v>127</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="I74" s="13"/>
       <c r="K74" s="13"/>
       <c r="L74" s="13"/>
       <c r="M74" s="13"/>
@@ -3734,15 +3741,16 @@
         <v>0</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F75" s="12">
         <v>9</v>
       </c>
       <c r="G75" s="12"/>
       <c r="H75" s="15" t="s">
-        <v>129</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="I75" s="13"/>
       <c r="K75" s="13"/>
       <c r="L75" s="13"/>
       <c r="M75" s="13"/>
@@ -3762,15 +3770,16 @@
         <v>0</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F76" s="12">
         <v>9</v>
       </c>
       <c r="G76" s="12"/>
       <c r="H76" s="15" t="s">
-        <v>131</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="I76" s="13"/>
       <c r="K76" s="13"/>
       <c r="L76" s="13"/>
       <c r="M76" s="13"/>
@@ -3790,15 +3799,16 @@
         <v>0</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F77" s="12">
         <v>9</v>
       </c>
       <c r="G77" s="12"/>
       <c r="H77" s="15" t="s">
-        <v>133</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I77" s="13"/>
       <c r="K77" s="13"/>
       <c r="L77" s="13"/>
       <c r="M77" s="13"/>
@@ -3818,13 +3828,14 @@
         <v>0</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="H78" s="9" t="s">
-        <v>135</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="I78" s="13"/>
       <c r="K78" s="13"/>
       <c r="L78" s="13"/>
       <c r="M78" s="13"/>
@@ -3844,13 +3855,14 @@
         <v>0</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
       <c r="H79" s="9" t="s">
-        <v>137</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="I79" s="13"/>
       <c r="K79" s="13"/>
       <c r="L79" s="13"/>
       <c r="M79" s="13"/>
@@ -3870,13 +3882,14 @@
         <v>0</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
       <c r="H80" s="9" t="s">
-        <v>139</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="I80" s="13"/>
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
       <c r="M80" s="13"/>
@@ -3896,13 +3909,14 @@
         <v>0</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
       <c r="H81" s="9" t="s">
-        <v>141</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="I81" s="13"/>
       <c r="K81" s="13"/>
       <c r="L81" s="13"/>
       <c r="M81" s="13"/>
@@ -3922,13 +3936,14 @@
         <v>0</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
       <c r="H82" s="9" t="s">
-        <v>143</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="I82" s="13"/>
       <c r="K82" s="13"/>
       <c r="L82" s="13"/>
       <c r="M82" s="13"/>
@@ -3948,13 +3963,14 @@
         <v>0</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
       <c r="H83" s="9" t="s">
-        <v>145</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="I83" s="13"/>
       <c r="K83" s="13"/>
       <c r="L83" s="13"/>
       <c r="M83" s="13"/>
@@ -3974,13 +3990,14 @@
         <v>2</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
       <c r="H84" s="9" t="s">
-        <v>147</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="I84" s="13"/>
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
       <c r="M84" s="13"/>
@@ -4000,13 +4017,14 @@
         <v>1</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
       <c r="H85" s="9" t="s">
-        <v>115</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="I85" s="13"/>
       <c r="K85" s="13"/>
       <c r="L85" s="13"/>
       <c r="M85" s="13"/>
@@ -4026,13 +4044,14 @@
         <v>2</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
       <c r="H86" s="9" t="s">
-        <v>150</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="I86" s="13"/>
       <c r="K86" s="13"/>
       <c r="L86" s="13"/>
       <c r="M86" s="13"/>
@@ -4052,13 +4071,14 @@
         <v>2</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
       <c r="H87" s="9" t="s">
-        <v>151</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="I87" s="13"/>
       <c r="K87" s="13"/>
       <c r="L87" s="13"/>
       <c r="M87" s="13"/>
@@ -4078,13 +4098,14 @@
         <v>2</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
       <c r="H88" s="9" t="s">
-        <v>152</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="I88" s="13"/>
       <c r="K88" s="13"/>
       <c r="L88" s="13"/>
       <c r="M88" s="13"/>
@@ -4104,13 +4125,14 @@
         <v>2</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
       <c r="H89" s="9" t="s">
-        <v>154</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="I89" s="13"/>
       <c r="K89" s="13"/>
       <c r="L89" s="13"/>
       <c r="M89" s="13"/>
@@ -4130,13 +4152,14 @@
         <v>2</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
       <c r="H90" s="9" t="s">
-        <v>155</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="I90" s="13"/>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
       <c r="M90" s="13"/>
@@ -4156,13 +4179,14 @@
         <v>2</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
       <c r="H91" s="9" t="s">
-        <v>156</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="I91" s="13"/>
       <c r="K91" s="13"/>
       <c r="L91" s="13"/>
       <c r="M91" s="13"/>
@@ -4182,13 +4206,14 @@
         <v>2</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
       <c r="H92" s="9" t="s">
-        <v>157</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="I92" s="13"/>
       <c r="K92" s="13"/>
       <c r="L92" s="13"/>
       <c r="M92" s="13"/>
@@ -4208,13 +4233,14 @@
         <v>2</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
       <c r="H93" s="9" t="s">
-        <v>158</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="I93" s="13"/>
       <c r="K93" s="13"/>
       <c r="L93" s="13"/>
       <c r="M93" s="13"/>
@@ -4234,13 +4260,14 @@
         <v>2</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
       <c r="H94" s="9" t="s">
-        <v>159</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="I94" s="13"/>
       <c r="K94" s="13"/>
       <c r="L94" s="13"/>
       <c r="M94" s="13"/>
@@ -4260,13 +4287,14 @@
         <v>2</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
       <c r="H95" s="9" t="s">
-        <v>160</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="I95" s="13"/>
       <c r="K95" s="13"/>
       <c r="L95" s="13"/>
       <c r="M95" s="13"/>
@@ -4286,13 +4314,14 @@
         <v>2</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
       <c r="H96" s="9" t="s">
-        <v>161</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="I96" s="13"/>
       <c r="K96" s="13"/>
       <c r="L96" s="13"/>
       <c r="M96" s="13"/>
@@ -4312,13 +4341,14 @@
         <v>2</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
       <c r="H97" s="9" t="s">
-        <v>162</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="I97" s="13"/>
       <c r="K97" s="13"/>
       <c r="L97" s="13"/>
       <c r="M97" s="13"/>
@@ -4338,13 +4368,14 @@
         <v>2</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
       <c r="H98" s="9" t="s">
-        <v>163</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="I98" s="13"/>
       <c r="K98" s="13"/>
       <c r="L98" s="13"/>
       <c r="M98" s="13"/>
@@ -4364,13 +4395,14 @@
         <v>2</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
       <c r="H99" s="9" t="s">
-        <v>164</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="I99" s="13"/>
       <c r="K99" s="13"/>
       <c r="L99" s="13"/>
       <c r="M99" s="13"/>
@@ -4390,13 +4422,14 @@
         <v>2</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
       <c r="H100" s="9" t="s">
-        <v>165</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="I100" s="13"/>
       <c r="K100" s="13"/>
       <c r="L100" s="13"/>
       <c r="M100" s="13"/>
@@ -4416,13 +4449,14 @@
         <v>2</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
       <c r="H101" s="9" t="s">
-        <v>166</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="I101" s="13"/>
       <c r="K101" s="13"/>
       <c r="L101" s="13"/>
       <c r="M101" s="13"/>
@@ -4442,13 +4476,14 @@
         <v>2</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
       <c r="H102" s="9" t="s">
-        <v>167</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="I102" s="13"/>
       <c r="K102" s="13"/>
       <c r="L102" s="13"/>
       <c r="M102" s="13"/>
@@ -4468,13 +4503,14 @@
         <v>2</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
       <c r="H103" s="9" t="s">
-        <v>168</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="I103" s="13"/>
       <c r="K103" s="13"/>
       <c r="L103" s="13"/>
       <c r="M103" s="13"/>
@@ -4494,13 +4530,14 @@
         <v>0</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F104" s="17"/>
       <c r="G104" s="17"/>
       <c r="H104" s="17" t="s">
-        <v>170</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="I104" s="13"/>
       <c r="K104" s="13"/>
       <c r="L104" s="13"/>
       <c r="M104" s="13"/>
@@ -4520,13 +4557,14 @@
         <v>0</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F105" s="17"/>
       <c r="G105" s="17"/>
       <c r="H105" s="17">
         <v>9</v>
       </c>
+      <c r="I105" s="13"/>
       <c r="K105" s="13"/>
       <c r="L105" s="13"/>
       <c r="M105" s="13"/>
@@ -4546,13 +4584,14 @@
         <v>0</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F106" s="17"/>
       <c r="G106" s="17"/>
       <c r="H106" s="17">
         <v>10</v>
       </c>
+      <c r="I106" s="13"/>
       <c r="K106" s="13"/>
       <c r="L106" s="13"/>
       <c r="M106" s="13"/>
@@ -4572,13 +4611,14 @@
         <v>0</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F107" s="17"/>
       <c r="G107" s="17"/>
       <c r="H107" s="17" t="s">
-        <v>19</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I107" s="13"/>
       <c r="K107" s="13"/>
       <c r="L107" s="13"/>
       <c r="M107" s="13"/>
@@ -4598,13 +4638,14 @@
         <v>0</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F108" s="17"/>
       <c r="G108" s="17"/>
       <c r="H108" s="17" t="s">
-        <v>21</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I108" s="13"/>
       <c r="K108" s="13"/>
       <c r="L108" s="13"/>
       <c r="M108" s="13"/>
@@ -4624,13 +4665,14 @@
         <v>0</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F109" s="17"/>
       <c r="G109" s="17"/>
       <c r="H109" s="17" t="s">
-        <v>23</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I109" s="13"/>
       <c r="K109" s="13"/>
       <c r="L109" s="13"/>
       <c r="M109" s="13"/>
@@ -4650,13 +4692,14 @@
         <v>0</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F110" s="17"/>
       <c r="G110" s="17"/>
       <c r="H110" s="17" t="s">
-        <v>25</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I110" s="13"/>
       <c r="K110" s="13"/>
       <c r="L110" s="13"/>
       <c r="M110" s="13"/>
@@ -4676,13 +4719,14 @@
         <v>0</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F111" s="17"/>
       <c r="G111" s="17"/>
       <c r="H111" s="17" t="s">
-        <v>178</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="I111" s="13"/>
       <c r="K111" s="13"/>
       <c r="L111" s="13"/>
       <c r="M111" s="13"/>
@@ -4702,13 +4746,14 @@
         <v>0</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F112" s="17"/>
       <c r="G112" s="17"/>
       <c r="H112" s="17" t="s">
-        <v>180</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="I112" s="13"/>
       <c r="K112" s="13"/>
       <c r="L112" s="13"/>
       <c r="M112" s="13"/>
@@ -4728,13 +4773,14 @@
         <v>0</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F113" s="17"/>
       <c r="G113" s="17"/>
       <c r="H113" s="17" t="s">
-        <v>182</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="I113" s="13"/>
       <c r="K113" s="13"/>
       <c r="L113" s="13"/>
       <c r="M113" s="13"/>
@@ -4754,13 +4800,14 @@
         <v>0</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F114" s="17"/>
       <c r="G114" s="17"/>
       <c r="H114" s="17" t="s">
-        <v>184</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="I114" s="13"/>
       <c r="K114" s="13"/>
       <c r="L114" s="13"/>
       <c r="M114" s="13"/>
@@ -4780,13 +4827,14 @@
         <v>1</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F115" s="17"/>
       <c r="G115" s="17"/>
       <c r="H115" s="17" t="s">
-        <v>115</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="I115" s="13"/>
       <c r="K115" s="13"/>
       <c r="L115" s="13"/>
       <c r="M115" s="13"/>
@@ -4806,13 +4854,14 @@
         <v>2</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
       <c r="H116" s="17" t="s">
-        <v>187</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="I116" s="13"/>
       <c r="K116" s="13"/>
       <c r="L116" s="13"/>
       <c r="M116" s="13"/>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -856,14 +856,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -875,7 +868,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -558,19 +558,19 @@
     <t>cs_zjm_tb_10.png</t>
   </si>
   <si>
+    <t>cs_zjm_tb_8.png</t>
+  </si>
+  <si>
+    <t>横财神第1行</t>
+  </si>
+  <si>
+    <t>横财神第2行</t>
+  </si>
+  <si>
+    <t>横财神第3行</t>
+  </si>
+  <si>
     <t>cs_zjm_tb_7.png</t>
-  </si>
-  <si>
-    <t>横财神第1行</t>
-  </si>
-  <si>
-    <t>横财神第2行</t>
-  </si>
-  <si>
-    <t>横财神第3行</t>
-  </si>
-  <si>
-    <t>cs_zjm_tb_8.png</t>
   </si>
   <si>
     <t>横财神第2列</t>
@@ -856,6 +856,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -868,14 +869,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="187">
   <si>
     <t>图标</t>
   </si>
@@ -858,12 +858,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -875,6 +869,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1750,7 +1750,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -4517,7 +4517,7 @@
     </row>
     <row r="104" ht="16.5" spans="1:13">
       <c r="A104" s="16">
-        <f t="shared" ref="A104:A116" si="4">B104*100+C104</f>
+        <f t="shared" ref="A104:A140" si="4">B104*100+C104</f>
         <v>10140001</v>
       </c>
       <c r="B104" s="16">
@@ -4865,6 +4865,654 @@
       <c r="K116" s="13"/>
       <c r="L116" s="13"/>
       <c r="M116" s="13"/>
+    </row>
+    <row r="117" ht="16.5" spans="1:13">
+      <c r="A117" s="4">
+        <f t="shared" si="4"/>
+        <v>10240001</v>
+      </c>
+      <c r="B117" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C117" s="5">
+        <v>1</v>
+      </c>
+      <c r="D117" s="5">
+        <v>0</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5">
+        <v>9</v>
+      </c>
+      <c r="I117" s="13"/>
+      <c r="K117" s="13"/>
+      <c r="L117" s="13"/>
+      <c r="M117" s="13"/>
+    </row>
+    <row r="118" ht="16.5" spans="1:13">
+      <c r="A118" s="4">
+        <f t="shared" si="4"/>
+        <v>10240002</v>
+      </c>
+      <c r="B118" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C118" s="5">
+        <v>2</v>
+      </c>
+      <c r="D118" s="5">
+        <v>0</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5">
+        <v>10</v>
+      </c>
+      <c r="I118" s="13"/>
+      <c r="K118" s="13"/>
+      <c r="L118" s="13"/>
+      <c r="M118" s="13"/>
+    </row>
+    <row r="119" ht="16.5" spans="1:13">
+      <c r="A119" s="4">
+        <f t="shared" si="4"/>
+        <v>10240003</v>
+      </c>
+      <c r="B119" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C119" s="5">
+        <v>3</v>
+      </c>
+      <c r="D119" s="5">
+        <v>0</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" s="13"/>
+      <c r="K119" s="13"/>
+      <c r="L119" s="13"/>
+      <c r="M119" s="13"/>
+    </row>
+    <row r="120" ht="16.5" spans="1:13">
+      <c r="A120" s="4">
+        <f t="shared" si="4"/>
+        <v>10240004</v>
+      </c>
+      <c r="B120" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C120" s="5">
+        <v>4</v>
+      </c>
+      <c r="D120" s="5">
+        <v>0</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I120" s="13"/>
+      <c r="K120" s="13"/>
+      <c r="L120" s="13"/>
+      <c r="M120" s="13"/>
+    </row>
+    <row r="121" ht="16.5" spans="1:13">
+      <c r="A121" s="4">
+        <f t="shared" si="4"/>
+        <v>10240005</v>
+      </c>
+      <c r="B121" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C121" s="5">
+        <v>5</v>
+      </c>
+      <c r="D121" s="5">
+        <v>0</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I121" s="13"/>
+      <c r="K121" s="13"/>
+      <c r="L121" s="13"/>
+      <c r="M121" s="13"/>
+    </row>
+    <row r="122" ht="16.5" spans="1:13">
+      <c r="A122" s="4">
+        <f t="shared" si="4"/>
+        <v>10240006</v>
+      </c>
+      <c r="B122" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C122" s="5">
+        <v>6</v>
+      </c>
+      <c r="D122" s="5">
+        <v>0</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I122" s="13"/>
+      <c r="K122" s="13"/>
+      <c r="L122" s="13"/>
+      <c r="M122" s="13"/>
+    </row>
+    <row r="123" ht="16.5" spans="1:13">
+      <c r="A123" s="4">
+        <f t="shared" si="4"/>
+        <v>10240007</v>
+      </c>
+      <c r="B123" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C123" s="5">
+        <v>7</v>
+      </c>
+      <c r="D123" s="5">
+        <v>0</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I123" s="13"/>
+      <c r="K123" s="13"/>
+      <c r="L123" s="13"/>
+      <c r="M123" s="13"/>
+    </row>
+    <row r="124" ht="16.5" spans="1:13">
+      <c r="A124" s="4">
+        <f t="shared" si="4"/>
+        <v>10240008</v>
+      </c>
+      <c r="B124" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C124" s="5">
+        <v>8</v>
+      </c>
+      <c r="D124" s="5">
+        <v>0</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I124" s="13"/>
+      <c r="K124" s="13"/>
+      <c r="L124" s="13"/>
+      <c r="M124" s="13"/>
+    </row>
+    <row r="125" ht="16.5" spans="1:13">
+      <c r="A125" s="4">
+        <f t="shared" si="4"/>
+        <v>10240009</v>
+      </c>
+      <c r="B125" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C125" s="5">
+        <v>9</v>
+      </c>
+      <c r="D125" s="5">
+        <v>0</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I125" s="13"/>
+      <c r="K125" s="13"/>
+      <c r="L125" s="13"/>
+      <c r="M125" s="13"/>
+    </row>
+    <row r="126" ht="16.5" spans="1:13">
+      <c r="A126" s="4">
+        <f t="shared" si="4"/>
+        <v>10240010</v>
+      </c>
+      <c r="B126" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C126" s="5">
+        <v>10</v>
+      </c>
+      <c r="D126" s="5">
+        <v>0</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I126" s="13"/>
+      <c r="K126" s="13"/>
+      <c r="L126" s="13"/>
+      <c r="M126" s="13"/>
+    </row>
+    <row r="127" ht="16.5" spans="1:13">
+      <c r="A127" s="4">
+        <f t="shared" si="4"/>
+        <v>10240011</v>
+      </c>
+      <c r="B127" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C127" s="5">
+        <v>11</v>
+      </c>
+      <c r="D127" s="5">
+        <v>0</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I127" s="13"/>
+      <c r="K127" s="13"/>
+      <c r="L127" s="13"/>
+      <c r="M127" s="13"/>
+    </row>
+    <row r="128" ht="16.5" spans="1:13">
+      <c r="A128" s="4">
+        <f t="shared" si="4"/>
+        <v>10240012</v>
+      </c>
+      <c r="B128" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C128" s="5">
+        <v>12</v>
+      </c>
+      <c r="D128" s="5">
+        <v>1</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I128" s="13"/>
+      <c r="K128" s="13"/>
+      <c r="L128" s="13"/>
+      <c r="M128" s="13"/>
+    </row>
+    <row r="129" ht="16.5" spans="1:13">
+      <c r="A129" s="4">
+        <f t="shared" si="4"/>
+        <v>10240013</v>
+      </c>
+      <c r="B129" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C129" s="5">
+        <v>13</v>
+      </c>
+      <c r="D129" s="5">
+        <v>1</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I129" s="13"/>
+      <c r="K129" s="13"/>
+      <c r="L129" s="13"/>
+      <c r="M129" s="13"/>
+    </row>
+    <row r="130" ht="16.5" spans="1:13">
+      <c r="A130" s="4">
+        <f t="shared" si="4"/>
+        <v>10240014</v>
+      </c>
+      <c r="B130" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C130" s="5">
+        <v>14</v>
+      </c>
+      <c r="D130" s="5">
+        <v>1</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I130" s="13"/>
+      <c r="K130" s="13"/>
+      <c r="L130" s="13"/>
+      <c r="M130" s="13"/>
+    </row>
+    <row r="131" ht="16.5" spans="1:13">
+      <c r="A131" s="4">
+        <f t="shared" si="4"/>
+        <v>10240015</v>
+      </c>
+      <c r="B131" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C131" s="5">
+        <v>15</v>
+      </c>
+      <c r="D131" s="5">
+        <v>2</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I131" s="13"/>
+      <c r="K131" s="13"/>
+      <c r="L131" s="13"/>
+      <c r="M131" s="13"/>
+    </row>
+    <row r="132" ht="16.5" spans="1:13">
+      <c r="A132" s="4">
+        <f t="shared" si="4"/>
+        <v>10240016</v>
+      </c>
+      <c r="B132" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C132" s="5">
+        <v>16</v>
+      </c>
+      <c r="D132" s="5">
+        <v>2</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I132" s="13"/>
+      <c r="K132" s="13"/>
+      <c r="L132" s="13"/>
+      <c r="M132" s="13"/>
+    </row>
+    <row r="133" ht="16.5" spans="1:13">
+      <c r="A133" s="4">
+        <f t="shared" si="4"/>
+        <v>10240017</v>
+      </c>
+      <c r="B133" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C133" s="5">
+        <v>17</v>
+      </c>
+      <c r="D133" s="5">
+        <v>2</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I133" s="13"/>
+      <c r="K133" s="13"/>
+      <c r="L133" s="13"/>
+      <c r="M133" s="13"/>
+    </row>
+    <row r="134" ht="16.5" spans="1:13">
+      <c r="A134" s="4">
+        <f t="shared" si="4"/>
+        <v>10240018</v>
+      </c>
+      <c r="B134" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C134" s="5">
+        <v>18</v>
+      </c>
+      <c r="D134" s="5">
+        <v>2</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I134" s="13"/>
+      <c r="K134" s="13"/>
+      <c r="L134" s="13"/>
+      <c r="M134" s="13"/>
+    </row>
+    <row r="135" ht="16.5" spans="1:13">
+      <c r="A135" s="4">
+        <f t="shared" si="4"/>
+        <v>10240019</v>
+      </c>
+      <c r="B135" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C135" s="5">
+        <v>19</v>
+      </c>
+      <c r="D135" s="5">
+        <v>3</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I135" s="13"/>
+      <c r="K135" s="13"/>
+      <c r="L135" s="13"/>
+      <c r="M135" s="13"/>
+    </row>
+    <row r="136" ht="16.5" spans="1:13">
+      <c r="A136" s="4">
+        <f t="shared" si="4"/>
+        <v>10240020</v>
+      </c>
+      <c r="B136" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C136" s="5">
+        <v>20</v>
+      </c>
+      <c r="D136" s="5">
+        <v>3</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I136" s="13"/>
+      <c r="K136" s="13"/>
+      <c r="L136" s="13"/>
+      <c r="M136" s="13"/>
+    </row>
+    <row r="137" ht="16.5" spans="1:13">
+      <c r="A137" s="4">
+        <f t="shared" si="4"/>
+        <v>10240021</v>
+      </c>
+      <c r="B137" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C137" s="5">
+        <v>21</v>
+      </c>
+      <c r="D137" s="5">
+        <v>3</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I137" s="13"/>
+      <c r="K137" s="13"/>
+      <c r="L137" s="13"/>
+      <c r="M137" s="13"/>
+    </row>
+    <row r="138" ht="16.5" spans="1:13">
+      <c r="A138" s="4">
+        <f t="shared" si="4"/>
+        <v>10240022</v>
+      </c>
+      <c r="B138" s="4">
+        <v>102400</v>
+      </c>
+      <c r="C138" s="5">
+        <v>22</v>
+      </c>
+      <c r="D138" s="5">
+        <v>3</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I138" s="13"/>
+      <c r="K138" s="13"/>
+      <c r="L138" s="13"/>
+      <c r="M138" s="13"/>
+    </row>
+    <row r="139" ht="16.5" spans="1:13">
+      <c r="A139" s="6">
+        <f t="shared" si="4"/>
+        <v>10240028</v>
+      </c>
+      <c r="B139" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C139" s="7">
+        <v>28</v>
+      </c>
+      <c r="D139" s="7">
+        <v>2</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F139" s="7"/>
+      <c r="G139" s="7"/>
+      <c r="H139" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I139" s="13"/>
+      <c r="K139" s="13"/>
+      <c r="L139" s="13"/>
+      <c r="M139" s="13"/>
+    </row>
+    <row r="140" ht="16.5" spans="1:13">
+      <c r="A140" s="6">
+        <f t="shared" si="4"/>
+        <v>10240030</v>
+      </c>
+      <c r="B140" s="6">
+        <v>102400</v>
+      </c>
+      <c r="C140" s="7">
+        <v>30</v>
+      </c>
+      <c r="D140" s="7">
+        <v>2</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F140" s="7"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I140" s="13"/>
+      <c r="K140" s="13"/>
+      <c r="L140" s="13"/>
+      <c r="M140" s="13"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:G2">

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BaseElement!$E$141:$E$158</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -112,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="279">
   <si>
     <t>图标</t>
   </si>
@@ -405,109 +408,109 @@
     <t>空元素</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_16.png</t>
+    <t>sdhl_zjm_sd_16.png</t>
   </si>
   <si>
     <t>2条</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_12.png</t>
+    <t>sdhl_zjm_sd_12.png</t>
   </si>
   <si>
     <t>2筒</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_14.png</t>
+    <t>sdhl_zjm_sd_14.png</t>
   </si>
   <si>
     <t>5条</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_10.png</t>
+    <t>sdhl_zjm_sd_10.png</t>
   </si>
   <si>
     <t>5筒</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_8.png</t>
+    <t>sdhl_zjm_sd_8.png</t>
   </si>
   <si>
     <t>八万</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_6.png</t>
+    <t>sdhl_zjm_sd_6.png</t>
   </si>
   <si>
     <t>白板</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_2.png</t>
+    <t>sdhl_zjm_sd_2.png</t>
   </si>
   <si>
     <t>红中</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_4.png</t>
+    <t>sdhl_zjm_sd_4.png</t>
   </si>
   <si>
     <t>发财</t>
   </si>
   <si>
-    <t>mjhl_zjm_wild.png</t>
+    <t>sdhl_zjm_wild.png</t>
   </si>
   <si>
     <t>Wild</t>
   </si>
   <si>
-    <t>mjhl_zjm_hu.png</t>
+    <t>sdhl_zjm_hu.png</t>
   </si>
   <si>
     <t>Scatter胡</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_15.png</t>
+    <t>sdhl_zjm_sd_15.png</t>
   </si>
   <si>
     <t>黄金_2条|消除后变为Wild百搭</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_11.png</t>
+    <t>sdhl_zjm_sd_11.png</t>
   </si>
   <si>
     <t>黄金_2筒|消除后变为Wild百搭</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_13.png</t>
+    <t>sdhl_zjm_sd_13.png</t>
   </si>
   <si>
     <t>黄金_5条|消除后变为Wild百搭</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_9.png</t>
+    <t>sdhl_zjm_sd_9.png</t>
   </si>
   <si>
     <t>黄金_5筒|消除后变为Wild百搭</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_7.png</t>
+    <t>sdhl_zjm_sd_7.png</t>
   </si>
   <si>
     <t>黄金_八万|消除后变为Wild百搭</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_5.png</t>
+    <t>sdhl_zjm_sd_5.png</t>
   </si>
   <si>
     <t>黄金_白板|消除后变为Wild百搭</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_1.png</t>
+    <t>sdhl_zjm_sd_1.png</t>
   </si>
   <si>
     <t>黄金_红中|消除后变为Wild百搭</t>
   </si>
   <si>
-    <t>mjhl_zjm_mj_3.png</t>
+    <t>sdhl_zjm_sd_3.png</t>
   </si>
   <si>
     <t>黄金_发财|消除后变为Wild百搭</t>
@@ -673,6 +676,282 @@
   </si>
   <si>
     <t>夺宝</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_16.png</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_12.png</t>
+  </si>
+  <si>
+    <t>鞋子</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_14.png</t>
+  </si>
+  <si>
+    <t>杯子</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_10.png</t>
+  </si>
+  <si>
+    <t>饮品</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_8.png</t>
+  </si>
+  <si>
+    <t>蛋糕1</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_6.png</t>
+  </si>
+  <si>
+    <t>蛋糕2</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_2.png</t>
+  </si>
+  <si>
+    <t>蛋糕3</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_4.png</t>
+  </si>
+  <si>
+    <t>蛋糕4</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_wild.png</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_hu.png</t>
+  </si>
+  <si>
+    <t>Scatter</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_15.png</t>
+  </si>
+  <si>
+    <t>黄金_铃铛|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_11.png</t>
+  </si>
+  <si>
+    <t>黄金_鞋子|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_13.png</t>
+  </si>
+  <si>
+    <t>黄金_杯子|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_9.png</t>
+  </si>
+  <si>
+    <t>黄金_饮品|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_7.png</t>
+  </si>
+  <si>
+    <t>黄金_蛋糕1|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_5.png</t>
+  </si>
+  <si>
+    <t>黄金_蛋糕2|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_1.png</t>
+  </si>
+  <si>
+    <t>黄金_蛋糕3|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_3.png</t>
+  </si>
+  <si>
+    <t>黄金_蛋糕4|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_21.png</t>
+  </si>
+  <si>
+    <t>MINI</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_22.png</t>
+  </si>
+  <si>
+    <t>MINOR</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_23.png</t>
+  </si>
+  <si>
+    <t>MAJOR</t>
+  </si>
+  <si>
+    <t>sdkhy_zjm_sd_24.png</t>
+  </si>
+  <si>
+    <t>GRAND</t>
+  </si>
+  <si>
+    <t>LS_icon_1.png</t>
+  </si>
+  <si>
+    <t>LS_icon_2.png</t>
+  </si>
+  <si>
+    <t>LS_icon_3.png</t>
+  </si>
+  <si>
+    <t>LS_icon_4.png</t>
+  </si>
+  <si>
+    <t>LS_icon_5.png</t>
+  </si>
+  <si>
+    <t>LS_icon_6.png</t>
+  </si>
+  <si>
+    <t>星云</t>
+  </si>
+  <si>
+    <t>LS_icon_7.png</t>
+  </si>
+  <si>
+    <t>海拉</t>
+  </si>
+  <si>
+    <t>LS_icon_8.png</t>
+  </si>
+  <si>
+    <t>海姆达尔</t>
+  </si>
+  <si>
+    <t>LS_icon_9.png</t>
+  </si>
+  <si>
+    <t>洛基</t>
+  </si>
+  <si>
+    <t>LS_icon_10.png</t>
+  </si>
+  <si>
+    <t>奥丁</t>
+  </si>
+  <si>
+    <t>LS_icon_11.png</t>
+  </si>
+  <si>
+    <t>wild</t>
+  </si>
+  <si>
+    <t>LS_icon_12.png</t>
+  </si>
+  <si>
+    <t>冻结wild</t>
+  </si>
+  <si>
+    <t>LS_icon_13.png</t>
+  </si>
+  <si>
+    <t>翻倍wild</t>
+  </si>
+  <si>
+    <t>LS_icon_14.png</t>
+  </si>
+  <si>
+    <t>LS_icon_15.png</t>
+  </si>
+  <si>
+    <t>LS_icon_16.png</t>
+  </si>
+  <si>
+    <t>jkcz_icon_1.png</t>
+  </si>
+  <si>
+    <t>双枪</t>
+  </si>
+  <si>
+    <t>jkcz_icon_2.png</t>
+  </si>
+  <si>
+    <t>骷髅头</t>
+  </si>
+  <si>
+    <t>jkcz_icon_3.png</t>
+  </si>
+  <si>
+    <t>硬币</t>
+  </si>
+  <si>
+    <t>jkcz_icon_4.png</t>
+  </si>
+  <si>
+    <t>宝箱</t>
+  </si>
+  <si>
+    <t>jkcz_icon_5.png</t>
+  </si>
+  <si>
+    <t>船</t>
+  </si>
+  <si>
+    <t>jkcz_icon_6.png</t>
+  </si>
+  <si>
+    <t>卷毛</t>
+  </si>
+  <si>
+    <t>jkcz_icon_7.png</t>
+  </si>
+  <si>
+    <t>金毛</t>
+  </si>
+  <si>
+    <t>jkcz_icon_8.png</t>
+  </si>
+  <si>
+    <t>章鱼</t>
+  </si>
+  <si>
+    <t>jkcz_icon_9.png</t>
+  </si>
+  <si>
+    <t>老巫婆</t>
+  </si>
+  <si>
+    <t>jkcz_icon_10.png</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>jkcz_icon_11.png</t>
+  </si>
+  <si>
+    <t>jkcz_icon_12.png</t>
+  </si>
+  <si>
+    <t>jkcz_icon_13.png</t>
+  </si>
+  <si>
+    <t>jkcz_icon_14.png</t>
+  </si>
+  <si>
+    <t>jkcz_icon_15.png</t>
+  </si>
+  <si>
+    <t>jkcz_icon_16.png</t>
   </si>
 </sst>
 </file>
@@ -685,7 +964,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,6 +987,18 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -880,7 +1171,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -914,6 +1205,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1104,7 +1413,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1124,6 +1433,36 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1245,137 +1584,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1394,6 +1733,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -1415,9 +1757,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -1429,6 +1768,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1750,7 +2125,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M140"/>
+  <dimension ref="A1:M196"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -1761,7 +2136,7 @@
     <col min="10" max="11" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="16.5" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1787,7 +2162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:8">
+    <row r="2" ht="16.5" spans="1:13">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +2184,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" ht="16.5" spans="1:8">
+    <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -1831,7 +2206,7 @@
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" ht="16.5" spans="1:8">
+    <row r="4" ht="16.5" spans="1:13">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
@@ -1863,10 +2238,10 @@
       <c r="H5" s="5">
         <v>9</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
+      <c r="I5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" ht="16.5" spans="1:13">
       <c r="A6" s="4">
@@ -1890,10 +2265,10 @@
       <c r="H6" s="5">
         <v>10</v>
       </c>
-      <c r="I6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
+      <c r="I6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
     </row>
     <row r="7" ht="16.5" spans="1:13">
       <c r="A7" s="4">
@@ -1917,10 +2292,10 @@
       <c r="H7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
+      <c r="I7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
     </row>
     <row r="8" ht="16.5" spans="1:13">
       <c r="A8" s="4">
@@ -1944,10 +2319,10 @@
       <c r="H8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="I8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9" ht="16.5" spans="1:13">
       <c r="A9" s="4">
@@ -1971,10 +2346,10 @@
       <c r="H9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
+      <c r="I9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" ht="16.5" spans="1:13">
       <c r="A10" s="4">
@@ -1998,10 +2373,10 @@
       <c r="H10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="I10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
     </row>
     <row r="11" ht="16.5" spans="1:13">
       <c r="A11" s="4">
@@ -2025,10 +2400,10 @@
       <c r="H11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="I11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
     </row>
     <row r="12" ht="16.5" spans="1:13">
       <c r="A12" s="4">
@@ -2052,10 +2427,10 @@
       <c r="H12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="I12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
     </row>
     <row r="13" ht="16.5" spans="1:13">
       <c r="A13" s="4">
@@ -2079,10 +2454,10 @@
       <c r="H13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="I13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
     </row>
     <row r="14" ht="16.5" spans="1:13">
       <c r="A14" s="4">
@@ -2106,10 +2481,10 @@
       <c r="H14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+      <c r="I14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
     </row>
     <row r="15" ht="16.5" spans="1:13">
       <c r="A15" s="4">
@@ -2133,10 +2508,10 @@
       <c r="H15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+      <c r="I15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
     </row>
     <row r="16" ht="16.5" spans="1:13">
       <c r="A16" s="4">
@@ -2160,10 +2535,10 @@
       <c r="H16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
+      <c r="I16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
     </row>
     <row r="17" ht="16.5" spans="1:13">
       <c r="A17" s="4">
@@ -2187,10 +2562,10 @@
       <c r="H17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="I17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
     </row>
     <row r="18" ht="16.5" spans="1:13">
       <c r="A18" s="4">
@@ -2214,10 +2589,10 @@
       <c r="H18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="I18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
     </row>
     <row r="19" ht="16.5" spans="1:13">
       <c r="A19" s="4">
@@ -2241,10 +2616,10 @@
       <c r="H19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
+      <c r="I19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
     </row>
     <row r="20" ht="16.5" spans="1:13">
       <c r="A20" s="4">
@@ -2268,10 +2643,10 @@
       <c r="H20" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
+      <c r="I20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
     </row>
     <row r="21" ht="16.5" spans="1:13">
       <c r="A21" s="4">
@@ -2295,10 +2670,10 @@
       <c r="H21" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
+      <c r="I21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
     </row>
     <row r="22" ht="16.5" spans="1:13">
       <c r="A22" s="4">
@@ -2322,10 +2697,10 @@
       <c r="H22" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
+      <c r="I22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
     </row>
     <row r="23" ht="16.5" spans="1:13">
       <c r="A23" s="4">
@@ -2349,10 +2724,10 @@
       <c r="H23" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
+      <c r="I23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
     </row>
     <row r="24" ht="16.5" spans="1:13">
       <c r="A24" s="4">
@@ -2376,10 +2751,10 @@
       <c r="H24" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
+      <c r="I24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
     </row>
     <row r="25" ht="16.5" spans="1:13">
       <c r="A25" s="4">
@@ -2403,10 +2778,10 @@
       <c r="H25" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
+      <c r="I25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
     </row>
     <row r="26" ht="16.5" spans="1:13">
       <c r="A26" s="4">
@@ -2430,1156 +2805,1156 @@
       <c r="H26" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
+      <c r="I26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
     </row>
     <row r="27" ht="16.5" spans="1:13">
-      <c r="A27" s="6">
+      <c r="A27" s="7">
         <f t="shared" si="0"/>
         <v>10010028</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="7">
         <v>100100</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <v>28</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <v>2</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7" t="s">
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
+      <c r="I27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
     </row>
     <row r="28" ht="16.5" spans="1:13">
-      <c r="A28" s="6">
+      <c r="A28" s="7">
         <f t="shared" si="0"/>
         <v>10010030</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="7">
         <v>100100</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="8">
         <v>30</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="8">
         <v>2</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7" t="s">
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
+      <c r="I28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
     </row>
     <row r="29" ht="16.5" spans="1:13">
-      <c r="A29" s="8">
+      <c r="A29" s="9">
         <f t="shared" si="0"/>
         <v>10030001</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="9">
         <v>100300</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="10">
         <v>1</v>
       </c>
-      <c r="D29" s="9">
-        <v>0</v>
-      </c>
-      <c r="E29" s="10" t="s">
+      <c r="D29" s="10">
+        <v>0</v>
+      </c>
+      <c r="E29" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9" t="s">
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
+      <c r="I29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
     </row>
     <row r="30" ht="16.5" spans="1:13">
-      <c r="A30" s="8">
+      <c r="A30" s="9">
         <f t="shared" si="0"/>
         <v>10030002</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="9">
         <v>100300</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="10">
         <v>2</v>
       </c>
-      <c r="D30" s="9">
-        <v>0</v>
-      </c>
-      <c r="E30" s="10" t="s">
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9" t="s">
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="I30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
+      <c r="I30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
     </row>
     <row r="31" ht="16.5" spans="1:13">
-      <c r="A31" s="8">
+      <c r="A31" s="9">
         <f t="shared" si="0"/>
         <v>10030003</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="9">
         <v>100300</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="10">
         <v>3</v>
       </c>
-      <c r="D31" s="9">
-        <v>0</v>
-      </c>
-      <c r="E31" s="10" t="s">
+      <c r="D31" s="10">
+        <v>0</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9" t="s">
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
+      <c r="I31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
     </row>
     <row r="32" ht="16.5" spans="1:13">
-      <c r="A32" s="8">
+      <c r="A32" s="9">
         <f t="shared" si="0"/>
         <v>10030004</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="9">
         <v>100300</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="10">
         <v>4</v>
       </c>
-      <c r="D32" s="9">
-        <v>0</v>
-      </c>
-      <c r="E32" s="10" t="s">
+      <c r="D32" s="10">
+        <v>0</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9" t="s">
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
+      <c r="I32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
     </row>
     <row r="33" ht="16.5" spans="1:13">
-      <c r="A33" s="8">
+      <c r="A33" s="9">
         <f t="shared" si="0"/>
         <v>10030005</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="9">
         <v>100300</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="10">
         <v>5</v>
       </c>
-      <c r="D33" s="9">
-        <v>0</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="D33" s="10">
+        <v>0</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="9" t="s">
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
+      <c r="I33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
     </row>
     <row r="34" ht="16.5" spans="1:13">
-      <c r="A34" s="8">
+      <c r="A34" s="9">
         <f t="shared" si="0"/>
         <v>10030006</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="9">
         <v>100300</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="10">
         <v>6</v>
       </c>
-      <c r="D34" s="9">
-        <v>0</v>
-      </c>
-      <c r="E34" s="10" t="s">
+      <c r="D34" s="10">
+        <v>0</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="9" t="s">
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="I34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
+      <c r="I34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
     </row>
     <row r="35" ht="16.5" spans="1:13">
-      <c r="A35" s="8">
+      <c r="A35" s="9">
         <f t="shared" si="0"/>
         <v>10030007</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="9">
         <v>100300</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="10">
         <v>7</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="10">
         <v>1</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8">
+      <c r="F35" s="9"/>
+      <c r="G35" s="9">
         <v>100300107</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
+      <c r="I35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
     </row>
     <row r="36" ht="16.5" spans="1:13">
-      <c r="A36" s="8">
+      <c r="A36" s="9">
         <f t="shared" si="0"/>
         <v>10030008</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="9">
         <v>100300</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="10">
         <v>8</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="10">
         <v>1</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8">
+      <c r="F36" s="9"/>
+      <c r="G36" s="9">
         <v>100300108</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
+      <c r="I36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
     </row>
     <row r="37" ht="16.5" spans="1:13">
-      <c r="A37" s="8">
+      <c r="A37" s="9">
         <f t="shared" si="0"/>
         <v>10030009</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="9">
         <v>100300</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="10">
         <v>9</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="10">
         <v>1</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8">
+      <c r="F37" s="9"/>
+      <c r="G37" s="9">
         <v>100300109</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
+      <c r="I37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
     </row>
     <row r="38" ht="16.5" spans="1:13">
-      <c r="A38" s="8">
+      <c r="A38" s="9">
         <f t="shared" si="0"/>
         <v>10030010</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="9">
         <v>100300</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="10">
         <v>10</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="10">
         <v>1</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8">
+      <c r="F38" s="9"/>
+      <c r="G38" s="9">
         <v>100300110</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-    </row>
-    <row r="39" ht="16.5" spans="1:8">
-      <c r="A39" s="8">
+      <c r="I38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+    </row>
+    <row r="39" ht="16.5" spans="1:13">
+      <c r="A39" s="9">
         <f t="shared" si="0"/>
         <v>10030021</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="9">
         <v>100300</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="10">
         <v>21</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="10">
         <v>1</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8">
+      <c r="F39" s="9"/>
+      <c r="G39" s="9">
         <v>100300021</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A40" s="8">
+    <row r="40" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A40" s="9">
         <f t="shared" si="0"/>
         <v>10030022</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="9">
         <v>100300</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="10">
         <v>22</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="10">
         <v>1</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8">
+      <c r="F40" s="9"/>
+      <c r="G40" s="9">
         <v>100300022</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I40" s="13"/>
-    </row>
-    <row r="41" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A41" s="8">
+      <c r="I40" s="6"/>
+    </row>
+    <row r="41" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A41" s="9">
         <f t="shared" si="0"/>
         <v>10030023</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="9">
         <v>100300</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="10">
         <v>23</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="10">
         <v>1</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8">
+      <c r="F41" s="9"/>
+      <c r="G41" s="9">
         <v>100300023</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I41" s="13"/>
-    </row>
-    <row r="42" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A42" s="8">
+      <c r="I41" s="6"/>
+    </row>
+    <row r="42" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A42" s="9">
         <f t="shared" si="0"/>
         <v>10030024</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="9">
         <v>100300</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="10">
         <v>24</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="10">
         <v>1</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8">
+      <c r="F42" s="9"/>
+      <c r="G42" s="9">
         <v>100300024</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I42" s="13"/>
-    </row>
-    <row r="43" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A43" s="8">
+      <c r="I42" s="6"/>
+    </row>
+    <row r="43" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A43" s="9">
         <f t="shared" si="0"/>
         <v>10030025</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="9">
         <v>100300</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="10">
         <v>25</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="10">
         <v>1</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8">
+      <c r="F43" s="9"/>
+      <c r="G43" s="9">
         <v>100300025</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H43" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="I43" s="13"/>
-    </row>
-    <row r="44" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A44" s="8">
+      <c r="I43" s="6"/>
+    </row>
+    <row r="44" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A44" s="9">
         <f t="shared" si="0"/>
         <v>10030026</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="9">
         <v>100300</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="10">
         <v>26</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="10">
         <v>1</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8">
+      <c r="F44" s="9"/>
+      <c r="G44" s="9">
         <v>100300026</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I44" s="13"/>
-    </row>
-    <row r="45" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A45" s="8">
+      <c r="I44" s="6"/>
+    </row>
+    <row r="45" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A45" s="9">
         <f t="shared" si="0"/>
         <v>10030027</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="9">
         <v>100300</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="10">
         <v>27</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="10">
         <v>1</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8">
+      <c r="F45" s="9"/>
+      <c r="G45" s="9">
         <v>100300027</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="I45" s="13"/>
-    </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A46" s="8">
+      <c r="I45" s="6"/>
+    </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A46" s="9">
         <f t="shared" si="0"/>
         <v>10030028</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="9">
         <v>100300</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="10">
         <v>28</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="10">
         <v>1</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8">
+      <c r="F46" s="9"/>
+      <c r="G46" s="9">
         <v>100300028</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="I46" s="13"/>
-    </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A47" s="8">
+      <c r="I46" s="6"/>
+    </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A47" s="9">
         <f t="shared" ref="A47:A59" si="1">B47*100+C47</f>
         <v>10030029</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="9">
         <v>100300</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="10">
         <v>29</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="10">
         <v>1</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8">
+      <c r="F47" s="9"/>
+      <c r="G47" s="9">
         <v>100300029</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I47" s="13"/>
-    </row>
-    <row r="48" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A48" s="8">
+      <c r="I47" s="6"/>
+    </row>
+    <row r="48" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A48" s="9">
         <f t="shared" si="1"/>
         <v>10030030</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="9">
         <v>100300</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="10">
         <v>30</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="10">
         <v>1</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8">
+      <c r="F48" s="9"/>
+      <c r="G48" s="9">
         <v>100300030</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="H48" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="I48" s="13"/>
-    </row>
-    <row r="49" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A49" s="8">
+      <c r="I48" s="6"/>
+    </row>
+    <row r="49" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A49" s="9">
         <f t="shared" si="1"/>
         <v>10030031</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="9">
         <v>100300</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="10">
         <v>31</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="10">
         <v>1</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8">
+      <c r="F49" s="9"/>
+      <c r="G49" s="9">
         <v>100300031</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="H49" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="I49" s="13"/>
-    </row>
-    <row r="50" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A50" s="8">
+      <c r="I49" s="6"/>
+    </row>
+    <row r="50" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A50" s="9">
         <f t="shared" si="1"/>
         <v>10030032</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="9">
         <v>100300</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="10">
         <v>32</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="10">
         <v>1</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8">
+      <c r="F50" s="9"/>
+      <c r="G50" s="9">
         <v>100300032</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I50" s="13"/>
-    </row>
-    <row r="51" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A51" s="8">
+      <c r="I50" s="6"/>
+    </row>
+    <row r="51" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A51" s="9">
         <f t="shared" si="1"/>
         <v>10030033</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="9">
         <v>100300</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="10">
         <v>33</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="10">
         <v>1</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8">
+      <c r="F51" s="9"/>
+      <c r="G51" s="9">
         <v>100300033</v>
       </c>
-      <c r="H51" s="9" t="s">
+      <c r="H51" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="I51" s="13"/>
-    </row>
-    <row r="52" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A52" s="8">
+      <c r="I51" s="6"/>
+    </row>
+    <row r="52" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A52" s="9">
         <f t="shared" si="1"/>
         <v>10030034</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="9">
         <v>100300</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="10">
         <v>34</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="10">
         <v>1</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8">
+      <c r="F52" s="9"/>
+      <c r="G52" s="9">
         <v>100300034</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="H52" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="I52" s="13"/>
-    </row>
-    <row r="53" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A53" s="8">
+      <c r="I52" s="6"/>
+    </row>
+    <row r="53" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A53" s="9">
         <f t="shared" si="1"/>
         <v>10030035</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="9">
         <v>100300</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="10">
         <v>35</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="10">
         <v>1</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8">
+      <c r="F53" s="9"/>
+      <c r="G53" s="9">
         <v>100300035</v>
       </c>
-      <c r="H53" s="9" t="s">
+      <c r="H53" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="I53" s="13"/>
-    </row>
-    <row r="54" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A54" s="8">
+      <c r="I53" s="6"/>
+    </row>
+    <row r="54" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A54" s="9">
         <f t="shared" si="1"/>
         <v>10030036</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="9">
         <v>100300</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="10">
         <v>36</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="10">
         <v>1</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8">
+      <c r="F54" s="9"/>
+      <c r="G54" s="9">
         <v>100300036</v>
       </c>
-      <c r="H54" s="9" t="s">
+      <c r="H54" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I54" s="13"/>
-    </row>
-    <row r="55" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A55" s="8">
+      <c r="I54" s="6"/>
+    </row>
+    <row r="55" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A55" s="9">
         <f t="shared" si="1"/>
         <v>10030037</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="9">
         <v>100300</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="10">
         <v>37</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="10">
         <v>1</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8">
+      <c r="F55" s="9"/>
+      <c r="G55" s="9">
         <v>100300037</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="H55" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I55" s="13"/>
-    </row>
-    <row r="56" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A56" s="8">
+      <c r="I55" s="6"/>
+    </row>
+    <row r="56" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A56" s="9">
         <f t="shared" si="1"/>
         <v>10030038</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="9">
         <v>100300</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="10">
         <v>38</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="10">
         <v>1</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8">
+      <c r="F56" s="9"/>
+      <c r="G56" s="9">
         <v>100300038</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="H56" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="I56" s="13"/>
-    </row>
-    <row r="57" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A57" s="8">
+      <c r="I56" s="6"/>
+    </row>
+    <row r="57" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A57" s="9">
         <f t="shared" si="1"/>
         <v>10030039</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="9">
         <v>100300</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C57" s="10">
         <v>39</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="10">
         <v>1</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8">
+      <c r="F57" s="9"/>
+      <c r="G57" s="9">
         <v>100300039</v>
       </c>
-      <c r="H57" s="9" t="s">
+      <c r="H57" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="I57" s="13"/>
-    </row>
-    <row r="58" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A58" s="8">
+      <c r="I57" s="6"/>
+    </row>
+    <row r="58" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A58" s="9">
         <f t="shared" si="1"/>
         <v>10030040</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="9">
         <v>100300</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="10">
         <v>40</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="10">
         <v>1</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8">
+      <c r="F58" s="9"/>
+      <c r="G58" s="9">
         <v>100300040</v>
       </c>
-      <c r="H58" s="9" t="s">
+      <c r="H58" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="I58" s="13"/>
+      <c r="I58" s="6"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A59" s="8">
+      <c r="A59" s="9">
         <f t="shared" si="1"/>
         <v>10030099</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="9">
         <v>100300</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="10">
         <v>99</v>
       </c>
-      <c r="D59" s="9">
-        <v>0</v>
-      </c>
-      <c r="E59" s="10"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="9" t="s">
+      <c r="D59" s="10">
+        <v>0</v>
+      </c>
+      <c r="E59" s="11"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="I59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
+      <c r="I59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
     </row>
     <row r="60" ht="16.5" spans="1:13">
-      <c r="A60" s="11">
+      <c r="A60" s="12">
         <f t="shared" ref="A60:A89" si="2">B60*100+C60</f>
         <v>10070001</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="12">
         <v>100700</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="13">
         <v>1</v>
       </c>
-      <c r="D60" s="12">
-        <v>0</v>
-      </c>
-      <c r="E60" s="12" t="s">
+      <c r="D60" s="13">
+        <v>0</v>
+      </c>
+      <c r="E60" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12" t="s">
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="I60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
+      <c r="I60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
     </row>
     <row r="61" ht="16.5" spans="1:13">
-      <c r="A61" s="11">
+      <c r="A61" s="12">
         <f t="shared" si="2"/>
         <v>10070002</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="12">
         <v>100700</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="13">
         <v>2</v>
       </c>
-      <c r="D61" s="12">
-        <v>0</v>
-      </c>
-      <c r="E61" s="12" t="s">
+      <c r="D61" s="13">
+        <v>0</v>
+      </c>
+      <c r="E61" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12" t="s">
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="I61" s="13"/>
-      <c r="K61" s="13"/>
-      <c r="L61" s="13"/>
-      <c r="M61" s="13"/>
+      <c r="I61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
     </row>
     <row r="62" ht="16.5" spans="1:13">
-      <c r="A62" s="11">
+      <c r="A62" s="12">
         <f t="shared" si="2"/>
         <v>10070003</v>
       </c>
-      <c r="B62" s="11">
+      <c r="B62" s="12">
         <v>100700</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="13">
         <v>3</v>
       </c>
-      <c r="D62" s="12">
-        <v>0</v>
-      </c>
-      <c r="E62" s="12" t="s">
+      <c r="D62" s="13">
+        <v>0</v>
+      </c>
+      <c r="E62" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12" t="s">
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="I62" s="13"/>
-      <c r="K62" s="13"/>
-      <c r="L62" s="13"/>
-      <c r="M62" s="13"/>
+      <c r="I62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
     </row>
     <row r="63" ht="16.5" spans="1:13">
-      <c r="A63" s="11">
+      <c r="A63" s="12">
         <f t="shared" si="2"/>
         <v>10070004</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="12">
         <v>100700</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="13">
         <v>4</v>
       </c>
-      <c r="D63" s="12">
-        <v>0</v>
-      </c>
-      <c r="E63" s="12" t="s">
+      <c r="D63" s="13">
+        <v>0</v>
+      </c>
+      <c r="E63" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12" t="s">
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I63" s="13"/>
-      <c r="K63" s="13"/>
-      <c r="L63" s="13"/>
-      <c r="M63" s="13"/>
+      <c r="I63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
     </row>
     <row r="64" ht="16.5" spans="1:13">
-      <c r="A64" s="11">
+      <c r="A64" s="12">
         <f t="shared" si="2"/>
         <v>10070005</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="12">
         <v>100700</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="13">
         <v>5</v>
       </c>
-      <c r="D64" s="12">
-        <v>0</v>
-      </c>
-      <c r="E64" s="12" t="s">
+      <c r="D64" s="13">
+        <v>0</v>
+      </c>
+      <c r="E64" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12" t="s">
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="I64" s="13"/>
-      <c r="K64" s="13"/>
-      <c r="L64" s="13"/>
-      <c r="M64" s="13"/>
+      <c r="I64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
     </row>
     <row r="65" ht="16.5" spans="1:13">
-      <c r="A65" s="11">
+      <c r="A65" s="12">
         <f t="shared" si="2"/>
         <v>10070006</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="12">
         <v>100700</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="13">
         <v>6</v>
       </c>
-      <c r="D65" s="12">
-        <v>0</v>
-      </c>
-      <c r="E65" s="12" t="s">
+      <c r="D65" s="13">
+        <v>0</v>
+      </c>
+      <c r="E65" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12" t="s">
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="I65" s="13"/>
-      <c r="K65" s="13"/>
-      <c r="L65" s="13"/>
-      <c r="M65" s="13"/>
+      <c r="I65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
     </row>
     <row r="66" ht="16.5" spans="1:13">
-      <c r="A66" s="11">
+      <c r="A66" s="12">
         <f t="shared" si="2"/>
         <v>10070007</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="12">
         <v>100700</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="13">
         <v>7</v>
       </c>
-      <c r="D66" s="12">
-        <v>0</v>
-      </c>
-      <c r="E66" s="12" t="s">
+      <c r="D66" s="13">
+        <v>0</v>
+      </c>
+      <c r="E66" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12" t="s">
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="I66" s="13"/>
-      <c r="K66" s="13"/>
-      <c r="L66" s="13"/>
-      <c r="M66" s="13"/>
+      <c r="I66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
     </row>
     <row r="67" ht="16.5" spans="1:13">
-      <c r="A67" s="11">
+      <c r="A67" s="12">
         <f t="shared" si="2"/>
         <v>10070008</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="12">
         <v>100700</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="13">
         <v>8</v>
       </c>
-      <c r="D67" s="12">
-        <v>0</v>
-      </c>
-      <c r="E67" s="12" t="s">
+      <c r="D67" s="13">
+        <v>0</v>
+      </c>
+      <c r="E67" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12" t="s">
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="I67" s="13"/>
-      <c r="K67" s="13"/>
-      <c r="L67" s="13"/>
-      <c r="M67" s="13"/>
+      <c r="I67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
     </row>
     <row r="68" ht="16.5" spans="1:13">
-      <c r="A68" s="11">
+      <c r="A68" s="12">
         <f t="shared" si="2"/>
         <v>10070009</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="12">
         <v>100700</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="13">
         <v>9</v>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="13">
         <v>1</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12" t="s">
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="I68" s="13"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
-      <c r="M68" s="13"/>
+      <c r="I68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
     </row>
     <row r="69" ht="16.5" spans="1:13">
-      <c r="A69" s="11">
+      <c r="A69" s="12">
         <f t="shared" si="2"/>
         <v>10070010</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="12">
         <v>100700</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="13">
         <v>10</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="13">
         <v>2</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12" t="s">
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="I69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
+      <c r="I69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
     </row>
     <row r="70" ht="16.5" spans="1:13">
       <c r="A70" s="14">
@@ -3598,17 +3973,17 @@
       <c r="E70" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="13">
         <v>9</v>
       </c>
-      <c r="G70" s="12"/>
+      <c r="G70" s="13"/>
       <c r="H70" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="I70" s="13"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
+      <c r="I70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
     </row>
     <row r="71" ht="16.5" spans="1:13">
       <c r="A71" s="14">
@@ -3627,17 +4002,17 @@
       <c r="E71" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F71" s="12">
+      <c r="F71" s="13">
         <v>9</v>
       </c>
-      <c r="G71" s="12"/>
+      <c r="G71" s="13"/>
       <c r="H71" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="I71" s="13"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
+      <c r="I71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
     </row>
     <row r="72" ht="16.5" spans="1:13">
       <c r="A72" s="14">
@@ -3656,17 +4031,17 @@
       <c r="E72" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F72" s="12">
+      <c r="F72" s="13">
         <v>9</v>
       </c>
-      <c r="G72" s="12"/>
+      <c r="G72" s="13"/>
       <c r="H72" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="I72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
+      <c r="I72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
     </row>
     <row r="73" ht="16.5" spans="1:13">
       <c r="A73" s="14">
@@ -3685,17 +4060,17 @@
       <c r="E73" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F73" s="12">
+      <c r="F73" s="13">
         <v>9</v>
       </c>
-      <c r="G73" s="12"/>
+      <c r="G73" s="13"/>
       <c r="H73" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="I73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
+      <c r="I73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
     </row>
     <row r="74" ht="16.5" spans="1:13">
       <c r="A74" s="14">
@@ -3714,17 +4089,17 @@
       <c r="E74" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="F74" s="12">
+      <c r="F74" s="13">
         <v>9</v>
       </c>
-      <c r="G74" s="12"/>
+      <c r="G74" s="13"/>
       <c r="H74" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="I74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
+      <c r="I74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
     </row>
     <row r="75" ht="16.5" spans="1:13">
       <c r="A75" s="14">
@@ -3743,17 +4118,17 @@
       <c r="E75" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="F75" s="12">
+      <c r="F75" s="13">
         <v>9</v>
       </c>
-      <c r="G75" s="12"/>
+      <c r="G75" s="13"/>
       <c r="H75" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="I75" s="13"/>
-      <c r="K75" s="13"/>
-      <c r="L75" s="13"/>
-      <c r="M75" s="13"/>
+      <c r="I75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
     </row>
     <row r="76" ht="16.5" spans="1:13">
       <c r="A76" s="14">
@@ -3772,17 +4147,17 @@
       <c r="E76" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F76" s="12">
+      <c r="F76" s="13">
         <v>9</v>
       </c>
-      <c r="G76" s="12"/>
+      <c r="G76" s="13"/>
       <c r="H76" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="I76" s="13"/>
-      <c r="K76" s="13"/>
-      <c r="L76" s="13"/>
-      <c r="M76" s="13"/>
+      <c r="I76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
     </row>
     <row r="77" ht="16.5" spans="1:13">
       <c r="A77" s="14">
@@ -3801,719 +4176,719 @@
       <c r="E77" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="F77" s="12">
+      <c r="F77" s="13">
         <v>9</v>
       </c>
-      <c r="G77" s="12"/>
+      <c r="G77" s="13"/>
       <c r="H77" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="I77" s="13"/>
-      <c r="K77" s="13"/>
-      <c r="L77" s="13"/>
-      <c r="M77" s="13"/>
+      <c r="I77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
     </row>
     <row r="78" ht="16.5" spans="1:13">
-      <c r="A78" s="8">
+      <c r="A78" s="9">
         <f t="shared" si="2"/>
         <v>10120001</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="9">
         <v>101200</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="10">
         <v>1</v>
       </c>
-      <c r="D78" s="9">
-        <v>0</v>
-      </c>
-      <c r="E78" s="10" t="s">
+      <c r="D78" s="10">
+        <v>0</v>
+      </c>
+      <c r="E78" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="9" t="s">
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="I78" s="13"/>
-      <c r="K78" s="13"/>
-      <c r="L78" s="13"/>
-      <c r="M78" s="13"/>
+      <c r="I78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
     </row>
     <row r="79" ht="16.5" spans="1:13">
-      <c r="A79" s="8">
+      <c r="A79" s="9">
         <f t="shared" si="2"/>
         <v>10120002</v>
       </c>
-      <c r="B79" s="8">
+      <c r="B79" s="9">
         <v>101200</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C79" s="10">
         <v>2</v>
       </c>
-      <c r="D79" s="9">
-        <v>0</v>
-      </c>
-      <c r="E79" s="10" t="s">
+      <c r="D79" s="10">
+        <v>0</v>
+      </c>
+      <c r="E79" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="9" t="s">
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="I79" s="13"/>
-      <c r="K79" s="13"/>
-      <c r="L79" s="13"/>
-      <c r="M79" s="13"/>
+      <c r="I79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
     </row>
     <row r="80" ht="16.5" spans="1:13">
-      <c r="A80" s="8">
+      <c r="A80" s="9">
         <f t="shared" si="2"/>
         <v>10120003</v>
       </c>
-      <c r="B80" s="8">
+      <c r="B80" s="9">
         <v>101200</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="10">
         <v>3</v>
       </c>
-      <c r="D80" s="9">
-        <v>0</v>
-      </c>
-      <c r="E80" s="10" t="s">
+      <c r="D80" s="10">
+        <v>0</v>
+      </c>
+      <c r="E80" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="9" t="s">
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I80" s="13"/>
-      <c r="K80" s="13"/>
-      <c r="L80" s="13"/>
-      <c r="M80" s="13"/>
+      <c r="I80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
     </row>
     <row r="81" ht="16.5" spans="1:13">
-      <c r="A81" s="8">
+      <c r="A81" s="9">
         <f t="shared" si="2"/>
         <v>10120004</v>
       </c>
-      <c r="B81" s="8">
+      <c r="B81" s="9">
         <v>101200</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C81" s="10">
         <v>4</v>
       </c>
-      <c r="D81" s="9">
-        <v>0</v>
-      </c>
-      <c r="E81" s="10" t="s">
+      <c r="D81" s="10">
+        <v>0</v>
+      </c>
+      <c r="E81" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="9" t="s">
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="I81" s="13"/>
-      <c r="K81" s="13"/>
-      <c r="L81" s="13"/>
-      <c r="M81" s="13"/>
+      <c r="I81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
     </row>
     <row r="82" ht="16.5" spans="1:13">
-      <c r="A82" s="8">
+      <c r="A82" s="9">
         <f t="shared" si="2"/>
         <v>10120005</v>
       </c>
-      <c r="B82" s="8">
+      <c r="B82" s="9">
         <v>101200</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="10">
         <v>5</v>
       </c>
-      <c r="D82" s="9">
-        <v>0</v>
-      </c>
-      <c r="E82" s="10" t="s">
+      <c r="D82" s="10">
+        <v>0</v>
+      </c>
+      <c r="E82" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="9" t="s">
+      <c r="F82" s="9"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="I82" s="13"/>
-      <c r="K82" s="13"/>
-      <c r="L82" s="13"/>
-      <c r="M82" s="13"/>
+      <c r="I82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
     </row>
     <row r="83" ht="16.5" spans="1:13">
-      <c r="A83" s="8">
+      <c r="A83" s="9">
         <f t="shared" si="2"/>
         <v>10120006</v>
       </c>
-      <c r="B83" s="8">
+      <c r="B83" s="9">
         <v>101200</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C83" s="10">
         <v>6</v>
       </c>
-      <c r="D83" s="9">
-        <v>0</v>
-      </c>
-      <c r="E83" s="10" t="s">
+      <c r="D83" s="10">
+        <v>0</v>
+      </c>
+      <c r="E83" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="9" t="s">
+      <c r="F83" s="9"/>
+      <c r="G83" s="9"/>
+      <c r="H83" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="I83" s="13"/>
-      <c r="K83" s="13"/>
-      <c r="L83" s="13"/>
-      <c r="M83" s="13"/>
+      <c r="I83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
     </row>
     <row r="84" ht="16.5" spans="1:13">
-      <c r="A84" s="8">
+      <c r="A84" s="9">
         <f t="shared" ref="A84:A103" si="3">B84*100+C84</f>
         <v>10120009</v>
       </c>
-      <c r="B84" s="8">
+      <c r="B84" s="9">
         <v>101200</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="10">
         <v>9</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="10">
         <v>2</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="9" t="s">
+      <c r="F84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="I84" s="13"/>
-      <c r="K84" s="13"/>
-      <c r="L84" s="13"/>
-      <c r="M84" s="13"/>
+      <c r="I84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
     </row>
     <row r="85" ht="16.5" spans="1:13">
-      <c r="A85" s="8">
+      <c r="A85" s="9">
         <f t="shared" si="3"/>
         <v>10120010</v>
       </c>
-      <c r="B85" s="8">
+      <c r="B85" s="9">
         <v>101200</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85" s="10">
         <v>10</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="10">
         <v>1</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="9" t="s">
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="I85" s="13"/>
-      <c r="K85" s="13"/>
-      <c r="L85" s="13"/>
-      <c r="M85" s="13"/>
+      <c r="I85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
     </row>
     <row r="86" ht="16.5" spans="1:13">
-      <c r="A86" s="8">
+      <c r="A86" s="9">
         <f t="shared" si="3"/>
         <v>10120011</v>
       </c>
-      <c r="B86" s="8">
+      <c r="B86" s="9">
         <v>101200</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="10">
         <v>11</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="10">
         <v>2</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="9" t="s">
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="I86" s="13"/>
-      <c r="K86" s="13"/>
-      <c r="L86" s="13"/>
-      <c r="M86" s="13"/>
+      <c r="I86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
     </row>
     <row r="87" ht="16.5" spans="1:13">
-      <c r="A87" s="8">
+      <c r="A87" s="9">
         <f t="shared" si="3"/>
         <v>10120012</v>
       </c>
-      <c r="B87" s="8">
+      <c r="B87" s="9">
         <v>101200</v>
       </c>
-      <c r="C87" s="9">
+      <c r="C87" s="10">
         <v>12</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="10">
         <v>2</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="9" t="s">
+      <c r="F87" s="9"/>
+      <c r="G87" s="9"/>
+      <c r="H87" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="I87" s="13"/>
-      <c r="K87" s="13"/>
-      <c r="L87" s="13"/>
-      <c r="M87" s="13"/>
+      <c r="I87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6"/>
     </row>
     <row r="88" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A88" s="8">
+      <c r="A88" s="9">
         <f t="shared" si="3"/>
         <v>10120013</v>
       </c>
-      <c r="B88" s="8">
+      <c r="B88" s="9">
         <v>101200</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="10">
         <v>13</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="10">
         <v>2</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E88" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F88" s="8"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="9" t="s">
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="I88" s="13"/>
-      <c r="K88" s="13"/>
-      <c r="L88" s="13"/>
-      <c r="M88" s="13"/>
+      <c r="I88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="6"/>
     </row>
     <row r="89" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A89" s="8">
+      <c r="A89" s="9">
         <f t="shared" si="3"/>
         <v>10120014</v>
       </c>
-      <c r="B89" s="8">
+      <c r="B89" s="9">
         <v>101200</v>
       </c>
-      <c r="C89" s="9">
+      <c r="C89" s="10">
         <v>14</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="10">
         <v>2</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="9" t="s">
+      <c r="F89" s="9"/>
+      <c r="G89" s="9"/>
+      <c r="H89" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="I89" s="13"/>
-      <c r="K89" s="13"/>
-      <c r="L89" s="13"/>
-      <c r="M89" s="13"/>
+      <c r="I89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="6"/>
     </row>
     <row r="90" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A90" s="8">
+      <c r="A90" s="9">
         <f t="shared" si="3"/>
         <v>10120015</v>
       </c>
-      <c r="B90" s="8">
+      <c r="B90" s="9">
         <v>101200</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="10">
         <v>15</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="10">
         <v>2</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E90" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="9" t="s">
+      <c r="F90" s="9"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="I90" s="13"/>
-      <c r="K90" s="13"/>
-      <c r="L90" s="13"/>
-      <c r="M90" s="13"/>
+      <c r="I90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
     </row>
     <row r="91" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A91" s="8">
+      <c r="A91" s="9">
         <f t="shared" si="3"/>
         <v>10120016</v>
       </c>
-      <c r="B91" s="8">
+      <c r="B91" s="9">
         <v>101200</v>
       </c>
-      <c r="C91" s="9">
+      <c r="C91" s="10">
         <v>16</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="10">
         <v>2</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="9" t="s">
+      <c r="F91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="I91" s="13"/>
-      <c r="K91" s="13"/>
-      <c r="L91" s="13"/>
-      <c r="M91" s="13"/>
+      <c r="I91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
     </row>
     <row r="92" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A92" s="8">
+      <c r="A92" s="9">
         <f t="shared" si="3"/>
         <v>10120021</v>
       </c>
-      <c r="B92" s="8">
+      <c r="B92" s="9">
         <v>101200</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="10">
         <v>21</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="10">
         <v>2</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="9" t="s">
+      <c r="F92" s="9"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="I92" s="13"/>
-      <c r="K92" s="13"/>
-      <c r="L92" s="13"/>
-      <c r="M92" s="13"/>
+      <c r="I92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
     </row>
     <row r="93" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A93" s="8">
+      <c r="A93" s="9">
         <f t="shared" si="3"/>
         <v>10120022</v>
       </c>
-      <c r="B93" s="8">
+      <c r="B93" s="9">
         <v>101200</v>
       </c>
-      <c r="C93" s="9">
+      <c r="C93" s="10">
         <v>22</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="10">
         <v>2</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="9" t="s">
+      <c r="F93" s="9"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I93" s="13"/>
-      <c r="K93" s="13"/>
-      <c r="L93" s="13"/>
-      <c r="M93" s="13"/>
+      <c r="I93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
     </row>
     <row r="94" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A94" s="8">
+      <c r="A94" s="9">
         <f t="shared" si="3"/>
         <v>10120023</v>
       </c>
-      <c r="B94" s="8">
+      <c r="B94" s="9">
         <v>101200</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="10">
         <v>23</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="10">
         <v>2</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="E94" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F94" s="8"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="9" t="s">
+      <c r="F94" s="9"/>
+      <c r="G94" s="9"/>
+      <c r="H94" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="I94" s="13"/>
-      <c r="K94" s="13"/>
-      <c r="L94" s="13"/>
-      <c r="M94" s="13"/>
+      <c r="I94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
     </row>
     <row r="95" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A95" s="8">
+      <c r="A95" s="9">
         <f t="shared" si="3"/>
         <v>10120024</v>
       </c>
-      <c r="B95" s="8">
+      <c r="B95" s="9">
         <v>101200</v>
       </c>
-      <c r="C95" s="9">
+      <c r="C95" s="10">
         <v>24</v>
       </c>
-      <c r="D95" s="9">
+      <c r="D95" s="10">
         <v>2</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E95" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F95" s="8"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="9" t="s">
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="I95" s="13"/>
-      <c r="K95" s="13"/>
-      <c r="L95" s="13"/>
-      <c r="M95" s="13"/>
+      <c r="I95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6"/>
     </row>
     <row r="96" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A96" s="8">
+      <c r="A96" s="9">
         <f t="shared" si="3"/>
         <v>10120025</v>
       </c>
-      <c r="B96" s="8">
+      <c r="B96" s="9">
         <v>101200</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="10">
         <v>25</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="10">
         <v>2</v>
       </c>
-      <c r="E96" s="10" t="s">
+      <c r="E96" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="9" t="s">
+      <c r="F96" s="9"/>
+      <c r="G96" s="9"/>
+      <c r="H96" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="I96" s="13"/>
-      <c r="K96" s="13"/>
-      <c r="L96" s="13"/>
-      <c r="M96" s="13"/>
+      <c r="I96" s="6"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
+      <c r="M96" s="6"/>
     </row>
     <row r="97" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A97" s="8">
+      <c r="A97" s="9">
         <f t="shared" si="3"/>
         <v>10120026</v>
       </c>
-      <c r="B97" s="8">
+      <c r="B97" s="9">
         <v>101200</v>
       </c>
-      <c r="C97" s="9">
+      <c r="C97" s="10">
         <v>26</v>
       </c>
-      <c r="D97" s="9">
+      <c r="D97" s="10">
         <v>2</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="9" t="s">
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="I97" s="13"/>
-      <c r="K97" s="13"/>
-      <c r="L97" s="13"/>
-      <c r="M97" s="13"/>
+      <c r="I97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
     </row>
     <row r="98" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A98" s="8">
+      <c r="A98" s="9">
         <f t="shared" si="3"/>
         <v>10120031</v>
       </c>
-      <c r="B98" s="8">
+      <c r="B98" s="9">
         <v>101200</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="10">
         <v>31</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="10">
         <v>2</v>
       </c>
-      <c r="E98" s="10" t="s">
+      <c r="E98" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F98" s="8"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="9" t="s">
+      <c r="F98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="I98" s="13"/>
-      <c r="K98" s="13"/>
-      <c r="L98" s="13"/>
-      <c r="M98" s="13"/>
+      <c r="I98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
     </row>
     <row r="99" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A99" s="8">
+      <c r="A99" s="9">
         <f t="shared" si="3"/>
         <v>10120032</v>
       </c>
-      <c r="B99" s="8">
+      <c r="B99" s="9">
         <v>101200</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C99" s="10">
         <v>32</v>
       </c>
-      <c r="D99" s="9">
+      <c r="D99" s="10">
         <v>2</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E99" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="9" t="s">
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="I99" s="13"/>
-      <c r="K99" s="13"/>
-      <c r="L99" s="13"/>
-      <c r="M99" s="13"/>
+      <c r="I99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="6"/>
     </row>
     <row r="100" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A100" s="8">
+      <c r="A100" s="9">
         <f t="shared" si="3"/>
         <v>10120033</v>
       </c>
-      <c r="B100" s="8">
+      <c r="B100" s="9">
         <v>101200</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="10">
         <v>33</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="10">
         <v>2</v>
       </c>
-      <c r="E100" s="10" t="s">
+      <c r="E100" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="9" t="s">
+      <c r="F100" s="9"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="I100" s="13"/>
-      <c r="K100" s="13"/>
-      <c r="L100" s="13"/>
-      <c r="M100" s="13"/>
+      <c r="I100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
     </row>
     <row r="101" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A101" s="8">
+      <c r="A101" s="9">
         <f t="shared" si="3"/>
         <v>10120034</v>
       </c>
-      <c r="B101" s="8">
+      <c r="B101" s="9">
         <v>101200</v>
       </c>
-      <c r="C101" s="9">
+      <c r="C101" s="10">
         <v>34</v>
       </c>
-      <c r="D101" s="9">
+      <c r="D101" s="10">
         <v>2</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="E101" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F101" s="8"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="9" t="s">
+      <c r="F101" s="9"/>
+      <c r="G101" s="9"/>
+      <c r="H101" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="I101" s="13"/>
-      <c r="K101" s="13"/>
-      <c r="L101" s="13"/>
-      <c r="M101" s="13"/>
+      <c r="I101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="6"/>
     </row>
     <row r="102" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A102" s="8">
+      <c r="A102" s="9">
         <f t="shared" si="3"/>
         <v>10120035</v>
       </c>
-      <c r="B102" s="8">
+      <c r="B102" s="9">
         <v>101200</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="10">
         <v>35</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="10">
         <v>2</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="E102" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F102" s="8"/>
-      <c r="G102" s="8"/>
-      <c r="H102" s="9" t="s">
+      <c r="F102" s="9"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="I102" s="13"/>
-      <c r="K102" s="13"/>
-      <c r="L102" s="13"/>
-      <c r="M102" s="13"/>
+      <c r="I102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
+      <c r="M102" s="6"/>
     </row>
     <row r="103" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A103" s="8">
+      <c r="A103" s="9">
         <f t="shared" si="3"/>
         <v>10120036</v>
       </c>
-      <c r="B103" s="8">
+      <c r="B103" s="9">
         <v>101200</v>
       </c>
-      <c r="C103" s="9">
+      <c r="C103" s="10">
         <v>36</v>
       </c>
-      <c r="D103" s="9">
+      <c r="D103" s="10">
         <v>2</v>
       </c>
-      <c r="E103" s="10" t="s">
+      <c r="E103" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F103" s="8"/>
-      <c r="G103" s="8"/>
-      <c r="H103" s="9" t="s">
+      <c r="F103" s="9"/>
+      <c r="G103" s="9"/>
+      <c r="H103" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="I103" s="13"/>
-      <c r="K103" s="13"/>
-      <c r="L103" s="13"/>
-      <c r="M103" s="13"/>
+      <c r="I103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="6"/>
     </row>
     <row r="104" ht="16.5" spans="1:13">
       <c r="A104" s="16">
@@ -4537,10 +4912,10 @@
       <c r="H104" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="I104" s="13"/>
-      <c r="K104" s="13"/>
-      <c r="L104" s="13"/>
-      <c r="M104" s="13"/>
+      <c r="I104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="6"/>
     </row>
     <row r="105" ht="16.5" spans="1:13">
       <c r="A105" s="16">
@@ -4564,10 +4939,10 @@
       <c r="H105" s="17">
         <v>9</v>
       </c>
-      <c r="I105" s="13"/>
-      <c r="K105" s="13"/>
-      <c r="L105" s="13"/>
-      <c r="M105" s="13"/>
+      <c r="I105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="6"/>
     </row>
     <row r="106" ht="16.5" spans="1:13">
       <c r="A106" s="16">
@@ -4591,10 +4966,10 @@
       <c r="H106" s="17">
         <v>10</v>
       </c>
-      <c r="I106" s="13"/>
-      <c r="K106" s="13"/>
-      <c r="L106" s="13"/>
-      <c r="M106" s="13"/>
+      <c r="I106" s="6"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="6"/>
+      <c r="M106" s="6"/>
     </row>
     <row r="107" ht="16.5" spans="1:13">
       <c r="A107" s="16">
@@ -4618,10 +4993,10 @@
       <c r="H107" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I107" s="13"/>
-      <c r="K107" s="13"/>
-      <c r="L107" s="13"/>
-      <c r="M107" s="13"/>
+      <c r="I107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
+      <c r="M107" s="6"/>
     </row>
     <row r="108" ht="16.5" spans="1:13">
       <c r="A108" s="16">
@@ -4645,10 +5020,10 @@
       <c r="H108" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I108" s="13"/>
-      <c r="K108" s="13"/>
-      <c r="L108" s="13"/>
-      <c r="M108" s="13"/>
+      <c r="I108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="6"/>
     </row>
     <row r="109" ht="16.5" spans="1:13">
       <c r="A109" s="16">
@@ -4672,10 +5047,10 @@
       <c r="H109" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I109" s="13"/>
-      <c r="K109" s="13"/>
-      <c r="L109" s="13"/>
-      <c r="M109" s="13"/>
+      <c r="I109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="6"/>
     </row>
     <row r="110" ht="16.5" spans="1:13">
       <c r="A110" s="16">
@@ -4699,10 +5074,10 @@
       <c r="H110" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="I110" s="13"/>
-      <c r="K110" s="13"/>
-      <c r="L110" s="13"/>
-      <c r="M110" s="13"/>
+      <c r="I110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
+      <c r="M110" s="6"/>
     </row>
     <row r="111" ht="16.5" spans="1:13">
       <c r="A111" s="16">
@@ -4726,10 +5101,10 @@
       <c r="H111" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="I111" s="13"/>
-      <c r="K111" s="13"/>
-      <c r="L111" s="13"/>
-      <c r="M111" s="13"/>
+      <c r="I111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
     </row>
     <row r="112" ht="16.5" spans="1:13">
       <c r="A112" s="16">
@@ -4753,10 +5128,10 @@
       <c r="H112" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I112" s="13"/>
-      <c r="K112" s="13"/>
-      <c r="L112" s="13"/>
-      <c r="M112" s="13"/>
+      <c r="I112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="6"/>
     </row>
     <row r="113" ht="16.5" spans="1:13">
       <c r="A113" s="16">
@@ -4780,10 +5155,10 @@
       <c r="H113" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="I113" s="13"/>
-      <c r="K113" s="13"/>
-      <c r="L113" s="13"/>
-      <c r="M113" s="13"/>
+      <c r="I113" s="6"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
+      <c r="M113" s="6"/>
     </row>
     <row r="114" ht="16.5" spans="1:13">
       <c r="A114" s="16">
@@ -4807,10 +5182,10 @@
       <c r="H114" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="I114" s="13"/>
-      <c r="K114" s="13"/>
-      <c r="L114" s="13"/>
-      <c r="M114" s="13"/>
+      <c r="I114" s="6"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
+      <c r="M114" s="6"/>
     </row>
     <row r="115" ht="16.5" spans="1:13">
       <c r="A115" s="16">
@@ -4834,10 +5209,10 @@
       <c r="H115" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="I115" s="13"/>
-      <c r="K115" s="13"/>
-      <c r="L115" s="13"/>
-      <c r="M115" s="13"/>
+      <c r="I115" s="6"/>
+      <c r="K115" s="6"/>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
     </row>
     <row r="116" ht="16.5" spans="1:13">
       <c r="A116" s="16">
@@ -4861,10 +5236,10 @@
       <c r="H116" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="I116" s="13"/>
-      <c r="K116" s="13"/>
-      <c r="L116" s="13"/>
-      <c r="M116" s="13"/>
+      <c r="I116" s="6"/>
+      <c r="K116" s="6"/>
+      <c r="L116" s="6"/>
+      <c r="M116" s="6"/>
     </row>
     <row r="117" ht="16.5" spans="1:13">
       <c r="A117" s="4">
@@ -4888,10 +5263,10 @@
       <c r="H117" s="5">
         <v>9</v>
       </c>
-      <c r="I117" s="13"/>
-      <c r="K117" s="13"/>
-      <c r="L117" s="13"/>
-      <c r="M117" s="13"/>
+      <c r="I117" s="6"/>
+      <c r="K117" s="6"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
     </row>
     <row r="118" ht="16.5" spans="1:13">
       <c r="A118" s="4">
@@ -4915,10 +5290,10 @@
       <c r="H118" s="5">
         <v>10</v>
       </c>
-      <c r="I118" s="13"/>
-      <c r="K118" s="13"/>
-      <c r="L118" s="13"/>
-      <c r="M118" s="13"/>
+      <c r="I118" s="6"/>
+      <c r="K118" s="6"/>
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
     </row>
     <row r="119" ht="16.5" spans="1:13">
       <c r="A119" s="4">
@@ -4942,10 +5317,10 @@
       <c r="H119" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I119" s="13"/>
-      <c r="K119" s="13"/>
-      <c r="L119" s="13"/>
-      <c r="M119" s="13"/>
+      <c r="I119" s="6"/>
+      <c r="K119" s="6"/>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
     </row>
     <row r="120" ht="16.5" spans="1:13">
       <c r="A120" s="4">
@@ -4969,10 +5344,10 @@
       <c r="H120" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I120" s="13"/>
-      <c r="K120" s="13"/>
-      <c r="L120" s="13"/>
-      <c r="M120" s="13"/>
+      <c r="I120" s="6"/>
+      <c r="K120" s="6"/>
+      <c r="L120" s="6"/>
+      <c r="M120" s="6"/>
     </row>
     <row r="121" ht="16.5" spans="1:13">
       <c r="A121" s="4">
@@ -4996,10 +5371,10 @@
       <c r="H121" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I121" s="13"/>
-      <c r="K121" s="13"/>
-      <c r="L121" s="13"/>
-      <c r="M121" s="13"/>
+      <c r="I121" s="6"/>
+      <c r="K121" s="6"/>
+      <c r="L121" s="6"/>
+      <c r="M121" s="6"/>
     </row>
     <row r="122" ht="16.5" spans="1:13">
       <c r="A122" s="4">
@@ -5023,10 +5398,10 @@
       <c r="H122" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I122" s="13"/>
-      <c r="K122" s="13"/>
-      <c r="L122" s="13"/>
-      <c r="M122" s="13"/>
+      <c r="I122" s="6"/>
+      <c r="K122" s="6"/>
+      <c r="L122" s="6"/>
+      <c r="M122" s="6"/>
     </row>
     <row r="123" ht="16.5" spans="1:13">
       <c r="A123" s="4">
@@ -5050,10 +5425,10 @@
       <c r="H123" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I123" s="13"/>
-      <c r="K123" s="13"/>
-      <c r="L123" s="13"/>
-      <c r="M123" s="13"/>
+      <c r="I123" s="6"/>
+      <c r="K123" s="6"/>
+      <c r="L123" s="6"/>
+      <c r="M123" s="6"/>
     </row>
     <row r="124" ht="16.5" spans="1:13">
       <c r="A124" s="4">
@@ -5077,10 +5452,10 @@
       <c r="H124" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I124" s="13"/>
-      <c r="K124" s="13"/>
-      <c r="L124" s="13"/>
-      <c r="M124" s="13"/>
+      <c r="I124" s="6"/>
+      <c r="K124" s="6"/>
+      <c r="L124" s="6"/>
+      <c r="M124" s="6"/>
     </row>
     <row r="125" ht="16.5" spans="1:13">
       <c r="A125" s="4">
@@ -5104,10 +5479,10 @@
       <c r="H125" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I125" s="13"/>
-      <c r="K125" s="13"/>
-      <c r="L125" s="13"/>
-      <c r="M125" s="13"/>
+      <c r="I125" s="6"/>
+      <c r="K125" s="6"/>
+      <c r="L125" s="6"/>
+      <c r="M125" s="6"/>
     </row>
     <row r="126" ht="16.5" spans="1:13">
       <c r="A126" s="4">
@@ -5131,10 +5506,10 @@
       <c r="H126" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I126" s="13"/>
-      <c r="K126" s="13"/>
-      <c r="L126" s="13"/>
-      <c r="M126" s="13"/>
+      <c r="I126" s="6"/>
+      <c r="K126" s="6"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="6"/>
     </row>
     <row r="127" ht="16.5" spans="1:13">
       <c r="A127" s="4">
@@ -5158,10 +5533,10 @@
       <c r="H127" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I127" s="13"/>
-      <c r="K127" s="13"/>
-      <c r="L127" s="13"/>
-      <c r="M127" s="13"/>
+      <c r="I127" s="6"/>
+      <c r="K127" s="6"/>
+      <c r="L127" s="6"/>
+      <c r="M127" s="6"/>
     </row>
     <row r="128" ht="16.5" spans="1:13">
       <c r="A128" s="4">
@@ -5185,10 +5560,10 @@
       <c r="H128" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I128" s="13"/>
-      <c r="K128" s="13"/>
-      <c r="L128" s="13"/>
-      <c r="M128" s="13"/>
+      <c r="I128" s="6"/>
+      <c r="K128" s="6"/>
+      <c r="L128" s="6"/>
+      <c r="M128" s="6"/>
     </row>
     <row r="129" ht="16.5" spans="1:13">
       <c r="A129" s="4">
@@ -5212,10 +5587,10 @@
       <c r="H129" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I129" s="13"/>
-      <c r="K129" s="13"/>
-      <c r="L129" s="13"/>
-      <c r="M129" s="13"/>
+      <c r="I129" s="6"/>
+      <c r="K129" s="6"/>
+      <c r="L129" s="6"/>
+      <c r="M129" s="6"/>
     </row>
     <row r="130" ht="16.5" spans="1:13">
       <c r="A130" s="4">
@@ -5239,10 +5614,10 @@
       <c r="H130" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I130" s="13"/>
-      <c r="K130" s="13"/>
-      <c r="L130" s="13"/>
-      <c r="M130" s="13"/>
+      <c r="I130" s="6"/>
+      <c r="K130" s="6"/>
+      <c r="L130" s="6"/>
+      <c r="M130" s="6"/>
     </row>
     <row r="131" ht="16.5" spans="1:13">
       <c r="A131" s="4">
@@ -5266,10 +5641,10 @@
       <c r="H131" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I131" s="13"/>
-      <c r="K131" s="13"/>
-      <c r="L131" s="13"/>
-      <c r="M131" s="13"/>
+      <c r="I131" s="6"/>
+      <c r="K131" s="6"/>
+      <c r="L131" s="6"/>
+      <c r="M131" s="6"/>
     </row>
     <row r="132" ht="16.5" spans="1:13">
       <c r="A132" s="4">
@@ -5293,10 +5668,10 @@
       <c r="H132" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I132" s="13"/>
-      <c r="K132" s="13"/>
-      <c r="L132" s="13"/>
-      <c r="M132" s="13"/>
+      <c r="I132" s="6"/>
+      <c r="K132" s="6"/>
+      <c r="L132" s="6"/>
+      <c r="M132" s="6"/>
     </row>
     <row r="133" ht="16.5" spans="1:13">
       <c r="A133" s="4">
@@ -5320,10 +5695,10 @@
       <c r="H133" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I133" s="13"/>
-      <c r="K133" s="13"/>
-      <c r="L133" s="13"/>
-      <c r="M133" s="13"/>
+      <c r="I133" s="6"/>
+      <c r="K133" s="6"/>
+      <c r="L133" s="6"/>
+      <c r="M133" s="6"/>
     </row>
     <row r="134" ht="16.5" spans="1:13">
       <c r="A134" s="4">
@@ -5347,10 +5722,10 @@
       <c r="H134" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I134" s="13"/>
-      <c r="K134" s="13"/>
-      <c r="L134" s="13"/>
-      <c r="M134" s="13"/>
+      <c r="I134" s="6"/>
+      <c r="K134" s="6"/>
+      <c r="L134" s="6"/>
+      <c r="M134" s="6"/>
     </row>
     <row r="135" ht="16.5" spans="1:13">
       <c r="A135" s="4">
@@ -5374,10 +5749,10 @@
       <c r="H135" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I135" s="13"/>
-      <c r="K135" s="13"/>
-      <c r="L135" s="13"/>
-      <c r="M135" s="13"/>
+      <c r="I135" s="6"/>
+      <c r="K135" s="6"/>
+      <c r="L135" s="6"/>
+      <c r="M135" s="6"/>
     </row>
     <row r="136" ht="16.5" spans="1:13">
       <c r="A136" s="4">
@@ -5401,10 +5776,10 @@
       <c r="H136" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I136" s="13"/>
-      <c r="K136" s="13"/>
-      <c r="L136" s="13"/>
-      <c r="M136" s="13"/>
+      <c r="I136" s="6"/>
+      <c r="K136" s="6"/>
+      <c r="L136" s="6"/>
+      <c r="M136" s="6"/>
     </row>
     <row r="137" ht="16.5" spans="1:13">
       <c r="A137" s="4">
@@ -5428,10 +5803,10 @@
       <c r="H137" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I137" s="13"/>
-      <c r="K137" s="13"/>
-      <c r="L137" s="13"/>
-      <c r="M137" s="13"/>
+      <c r="I137" s="6"/>
+      <c r="K137" s="6"/>
+      <c r="L137" s="6"/>
+      <c r="M137" s="6"/>
     </row>
     <row r="138" ht="16.5" spans="1:13">
       <c r="A138" s="4">
@@ -5455,64 +5830,1352 @@
       <c r="H138" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I138" s="13"/>
-      <c r="K138" s="13"/>
-      <c r="L138" s="13"/>
-      <c r="M138" s="13"/>
+      <c r="I138" s="6"/>
+      <c r="K138" s="6"/>
+      <c r="L138" s="6"/>
+      <c r="M138" s="6"/>
     </row>
     <row r="139" ht="16.5" spans="1:13">
-      <c r="A139" s="6">
+      <c r="A139" s="7">
         <f t="shared" si="4"/>
         <v>10240028</v>
       </c>
-      <c r="B139" s="6">
+      <c r="B139" s="7">
         <v>102400</v>
       </c>
-      <c r="C139" s="7">
+      <c r="C139" s="8">
         <v>28</v>
       </c>
-      <c r="D139" s="7">
+      <c r="D139" s="8">
         <v>2</v>
       </c>
-      <c r="E139" s="7" t="s">
+      <c r="E139" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F139" s="7"/>
-      <c r="G139" s="7"/>
-      <c r="H139" s="7" t="s">
+      <c r="F139" s="8"/>
+      <c r="G139" s="8"/>
+      <c r="H139" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I139" s="13"/>
-      <c r="K139" s="13"/>
-      <c r="L139" s="13"/>
-      <c r="M139" s="13"/>
+      <c r="I139" s="6"/>
+      <c r="K139" s="6"/>
+      <c r="L139" s="6"/>
+      <c r="M139" s="6"/>
     </row>
     <row r="140" ht="16.5" spans="1:13">
-      <c r="A140" s="6">
+      <c r="A140" s="7">
         <f t="shared" si="4"/>
         <v>10240030</v>
       </c>
-      <c r="B140" s="6">
+      <c r="B140" s="7">
         <v>102400</v>
       </c>
-      <c r="C140" s="7">
+      <c r="C140" s="8">
         <v>30</v>
       </c>
-      <c r="D140" s="7">
+      <c r="D140" s="8">
         <v>2</v>
       </c>
-      <c r="E140" s="7" t="s">
+      <c r="E140" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7" t="s">
+      <c r="F140" s="8"/>
+      <c r="G140" s="8"/>
+      <c r="H140" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I140" s="13"/>
-      <c r="K140" s="13"/>
-      <c r="L140" s="13"/>
-      <c r="M140" s="13"/>
+      <c r="I140" s="6"/>
+      <c r="K140" s="6"/>
+      <c r="L140" s="6"/>
+      <c r="M140" s="6"/>
+    </row>
+    <row r="141" ht="16.5" spans="1:13">
+      <c r="A141" s="18">
+        <f t="shared" ref="A141:A162" si="5">B141*100+C141</f>
+        <v>10170001</v>
+      </c>
+      <c r="B141" s="19">
+        <v>101700</v>
+      </c>
+      <c r="C141" s="19">
+        <v>1</v>
+      </c>
+      <c r="D141" s="19">
+        <v>0</v>
+      </c>
+      <c r="E141" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F141" s="19"/>
+      <c r="G141" s="19"/>
+      <c r="H141" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="142" ht="16.5" spans="1:13">
+      <c r="A142" s="20">
+        <f t="shared" si="5"/>
+        <v>10170002</v>
+      </c>
+      <c r="B142" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C142" s="21">
+        <v>2</v>
+      </c>
+      <c r="D142" s="21">
+        <v>0</v>
+      </c>
+      <c r="E142" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="F142" s="21"/>
+      <c r="G142" s="21"/>
+      <c r="H142" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="143" ht="16.5" spans="1:13">
+      <c r="A143" s="20">
+        <f t="shared" si="5"/>
+        <v>10170003</v>
+      </c>
+      <c r="B143" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C143" s="21">
+        <v>3</v>
+      </c>
+      <c r="D143" s="21">
+        <v>0</v>
+      </c>
+      <c r="E143" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="F143" s="21"/>
+      <c r="G143" s="21"/>
+      <c r="H143" s="21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="144" ht="16.5" spans="1:13">
+      <c r="A144" s="20">
+        <f t="shared" si="5"/>
+        <v>10170004</v>
+      </c>
+      <c r="B144" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C144" s="21">
+        <v>4</v>
+      </c>
+      <c r="D144" s="21">
+        <v>0</v>
+      </c>
+      <c r="E144" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F144" s="21"/>
+      <c r="G144" s="21"/>
+      <c r="H144" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="145" ht="16.5" spans="1:8">
+      <c r="A145" s="20">
+        <f t="shared" si="5"/>
+        <v>10170005</v>
+      </c>
+      <c r="B145" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C145" s="21">
+        <v>5</v>
+      </c>
+      <c r="D145" s="21">
+        <v>0</v>
+      </c>
+      <c r="E145" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="F145" s="21"/>
+      <c r="G145" s="21"/>
+      <c r="H145" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="146" ht="16.5" spans="1:8">
+      <c r="A146" s="20">
+        <f t="shared" si="5"/>
+        <v>10170006</v>
+      </c>
+      <c r="B146" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C146" s="21">
+        <v>6</v>
+      </c>
+      <c r="D146" s="21">
+        <v>0</v>
+      </c>
+      <c r="E146" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="F146" s="21"/>
+      <c r="G146" s="21"/>
+      <c r="H146" s="21" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="147" ht="16.5" spans="1:8">
+      <c r="A147" s="20">
+        <f t="shared" si="5"/>
+        <v>10170007</v>
+      </c>
+      <c r="B147" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C147" s="21">
+        <v>7</v>
+      </c>
+      <c r="D147" s="21">
+        <v>0</v>
+      </c>
+      <c r="E147" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F147" s="21"/>
+      <c r="G147" s="21"/>
+      <c r="H147" s="21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="148" ht="16.5" spans="1:8">
+      <c r="A148" s="20">
+        <f t="shared" si="5"/>
+        <v>10170008</v>
+      </c>
+      <c r="B148" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C148" s="21">
+        <v>8</v>
+      </c>
+      <c r="D148" s="21">
+        <v>0</v>
+      </c>
+      <c r="E148" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="F148" s="21"/>
+      <c r="G148" s="21"/>
+      <c r="H148" s="21" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="149" ht="16.5" spans="1:8">
+      <c r="A149" s="20">
+        <f t="shared" si="5"/>
+        <v>10170009</v>
+      </c>
+      <c r="B149" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C149" s="21">
+        <v>9</v>
+      </c>
+      <c r="D149" s="21">
+        <v>1</v>
+      </c>
+      <c r="E149" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="F149" s="21"/>
+      <c r="G149" s="21"/>
+      <c r="H149" s="21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="150" ht="16.5" spans="1:8">
+      <c r="A150" s="20">
+        <f t="shared" si="5"/>
+        <v>10170010</v>
+      </c>
+      <c r="B150" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C150" s="21">
+        <v>10</v>
+      </c>
+      <c r="D150" s="21">
+        <v>2</v>
+      </c>
+      <c r="E150" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="F150" s="21"/>
+      <c r="G150" s="21"/>
+      <c r="H150" s="21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="151" ht="16.5" spans="1:8">
+      <c r="A151" s="20">
+        <f t="shared" si="5"/>
+        <v>10170011</v>
+      </c>
+      <c r="B151" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C151" s="21">
+        <v>11</v>
+      </c>
+      <c r="D151" s="21">
+        <v>0</v>
+      </c>
+      <c r="E151" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="F151" s="22">
+        <v>9</v>
+      </c>
+      <c r="G151" s="21"/>
+      <c r="H151" s="21" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="152" ht="16.5" spans="1:8">
+      <c r="A152" s="20">
+        <f t="shared" si="5"/>
+        <v>10170012</v>
+      </c>
+      <c r="B152" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C152" s="21">
+        <v>12</v>
+      </c>
+      <c r="D152" s="21">
+        <v>0</v>
+      </c>
+      <c r="E152" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="F152" s="22">
+        <v>9</v>
+      </c>
+      <c r="G152" s="21"/>
+      <c r="H152" s="21" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="153" ht="16.5" spans="1:8">
+      <c r="A153" s="20">
+        <f t="shared" si="5"/>
+        <v>10170013</v>
+      </c>
+      <c r="B153" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C153" s="21">
+        <v>13</v>
+      </c>
+      <c r="D153" s="21">
+        <v>0</v>
+      </c>
+      <c r="E153" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="F153" s="22">
+        <v>9</v>
+      </c>
+      <c r="G153" s="21"/>
+      <c r="H153" s="21" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="154" ht="16.5" spans="1:8">
+      <c r="A154" s="20">
+        <f t="shared" si="5"/>
+        <v>10170014</v>
+      </c>
+      <c r="B154" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C154" s="21">
+        <v>14</v>
+      </c>
+      <c r="D154" s="21">
+        <v>0</v>
+      </c>
+      <c r="E154" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="F154" s="22">
+        <v>9</v>
+      </c>
+      <c r="G154" s="21"/>
+      <c r="H154" s="21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="155" ht="16.5" spans="1:8">
+      <c r="A155" s="20">
+        <f t="shared" si="5"/>
+        <v>10170015</v>
+      </c>
+      <c r="B155" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C155" s="21">
+        <v>15</v>
+      </c>
+      <c r="D155" s="21">
+        <v>0</v>
+      </c>
+      <c r="E155" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="F155" s="22">
+        <v>9</v>
+      </c>
+      <c r="G155" s="21"/>
+      <c r="H155" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="156" ht="16.5" spans="1:8">
+      <c r="A156" s="20">
+        <f t="shared" si="5"/>
+        <v>10170016</v>
+      </c>
+      <c r="B156" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C156" s="21">
+        <v>16</v>
+      </c>
+      <c r="D156" s="21">
+        <v>0</v>
+      </c>
+      <c r="E156" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F156" s="22">
+        <v>9</v>
+      </c>
+      <c r="G156" s="21"/>
+      <c r="H156" s="21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="157" ht="16.5" spans="1:8">
+      <c r="A157" s="20">
+        <f t="shared" si="5"/>
+        <v>10170017</v>
+      </c>
+      <c r="B157" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C157" s="21">
+        <v>17</v>
+      </c>
+      <c r="D157" s="21">
+        <v>0</v>
+      </c>
+      <c r="E157" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="F157" s="22">
+        <v>9</v>
+      </c>
+      <c r="G157" s="21"/>
+      <c r="H157" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="158" ht="16.5" spans="1:8">
+      <c r="A158" s="20">
+        <f t="shared" si="5"/>
+        <v>10170018</v>
+      </c>
+      <c r="B158" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C158" s="21">
+        <v>18</v>
+      </c>
+      <c r="D158" s="21">
+        <v>0</v>
+      </c>
+      <c r="E158" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="F158" s="22">
+        <v>9</v>
+      </c>
+      <c r="G158" s="21"/>
+      <c r="H158" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="159" ht="16.5" spans="1:8">
+      <c r="A159" s="20">
+        <f t="shared" si="5"/>
+        <v>10170019</v>
+      </c>
+      <c r="B159" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C159" s="21">
+        <v>19</v>
+      </c>
+      <c r="D159" s="21">
+        <v>3</v>
+      </c>
+      <c r="E159" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="F159" s="21"/>
+      <c r="G159" s="21"/>
+      <c r="H159" s="21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="160" ht="16.5" spans="1:8">
+      <c r="A160" s="20">
+        <f t="shared" si="5"/>
+        <v>10170020</v>
+      </c>
+      <c r="B160" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C160" s="21">
+        <v>20</v>
+      </c>
+      <c r="D160" s="21">
+        <v>3</v>
+      </c>
+      <c r="E160" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="F160" s="21"/>
+      <c r="G160" s="21"/>
+      <c r="H160" s="21" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="161" ht="16.5" spans="1:8">
+      <c r="A161" s="20">
+        <f t="shared" si="5"/>
+        <v>10170021</v>
+      </c>
+      <c r="B161" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C161" s="21">
+        <v>21</v>
+      </c>
+      <c r="D161" s="21">
+        <v>3</v>
+      </c>
+      <c r="E161" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="F161" s="21"/>
+      <c r="G161" s="21"/>
+      <c r="H161" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="162" ht="16.5" spans="1:8">
+      <c r="A162" s="20">
+        <f t="shared" si="5"/>
+        <v>10170022</v>
+      </c>
+      <c r="B162" s="21">
+        <v>101700</v>
+      </c>
+      <c r="C162" s="21">
+        <v>22</v>
+      </c>
+      <c r="D162" s="21">
+        <v>3</v>
+      </c>
+      <c r="E162" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="F162" s="21"/>
+      <c r="G162" s="21"/>
+      <c r="H162" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="163" ht="16.5" spans="1:8">
+      <c r="A163" s="23">
+        <f t="shared" ref="A163:A180" si="6">B163*100+C163</f>
+        <v>10220001</v>
+      </c>
+      <c r="B163" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C163" s="24">
+        <v>1</v>
+      </c>
+      <c r="D163" s="24">
+        <v>0</v>
+      </c>
+      <c r="E163" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="F163" s="24"/>
+      <c r="G163" s="24"/>
+      <c r="H163" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" ht="16.5" spans="1:8">
+      <c r="A164" s="23">
+        <f t="shared" si="6"/>
+        <v>10220002</v>
+      </c>
+      <c r="B164" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C164" s="24">
+        <v>2</v>
+      </c>
+      <c r="D164" s="24">
+        <v>0</v>
+      </c>
+      <c r="E164" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="165" ht="16.5" spans="1:8">
+      <c r="A165" s="23">
+        <f t="shared" si="6"/>
+        <v>10220003</v>
+      </c>
+      <c r="B165" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C165" s="24">
+        <v>3</v>
+      </c>
+      <c r="D165" s="24">
+        <v>0</v>
+      </c>
+      <c r="E165" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="F165" s="24"/>
+      <c r="G165" s="24"/>
+      <c r="H165" s="24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" ht="16.5" spans="1:8">
+      <c r="A166" s="23">
+        <f t="shared" si="6"/>
+        <v>10220004</v>
+      </c>
+      <c r="B166" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C166" s="24">
+        <v>4</v>
+      </c>
+      <c r="D166" s="24">
+        <v>0</v>
+      </c>
+      <c r="E166" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="F166" s="24"/>
+      <c r="G166" s="24"/>
+      <c r="H166" s="24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167" ht="16.5" spans="1:8">
+      <c r="A167" s="23">
+        <f t="shared" si="6"/>
+        <v>10220005</v>
+      </c>
+      <c r="B167" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C167" s="24">
+        <v>5</v>
+      </c>
+      <c r="D167" s="24">
+        <v>0</v>
+      </c>
+      <c r="E167" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" ht="16.5" spans="1:8">
+      <c r="A168" s="23">
+        <f t="shared" si="6"/>
+        <v>10220006</v>
+      </c>
+      <c r="B168" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C168" s="24">
+        <v>6</v>
+      </c>
+      <c r="D168" s="24">
+        <v>0</v>
+      </c>
+      <c r="E168" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F168" s="24"/>
+      <c r="G168" s="24"/>
+      <c r="H168" s="24" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="169" ht="16.5" spans="1:8">
+      <c r="A169" s="23">
+        <f t="shared" si="6"/>
+        <v>10220007</v>
+      </c>
+      <c r="B169" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C169" s="24">
+        <v>7</v>
+      </c>
+      <c r="D169" s="24">
+        <v>0</v>
+      </c>
+      <c r="E169" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="F169" s="24"/>
+      <c r="G169" s="24"/>
+      <c r="H169" s="24" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="170" ht="16.5" spans="1:8">
+      <c r="A170" s="23">
+        <f t="shared" si="6"/>
+        <v>10220008</v>
+      </c>
+      <c r="B170" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C170" s="24">
+        <v>8</v>
+      </c>
+      <c r="D170" s="24">
+        <v>0</v>
+      </c>
+      <c r="E170" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F170" s="24"/>
+      <c r="G170" s="24"/>
+      <c r="H170" s="24" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="171" ht="16.5" spans="1:8">
+      <c r="A171" s="23">
+        <f t="shared" si="6"/>
+        <v>10220009</v>
+      </c>
+      <c r="B171" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C171" s="24">
+        <v>9</v>
+      </c>
+      <c r="D171" s="24">
+        <v>0</v>
+      </c>
+      <c r="E171" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="F171" s="24"/>
+      <c r="G171" s="24"/>
+      <c r="H171" s="24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="172" ht="16.5" spans="1:8">
+      <c r="A172" s="23">
+        <f t="shared" si="6"/>
+        <v>10220010</v>
+      </c>
+      <c r="B172" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C172" s="24">
+        <v>10</v>
+      </c>
+      <c r="D172" s="24">
+        <v>0</v>
+      </c>
+      <c r="E172" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="F172" s="24"/>
+      <c r="G172" s="24"/>
+      <c r="H172" s="24" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="173" ht="16.5" spans="1:8">
+      <c r="A173" s="23">
+        <f t="shared" si="6"/>
+        <v>10220011</v>
+      </c>
+      <c r="B173" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C173" s="24">
+        <v>11</v>
+      </c>
+      <c r="D173" s="24">
+        <v>1</v>
+      </c>
+      <c r="E173" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="F173" s="24"/>
+      <c r="G173" s="24"/>
+      <c r="H173" s="24" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="174" ht="16.5" spans="1:8">
+      <c r="A174" s="23">
+        <f t="shared" si="6"/>
+        <v>10220012</v>
+      </c>
+      <c r="B174" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C174" s="24">
+        <v>12</v>
+      </c>
+      <c r="D174" s="24">
+        <v>1</v>
+      </c>
+      <c r="E174" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="F174" s="24"/>
+      <c r="G174" s="24"/>
+      <c r="H174" s="24" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="175" ht="16.5" spans="1:8">
+      <c r="A175" s="23">
+        <f t="shared" si="6"/>
+        <v>10220013</v>
+      </c>
+      <c r="B175" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C175" s="24">
+        <v>13</v>
+      </c>
+      <c r="D175" s="24">
+        <v>1</v>
+      </c>
+      <c r="E175" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="F175" s="24"/>
+      <c r="G175" s="24"/>
+      <c r="H175" s="24" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="176" ht="16.5" spans="1:8">
+      <c r="A176" s="23">
+        <f t="shared" si="6"/>
+        <v>10220014</v>
+      </c>
+      <c r="B176" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C176" s="24">
+        <v>14</v>
+      </c>
+      <c r="D176" s="24">
+        <v>2</v>
+      </c>
+      <c r="E176" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="F176" s="24"/>
+      <c r="G176" s="24"/>
+      <c r="H176" s="24" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="177" ht="16.5" spans="1:8">
+      <c r="A177" s="23">
+        <f t="shared" si="6"/>
+        <v>10220015</v>
+      </c>
+      <c r="B177" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C177" s="24">
+        <v>15</v>
+      </c>
+      <c r="D177" s="24">
+        <v>3</v>
+      </c>
+      <c r="E177" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="F177" s="24"/>
+      <c r="G177" s="24"/>
+      <c r="H177" s="24" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="178" ht="16.5" spans="1:8">
+      <c r="A178" s="23">
+        <f t="shared" si="6"/>
+        <v>10220016</v>
+      </c>
+      <c r="B178" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C178" s="24">
+        <v>16</v>
+      </c>
+      <c r="D178" s="24">
+        <v>3</v>
+      </c>
+      <c r="E178" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="F178" s="24"/>
+      <c r="G178" s="24"/>
+      <c r="H178" s="24" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="179" ht="16.5" spans="1:8">
+      <c r="A179" s="23">
+        <f t="shared" si="6"/>
+        <v>10220017</v>
+      </c>
+      <c r="B179" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C179" s="24">
+        <v>17</v>
+      </c>
+      <c r="D179" s="24">
+        <v>3</v>
+      </c>
+      <c r="E179" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F179" s="24"/>
+      <c r="G179" s="24"/>
+      <c r="H179" s="24" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="180" ht="16.5" spans="1:8">
+      <c r="A180" s="23">
+        <f t="shared" si="6"/>
+        <v>10220018</v>
+      </c>
+      <c r="B180" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C180" s="24">
+        <v>18</v>
+      </c>
+      <c r="D180" s="24">
+        <v>3</v>
+      </c>
+      <c r="E180" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="F180" s="24"/>
+      <c r="G180" s="24"/>
+      <c r="H180" s="24" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="181" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A181" s="26">
+        <v>10210001</v>
+      </c>
+      <c r="B181" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C181" s="26">
+        <v>1</v>
+      </c>
+      <c r="D181" s="26">
+        <v>0</v>
+      </c>
+      <c r="E181" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="F181" s="26"/>
+      <c r="G181" s="26"/>
+      <c r="H181" s="27" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="182" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A182" s="26">
+        <v>10210002</v>
+      </c>
+      <c r="B182" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C182" s="26">
+        <v>2</v>
+      </c>
+      <c r="D182" s="26">
+        <v>0</v>
+      </c>
+      <c r="E182" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="F182" s="26"/>
+      <c r="G182" s="26"/>
+      <c r="H182" s="27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="183" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A183" s="26">
+        <v>10210003</v>
+      </c>
+      <c r="B183" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C183" s="26">
+        <v>3</v>
+      </c>
+      <c r="D183" s="26">
+        <v>0</v>
+      </c>
+      <c r="E183" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="F183" s="26"/>
+      <c r="G183" s="26"/>
+      <c r="H183" s="27" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="184" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A184" s="26">
+        <v>10210004</v>
+      </c>
+      <c r="B184" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C184" s="26">
+        <v>4</v>
+      </c>
+      <c r="D184" s="26">
+        <v>0</v>
+      </c>
+      <c r="E184" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="F184" s="26"/>
+      <c r="G184" s="26"/>
+      <c r="H184" s="27" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="185" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A185" s="26">
+        <v>10210005</v>
+      </c>
+      <c r="B185" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C185" s="26">
+        <v>5</v>
+      </c>
+      <c r="D185" s="26">
+        <v>0</v>
+      </c>
+      <c r="E185" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="F185" s="26"/>
+      <c r="G185" s="26"/>
+      <c r="H185" s="27" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="186" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A186" s="26">
+        <v>10210006</v>
+      </c>
+      <c r="B186" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C186" s="26">
+        <v>6</v>
+      </c>
+      <c r="D186" s="26">
+        <v>0</v>
+      </c>
+      <c r="E186" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="F186" s="26"/>
+      <c r="G186" s="26"/>
+      <c r="H186" s="26" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="187" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A187" s="26">
+        <v>10210007</v>
+      </c>
+      <c r="B187" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C187" s="26">
+        <v>7</v>
+      </c>
+      <c r="D187" s="26">
+        <v>0</v>
+      </c>
+      <c r="E187" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="F187" s="26"/>
+      <c r="G187" s="26"/>
+      <c r="H187" s="28" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="188" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A188" s="26">
+        <v>10210008</v>
+      </c>
+      <c r="B188" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C188" s="26">
+        <v>8</v>
+      </c>
+      <c r="D188" s="26">
+        <v>0</v>
+      </c>
+      <c r="E188" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="F188" s="26"/>
+      <c r="G188" s="26"/>
+      <c r="H188" s="26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="189" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A189" s="26">
+        <v>10210009</v>
+      </c>
+      <c r="B189" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C189" s="26">
+        <v>9</v>
+      </c>
+      <c r="D189" s="26">
+        <v>0</v>
+      </c>
+      <c r="E189" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="F189" s="26"/>
+      <c r="G189" s="26"/>
+      <c r="H189" s="26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="190" ht="16.5" spans="1:8">
+      <c r="A190" s="26">
+        <v>10210010</v>
+      </c>
+      <c r="B190" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C190" s="26">
+        <v>10</v>
+      </c>
+      <c r="D190" s="26">
+        <v>2</v>
+      </c>
+      <c r="E190" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="F190" s="28"/>
+      <c r="G190" s="28"/>
+      <c r="H190" s="27" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="191" ht="16.5" spans="1:8">
+      <c r="A191" s="26">
+        <v>10210011</v>
+      </c>
+      <c r="B191" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C191" s="26">
+        <v>11</v>
+      </c>
+      <c r="D191" s="26">
+        <v>1</v>
+      </c>
+      <c r="E191" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="F191" s="28"/>
+      <c r="G191" s="28"/>
+      <c r="H191" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="192" ht="16.5" spans="1:8">
+      <c r="A192" s="26">
+        <v>10210012</v>
+      </c>
+      <c r="B192" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C192" s="26">
+        <v>12</v>
+      </c>
+      <c r="D192" s="26">
+        <v>2</v>
+      </c>
+      <c r="E192" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="F192" s="28"/>
+      <c r="G192" s="28"/>
+      <c r="H192" s="27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="193" ht="17.25" spans="1:8">
+      <c r="A193" s="26">
+        <v>10210013</v>
+      </c>
+      <c r="B193" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C193" s="26">
+        <v>13</v>
+      </c>
+      <c r="D193" s="26">
+        <v>3</v>
+      </c>
+      <c r="E193" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="F193" s="28"/>
+      <c r="G193" s="28"/>
+      <c r="H193" s="29" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="194" ht="17.25" spans="1:8">
+      <c r="A194" s="26">
+        <v>10210014</v>
+      </c>
+      <c r="B194" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C194" s="26">
+        <v>14</v>
+      </c>
+      <c r="D194" s="26">
+        <v>3</v>
+      </c>
+      <c r="E194" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="F194" s="28"/>
+      <c r="G194" s="28"/>
+      <c r="H194" s="29" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="195" ht="17.25" spans="1:8">
+      <c r="A195" s="26">
+        <v>10210015</v>
+      </c>
+      <c r="B195" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C195" s="26">
+        <v>15</v>
+      </c>
+      <c r="D195" s="26">
+        <v>3</v>
+      </c>
+      <c r="E195" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="F195" s="28"/>
+      <c r="G195" s="28"/>
+      <c r="H195" s="29" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="196" ht="17.25" spans="1:8">
+      <c r="A196" s="26">
+        <v>10210016</v>
+      </c>
+      <c r="B196" s="26">
+        <v>102100</v>
+      </c>
+      <c r="C196" s="26">
+        <v>16</v>
+      </c>
+      <c r="D196" s="26">
+        <v>3</v>
+      </c>
+      <c r="E196" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="F196" s="28"/>
+      <c r="G196" s="28"/>
+      <c r="H196" s="29" t="s">
+        <v>228</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:G2">

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="302">
   <si>
     <t>图标</t>
   </si>
@@ -952,6 +952,75 @@
   </si>
   <si>
     <t>jkcz_icon_16.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_1.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_2.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_3.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_4.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_5.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_6.png</t>
+  </si>
+  <si>
+    <t>球星1</t>
+  </si>
+  <si>
+    <t>lqjx_icon_7.png</t>
+  </si>
+  <si>
+    <t>球星2</t>
+  </si>
+  <si>
+    <t>lqjx_icon_8.png</t>
+  </si>
+  <si>
+    <t>球星3</t>
+  </si>
+  <si>
+    <t>lqjx_icon_9.png</t>
+  </si>
+  <si>
+    <t>球星4</t>
+  </si>
+  <si>
+    <t>lqjx_icon_10.png</t>
+  </si>
+  <si>
+    <t>球星5</t>
+  </si>
+  <si>
+    <t>lqjx_icon_11.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_12.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_13.png</t>
+  </si>
+  <si>
+    <t>+1免费游戏</t>
+  </si>
+  <si>
+    <t>lqjx_icon_14.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_15.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_16.png</t>
+  </si>
+  <si>
+    <t>lqjx_icon_17.png</t>
   </si>
 </sst>
 </file>
@@ -973,6 +1042,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
@@ -987,12 +1062,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1171,7 +1240,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1223,6 +1292,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1590,7 +1665,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1614,16 +1689,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1632,177 +1707,192 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2125,7 +2215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M196"/>
+  <dimension ref="A1:M224"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -2137,5046 +2227,5441 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:13">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" ht="16.5" spans="1:13">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" ht="16.5" spans="1:13">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" ht="16.5" spans="1:13">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <f>B5*100+C5</f>
         <v>10010001</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>100100</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5">
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6">
         <v>9</v>
       </c>
-      <c r="I5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="I5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
     </row>
     <row r="6" ht="16.5" spans="1:13">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <f t="shared" ref="A6:A46" si="0">B6*100+C6</f>
         <v>10010002</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>100100</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <v>2</v>
       </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6">
         <v>10</v>
       </c>
-      <c r="I6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="I6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" ht="16.5" spans="1:13">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>10010003</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <v>100100</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <v>3</v>
       </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="I7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" ht="16.5" spans="1:13">
-      <c r="A8" s="4">
+      <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>10010004</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>100100</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>4</v>
       </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5" t="s">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="I8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" ht="16.5" spans="1:13">
-      <c r="A9" s="4">
+      <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>10010005</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>100100</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>5</v>
       </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="s">
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="I9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" ht="16.5" spans="1:13">
-      <c r="A10" s="4">
+      <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>10010006</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>100100</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="6">
         <v>6</v>
       </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="I10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" ht="16.5" spans="1:13">
-      <c r="A11" s="4">
+      <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>10010007</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>100100</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="6">
         <v>7</v>
       </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="s">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="I11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
     </row>
     <row r="12" ht="16.5" spans="1:13">
-      <c r="A12" s="4">
+      <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>10010008</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <v>100100</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <v>8</v>
       </c>
-      <c r="D12" s="5">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5" t="s">
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="I12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
     </row>
     <row r="13" ht="16.5" spans="1:13">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>10010009</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <v>100100</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="6">
         <v>9</v>
       </c>
-      <c r="D13" s="5">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5" t="s">
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="I13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
     </row>
     <row r="14" ht="16.5" spans="1:13">
-      <c r="A14" s="4">
+      <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>10010010</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>100100</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="6">
         <v>10</v>
       </c>
-      <c r="D14" s="5">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5" t="s">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
+      <c r="I14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
     </row>
     <row r="15" ht="16.5" spans="1:13">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>10010011</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>100100</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="6">
         <v>11</v>
       </c>
-      <c r="D15" s="5">
-        <v>0</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="s">
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="I15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
     </row>
     <row r="16" ht="16.5" spans="1:13">
-      <c r="A16" s="4">
+      <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>10010012</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <v>100100</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="6">
         <v>12</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="6">
         <v>1</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="I16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
     </row>
     <row r="17" ht="16.5" spans="1:13">
-      <c r="A17" s="4">
+      <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>10010013</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="5">
         <v>100100</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="6">
         <v>13</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="6">
         <v>1</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5" t="s">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="I17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
     </row>
     <row r="18" ht="16.5" spans="1:13">
-      <c r="A18" s="4">
+      <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>10010014</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="5">
         <v>100100</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="6">
         <v>14</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="6">
         <v>1</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5" t="s">
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="I18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
     </row>
     <row r="19" ht="16.5" spans="1:13">
-      <c r="A19" s="4">
+      <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>10010015</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="5">
         <v>100100</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="6">
         <v>15</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="6">
         <v>2</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5" t="s">
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="I19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
     </row>
     <row r="20" ht="16.5" spans="1:13">
-      <c r="A20" s="4">
+      <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>10010016</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="5">
         <v>100100</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="6">
         <v>16</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="6">
         <v>2</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5" t="s">
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="I20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
     </row>
     <row r="21" ht="16.5" spans="1:13">
-      <c r="A21" s="4">
+      <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>10010017</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="5">
         <v>100100</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="6">
         <v>17</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="6">
         <v>2</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5" t="s">
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="I21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
     </row>
     <row r="22" ht="16.5" spans="1:13">
-      <c r="A22" s="4">
+      <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>10010018</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="5">
         <v>100100</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="6">
         <v>18</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="6">
         <v>2</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5" t="s">
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="I22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
     </row>
     <row r="23" ht="16.5" spans="1:13">
-      <c r="A23" s="4">
+      <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>10010019</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="5">
         <v>100100</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="6">
         <v>19</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="6">
         <v>3</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5" t="s">
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="I23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
     </row>
     <row r="24" ht="16.5" spans="1:13">
-      <c r="A24" s="4">
+      <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>10010020</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="5">
         <v>100100</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="6">
         <v>20</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="6">
         <v>3</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5" t="s">
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="I24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
     </row>
     <row r="25" ht="16.5" spans="1:13">
-      <c r="A25" s="4">
+      <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>10010021</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="5">
         <v>100100</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="6">
         <v>21</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="6">
         <v>3</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5" t="s">
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="I25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
     </row>
     <row r="26" ht="16.5" spans="1:13">
-      <c r="A26" s="4">
+      <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>10010022</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="5">
         <v>100100</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="6">
         <v>22</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="6">
         <v>3</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5" t="s">
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
+      <c r="I26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
     </row>
     <row r="27" ht="16.5" spans="1:13">
-      <c r="A27" s="7">
+      <c r="A27" s="8">
         <f t="shared" si="0"/>
         <v>10010028</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <v>100100</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="9">
         <v>28</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="9">
         <v>2</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8" t="s">
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="I27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
+      <c r="I27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
     </row>
     <row r="28" ht="16.5" spans="1:13">
-      <c r="A28" s="7">
+      <c r="A28" s="8">
         <f t="shared" si="0"/>
         <v>10010030</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <v>100100</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="9">
         <v>30</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="9">
         <v>2</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8" t="s">
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
+      <c r="I28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
     </row>
     <row r="29" ht="16.5" spans="1:13">
-      <c r="A29" s="9">
+      <c r="A29" s="10">
         <f t="shared" si="0"/>
         <v>10030001</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="10">
         <v>100300</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="11">
         <v>1</v>
       </c>
-      <c r="D29" s="10">
-        <v>0</v>
-      </c>
-      <c r="E29" s="11" t="s">
+      <c r="D29" s="11">
+        <v>0</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="10" t="s">
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
+      <c r="I29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
     </row>
     <row r="30" ht="16.5" spans="1:13">
-      <c r="A30" s="9">
+      <c r="A30" s="10">
         <f t="shared" si="0"/>
         <v>10030002</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="10">
         <v>100300</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="11">
         <v>2</v>
       </c>
-      <c r="D30" s="10">
-        <v>0</v>
-      </c>
-      <c r="E30" s="11" t="s">
+      <c r="D30" s="11">
+        <v>0</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="10" t="s">
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="I30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
+      <c r="I30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
     </row>
     <row r="31" ht="16.5" spans="1:13">
-      <c r="A31" s="9">
+      <c r="A31" s="10">
         <f t="shared" si="0"/>
         <v>10030003</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="10">
         <v>100300</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="11">
         <v>3</v>
       </c>
-      <c r="D31" s="10">
-        <v>0</v>
-      </c>
-      <c r="E31" s="11" t="s">
+      <c r="D31" s="11">
+        <v>0</v>
+      </c>
+      <c r="E31" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="10" t="s">
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
+      <c r="I31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
     </row>
     <row r="32" ht="16.5" spans="1:13">
-      <c r="A32" s="9">
+      <c r="A32" s="10">
         <f t="shared" si="0"/>
         <v>10030004</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="10">
         <v>100300</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="11">
         <v>4</v>
       </c>
-      <c r="D32" s="10">
-        <v>0</v>
-      </c>
-      <c r="E32" s="11" t="s">
+      <c r="D32" s="11">
+        <v>0</v>
+      </c>
+      <c r="E32" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="10" t="s">
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
+      <c r="I32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
     </row>
     <row r="33" ht="16.5" spans="1:13">
-      <c r="A33" s="9">
+      <c r="A33" s="10">
         <f t="shared" si="0"/>
         <v>10030005</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="10">
         <v>100300</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="11">
         <v>5</v>
       </c>
-      <c r="D33" s="10">
-        <v>0</v>
-      </c>
-      <c r="E33" s="11" t="s">
+      <c r="D33" s="11">
+        <v>0</v>
+      </c>
+      <c r="E33" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="10" t="s">
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
+      <c r="I33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
     </row>
     <row r="34" ht="16.5" spans="1:13">
-      <c r="A34" s="9">
+      <c r="A34" s="10">
         <f t="shared" si="0"/>
         <v>10030006</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="10">
         <v>100300</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="11">
         <v>6</v>
       </c>
-      <c r="D34" s="10">
-        <v>0</v>
-      </c>
-      <c r="E34" s="11" t="s">
+      <c r="D34" s="11">
+        <v>0</v>
+      </c>
+      <c r="E34" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="10" t="s">
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="I34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
+      <c r="I34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
     </row>
     <row r="35" ht="16.5" spans="1:13">
-      <c r="A35" s="9">
+      <c r="A35" s="10">
         <f t="shared" si="0"/>
         <v>10030007</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="10">
         <v>100300</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="11">
         <v>7</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="11">
         <v>1</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9">
+      <c r="F35" s="10"/>
+      <c r="G35" s="10">
         <v>100300107</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
+      <c r="I35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
     </row>
     <row r="36" ht="16.5" spans="1:13">
-      <c r="A36" s="9">
+      <c r="A36" s="10">
         <f t="shared" si="0"/>
         <v>10030008</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="10">
         <v>100300</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="11">
         <v>8</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="11">
         <v>1</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9">
+      <c r="F36" s="10"/>
+      <c r="G36" s="10">
         <v>100300108</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="I36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
+      <c r="I36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
     </row>
     <row r="37" ht="16.5" spans="1:13">
-      <c r="A37" s="9">
+      <c r="A37" s="10">
         <f t="shared" si="0"/>
         <v>10030009</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="10">
         <v>100300</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="11">
         <v>9</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="11">
         <v>1</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9">
+      <c r="F37" s="10"/>
+      <c r="G37" s="10">
         <v>100300109</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="I37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
+      <c r="I37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
     </row>
     <row r="38" ht="16.5" spans="1:13">
-      <c r="A38" s="9">
+      <c r="A38" s="10">
         <f t="shared" si="0"/>
         <v>10030010</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="10">
         <v>100300</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="11">
         <v>10</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="11">
         <v>1</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9">
+      <c r="F38" s="10"/>
+      <c r="G38" s="10">
         <v>100300110</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="I38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
+      <c r="I38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
     </row>
     <row r="39" ht="16.5" spans="1:13">
-      <c r="A39" s="9">
+      <c r="A39" s="10">
         <f t="shared" si="0"/>
         <v>10030021</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="10">
         <v>100300</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="11">
         <v>21</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="11">
         <v>1</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9">
+      <c r="F39" s="10"/>
+      <c r="G39" s="10">
         <v>100300021</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="40" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A40" s="9">
+      <c r="A40" s="10">
         <f t="shared" si="0"/>
         <v>10030022</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="10">
         <v>100300</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="11">
         <v>22</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="11">
         <v>1</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9">
+      <c r="F40" s="10"/>
+      <c r="G40" s="10">
         <v>100300022</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="I40" s="6"/>
+      <c r="I40" s="7"/>
     </row>
     <row r="41" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A41" s="9">
+      <c r="A41" s="10">
         <f t="shared" si="0"/>
         <v>10030023</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="10">
         <v>100300</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="11">
         <v>23</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="11">
         <v>1</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9">
+      <c r="F41" s="10"/>
+      <c r="G41" s="10">
         <v>100300023</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="I41" s="6"/>
+      <c r="I41" s="7"/>
     </row>
     <row r="42" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A42" s="9">
+      <c r="A42" s="10">
         <f t="shared" si="0"/>
         <v>10030024</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="10">
         <v>100300</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="11">
         <v>24</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="11">
         <v>1</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9">
+      <c r="F42" s="10"/>
+      <c r="G42" s="10">
         <v>100300024</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="I42" s="6"/>
+      <c r="I42" s="7"/>
     </row>
     <row r="43" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A43" s="9">
+      <c r="A43" s="10">
         <f t="shared" si="0"/>
         <v>10030025</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="10">
         <v>100300</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="11">
         <v>25</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="11">
         <v>1</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9">
+      <c r="F43" s="10"/>
+      <c r="G43" s="10">
         <v>100300025</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="I43" s="6"/>
+      <c r="I43" s="7"/>
     </row>
     <row r="44" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A44" s="9">
+      <c r="A44" s="10">
         <f t="shared" si="0"/>
         <v>10030026</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="10">
         <v>100300</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="11">
         <v>26</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="11">
         <v>1</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9">
+      <c r="F44" s="10"/>
+      <c r="G44" s="10">
         <v>100300026</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="I44" s="6"/>
+      <c r="I44" s="7"/>
     </row>
     <row r="45" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A45" s="9">
+      <c r="A45" s="10">
         <f t="shared" si="0"/>
         <v>10030027</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="10">
         <v>100300</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="11">
         <v>27</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="11">
         <v>1</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9">
+      <c r="F45" s="10"/>
+      <c r="G45" s="10">
         <v>100300027</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="I45" s="6"/>
+      <c r="I45" s="7"/>
     </row>
     <row r="46" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A46" s="9">
+      <c r="A46" s="10">
         <f t="shared" si="0"/>
         <v>10030028</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="10">
         <v>100300</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C46" s="11">
         <v>28</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="11">
         <v>1</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9">
+      <c r="F46" s="10"/>
+      <c r="G46" s="10">
         <v>100300028</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="I46" s="6"/>
+      <c r="I46" s="7"/>
     </row>
     <row r="47" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A47" s="9">
+      <c r="A47" s="10">
         <f t="shared" ref="A47:A59" si="1">B47*100+C47</f>
         <v>10030029</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="10">
         <v>100300</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C47" s="11">
         <v>29</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="11">
         <v>1</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9">
+      <c r="F47" s="10"/>
+      <c r="G47" s="10">
         <v>100300029</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="I47" s="6"/>
+      <c r="I47" s="7"/>
     </row>
     <row r="48" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A48" s="9">
+      <c r="A48" s="10">
         <f t="shared" si="1"/>
         <v>10030030</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="10">
         <v>100300</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="11">
         <v>30</v>
       </c>
-      <c r="D48" s="10">
+      <c r="D48" s="11">
         <v>1</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9">
+      <c r="F48" s="10"/>
+      <c r="G48" s="10">
         <v>100300030</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="I48" s="6"/>
+      <c r="I48" s="7"/>
     </row>
     <row r="49" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A49" s="9">
+      <c r="A49" s="10">
         <f t="shared" si="1"/>
         <v>10030031</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="10">
         <v>100300</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="11">
         <v>31</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="11">
         <v>1</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9">
+      <c r="F49" s="10"/>
+      <c r="G49" s="10">
         <v>100300031</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="I49" s="6"/>
+      <c r="I49" s="7"/>
     </row>
     <row r="50" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A50" s="9">
+      <c r="A50" s="10">
         <f t="shared" si="1"/>
         <v>10030032</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="10">
         <v>100300</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C50" s="11">
         <v>32</v>
       </c>
-      <c r="D50" s="10">
+      <c r="D50" s="11">
         <v>1</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9">
+      <c r="F50" s="10"/>
+      <c r="G50" s="10">
         <v>100300032</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H50" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="I50" s="6"/>
+      <c r="I50" s="7"/>
     </row>
     <row r="51" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A51" s="9">
+      <c r="A51" s="10">
         <f t="shared" si="1"/>
         <v>10030033</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="10">
         <v>100300</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="11">
         <v>33</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="11">
         <v>1</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9">
+      <c r="F51" s="10"/>
+      <c r="G51" s="10">
         <v>100300033</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="I51" s="6"/>
+      <c r="I51" s="7"/>
     </row>
     <row r="52" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A52" s="9">
+      <c r="A52" s="10">
         <f t="shared" si="1"/>
         <v>10030034</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="10">
         <v>100300</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="11">
         <v>34</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="11">
         <v>1</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9">
+      <c r="F52" s="10"/>
+      <c r="G52" s="10">
         <v>100300034</v>
       </c>
-      <c r="H52" s="10" t="s">
+      <c r="H52" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="I52" s="6"/>
+      <c r="I52" s="7"/>
     </row>
     <row r="53" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A53" s="9">
+      <c r="A53" s="10">
         <f t="shared" si="1"/>
         <v>10030035</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="10">
         <v>100300</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="11">
         <v>35</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="11">
         <v>1</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9">
+      <c r="F53" s="10"/>
+      <c r="G53" s="10">
         <v>100300035</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="I53" s="6"/>
+      <c r="I53" s="7"/>
     </row>
     <row r="54" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A54" s="9">
+      <c r="A54" s="10">
         <f t="shared" si="1"/>
         <v>10030036</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="10">
         <v>100300</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="11">
         <v>36</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D54" s="11">
         <v>1</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9">
+      <c r="F54" s="10"/>
+      <c r="G54" s="10">
         <v>100300036</v>
       </c>
-      <c r="H54" s="10" t="s">
+      <c r="H54" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="I54" s="6"/>
+      <c r="I54" s="7"/>
     </row>
     <row r="55" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A55" s="9">
+      <c r="A55" s="10">
         <f t="shared" si="1"/>
         <v>10030037</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="10">
         <v>100300</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="11">
         <v>37</v>
       </c>
-      <c r="D55" s="10">
+      <c r="D55" s="11">
         <v>1</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9">
+      <c r="F55" s="10"/>
+      <c r="G55" s="10">
         <v>100300037</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I55" s="6"/>
+      <c r="I55" s="7"/>
     </row>
     <row r="56" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A56" s="9">
+      <c r="A56" s="10">
         <f t="shared" si="1"/>
         <v>10030038</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="10">
         <v>100300</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="11">
         <v>38</v>
       </c>
-      <c r="D56" s="10">
+      <c r="D56" s="11">
         <v>1</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9">
+      <c r="F56" s="10"/>
+      <c r="G56" s="10">
         <v>100300038</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="H56" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I56" s="6"/>
+      <c r="I56" s="7"/>
     </row>
     <row r="57" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A57" s="9">
+      <c r="A57" s="10">
         <f t="shared" si="1"/>
         <v>10030039</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="10">
         <v>100300</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="11">
         <v>39</v>
       </c>
-      <c r="D57" s="10">
+      <c r="D57" s="11">
         <v>1</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9">
+      <c r="F57" s="10"/>
+      <c r="G57" s="10">
         <v>100300039</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="I57" s="6"/>
+      <c r="I57" s="7"/>
     </row>
     <row r="58" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A58" s="9">
+      <c r="A58" s="10">
         <f t="shared" si="1"/>
         <v>10030040</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="10">
         <v>100300</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="11">
         <v>40</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="11">
         <v>1</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9">
+      <c r="F58" s="10"/>
+      <c r="G58" s="10">
         <v>100300040</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="H58" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="I58" s="6"/>
+      <c r="I58" s="7"/>
     </row>
     <row r="59" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A59" s="9">
+      <c r="A59" s="10">
         <f t="shared" si="1"/>
         <v>10030099</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="10">
         <v>100300</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C59" s="11">
         <v>99</v>
       </c>
-      <c r="D59" s="10">
-        <v>0</v>
-      </c>
-      <c r="E59" s="11"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="10" t="s">
+      <c r="D59" s="11">
+        <v>0</v>
+      </c>
+      <c r="E59" s="12"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="I59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
+      <c r="I59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
     </row>
     <row r="60" ht="16.5" spans="1:13">
-      <c r="A60" s="12">
+      <c r="A60" s="13">
         <f t="shared" ref="A60:A89" si="2">B60*100+C60</f>
         <v>10070001</v>
       </c>
-      <c r="B60" s="12">
+      <c r="B60" s="13">
         <v>100700</v>
       </c>
-      <c r="C60" s="13">
+      <c r="C60" s="14">
         <v>1</v>
       </c>
-      <c r="D60" s="13">
-        <v>0</v>
-      </c>
-      <c r="E60" s="13" t="s">
+      <c r="D60" s="14">
+        <v>0</v>
+      </c>
+      <c r="E60" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13" t="s">
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="I60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
+      <c r="I60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
     </row>
     <row r="61" ht="16.5" spans="1:13">
-      <c r="A61" s="12">
+      <c r="A61" s="13">
         <f t="shared" si="2"/>
         <v>10070002</v>
       </c>
-      <c r="B61" s="12">
+      <c r="B61" s="13">
         <v>100700</v>
       </c>
-      <c r="C61" s="13">
+      <c r="C61" s="14">
         <v>2</v>
       </c>
-      <c r="D61" s="13">
-        <v>0</v>
-      </c>
-      <c r="E61" s="13" t="s">
+      <c r="D61" s="14">
+        <v>0</v>
+      </c>
+      <c r="E61" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13" t="s">
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="I61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
+      <c r="I61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
+      <c r="M61" s="7"/>
     </row>
     <row r="62" ht="16.5" spans="1:13">
-      <c r="A62" s="12">
+      <c r="A62" s="13">
         <f t="shared" si="2"/>
         <v>10070003</v>
       </c>
-      <c r="B62" s="12">
+      <c r="B62" s="13">
         <v>100700</v>
       </c>
-      <c r="C62" s="13">
+      <c r="C62" s="14">
         <v>3</v>
       </c>
-      <c r="D62" s="13">
-        <v>0</v>
-      </c>
-      <c r="E62" s="13" t="s">
+      <c r="D62" s="14">
+        <v>0</v>
+      </c>
+      <c r="E62" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13" t="s">
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="I62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
+      <c r="I62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+      <c r="M62" s="7"/>
     </row>
     <row r="63" ht="16.5" spans="1:13">
-      <c r="A63" s="12">
+      <c r="A63" s="13">
         <f t="shared" si="2"/>
         <v>10070004</v>
       </c>
-      <c r="B63" s="12">
+      <c r="B63" s="13">
         <v>100700</v>
       </c>
-      <c r="C63" s="13">
+      <c r="C63" s="14">
         <v>4</v>
       </c>
-      <c r="D63" s="13">
-        <v>0</v>
-      </c>
-      <c r="E63" s="13" t="s">
+      <c r="D63" s="14">
+        <v>0</v>
+      </c>
+      <c r="E63" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13" t="s">
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="I63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
+      <c r="I63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+      <c r="M63" s="7"/>
     </row>
     <row r="64" ht="16.5" spans="1:13">
-      <c r="A64" s="12">
+      <c r="A64" s="13">
         <f t="shared" si="2"/>
         <v>10070005</v>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="13">
         <v>100700</v>
       </c>
-      <c r="C64" s="13">
+      <c r="C64" s="14">
         <v>5</v>
       </c>
-      <c r="D64" s="13">
-        <v>0</v>
-      </c>
-      <c r="E64" s="13" t="s">
+      <c r="D64" s="14">
+        <v>0</v>
+      </c>
+      <c r="E64" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13" t="s">
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
+      <c r="I64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7"/>
     </row>
     <row r="65" ht="16.5" spans="1:13">
-      <c r="A65" s="12">
+      <c r="A65" s="13">
         <f t="shared" si="2"/>
         <v>10070006</v>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="13">
         <v>100700</v>
       </c>
-      <c r="C65" s="13">
+      <c r="C65" s="14">
         <v>6</v>
       </c>
-      <c r="D65" s="13">
-        <v>0</v>
-      </c>
-      <c r="E65" s="13" t="s">
+      <c r="D65" s="14">
+        <v>0</v>
+      </c>
+      <c r="E65" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13" t="s">
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
+      <c r="I65" s="7"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7"/>
+      <c r="M65" s="7"/>
     </row>
     <row r="66" ht="16.5" spans="1:13">
-      <c r="A66" s="12">
+      <c r="A66" s="13">
         <f t="shared" si="2"/>
         <v>10070007</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="13">
         <v>100700</v>
       </c>
-      <c r="C66" s="13">
+      <c r="C66" s="14">
         <v>7</v>
       </c>
-      <c r="D66" s="13">
-        <v>0</v>
-      </c>
-      <c r="E66" s="13" t="s">
+      <c r="D66" s="14">
+        <v>0</v>
+      </c>
+      <c r="E66" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13" t="s">
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="I66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
+      <c r="I66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
+      <c r="M66" s="7"/>
     </row>
     <row r="67" ht="16.5" spans="1:13">
-      <c r="A67" s="12">
+      <c r="A67" s="13">
         <f t="shared" si="2"/>
         <v>10070008</v>
       </c>
-      <c r="B67" s="12">
+      <c r="B67" s="13">
         <v>100700</v>
       </c>
-      <c r="C67" s="13">
+      <c r="C67" s="14">
         <v>8</v>
       </c>
-      <c r="D67" s="13">
-        <v>0</v>
-      </c>
-      <c r="E67" s="13" t="s">
+      <c r="D67" s="14">
+        <v>0</v>
+      </c>
+      <c r="E67" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13" t="s">
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="I67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
-      <c r="M67" s="6"/>
+      <c r="I67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
     </row>
     <row r="68" ht="16.5" spans="1:13">
-      <c r="A68" s="12">
+      <c r="A68" s="13">
         <f t="shared" si="2"/>
         <v>10070009</v>
       </c>
-      <c r="B68" s="12">
+      <c r="B68" s="13">
         <v>100700</v>
       </c>
-      <c r="C68" s="13">
+      <c r="C68" s="14">
         <v>9</v>
       </c>
-      <c r="D68" s="13">
+      <c r="D68" s="14">
         <v>1</v>
       </c>
-      <c r="E68" s="13" t="s">
+      <c r="E68" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13" t="s">
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="I68" s="6"/>
-      <c r="K68" s="6"/>
-      <c r="L68" s="6"/>
-      <c r="M68" s="6"/>
+      <c r="I68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7"/>
     </row>
     <row r="69" ht="16.5" spans="1:13">
-      <c r="A69" s="12">
+      <c r="A69" s="13">
         <f t="shared" si="2"/>
         <v>10070010</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="13">
         <v>100700</v>
       </c>
-      <c r="C69" s="13">
+      <c r="C69" s="14">
         <v>10</v>
       </c>
-      <c r="D69" s="13">
+      <c r="D69" s="14">
         <v>2</v>
       </c>
-      <c r="E69" s="13" t="s">
+      <c r="E69" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13" t="s">
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="I69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6"/>
+      <c r="I69" s="7"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
+      <c r="M69" s="7"/>
     </row>
     <row r="70" ht="16.5" spans="1:13">
-      <c r="A70" s="14">
+      <c r="A70" s="15">
         <f t="shared" si="2"/>
         <v>10070011</v>
       </c>
-      <c r="B70" s="14">
+      <c r="B70" s="15">
         <v>100700</v>
       </c>
-      <c r="C70" s="15">
+      <c r="C70" s="16">
         <v>11</v>
       </c>
-      <c r="D70" s="15">
-        <v>0</v>
-      </c>
-      <c r="E70" s="15" t="s">
+      <c r="D70" s="16">
+        <v>0</v>
+      </c>
+      <c r="E70" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="14">
         <v>9</v>
       </c>
-      <c r="G70" s="13"/>
-      <c r="H70" s="15" t="s">
+      <c r="G70" s="14"/>
+      <c r="H70" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="I70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6"/>
+      <c r="I70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
     </row>
     <row r="71" ht="16.5" spans="1:13">
-      <c r="A71" s="14">
+      <c r="A71" s="15">
         <f t="shared" si="2"/>
         <v>10070012</v>
       </c>
-      <c r="B71" s="14">
+      <c r="B71" s="15">
         <v>100700</v>
       </c>
-      <c r="C71" s="15">
+      <c r="C71" s="16">
         <v>12</v>
       </c>
-      <c r="D71" s="15">
-        <v>0</v>
-      </c>
-      <c r="E71" s="15" t="s">
+      <c r="D71" s="16">
+        <v>0</v>
+      </c>
+      <c r="E71" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="14">
         <v>9</v>
       </c>
-      <c r="G71" s="13"/>
-      <c r="H71" s="15" t="s">
+      <c r="G71" s="14"/>
+      <c r="H71" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-      <c r="M71" s="6"/>
+      <c r="I71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
+      <c r="M71" s="7"/>
     </row>
     <row r="72" ht="16.5" spans="1:13">
-      <c r="A72" s="14">
+      <c r="A72" s="15">
         <f t="shared" si="2"/>
         <v>10070013</v>
       </c>
-      <c r="B72" s="14">
+      <c r="B72" s="15">
         <v>100700</v>
       </c>
-      <c r="C72" s="15">
+      <c r="C72" s="16">
         <v>13</v>
       </c>
-      <c r="D72" s="15">
-        <v>0</v>
-      </c>
-      <c r="E72" s="15" t="s">
+      <c r="D72" s="16">
+        <v>0</v>
+      </c>
+      <c r="E72" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72" s="14">
         <v>9</v>
       </c>
-      <c r="G72" s="13"/>
-      <c r="H72" s="15" t="s">
+      <c r="G72" s="14"/>
+      <c r="H72" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="I72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
+      <c r="I72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
+      <c r="M72" s="7"/>
     </row>
     <row r="73" ht="16.5" spans="1:13">
-      <c r="A73" s="14">
+      <c r="A73" s="15">
         <f t="shared" si="2"/>
         <v>10070014</v>
       </c>
-      <c r="B73" s="14">
+      <c r="B73" s="15">
         <v>100700</v>
       </c>
-      <c r="C73" s="15">
+      <c r="C73" s="16">
         <v>14</v>
       </c>
-      <c r="D73" s="15">
-        <v>0</v>
-      </c>
-      <c r="E73" s="15" t="s">
+      <c r="D73" s="16">
+        <v>0</v>
+      </c>
+      <c r="E73" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F73" s="13">
+      <c r="F73" s="14">
         <v>9</v>
       </c>
-      <c r="G73" s="13"/>
-      <c r="H73" s="15" t="s">
+      <c r="G73" s="14"/>
+      <c r="H73" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="I73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6"/>
+      <c r="I73" s="7"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
+      <c r="M73" s="7"/>
     </row>
     <row r="74" ht="16.5" spans="1:13">
-      <c r="A74" s="14">
+      <c r="A74" s="15">
         <f t="shared" si="2"/>
         <v>10070015</v>
       </c>
-      <c r="B74" s="14">
+      <c r="B74" s="15">
         <v>100700</v>
       </c>
-      <c r="C74" s="15">
+      <c r="C74" s="16">
         <v>15</v>
       </c>
-      <c r="D74" s="15">
-        <v>0</v>
-      </c>
-      <c r="E74" s="15" t="s">
+      <c r="D74" s="16">
+        <v>0</v>
+      </c>
+      <c r="E74" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="F74" s="13">
+      <c r="F74" s="14">
         <v>9</v>
       </c>
-      <c r="G74" s="13"/>
-      <c r="H74" s="15" t="s">
+      <c r="G74" s="14"/>
+      <c r="H74" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="I74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="M74" s="6"/>
+      <c r="I74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
+      <c r="M74" s="7"/>
     </row>
     <row r="75" ht="16.5" spans="1:13">
-      <c r="A75" s="14">
+      <c r="A75" s="15">
         <f t="shared" si="2"/>
         <v>10070016</v>
       </c>
-      <c r="B75" s="14">
+      <c r="B75" s="15">
         <v>100700</v>
       </c>
-      <c r="C75" s="15">
+      <c r="C75" s="16">
         <v>16</v>
       </c>
-      <c r="D75" s="15">
-        <v>0</v>
-      </c>
-      <c r="E75" s="15" t="s">
+      <c r="D75" s="16">
+        <v>0</v>
+      </c>
+      <c r="E75" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F75" s="13">
+      <c r="F75" s="14">
         <v>9</v>
       </c>
-      <c r="G75" s="13"/>
-      <c r="H75" s="15" t="s">
+      <c r="G75" s="14"/>
+      <c r="H75" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="I75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
+      <c r="I75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+      <c r="M75" s="7"/>
     </row>
     <row r="76" ht="16.5" spans="1:13">
-      <c r="A76" s="14">
+      <c r="A76" s="15">
         <f t="shared" si="2"/>
         <v>10070017</v>
       </c>
-      <c r="B76" s="14">
+      <c r="B76" s="15">
         <v>100700</v>
       </c>
-      <c r="C76" s="15">
+      <c r="C76" s="16">
         <v>17</v>
       </c>
-      <c r="D76" s="15">
-        <v>0</v>
-      </c>
-      <c r="E76" s="15" t="s">
+      <c r="D76" s="16">
+        <v>0</v>
+      </c>
+      <c r="E76" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="F76" s="13">
+      <c r="F76" s="14">
         <v>9</v>
       </c>
-      <c r="G76" s="13"/>
-      <c r="H76" s="15" t="s">
+      <c r="G76" s="14"/>
+      <c r="H76" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="I76" s="6"/>
-      <c r="K76" s="6"/>
-      <c r="L76" s="6"/>
-      <c r="M76" s="6"/>
+      <c r="I76" s="7"/>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
+      <c r="M76" s="7"/>
     </row>
     <row r="77" ht="16.5" spans="1:13">
-      <c r="A77" s="14">
+      <c r="A77" s="15">
         <f t="shared" si="2"/>
         <v>10070018</v>
       </c>
-      <c r="B77" s="14">
+      <c r="B77" s="15">
         <v>100700</v>
       </c>
-      <c r="C77" s="15">
+      <c r="C77" s="16">
         <v>18</v>
       </c>
-      <c r="D77" s="15">
-        <v>0</v>
-      </c>
-      <c r="E77" s="15" t="s">
+      <c r="D77" s="16">
+        <v>0</v>
+      </c>
+      <c r="E77" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F77" s="13">
+      <c r="F77" s="14">
         <v>9</v>
       </c>
-      <c r="G77" s="13"/>
-      <c r="H77" s="15" t="s">
+      <c r="G77" s="14"/>
+      <c r="H77" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I77" s="6"/>
-      <c r="K77" s="6"/>
-      <c r="L77" s="6"/>
-      <c r="M77" s="6"/>
+      <c r="I77" s="7"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+      <c r="M77" s="7"/>
     </row>
     <row r="78" ht="16.5" spans="1:13">
-      <c r="A78" s="9">
+      <c r="A78" s="10">
         <f t="shared" si="2"/>
         <v>10120001</v>
       </c>
-      <c r="B78" s="9">
+      <c r="B78" s="10">
         <v>101200</v>
       </c>
-      <c r="C78" s="10">
+      <c r="C78" s="11">
         <v>1</v>
       </c>
-      <c r="D78" s="10">
-        <v>0</v>
-      </c>
-      <c r="E78" s="11" t="s">
+      <c r="D78" s="11">
+        <v>0</v>
+      </c>
+      <c r="E78" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="10" t="s">
+      <c r="F78" s="10"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="I78" s="6"/>
-      <c r="K78" s="6"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="6"/>
+      <c r="I78" s="7"/>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
+      <c r="M78" s="7"/>
     </row>
     <row r="79" ht="16.5" spans="1:13">
-      <c r="A79" s="9">
+      <c r="A79" s="10">
         <f t="shared" si="2"/>
         <v>10120002</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="10">
         <v>101200</v>
       </c>
-      <c r="C79" s="10">
+      <c r="C79" s="11">
         <v>2</v>
       </c>
-      <c r="D79" s="10">
-        <v>0</v>
-      </c>
-      <c r="E79" s="11" t="s">
+      <c r="D79" s="11">
+        <v>0</v>
+      </c>
+      <c r="E79" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="10" t="s">
+      <c r="F79" s="10"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="I79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="6"/>
+      <c r="I79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+      <c r="M79" s="7"/>
     </row>
     <row r="80" ht="16.5" spans="1:13">
-      <c r="A80" s="9">
+      <c r="A80" s="10">
         <f t="shared" si="2"/>
         <v>10120003</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="10">
         <v>101200</v>
       </c>
-      <c r="C80" s="10">
+      <c r="C80" s="11">
         <v>3</v>
       </c>
-      <c r="D80" s="10">
-        <v>0</v>
-      </c>
-      <c r="E80" s="11" t="s">
+      <c r="D80" s="11">
+        <v>0</v>
+      </c>
+      <c r="E80" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="10" t="s">
+      <c r="F80" s="10"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="I80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-      <c r="M80" s="6"/>
+      <c r="I80" s="7"/>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
+      <c r="M80" s="7"/>
     </row>
     <row r="81" ht="16.5" spans="1:13">
-      <c r="A81" s="9">
+      <c r="A81" s="10">
         <f t="shared" si="2"/>
         <v>10120004</v>
       </c>
-      <c r="B81" s="9">
+      <c r="B81" s="10">
         <v>101200</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C81" s="11">
         <v>4</v>
       </c>
-      <c r="D81" s="10">
-        <v>0</v>
-      </c>
-      <c r="E81" s="11" t="s">
+      <c r="D81" s="11">
+        <v>0</v>
+      </c>
+      <c r="E81" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="10" t="s">
+      <c r="F81" s="10"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="I81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-      <c r="M81" s="6"/>
+      <c r="I81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7"/>
     </row>
     <row r="82" ht="16.5" spans="1:13">
-      <c r="A82" s="9">
+      <c r="A82" s="10">
         <f t="shared" si="2"/>
         <v>10120005</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="10">
         <v>101200</v>
       </c>
-      <c r="C82" s="10">
+      <c r="C82" s="11">
         <v>5</v>
       </c>
-      <c r="D82" s="10">
-        <v>0</v>
-      </c>
-      <c r="E82" s="11" t="s">
+      <c r="D82" s="11">
+        <v>0</v>
+      </c>
+      <c r="E82" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="10" t="s">
+      <c r="F82" s="10"/>
+      <c r="G82" s="10"/>
+      <c r="H82" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="I82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-      <c r="M82" s="6"/>
+      <c r="I82" s="7"/>
+      <c r="K82" s="7"/>
+      <c r="L82" s="7"/>
+      <c r="M82" s="7"/>
     </row>
     <row r="83" ht="16.5" spans="1:13">
-      <c r="A83" s="9">
+      <c r="A83" s="10">
         <f t="shared" si="2"/>
         <v>10120006</v>
       </c>
-      <c r="B83" s="9">
+      <c r="B83" s="10">
         <v>101200</v>
       </c>
-      <c r="C83" s="10">
+      <c r="C83" s="11">
         <v>6</v>
       </c>
-      <c r="D83" s="10">
-        <v>0</v>
-      </c>
-      <c r="E83" s="11" t="s">
+      <c r="D83" s="11">
+        <v>0</v>
+      </c>
+      <c r="E83" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="10" t="s">
+      <c r="F83" s="10"/>
+      <c r="G83" s="10"/>
+      <c r="H83" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="I83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-      <c r="M83" s="6"/>
+      <c r="I83" s="7"/>
+      <c r="K83" s="7"/>
+      <c r="L83" s="7"/>
+      <c r="M83" s="7"/>
     </row>
     <row r="84" ht="16.5" spans="1:13">
-      <c r="A84" s="9">
+      <c r="A84" s="10">
         <f t="shared" ref="A84:A103" si="3">B84*100+C84</f>
         <v>10120009</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="10">
         <v>101200</v>
       </c>
-      <c r="C84" s="10">
+      <c r="C84" s="11">
         <v>9</v>
       </c>
-      <c r="D84" s="10">
+      <c r="D84" s="11">
         <v>2</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="10" t="s">
+      <c r="F84" s="10"/>
+      <c r="G84" s="10"/>
+      <c r="H84" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="I84" s="6"/>
-      <c r="K84" s="6"/>
-      <c r="L84" s="6"/>
-      <c r="M84" s="6"/>
+      <c r="I84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="7"/>
+      <c r="M84" s="7"/>
     </row>
     <row r="85" ht="16.5" spans="1:13">
-      <c r="A85" s="9">
+      <c r="A85" s="10">
         <f t="shared" si="3"/>
         <v>10120010</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="10">
         <v>101200</v>
       </c>
-      <c r="C85" s="10">
+      <c r="C85" s="11">
         <v>10</v>
       </c>
-      <c r="D85" s="10">
+      <c r="D85" s="11">
         <v>1</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="10" t="s">
+      <c r="F85" s="10"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="I85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-      <c r="M85" s="6"/>
+      <c r="I85" s="7"/>
+      <c r="K85" s="7"/>
+      <c r="L85" s="7"/>
+      <c r="M85" s="7"/>
     </row>
     <row r="86" ht="16.5" spans="1:13">
-      <c r="A86" s="9">
+      <c r="A86" s="10">
         <f t="shared" si="3"/>
         <v>10120011</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="10">
         <v>101200</v>
       </c>
-      <c r="C86" s="10">
+      <c r="C86" s="11">
         <v>11</v>
       </c>
-      <c r="D86" s="10">
+      <c r="D86" s="11">
         <v>2</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="10" t="s">
+      <c r="F86" s="10"/>
+      <c r="G86" s="10"/>
+      <c r="H86" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="I86" s="6"/>
-      <c r="K86" s="6"/>
-      <c r="L86" s="6"/>
-      <c r="M86" s="6"/>
+      <c r="I86" s="7"/>
+      <c r="K86" s="7"/>
+      <c r="L86" s="7"/>
+      <c r="M86" s="7"/>
     </row>
     <row r="87" ht="16.5" spans="1:13">
-      <c r="A87" s="9">
+      <c r="A87" s="10">
         <f t="shared" si="3"/>
         <v>10120012</v>
       </c>
-      <c r="B87" s="9">
+      <c r="B87" s="10">
         <v>101200</v>
       </c>
-      <c r="C87" s="10">
+      <c r="C87" s="11">
         <v>12</v>
       </c>
-      <c r="D87" s="10">
+      <c r="D87" s="11">
         <v>2</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="10" t="s">
+      <c r="F87" s="10"/>
+      <c r="G87" s="10"/>
+      <c r="H87" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="I87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
-      <c r="M87" s="6"/>
+      <c r="I87" s="7"/>
+      <c r="K87" s="7"/>
+      <c r="L87" s="7"/>
+      <c r="M87" s="7"/>
     </row>
     <row r="88" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A88" s="9">
+      <c r="A88" s="10">
         <f t="shared" si="3"/>
         <v>10120013</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="10">
         <v>101200</v>
       </c>
-      <c r="C88" s="10">
+      <c r="C88" s="11">
         <v>13</v>
       </c>
-      <c r="D88" s="10">
+      <c r="D88" s="11">
         <v>2</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="10" t="s">
+      <c r="F88" s="10"/>
+      <c r="G88" s="10"/>
+      <c r="H88" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="I88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
-      <c r="M88" s="6"/>
+      <c r="I88" s="7"/>
+      <c r="K88" s="7"/>
+      <c r="L88" s="7"/>
+      <c r="M88" s="7"/>
     </row>
     <row r="89" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A89" s="9">
+      <c r="A89" s="10">
         <f t="shared" si="3"/>
         <v>10120014</v>
       </c>
-      <c r="B89" s="9">
+      <c r="B89" s="10">
         <v>101200</v>
       </c>
-      <c r="C89" s="10">
+      <c r="C89" s="11">
         <v>14</v>
       </c>
-      <c r="D89" s="10">
+      <c r="D89" s="11">
         <v>2</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="10" t="s">
+      <c r="F89" s="10"/>
+      <c r="G89" s="10"/>
+      <c r="H89" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="I89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
-      <c r="M89" s="6"/>
+      <c r="I89" s="7"/>
+      <c r="K89" s="7"/>
+      <c r="L89" s="7"/>
+      <c r="M89" s="7"/>
     </row>
     <row r="90" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A90" s="9">
+      <c r="A90" s="10">
         <f t="shared" si="3"/>
         <v>10120015</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="10">
         <v>101200</v>
       </c>
-      <c r="C90" s="10">
+      <c r="C90" s="11">
         <v>15</v>
       </c>
-      <c r="D90" s="10">
+      <c r="D90" s="11">
         <v>2</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="10" t="s">
+      <c r="F90" s="10"/>
+      <c r="G90" s="10"/>
+      <c r="H90" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="I90" s="6"/>
-      <c r="K90" s="6"/>
-      <c r="L90" s="6"/>
-      <c r="M90" s="6"/>
+      <c r="I90" s="7"/>
+      <c r="K90" s="7"/>
+      <c r="L90" s="7"/>
+      <c r="M90" s="7"/>
     </row>
     <row r="91" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A91" s="9">
+      <c r="A91" s="10">
         <f t="shared" si="3"/>
         <v>10120016</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91" s="10">
         <v>101200</v>
       </c>
-      <c r="C91" s="10">
+      <c r="C91" s="11">
         <v>16</v>
       </c>
-      <c r="D91" s="10">
+      <c r="D91" s="11">
         <v>2</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="10" t="s">
+      <c r="F91" s="10"/>
+      <c r="G91" s="10"/>
+      <c r="H91" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="I91" s="6"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="6"/>
-      <c r="M91" s="6"/>
+      <c r="I91" s="7"/>
+      <c r="K91" s="7"/>
+      <c r="L91" s="7"/>
+      <c r="M91" s="7"/>
     </row>
     <row r="92" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A92" s="9">
+      <c r="A92" s="10">
         <f t="shared" si="3"/>
         <v>10120021</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="10">
         <v>101200</v>
       </c>
-      <c r="C92" s="10">
+      <c r="C92" s="11">
         <v>21</v>
       </c>
-      <c r="D92" s="10">
+      <c r="D92" s="11">
         <v>2</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="10" t="s">
+      <c r="F92" s="10"/>
+      <c r="G92" s="10"/>
+      <c r="H92" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="I92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
-      <c r="M92" s="6"/>
+      <c r="I92" s="7"/>
+      <c r="K92" s="7"/>
+      <c r="L92" s="7"/>
+      <c r="M92" s="7"/>
     </row>
     <row r="93" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A93" s="9">
+      <c r="A93" s="10">
         <f t="shared" si="3"/>
         <v>10120022</v>
       </c>
-      <c r="B93" s="9">
+      <c r="B93" s="10">
         <v>101200</v>
       </c>
-      <c r="C93" s="10">
+      <c r="C93" s="11">
         <v>22</v>
       </c>
-      <c r="D93" s="10">
+      <c r="D93" s="11">
         <v>2</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="10" t="s">
+      <c r="F93" s="10"/>
+      <c r="G93" s="10"/>
+      <c r="H93" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="I93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
-      <c r="M93" s="6"/>
+      <c r="I93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
+      <c r="M93" s="7"/>
     </row>
     <row r="94" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A94" s="9">
+      <c r="A94" s="10">
         <f t="shared" si="3"/>
         <v>10120023</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="10">
         <v>101200</v>
       </c>
-      <c r="C94" s="10">
+      <c r="C94" s="11">
         <v>23</v>
       </c>
-      <c r="D94" s="10">
+      <c r="D94" s="11">
         <v>2</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="10" t="s">
+      <c r="F94" s="10"/>
+      <c r="G94" s="10"/>
+      <c r="H94" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="I94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="6"/>
+      <c r="I94" s="7"/>
+      <c r="K94" s="7"/>
+      <c r="L94" s="7"/>
+      <c r="M94" s="7"/>
     </row>
     <row r="95" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A95" s="9">
+      <c r="A95" s="10">
         <f t="shared" si="3"/>
         <v>10120024</v>
       </c>
-      <c r="B95" s="9">
+      <c r="B95" s="10">
         <v>101200</v>
       </c>
-      <c r="C95" s="10">
+      <c r="C95" s="11">
         <v>24</v>
       </c>
-      <c r="D95" s="10">
+      <c r="D95" s="11">
         <v>2</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
-      <c r="H95" s="10" t="s">
+      <c r="F95" s="10"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="I95" s="6"/>
-      <c r="K95" s="6"/>
-      <c r="L95" s="6"/>
-      <c r="M95" s="6"/>
+      <c r="I95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
+      <c r="M95" s="7"/>
     </row>
     <row r="96" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A96" s="9">
+      <c r="A96" s="10">
         <f t="shared" si="3"/>
         <v>10120025</v>
       </c>
-      <c r="B96" s="9">
+      <c r="B96" s="10">
         <v>101200</v>
       </c>
-      <c r="C96" s="10">
+      <c r="C96" s="11">
         <v>25</v>
       </c>
-      <c r="D96" s="10">
+      <c r="D96" s="11">
         <v>2</v>
       </c>
-      <c r="E96" s="11" t="s">
+      <c r="E96" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
-      <c r="H96" s="10" t="s">
+      <c r="F96" s="10"/>
+      <c r="G96" s="10"/>
+      <c r="H96" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="I96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
-      <c r="M96" s="6"/>
+      <c r="I96" s="7"/>
+      <c r="K96" s="7"/>
+      <c r="L96" s="7"/>
+      <c r="M96" s="7"/>
     </row>
     <row r="97" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A97" s="9">
+      <c r="A97" s="10">
         <f t="shared" si="3"/>
         <v>10120026</v>
       </c>
-      <c r="B97" s="9">
+      <c r="B97" s="10">
         <v>101200</v>
       </c>
-      <c r="C97" s="10">
+      <c r="C97" s="11">
         <v>26</v>
       </c>
-      <c r="D97" s="10">
+      <c r="D97" s="11">
         <v>2</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="E97" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F97" s="9"/>
-      <c r="G97" s="9"/>
-      <c r="H97" s="10" t="s">
+      <c r="F97" s="10"/>
+      <c r="G97" s="10"/>
+      <c r="H97" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="I97" s="6"/>
-      <c r="K97" s="6"/>
-      <c r="L97" s="6"/>
-      <c r="M97" s="6"/>
+      <c r="I97" s="7"/>
+      <c r="K97" s="7"/>
+      <c r="L97" s="7"/>
+      <c r="M97" s="7"/>
     </row>
     <row r="98" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A98" s="9">
+      <c r="A98" s="10">
         <f t="shared" si="3"/>
         <v>10120031</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="10">
         <v>101200</v>
       </c>
-      <c r="C98" s="10">
+      <c r="C98" s="11">
         <v>31</v>
       </c>
-      <c r="D98" s="10">
+      <c r="D98" s="11">
         <v>2</v>
       </c>
-      <c r="E98" s="11" t="s">
+      <c r="E98" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="10" t="s">
+      <c r="F98" s="10"/>
+      <c r="G98" s="10"/>
+      <c r="H98" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="I98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
-      <c r="M98" s="6"/>
+      <c r="I98" s="7"/>
+      <c r="K98" s="7"/>
+      <c r="L98" s="7"/>
+      <c r="M98" s="7"/>
     </row>
     <row r="99" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A99" s="9">
+      <c r="A99" s="10">
         <f t="shared" si="3"/>
         <v>10120032</v>
       </c>
-      <c r="B99" s="9">
+      <c r="B99" s="10">
         <v>101200</v>
       </c>
-      <c r="C99" s="10">
+      <c r="C99" s="11">
         <v>32</v>
       </c>
-      <c r="D99" s="10">
+      <c r="D99" s="11">
         <v>2</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="10" t="s">
+      <c r="F99" s="10"/>
+      <c r="G99" s="10"/>
+      <c r="H99" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="I99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="6"/>
+      <c r="I99" s="7"/>
+      <c r="K99" s="7"/>
+      <c r="L99" s="7"/>
+      <c r="M99" s="7"/>
     </row>
     <row r="100" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A100" s="9">
+      <c r="A100" s="10">
         <f t="shared" si="3"/>
         <v>10120033</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="10">
         <v>101200</v>
       </c>
-      <c r="C100" s="10">
+      <c r="C100" s="11">
         <v>33</v>
       </c>
-      <c r="D100" s="10">
+      <c r="D100" s="11">
         <v>2</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="E100" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="10" t="s">
+      <c r="F100" s="10"/>
+      <c r="G100" s="10"/>
+      <c r="H100" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="I100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="6"/>
+      <c r="I100" s="7"/>
+      <c r="K100" s="7"/>
+      <c r="L100" s="7"/>
+      <c r="M100" s="7"/>
     </row>
     <row r="101" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A101" s="9">
+      <c r="A101" s="10">
         <f t="shared" si="3"/>
         <v>10120034</v>
       </c>
-      <c r="B101" s="9">
+      <c r="B101" s="10">
         <v>101200</v>
       </c>
-      <c r="C101" s="10">
+      <c r="C101" s="11">
         <v>34</v>
       </c>
-      <c r="D101" s="10">
+      <c r="D101" s="11">
         <v>2</v>
       </c>
-      <c r="E101" s="11" t="s">
+      <c r="E101" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F101" s="9"/>
-      <c r="G101" s="9"/>
-      <c r="H101" s="10" t="s">
+      <c r="F101" s="10"/>
+      <c r="G101" s="10"/>
+      <c r="H101" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="I101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="6"/>
+      <c r="I101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="7"/>
+      <c r="M101" s="7"/>
     </row>
     <row r="102" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A102" s="9">
+      <c r="A102" s="10">
         <f t="shared" si="3"/>
         <v>10120035</v>
       </c>
-      <c r="B102" s="9">
+      <c r="B102" s="10">
         <v>101200</v>
       </c>
-      <c r="C102" s="10">
+      <c r="C102" s="11">
         <v>35</v>
       </c>
-      <c r="D102" s="10">
+      <c r="D102" s="11">
         <v>2</v>
       </c>
-      <c r="E102" s="11" t="s">
+      <c r="E102" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F102" s="9"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="10" t="s">
+      <c r="F102" s="10"/>
+      <c r="G102" s="10"/>
+      <c r="H102" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="I102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-      <c r="M102" s="6"/>
+      <c r="I102" s="7"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="7"/>
+      <c r="M102" s="7"/>
     </row>
     <row r="103" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A103" s="9">
+      <c r="A103" s="10">
         <f t="shared" si="3"/>
         <v>10120036</v>
       </c>
-      <c r="B103" s="9">
+      <c r="B103" s="10">
         <v>101200</v>
       </c>
-      <c r="C103" s="10">
+      <c r="C103" s="11">
         <v>36</v>
       </c>
-      <c r="D103" s="10">
+      <c r="D103" s="11">
         <v>2</v>
       </c>
-      <c r="E103" s="11" t="s">
+      <c r="E103" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F103" s="9"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="10" t="s">
+      <c r="F103" s="10"/>
+      <c r="G103" s="10"/>
+      <c r="H103" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="I103" s="6"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="6"/>
-      <c r="M103" s="6"/>
+      <c r="I103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="7"/>
+      <c r="M103" s="7"/>
     </row>
     <row r="104" ht="16.5" spans="1:13">
-      <c r="A104" s="16">
+      <c r="A104" s="17">
         <f t="shared" ref="A104:A140" si="4">B104*100+C104</f>
         <v>10140001</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B104" s="17">
         <v>101400</v>
       </c>
-      <c r="C104" s="17">
+      <c r="C104" s="18">
         <v>1</v>
       </c>
-      <c r="D104" s="17">
-        <v>0</v>
-      </c>
-      <c r="E104" s="17" t="s">
+      <c r="D104" s="18">
+        <v>0</v>
+      </c>
+      <c r="E104" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="F104" s="17"/>
-      <c r="G104" s="17"/>
-      <c r="H104" s="17" t="s">
+      <c r="F104" s="18"/>
+      <c r="G104" s="18"/>
+      <c r="H104" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="I104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
-      <c r="M104" s="6"/>
+      <c r="I104" s="7"/>
+      <c r="K104" s="7"/>
+      <c r="L104" s="7"/>
+      <c r="M104" s="7"/>
     </row>
     <row r="105" ht="16.5" spans="1:13">
-      <c r="A105" s="16">
+      <c r="A105" s="17">
         <f t="shared" si="4"/>
         <v>10140002</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B105" s="17">
         <v>101400</v>
       </c>
-      <c r="C105" s="17">
+      <c r="C105" s="18">
         <v>2</v>
       </c>
-      <c r="D105" s="17">
-        <v>0</v>
-      </c>
-      <c r="E105" s="17" t="s">
+      <c r="D105" s="18">
+        <v>0</v>
+      </c>
+      <c r="E105" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="F105" s="17"/>
-      <c r="G105" s="17"/>
-      <c r="H105" s="17">
+      <c r="F105" s="18"/>
+      <c r="G105" s="18"/>
+      <c r="H105" s="18">
         <v>9</v>
       </c>
-      <c r="I105" s="6"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
-      <c r="M105" s="6"/>
+      <c r="I105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="7"/>
+      <c r="M105" s="7"/>
     </row>
     <row r="106" ht="16.5" spans="1:13">
-      <c r="A106" s="16">
+      <c r="A106" s="17">
         <f t="shared" si="4"/>
         <v>10140003</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B106" s="17">
         <v>101400</v>
       </c>
-      <c r="C106" s="17">
+      <c r="C106" s="18">
         <v>3</v>
       </c>
-      <c r="D106" s="17">
-        <v>0</v>
-      </c>
-      <c r="E106" s="17" t="s">
+      <c r="D106" s="18">
+        <v>0</v>
+      </c>
+      <c r="E106" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="F106" s="17"/>
-      <c r="G106" s="17"/>
-      <c r="H106" s="17">
+      <c r="F106" s="18"/>
+      <c r="G106" s="18"/>
+      <c r="H106" s="18">
         <v>10</v>
       </c>
-      <c r="I106" s="6"/>
-      <c r="K106" s="6"/>
-      <c r="L106" s="6"/>
-      <c r="M106" s="6"/>
+      <c r="I106" s="7"/>
+      <c r="K106" s="7"/>
+      <c r="L106" s="7"/>
+      <c r="M106" s="7"/>
     </row>
     <row r="107" ht="16.5" spans="1:13">
-      <c r="A107" s="16">
+      <c r="A107" s="17">
         <f t="shared" si="4"/>
         <v>10140004</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B107" s="17">
         <v>101400</v>
       </c>
-      <c r="C107" s="17">
+      <c r="C107" s="18">
         <v>4</v>
       </c>
-      <c r="D107" s="17">
-        <v>0</v>
-      </c>
-      <c r="E107" s="17" t="s">
+      <c r="D107" s="18">
+        <v>0</v>
+      </c>
+      <c r="E107" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F107" s="17"/>
-      <c r="G107" s="17"/>
-      <c r="H107" s="17" t="s">
+      <c r="F107" s="18"/>
+      <c r="G107" s="18"/>
+      <c r="H107" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
-      <c r="M107" s="6"/>
+      <c r="I107" s="7"/>
+      <c r="K107" s="7"/>
+      <c r="L107" s="7"/>
+      <c r="M107" s="7"/>
     </row>
     <row r="108" ht="16.5" spans="1:13">
-      <c r="A108" s="16">
+      <c r="A108" s="17">
         <f t="shared" si="4"/>
         <v>10140005</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B108" s="17">
         <v>101400</v>
       </c>
-      <c r="C108" s="17">
+      <c r="C108" s="18">
         <v>5</v>
       </c>
-      <c r="D108" s="17">
-        <v>0</v>
-      </c>
-      <c r="E108" s="17" t="s">
+      <c r="D108" s="18">
+        <v>0</v>
+      </c>
+      <c r="E108" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="F108" s="17"/>
-      <c r="G108" s="17"/>
-      <c r="H108" s="17" t="s">
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
+      <c r="H108" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="I108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="6"/>
+      <c r="I108" s="7"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7"/>
+      <c r="M108" s="7"/>
     </row>
     <row r="109" ht="16.5" spans="1:13">
-      <c r="A109" s="16">
+      <c r="A109" s="17">
         <f t="shared" si="4"/>
         <v>10140006</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B109" s="17">
         <v>101400</v>
       </c>
-      <c r="C109" s="17">
+      <c r="C109" s="18">
         <v>6</v>
       </c>
-      <c r="D109" s="17">
-        <v>0</v>
-      </c>
-      <c r="E109" s="17" t="s">
+      <c r="D109" s="18">
+        <v>0</v>
+      </c>
+      <c r="E109" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F109" s="17"/>
-      <c r="G109" s="17"/>
-      <c r="H109" s="17" t="s">
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
+      <c r="H109" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="I109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
-      <c r="M109" s="6"/>
+      <c r="I109" s="7"/>
+      <c r="K109" s="7"/>
+      <c r="L109" s="7"/>
+      <c r="M109" s="7"/>
     </row>
     <row r="110" ht="16.5" spans="1:13">
-      <c r="A110" s="16">
+      <c r="A110" s="17">
         <f t="shared" si="4"/>
         <v>10140007</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B110" s="17">
         <v>101400</v>
       </c>
-      <c r="C110" s="17">
+      <c r="C110" s="18">
         <v>7</v>
       </c>
-      <c r="D110" s="17">
-        <v>0</v>
-      </c>
-      <c r="E110" s="17" t="s">
+      <c r="D110" s="18">
+        <v>0</v>
+      </c>
+      <c r="E110" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="F110" s="17"/>
-      <c r="G110" s="17"/>
-      <c r="H110" s="17" t="s">
+      <c r="F110" s="18"/>
+      <c r="G110" s="18"/>
+      <c r="H110" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
-      <c r="M110" s="6"/>
+      <c r="I110" s="7"/>
+      <c r="K110" s="7"/>
+      <c r="L110" s="7"/>
+      <c r="M110" s="7"/>
     </row>
     <row r="111" ht="16.5" spans="1:13">
-      <c r="A111" s="16">
+      <c r="A111" s="17">
         <f t="shared" si="4"/>
         <v>10140008</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B111" s="17">
         <v>101400</v>
       </c>
-      <c r="C111" s="17">
+      <c r="C111" s="18">
         <v>8</v>
       </c>
-      <c r="D111" s="17">
-        <v>0</v>
-      </c>
-      <c r="E111" s="17" t="s">
+      <c r="D111" s="18">
+        <v>0</v>
+      </c>
+      <c r="E111" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="F111" s="17"/>
-      <c r="G111" s="17"/>
-      <c r="H111" s="17" t="s">
+      <c r="F111" s="18"/>
+      <c r="G111" s="18"/>
+      <c r="H111" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="I111" s="6"/>
-      <c r="K111" s="6"/>
-      <c r="L111" s="6"/>
-      <c r="M111" s="6"/>
+      <c r="I111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="7"/>
+      <c r="M111" s="7"/>
     </row>
     <row r="112" ht="16.5" spans="1:13">
-      <c r="A112" s="16">
+      <c r="A112" s="17">
         <f t="shared" si="4"/>
         <v>10140009</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B112" s="17">
         <v>101400</v>
       </c>
-      <c r="C112" s="17">
+      <c r="C112" s="18">
         <v>9</v>
       </c>
-      <c r="D112" s="17">
-        <v>0</v>
-      </c>
-      <c r="E112" s="17" t="s">
+      <c r="D112" s="18">
+        <v>0</v>
+      </c>
+      <c r="E112" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="F112" s="17"/>
-      <c r="G112" s="17"/>
-      <c r="H112" s="17" t="s">
+      <c r="F112" s="18"/>
+      <c r="G112" s="18"/>
+      <c r="H112" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="I112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
-      <c r="M112" s="6"/>
+      <c r="I112" s="7"/>
+      <c r="K112" s="7"/>
+      <c r="L112" s="7"/>
+      <c r="M112" s="7"/>
     </row>
     <row r="113" ht="16.5" spans="1:13">
-      <c r="A113" s="16">
+      <c r="A113" s="17">
         <f t="shared" si="4"/>
         <v>10140010</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B113" s="17">
         <v>101400</v>
       </c>
-      <c r="C113" s="17">
+      <c r="C113" s="18">
         <v>10</v>
       </c>
-      <c r="D113" s="17">
-        <v>0</v>
-      </c>
-      <c r="E113" s="17" t="s">
+      <c r="D113" s="18">
+        <v>0</v>
+      </c>
+      <c r="E113" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="F113" s="17"/>
-      <c r="G113" s="17"/>
-      <c r="H113" s="17" t="s">
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="I113" s="6"/>
-      <c r="K113" s="6"/>
-      <c r="L113" s="6"/>
-      <c r="M113" s="6"/>
+      <c r="I113" s="7"/>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7"/>
+      <c r="M113" s="7"/>
     </row>
     <row r="114" ht="16.5" spans="1:13">
-      <c r="A114" s="16">
+      <c r="A114" s="17">
         <f t="shared" si="4"/>
         <v>10140011</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B114" s="17">
         <v>101400</v>
       </c>
-      <c r="C114" s="17">
+      <c r="C114" s="18">
         <v>11</v>
       </c>
-      <c r="D114" s="17">
-        <v>0</v>
-      </c>
-      <c r="E114" s="17" t="s">
+      <c r="D114" s="18">
+        <v>0</v>
+      </c>
+      <c r="E114" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="F114" s="17"/>
-      <c r="G114" s="17"/>
-      <c r="H114" s="17" t="s">
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="I114" s="6"/>
-      <c r="K114" s="6"/>
-      <c r="L114" s="6"/>
-      <c r="M114" s="6"/>
+      <c r="I114" s="7"/>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7"/>
+      <c r="M114" s="7"/>
     </row>
     <row r="115" ht="16.5" spans="1:13">
-      <c r="A115" s="16">
+      <c r="A115" s="17">
         <f t="shared" si="4"/>
         <v>10140012</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="17">
         <v>101400</v>
       </c>
-      <c r="C115" s="17">
+      <c r="C115" s="18">
         <v>12</v>
       </c>
-      <c r="D115" s="17">
+      <c r="D115" s="18">
         <v>1</v>
       </c>
-      <c r="E115" s="17" t="s">
+      <c r="E115" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F115" s="17"/>
-      <c r="G115" s="17"/>
-      <c r="H115" s="17" t="s">
+      <c r="F115" s="18"/>
+      <c r="G115" s="18"/>
+      <c r="H115" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="I115" s="6"/>
-      <c r="K115" s="6"/>
-      <c r="L115" s="6"/>
-      <c r="M115" s="6"/>
+      <c r="I115" s="7"/>
+      <c r="K115" s="7"/>
+      <c r="L115" s="7"/>
+      <c r="M115" s="7"/>
     </row>
     <row r="116" ht="16.5" spans="1:13">
-      <c r="A116" s="16">
+      <c r="A116" s="17">
         <f t="shared" si="4"/>
         <v>10140013</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B116" s="17">
         <v>101400</v>
       </c>
-      <c r="C116" s="17">
+      <c r="C116" s="18">
         <v>13</v>
       </c>
-      <c r="D116" s="17">
+      <c r="D116" s="18">
         <v>2</v>
       </c>
-      <c r="E116" s="17" t="s">
+      <c r="E116" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="F116" s="17"/>
-      <c r="G116" s="17"/>
-      <c r="H116" s="17" t="s">
+      <c r="F116" s="18"/>
+      <c r="G116" s="18"/>
+      <c r="H116" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="I116" s="6"/>
-      <c r="K116" s="6"/>
-      <c r="L116" s="6"/>
-      <c r="M116" s="6"/>
+      <c r="I116" s="7"/>
+      <c r="K116" s="7"/>
+      <c r="L116" s="7"/>
+      <c r="M116" s="7"/>
     </row>
     <row r="117" ht="16.5" spans="1:13">
-      <c r="A117" s="4">
+      <c r="A117" s="5">
         <f t="shared" si="4"/>
         <v>10240001</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="5">
         <v>102400</v>
       </c>
-      <c r="C117" s="5">
+      <c r="C117" s="6">
         <v>1</v>
       </c>
-      <c r="D117" s="5">
-        <v>0</v>
-      </c>
-      <c r="E117" s="5" t="s">
+      <c r="D117" s="6">
+        <v>0</v>
+      </c>
+      <c r="E117" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5">
+      <c r="F117" s="6"/>
+      <c r="G117" s="6"/>
+      <c r="H117" s="6">
         <v>9</v>
       </c>
-      <c r="I117" s="6"/>
-      <c r="K117" s="6"/>
-      <c r="L117" s="6"/>
-      <c r="M117" s="6"/>
+      <c r="I117" s="7"/>
+      <c r="K117" s="7"/>
+      <c r="L117" s="7"/>
+      <c r="M117" s="7"/>
     </row>
     <row r="118" ht="16.5" spans="1:13">
-      <c r="A118" s="4">
+      <c r="A118" s="5">
         <f t="shared" si="4"/>
         <v>10240002</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="5">
         <v>102400</v>
       </c>
-      <c r="C118" s="5">
+      <c r="C118" s="6">
         <v>2</v>
       </c>
-      <c r="D118" s="5">
-        <v>0</v>
-      </c>
-      <c r="E118" s="5" t="s">
+      <c r="D118" s="6">
+        <v>0</v>
+      </c>
+      <c r="E118" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F118" s="5"/>
-      <c r="G118" s="5"/>
-      <c r="H118" s="5">
+      <c r="F118" s="6"/>
+      <c r="G118" s="6"/>
+      <c r="H118" s="6">
         <v>10</v>
       </c>
-      <c r="I118" s="6"/>
-      <c r="K118" s="6"/>
-      <c r="L118" s="6"/>
-      <c r="M118" s="6"/>
+      <c r="I118" s="7"/>
+      <c r="K118" s="7"/>
+      <c r="L118" s="7"/>
+      <c r="M118" s="7"/>
     </row>
     <row r="119" ht="16.5" spans="1:13">
-      <c r="A119" s="4">
+      <c r="A119" s="5">
         <f t="shared" si="4"/>
         <v>10240003</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="5">
         <v>102400</v>
       </c>
-      <c r="C119" s="5">
+      <c r="C119" s="6">
         <v>3</v>
       </c>
-      <c r="D119" s="5">
-        <v>0</v>
-      </c>
-      <c r="E119" s="5" t="s">
+      <c r="D119" s="6">
+        <v>0</v>
+      </c>
+      <c r="E119" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F119" s="5"/>
-      <c r="G119" s="5"/>
-      <c r="H119" s="5" t="s">
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I119" s="6"/>
-      <c r="K119" s="6"/>
-      <c r="L119" s="6"/>
-      <c r="M119" s="6"/>
+      <c r="I119" s="7"/>
+      <c r="K119" s="7"/>
+      <c r="L119" s="7"/>
+      <c r="M119" s="7"/>
     </row>
     <row r="120" ht="16.5" spans="1:13">
-      <c r="A120" s="4">
+      <c r="A120" s="5">
         <f t="shared" si="4"/>
         <v>10240004</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="5">
         <v>102400</v>
       </c>
-      <c r="C120" s="5">
+      <c r="C120" s="6">
         <v>4</v>
       </c>
-      <c r="D120" s="5">
-        <v>0</v>
-      </c>
-      <c r="E120" s="5" t="s">
+      <c r="D120" s="6">
+        <v>0</v>
+      </c>
+      <c r="E120" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F120" s="5"/>
-      <c r="G120" s="5"/>
-      <c r="H120" s="5" t="s">
+      <c r="F120" s="6"/>
+      <c r="G120" s="6"/>
+      <c r="H120" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I120" s="6"/>
-      <c r="K120" s="6"/>
-      <c r="L120" s="6"/>
-      <c r="M120" s="6"/>
+      <c r="I120" s="7"/>
+      <c r="K120" s="7"/>
+      <c r="L120" s="7"/>
+      <c r="M120" s="7"/>
     </row>
     <row r="121" ht="16.5" spans="1:13">
-      <c r="A121" s="4">
+      <c r="A121" s="5">
         <f t="shared" si="4"/>
         <v>10240005</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="5">
         <v>102400</v>
       </c>
-      <c r="C121" s="5">
+      <c r="C121" s="6">
         <v>5</v>
       </c>
-      <c r="D121" s="5">
-        <v>0</v>
-      </c>
-      <c r="E121" s="5" t="s">
+      <c r="D121" s="6">
+        <v>0</v>
+      </c>
+      <c r="E121" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="5" t="s">
+      <c r="F121" s="6"/>
+      <c r="G121" s="6"/>
+      <c r="H121" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
-      <c r="M121" s="6"/>
+      <c r="I121" s="7"/>
+      <c r="K121" s="7"/>
+      <c r="L121" s="7"/>
+      <c r="M121" s="7"/>
     </row>
     <row r="122" ht="16.5" spans="1:13">
-      <c r="A122" s="4">
+      <c r="A122" s="5">
         <f t="shared" si="4"/>
         <v>10240006</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="5">
         <v>102400</v>
       </c>
-      <c r="C122" s="5">
+      <c r="C122" s="6">
         <v>6</v>
       </c>
-      <c r="D122" s="5">
-        <v>0</v>
-      </c>
-      <c r="E122" s="5" t="s">
+      <c r="D122" s="6">
+        <v>0</v>
+      </c>
+      <c r="E122" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F122" s="5"/>
-      <c r="G122" s="5"/>
-      <c r="H122" s="5" t="s">
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
+      <c r="H122" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I122" s="6"/>
-      <c r="K122" s="6"/>
-      <c r="L122" s="6"/>
-      <c r="M122" s="6"/>
+      <c r="I122" s="7"/>
+      <c r="K122" s="7"/>
+      <c r="L122" s="7"/>
+      <c r="M122" s="7"/>
     </row>
     <row r="123" ht="16.5" spans="1:13">
-      <c r="A123" s="4">
+      <c r="A123" s="5">
         <f t="shared" si="4"/>
         <v>10240007</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="5">
         <v>102400</v>
       </c>
-      <c r="C123" s="5">
+      <c r="C123" s="6">
         <v>7</v>
       </c>
-      <c r="D123" s="5">
-        <v>0</v>
-      </c>
-      <c r="E123" s="5" t="s">
+      <c r="D123" s="6">
+        <v>0</v>
+      </c>
+      <c r="E123" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F123" s="5"/>
-      <c r="G123" s="5"/>
-      <c r="H123" s="5" t="s">
+      <c r="F123" s="6"/>
+      <c r="G123" s="6"/>
+      <c r="H123" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I123" s="6"/>
-      <c r="K123" s="6"/>
-      <c r="L123" s="6"/>
-      <c r="M123" s="6"/>
+      <c r="I123" s="7"/>
+      <c r="K123" s="7"/>
+      <c r="L123" s="7"/>
+      <c r="M123" s="7"/>
     </row>
     <row r="124" ht="16.5" spans="1:13">
-      <c r="A124" s="4">
+      <c r="A124" s="5">
         <f t="shared" si="4"/>
         <v>10240008</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="5">
         <v>102400</v>
       </c>
-      <c r="C124" s="5">
+      <c r="C124" s="6">
         <v>8</v>
       </c>
-      <c r="D124" s="5">
-        <v>0</v>
-      </c>
-      <c r="E124" s="5" t="s">
+      <c r="D124" s="6">
+        <v>0</v>
+      </c>
+      <c r="E124" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F124" s="5"/>
-      <c r="G124" s="5"/>
-      <c r="H124" s="5" t="s">
+      <c r="F124" s="6"/>
+      <c r="G124" s="6"/>
+      <c r="H124" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I124" s="6"/>
-      <c r="K124" s="6"/>
-      <c r="L124" s="6"/>
-      <c r="M124" s="6"/>
+      <c r="I124" s="7"/>
+      <c r="K124" s="7"/>
+      <c r="L124" s="7"/>
+      <c r="M124" s="7"/>
     </row>
     <row r="125" ht="16.5" spans="1:13">
-      <c r="A125" s="4">
+      <c r="A125" s="5">
         <f t="shared" si="4"/>
         <v>10240009</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="5">
         <v>102400</v>
       </c>
-      <c r="C125" s="5">
+      <c r="C125" s="6">
         <v>9</v>
       </c>
-      <c r="D125" s="5">
-        <v>0</v>
-      </c>
-      <c r="E125" s="5" t="s">
+      <c r="D125" s="6">
+        <v>0</v>
+      </c>
+      <c r="E125" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F125" s="5"/>
-      <c r="G125" s="5"/>
-      <c r="H125" s="5" t="s">
+      <c r="F125" s="6"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I125" s="6"/>
-      <c r="K125" s="6"/>
-      <c r="L125" s="6"/>
-      <c r="M125" s="6"/>
+      <c r="I125" s="7"/>
+      <c r="K125" s="7"/>
+      <c r="L125" s="7"/>
+      <c r="M125" s="7"/>
     </row>
     <row r="126" ht="16.5" spans="1:13">
-      <c r="A126" s="4">
+      <c r="A126" s="5">
         <f t="shared" si="4"/>
         <v>10240010</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="5">
         <v>102400</v>
       </c>
-      <c r="C126" s="5">
+      <c r="C126" s="6">
         <v>10</v>
       </c>
-      <c r="D126" s="5">
-        <v>0</v>
-      </c>
-      <c r="E126" s="5" t="s">
+      <c r="D126" s="6">
+        <v>0</v>
+      </c>
+      <c r="E126" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F126" s="5"/>
-      <c r="G126" s="5"/>
-      <c r="H126" s="5" t="s">
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I126" s="6"/>
-      <c r="K126" s="6"/>
-      <c r="L126" s="6"/>
-      <c r="M126" s="6"/>
+      <c r="I126" s="7"/>
+      <c r="K126" s="7"/>
+      <c r="L126" s="7"/>
+      <c r="M126" s="7"/>
     </row>
     <row r="127" ht="16.5" spans="1:13">
-      <c r="A127" s="4">
+      <c r="A127" s="5">
         <f t="shared" si="4"/>
         <v>10240011</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127" s="5">
         <v>102400</v>
       </c>
-      <c r="C127" s="5">
+      <c r="C127" s="6">
         <v>11</v>
       </c>
-      <c r="D127" s="5">
-        <v>0</v>
-      </c>
-      <c r="E127" s="5" t="s">
+      <c r="D127" s="6">
+        <v>0</v>
+      </c>
+      <c r="E127" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
-      <c r="H127" s="5" t="s">
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I127" s="6"/>
-      <c r="K127" s="6"/>
-      <c r="L127" s="6"/>
-      <c r="M127" s="6"/>
+      <c r="I127" s="7"/>
+      <c r="K127" s="7"/>
+      <c r="L127" s="7"/>
+      <c r="M127" s="7"/>
     </row>
     <row r="128" ht="16.5" spans="1:13">
-      <c r="A128" s="4">
+      <c r="A128" s="5">
         <f t="shared" si="4"/>
         <v>10240012</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="5">
         <v>102400</v>
       </c>
-      <c r="C128" s="5">
+      <c r="C128" s="6">
         <v>12</v>
       </c>
-      <c r="D128" s="5">
+      <c r="D128" s="6">
         <v>1</v>
       </c>
-      <c r="E128" s="5" t="s">
+      <c r="E128" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F128" s="5"/>
-      <c r="G128" s="5"/>
-      <c r="H128" s="5" t="s">
+      <c r="F128" s="6"/>
+      <c r="G128" s="6"/>
+      <c r="H128" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I128" s="6"/>
-      <c r="K128" s="6"/>
-      <c r="L128" s="6"/>
-      <c r="M128" s="6"/>
+      <c r="I128" s="7"/>
+      <c r="K128" s="7"/>
+      <c r="L128" s="7"/>
+      <c r="M128" s="7"/>
     </row>
     <row r="129" ht="16.5" spans="1:13">
-      <c r="A129" s="4">
+      <c r="A129" s="5">
         <f t="shared" si="4"/>
         <v>10240013</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129" s="5">
         <v>102400</v>
       </c>
-      <c r="C129" s="5">
+      <c r="C129" s="6">
         <v>13</v>
       </c>
-      <c r="D129" s="5">
+      <c r="D129" s="6">
         <v>1</v>
       </c>
-      <c r="E129" s="5" t="s">
+      <c r="E129" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F129" s="5"/>
-      <c r="G129" s="5"/>
-      <c r="H129" s="5" t="s">
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I129" s="6"/>
-      <c r="K129" s="6"/>
-      <c r="L129" s="6"/>
-      <c r="M129" s="6"/>
+      <c r="I129" s="7"/>
+      <c r="K129" s="7"/>
+      <c r="L129" s="7"/>
+      <c r="M129" s="7"/>
     </row>
     <row r="130" ht="16.5" spans="1:13">
-      <c r="A130" s="4">
+      <c r="A130" s="5">
         <f t="shared" si="4"/>
         <v>10240014</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="5">
         <v>102400</v>
       </c>
-      <c r="C130" s="5">
+      <c r="C130" s="6">
         <v>14</v>
       </c>
-      <c r="D130" s="5">
+      <c r="D130" s="6">
         <v>1</v>
       </c>
-      <c r="E130" s="5" t="s">
+      <c r="E130" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F130" s="5"/>
-      <c r="G130" s="5"/>
-      <c r="H130" s="5" t="s">
+      <c r="F130" s="6"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I130" s="6"/>
-      <c r="K130" s="6"/>
-      <c r="L130" s="6"/>
-      <c r="M130" s="6"/>
+      <c r="I130" s="7"/>
+      <c r="K130" s="7"/>
+      <c r="L130" s="7"/>
+      <c r="M130" s="7"/>
     </row>
     <row r="131" ht="16.5" spans="1:13">
-      <c r="A131" s="4">
+      <c r="A131" s="5">
         <f t="shared" si="4"/>
         <v>10240015</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131" s="5">
         <v>102400</v>
       </c>
-      <c r="C131" s="5">
+      <c r="C131" s="6">
         <v>15</v>
       </c>
-      <c r="D131" s="5">
+      <c r="D131" s="6">
         <v>2</v>
       </c>
-      <c r="E131" s="5" t="s">
+      <c r="E131" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F131" s="5"/>
-      <c r="G131" s="5"/>
-      <c r="H131" s="5" t="s">
+      <c r="F131" s="6"/>
+      <c r="G131" s="6"/>
+      <c r="H131" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I131" s="6"/>
-      <c r="K131" s="6"/>
-      <c r="L131" s="6"/>
-      <c r="M131" s="6"/>
+      <c r="I131" s="7"/>
+      <c r="K131" s="7"/>
+      <c r="L131" s="7"/>
+      <c r="M131" s="7"/>
     </row>
     <row r="132" ht="16.5" spans="1:13">
-      <c r="A132" s="4">
+      <c r="A132" s="5">
         <f t="shared" si="4"/>
         <v>10240016</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="5">
         <v>102400</v>
       </c>
-      <c r="C132" s="5">
+      <c r="C132" s="6">
         <v>16</v>
       </c>
-      <c r="D132" s="5">
+      <c r="D132" s="6">
         <v>2</v>
       </c>
-      <c r="E132" s="5" t="s">
+      <c r="E132" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F132" s="5"/>
-      <c r="G132" s="5"/>
-      <c r="H132" s="5" t="s">
+      <c r="F132" s="6"/>
+      <c r="G132" s="6"/>
+      <c r="H132" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I132" s="6"/>
-      <c r="K132" s="6"/>
-      <c r="L132" s="6"/>
-      <c r="M132" s="6"/>
+      <c r="I132" s="7"/>
+      <c r="K132" s="7"/>
+      <c r="L132" s="7"/>
+      <c r="M132" s="7"/>
     </row>
     <row r="133" ht="16.5" spans="1:13">
-      <c r="A133" s="4">
+      <c r="A133" s="5">
         <f t="shared" si="4"/>
         <v>10240017</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="5">
         <v>102400</v>
       </c>
-      <c r="C133" s="5">
+      <c r="C133" s="6">
         <v>17</v>
       </c>
-      <c r="D133" s="5">
+      <c r="D133" s="6">
         <v>2</v>
       </c>
-      <c r="E133" s="5" t="s">
+      <c r="E133" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F133" s="5"/>
-      <c r="G133" s="5"/>
-      <c r="H133" s="5" t="s">
+      <c r="F133" s="6"/>
+      <c r="G133" s="6"/>
+      <c r="H133" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I133" s="6"/>
-      <c r="K133" s="6"/>
-      <c r="L133" s="6"/>
-      <c r="M133" s="6"/>
+      <c r="I133" s="7"/>
+      <c r="K133" s="7"/>
+      <c r="L133" s="7"/>
+      <c r="M133" s="7"/>
     </row>
     <row r="134" ht="16.5" spans="1:13">
-      <c r="A134" s="4">
+      <c r="A134" s="5">
         <f t="shared" si="4"/>
         <v>10240018</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="5">
         <v>102400</v>
       </c>
-      <c r="C134" s="5">
+      <c r="C134" s="6">
         <v>18</v>
       </c>
-      <c r="D134" s="5">
+      <c r="D134" s="6">
         <v>2</v>
       </c>
-      <c r="E134" s="5" t="s">
+      <c r="E134" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F134" s="5"/>
-      <c r="G134" s="5"/>
-      <c r="H134" s="5" t="s">
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I134" s="6"/>
-      <c r="K134" s="6"/>
-      <c r="L134" s="6"/>
-      <c r="M134" s="6"/>
+      <c r="I134" s="7"/>
+      <c r="K134" s="7"/>
+      <c r="L134" s="7"/>
+      <c r="M134" s="7"/>
     </row>
     <row r="135" ht="16.5" spans="1:13">
-      <c r="A135" s="4">
+      <c r="A135" s="5">
         <f t="shared" si="4"/>
         <v>10240019</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135" s="5">
         <v>102400</v>
       </c>
-      <c r="C135" s="5">
+      <c r="C135" s="6">
         <v>19</v>
       </c>
-      <c r="D135" s="5">
+      <c r="D135" s="6">
         <v>3</v>
       </c>
-      <c r="E135" s="5" t="s">
+      <c r="E135" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F135" s="5"/>
-      <c r="G135" s="5"/>
-      <c r="H135" s="5" t="s">
+      <c r="F135" s="6"/>
+      <c r="G135" s="6"/>
+      <c r="H135" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I135" s="6"/>
-      <c r="K135" s="6"/>
-      <c r="L135" s="6"/>
-      <c r="M135" s="6"/>
+      <c r="I135" s="7"/>
+      <c r="K135" s="7"/>
+      <c r="L135" s="7"/>
+      <c r="M135" s="7"/>
     </row>
     <row r="136" ht="16.5" spans="1:13">
-      <c r="A136" s="4">
+      <c r="A136" s="5">
         <f t="shared" si="4"/>
         <v>10240020</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="5">
         <v>102400</v>
       </c>
-      <c r="C136" s="5">
+      <c r="C136" s="6">
         <v>20</v>
       </c>
-      <c r="D136" s="5">
+      <c r="D136" s="6">
         <v>3</v>
       </c>
-      <c r="E136" s="5" t="s">
+      <c r="E136" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F136" s="5"/>
-      <c r="G136" s="5"/>
-      <c r="H136" s="5" t="s">
+      <c r="F136" s="6"/>
+      <c r="G136" s="6"/>
+      <c r="H136" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I136" s="6"/>
-      <c r="K136" s="6"/>
-      <c r="L136" s="6"/>
-      <c r="M136" s="6"/>
+      <c r="I136" s="7"/>
+      <c r="K136" s="7"/>
+      <c r="L136" s="7"/>
+      <c r="M136" s="7"/>
     </row>
     <row r="137" ht="16.5" spans="1:13">
-      <c r="A137" s="4">
+      <c r="A137" s="5">
         <f t="shared" si="4"/>
         <v>10240021</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137" s="5">
         <v>102400</v>
       </c>
-      <c r="C137" s="5">
+      <c r="C137" s="6">
         <v>21</v>
       </c>
-      <c r="D137" s="5">
+      <c r="D137" s="6">
         <v>3</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="E137" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F137" s="5"/>
-      <c r="G137" s="5"/>
-      <c r="H137" s="5" t="s">
+      <c r="F137" s="6"/>
+      <c r="G137" s="6"/>
+      <c r="H137" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I137" s="6"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
-      <c r="M137" s="6"/>
+      <c r="I137" s="7"/>
+      <c r="K137" s="7"/>
+      <c r="L137" s="7"/>
+      <c r="M137" s="7"/>
     </row>
     <row r="138" ht="16.5" spans="1:13">
-      <c r="A138" s="4">
+      <c r="A138" s="5">
         <f t="shared" si="4"/>
         <v>10240022</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="5">
         <v>102400</v>
       </c>
-      <c r="C138" s="5">
+      <c r="C138" s="6">
         <v>22</v>
       </c>
-      <c r="D138" s="5">
+      <c r="D138" s="6">
         <v>3</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="E138" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F138" s="5"/>
-      <c r="G138" s="5"/>
-      <c r="H138" s="5" t="s">
+      <c r="F138" s="6"/>
+      <c r="G138" s="6"/>
+      <c r="H138" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I138" s="6"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
-      <c r="M138" s="6"/>
+      <c r="I138" s="7"/>
+      <c r="K138" s="7"/>
+      <c r="L138" s="7"/>
+      <c r="M138" s="7"/>
     </row>
     <row r="139" ht="16.5" spans="1:13">
-      <c r="A139" s="7">
+      <c r="A139" s="8">
         <f t="shared" si="4"/>
         <v>10240028</v>
       </c>
-      <c r="B139" s="7">
+      <c r="B139" s="8">
         <v>102400</v>
       </c>
-      <c r="C139" s="8">
+      <c r="C139" s="9">
         <v>28</v>
       </c>
-      <c r="D139" s="8">
+      <c r="D139" s="9">
         <v>2</v>
       </c>
-      <c r="E139" s="8" t="s">
+      <c r="E139" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F139" s="8"/>
-      <c r="G139" s="8"/>
-      <c r="H139" s="8" t="s">
+      <c r="F139" s="9"/>
+      <c r="G139" s="9"/>
+      <c r="H139" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="I139" s="6"/>
-      <c r="K139" s="6"/>
-      <c r="L139" s="6"/>
-      <c r="M139" s="6"/>
+      <c r="I139" s="7"/>
+      <c r="K139" s="7"/>
+      <c r="L139" s="7"/>
+      <c r="M139" s="7"/>
     </row>
     <row r="140" ht="16.5" spans="1:13">
-      <c r="A140" s="7">
+      <c r="A140" s="8">
         <f t="shared" si="4"/>
         <v>10240030</v>
       </c>
-      <c r="B140" s="7">
+      <c r="B140" s="8">
         <v>102400</v>
       </c>
-      <c r="C140" s="8">
+      <c r="C140" s="9">
         <v>30</v>
       </c>
-      <c r="D140" s="8">
+      <c r="D140" s="9">
         <v>2</v>
       </c>
-      <c r="E140" s="8" t="s">
+      <c r="E140" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F140" s="8"/>
-      <c r="G140" s="8"/>
-      <c r="H140" s="8" t="s">
+      <c r="F140" s="9"/>
+      <c r="G140" s="9"/>
+      <c r="H140" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
-      <c r="M140" s="6"/>
+      <c r="I140" s="7"/>
+      <c r="K140" s="7"/>
+      <c r="L140" s="7"/>
+      <c r="M140" s="7"/>
     </row>
     <row r="141" ht="16.5" spans="1:13">
-      <c r="A141" s="18">
+      <c r="A141" s="19">
         <f t="shared" ref="A141:A162" si="5">B141*100+C141</f>
         <v>10170001</v>
       </c>
-      <c r="B141" s="19">
+      <c r="B141" s="20">
         <v>101700</v>
       </c>
-      <c r="C141" s="19">
+      <c r="C141" s="20">
         <v>1</v>
       </c>
-      <c r="D141" s="19">
-        <v>0</v>
-      </c>
-      <c r="E141" s="19" t="s">
+      <c r="D141" s="20">
+        <v>0</v>
+      </c>
+      <c r="E141" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="F141" s="19"/>
-      <c r="G141" s="19"/>
-      <c r="H141" s="19" t="s">
+      <c r="F141" s="20"/>
+      <c r="G141" s="20"/>
+      <c r="H141" s="20" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:13">
-      <c r="A142" s="20">
+      <c r="A142" s="21">
         <f t="shared" si="5"/>
         <v>10170002</v>
       </c>
-      <c r="B142" s="21">
+      <c r="B142" s="22">
         <v>101700</v>
       </c>
-      <c r="C142" s="21">
+      <c r="C142" s="22">
         <v>2</v>
       </c>
-      <c r="D142" s="21">
-        <v>0</v>
-      </c>
-      <c r="E142" s="21" t="s">
+      <c r="D142" s="22">
+        <v>0</v>
+      </c>
+      <c r="E142" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="F142" s="21"/>
-      <c r="G142" s="21"/>
-      <c r="H142" s="21" t="s">
+      <c r="F142" s="22"/>
+      <c r="G142" s="22"/>
+      <c r="H142" s="22" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:13">
-      <c r="A143" s="20">
+      <c r="A143" s="21">
         <f t="shared" si="5"/>
         <v>10170003</v>
       </c>
-      <c r="B143" s="21">
+      <c r="B143" s="22">
         <v>101700</v>
       </c>
-      <c r="C143" s="21">
+      <c r="C143" s="22">
         <v>3</v>
       </c>
-      <c r="D143" s="21">
-        <v>0</v>
-      </c>
-      <c r="E143" s="21" t="s">
+      <c r="D143" s="22">
+        <v>0</v>
+      </c>
+      <c r="E143" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="F143" s="21"/>
-      <c r="G143" s="21"/>
-      <c r="H143" s="21" t="s">
+      <c r="F143" s="22"/>
+      <c r="G143" s="22"/>
+      <c r="H143" s="22" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:13">
-      <c r="A144" s="20">
+      <c r="A144" s="21">
         <f t="shared" si="5"/>
         <v>10170004</v>
       </c>
-      <c r="B144" s="21">
+      <c r="B144" s="22">
         <v>101700</v>
       </c>
-      <c r="C144" s="21">
+      <c r="C144" s="22">
         <v>4</v>
       </c>
-      <c r="D144" s="21">
-        <v>0</v>
-      </c>
-      <c r="E144" s="21" t="s">
+      <c r="D144" s="22">
+        <v>0</v>
+      </c>
+      <c r="E144" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="F144" s="21"/>
-      <c r="G144" s="21"/>
-      <c r="H144" s="21" t="s">
+      <c r="F144" s="22"/>
+      <c r="G144" s="22"/>
+      <c r="H144" s="22" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:8">
-      <c r="A145" s="20">
+      <c r="A145" s="21">
         <f t="shared" si="5"/>
         <v>10170005</v>
       </c>
-      <c r="B145" s="21">
+      <c r="B145" s="22">
         <v>101700</v>
       </c>
-      <c r="C145" s="21">
+      <c r="C145" s="22">
         <v>5</v>
       </c>
-      <c r="D145" s="21">
-        <v>0</v>
-      </c>
-      <c r="E145" s="21" t="s">
+      <c r="D145" s="22">
+        <v>0</v>
+      </c>
+      <c r="E145" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="F145" s="21"/>
-      <c r="G145" s="21"/>
-      <c r="H145" s="21" t="s">
+      <c r="F145" s="22"/>
+      <c r="G145" s="22"/>
+      <c r="H145" s="22" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:8">
-      <c r="A146" s="20">
+      <c r="A146" s="21">
         <f t="shared" si="5"/>
         <v>10170006</v>
       </c>
-      <c r="B146" s="21">
+      <c r="B146" s="22">
         <v>101700</v>
       </c>
-      <c r="C146" s="21">
+      <c r="C146" s="22">
         <v>6</v>
       </c>
-      <c r="D146" s="21">
-        <v>0</v>
-      </c>
-      <c r="E146" s="21" t="s">
+      <c r="D146" s="22">
+        <v>0</v>
+      </c>
+      <c r="E146" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="F146" s="21"/>
-      <c r="G146" s="21"/>
-      <c r="H146" s="21" t="s">
+      <c r="F146" s="22"/>
+      <c r="G146" s="22"/>
+      <c r="H146" s="22" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="1:8">
-      <c r="A147" s="20">
+      <c r="A147" s="21">
         <f t="shared" si="5"/>
         <v>10170007</v>
       </c>
-      <c r="B147" s="21">
+      <c r="B147" s="22">
         <v>101700</v>
       </c>
-      <c r="C147" s="21">
+      <c r="C147" s="22">
         <v>7</v>
       </c>
-      <c r="D147" s="21">
-        <v>0</v>
-      </c>
-      <c r="E147" s="21" t="s">
+      <c r="D147" s="22">
+        <v>0</v>
+      </c>
+      <c r="E147" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="F147" s="21"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21" t="s">
+      <c r="F147" s="22"/>
+      <c r="G147" s="22"/>
+      <c r="H147" s="22" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="1:8">
-      <c r="A148" s="20">
+      <c r="A148" s="21">
         <f t="shared" si="5"/>
         <v>10170008</v>
       </c>
-      <c r="B148" s="21">
+      <c r="B148" s="22">
         <v>101700</v>
       </c>
-      <c r="C148" s="21">
+      <c r="C148" s="22">
         <v>8</v>
       </c>
-      <c r="D148" s="21">
-        <v>0</v>
-      </c>
-      <c r="E148" s="21" t="s">
+      <c r="D148" s="22">
+        <v>0</v>
+      </c>
+      <c r="E148" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="F148" s="21"/>
-      <c r="G148" s="21"/>
-      <c r="H148" s="21" t="s">
+      <c r="F148" s="22"/>
+      <c r="G148" s="22"/>
+      <c r="H148" s="22" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="1:8">
-      <c r="A149" s="20">
+      <c r="A149" s="21">
         <f t="shared" si="5"/>
         <v>10170009</v>
       </c>
-      <c r="B149" s="21">
+      <c r="B149" s="22">
         <v>101700</v>
       </c>
-      <c r="C149" s="21">
+      <c r="C149" s="22">
         <v>9</v>
       </c>
-      <c r="D149" s="21">
+      <c r="D149" s="22">
         <v>1</v>
       </c>
-      <c r="E149" s="21" t="s">
+      <c r="E149" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="F149" s="21"/>
-      <c r="G149" s="21"/>
-      <c r="H149" s="21" t="s">
+      <c r="F149" s="22"/>
+      <c r="G149" s="22"/>
+      <c r="H149" s="22" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:8">
-      <c r="A150" s="20">
+      <c r="A150" s="21">
         <f t="shared" si="5"/>
         <v>10170010</v>
       </c>
-      <c r="B150" s="21">
+      <c r="B150" s="22">
         <v>101700</v>
       </c>
-      <c r="C150" s="21">
+      <c r="C150" s="22">
         <v>10</v>
       </c>
-      <c r="D150" s="21">
+      <c r="D150" s="22">
         <v>2</v>
       </c>
-      <c r="E150" s="21" t="s">
+      <c r="E150" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="F150" s="21"/>
-      <c r="G150" s="21"/>
-      <c r="H150" s="21" t="s">
+      <c r="F150" s="22"/>
+      <c r="G150" s="22"/>
+      <c r="H150" s="22" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:8">
-      <c r="A151" s="20">
+      <c r="A151" s="21">
         <f t="shared" si="5"/>
         <v>10170011</v>
       </c>
-      <c r="B151" s="21">
+      <c r="B151" s="22">
         <v>101700</v>
       </c>
-      <c r="C151" s="21">
+      <c r="C151" s="22">
         <v>11</v>
       </c>
-      <c r="D151" s="21">
-        <v>0</v>
-      </c>
-      <c r="E151" s="21" t="s">
+      <c r="D151" s="22">
+        <v>0</v>
+      </c>
+      <c r="E151" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="F151" s="22">
+      <c r="F151" s="23">
         <v>9</v>
       </c>
-      <c r="G151" s="21"/>
-      <c r="H151" s="21" t="s">
+      <c r="G151" s="22"/>
+      <c r="H151" s="22" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="152" ht="16.5" spans="1:8">
-      <c r="A152" s="20">
+      <c r="A152" s="21">
         <f t="shared" si="5"/>
         <v>10170012</v>
       </c>
-      <c r="B152" s="21">
+      <c r="B152" s="22">
         <v>101700</v>
       </c>
-      <c r="C152" s="21">
+      <c r="C152" s="22">
         <v>12</v>
       </c>
-      <c r="D152" s="21">
-        <v>0</v>
-      </c>
-      <c r="E152" s="21" t="s">
+      <c r="D152" s="22">
+        <v>0</v>
+      </c>
+      <c r="E152" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="F152" s="22">
+      <c r="F152" s="23">
         <v>9</v>
       </c>
-      <c r="G152" s="21"/>
-      <c r="H152" s="21" t="s">
+      <c r="G152" s="22"/>
+      <c r="H152" s="22" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="153" ht="16.5" spans="1:8">
-      <c r="A153" s="20">
+      <c r="A153" s="21">
         <f t="shared" si="5"/>
         <v>10170013</v>
       </c>
-      <c r="B153" s="21">
+      <c r="B153" s="22">
         <v>101700</v>
       </c>
-      <c r="C153" s="21">
+      <c r="C153" s="22">
         <v>13</v>
       </c>
-      <c r="D153" s="21">
-        <v>0</v>
-      </c>
-      <c r="E153" s="21" t="s">
+      <c r="D153" s="22">
+        <v>0</v>
+      </c>
+      <c r="E153" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="F153" s="22">
+      <c r="F153" s="23">
         <v>9</v>
       </c>
-      <c r="G153" s="21"/>
-      <c r="H153" s="21" t="s">
+      <c r="G153" s="22"/>
+      <c r="H153" s="22" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="154" ht="16.5" spans="1:8">
-      <c r="A154" s="20">
+      <c r="A154" s="21">
         <f t="shared" si="5"/>
         <v>10170014</v>
       </c>
-      <c r="B154" s="21">
+      <c r="B154" s="22">
         <v>101700</v>
       </c>
-      <c r="C154" s="21">
+      <c r="C154" s="22">
         <v>14</v>
       </c>
-      <c r="D154" s="21">
-        <v>0</v>
-      </c>
-      <c r="E154" s="21" t="s">
+      <c r="D154" s="22">
+        <v>0</v>
+      </c>
+      <c r="E154" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="F154" s="22">
+      <c r="F154" s="23">
         <v>9</v>
       </c>
-      <c r="G154" s="21"/>
-      <c r="H154" s="21" t="s">
+      <c r="G154" s="22"/>
+      <c r="H154" s="22" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="155" ht="16.5" spans="1:8">
-      <c r="A155" s="20">
+      <c r="A155" s="21">
         <f t="shared" si="5"/>
         <v>10170015</v>
       </c>
-      <c r="B155" s="21">
+      <c r="B155" s="22">
         <v>101700</v>
       </c>
-      <c r="C155" s="21">
+      <c r="C155" s="22">
         <v>15</v>
       </c>
-      <c r="D155" s="21">
-        <v>0</v>
-      </c>
-      <c r="E155" s="21" t="s">
+      <c r="D155" s="22">
+        <v>0</v>
+      </c>
+      <c r="E155" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="F155" s="22">
+      <c r="F155" s="23">
         <v>9</v>
       </c>
-      <c r="G155" s="21"/>
-      <c r="H155" s="21" t="s">
+      <c r="G155" s="22"/>
+      <c r="H155" s="22" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="156" ht="16.5" spans="1:8">
-      <c r="A156" s="20">
+      <c r="A156" s="21">
         <f t="shared" si="5"/>
         <v>10170016</v>
       </c>
-      <c r="B156" s="21">
+      <c r="B156" s="22">
         <v>101700</v>
       </c>
-      <c r="C156" s="21">
+      <c r="C156" s="22">
         <v>16</v>
       </c>
-      <c r="D156" s="21">
-        <v>0</v>
-      </c>
-      <c r="E156" s="21" t="s">
+      <c r="D156" s="22">
+        <v>0</v>
+      </c>
+      <c r="E156" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="F156" s="22">
+      <c r="F156" s="23">
         <v>9</v>
       </c>
-      <c r="G156" s="21"/>
-      <c r="H156" s="21" t="s">
+      <c r="G156" s="22"/>
+      <c r="H156" s="22" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="157" ht="16.5" spans="1:8">
-      <c r="A157" s="20">
+      <c r="A157" s="21">
         <f t="shared" si="5"/>
         <v>10170017</v>
       </c>
-      <c r="B157" s="21">
+      <c r="B157" s="22">
         <v>101700</v>
       </c>
-      <c r="C157" s="21">
+      <c r="C157" s="22">
         <v>17</v>
       </c>
-      <c r="D157" s="21">
-        <v>0</v>
-      </c>
-      <c r="E157" s="21" t="s">
+      <c r="D157" s="22">
+        <v>0</v>
+      </c>
+      <c r="E157" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="F157" s="22">
+      <c r="F157" s="23">
         <v>9</v>
       </c>
-      <c r="G157" s="21"/>
-      <c r="H157" s="21" t="s">
+      <c r="G157" s="22"/>
+      <c r="H157" s="22" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="158" ht="16.5" spans="1:8">
-      <c r="A158" s="20">
+      <c r="A158" s="21">
         <f t="shared" si="5"/>
         <v>10170018</v>
       </c>
-      <c r="B158" s="21">
+      <c r="B158" s="22">
         <v>101700</v>
       </c>
-      <c r="C158" s="21">
+      <c r="C158" s="22">
         <v>18</v>
       </c>
-      <c r="D158" s="21">
-        <v>0</v>
-      </c>
-      <c r="E158" s="21" t="s">
+      <c r="D158" s="22">
+        <v>0</v>
+      </c>
+      <c r="E158" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="F158" s="22">
+      <c r="F158" s="23">
         <v>9</v>
       </c>
-      <c r="G158" s="21"/>
-      <c r="H158" s="21" t="s">
+      <c r="G158" s="22"/>
+      <c r="H158" s="22" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="159" ht="16.5" spans="1:8">
-      <c r="A159" s="20">
+      <c r="A159" s="21">
         <f t="shared" si="5"/>
         <v>10170019</v>
       </c>
-      <c r="B159" s="21">
+      <c r="B159" s="22">
         <v>101700</v>
       </c>
-      <c r="C159" s="21">
+      <c r="C159" s="22">
         <v>19</v>
       </c>
-      <c r="D159" s="21">
+      <c r="D159" s="22">
         <v>3</v>
       </c>
-      <c r="E159" s="21" t="s">
+      <c r="E159" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="F159" s="21"/>
-      <c r="G159" s="21"/>
-      <c r="H159" s="21" t="s">
+      <c r="F159" s="22"/>
+      <c r="G159" s="22"/>
+      <c r="H159" s="22" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="160" ht="16.5" spans="1:8">
-      <c r="A160" s="20">
+      <c r="A160" s="21">
         <f t="shared" si="5"/>
         <v>10170020</v>
       </c>
-      <c r="B160" s="21">
+      <c r="B160" s="22">
         <v>101700</v>
       </c>
-      <c r="C160" s="21">
+      <c r="C160" s="22">
         <v>20</v>
       </c>
-      <c r="D160" s="21">
+      <c r="D160" s="22">
         <v>3</v>
       </c>
-      <c r="E160" s="21" t="s">
+      <c r="E160" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="F160" s="21"/>
-      <c r="G160" s="21"/>
-      <c r="H160" s="21" t="s">
+      <c r="F160" s="22"/>
+      <c r="G160" s="22"/>
+      <c r="H160" s="22" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="161" ht="16.5" spans="1:8">
-      <c r="A161" s="20">
+      <c r="A161" s="21">
         <f t="shared" si="5"/>
         <v>10170021</v>
       </c>
-      <c r="B161" s="21">
+      <c r="B161" s="22">
         <v>101700</v>
       </c>
-      <c r="C161" s="21">
+      <c r="C161" s="22">
         <v>21</v>
       </c>
-      <c r="D161" s="21">
+      <c r="D161" s="22">
         <v>3</v>
       </c>
-      <c r="E161" s="21" t="s">
+      <c r="E161" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="F161" s="21"/>
-      <c r="G161" s="21"/>
-      <c r="H161" s="21" t="s">
+      <c r="F161" s="22"/>
+      <c r="G161" s="22"/>
+      <c r="H161" s="22" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="162" ht="16.5" spans="1:8">
-      <c r="A162" s="20">
+      <c r="A162" s="21">
         <f t="shared" si="5"/>
         <v>10170022</v>
       </c>
-      <c r="B162" s="21">
+      <c r="B162" s="22">
         <v>101700</v>
       </c>
-      <c r="C162" s="21">
+      <c r="C162" s="22">
         <v>22</v>
       </c>
-      <c r="D162" s="21">
+      <c r="D162" s="22">
         <v>3</v>
       </c>
-      <c r="E162" s="21" t="s">
+      <c r="E162" s="22" t="s">
         <v>227</v>
       </c>
-      <c r="F162" s="21"/>
-      <c r="G162" s="21"/>
-      <c r="H162" s="21" t="s">
+      <c r="F162" s="22"/>
+      <c r="G162" s="22"/>
+      <c r="H162" s="22" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="163" ht="16.5" spans="1:8">
-      <c r="A163" s="23">
-        <f t="shared" ref="A163:A180" si="6">B163*100+C163</f>
+      <c r="A163" s="24">
+        <f t="shared" ref="A163:A182" si="6">B163*100+C163</f>
         <v>10220001</v>
       </c>
-      <c r="B163" s="24">
+      <c r="B163" s="25">
         <v>102200</v>
       </c>
-      <c r="C163" s="24">
+      <c r="C163" s="25">
         <v>1</v>
       </c>
-      <c r="D163" s="24">
-        <v>0</v>
-      </c>
-      <c r="E163" s="24" t="s">
+      <c r="D163" s="25">
+        <v>0</v>
+      </c>
+      <c r="E163" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="F163" s="24"/>
-      <c r="G163" s="24"/>
-      <c r="H163" s="25">
+      <c r="F163" s="25"/>
+      <c r="G163" s="25"/>
+      <c r="H163" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="164" ht="16.5" spans="1:8">
-      <c r="A164" s="23">
+      <c r="A164" s="24">
         <f t="shared" si="6"/>
         <v>10220002</v>
       </c>
-      <c r="B164" s="24">
+      <c r="B164" s="25">
         <v>102200</v>
       </c>
-      <c r="C164" s="24">
+      <c r="C164" s="25">
         <v>2</v>
       </c>
-      <c r="D164" s="24">
-        <v>0</v>
-      </c>
-      <c r="E164" s="24" t="s">
+      <c r="D164" s="25">
+        <v>0</v>
+      </c>
+      <c r="E164" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-      <c r="H164" s="24" t="s">
+      <c r="F164" s="25"/>
+      <c r="G164" s="25"/>
+      <c r="H164" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="165" ht="16.5" spans="1:8">
-      <c r="A165" s="23">
+      <c r="A165" s="24">
         <f t="shared" si="6"/>
         <v>10220003</v>
       </c>
-      <c r="B165" s="24">
+      <c r="B165" s="25">
         <v>102200</v>
       </c>
-      <c r="C165" s="24">
+      <c r="C165" s="25">
         <v>3</v>
       </c>
-      <c r="D165" s="24">
-        <v>0</v>
-      </c>
-      <c r="E165" s="24" t="s">
+      <c r="D165" s="25">
+        <v>0</v>
+      </c>
+      <c r="E165" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="F165" s="24"/>
-      <c r="G165" s="24"/>
-      <c r="H165" s="24" t="s">
+      <c r="F165" s="25"/>
+      <c r="G165" s="25"/>
+      <c r="H165" s="25" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="166" ht="16.5" spans="1:8">
-      <c r="A166" s="23">
+      <c r="A166" s="24">
         <f t="shared" si="6"/>
         <v>10220004</v>
       </c>
-      <c r="B166" s="24">
+      <c r="B166" s="25">
         <v>102200</v>
       </c>
-      <c r="C166" s="24">
+      <c r="C166" s="25">
         <v>4</v>
       </c>
-      <c r="D166" s="24">
-        <v>0</v>
-      </c>
-      <c r="E166" s="24" t="s">
+      <c r="D166" s="25">
+        <v>0</v>
+      </c>
+      <c r="E166" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="F166" s="24"/>
-      <c r="G166" s="24"/>
-      <c r="H166" s="24" t="s">
+      <c r="F166" s="25"/>
+      <c r="G166" s="25"/>
+      <c r="H166" s="25" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="167" ht="16.5" spans="1:8">
-      <c r="A167" s="23">
+      <c r="A167" s="24">
         <f t="shared" si="6"/>
         <v>10220005</v>
       </c>
-      <c r="B167" s="24">
+      <c r="B167" s="25">
         <v>102200</v>
       </c>
-      <c r="C167" s="24">
+      <c r="C167" s="25">
         <v>5</v>
       </c>
-      <c r="D167" s="24">
-        <v>0</v>
-      </c>
-      <c r="E167" s="24" t="s">
+      <c r="D167" s="25">
+        <v>0</v>
+      </c>
+      <c r="E167" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
-      <c r="H167" s="24" t="s">
+      <c r="F167" s="25"/>
+      <c r="G167" s="25"/>
+      <c r="H167" s="25" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="168" ht="16.5" spans="1:8">
-      <c r="A168" s="23">
+      <c r="A168" s="24">
         <f t="shared" si="6"/>
         <v>10220006</v>
       </c>
-      <c r="B168" s="24">
+      <c r="B168" s="25">
         <v>102200</v>
       </c>
-      <c r="C168" s="24">
+      <c r="C168" s="25">
         <v>6</v>
       </c>
-      <c r="D168" s="24">
-        <v>0</v>
-      </c>
-      <c r="E168" s="24" t="s">
+      <c r="D168" s="25">
+        <v>0</v>
+      </c>
+      <c r="E168" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="F168" s="24"/>
-      <c r="G168" s="24"/>
-      <c r="H168" s="24" t="s">
+      <c r="F168" s="25"/>
+      <c r="G168" s="25"/>
+      <c r="H168" s="25" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="169" ht="16.5" spans="1:8">
-      <c r="A169" s="23">
+      <c r="A169" s="24">
         <f t="shared" si="6"/>
         <v>10220007</v>
       </c>
-      <c r="B169" s="24">
+      <c r="B169" s="25">
         <v>102200</v>
       </c>
-      <c r="C169" s="24">
+      <c r="C169" s="25">
         <v>7</v>
       </c>
-      <c r="D169" s="24">
-        <v>0</v>
-      </c>
-      <c r="E169" s="24" t="s">
+      <c r="D169" s="25">
+        <v>0</v>
+      </c>
+      <c r="E169" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="F169" s="24"/>
-      <c r="G169" s="24"/>
-      <c r="H169" s="24" t="s">
+      <c r="F169" s="25"/>
+      <c r="G169" s="25"/>
+      <c r="H169" s="25" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="170" ht="16.5" spans="1:8">
-      <c r="A170" s="23">
+      <c r="A170" s="24">
         <f t="shared" si="6"/>
         <v>10220008</v>
       </c>
-      <c r="B170" s="24">
+      <c r="B170" s="25">
         <v>102200</v>
       </c>
-      <c r="C170" s="24">
+      <c r="C170" s="25">
         <v>8</v>
       </c>
-      <c r="D170" s="24">
-        <v>0</v>
-      </c>
-      <c r="E170" s="24" t="s">
+      <c r="D170" s="25">
+        <v>0</v>
+      </c>
+      <c r="E170" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="F170" s="24"/>
-      <c r="G170" s="24"/>
-      <c r="H170" s="24" t="s">
+      <c r="F170" s="25"/>
+      <c r="G170" s="25"/>
+      <c r="H170" s="25" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="171" ht="16.5" spans="1:8">
-      <c r="A171" s="23">
+      <c r="A171" s="24">
         <f t="shared" si="6"/>
         <v>10220009</v>
       </c>
-      <c r="B171" s="24">
+      <c r="B171" s="25">
         <v>102200</v>
       </c>
-      <c r="C171" s="24">
+      <c r="C171" s="25">
         <v>9</v>
       </c>
-      <c r="D171" s="24">
-        <v>0</v>
-      </c>
-      <c r="E171" s="24" t="s">
+      <c r="D171" s="25">
+        <v>0</v>
+      </c>
+      <c r="E171" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="F171" s="24"/>
-      <c r="G171" s="24"/>
-      <c r="H171" s="24" t="s">
+      <c r="F171" s="25"/>
+      <c r="G171" s="25"/>
+      <c r="H171" s="25" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="172" ht="16.5" spans="1:8">
-      <c r="A172" s="23">
+      <c r="A172" s="24">
         <f t="shared" si="6"/>
         <v>10220010</v>
       </c>
-      <c r="B172" s="24">
+      <c r="B172" s="25">
         <v>102200</v>
       </c>
-      <c r="C172" s="24">
+      <c r="C172" s="25">
         <v>10</v>
       </c>
-      <c r="D172" s="24">
-        <v>0</v>
-      </c>
-      <c r="E172" s="24" t="s">
+      <c r="D172" s="25">
+        <v>0</v>
+      </c>
+      <c r="E172" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="F172" s="24"/>
-      <c r="G172" s="24"/>
-      <c r="H172" s="24" t="s">
+      <c r="F172" s="25"/>
+      <c r="G172" s="25"/>
+      <c r="H172" s="25" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="173" ht="16.5" spans="1:8">
-      <c r="A173" s="23">
+      <c r="A173" s="24">
         <f t="shared" si="6"/>
         <v>10220011</v>
       </c>
-      <c r="B173" s="24">
+      <c r="B173" s="25">
         <v>102200</v>
       </c>
-      <c r="C173" s="24">
+      <c r="C173" s="25">
         <v>11</v>
       </c>
-      <c r="D173" s="24">
+      <c r="D173" s="25">
         <v>1</v>
       </c>
-      <c r="E173" s="24" t="s">
+      <c r="E173" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="F173" s="24"/>
-      <c r="G173" s="24"/>
-      <c r="H173" s="24" t="s">
+      <c r="F173" s="25"/>
+      <c r="G173" s="25"/>
+      <c r="H173" s="25" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="174" ht="16.5" spans="1:8">
-      <c r="A174" s="23">
+      <c r="A174" s="24">
         <f t="shared" si="6"/>
         <v>10220012</v>
       </c>
-      <c r="B174" s="24">
+      <c r="B174" s="25">
         <v>102200</v>
       </c>
-      <c r="C174" s="24">
+      <c r="C174" s="25">
         <v>12</v>
       </c>
-      <c r="D174" s="24">
+      <c r="D174" s="25">
         <v>1</v>
       </c>
-      <c r="E174" s="24" t="s">
+      <c r="E174" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="F174" s="24"/>
-      <c r="G174" s="24"/>
-      <c r="H174" s="24" t="s">
+      <c r="F174" s="25"/>
+      <c r="G174" s="25"/>
+      <c r="H174" s="25" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="175" ht="16.5" spans="1:8">
-      <c r="A175" s="23">
+      <c r="A175" s="24">
         <f t="shared" si="6"/>
         <v>10220013</v>
       </c>
-      <c r="B175" s="24">
+      <c r="B175" s="25">
         <v>102200</v>
       </c>
-      <c r="C175" s="24">
+      <c r="C175" s="25">
         <v>13</v>
       </c>
-      <c r="D175" s="24">
+      <c r="D175" s="25">
         <v>1</v>
       </c>
-      <c r="E175" s="24" t="s">
+      <c r="E175" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="F175" s="24"/>
-      <c r="G175" s="24"/>
-      <c r="H175" s="24" t="s">
+      <c r="F175" s="25"/>
+      <c r="G175" s="25"/>
+      <c r="H175" s="25" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="1:8">
-      <c r="A176" s="23">
+      <c r="A176" s="24">
         <f t="shared" si="6"/>
         <v>10220014</v>
       </c>
-      <c r="B176" s="24">
+      <c r="B176" s="25">
         <v>102200</v>
       </c>
-      <c r="C176" s="24">
+      <c r="C176" s="25">
         <v>14</v>
       </c>
-      <c r="D176" s="24">
+      <c r="D176" s="25">
         <v>2</v>
       </c>
-      <c r="E176" s="24" t="s">
+      <c r="E176" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="F176" s="24"/>
-      <c r="G176" s="24"/>
-      <c r="H176" s="24" t="s">
+      <c r="F176" s="25"/>
+      <c r="G176" s="25"/>
+      <c r="H176" s="25" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="177" ht="16.5" spans="1:8">
-      <c r="A177" s="23">
+      <c r="A177" s="24">
         <f t="shared" si="6"/>
         <v>10220015</v>
       </c>
-      <c r="B177" s="24">
+      <c r="B177" s="25">
         <v>102200</v>
       </c>
-      <c r="C177" s="24">
+      <c r="C177" s="25">
         <v>15</v>
       </c>
-      <c r="D177" s="24">
+      <c r="D177" s="25">
         <v>3</v>
       </c>
-      <c r="E177" s="24" t="s">
+      <c r="E177" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="F177" s="24"/>
-      <c r="G177" s="24"/>
-      <c r="H177" s="24" t="s">
+      <c r="F177" s="25"/>
+      <c r="G177" s="25"/>
+      <c r="H177" s="25" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="178" ht="16.5" spans="1:8">
-      <c r="A178" s="23">
+      <c r="A178" s="24">
         <f t="shared" si="6"/>
         <v>10220016</v>
       </c>
-      <c r="B178" s="24">
+      <c r="B178" s="25">
         <v>102200</v>
       </c>
-      <c r="C178" s="24">
+      <c r="C178" s="25">
         <v>16</v>
       </c>
-      <c r="D178" s="24">
+      <c r="D178" s="25">
         <v>3</v>
       </c>
-      <c r="E178" s="24" t="s">
+      <c r="E178" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="F178" s="24"/>
-      <c r="G178" s="24"/>
-      <c r="H178" s="24" t="s">
+      <c r="F178" s="25"/>
+      <c r="G178" s="25"/>
+      <c r="H178" s="25" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="179" ht="16.5" spans="1:8">
-      <c r="A179" s="23">
+      <c r="A179" s="24">
         <f t="shared" si="6"/>
         <v>10220017</v>
       </c>
-      <c r="B179" s="24">
+      <c r="B179" s="25">
         <v>102200</v>
       </c>
-      <c r="C179" s="24">
+      <c r="C179" s="25">
         <v>17</v>
       </c>
-      <c r="D179" s="24">
+      <c r="D179" s="25">
         <v>3</v>
       </c>
-      <c r="E179" s="24" t="s">
+      <c r="E179" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="F179" s="24"/>
-      <c r="G179" s="24"/>
-      <c r="H179" s="24" t="s">
+      <c r="F179" s="25"/>
+      <c r="G179" s="25"/>
+      <c r="H179" s="25" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="180" ht="16.5" spans="1:8">
-      <c r="A180" s="23">
+      <c r="A180" s="24">
         <f t="shared" si="6"/>
         <v>10220018</v>
       </c>
-      <c r="B180" s="24">
+      <c r="B180" s="25">
         <v>102200</v>
       </c>
-      <c r="C180" s="24">
+      <c r="C180" s="25">
         <v>18</v>
       </c>
-      <c r="D180" s="24">
+      <c r="D180" s="25">
         <v>3</v>
       </c>
-      <c r="E180" s="24" t="s">
+      <c r="E180" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="F180" s="24"/>
-      <c r="G180" s="24"/>
-      <c r="H180" s="24" t="s">
+      <c r="F180" s="25"/>
+      <c r="G180" s="25"/>
+      <c r="H180" s="25" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="181" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A181" s="26">
+    <row r="181" ht="16.5" spans="1:8">
+      <c r="A181" s="24">
+        <f t="shared" si="6"/>
+        <v>10220019</v>
+      </c>
+      <c r="B181" s="25">
+        <v>102200</v>
+      </c>
+      <c r="C181" s="25">
+        <v>19</v>
+      </c>
+      <c r="D181" s="25">
+        <v>2</v>
+      </c>
+      <c r="E181" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="F181" s="25"/>
+      <c r="G181" s="25"/>
+      <c r="H181" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="182" ht="16.5" spans="1:8">
+      <c r="A182" s="24">
+        <f t="shared" si="6"/>
+        <v>10220020</v>
+      </c>
+      <c r="B182" s="25">
+        <v>102200</v>
+      </c>
+      <c r="C182" s="25">
+        <v>20</v>
+      </c>
+      <c r="D182" s="25">
+        <v>2</v>
+      </c>
+      <c r="E182" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="F182" s="25"/>
+      <c r="G182" s="25"/>
+      <c r="H182" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="183" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A183" s="27">
         <v>10210001</v>
       </c>
-      <c r="B181" s="26">
+      <c r="B183" s="27">
         <v>102100</v>
       </c>
-      <c r="C181" s="26">
+      <c r="C183" s="27">
         <v>1</v>
       </c>
-      <c r="D181" s="26">
-        <v>0</v>
-      </c>
-      <c r="E181" s="27" t="s">
+      <c r="D183" s="27">
+        <v>0</v>
+      </c>
+      <c r="E183" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="F181" s="26"/>
-      <c r="G181" s="26"/>
-      <c r="H181" s="27" t="s">
+      <c r="F183" s="27"/>
+      <c r="G183" s="27"/>
+      <c r="H183" s="27" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="182" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A182" s="26">
+    <row r="184" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A184" s="27">
         <v>10210002</v>
       </c>
-      <c r="B182" s="26">
+      <c r="B184" s="27">
         <v>102100</v>
       </c>
-      <c r="C182" s="26">
+      <c r="C184" s="27">
         <v>2</v>
       </c>
-      <c r="D182" s="26">
-        <v>0</v>
-      </c>
-      <c r="E182" s="27" t="s">
+      <c r="D184" s="27">
+        <v>0</v>
+      </c>
+      <c r="E184" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="F182" s="26"/>
-      <c r="G182" s="26"/>
-      <c r="H182" s="27" t="s">
+      <c r="F184" s="27"/>
+      <c r="G184" s="27"/>
+      <c r="H184" s="27" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="183" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A183" s="26">
+    <row r="185" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A185" s="27">
         <v>10210003</v>
       </c>
-      <c r="B183" s="26">
+      <c r="B185" s="27">
         <v>102100</v>
       </c>
-      <c r="C183" s="26">
+      <c r="C185" s="27">
         <v>3</v>
       </c>
-      <c r="D183" s="26">
-        <v>0</v>
-      </c>
-      <c r="E183" s="27" t="s">
+      <c r="D185" s="27">
+        <v>0</v>
+      </c>
+      <c r="E185" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="F183" s="26"/>
-      <c r="G183" s="26"/>
-      <c r="H183" s="27" t="s">
+      <c r="F185" s="27"/>
+      <c r="G185" s="27"/>
+      <c r="H185" s="27" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="184" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A184" s="26">
+    <row r="186" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A186" s="27">
         <v>10210004</v>
       </c>
-      <c r="B184" s="26">
+      <c r="B186" s="27">
         <v>102100</v>
       </c>
-      <c r="C184" s="26">
+      <c r="C186" s="27">
         <v>4</v>
       </c>
-      <c r="D184" s="26">
-        <v>0</v>
-      </c>
-      <c r="E184" s="27" t="s">
+      <c r="D186" s="27">
+        <v>0</v>
+      </c>
+      <c r="E186" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="27" t="s">
+      <c r="F186" s="27"/>
+      <c r="G186" s="27"/>
+      <c r="H186" s="27" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="185" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A185" s="26">
+    <row r="187" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A187" s="27">
         <v>10210005</v>
       </c>
-      <c r="B185" s="26">
+      <c r="B187" s="27">
         <v>102100</v>
       </c>
-      <c r="C185" s="26">
+      <c r="C187" s="27">
         <v>5</v>
       </c>
-      <c r="D185" s="26">
-        <v>0</v>
-      </c>
-      <c r="E185" s="27" t="s">
+      <c r="D187" s="27">
+        <v>0</v>
+      </c>
+      <c r="E187" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="F185" s="26"/>
-      <c r="G185" s="26"/>
-      <c r="H185" s="27" t="s">
+      <c r="F187" s="27"/>
+      <c r="G187" s="27"/>
+      <c r="H187" s="27" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="186" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A186" s="26">
+    <row r="188" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A188" s="27">
         <v>10210006</v>
       </c>
-      <c r="B186" s="26">
+      <c r="B188" s="27">
         <v>102100</v>
       </c>
-      <c r="C186" s="26">
+      <c r="C188" s="27">
         <v>6</v>
       </c>
-      <c r="D186" s="26">
-        <v>0</v>
-      </c>
-      <c r="E186" s="27" t="s">
+      <c r="D188" s="27">
+        <v>0</v>
+      </c>
+      <c r="E188" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="F186" s="26"/>
-      <c r="G186" s="26"/>
-      <c r="H186" s="26" t="s">
+      <c r="F188" s="27"/>
+      <c r="G188" s="27"/>
+      <c r="H188" s="27" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="187" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A187" s="26">
+    <row r="189" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A189" s="27">
         <v>10210007</v>
       </c>
-      <c r="B187" s="26">
+      <c r="B189" s="27">
         <v>102100</v>
       </c>
-      <c r="C187" s="26">
+      <c r="C189" s="27">
         <v>7</v>
       </c>
-      <c r="D187" s="26">
-        <v>0</v>
-      </c>
-      <c r="E187" s="27" t="s">
+      <c r="D189" s="27">
+        <v>0</v>
+      </c>
+      <c r="E189" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="F187" s="26"/>
-      <c r="G187" s="26"/>
-      <c r="H187" s="28" t="s">
+      <c r="F189" s="27"/>
+      <c r="G189" s="27"/>
+      <c r="H189" s="28" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="188" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A188" s="26">
+    <row r="190" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A190" s="27">
         <v>10210008</v>
       </c>
-      <c r="B188" s="26">
+      <c r="B190" s="27">
         <v>102100</v>
       </c>
-      <c r="C188" s="26">
+      <c r="C190" s="27">
         <v>8</v>
       </c>
-      <c r="D188" s="26">
-        <v>0</v>
-      </c>
-      <c r="E188" s="27" t="s">
+      <c r="D190" s="27">
+        <v>0</v>
+      </c>
+      <c r="E190" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="F188" s="26"/>
-      <c r="G188" s="26"/>
-      <c r="H188" s="26" t="s">
+      <c r="F190" s="27"/>
+      <c r="G190" s="27"/>
+      <c r="H190" s="27" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="189" ht="16.5" customHeight="1" spans="1:8">
-      <c r="A189" s="26">
+    <row r="191" ht="16.5" customHeight="1" spans="1:8">
+      <c r="A191" s="27">
         <v>10210009</v>
       </c>
-      <c r="B189" s="26">
+      <c r="B191" s="27">
         <v>102100</v>
       </c>
-      <c r="C189" s="26">
+      <c r="C191" s="27">
         <v>9</v>
       </c>
-      <c r="D189" s="26">
-        <v>0</v>
-      </c>
-      <c r="E189" s="27" t="s">
+      <c r="D191" s="27">
+        <v>0</v>
+      </c>
+      <c r="E191" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="F189" s="26"/>
-      <c r="G189" s="26"/>
-      <c r="H189" s="26" t="s">
+      <c r="F191" s="27"/>
+      <c r="G191" s="27"/>
+      <c r="H191" s="27" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="190" ht="16.5" spans="1:8">
-      <c r="A190" s="26">
+    <row r="192" ht="16.5" spans="1:8">
+      <c r="A192" s="27">
         <v>10210010</v>
       </c>
-      <c r="B190" s="26">
+      <c r="B192" s="27">
         <v>102100</v>
       </c>
-      <c r="C190" s="26">
+      <c r="C192" s="27">
         <v>10</v>
       </c>
-      <c r="D190" s="26">
+      <c r="D192" s="27">
         <v>2</v>
       </c>
-      <c r="E190" s="27" t="s">
+      <c r="E192" s="27" t="s">
         <v>271</v>
-      </c>
-      <c r="F190" s="28"/>
-      <c r="G190" s="28"/>
-      <c r="H190" s="27" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="191" ht="16.5" spans="1:8">
-      <c r="A191" s="26">
-        <v>10210011</v>
-      </c>
-      <c r="B191" s="26">
-        <v>102100</v>
-      </c>
-      <c r="C191" s="26">
-        <v>11</v>
-      </c>
-      <c r="D191" s="26">
-        <v>1</v>
-      </c>
-      <c r="E191" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="F191" s="28"/>
-      <c r="G191" s="28"/>
-      <c r="H191" s="27" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="192" ht="16.5" spans="1:8">
-      <c r="A192" s="26">
-        <v>10210012</v>
-      </c>
-      <c r="B192" s="26">
-        <v>102100</v>
-      </c>
-      <c r="C192" s="26">
-        <v>12</v>
-      </c>
-      <c r="D192" s="26">
-        <v>2</v>
-      </c>
-      <c r="E192" s="27" t="s">
-        <v>274</v>
       </c>
       <c r="F192" s="28"/>
       <c r="G192" s="28"/>
       <c r="H192" s="27" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="193" ht="17.25" spans="1:8">
-      <c r="A193" s="26">
-        <v>10210013</v>
-      </c>
-      <c r="B193" s="26">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="193" ht="16.5" spans="1:8">
+      <c r="A193" s="27">
+        <v>10210011</v>
+      </c>
+      <c r="B193" s="27">
         <v>102100</v>
       </c>
-      <c r="C193" s="26">
-        <v>13</v>
-      </c>
-      <c r="D193" s="26">
-        <v>3</v>
+      <c r="C193" s="27">
+        <v>11</v>
+      </c>
+      <c r="D193" s="27">
+        <v>1</v>
       </c>
       <c r="E193" s="27" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F193" s="28"/>
       <c r="G193" s="28"/>
-      <c r="H193" s="29" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="194" ht="17.25" spans="1:8">
-      <c r="A194" s="26">
-        <v>10210014</v>
-      </c>
-      <c r="B194" s="26">
+      <c r="H193" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="194" ht="16.5" spans="1:8">
+      <c r="A194" s="27">
+        <v>10210012</v>
+      </c>
+      <c r="B194" s="27">
         <v>102100</v>
       </c>
-      <c r="C194" s="26">
-        <v>14</v>
-      </c>
-      <c r="D194" s="26">
-        <v>3</v>
+      <c r="C194" s="27">
+        <v>12</v>
+      </c>
+      <c r="D194" s="27">
+        <v>2</v>
       </c>
       <c r="E194" s="27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F194" s="28"/>
       <c r="G194" s="28"/>
-      <c r="H194" s="29" t="s">
-        <v>224</v>
+      <c r="H194" s="27" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="195" ht="17.25" spans="1:8">
-      <c r="A195" s="26">
-        <v>10210015</v>
-      </c>
-      <c r="B195" s="26">
+      <c r="A195" s="27">
+        <v>10210013</v>
+      </c>
+      <c r="B195" s="27">
         <v>102100</v>
       </c>
-      <c r="C195" s="26">
-        <v>15</v>
-      </c>
-      <c r="D195" s="26">
+      <c r="C195" s="27">
+        <v>13</v>
+      </c>
+      <c r="D195" s="27">
         <v>3</v>
       </c>
       <c r="E195" s="27" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F195" s="28"/>
       <c r="G195" s="28"/>
       <c r="H195" s="29" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="196" ht="17.25" spans="1:8">
-      <c r="A196" s="26">
-        <v>10210016</v>
-      </c>
-      <c r="B196" s="26">
+      <c r="A196" s="27">
+        <v>10210014</v>
+      </c>
+      <c r="B196" s="27">
         <v>102100</v>
       </c>
-      <c r="C196" s="26">
-        <v>16</v>
-      </c>
-      <c r="D196" s="26">
+      <c r="C196" s="27">
+        <v>14</v>
+      </c>
+      <c r="D196" s="27">
         <v>3</v>
       </c>
       <c r="E196" s="27" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F196" s="28"/>
       <c r="G196" s="28"/>
       <c r="H196" s="29" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="197" ht="17.25" spans="1:8">
+      <c r="A197" s="27">
+        <v>10210015</v>
+      </c>
+      <c r="B197" s="27">
+        <v>102100</v>
+      </c>
+      <c r="C197" s="27">
+        <v>15</v>
+      </c>
+      <c r="D197" s="27">
+        <v>3</v>
+      </c>
+      <c r="E197" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="F197" s="28"/>
+      <c r="G197" s="28"/>
+      <c r="H197" s="29" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="198" ht="17.25" spans="1:8">
+      <c r="A198" s="27">
+        <v>10210016</v>
+      </c>
+      <c r="B198" s="27">
+        <v>102100</v>
+      </c>
+      <c r="C198" s="27">
+        <v>16</v>
+      </c>
+      <c r="D198" s="27">
+        <v>3</v>
+      </c>
+      <c r="E198" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="F198" s="28"/>
+      <c r="G198" s="28"/>
+      <c r="H198" s="29" t="s">
         <v>228</v>
       </c>
     </row>
+    <row r="199" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A199" s="30">
+        <v>10180001</v>
+      </c>
+      <c r="B199" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C199" s="30">
+        <v>1</v>
+      </c>
+      <c r="D199" s="30"/>
+      <c r="E199" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="F199" s="31"/>
+      <c r="G199" s="31"/>
+      <c r="H199" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A200" s="30">
+        <v>10180002</v>
+      </c>
+      <c r="B200" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C200" s="30">
+        <v>2</v>
+      </c>
+      <c r="D200" s="30"/>
+      <c r="E200" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="F200" s="31"/>
+      <c r="G200" s="31"/>
+      <c r="H200" s="33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="201" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A201" s="30">
+        <v>10180003</v>
+      </c>
+      <c r="B201" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C201" s="30">
+        <v>3</v>
+      </c>
+      <c r="D201" s="30"/>
+      <c r="E201" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="F201" s="31"/>
+      <c r="G201" s="31"/>
+      <c r="H201" s="33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A202" s="30">
+        <v>10180004</v>
+      </c>
+      <c r="B202" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C202" s="30">
+        <v>4</v>
+      </c>
+      <c r="D202" s="30"/>
+      <c r="E202" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="F202" s="31"/>
+      <c r="G202" s="31"/>
+      <c r="H202" s="33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="203" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A203" s="30">
+        <v>10180005</v>
+      </c>
+      <c r="B203" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C203" s="30">
+        <v>5</v>
+      </c>
+      <c r="D203" s="30"/>
+      <c r="E203" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="F203" s="31"/>
+      <c r="G203" s="31"/>
+      <c r="H203" s="33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="204" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A204" s="30">
+        <v>10180006</v>
+      </c>
+      <c r="B204" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C204" s="30">
+        <v>6</v>
+      </c>
+      <c r="D204" s="30"/>
+      <c r="E204" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="F204" s="31"/>
+      <c r="G204" s="31"/>
+      <c r="H204" s="33" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="205" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A205" s="30">
+        <v>10180007</v>
+      </c>
+      <c r="B205" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C205" s="30">
+        <v>7</v>
+      </c>
+      <c r="D205" s="30"/>
+      <c r="E205" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="F205" s="31"/>
+      <c r="G205" s="31"/>
+      <c r="H205" s="33" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="206" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A206" s="30">
+        <v>10180008</v>
+      </c>
+      <c r="B206" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C206" s="30">
+        <v>8</v>
+      </c>
+      <c r="D206" s="30"/>
+      <c r="E206" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="F206" s="31"/>
+      <c r="G206" s="31"/>
+      <c r="H206" s="33" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="207" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A207" s="30">
+        <v>10180009</v>
+      </c>
+      <c r="B207" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C207" s="30">
+        <v>9</v>
+      </c>
+      <c r="D207" s="30"/>
+      <c r="E207" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="F207" s="31"/>
+      <c r="G207" s="31"/>
+      <c r="H207" s="33" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="208" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A208" s="30">
+        <v>10180010</v>
+      </c>
+      <c r="B208" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C208" s="30">
+        <v>10</v>
+      </c>
+      <c r="D208" s="30"/>
+      <c r="E208" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="F208" s="31"/>
+      <c r="G208" s="31"/>
+      <c r="H208" s="33" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="209" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A209" s="30">
+        <v>10180011</v>
+      </c>
+      <c r="B209" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C209" s="30">
+        <v>11</v>
+      </c>
+      <c r="D209" s="30"/>
+      <c r="E209" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="F209" s="31"/>
+      <c r="G209" s="31"/>
+      <c r="H209" s="33" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="210" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A210" s="30">
+        <v>10180012</v>
+      </c>
+      <c r="B210" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C210" s="30">
+        <v>12</v>
+      </c>
+      <c r="D210" s="30"/>
+      <c r="E210" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="F210" s="31"/>
+      <c r="G210" s="31"/>
+      <c r="H210" s="33" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="211" customFormat="1" ht="17.25" spans="1:8">
+      <c r="A211" s="30">
+        <v>10180013</v>
+      </c>
+      <c r="B211" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C211" s="30">
+        <v>13</v>
+      </c>
+      <c r="D211" s="30"/>
+      <c r="E211" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F211" s="31"/>
+      <c r="G211" s="31"/>
+      <c r="H211" s="34" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A212" s="30">
+        <v>10180014</v>
+      </c>
+      <c r="B212" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C212" s="30">
+        <v>14</v>
+      </c>
+      <c r="D212" s="30"/>
+      <c r="E212" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="F212" s="31"/>
+      <c r="G212" s="31"/>
+      <c r="H212" s="31" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="213" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A213" s="30">
+        <v>10180015</v>
+      </c>
+      <c r="B213" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C213" s="30">
+        <v>15</v>
+      </c>
+      <c r="D213" s="30"/>
+      <c r="E213" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="F213" s="31"/>
+      <c r="G213" s="31"/>
+      <c r="H213" s="31" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="214" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A214" s="30">
+        <v>10180016</v>
+      </c>
+      <c r="B214" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C214" s="30">
+        <v>16</v>
+      </c>
+      <c r="D214" s="30"/>
+      <c r="E214" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="F214" s="31"/>
+      <c r="G214" s="31"/>
+      <c r="H214" s="31" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="215" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A215" s="30">
+        <v>10180017</v>
+      </c>
+      <c r="B215" s="30">
+        <v>101800</v>
+      </c>
+      <c r="C215" s="30">
+        <v>17</v>
+      </c>
+      <c r="D215" s="30"/>
+      <c r="E215" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="F215" s="31"/>
+      <c r="G215" s="31"/>
+      <c r="H215" s="31" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="216" s="1" customFormat="1" ht="16.5"/>
+    <row r="217" s="1" customFormat="1" ht="16.5"/>
+    <row r="218" s="1" customFormat="1" ht="16.5"/>
+    <row r="219" s="1" customFormat="1" ht="16.5"/>
+    <row r="220" s="1" customFormat="1" ht="16.5"/>
+    <row r="221" s="1" customFormat="1" ht="16.5"/>
+    <row r="222" s="1" customFormat="1" ht="16.5"/>
+    <row r="223" s="1" customFormat="1" ht="16.5"/>
+    <row r="224" s="1" customFormat="1" ht="16.5"/>
   </sheetData>
   <conditionalFormatting sqref="F2:G2">
     <cfRule type="expression" dxfId="0" priority="2">

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="322">
   <si>
     <t>图标</t>
   </si>
@@ -1021,6 +1021,66 @@
   </si>
   <si>
     <t>lqjx_icon_17.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_1.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_2.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_3.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_4.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_5.png</t>
+  </si>
+  <si>
+    <t>亡灵战士</t>
+  </si>
+  <si>
+    <t>hbwz_icon_6.png</t>
+  </si>
+  <si>
+    <t>亡灵法师</t>
+  </si>
+  <si>
+    <t>hbwz_icon_7.png</t>
+  </si>
+  <si>
+    <t>憎恶</t>
+  </si>
+  <si>
+    <t>hbwz_icon_8.png</t>
+  </si>
+  <si>
+    <t>冰龙</t>
+  </si>
+  <si>
+    <t>hbwz_icon_9.png</t>
+  </si>
+  <si>
+    <t>亡灵大军</t>
+  </si>
+  <si>
+    <t>hbwz_icon_10.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_11.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_12.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_13.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_14.png</t>
+  </si>
+  <si>
+    <t>hbwz_icon_15.png</t>
   </si>
 </sst>
 </file>
@@ -1229,12 +1289,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1789,7 +1849,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1890,6 +1950,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -2215,7 +2281,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M224"/>
+  <dimension ref="A1:M230"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -7323,7 +7389,9 @@
       <c r="C199" s="30">
         <v>1</v>
       </c>
-      <c r="D199" s="30"/>
+      <c r="D199" s="30">
+        <v>0</v>
+      </c>
       <c r="E199" s="30" t="s">
         <v>279</v>
       </c>
@@ -7343,7 +7411,9 @@
       <c r="C200" s="30">
         <v>2</v>
       </c>
-      <c r="D200" s="30"/>
+      <c r="D200" s="30">
+        <v>0</v>
+      </c>
       <c r="E200" s="30" t="s">
         <v>280</v>
       </c>
@@ -7363,7 +7433,9 @@
       <c r="C201" s="30">
         <v>3</v>
       </c>
-      <c r="D201" s="30"/>
+      <c r="D201" s="30">
+        <v>0</v>
+      </c>
       <c r="E201" s="30" t="s">
         <v>281</v>
       </c>
@@ -7383,7 +7455,9 @@
       <c r="C202" s="30">
         <v>4</v>
       </c>
-      <c r="D202" s="30"/>
+      <c r="D202" s="30">
+        <v>0</v>
+      </c>
       <c r="E202" s="30" t="s">
         <v>282</v>
       </c>
@@ -7403,7 +7477,9 @@
       <c r="C203" s="30">
         <v>5</v>
       </c>
-      <c r="D203" s="30"/>
+      <c r="D203" s="30">
+        <v>0</v>
+      </c>
       <c r="E203" s="30" t="s">
         <v>283</v>
       </c>
@@ -7423,7 +7499,9 @@
       <c r="C204" s="30">
         <v>6</v>
       </c>
-      <c r="D204" s="30"/>
+      <c r="D204" s="30">
+        <v>0</v>
+      </c>
       <c r="E204" s="30" t="s">
         <v>284</v>
       </c>
@@ -7443,7 +7521,9 @@
       <c r="C205" s="30">
         <v>7</v>
       </c>
-      <c r="D205" s="30"/>
+      <c r="D205" s="30">
+        <v>0</v>
+      </c>
       <c r="E205" s="30" t="s">
         <v>286</v>
       </c>
@@ -7463,7 +7543,9 @@
       <c r="C206" s="30">
         <v>8</v>
       </c>
-      <c r="D206" s="30"/>
+      <c r="D206" s="30">
+        <v>0</v>
+      </c>
       <c r="E206" s="30" t="s">
         <v>288</v>
       </c>
@@ -7483,7 +7565,9 @@
       <c r="C207" s="30">
         <v>9</v>
       </c>
-      <c r="D207" s="30"/>
+      <c r="D207" s="30">
+        <v>0</v>
+      </c>
       <c r="E207" s="30" t="s">
         <v>290</v>
       </c>
@@ -7503,7 +7587,9 @@
       <c r="C208" s="30">
         <v>10</v>
       </c>
-      <c r="D208" s="30"/>
+      <c r="D208" s="30">
+        <v>0</v>
+      </c>
       <c r="E208" s="30" t="s">
         <v>292</v>
       </c>
@@ -7523,7 +7609,9 @@
       <c r="C209" s="30">
         <v>11</v>
       </c>
-      <c r="D209" s="30"/>
+      <c r="D209" s="30">
+        <v>1</v>
+      </c>
       <c r="E209" s="30" t="s">
         <v>294</v>
       </c>
@@ -7543,7 +7631,9 @@
       <c r="C210" s="30">
         <v>12</v>
       </c>
-      <c r="D210" s="30"/>
+      <c r="D210" s="30">
+        <v>2</v>
+      </c>
       <c r="E210" s="30" t="s">
         <v>295</v>
       </c>
@@ -7563,13 +7653,15 @@
       <c r="C211" s="30">
         <v>13</v>
       </c>
-      <c r="D211" s="30"/>
+      <c r="D211" s="30">
+        <v>2</v>
+      </c>
       <c r="E211" s="30" t="s">
         <v>296</v>
       </c>
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
-      <c r="H211" s="34" t="s">
+      <c r="H211" s="36" t="s">
         <v>297</v>
       </c>
     </row>
@@ -7583,13 +7675,15 @@
       <c r="C212" s="30">
         <v>14</v>
       </c>
-      <c r="D212" s="30"/>
+      <c r="D212" s="30">
+        <v>3</v>
+      </c>
       <c r="E212" s="30" t="s">
         <v>298</v>
       </c>
       <c r="F212" s="31"/>
       <c r="G212" s="31"/>
-      <c r="H212" s="31" t="s">
+      <c r="H212" s="30" t="s">
         <v>222</v>
       </c>
     </row>
@@ -7603,13 +7697,15 @@
       <c r="C213" s="30">
         <v>15</v>
       </c>
-      <c r="D213" s="30"/>
+      <c r="D213" s="30">
+        <v>3</v>
+      </c>
       <c r="E213" s="30" t="s">
         <v>299</v>
       </c>
       <c r="F213" s="31"/>
       <c r="G213" s="31"/>
-      <c r="H213" s="31" t="s">
+      <c r="H213" s="30" t="s">
         <v>224</v>
       </c>
     </row>
@@ -7623,13 +7719,15 @@
       <c r="C214" s="30">
         <v>16</v>
       </c>
-      <c r="D214" s="30"/>
+      <c r="D214" s="30">
+        <v>3</v>
+      </c>
       <c r="E214" s="30" t="s">
         <v>300</v>
       </c>
       <c r="F214" s="31"/>
       <c r="G214" s="31"/>
-      <c r="H214" s="31" t="s">
+      <c r="H214" s="30" t="s">
         <v>226</v>
       </c>
     </row>
@@ -7643,25 +7741,333 @@
       <c r="C215" s="30">
         <v>17</v>
       </c>
-      <c r="D215" s="30"/>
+      <c r="D215" s="30">
+        <v>3</v>
+      </c>
       <c r="E215" s="30" t="s">
         <v>301</v>
       </c>
       <c r="F215" s="31"/>
       <c r="G215" s="31"/>
-      <c r="H215" s="31" t="s">
+      <c r="H215" s="30" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="216" s="1" customFormat="1" ht="16.5"/>
-    <row r="217" s="1" customFormat="1" ht="16.5"/>
-    <row r="218" s="1" customFormat="1" ht="16.5"/>
-    <row r="219" s="1" customFormat="1" ht="16.5"/>
-    <row r="220" s="1" customFormat="1" ht="16.5"/>
-    <row r="221" s="1" customFormat="1" ht="16.5"/>
-    <row r="222" s="1" customFormat="1" ht="16.5"/>
-    <row r="223" s="1" customFormat="1" ht="16.5"/>
-    <row r="224" s="1" customFormat="1" ht="16.5"/>
+    <row r="216" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A216" s="34">
+        <f>B216*100+C216</f>
+        <v>10250001</v>
+      </c>
+      <c r="B216" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C216" s="34">
+        <v>1</v>
+      </c>
+      <c r="D216" s="34"/>
+      <c r="E216" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="F216" s="35"/>
+      <c r="G216" s="35"/>
+      <c r="H216" s="34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="217" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A217" s="34">
+        <f t="shared" ref="A217:A226" si="7">B217*100+C217</f>
+        <v>10250002</v>
+      </c>
+      <c r="B217" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C217" s="34">
+        <v>2</v>
+      </c>
+      <c r="D217" s="34"/>
+      <c r="E217" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="F217" s="35"/>
+      <c r="G217" s="35"/>
+      <c r="H217" s="34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="218" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A218" s="34">
+        <f t="shared" si="7"/>
+        <v>10250003</v>
+      </c>
+      <c r="B218" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C218" s="34">
+        <v>3</v>
+      </c>
+      <c r="D218" s="34"/>
+      <c r="E218" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="F218" s="35"/>
+      <c r="G218" s="35"/>
+      <c r="H218" s="34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="219" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A219" s="34">
+        <f t="shared" si="7"/>
+        <v>10250004</v>
+      </c>
+      <c r="B219" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C219" s="34">
+        <v>4</v>
+      </c>
+      <c r="D219" s="34"/>
+      <c r="E219" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="F219" s="35"/>
+      <c r="G219" s="35"/>
+      <c r="H219" s="34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="220" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A220" s="34">
+        <f t="shared" si="7"/>
+        <v>10250005</v>
+      </c>
+      <c r="B220" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C220" s="34">
+        <v>5</v>
+      </c>
+      <c r="D220" s="34"/>
+      <c r="E220" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="F220" s="35"/>
+      <c r="G220" s="35"/>
+      <c r="H220" s="34" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="221" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A221" s="34">
+        <f t="shared" si="7"/>
+        <v>10250006</v>
+      </c>
+      <c r="B221" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C221" s="34">
+        <v>6</v>
+      </c>
+      <c r="D221" s="34"/>
+      <c r="E221" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="F221" s="35"/>
+      <c r="G221" s="35"/>
+      <c r="H221" s="34" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="222" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A222" s="34">
+        <f t="shared" si="7"/>
+        <v>10250007</v>
+      </c>
+      <c r="B222" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C222" s="34">
+        <v>7</v>
+      </c>
+      <c r="D222" s="34"/>
+      <c r="E222" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="F222" s="35"/>
+      <c r="G222" s="35"/>
+      <c r="H222" s="34" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="223" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A223" s="34">
+        <f t="shared" si="7"/>
+        <v>10250008</v>
+      </c>
+      <c r="B223" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C223" s="34">
+        <v>8</v>
+      </c>
+      <c r="D223" s="34"/>
+      <c r="E223" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="F223" s="35"/>
+      <c r="G223" s="35"/>
+      <c r="H223" s="34" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="224" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A224" s="34">
+        <f t="shared" si="7"/>
+        <v>10250009</v>
+      </c>
+      <c r="B224" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C224" s="34">
+        <v>9</v>
+      </c>
+      <c r="D224" s="34"/>
+      <c r="E224" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="F224" s="35"/>
+      <c r="G224" s="35"/>
+      <c r="H224" s="34" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="225" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A225" s="34">
+        <f t="shared" si="7"/>
+        <v>10250010</v>
+      </c>
+      <c r="B225" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C225" s="34">
+        <v>10</v>
+      </c>
+      <c r="D225" s="34"/>
+      <c r="E225" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="F225" s="35"/>
+      <c r="G225" s="35"/>
+      <c r="H225" s="34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="226" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A226" s="34">
+        <f t="shared" si="7"/>
+        <v>10250011</v>
+      </c>
+      <c r="B226" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C226" s="34">
+        <v>11</v>
+      </c>
+      <c r="D226" s="34"/>
+      <c r="E226" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="F226" s="35"/>
+      <c r="G226" s="35"/>
+      <c r="H226" s="34" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="227" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A227" s="34">
+        <f>B227*100+C227</f>
+        <v>10250012</v>
+      </c>
+      <c r="B227" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C227" s="34">
+        <v>12</v>
+      </c>
+      <c r="D227" s="34"/>
+      <c r="E227" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="F227" s="35"/>
+      <c r="G227" s="35"/>
+      <c r="H227" s="34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="228" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A228" s="34">
+        <f>B228*100+C228</f>
+        <v>10250013</v>
+      </c>
+      <c r="B228" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C228" s="34">
+        <v>13</v>
+      </c>
+      <c r="D228" s="34"/>
+      <c r="E228" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="F228" s="35"/>
+      <c r="G228" s="35"/>
+      <c r="H228" s="34" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="229" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A229" s="34">
+        <f>B229*100+C229</f>
+        <v>10250014</v>
+      </c>
+      <c r="B229" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C229" s="34">
+        <v>14</v>
+      </c>
+      <c r="D229" s="34"/>
+      <c r="E229" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="F229" s="35"/>
+      <c r="G229" s="35"/>
+      <c r="H229" s="34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="230" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A230" s="34">
+        <f>B230*100+C230</f>
+        <v>10250015</v>
+      </c>
+      <c r="B230" s="34">
+        <v>102500</v>
+      </c>
+      <c r="C230" s="34">
+        <v>15</v>
+      </c>
+      <c r="D230" s="34"/>
+      <c r="E230" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="F230" s="35"/>
+      <c r="G230" s="35"/>
+      <c r="H230" s="34" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F2:G2">
     <cfRule type="expression" dxfId="0" priority="2">

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -876,82 +876,82 @@
     <t>LS_icon_16.png</t>
   </si>
   <si>
-    <t>jkcz_icon_1.png</t>
-  </si>
-  <si>
-    <t>双枪</t>
-  </si>
-  <si>
-    <t>jkcz_icon_2.png</t>
-  </si>
-  <si>
-    <t>骷髅头</t>
-  </si>
-  <si>
-    <t>jkcz_icon_3.png</t>
-  </si>
-  <si>
-    <t>硬币</t>
-  </si>
-  <si>
-    <t>jkcz_icon_4.png</t>
-  </si>
-  <si>
-    <t>宝箱</t>
-  </si>
-  <si>
-    <t>jkcz_icon_5.png</t>
+    <t>jkcz_zjm_tb7</t>
+  </si>
+  <si>
+    <t>枪</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb1</t>
+  </si>
+  <si>
+    <t>药瓶</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb6</t>
+  </si>
+  <si>
+    <t>罗盘</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb3</t>
+  </si>
+  <si>
+    <t>地图</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb12</t>
   </si>
   <si>
     <t>船</t>
   </si>
   <si>
-    <t>jkcz_icon_6.png</t>
-  </si>
-  <si>
-    <t>卷毛</t>
-  </si>
-  <si>
-    <t>jkcz_icon_7.png</t>
-  </si>
-  <si>
-    <t>金毛</t>
-  </si>
-  <si>
-    <t>jkcz_icon_8.png</t>
-  </si>
-  <si>
-    <t>章鱼</t>
-  </si>
-  <si>
-    <t>jkcz_icon_9.png</t>
-  </si>
-  <si>
-    <t>老巫婆</t>
-  </si>
-  <si>
-    <t>jkcz_icon_10.png</t>
+    <t>jkcz_zjm_tb5</t>
+  </si>
+  <si>
+    <t>海盗帽</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb8</t>
+  </si>
+  <si>
+    <t>鹦鹉</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb4</t>
+  </si>
+  <si>
+    <t>船锚</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb2</t>
+  </si>
+  <si>
+    <t>大炮</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb11</t>
   </si>
   <si>
     <t>Bonus</t>
   </si>
   <si>
-    <t>jkcz_icon_11.png</t>
-  </si>
-  <si>
-    <t>jkcz_icon_12.png</t>
-  </si>
-  <si>
-    <t>jkcz_icon_13.png</t>
-  </si>
-  <si>
-    <t>jkcz_icon_14.png</t>
-  </si>
-  <si>
-    <t>jkcz_icon_15.png</t>
-  </si>
-  <si>
-    <t>jkcz_icon_16.png</t>
+    <t>jkcz_zjm_tb9</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb10</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb13</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb14</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb15</t>
+  </si>
+  <si>
+    <t>jkcz_zjm_tb16</t>
   </si>
   <si>
     <t>lqjx_icon_1.png</t>
@@ -1276,13 +1276,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -7776,7 +7776,7 @@
     </row>
     <row r="217" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A217" s="34">
-        <f t="shared" ref="A217:A226" si="7">B217*100+C217</f>
+        <f t="shared" ref="A217:A230" si="7">B217*100+C217</f>
         <v>10250002</v>
       </c>
       <c r="B217" s="34">
@@ -7986,7 +7986,7 @@
     </row>
     <row r="227" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A227" s="34">
-        <f>B227*100+C227</f>
+        <f t="shared" si="7"/>
         <v>10250012</v>
       </c>
       <c r="B227" s="34">
@@ -8007,7 +8007,7 @@
     </row>
     <row r="228" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A228" s="34">
-        <f>B228*100+C228</f>
+        <f t="shared" si="7"/>
         <v>10250013</v>
       </c>
       <c r="B228" s="34">
@@ -8028,7 +8028,7 @@
     </row>
     <row r="229" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A229" s="34">
-        <f>B229*100+C229</f>
+        <f t="shared" si="7"/>
         <v>10250014</v>
       </c>
       <c r="B229" s="34">
@@ -8049,7 +8049,7 @@
     </row>
     <row r="230" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A230" s="34">
-        <f>B230*100+C230</f>
+        <f t="shared" si="7"/>
         <v>10250015</v>
       </c>
       <c r="B230" s="34">

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="342">
   <si>
     <t>图标</t>
   </si>
@@ -1081,6 +1081,66 @@
   </si>
   <si>
     <t>hbwz_icon_15.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_1.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_2.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_3.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_4.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_5.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_6.png</t>
+  </si>
+  <si>
+    <t>朋克眼镜</t>
+  </si>
+  <si>
+    <t>zqsd_icon_7.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_8.png</t>
+  </si>
+  <si>
+    <t>书</t>
+  </si>
+  <si>
+    <t>zqsd_icon_9.png</t>
+  </si>
+  <si>
+    <t>火枪</t>
+  </si>
+  <si>
+    <t>zqsd_icon_10.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_11.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_12.png</t>
+  </si>
+  <si>
+    <t>免费+1</t>
+  </si>
+  <si>
+    <t>zqsd_icon_13.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_14.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_15.png</t>
+  </si>
+  <si>
+    <t>zqsd_icon_16.png</t>
   </si>
 </sst>
 </file>
@@ -1289,12 +1349,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1849,7 +1909,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1957,6 +2017,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -2281,7 +2344,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M230"/>
+  <dimension ref="A1:M246"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -7661,7 +7724,7 @@
       </c>
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
-      <c r="H211" s="36" t="s">
+      <c r="H211" s="37" t="s">
         <v>297</v>
       </c>
     </row>
@@ -8065,6 +8128,342 @@
       <c r="F230" s="35"/>
       <c r="G230" s="35"/>
       <c r="H230" s="34" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A231" s="34">
+        <f t="shared" ref="A231:A246" si="8">B231*100+C231</f>
+        <v>10230001</v>
+      </c>
+      <c r="B231" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C231" s="34">
+        <v>1</v>
+      </c>
+      <c r="D231" s="34"/>
+      <c r="E231" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="F231" s="35"/>
+      <c r="G231" s="35"/>
+      <c r="H231" s="36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="232" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A232" s="34">
+        <f t="shared" si="8"/>
+        <v>10230002</v>
+      </c>
+      <c r="B232" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C232" s="34">
+        <v>2</v>
+      </c>
+      <c r="D232" s="34"/>
+      <c r="E232" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="F232" s="35"/>
+      <c r="G232" s="35"/>
+      <c r="H232" s="34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="233" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A233" s="34">
+        <f t="shared" si="8"/>
+        <v>10230003</v>
+      </c>
+      <c r="B233" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C233" s="34">
+        <v>3</v>
+      </c>
+      <c r="D233" s="34"/>
+      <c r="E233" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="F233" s="35"/>
+      <c r="G233" s="35"/>
+      <c r="H233" s="34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="234" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A234" s="34">
+        <f t="shared" si="8"/>
+        <v>10230004</v>
+      </c>
+      <c r="B234" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C234" s="34">
+        <v>4</v>
+      </c>
+      <c r="D234" s="34"/>
+      <c r="E234" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="F234" s="35"/>
+      <c r="G234" s="35"/>
+      <c r="H234" s="34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="235" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A235" s="34">
+        <f t="shared" si="8"/>
+        <v>10230005</v>
+      </c>
+      <c r="B235" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C235" s="34">
+        <v>5</v>
+      </c>
+      <c r="D235" s="34"/>
+      <c r="E235" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="F235" s="35"/>
+      <c r="G235" s="35"/>
+      <c r="H235" s="34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="236" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A236" s="34">
+        <f t="shared" si="8"/>
+        <v>10230006</v>
+      </c>
+      <c r="B236" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C236" s="34">
+        <v>6</v>
+      </c>
+      <c r="D236" s="34"/>
+      <c r="E236" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="F236" s="35"/>
+      <c r="G236" s="35"/>
+      <c r="H236" s="34" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="237" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A237" s="34">
+        <f t="shared" si="8"/>
+        <v>10230007</v>
+      </c>
+      <c r="B237" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C237" s="34">
+        <v>7</v>
+      </c>
+      <c r="D237" s="34"/>
+      <c r="E237" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="F237" s="35"/>
+      <c r="G237" s="35"/>
+      <c r="H237" s="34" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="238" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A238" s="34">
+        <f t="shared" si="8"/>
+        <v>10230008</v>
+      </c>
+      <c r="B238" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C238" s="34">
+        <v>8</v>
+      </c>
+      <c r="D238" s="34"/>
+      <c r="E238" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="F238" s="35"/>
+      <c r="G238" s="35"/>
+      <c r="H238" s="34" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="239" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A239" s="34">
+        <f t="shared" si="8"/>
+        <v>10230009</v>
+      </c>
+      <c r="B239" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C239" s="34">
+        <v>9</v>
+      </c>
+      <c r="D239" s="34"/>
+      <c r="E239" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="F239" s="35"/>
+      <c r="G239" s="35"/>
+      <c r="H239" s="34" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="240" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A240" s="34">
+        <f t="shared" si="8"/>
+        <v>10230010</v>
+      </c>
+      <c r="B240" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C240" s="34">
+        <v>10</v>
+      </c>
+      <c r="D240" s="34"/>
+      <c r="E240" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="F240" s="35"/>
+      <c r="G240" s="35"/>
+      <c r="H240" s="34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="241" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A241" s="34">
+        <f t="shared" si="8"/>
+        <v>10230011</v>
+      </c>
+      <c r="B241" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C241" s="34">
+        <v>11</v>
+      </c>
+      <c r="D241" s="34"/>
+      <c r="E241" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="F241" s="35"/>
+      <c r="G241" s="35"/>
+      <c r="H241" s="34" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="242" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A242" s="34">
+        <f t="shared" si="8"/>
+        <v>10230012</v>
+      </c>
+      <c r="B242" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C242" s="34">
+        <v>12</v>
+      </c>
+      <c r="D242" s="34"/>
+      <c r="E242" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="F242" s="35"/>
+      <c r="G242" s="35"/>
+      <c r="H242" s="34" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="243" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A243" s="34">
+        <f t="shared" si="8"/>
+        <v>10230013</v>
+      </c>
+      <c r="B243" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C243" s="34">
+        <v>13</v>
+      </c>
+      <c r="D243" s="34"/>
+      <c r="E243" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="F243" s="35"/>
+      <c r="G243" s="35"/>
+      <c r="H243" s="34" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="244" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A244" s="34">
+        <f t="shared" si="8"/>
+        <v>10230014</v>
+      </c>
+      <c r="B244" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C244" s="34">
+        <v>14</v>
+      </c>
+      <c r="D244" s="34"/>
+      <c r="E244" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="F244" s="35"/>
+      <c r="G244" s="35"/>
+      <c r="H244" s="34" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="245" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A245" s="34">
+        <f t="shared" si="8"/>
+        <v>10230015</v>
+      </c>
+      <c r="B245" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C245" s="34">
+        <v>15</v>
+      </c>
+      <c r="D245" s="34"/>
+      <c r="E245" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="F245" s="35"/>
+      <c r="G245" s="35"/>
+      <c r="H245" s="34" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="246" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A246" s="34">
+        <f t="shared" si="8"/>
+        <v>10230016</v>
+      </c>
+      <c r="B246" s="34">
+        <v>102300</v>
+      </c>
+      <c r="C246" s="34">
+        <v>16</v>
+      </c>
+      <c r="D246" s="34"/>
+      <c r="E246" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="F246" s="35"/>
+      <c r="G246" s="35"/>
+      <c r="H246" s="34" t="s">
         <v>228</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -1349,12 +1349,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="355">
   <si>
     <t>图标</t>
   </si>
@@ -1141,6 +1141,45 @@
   </si>
   <si>
     <t>zqsd_icon_16.png</t>
+  </si>
+  <si>
+    <t>smfy_icon_1.png</t>
+  </si>
+  <si>
+    <t>橘子</t>
+  </si>
+  <si>
+    <t>smfy_icon_2.png</t>
+  </si>
+  <si>
+    <t>鞭炮</t>
+  </si>
+  <si>
+    <t>smfy_icon_3.png</t>
+  </si>
+  <si>
+    <t>红包</t>
+  </si>
+  <si>
+    <t>smfy_icon_4.png</t>
+  </si>
+  <si>
+    <t>福袋</t>
+  </si>
+  <si>
+    <t>smfy_icon_5.png</t>
+  </si>
+  <si>
+    <t>玉如意</t>
+  </si>
+  <si>
+    <t>smfy_icon_6.png</t>
+  </si>
+  <si>
+    <t>元宝</t>
+  </si>
+  <si>
+    <t>smfy_icon_7.png</t>
   </si>
 </sst>
 </file>
@@ -1336,13 +1375,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1360,7 +1399,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1418,6 +1457,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1785,7 +1830,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1809,16 +1854,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1827,89 +1872,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2020,6 +2065,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -2344,7 +2395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M246"/>
+  <dimension ref="A1:M253"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -7724,7 +7775,7 @@
       </c>
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
-      <c r="H211" s="37" t="s">
+      <c r="H211" s="39" t="s">
         <v>297</v>
       </c>
     </row>
@@ -7827,7 +7878,9 @@
       <c r="C216" s="34">
         <v>1</v>
       </c>
-      <c r="D216" s="34"/>
+      <c r="D216" s="34">
+        <v>0</v>
+      </c>
       <c r="E216" s="34" t="s">
         <v>302</v>
       </c>
@@ -7848,7 +7901,9 @@
       <c r="C217" s="34">
         <v>2</v>
       </c>
-      <c r="D217" s="34"/>
+      <c r="D217" s="34">
+        <v>0</v>
+      </c>
       <c r="E217" s="34" t="s">
         <v>303</v>
       </c>
@@ -7869,7 +7924,9 @@
       <c r="C218" s="34">
         <v>3</v>
       </c>
-      <c r="D218" s="34"/>
+      <c r="D218" s="34">
+        <v>0</v>
+      </c>
       <c r="E218" s="34" t="s">
         <v>304</v>
       </c>
@@ -7890,7 +7947,9 @@
       <c r="C219" s="34">
         <v>4</v>
       </c>
-      <c r="D219" s="34"/>
+      <c r="D219" s="34">
+        <v>0</v>
+      </c>
       <c r="E219" s="34" t="s">
         <v>305</v>
       </c>
@@ -7911,7 +7970,9 @@
       <c r="C220" s="34">
         <v>5</v>
       </c>
-      <c r="D220" s="34"/>
+      <c r="D220" s="34">
+        <v>0</v>
+      </c>
       <c r="E220" s="34" t="s">
         <v>306</v>
       </c>
@@ -7932,7 +7993,9 @@
       <c r="C221" s="34">
         <v>6</v>
       </c>
-      <c r="D221" s="34"/>
+      <c r="D221" s="34">
+        <v>0</v>
+      </c>
       <c r="E221" s="34" t="s">
         <v>308</v>
       </c>
@@ -7953,7 +8016,9 @@
       <c r="C222" s="34">
         <v>7</v>
       </c>
-      <c r="D222" s="34"/>
+      <c r="D222" s="34">
+        <v>0</v>
+      </c>
       <c r="E222" s="34" t="s">
         <v>310</v>
       </c>
@@ -7974,7 +8039,9 @@
       <c r="C223" s="34">
         <v>8</v>
       </c>
-      <c r="D223" s="34"/>
+      <c r="D223" s="34">
+        <v>0</v>
+      </c>
       <c r="E223" s="34" t="s">
         <v>312</v>
       </c>
@@ -7995,7 +8062,9 @@
       <c r="C224" s="34">
         <v>9</v>
       </c>
-      <c r="D224" s="34"/>
+      <c r="D224" s="34">
+        <v>0</v>
+      </c>
       <c r="E224" s="34" t="s">
         <v>314</v>
       </c>
@@ -8016,7 +8085,9 @@
       <c r="C225" s="34">
         <v>10</v>
       </c>
-      <c r="D225" s="34"/>
+      <c r="D225" s="34">
+        <v>1</v>
+      </c>
       <c r="E225" s="34" t="s">
         <v>316</v>
       </c>
@@ -8037,7 +8108,9 @@
       <c r="C226" s="34">
         <v>11</v>
       </c>
-      <c r="D226" s="34"/>
+      <c r="D226" s="34">
+        <v>2</v>
+      </c>
       <c r="E226" s="34" t="s">
         <v>317</v>
       </c>
@@ -8058,7 +8131,9 @@
       <c r="C227" s="34">
         <v>12</v>
       </c>
-      <c r="D227" s="34"/>
+      <c r="D227" s="34">
+        <v>3</v>
+      </c>
       <c r="E227" s="34" t="s">
         <v>318</v>
       </c>
@@ -8079,7 +8154,9 @@
       <c r="C228" s="34">
         <v>13</v>
       </c>
-      <c r="D228" s="34"/>
+      <c r="D228" s="34">
+        <v>3</v>
+      </c>
       <c r="E228" s="34" t="s">
         <v>319</v>
       </c>
@@ -8100,7 +8177,9 @@
       <c r="C229" s="34">
         <v>14</v>
       </c>
-      <c r="D229" s="34"/>
+      <c r="D229" s="34">
+        <v>3</v>
+      </c>
       <c r="E229" s="34" t="s">
         <v>320</v>
       </c>
@@ -8121,7 +8200,9 @@
       <c r="C230" s="34">
         <v>15</v>
       </c>
-      <c r="D230" s="34"/>
+      <c r="D230" s="34">
+        <v>3</v>
+      </c>
       <c r="E230" s="34" t="s">
         <v>321</v>
       </c>
@@ -8133,7 +8214,7 @@
     </row>
     <row r="231" s="1" customFormat="1" ht="16.5" spans="1:8">
       <c r="A231" s="34">
-        <f t="shared" ref="A231:A246" si="8">B231*100+C231</f>
+        <f t="shared" ref="A231:A247" si="8">B231*100+C231</f>
         <v>10230001</v>
       </c>
       <c r="B231" s="34">
@@ -8142,7 +8223,9 @@
       <c r="C231" s="34">
         <v>1</v>
       </c>
-      <c r="D231" s="34"/>
+      <c r="D231" s="34">
+        <v>0</v>
+      </c>
       <c r="E231" s="34" t="s">
         <v>322</v>
       </c>
@@ -8163,7 +8246,9 @@
       <c r="C232" s="34">
         <v>2</v>
       </c>
-      <c r="D232" s="34"/>
+      <c r="D232" s="34">
+        <v>0</v>
+      </c>
       <c r="E232" s="34" t="s">
         <v>323</v>
       </c>
@@ -8184,7 +8269,9 @@
       <c r="C233" s="34">
         <v>3</v>
       </c>
-      <c r="D233" s="34"/>
+      <c r="D233" s="34">
+        <v>0</v>
+      </c>
       <c r="E233" s="34" t="s">
         <v>324</v>
       </c>
@@ -8205,7 +8292,9 @@
       <c r="C234" s="34">
         <v>4</v>
       </c>
-      <c r="D234" s="34"/>
+      <c r="D234" s="34">
+        <v>0</v>
+      </c>
       <c r="E234" s="34" t="s">
         <v>325</v>
       </c>
@@ -8226,7 +8315,9 @@
       <c r="C235" s="34">
         <v>5</v>
       </c>
-      <c r="D235" s="34"/>
+      <c r="D235" s="34">
+        <v>0</v>
+      </c>
       <c r="E235" s="34" t="s">
         <v>326</v>
       </c>
@@ -8247,7 +8338,9 @@
       <c r="C236" s="34">
         <v>6</v>
       </c>
-      <c r="D236" s="34"/>
+      <c r="D236" s="34">
+        <v>0</v>
+      </c>
       <c r="E236" s="34" t="s">
         <v>327</v>
       </c>
@@ -8268,7 +8361,9 @@
       <c r="C237" s="34">
         <v>7</v>
       </c>
-      <c r="D237" s="34"/>
+      <c r="D237" s="34">
+        <v>0</v>
+      </c>
       <c r="E237" s="34" t="s">
         <v>329</v>
       </c>
@@ -8289,7 +8384,9 @@
       <c r="C238" s="34">
         <v>8</v>
       </c>
-      <c r="D238" s="34"/>
+      <c r="D238" s="34">
+        <v>0</v>
+      </c>
       <c r="E238" s="34" t="s">
         <v>330</v>
       </c>
@@ -8310,7 +8407,9 @@
       <c r="C239" s="34">
         <v>9</v>
       </c>
-      <c r="D239" s="34"/>
+      <c r="D239" s="34">
+        <v>0</v>
+      </c>
       <c r="E239" s="34" t="s">
         <v>332</v>
       </c>
@@ -8331,7 +8430,9 @@
       <c r="C240" s="34">
         <v>10</v>
       </c>
-      <c r="D240" s="34"/>
+      <c r="D240" s="34">
+        <v>1</v>
+      </c>
       <c r="E240" s="34" t="s">
         <v>334</v>
       </c>
@@ -8352,7 +8453,9 @@
       <c r="C241" s="34">
         <v>11</v>
       </c>
-      <c r="D241" s="34"/>
+      <c r="D241" s="34">
+        <v>2</v>
+      </c>
       <c r="E241" s="34" t="s">
         <v>335</v>
       </c>
@@ -8373,7 +8476,9 @@
       <c r="C242" s="34">
         <v>12</v>
       </c>
-      <c r="D242" s="34"/>
+      <c r="D242" s="34">
+        <v>2</v>
+      </c>
       <c r="E242" s="34" t="s">
         <v>336</v>
       </c>
@@ -8394,7 +8499,9 @@
       <c r="C243" s="34">
         <v>13</v>
       </c>
-      <c r="D243" s="34"/>
+      <c r="D243" s="34">
+        <v>3</v>
+      </c>
       <c r="E243" s="34" t="s">
         <v>338</v>
       </c>
@@ -8415,7 +8522,9 @@
       <c r="C244" s="34">
         <v>14</v>
       </c>
-      <c r="D244" s="34"/>
+      <c r="D244" s="34">
+        <v>3</v>
+      </c>
       <c r="E244" s="34" t="s">
         <v>339</v>
       </c>
@@ -8436,7 +8545,9 @@
       <c r="C245" s="34">
         <v>15</v>
       </c>
-      <c r="D245" s="34"/>
+      <c r="D245" s="34">
+        <v>3</v>
+      </c>
       <c r="E245" s="34" t="s">
         <v>340</v>
       </c>
@@ -8457,7 +8568,9 @@
       <c r="C246" s="34">
         <v>16</v>
       </c>
-      <c r="D246" s="34"/>
+      <c r="D246" s="34">
+        <v>3</v>
+      </c>
       <c r="E246" s="34" t="s">
         <v>341</v>
       </c>
@@ -8465,6 +8578,167 @@
       <c r="G246" s="35"/>
       <c r="H246" s="34" t="s">
         <v>228</v>
+      </c>
+    </row>
+    <row r="247" s="1" customFormat="1" ht="16.5" spans="1:8">
+      <c r="A247" s="37">
+        <f t="shared" si="8"/>
+        <v>10340001</v>
+      </c>
+      <c r="B247" s="37">
+        <v>103400</v>
+      </c>
+      <c r="C247" s="37">
+        <v>1</v>
+      </c>
+      <c r="D247" s="37">
+        <v>0</v>
+      </c>
+      <c r="E247" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="F247" s="38"/>
+      <c r="G247" s="38"/>
+      <c r="H247" s="37" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="248" ht="16.5" spans="1:8">
+      <c r="A248" s="37">
+        <f t="shared" ref="A248:A254" si="9">B248*100+C248</f>
+        <v>10340002</v>
+      </c>
+      <c r="B248" s="37">
+        <v>103400</v>
+      </c>
+      <c r="C248" s="37">
+        <v>2</v>
+      </c>
+      <c r="D248" s="37">
+        <v>0</v>
+      </c>
+      <c r="E248" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F248" s="38"/>
+      <c r="G248" s="38"/>
+      <c r="H248" s="37" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="249" ht="16.5" spans="1:8">
+      <c r="A249" s="37">
+        <f t="shared" si="9"/>
+        <v>10340003</v>
+      </c>
+      <c r="B249" s="37">
+        <v>103400</v>
+      </c>
+      <c r="C249" s="37">
+        <v>3</v>
+      </c>
+      <c r="D249" s="37">
+        <v>0</v>
+      </c>
+      <c r="E249" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="F249" s="38"/>
+      <c r="G249" s="38"/>
+      <c r="H249" s="37" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="250" ht="16.5" spans="1:8">
+      <c r="A250" s="37">
+        <f t="shared" si="9"/>
+        <v>10340004</v>
+      </c>
+      <c r="B250" s="37">
+        <v>103400</v>
+      </c>
+      <c r="C250" s="37">
+        <v>4</v>
+      </c>
+      <c r="D250" s="37">
+        <v>0</v>
+      </c>
+      <c r="E250" s="37" t="s">
+        <v>348</v>
+      </c>
+      <c r="F250" s="38"/>
+      <c r="G250" s="38"/>
+      <c r="H250" s="37" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="251" ht="16.5" spans="1:8">
+      <c r="A251" s="37">
+        <f t="shared" si="9"/>
+        <v>10340005</v>
+      </c>
+      <c r="B251" s="37">
+        <v>103400</v>
+      </c>
+      <c r="C251" s="37">
+        <v>5</v>
+      </c>
+      <c r="D251" s="37">
+        <v>0</v>
+      </c>
+      <c r="E251" s="37" t="s">
+        <v>350</v>
+      </c>
+      <c r="F251" s="38"/>
+      <c r="G251" s="38"/>
+      <c r="H251" s="37" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="252" ht="16.5" spans="1:8">
+      <c r="A252" s="37">
+        <f t="shared" si="9"/>
+        <v>10340006</v>
+      </c>
+      <c r="B252" s="37">
+        <v>103400</v>
+      </c>
+      <c r="C252" s="37">
+        <v>6</v>
+      </c>
+      <c r="D252" s="37">
+        <v>0</v>
+      </c>
+      <c r="E252" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="F252" s="38"/>
+      <c r="G252" s="38"/>
+      <c r="H252" s="37" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="253" ht="16.5" spans="1:8">
+      <c r="A253" s="37">
+        <f t="shared" si="9"/>
+        <v>10340007</v>
+      </c>
+      <c r="B253" s="37">
+        <v>103400</v>
+      </c>
+      <c r="C253" s="37">
+        <v>7</v>
+      </c>
+      <c r="D253" s="37">
+        <v>1</v>
+      </c>
+      <c r="E253" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="F253" s="38"/>
+      <c r="G253" s="38"/>
+      <c r="H253" s="37" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -1023,64 +1023,64 @@
     <t>lqjx_icon_17.png</t>
   </si>
   <si>
-    <t>hbwz_icon_1.png</t>
-  </si>
-  <si>
-    <t>hbwz_icon_2.png</t>
-  </si>
-  <si>
-    <t>hbwz_icon_3.png</t>
-  </si>
-  <si>
-    <t>hbwz_icon_4.png</t>
-  </si>
-  <si>
-    <t>hbwz_icon_5.png</t>
+    <t>hbwz_zjm_tb_4</t>
+  </si>
+  <si>
+    <t>hbwz_zjm_tb_3</t>
+  </si>
+  <si>
+    <t>hbwz_zjm_tb_2</t>
+  </si>
+  <si>
+    <t>hbwz_zjm_tb_1</t>
+  </si>
+  <si>
+    <t>hbwz_zjm_tb_10</t>
   </si>
   <si>
     <t>亡灵战士</t>
   </si>
   <si>
-    <t>hbwz_icon_6.png</t>
+    <t>hbwz_zjm_tb_12</t>
   </si>
   <si>
     <t>亡灵法师</t>
   </si>
   <si>
-    <t>hbwz_icon_7.png</t>
+    <t>hbwz_zjm_tb_15</t>
   </si>
   <si>
     <t>憎恶</t>
   </si>
   <si>
-    <t>hbwz_icon_8.png</t>
+    <t>hbwz_zjm_tb_14</t>
   </si>
   <si>
     <t>冰龙</t>
   </si>
   <si>
-    <t>hbwz_icon_9.png</t>
+    <t>hbwz_zjm_tb_13</t>
   </si>
   <si>
     <t>亡灵大军</t>
   </si>
   <si>
-    <t>hbwz_icon_10.png</t>
-  </si>
-  <si>
-    <t>hbwz_icon_11.png</t>
-  </si>
-  <si>
-    <t>hbwz_icon_12.png</t>
-  </si>
-  <si>
-    <t>hbwz_icon_13.png</t>
-  </si>
-  <si>
-    <t>hbwz_icon_14.png</t>
-  </si>
-  <si>
-    <t>hbwz_icon_15.png</t>
+    <t>hbwz_zjm_tb_9</t>
+  </si>
+  <si>
+    <t>hbwz_zjm_tb_11</t>
+  </si>
+  <si>
+    <t>hbwz_zjm_tb_7</t>
+  </si>
+  <si>
+    <t>hbwz_zjm_tb_6</t>
+  </si>
+  <si>
+    <t>hbwz_zjm_tb_5</t>
+  </si>
+  <si>
+    <t>hbwz_zjm_tb_8</t>
   </si>
   <si>
     <t>zqsd_icon_1.png</t>
@@ -1377,6 +1377,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1384,12 +1390,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="356">
   <si>
     <t>图标</t>
   </si>
@@ -1083,64 +1083,64 @@
     <t>hbwz_zjm_tb_8</t>
   </si>
   <si>
-    <t>zqsd_icon_1.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_2.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_3.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_4.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_5.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_6.png</t>
+    <t>zqsd_16</t>
+  </si>
+  <si>
+    <t>zqsd_15</t>
+  </si>
+  <si>
+    <t>zqsd_14</t>
+  </si>
+  <si>
+    <t>zqsd_13</t>
+  </si>
+  <si>
+    <t>zqsd_12</t>
+  </si>
+  <si>
+    <t>zqsd_10</t>
   </si>
   <si>
     <t>朋克眼镜</t>
   </si>
   <si>
-    <t>zqsd_icon_7.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_8.png</t>
+    <t>zqsd_8</t>
+  </si>
+  <si>
+    <t>zqsd_9</t>
   </si>
   <si>
     <t>书</t>
   </si>
   <si>
-    <t>zqsd_icon_9.png</t>
+    <t>zqsd_11</t>
   </si>
   <si>
     <t>火枪</t>
   </si>
   <si>
-    <t>zqsd_icon_10.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_11.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_12.png</t>
+    <t>zqsd_1</t>
+  </si>
+  <si>
+    <t>zqsd_2</t>
+  </si>
+  <si>
+    <t>zqsd_3</t>
   </si>
   <si>
     <t>免费+1</t>
   </si>
   <si>
-    <t>zqsd_icon_13.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_14.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_15.png</t>
-  </si>
-  <si>
-    <t>zqsd_icon_16.png</t>
+    <t>zqsd_7</t>
+  </si>
+  <si>
+    <t>zqsd_6</t>
+  </si>
+  <si>
+    <t>zqsd_5</t>
+  </si>
+  <si>
+    <t>zqsd_4</t>
   </si>
   <si>
     <t>smfy_icon_1.png</t>
@@ -1180,6 +1180,9 @@
   </si>
   <si>
     <t>smfy_icon_7.png</t>
+  </si>
+  <si>
+    <t>空格符号</t>
   </si>
 </sst>
 </file>
@@ -1377,24 +1380,24 @@
     <font>
       <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2395,7 +2398,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M253"/>
+  <dimension ref="A1:M254"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -8739,6 +8742,29 @@
       <c r="G253" s="38"/>
       <c r="H253" s="37" t="s">
         <v>245</v>
+      </c>
+    </row>
+    <row r="254" ht="16.5" spans="1:8">
+      <c r="A254" s="37">
+        <f t="shared" si="9"/>
+        <v>10340008</v>
+      </c>
+      <c r="B254" s="37">
+        <v>103400</v>
+      </c>
+      <c r="C254" s="37">
+        <v>8</v>
+      </c>
+      <c r="D254" s="37">
+        <v>2</v>
+      </c>
+      <c r="E254" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="F254" s="38"/>
+      <c r="G254" s="38"/>
+      <c r="H254" s="37" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="358">
   <si>
     <t>图标</t>
   </si>
@@ -1180,6 +1180,12 @@
   </si>
   <si>
     <t>smfy_icon_7.png</t>
+  </si>
+  <si>
+    <t>大奖符号</t>
+  </si>
+  <si>
+    <t>smfy_icon_8.png</t>
   </si>
   <si>
     <t>空格符号</t>
@@ -1386,6 +1392,7 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1397,7 +1404,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2398,7 +2404,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M254"/>
+  <dimension ref="A1:M255"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -8765,6 +8771,29 @@
       <c r="G254" s="38"/>
       <c r="H254" s="37" t="s">
         <v>355</v>
+      </c>
+    </row>
+    <row r="255" ht="16.5" spans="1:8">
+      <c r="A255" s="37">
+        <f>B255*100+C255</f>
+        <v>10340009</v>
+      </c>
+      <c r="B255" s="37">
+        <v>103400</v>
+      </c>
+      <c r="C255" s="37">
+        <v>9</v>
+      </c>
+      <c r="D255" s="37">
+        <v>2</v>
+      </c>
+      <c r="E255" s="37" t="s">
+        <v>356</v>
+      </c>
+      <c r="F255" s="38"/>
+      <c r="G255" s="38"/>
+      <c r="H255" s="37" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="394">
   <si>
     <t>图标</t>
   </si>
@@ -1189,6 +1189,114 @@
   </si>
   <si>
     <t>空格符号</t>
+  </si>
+  <si>
+    <t>jszc_icon_1.png</t>
+  </si>
+  <si>
+    <t>jszc_icon_2.png</t>
+  </si>
+  <si>
+    <t>钱币</t>
+  </si>
+  <si>
+    <t>jszc_icon_3.png</t>
+  </si>
+  <si>
+    <t>话筒</t>
+  </si>
+  <si>
+    <t>jszc_icon_4.png</t>
+  </si>
+  <si>
+    <t>jszc_icon_5.png</t>
+  </si>
+  <si>
+    <t>项链</t>
+  </si>
+  <si>
+    <t>jszc_icon_6.png</t>
+  </si>
+  <si>
+    <t>jszc_icon_7.png</t>
+  </si>
+  <si>
+    <t>jszc_icon_8.png</t>
+  </si>
+  <si>
+    <t>奖金符号</t>
+  </si>
+  <si>
+    <t>jszc_icon_9.png</t>
+  </si>
+  <si>
+    <t>Mini</t>
+  </si>
+  <si>
+    <t>jszc_icon_10.png</t>
+  </si>
+  <si>
+    <t>jszc_icon_11.png</t>
+  </si>
+  <si>
+    <t>jszc_icon_12.png</t>
+  </si>
+  <si>
+    <t>jszc_icon_13.png</t>
+  </si>
+  <si>
+    <t>jszc_icon_14.png</t>
+  </si>
+  <si>
+    <t>隐藏符号，用于触发金钱兔模式</t>
+  </si>
+  <si>
+    <t>jqt_icon_1.png</t>
+  </si>
+  <si>
+    <t>萝卜</t>
+  </si>
+  <si>
+    <t>jqt_icon_2.png</t>
+  </si>
+  <si>
+    <t>烟花</t>
+  </si>
+  <si>
+    <t>jqt_icon_3.png</t>
+  </si>
+  <si>
+    <t>jqt_icon_4.png</t>
+  </si>
+  <si>
+    <t>jqt_icon_5.png</t>
+  </si>
+  <si>
+    <t>百宝袋</t>
+  </si>
+  <si>
+    <t>jqt_icon_6.png</t>
+  </si>
+  <si>
+    <t>jqt_icon_7.png</t>
+  </si>
+  <si>
+    <t>jqt_icon_8.png</t>
+  </si>
+  <si>
+    <t>jqt_icon_9.png</t>
+  </si>
+  <si>
+    <t>jqt_icon_10.png</t>
+  </si>
+  <si>
+    <t>jqt_icon_11.png</t>
+  </si>
+  <si>
+    <t>jqt_icon_12.png</t>
+  </si>
+  <si>
+    <t>jqt_icon_13.png</t>
   </si>
 </sst>
 </file>
@@ -1392,6 +1500,11 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1402,13 +1515,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="43">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1472,6 +1580,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1839,7 +1959,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1863,16 +1983,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1881,89 +2001,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2079,6 +2199,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -2404,7 +2536,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M255"/>
+  <dimension ref="A1:M283"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -7784,7 +7916,7 @@
       </c>
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
-      <c r="H211" s="39" t="s">
+      <c r="H211" s="43" t="s">
         <v>297</v>
       </c>
     </row>
@@ -8614,7 +8746,7 @@
     </row>
     <row r="248" ht="16.5" spans="1:8">
       <c r="A248" s="37">
-        <f t="shared" ref="A248:A254" si="9">B248*100+C248</f>
+        <f t="shared" ref="A248:A255" si="9">B248*100+C248</f>
         <v>10340002</v>
       </c>
       <c r="B248" s="37">
@@ -8775,7 +8907,7 @@
     </row>
     <row r="255" ht="16.5" spans="1:8">
       <c r="A255" s="37">
-        <f>B255*100+C255</f>
+        <f t="shared" si="9"/>
         <v>10340009</v>
       </c>
       <c r="B255" s="37">
@@ -8794,6 +8926,650 @@
       <c r="G255" s="38"/>
       <c r="H255" s="37" t="s">
         <v>357</v>
+      </c>
+    </row>
+    <row r="256" ht="16.5" spans="1:8">
+      <c r="A256" s="37">
+        <f t="shared" ref="A256:A281" si="10">B256*100+C256</f>
+        <v>10350001</v>
+      </c>
+      <c r="B256" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C256" s="25">
+        <v>1</v>
+      </c>
+      <c r="D256" s="25">
+        <v>0</v>
+      </c>
+      <c r="E256" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="F256" s="39"/>
+      <c r="G256" s="39"/>
+      <c r="H256" s="25" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="257" ht="16.5" spans="1:8">
+      <c r="A257" s="37">
+        <f t="shared" si="10"/>
+        <v>10350002</v>
+      </c>
+      <c r="B257" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C257" s="25">
+        <v>2</v>
+      </c>
+      <c r="D257" s="25">
+        <v>0</v>
+      </c>
+      <c r="E257" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="F257" s="39"/>
+      <c r="G257" s="39"/>
+      <c r="H257" s="25" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="258" ht="16.5" spans="1:8">
+      <c r="A258" s="37">
+        <f t="shared" si="10"/>
+        <v>10350003</v>
+      </c>
+      <c r="B258" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C258" s="25">
+        <v>3</v>
+      </c>
+      <c r="D258" s="25">
+        <v>0</v>
+      </c>
+      <c r="E258" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="F258" s="39"/>
+      <c r="G258" s="39"/>
+      <c r="H258" s="25" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="259" ht="16.5" spans="1:8">
+      <c r="A259" s="37">
+        <f t="shared" si="10"/>
+        <v>10350004</v>
+      </c>
+      <c r="B259" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C259" s="25">
+        <v>4</v>
+      </c>
+      <c r="D259" s="25">
+        <v>0</v>
+      </c>
+      <c r="E259" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="F259" s="39"/>
+      <c r="G259" s="39"/>
+      <c r="H259" s="25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="260" ht="16.5" spans="1:8">
+      <c r="A260" s="37">
+        <f t="shared" si="10"/>
+        <v>10350005</v>
+      </c>
+      <c r="B260" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C260" s="25">
+        <v>5</v>
+      </c>
+      <c r="D260" s="25">
+        <v>0</v>
+      </c>
+      <c r="E260" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="F260" s="39"/>
+      <c r="G260" s="39"/>
+      <c r="H260" s="25" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="261" ht="16.5" spans="1:8">
+      <c r="A261" s="37">
+        <f t="shared" si="10"/>
+        <v>10350006</v>
+      </c>
+      <c r="B261" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C261" s="25">
+        <v>6</v>
+      </c>
+      <c r="D261" s="25">
+        <v>0</v>
+      </c>
+      <c r="E261" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="F261" s="39"/>
+      <c r="G261" s="39"/>
+      <c r="H261" s="25" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="262" ht="16.5" spans="1:8">
+      <c r="A262" s="37">
+        <f t="shared" si="10"/>
+        <v>10350007</v>
+      </c>
+      <c r="B262" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C262" s="25">
+        <v>7</v>
+      </c>
+      <c r="D262" s="25">
+        <v>1</v>
+      </c>
+      <c r="E262" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="F262" s="39"/>
+      <c r="G262" s="39"/>
+      <c r="H262" s="25" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="263" ht="16.5" spans="1:8">
+      <c r="A263" s="37">
+        <f t="shared" si="10"/>
+        <v>10350008</v>
+      </c>
+      <c r="B263" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C263" s="25">
+        <v>8</v>
+      </c>
+      <c r="D263" s="25">
+        <v>2</v>
+      </c>
+      <c r="E263" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="F263" s="39"/>
+      <c r="G263" s="39"/>
+      <c r="H263" s="25" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="264" ht="16.5" spans="1:8">
+      <c r="A264" s="37">
+        <f t="shared" si="10"/>
+        <v>10350009</v>
+      </c>
+      <c r="B264" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C264" s="25">
+        <v>9</v>
+      </c>
+      <c r="D264" s="25">
+        <v>2</v>
+      </c>
+      <c r="E264" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="F264" s="39"/>
+      <c r="G264" s="39"/>
+      <c r="H264" s="25" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="265" ht="16.5" spans="1:8">
+      <c r="A265" s="37">
+        <f t="shared" si="10"/>
+        <v>10350010</v>
+      </c>
+      <c r="B265" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C265" s="25">
+        <v>10</v>
+      </c>
+      <c r="D265" s="25">
+        <v>2</v>
+      </c>
+      <c r="E265" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="F265" s="39"/>
+      <c r="G265" s="39"/>
+      <c r="H265" s="25" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="266" ht="16.5" spans="1:8">
+      <c r="A266" s="37">
+        <f t="shared" si="10"/>
+        <v>10350011</v>
+      </c>
+      <c r="B266" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C266" s="25">
+        <v>11</v>
+      </c>
+      <c r="D266" s="25">
+        <v>2</v>
+      </c>
+      <c r="E266" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="F266" s="39"/>
+      <c r="G266" s="39"/>
+      <c r="H266" s="25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="267" ht="16.5" spans="1:8">
+      <c r="A267" s="37">
+        <f t="shared" si="10"/>
+        <v>10350012</v>
+      </c>
+      <c r="B267" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C267" s="25">
+        <v>12</v>
+      </c>
+      <c r="D267" s="25">
+        <v>2</v>
+      </c>
+      <c r="E267" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="F267" s="39"/>
+      <c r="G267" s="39"/>
+      <c r="H267" s="25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="268" ht="16.5" spans="1:8">
+      <c r="A268" s="37">
+        <f t="shared" si="10"/>
+        <v>10350013</v>
+      </c>
+      <c r="B268" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C268" s="25">
+        <v>13</v>
+      </c>
+      <c r="D268" s="25">
+        <v>2</v>
+      </c>
+      <c r="E268" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="F268" s="39"/>
+      <c r="G268" s="39"/>
+      <c r="H268" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="269" ht="16.5" spans="1:8">
+      <c r="A269" s="37">
+        <f>B269*100+C269</f>
+        <v>10350014</v>
+      </c>
+      <c r="B269" s="25">
+        <v>103500</v>
+      </c>
+      <c r="C269" s="25">
+        <v>14</v>
+      </c>
+      <c r="D269" s="25">
+        <v>2</v>
+      </c>
+      <c r="E269" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="F269" s="39"/>
+      <c r="G269" s="39"/>
+      <c r="H269" s="25" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="270" ht="16.5" spans="1:8">
+      <c r="A270" s="40">
+        <f>B270*100+C270</f>
+        <v>10350101</v>
+      </c>
+      <c r="B270" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C270" s="40">
+        <v>1</v>
+      </c>
+      <c r="D270" s="40">
+        <v>0</v>
+      </c>
+      <c r="E270" s="40" t="s">
+        <v>378</v>
+      </c>
+      <c r="F270" s="41"/>
+      <c r="G270" s="41"/>
+      <c r="H270" s="40" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="271" ht="16.5" spans="1:8">
+      <c r="A271" s="40">
+        <f>B271*100+C271</f>
+        <v>10350102</v>
+      </c>
+      <c r="B271" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C271" s="40">
+        <v>2</v>
+      </c>
+      <c r="D271" s="40">
+        <v>0</v>
+      </c>
+      <c r="E271" s="40" t="s">
+        <v>380</v>
+      </c>
+      <c r="F271" s="41"/>
+      <c r="G271" s="41"/>
+      <c r="H271" s="40" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="272" ht="16.5" spans="1:8">
+      <c r="A272" s="40">
+        <f>B272*100+C272</f>
+        <v>10350103</v>
+      </c>
+      <c r="B272" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C272" s="40">
+        <v>3</v>
+      </c>
+      <c r="D272" s="40">
+        <v>0</v>
+      </c>
+      <c r="E272" s="40" t="s">
+        <v>382</v>
+      </c>
+      <c r="F272" s="41"/>
+      <c r="G272" s="41"/>
+      <c r="H272" s="40" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="273" ht="16.5" spans="1:8">
+      <c r="A273" s="40">
+        <f>B273*100+C273</f>
+        <v>10350104</v>
+      </c>
+      <c r="B273" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C273" s="40">
+        <v>4</v>
+      </c>
+      <c r="D273" s="40">
+        <v>0</v>
+      </c>
+      <c r="E273" s="40" t="s">
+        <v>383</v>
+      </c>
+      <c r="F273" s="41"/>
+      <c r="G273" s="41"/>
+      <c r="H273" s="40" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="274" ht="16.5" spans="1:8">
+      <c r="A274" s="40">
+        <f>B274*100+C274</f>
+        <v>10350105</v>
+      </c>
+      <c r="B274" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C274" s="40">
+        <v>5</v>
+      </c>
+      <c r="D274" s="40">
+        <v>0</v>
+      </c>
+      <c r="E274" s="40" t="s">
+        <v>384</v>
+      </c>
+      <c r="F274" s="41"/>
+      <c r="G274" s="41"/>
+      <c r="H274" s="40" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="275" ht="16.5" spans="1:8">
+      <c r="A275" s="40">
+        <f>B275*100+C275</f>
+        <v>10350106</v>
+      </c>
+      <c r="B275" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C275" s="40">
+        <v>6</v>
+      </c>
+      <c r="D275" s="40">
+        <v>0</v>
+      </c>
+      <c r="E275" s="40" t="s">
+        <v>386</v>
+      </c>
+      <c r="F275" s="41"/>
+      <c r="G275" s="41"/>
+      <c r="H275" s="40" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="276" ht="16.5" spans="1:8">
+      <c r="A276" s="40">
+        <f>B276*100+C276</f>
+        <v>10350107</v>
+      </c>
+      <c r="B276" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C276" s="40">
+        <v>7</v>
+      </c>
+      <c r="D276" s="40">
+        <v>1</v>
+      </c>
+      <c r="E276" s="40" t="s">
+        <v>387</v>
+      </c>
+      <c r="F276" s="41"/>
+      <c r="G276" s="41"/>
+      <c r="H276" s="40" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="277" ht="16.5" spans="1:8">
+      <c r="A277" s="40">
+        <f>B277*100+C277</f>
+        <v>10350108</v>
+      </c>
+      <c r="B277" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C277" s="40">
+        <v>8</v>
+      </c>
+      <c r="D277" s="40">
+        <v>2</v>
+      </c>
+      <c r="E277" s="40" t="s">
+        <v>388</v>
+      </c>
+      <c r="F277" s="41"/>
+      <c r="G277" s="41"/>
+      <c r="H277" s="40" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="278" ht="16.5" spans="1:8">
+      <c r="A278" s="40">
+        <f>B278*100+C278</f>
+        <v>10350109</v>
+      </c>
+      <c r="B278" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C278" s="40">
+        <v>9</v>
+      </c>
+      <c r="D278" s="40">
+        <v>2</v>
+      </c>
+      <c r="E278" s="40" t="s">
+        <v>389</v>
+      </c>
+      <c r="F278" s="41"/>
+      <c r="G278" s="41"/>
+      <c r="H278" s="40" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="279" ht="16.5" spans="1:8">
+      <c r="A279" s="40">
+        <f>B279*100+C279</f>
+        <v>10350110</v>
+      </c>
+      <c r="B279" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C279" s="40">
+        <v>10</v>
+      </c>
+      <c r="D279" s="40">
+        <v>2</v>
+      </c>
+      <c r="E279" s="40" t="s">
+        <v>390</v>
+      </c>
+      <c r="F279" s="41"/>
+      <c r="G279" s="41"/>
+      <c r="H279" s="40" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="280" ht="16.5" spans="1:8">
+      <c r="A280" s="40">
+        <f>B280*100+C280</f>
+        <v>10350111</v>
+      </c>
+      <c r="B280" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C280" s="40">
+        <v>11</v>
+      </c>
+      <c r="D280" s="40">
+        <v>2</v>
+      </c>
+      <c r="E280" s="40" t="s">
+        <v>391</v>
+      </c>
+      <c r="F280" s="41"/>
+      <c r="G280" s="41"/>
+      <c r="H280" s="40" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="281" ht="16.5" spans="1:8">
+      <c r="A281" s="40">
+        <f>B281*100+C281</f>
+        <v>10350112</v>
+      </c>
+      <c r="B281" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C281" s="40">
+        <v>12</v>
+      </c>
+      <c r="D281" s="40">
+        <v>2</v>
+      </c>
+      <c r="E281" s="40" t="s">
+        <v>392</v>
+      </c>
+      <c r="F281" s="41"/>
+      <c r="G281" s="41"/>
+      <c r="H281" s="40" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="282" ht="16.5" spans="1:8">
+      <c r="A282" s="40">
+        <f>B282*100+C282</f>
+        <v>10350113</v>
+      </c>
+      <c r="B282" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C282" s="40">
+        <v>13</v>
+      </c>
+      <c r="D282" s="40">
+        <v>2</v>
+      </c>
+      <c r="E282" s="40" t="s">
+        <v>392</v>
+      </c>
+      <c r="F282" s="41"/>
+      <c r="G282" s="41"/>
+      <c r="H282" s="40" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="283" ht="16.5" spans="1:8">
+      <c r="A283" s="40">
+        <f>B283*100+C283</f>
+        <v>10350114</v>
+      </c>
+      <c r="B283" s="40">
+        <v>103501</v>
+      </c>
+      <c r="C283" s="40">
+        <v>14</v>
+      </c>
+      <c r="D283" s="40">
+        <v>2</v>
+      </c>
+      <c r="E283" s="40" t="s">
+        <v>393</v>
+      </c>
+      <c r="F283" s="41"/>
+      <c r="G283" s="41"/>
+      <c r="H283" s="42" t="s">
+        <v>377</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="395">
   <si>
     <t>图标</t>
   </si>
@@ -804,73 +804,76 @@
     <t>GRAND</t>
   </si>
   <si>
-    <t>LS_icon_1.png</t>
-  </si>
-  <si>
-    <t>LS_icon_2.png</t>
-  </si>
-  <si>
-    <t>LS_icon_3.png</t>
-  </si>
-  <si>
-    <t>LS_icon_4.png</t>
-  </si>
-  <si>
-    <t>LS_icon_5.png</t>
-  </si>
-  <si>
-    <t>LS_icon_6.png</t>
+    <t>ls_icon_101</t>
+  </si>
+  <si>
+    <t>ls_icon_102</t>
+  </si>
+  <si>
+    <t>ls_icon_103</t>
+  </si>
+  <si>
+    <t>ls_icon_104</t>
+  </si>
+  <si>
+    <t>ls_icon_105</t>
+  </si>
+  <si>
+    <t>ls_icon_106</t>
   </si>
   <si>
     <t>星云</t>
   </si>
   <si>
-    <t>LS_icon_7.png</t>
+    <t>ls_icon_107</t>
   </si>
   <si>
     <t>海拉</t>
   </si>
   <si>
-    <t>LS_icon_8.png</t>
+    <t>ls_icon_108</t>
   </si>
   <si>
     <t>海姆达尔</t>
   </si>
   <si>
-    <t>LS_icon_9.png</t>
+    <t>ls_icon_109</t>
   </si>
   <si>
     <t>洛基</t>
   </si>
   <si>
-    <t>LS_icon_10.png</t>
+    <t>ls_icon_110</t>
   </si>
   <si>
     <t>奥丁</t>
   </si>
   <si>
-    <t>LS_icon_11.png</t>
+    <t>ls_icon_201</t>
   </si>
   <si>
     <t>wild</t>
   </si>
   <si>
-    <t>LS_icon_12.png</t>
+    <t>ls_icon_401</t>
   </si>
   <si>
     <t>冻结wild</t>
   </si>
   <si>
-    <t>LS_icon_13.png</t>
-  </si>
-  <si>
     <t>翻倍wild</t>
   </si>
   <si>
-    <t>LS_icon_14.png</t>
-  </si>
-  <si>
-    <t>LS_icon_15.png</t>
+    <t>ls_icon_501</t>
+  </si>
+  <si>
+    <t>ls_icon_502</t>
+  </si>
+  <si>
+    <t>ls_icon_503</t>
+  </si>
+  <si>
+    <t>ls_icon_504</t>
   </si>
   <si>
     <t>LS_icon_16.png</t>
@@ -1492,18 +1495,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1515,8 +1513,13 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1580,12 +1583,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1959,7 +1956,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1983,16 +1980,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2001,89 +1998,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2208,9 +2205,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -7113,12 +7107,12 @@
         <v>1</v>
       </c>
       <c r="E175" s="25" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F175" s="25"/>
       <c r="G175" s="25"/>
       <c r="H175" s="25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="176" ht="16.5" spans="1:8">
@@ -7159,7 +7153,7 @@
         <v>3</v>
       </c>
       <c r="E177" s="25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F177" s="25"/>
       <c r="G177" s="25"/>
@@ -7251,7 +7245,7 @@
         <v>2</v>
       </c>
       <c r="E181" s="25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F181" s="25"/>
       <c r="G181" s="25"/>
@@ -7274,7 +7268,7 @@
         <v>2</v>
       </c>
       <c r="E182" s="25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F182" s="25"/>
       <c r="G182" s="25"/>
@@ -7296,12 +7290,12 @@
         <v>0</v>
       </c>
       <c r="E183" s="27" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F183" s="27"/>
       <c r="G183" s="27"/>
       <c r="H183" s="27" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="184" ht="16.5" customHeight="1" spans="1:8">
@@ -7318,12 +7312,12 @@
         <v>0</v>
       </c>
       <c r="E184" s="27" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F184" s="27"/>
       <c r="G184" s="27"/>
       <c r="H184" s="27" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="185" ht="16.5" customHeight="1" spans="1:8">
@@ -7340,12 +7334,12 @@
         <v>0</v>
       </c>
       <c r="E185" s="27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F185" s="27"/>
       <c r="G185" s="27"/>
       <c r="H185" s="27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="186" ht="16.5" customHeight="1" spans="1:8">
@@ -7362,12 +7356,12 @@
         <v>0</v>
       </c>
       <c r="E186" s="27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F186" s="27"/>
       <c r="G186" s="27"/>
       <c r="H186" s="27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="187" ht="16.5" customHeight="1" spans="1:8">
@@ -7384,12 +7378,12 @@
         <v>0</v>
       </c>
       <c r="E187" s="27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F187" s="27"/>
       <c r="G187" s="27"/>
       <c r="H187" s="27" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="188" ht="16.5" customHeight="1" spans="1:8">
@@ -7406,12 +7400,12 @@
         <v>0</v>
       </c>
       <c r="E188" s="27" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F188" s="27"/>
       <c r="G188" s="27"/>
       <c r="H188" s="27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="189" ht="16.5" customHeight="1" spans="1:8">
@@ -7428,12 +7422,12 @@
         <v>0</v>
       </c>
       <c r="E189" s="27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F189" s="27"/>
       <c r="G189" s="27"/>
       <c r="H189" s="28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="190" ht="16.5" customHeight="1" spans="1:8">
@@ -7450,12 +7444,12 @@
         <v>0</v>
       </c>
       <c r="E190" s="27" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F190" s="27"/>
       <c r="G190" s="27"/>
       <c r="H190" s="27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="191" ht="16.5" customHeight="1" spans="1:8">
@@ -7472,12 +7466,12 @@
         <v>0</v>
       </c>
       <c r="E191" s="27" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F191" s="27"/>
       <c r="G191" s="27"/>
       <c r="H191" s="27" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="192" ht="16.5" spans="1:8">
@@ -7494,12 +7488,12 @@
         <v>2</v>
       </c>
       <c r="E192" s="27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F192" s="28"/>
       <c r="G192" s="28"/>
       <c r="H192" s="27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="193" ht="16.5" spans="1:8">
@@ -7516,7 +7510,7 @@
         <v>1</v>
       </c>
       <c r="E193" s="27" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F193" s="28"/>
       <c r="G193" s="28"/>
@@ -7538,7 +7532,7 @@
         <v>2</v>
       </c>
       <c r="E194" s="27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F194" s="28"/>
       <c r="G194" s="28"/>
@@ -7560,7 +7554,7 @@
         <v>3</v>
       </c>
       <c r="E195" s="27" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F195" s="28"/>
       <c r="G195" s="28"/>
@@ -7582,7 +7576,7 @@
         <v>3</v>
       </c>
       <c r="E196" s="27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F196" s="28"/>
       <c r="G196" s="28"/>
@@ -7604,7 +7598,7 @@
         <v>3</v>
       </c>
       <c r="E197" s="27" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F197" s="28"/>
       <c r="G197" s="28"/>
@@ -7626,7 +7620,7 @@
         <v>3</v>
       </c>
       <c r="E198" s="27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F198" s="28"/>
       <c r="G198" s="28"/>
@@ -7648,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F199" s="31"/>
       <c r="G199" s="31"/>
@@ -7670,7 +7664,7 @@
         <v>0</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F200" s="31"/>
       <c r="G200" s="31"/>
@@ -7692,7 +7686,7 @@
         <v>0</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F201" s="31"/>
       <c r="G201" s="31"/>
@@ -7714,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F202" s="31"/>
       <c r="G202" s="31"/>
@@ -7736,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F203" s="31"/>
       <c r="G203" s="31"/>
@@ -7758,12 +7752,12 @@
         <v>0</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F204" s="31"/>
       <c r="G204" s="31"/>
       <c r="H204" s="33" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="205" customFormat="1" ht="17.25" spans="1:8">
@@ -7780,12 +7774,12 @@
         <v>0</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F205" s="31"/>
       <c r="G205" s="31"/>
       <c r="H205" s="33" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="206" customFormat="1" ht="17.25" spans="1:8">
@@ -7802,12 +7796,12 @@
         <v>0</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F206" s="31"/>
       <c r="G206" s="31"/>
       <c r="H206" s="33" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="207" customFormat="1" ht="17.25" spans="1:8">
@@ -7824,12 +7818,12 @@
         <v>0</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F207" s="31"/>
       <c r="G207" s="31"/>
       <c r="H207" s="33" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="208" customFormat="1" ht="17.25" spans="1:8">
@@ -7846,12 +7840,12 @@
         <v>0</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F208" s="31"/>
       <c r="G208" s="31"/>
       <c r="H208" s="33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="209" customFormat="1" ht="17.25" spans="1:8">
@@ -7868,7 +7862,7 @@
         <v>1</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F209" s="31"/>
       <c r="G209" s="31"/>
@@ -7890,7 +7884,7 @@
         <v>2</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F210" s="31"/>
       <c r="G210" s="31"/>
@@ -7912,12 +7906,12 @@
         <v>2</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
-      <c r="H211" s="43" t="s">
-        <v>297</v>
+      <c r="H211" s="42" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -7934,7 +7928,7 @@
         <v>3</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F212" s="31"/>
       <c r="G212" s="31"/>
@@ -7956,7 +7950,7 @@
         <v>3</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F213" s="31"/>
       <c r="G213" s="31"/>
@@ -7978,7 +7972,7 @@
         <v>3</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F214" s="31"/>
       <c r="G214" s="31"/>
@@ -8000,7 +7994,7 @@
         <v>3</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F215" s="31"/>
       <c r="G215" s="31"/>
@@ -8023,7 +8017,7 @@
         <v>0</v>
       </c>
       <c r="E216" s="34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F216" s="35"/>
       <c r="G216" s="35"/>
@@ -8046,7 +8040,7 @@
         <v>0</v>
       </c>
       <c r="E217" s="34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F217" s="35"/>
       <c r="G217" s="35"/>
@@ -8069,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="E218" s="34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F218" s="35"/>
       <c r="G218" s="35"/>
@@ -8092,7 +8086,7 @@
         <v>0</v>
       </c>
       <c r="E219" s="34" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F219" s="35"/>
       <c r="G219" s="35"/>
@@ -8115,12 +8109,12 @@
         <v>0</v>
       </c>
       <c r="E220" s="34" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F220" s="35"/>
       <c r="G220" s="35"/>
       <c r="H220" s="34" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="221" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8138,12 +8132,12 @@
         <v>0</v>
       </c>
       <c r="E221" s="34" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F221" s="35"/>
       <c r="G221" s="35"/>
       <c r="H221" s="34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="222" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8161,12 +8155,12 @@
         <v>0</v>
       </c>
       <c r="E222" s="34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F222" s="35"/>
       <c r="G222" s="35"/>
       <c r="H222" s="34" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="223" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8184,12 +8178,12 @@
         <v>0</v>
       </c>
       <c r="E223" s="34" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F223" s="35"/>
       <c r="G223" s="35"/>
       <c r="H223" s="34" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="224" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8207,12 +8201,12 @@
         <v>0</v>
       </c>
       <c r="E224" s="34" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F224" s="35"/>
       <c r="G224" s="35"/>
       <c r="H224" s="34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="225" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8230,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="E225" s="34" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F225" s="35"/>
       <c r="G225" s="35"/>
@@ -8253,7 +8247,7 @@
         <v>2</v>
       </c>
       <c r="E226" s="34" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F226" s="35"/>
       <c r="G226" s="35"/>
@@ -8276,7 +8270,7 @@
         <v>3</v>
       </c>
       <c r="E227" s="34" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F227" s="35"/>
       <c r="G227" s="35"/>
@@ -8299,7 +8293,7 @@
         <v>3</v>
       </c>
       <c r="E228" s="34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F228" s="35"/>
       <c r="G228" s="35"/>
@@ -8322,7 +8316,7 @@
         <v>3</v>
       </c>
       <c r="E229" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F229" s="35"/>
       <c r="G229" s="35"/>
@@ -8345,7 +8339,7 @@
         <v>3</v>
       </c>
       <c r="E230" s="34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F230" s="35"/>
       <c r="G230" s="35"/>
@@ -8368,7 +8362,7 @@
         <v>0</v>
       </c>
       <c r="E231" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F231" s="35"/>
       <c r="G231" s="35"/>
@@ -8391,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="E232" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F232" s="35"/>
       <c r="G232" s="35"/>
@@ -8414,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="E233" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F233" s="35"/>
       <c r="G233" s="35"/>
@@ -8437,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="E234" s="34" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F234" s="35"/>
       <c r="G234" s="35"/>
@@ -8460,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="E235" s="34" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F235" s="35"/>
       <c r="G235" s="35"/>
@@ -8483,12 +8477,12 @@
         <v>0</v>
       </c>
       <c r="E236" s="34" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F236" s="35"/>
       <c r="G236" s="35"/>
       <c r="H236" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="237" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8506,12 +8500,12 @@
         <v>0</v>
       </c>
       <c r="E237" s="34" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F237" s="35"/>
       <c r="G237" s="35"/>
       <c r="H237" s="34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="238" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8529,12 +8523,12 @@
         <v>0</v>
       </c>
       <c r="E238" s="34" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F238" s="35"/>
       <c r="G238" s="35"/>
       <c r="H238" s="34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="239" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8552,12 +8546,12 @@
         <v>0</v>
       </c>
       <c r="E239" s="34" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F239" s="35"/>
       <c r="G239" s="35"/>
       <c r="H239" s="34" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="240" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8575,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="E240" s="34" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F240" s="35"/>
       <c r="G240" s="35"/>
@@ -8598,7 +8592,7 @@
         <v>2</v>
       </c>
       <c r="E241" s="34" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F241" s="35"/>
       <c r="G241" s="35"/>
@@ -8621,12 +8615,12 @@
         <v>2</v>
       </c>
       <c r="E242" s="34" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F242" s="35"/>
       <c r="G242" s="35"/>
       <c r="H242" s="34" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="243" s="1" customFormat="1" ht="16.5" spans="1:8">
@@ -8644,7 +8638,7 @@
         <v>3</v>
       </c>
       <c r="E243" s="34" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F243" s="35"/>
       <c r="G243" s="35"/>
@@ -8667,7 +8661,7 @@
         <v>3</v>
       </c>
       <c r="E244" s="34" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F244" s="35"/>
       <c r="G244" s="35"/>
@@ -8690,7 +8684,7 @@
         <v>3</v>
       </c>
       <c r="E245" s="34" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F245" s="35"/>
       <c r="G245" s="35"/>
@@ -8713,7 +8707,7 @@
         <v>3</v>
       </c>
       <c r="E246" s="34" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F246" s="35"/>
       <c r="G246" s="35"/>
@@ -8736,12 +8730,12 @@
         <v>0</v>
       </c>
       <c r="E247" s="37" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F247" s="38"/>
       <c r="G247" s="38"/>
       <c r="H247" s="37" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="248" ht="16.5" spans="1:8">
@@ -8759,12 +8753,12 @@
         <v>0</v>
       </c>
       <c r="E248" s="37" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F248" s="38"/>
       <c r="G248" s="38"/>
       <c r="H248" s="37" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="249" ht="16.5" spans="1:8">
@@ -8782,12 +8776,12 @@
         <v>0</v>
       </c>
       <c r="E249" s="37" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F249" s="38"/>
       <c r="G249" s="38"/>
       <c r="H249" s="37" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="250" ht="16.5" spans="1:8">
@@ -8805,12 +8799,12 @@
         <v>0</v>
       </c>
       <c r="E250" s="37" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F250" s="38"/>
       <c r="G250" s="38"/>
       <c r="H250" s="37" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="251" ht="16.5" spans="1:8">
@@ -8828,12 +8822,12 @@
         <v>0</v>
       </c>
       <c r="E251" s="37" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F251" s="38"/>
       <c r="G251" s="38"/>
       <c r="H251" s="37" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="252" ht="16.5" spans="1:8">
@@ -8851,12 +8845,12 @@
         <v>0</v>
       </c>
       <c r="E252" s="37" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F252" s="38"/>
       <c r="G252" s="38"/>
       <c r="H252" s="37" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="253" ht="16.5" spans="1:8">
@@ -8874,7 +8868,7 @@
         <v>1</v>
       </c>
       <c r="E253" s="37" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F253" s="38"/>
       <c r="G253" s="38"/>
@@ -8897,12 +8891,12 @@
         <v>2</v>
       </c>
       <c r="E254" s="37" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F254" s="38"/>
       <c r="G254" s="38"/>
       <c r="H254" s="37" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="255" ht="16.5" spans="1:8">
@@ -8920,17 +8914,17 @@
         <v>2</v>
       </c>
       <c r="E255" s="37" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F255" s="38"/>
       <c r="G255" s="38"/>
       <c r="H255" s="37" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="256" ht="16.5" spans="1:8">
       <c r="A256" s="37">
-        <f t="shared" ref="A256:A281" si="10">B256*100+C256</f>
+        <f t="shared" ref="A256:A283" si="10">B256*100+C256</f>
         <v>10350001</v>
       </c>
       <c r="B256" s="25">
@@ -8943,12 +8937,12 @@
         <v>0</v>
       </c>
       <c r="E256" s="25" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F256" s="39"/>
       <c r="G256" s="39"/>
       <c r="H256" s="25" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="257" ht="16.5" spans="1:8">
@@ -8966,12 +8960,12 @@
         <v>0</v>
       </c>
       <c r="E257" s="25" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F257" s="39"/>
       <c r="G257" s="39"/>
       <c r="H257" s="25" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="258" ht="16.5" spans="1:8">
@@ -8989,12 +8983,12 @@
         <v>0</v>
       </c>
       <c r="E258" s="25" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F258" s="39"/>
       <c r="G258" s="39"/>
       <c r="H258" s="25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="259" ht="16.5" spans="1:8">
@@ -9012,12 +9006,12 @@
         <v>0</v>
       </c>
       <c r="E259" s="25" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F259" s="39"/>
       <c r="G259" s="39"/>
       <c r="H259" s="25" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="260" ht="16.5" spans="1:8">
@@ -9035,12 +9029,12 @@
         <v>0</v>
       </c>
       <c r="E260" s="25" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F260" s="39"/>
       <c r="G260" s="39"/>
       <c r="H260" s="25" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="261" ht="16.5" spans="1:8">
@@ -9058,12 +9052,12 @@
         <v>0</v>
       </c>
       <c r="E261" s="25" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F261" s="39"/>
       <c r="G261" s="39"/>
       <c r="H261" s="25" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="262" ht="16.5" spans="1:8">
@@ -9081,7 +9075,7 @@
         <v>1</v>
       </c>
       <c r="E262" s="25" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F262" s="39"/>
       <c r="G262" s="39"/>
@@ -9104,12 +9098,12 @@
         <v>2</v>
       </c>
       <c r="E263" s="25" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F263" s="39"/>
       <c r="G263" s="39"/>
       <c r="H263" s="25" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="264" ht="16.5" spans="1:8">
@@ -9127,12 +9121,12 @@
         <v>2</v>
       </c>
       <c r="E264" s="25" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F264" s="39"/>
       <c r="G264" s="39"/>
       <c r="H264" s="25" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="265" ht="16.5" spans="1:8">
@@ -9150,7 +9144,7 @@
         <v>2</v>
       </c>
       <c r="E265" s="25" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F265" s="39"/>
       <c r="G265" s="39"/>
@@ -9173,7 +9167,7 @@
         <v>2</v>
       </c>
       <c r="E266" s="25" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F266" s="39"/>
       <c r="G266" s="39"/>
@@ -9196,7 +9190,7 @@
         <v>2</v>
       </c>
       <c r="E267" s="25" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F267" s="39"/>
       <c r="G267" s="39"/>
@@ -9219,17 +9213,17 @@
         <v>2</v>
       </c>
       <c r="E268" s="25" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F268" s="39"/>
       <c r="G268" s="39"/>
       <c r="H268" s="25" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="269" ht="16.5" spans="1:8">
       <c r="A269" s="37">
-        <f>B269*100+C269</f>
+        <f t="shared" si="10"/>
         <v>10350014</v>
       </c>
       <c r="B269" s="25">
@@ -9242,17 +9236,17 @@
         <v>2</v>
       </c>
       <c r="E269" s="25" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F269" s="39"/>
       <c r="G269" s="39"/>
       <c r="H269" s="25" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="270" ht="16.5" spans="1:8">
       <c r="A270" s="40">
-        <f>B270*100+C270</f>
+        <f t="shared" si="10"/>
         <v>10350101</v>
       </c>
       <c r="B270" s="40">
@@ -9265,17 +9259,17 @@
         <v>0</v>
       </c>
       <c r="E270" s="40" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F270" s="41"/>
       <c r="G270" s="41"/>
       <c r="H270" s="40" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="271" ht="16.5" spans="1:8">
       <c r="A271" s="40">
-        <f>B271*100+C271</f>
+        <f t="shared" si="10"/>
         <v>10350102</v>
       </c>
       <c r="B271" s="40">
@@ -9288,17 +9282,17 @@
         <v>0</v>
       </c>
       <c r="E271" s="40" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F271" s="41"/>
       <c r="G271" s="41"/>
       <c r="H271" s="40" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="272" ht="16.5" spans="1:8">
       <c r="A272" s="40">
-        <f>B272*100+C272</f>
+        <f t="shared" si="10"/>
         <v>10350103</v>
       </c>
       <c r="B272" s="40">
@@ -9311,17 +9305,17 @@
         <v>0</v>
       </c>
       <c r="E272" s="40" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F272" s="41"/>
       <c r="G272" s="41"/>
       <c r="H272" s="40" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="273" ht="16.5" spans="1:8">
       <c r="A273" s="40">
-        <f>B273*100+C273</f>
+        <f t="shared" si="10"/>
         <v>10350104</v>
       </c>
       <c r="B273" s="40">
@@ -9334,17 +9328,17 @@
         <v>0</v>
       </c>
       <c r="E273" s="40" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F273" s="41"/>
       <c r="G273" s="41"/>
       <c r="H273" s="40" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="274" ht="16.5" spans="1:8">
       <c r="A274" s="40">
-        <f>B274*100+C274</f>
+        <f t="shared" si="10"/>
         <v>10350105</v>
       </c>
       <c r="B274" s="40">
@@ -9357,17 +9351,17 @@
         <v>0</v>
       </c>
       <c r="E274" s="40" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F274" s="41"/>
       <c r="G274" s="41"/>
       <c r="H274" s="40" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="275" ht="16.5" spans="1:8">
       <c r="A275" s="40">
-        <f>B275*100+C275</f>
+        <f t="shared" si="10"/>
         <v>10350106</v>
       </c>
       <c r="B275" s="40">
@@ -9380,17 +9374,17 @@
         <v>0</v>
       </c>
       <c r="E275" s="40" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F275" s="41"/>
       <c r="G275" s="41"/>
       <c r="H275" s="40" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="276" ht="16.5" spans="1:8">
       <c r="A276" s="40">
-        <f>B276*100+C276</f>
+        <f t="shared" si="10"/>
         <v>10350107</v>
       </c>
       <c r="B276" s="40">
@@ -9403,7 +9397,7 @@
         <v>1</v>
       </c>
       <c r="E276" s="40" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F276" s="41"/>
       <c r="G276" s="41"/>
@@ -9413,7 +9407,7 @@
     </row>
     <row r="277" ht="16.5" spans="1:8">
       <c r="A277" s="40">
-        <f>B277*100+C277</f>
+        <f t="shared" si="10"/>
         <v>10350108</v>
       </c>
       <c r="B277" s="40">
@@ -9426,17 +9420,17 @@
         <v>2</v>
       </c>
       <c r="E277" s="40" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F277" s="41"/>
       <c r="G277" s="41"/>
       <c r="H277" s="40" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="278" ht="16.5" spans="1:8">
       <c r="A278" s="40">
-        <f>B278*100+C278</f>
+        <f t="shared" si="10"/>
         <v>10350109</v>
       </c>
       <c r="B278" s="40">
@@ -9449,17 +9443,17 @@
         <v>2</v>
       </c>
       <c r="E278" s="40" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F278" s="41"/>
       <c r="G278" s="41"/>
       <c r="H278" s="40" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="279" ht="16.5" spans="1:8">
       <c r="A279" s="40">
-        <f>B279*100+C279</f>
+        <f t="shared" si="10"/>
         <v>10350110</v>
       </c>
       <c r="B279" s="40">
@@ -9472,7 +9466,7 @@
         <v>2</v>
       </c>
       <c r="E279" s="40" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F279" s="41"/>
       <c r="G279" s="41"/>
@@ -9482,7 +9476,7 @@
     </row>
     <row r="280" ht="16.5" spans="1:8">
       <c r="A280" s="40">
-        <f>B280*100+C280</f>
+        <f t="shared" si="10"/>
         <v>10350111</v>
       </c>
       <c r="B280" s="40">
@@ -9495,7 +9489,7 @@
         <v>2</v>
       </c>
       <c r="E280" s="40" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F280" s="41"/>
       <c r="G280" s="41"/>
@@ -9505,7 +9499,7 @@
     </row>
     <row r="281" ht="16.5" spans="1:8">
       <c r="A281" s="40">
-        <f>B281*100+C281</f>
+        <f t="shared" si="10"/>
         <v>10350112</v>
       </c>
       <c r="B281" s="40">
@@ -9518,7 +9512,7 @@
         <v>2</v>
       </c>
       <c r="E281" s="40" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F281" s="41"/>
       <c r="G281" s="41"/>
@@ -9528,7 +9522,7 @@
     </row>
     <row r="282" ht="16.5" spans="1:8">
       <c r="A282" s="40">
-        <f>B282*100+C282</f>
+        <f t="shared" si="10"/>
         <v>10350113</v>
       </c>
       <c r="B282" s="40">
@@ -9541,17 +9535,17 @@
         <v>2</v>
       </c>
       <c r="E282" s="40" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F282" s="41"/>
       <c r="G282" s="41"/>
       <c r="H282" s="40" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="283" ht="16.5" spans="1:8">
       <c r="A283" s="40">
-        <f>B283*100+C283</f>
+        <f t="shared" si="10"/>
         <v>10350114</v>
       </c>
       <c r="B283" s="40">
@@ -9564,12 +9558,12 @@
         <v>2</v>
       </c>
       <c r="E283" s="40" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F283" s="41"/>
       <c r="G283" s="41"/>
-      <c r="H283" s="42" t="s">
-        <v>377</v>
+      <c r="H283" s="41" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="396">
   <si>
     <t>图标</t>
   </si>
@@ -1194,58 +1194,58 @@
     <t>空格符号</t>
   </si>
   <si>
-    <t>jszc_icon_1.png</t>
-  </si>
-  <si>
-    <t>jszc_icon_2.png</t>
+    <t>jszc_icon_bianpao</t>
+  </si>
+  <si>
+    <t>jszc_icon_tongqian</t>
   </si>
   <si>
     <t>钱币</t>
   </si>
   <si>
-    <t>jszc_icon_3.png</t>
+    <t>jszc_icon_denglong</t>
   </si>
   <si>
     <t>话筒</t>
   </si>
   <si>
-    <t>jszc_icon_4.png</t>
-  </si>
-  <si>
-    <t>jszc_icon_5.png</t>
+    <t>jszc_icon_hongbao</t>
+  </si>
+  <si>
+    <t>jszc_icon_yuruyi</t>
   </si>
   <si>
     <t>项链</t>
   </si>
   <si>
-    <t>jszc_icon_6.png</t>
-  </si>
-  <si>
-    <t>jszc_icon_7.png</t>
-  </si>
-  <si>
-    <t>jszc_icon_8.png</t>
+    <t>jszc_icon_yuanbao</t>
+  </si>
+  <si>
+    <t>jszc_wild</t>
+  </si>
+  <si>
+    <t>jszc_d1</t>
   </si>
   <si>
     <t>奖金符号</t>
   </si>
   <si>
-    <t>jszc_icon_9.png</t>
+    <t>jszc_jiangchi_MINI</t>
   </si>
   <si>
     <t>Mini</t>
   </si>
   <si>
-    <t>jszc_icon_10.png</t>
-  </si>
-  <si>
-    <t>jszc_icon_11.png</t>
-  </si>
-  <si>
-    <t>jszc_icon_12.png</t>
-  </si>
-  <si>
-    <t>jszc_icon_13.png</t>
+    <t>jszc_jiangchi_MINOR</t>
+  </si>
+  <si>
+    <t>jszc_jiangchi_MAJOR</t>
+  </si>
+  <si>
+    <t>jszc_jiangchi_GRAND</t>
+  </si>
+  <si>
+    <t>jszc_d5</t>
   </si>
   <si>
     <t>jszc_icon_14.png</t>
@@ -1254,49 +1254,52 @@
     <t>隐藏符号，用于触发金钱兔模式</t>
   </si>
   <si>
-    <t>jqt_icon_1.png</t>
+    <t>jqt_tb_4</t>
   </si>
   <si>
     <t>萝卜</t>
   </si>
   <si>
-    <t>jqt_icon_2.png</t>
+    <t>jqt_tb_7</t>
   </si>
   <si>
     <t>烟花</t>
   </si>
   <si>
-    <t>jqt_icon_3.png</t>
-  </si>
-  <si>
-    <t>jqt_icon_4.png</t>
-  </si>
-  <si>
-    <t>jqt_icon_5.png</t>
+    <t>jqt_tb_2</t>
+  </si>
+  <si>
+    <t>jqt_tb_3</t>
+  </si>
+  <si>
+    <t>jqt_tb_6</t>
   </si>
   <si>
     <t>百宝袋</t>
   </si>
   <si>
-    <t>jqt_icon_6.png</t>
-  </si>
-  <si>
-    <t>jqt_icon_7.png</t>
-  </si>
-  <si>
-    <t>jqt_icon_8.png</t>
-  </si>
-  <si>
-    <t>jqt_icon_9.png</t>
-  </si>
-  <si>
-    <t>jqt_icon_10.png</t>
-  </si>
-  <si>
-    <t>jqt_icon_11.png</t>
-  </si>
-  <si>
-    <t>jqt_icon_12.png</t>
+    <t>jqt_tb_5</t>
+  </si>
+  <si>
+    <t>jqt_tb_1</t>
+  </si>
+  <si>
+    <t>jqt_tb_12</t>
+  </si>
+  <si>
+    <t>jqt_tb_8</t>
+  </si>
+  <si>
+    <t>jqt_tb_9</t>
+  </si>
+  <si>
+    <t>jqt_tb_10</t>
+  </si>
+  <si>
+    <t>jqt_tb_11</t>
+  </si>
+  <si>
+    <t>jqt_tb_13</t>
   </si>
   <si>
     <t>jqt_icon_13.png</t>
@@ -1495,12 +1498,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -1510,6 +1507,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -9535,7 +9538,7 @@
         <v>2</v>
       </c>
       <c r="E282" s="40" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F282" s="41"/>
       <c r="G282" s="41"/>
@@ -9558,7 +9561,7 @@
         <v>2</v>
       </c>
       <c r="E283" s="40" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F283" s="41"/>
       <c r="G283" s="41"/>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="409">
   <si>
     <t>图标</t>
   </si>
@@ -1303,6 +1303,45 @@
   </si>
   <si>
     <t>jqt_icon_13.png</t>
+  </si>
+  <si>
+    <t>ssff_tb_1</t>
+  </si>
+  <si>
+    <t>花生</t>
+  </si>
+  <si>
+    <t>ssff_tb_2</t>
+  </si>
+  <si>
+    <t>ssff_tb_3</t>
+  </si>
+  <si>
+    <t>ssff_tb_4</t>
+  </si>
+  <si>
+    <t>ssff_tb_5</t>
+  </si>
+  <si>
+    <t>ssff_tb_6</t>
+  </si>
+  <si>
+    <t>福字</t>
+  </si>
+  <si>
+    <t>ssff_tb_7</t>
+  </si>
+  <si>
+    <t>ssff_tb_8</t>
+  </si>
+  <si>
+    <t>Jackpot</t>
+  </si>
+  <si>
+    <t>ssff_tb_9</t>
+  </si>
+  <si>
+    <t>隐藏符号，用于触发福鼠模式</t>
   </si>
 </sst>
 </file>
@@ -1505,14 +1544,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2533,7 +2572,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M283"/>
+  <dimension ref="A1:M292"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -9565,8 +9604,215 @@
       </c>
       <c r="F283" s="41"/>
       <c r="G283" s="41"/>
-      <c r="H283" s="41" t="s">
+      <c r="H283" s="40" t="s">
         <v>378</v>
+      </c>
+    </row>
+    <row r="284" ht="16.5" spans="1:8">
+      <c r="A284" s="27">
+        <f t="shared" ref="A284:A291" si="11">B284*100+C284</f>
+        <v>10360001</v>
+      </c>
+      <c r="B284" s="27">
+        <v>103600</v>
+      </c>
+      <c r="C284" s="27">
+        <v>1</v>
+      </c>
+      <c r="D284" s="27">
+        <v>0</v>
+      </c>
+      <c r="E284" s="27" t="s">
+        <v>396</v>
+      </c>
+      <c r="F284" s="28"/>
+      <c r="G284" s="28"/>
+      <c r="H284" s="27" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="285" ht="16.5" spans="1:8">
+      <c r="A285" s="27">
+        <f t="shared" si="11"/>
+        <v>10360002</v>
+      </c>
+      <c r="B285" s="27">
+        <v>103600</v>
+      </c>
+      <c r="C285" s="27">
+        <v>2</v>
+      </c>
+      <c r="D285" s="27">
+        <v>0</v>
+      </c>
+      <c r="E285" s="27" t="s">
+        <v>398</v>
+      </c>
+      <c r="F285" s="28"/>
+      <c r="G285" s="28"/>
+      <c r="H285" s="27" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="286" ht="16.5" spans="1:8">
+      <c r="A286" s="27">
+        <f t="shared" si="11"/>
+        <v>10360003</v>
+      </c>
+      <c r="B286" s="27">
+        <v>103600</v>
+      </c>
+      <c r="C286" s="27">
+        <v>3</v>
+      </c>
+      <c r="D286" s="27">
+        <v>0</v>
+      </c>
+      <c r="E286" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="F286" s="28"/>
+      <c r="G286" s="28"/>
+      <c r="H286" s="27" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="287" ht="16.5" spans="1:8">
+      <c r="A287" s="27">
+        <f t="shared" si="11"/>
+        <v>10360004</v>
+      </c>
+      <c r="B287" s="27">
+        <v>103600</v>
+      </c>
+      <c r="C287" s="27">
+        <v>4</v>
+      </c>
+      <c r="D287" s="27">
+        <v>0</v>
+      </c>
+      <c r="E287" s="27" t="s">
+        <v>400</v>
+      </c>
+      <c r="F287" s="28"/>
+      <c r="G287" s="28"/>
+      <c r="H287" s="27" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="288" ht="16.5" spans="1:8">
+      <c r="A288" s="27">
+        <f t="shared" si="11"/>
+        <v>10360005</v>
+      </c>
+      <c r="B288" s="27">
+        <v>103600</v>
+      </c>
+      <c r="C288" s="27">
+        <v>5</v>
+      </c>
+      <c r="D288" s="27">
+        <v>0</v>
+      </c>
+      <c r="E288" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="F288" s="28"/>
+      <c r="G288" s="28"/>
+      <c r="H288" s="27" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="289" ht="16.5" spans="1:8">
+      <c r="A289" s="27">
+        <f t="shared" si="11"/>
+        <v>10360006</v>
+      </c>
+      <c r="B289" s="27">
+        <v>103600</v>
+      </c>
+      <c r="C289" s="27">
+        <v>6</v>
+      </c>
+      <c r="D289" s="27">
+        <v>0</v>
+      </c>
+      <c r="E289" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="F289" s="28"/>
+      <c r="G289" s="28"/>
+      <c r="H289" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="290" ht="16.5" spans="1:8">
+      <c r="A290" s="27">
+        <f t="shared" si="11"/>
+        <v>10360007</v>
+      </c>
+      <c r="B290" s="27">
+        <v>103600</v>
+      </c>
+      <c r="C290" s="27">
+        <v>7</v>
+      </c>
+      <c r="D290" s="27">
+        <v>1</v>
+      </c>
+      <c r="E290" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="F290" s="28"/>
+      <c r="G290" s="28"/>
+      <c r="H290" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="291" ht="16.5" spans="1:8">
+      <c r="A291" s="27">
+        <f t="shared" si="11"/>
+        <v>10360008</v>
+      </c>
+      <c r="B291" s="27">
+        <v>103600</v>
+      </c>
+      <c r="C291" s="27">
+        <v>8</v>
+      </c>
+      <c r="D291" s="27">
+        <v>3</v>
+      </c>
+      <c r="E291" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="F291" s="28"/>
+      <c r="G291" s="28"/>
+      <c r="H291" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="292" ht="16.5" spans="1:8">
+      <c r="A292" s="27">
+        <f>B292*100+C292</f>
+        <v>10360009</v>
+      </c>
+      <c r="B292" s="27">
+        <v>103600</v>
+      </c>
+      <c r="C292" s="27">
+        <v>9</v>
+      </c>
+      <c r="D292" s="27">
+        <v>2</v>
+      </c>
+      <c r="E292" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="F292" s="28"/>
+      <c r="G292" s="28"/>
+      <c r="H292" s="27" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="662">
   <si>
     <t>图标</t>
   </si>
@@ -1998,28 +1998,109 @@
     <t>zsvshds_icon_21.png</t>
   </si>
   <si>
-    <t>wild1</t>
-  </si>
-  <si>
     <t>zsvshds_icon_22.png</t>
   </si>
   <si>
-    <t>wild2</t>
+    <t>vs1-普通模式</t>
   </si>
   <si>
     <t>zsvshds_icon_23.png</t>
   </si>
   <si>
+    <t>vs2-普通模式</t>
+  </si>
+  <si>
     <t>zsvshds_icon_24.png</t>
   </si>
   <si>
+    <t>vs3-普通模式</t>
+  </si>
+  <si>
     <t>zsvshds_icon_25.png</t>
   </si>
   <si>
+    <t>vs4-普通模式</t>
+  </si>
+  <si>
     <t>zsvshds_icon_26.png</t>
   </si>
   <si>
+    <t>vs1-宙斯</t>
+  </si>
+  <si>
     <t>zsvshds_icon_27.png</t>
+  </si>
+  <si>
+    <t>vs2-宙斯</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_28.png</t>
+  </si>
+  <si>
+    <t>vs3-宙斯</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_29.png</t>
+  </si>
+  <si>
+    <t>vs4-宙斯</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_30.png</t>
+  </si>
+  <si>
+    <t>vs1-哈迪斯</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_31.png</t>
+  </si>
+  <si>
+    <t>vs2-哈迪斯</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_32.png</t>
+  </si>
+  <si>
+    <t>vs3-哈迪斯</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_33.png</t>
+  </si>
+  <si>
+    <t>vs4-哈迪斯</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_34.png</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_35.png</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_36.png</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_37.png</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_38.png</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_39.png</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_40.png</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_41.png</t>
+  </si>
+  <si>
+    <t>宙斯百搭</t>
+  </si>
+  <si>
+    <t>zsvshds_icon_42.png</t>
+  </si>
+  <si>
+    <t>哈迪斯百搭</t>
   </si>
 </sst>
 </file>
@@ -2239,7 +2320,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2309,12 +2390,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2663,7 +2738,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2688,7 +2763,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2712,16 +2787,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2730,89 +2805,90 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2945,14 +3021,11 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -3002,6 +3075,7 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -3271,7 +3345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N422"/>
+  <dimension ref="A1:N433"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -8868,7 +8942,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
       <c r="H211" s="33"/>
-      <c r="I211" s="45" t="s">
+      <c r="I211" s="44" t="s">
         <v>300</v>
       </c>
     </row>
@@ -13301,22 +13375,22 @@
         <f t="shared" ref="A388:A414" si="15">B388*100+C388</f>
         <v>10200001</v>
       </c>
-      <c r="B388" s="44">
+      <c r="B388" s="43">
         <v>102000</v>
       </c>
-      <c r="C388" s="44">
+      <c r="C388" s="43">
         <v>1</v>
       </c>
-      <c r="D388" s="44">
-        <v>0</v>
-      </c>
-      <c r="E388" s="44" t="s">
+      <c r="D388" s="43">
+        <v>0</v>
+      </c>
+      <c r="E388" s="43" t="s">
         <v>586</v>
       </c>
-      <c r="F388" s="44"/>
-      <c r="G388" s="44"/>
-      <c r="H388" s="44"/>
-      <c r="I388" s="44" t="s">
+      <c r="F388" s="43"/>
+      <c r="G388" s="43"/>
+      <c r="H388" s="43"/>
+      <c r="I388" s="43" t="s">
         <v>587</v>
       </c>
     </row>
@@ -13325,22 +13399,22 @@
         <f t="shared" si="15"/>
         <v>10200002</v>
       </c>
-      <c r="B389" s="44">
+      <c r="B389" s="43">
         <v>102000</v>
       </c>
-      <c r="C389" s="44">
+      <c r="C389" s="43">
         <v>2</v>
       </c>
-      <c r="D389" s="44">
-        <v>0</v>
-      </c>
-      <c r="E389" s="44" t="s">
+      <c r="D389" s="43">
+        <v>0</v>
+      </c>
+      <c r="E389" s="43" t="s">
         <v>588</v>
       </c>
-      <c r="F389" s="44"/>
-      <c r="G389" s="44"/>
-      <c r="H389" s="44"/>
-      <c r="I389" s="44" t="s">
+      <c r="F389" s="43"/>
+      <c r="G389" s="43"/>
+      <c r="H389" s="43"/>
+      <c r="I389" s="43" t="s">
         <v>589</v>
       </c>
     </row>
@@ -13349,22 +13423,22 @@
         <f t="shared" si="15"/>
         <v>10200003</v>
       </c>
-      <c r="B390" s="44">
+      <c r="B390" s="43">
         <v>102000</v>
       </c>
-      <c r="C390" s="44">
+      <c r="C390" s="43">
         <v>3</v>
       </c>
-      <c r="D390" s="44">
-        <v>0</v>
-      </c>
-      <c r="E390" s="44" t="s">
+      <c r="D390" s="43">
+        <v>0</v>
+      </c>
+      <c r="E390" s="43" t="s">
         <v>590</v>
       </c>
-      <c r="F390" s="44"/>
-      <c r="G390" s="44"/>
-      <c r="H390" s="44"/>
-      <c r="I390" s="44" t="s">
+      <c r="F390" s="43"/>
+      <c r="G390" s="43"/>
+      <c r="H390" s="43"/>
+      <c r="I390" s="43" t="s">
         <v>591</v>
       </c>
     </row>
@@ -13373,22 +13447,22 @@
         <f t="shared" si="15"/>
         <v>10200004</v>
       </c>
-      <c r="B391" s="44">
+      <c r="B391" s="43">
         <v>102000</v>
       </c>
-      <c r="C391" s="44">
+      <c r="C391" s="43">
         <v>4</v>
       </c>
-      <c r="D391" s="44">
-        <v>0</v>
-      </c>
-      <c r="E391" s="44" t="s">
+      <c r="D391" s="43">
+        <v>0</v>
+      </c>
+      <c r="E391" s="43" t="s">
         <v>592</v>
       </c>
-      <c r="F391" s="44"/>
-      <c r="G391" s="44"/>
-      <c r="H391" s="44"/>
-      <c r="I391" s="44" t="s">
+      <c r="F391" s="43"/>
+      <c r="G391" s="43"/>
+      <c r="H391" s="43"/>
+      <c r="I391" s="43" t="s">
         <v>593</v>
       </c>
     </row>
@@ -13397,22 +13471,22 @@
         <f t="shared" si="15"/>
         <v>10200005</v>
       </c>
-      <c r="B392" s="44">
+      <c r="B392" s="43">
         <v>102000</v>
       </c>
-      <c r="C392" s="44">
+      <c r="C392" s="43">
         <v>5</v>
       </c>
-      <c r="D392" s="44">
-        <v>0</v>
-      </c>
-      <c r="E392" s="44" t="s">
+      <c r="D392" s="43">
+        <v>0</v>
+      </c>
+      <c r="E392" s="43" t="s">
         <v>594</v>
       </c>
-      <c r="F392" s="44"/>
-      <c r="G392" s="44"/>
-      <c r="H392" s="44"/>
-      <c r="I392" s="44" t="s">
+      <c r="F392" s="43"/>
+      <c r="G392" s="43"/>
+      <c r="H392" s="43"/>
+      <c r="I392" s="43" t="s">
         <v>595</v>
       </c>
     </row>
@@ -13421,22 +13495,22 @@
         <f t="shared" si="15"/>
         <v>10200006</v>
       </c>
-      <c r="B393" s="44">
+      <c r="B393" s="43">
         <v>102000</v>
       </c>
-      <c r="C393" s="44">
+      <c r="C393" s="43">
         <v>6</v>
       </c>
-      <c r="D393" s="44">
-        <v>0</v>
-      </c>
-      <c r="E393" s="44" t="s">
+      <c r="D393" s="43">
+        <v>0</v>
+      </c>
+      <c r="E393" s="43" t="s">
         <v>596</v>
       </c>
-      <c r="F393" s="44"/>
-      <c r="G393" s="44"/>
-      <c r="H393" s="44"/>
-      <c r="I393" s="44" t="s">
+      <c r="F393" s="43"/>
+      <c r="G393" s="43"/>
+      <c r="H393" s="43"/>
+      <c r="I393" s="43" t="s">
         <v>597</v>
       </c>
     </row>
@@ -13445,22 +13519,22 @@
         <f t="shared" si="15"/>
         <v>10200007</v>
       </c>
-      <c r="B394" s="44">
+      <c r="B394" s="43">
         <v>102000</v>
       </c>
-      <c r="C394" s="44">
+      <c r="C394" s="43">
         <v>7</v>
       </c>
-      <c r="D394" s="44">
-        <v>0</v>
-      </c>
-      <c r="E394" s="44" t="s">
+      <c r="D394" s="43">
+        <v>0</v>
+      </c>
+      <c r="E394" s="43" t="s">
         <v>598</v>
       </c>
-      <c r="F394" s="44"/>
-      <c r="G394" s="44"/>
-      <c r="H394" s="44"/>
-      <c r="I394" s="44" t="s">
+      <c r="F394" s="43"/>
+      <c r="G394" s="43"/>
+      <c r="H394" s="43"/>
+      <c r="I394" s="43" t="s">
         <v>599</v>
       </c>
     </row>
@@ -13469,22 +13543,22 @@
         <f t="shared" si="15"/>
         <v>10200008</v>
       </c>
-      <c r="B395" s="44">
+      <c r="B395" s="43">
         <v>102000</v>
       </c>
-      <c r="C395" s="44">
+      <c r="C395" s="43">
         <v>8</v>
       </c>
-      <c r="D395" s="44">
-        <v>0</v>
-      </c>
-      <c r="E395" s="44" t="s">
+      <c r="D395" s="43">
+        <v>0</v>
+      </c>
+      <c r="E395" s="43" t="s">
         <v>600</v>
       </c>
-      <c r="F395" s="44"/>
-      <c r="G395" s="44"/>
-      <c r="H395" s="44"/>
-      <c r="I395" s="44" t="s">
+      <c r="F395" s="43"/>
+      <c r="G395" s="43"/>
+      <c r="H395" s="43"/>
+      <c r="I395" s="43" t="s">
         <v>601</v>
       </c>
     </row>
@@ -13493,22 +13567,22 @@
         <f t="shared" si="15"/>
         <v>10200009</v>
       </c>
-      <c r="B396" s="44">
+      <c r="B396" s="43">
         <v>102000</v>
       </c>
-      <c r="C396" s="44">
+      <c r="C396" s="43">
         <v>9</v>
       </c>
-      <c r="D396" s="44">
-        <v>0</v>
-      </c>
-      <c r="E396" s="44" t="s">
+      <c r="D396" s="43">
+        <v>0</v>
+      </c>
+      <c r="E396" s="43" t="s">
         <v>602</v>
       </c>
-      <c r="F396" s="44"/>
-      <c r="G396" s="44"/>
-      <c r="H396" s="44"/>
-      <c r="I396" s="44" t="s">
+      <c r="F396" s="43"/>
+      <c r="G396" s="43"/>
+      <c r="H396" s="43"/>
+      <c r="I396" s="43" t="s">
         <v>603</v>
       </c>
     </row>
@@ -13517,22 +13591,22 @@
         <f t="shared" si="15"/>
         <v>10200010</v>
       </c>
-      <c r="B397" s="44">
+      <c r="B397" s="43">
         <v>102000</v>
       </c>
-      <c r="C397" s="44">
+      <c r="C397" s="43">
         <v>10</v>
       </c>
-      <c r="D397" s="44">
-        <v>0</v>
-      </c>
-      <c r="E397" s="44" t="s">
+      <c r="D397" s="43">
+        <v>0</v>
+      </c>
+      <c r="E397" s="43" t="s">
         <v>604</v>
       </c>
-      <c r="F397" s="44"/>
-      <c r="G397" s="44"/>
-      <c r="H397" s="44"/>
-      <c r="I397" s="44" t="s">
+      <c r="F397" s="43"/>
+      <c r="G397" s="43"/>
+      <c r="H397" s="43"/>
+      <c r="I397" s="43" t="s">
         <v>605</v>
       </c>
     </row>
@@ -13541,22 +13615,22 @@
         <f t="shared" si="15"/>
         <v>10200011</v>
       </c>
-      <c r="B398" s="44">
+      <c r="B398" s="43">
         <v>102000</v>
       </c>
-      <c r="C398" s="44">
+      <c r="C398" s="43">
         <v>11</v>
       </c>
-      <c r="D398" s="44">
-        <v>0</v>
-      </c>
-      <c r="E398" s="44" t="s">
+      <c r="D398" s="43">
+        <v>0</v>
+      </c>
+      <c r="E398" s="43" t="s">
         <v>606</v>
       </c>
-      <c r="F398" s="44"/>
-      <c r="G398" s="44"/>
-      <c r="H398" s="44"/>
-      <c r="I398" s="44" t="s">
+      <c r="F398" s="43"/>
+      <c r="G398" s="43"/>
+      <c r="H398" s="43"/>
+      <c r="I398" s="43" t="s">
         <v>607</v>
       </c>
     </row>
@@ -13565,22 +13639,22 @@
         <f t="shared" si="15"/>
         <v>10200012</v>
       </c>
-      <c r="B399" s="44">
+      <c r="B399" s="43">
         <v>102000</v>
       </c>
-      <c r="C399" s="44">
+      <c r="C399" s="43">
         <v>12</v>
       </c>
-      <c r="D399" s="44">
-        <v>0</v>
-      </c>
-      <c r="E399" s="44" t="s">
+      <c r="D399" s="43">
+        <v>0</v>
+      </c>
+      <c r="E399" s="43" t="s">
         <v>608</v>
       </c>
-      <c r="F399" s="44"/>
-      <c r="G399" s="44"/>
-      <c r="H399" s="44"/>
-      <c r="I399" s="44" t="s">
+      <c r="F399" s="43"/>
+      <c r="G399" s="43"/>
+      <c r="H399" s="43"/>
+      <c r="I399" s="43" t="s">
         <v>609</v>
       </c>
     </row>
@@ -13589,22 +13663,22 @@
         <f t="shared" si="15"/>
         <v>10200013</v>
       </c>
-      <c r="B400" s="44">
+      <c r="B400" s="43">
         <v>102000</v>
       </c>
-      <c r="C400" s="44">
+      <c r="C400" s="43">
         <v>13</v>
       </c>
-      <c r="D400" s="44">
-        <v>0</v>
-      </c>
-      <c r="E400" s="44" t="s">
+      <c r="D400" s="43">
+        <v>0</v>
+      </c>
+      <c r="E400" s="43" t="s">
         <v>610</v>
       </c>
-      <c r="F400" s="44"/>
-      <c r="G400" s="44"/>
-      <c r="H400" s="44"/>
-      <c r="I400" s="44" t="s">
+      <c r="F400" s="43"/>
+      <c r="G400" s="43"/>
+      <c r="H400" s="43"/>
+      <c r="I400" s="43" t="s">
         <v>611</v>
       </c>
     </row>
@@ -13613,22 +13687,22 @@
         <f t="shared" si="15"/>
         <v>10200014</v>
       </c>
-      <c r="B401" s="44">
+      <c r="B401" s="43">
         <v>102000</v>
       </c>
-      <c r="C401" s="44">
+      <c r="C401" s="43">
         <v>14</v>
       </c>
-      <c r="D401" s="44">
-        <v>0</v>
-      </c>
-      <c r="E401" s="44" t="s">
+      <c r="D401" s="43">
+        <v>0</v>
+      </c>
+      <c r="E401" s="43" t="s">
         <v>612</v>
       </c>
-      <c r="F401" s="44"/>
-      <c r="G401" s="44"/>
-      <c r="H401" s="44"/>
-      <c r="I401" s="44" t="s">
+      <c r="F401" s="43"/>
+      <c r="G401" s="43"/>
+      <c r="H401" s="43"/>
+      <c r="I401" s="43" t="s">
         <v>613</v>
       </c>
     </row>
@@ -13637,22 +13711,22 @@
         <f t="shared" si="15"/>
         <v>10200015</v>
       </c>
-      <c r="B402" s="44">
+      <c r="B402" s="43">
         <v>102000</v>
       </c>
-      <c r="C402" s="44">
+      <c r="C402" s="43">
         <v>15</v>
       </c>
-      <c r="D402" s="44">
-        <v>0</v>
-      </c>
-      <c r="E402" s="44" t="s">
+      <c r="D402" s="43">
+        <v>0</v>
+      </c>
+      <c r="E402" s="43" t="s">
         <v>614</v>
       </c>
-      <c r="F402" s="44"/>
-      <c r="G402" s="44"/>
-      <c r="H402" s="44"/>
-      <c r="I402" s="44" t="s">
+      <c r="F402" s="43"/>
+      <c r="G402" s="43"/>
+      <c r="H402" s="43"/>
+      <c r="I402" s="43" t="s">
         <v>615</v>
       </c>
     </row>
@@ -13661,22 +13735,22 @@
         <f t="shared" si="15"/>
         <v>10200016</v>
       </c>
-      <c r="B403" s="44">
+      <c r="B403" s="43">
         <v>102000</v>
       </c>
-      <c r="C403" s="44">
+      <c r="C403" s="43">
         <v>16</v>
       </c>
-      <c r="D403" s="44">
-        <v>0</v>
-      </c>
-      <c r="E403" s="44" t="s">
+      <c r="D403" s="43">
+        <v>0</v>
+      </c>
+      <c r="E403" s="43" t="s">
         <v>616</v>
       </c>
-      <c r="F403" s="44"/>
-      <c r="G403" s="44"/>
-      <c r="H403" s="44"/>
-      <c r="I403" s="44" t="s">
+      <c r="F403" s="43"/>
+      <c r="G403" s="43"/>
+      <c r="H403" s="43"/>
+      <c r="I403" s="43" t="s">
         <v>617</v>
       </c>
     </row>
@@ -13685,22 +13759,22 @@
         <f t="shared" si="15"/>
         <v>10200017</v>
       </c>
-      <c r="B404" s="44">
+      <c r="B404" s="43">
         <v>102000</v>
       </c>
-      <c r="C404" s="44">
+      <c r="C404" s="43">
         <v>17</v>
       </c>
-      <c r="D404" s="44">
-        <v>0</v>
-      </c>
-      <c r="E404" s="44" t="s">
+      <c r="D404" s="43">
+        <v>0</v>
+      </c>
+      <c r="E404" s="43" t="s">
         <v>618</v>
       </c>
-      <c r="F404" s="44"/>
-      <c r="G404" s="44"/>
-      <c r="H404" s="44"/>
-      <c r="I404" s="44" t="s">
+      <c r="F404" s="43"/>
+      <c r="G404" s="43"/>
+      <c r="H404" s="43"/>
+      <c r="I404" s="43" t="s">
         <v>619</v>
       </c>
     </row>
@@ -13709,22 +13783,22 @@
         <f t="shared" si="15"/>
         <v>10200018</v>
       </c>
-      <c r="B405" s="44">
+      <c r="B405" s="43">
         <v>102000</v>
       </c>
-      <c r="C405" s="44">
+      <c r="C405" s="43">
         <v>18</v>
       </c>
-      <c r="D405" s="44">
-        <v>0</v>
-      </c>
-      <c r="E405" s="44" t="s">
+      <c r="D405" s="43">
+        <v>0</v>
+      </c>
+      <c r="E405" s="43" t="s">
         <v>620</v>
       </c>
-      <c r="F405" s="44"/>
-      <c r="G405" s="44"/>
-      <c r="H405" s="44"/>
-      <c r="I405" s="44" t="s">
+      <c r="F405" s="43"/>
+      <c r="G405" s="43"/>
+      <c r="H405" s="43"/>
+      <c r="I405" s="43" t="s">
         <v>621</v>
       </c>
     </row>
@@ -13733,22 +13807,22 @@
         <f t="shared" si="15"/>
         <v>10200019</v>
       </c>
-      <c r="B406" s="44">
+      <c r="B406" s="43">
         <v>102000</v>
       </c>
-      <c r="C406" s="44">
+      <c r="C406" s="43">
         <v>19</v>
       </c>
-      <c r="D406" s="44">
-        <v>0</v>
-      </c>
-      <c r="E406" s="44" t="s">
+      <c r="D406" s="43">
+        <v>0</v>
+      </c>
+      <c r="E406" s="43" t="s">
         <v>622</v>
       </c>
-      <c r="F406" s="44"/>
-      <c r="G406" s="44"/>
-      <c r="H406" s="44"/>
-      <c r="I406" s="44" t="s">
+      <c r="F406" s="43"/>
+      <c r="G406" s="43"/>
+      <c r="H406" s="43"/>
+      <c r="I406" s="43" t="s">
         <v>623</v>
       </c>
     </row>
@@ -13757,22 +13831,22 @@
         <f t="shared" si="15"/>
         <v>10200020</v>
       </c>
-      <c r="B407" s="44">
+      <c r="B407" s="43">
         <v>102000</v>
       </c>
-      <c r="C407" s="44">
+      <c r="C407" s="43">
         <v>20</v>
       </c>
-      <c r="D407" s="44">
-        <v>0</v>
-      </c>
-      <c r="E407" s="44" t="s">
+      <c r="D407" s="43">
+        <v>0</v>
+      </c>
+      <c r="E407" s="43" t="s">
         <v>624</v>
       </c>
-      <c r="F407" s="44"/>
-      <c r="G407" s="44"/>
-      <c r="H407" s="44"/>
-      <c r="I407" s="44" t="s">
+      <c r="F407" s="43"/>
+      <c r="G407" s="43"/>
+      <c r="H407" s="43"/>
+      <c r="I407" s="43" t="s">
         <v>625</v>
       </c>
     </row>
@@ -13781,23 +13855,23 @@
         <f t="shared" si="15"/>
         <v>10200021</v>
       </c>
-      <c r="B408" s="44">
+      <c r="B408" s="43">
         <v>102000</v>
       </c>
-      <c r="C408" s="44">
+      <c r="C408" s="43">
         <v>21</v>
       </c>
-      <c r="D408" s="44">
+      <c r="D408" s="43">
         <v>1</v>
       </c>
-      <c r="E408" s="44" t="s">
+      <c r="E408" s="43" t="s">
         <v>626</v>
       </c>
-      <c r="F408" s="44"/>
-      <c r="G408" s="44"/>
-      <c r="H408" s="44"/>
-      <c r="I408" s="44" t="s">
-        <v>627</v>
+      <c r="F408" s="43"/>
+      <c r="G408" s="43"/>
+      <c r="H408" s="43"/>
+      <c r="I408" s="43" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="409" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -13805,23 +13879,23 @@
         <f t="shared" si="15"/>
         <v>10200022</v>
       </c>
-      <c r="B409" s="44">
+      <c r="B409" s="43">
         <v>102000</v>
       </c>
-      <c r="C409" s="44">
+      <c r="C409" s="43">
         <v>22</v>
       </c>
-      <c r="D409" s="44">
-        <v>1</v>
-      </c>
-      <c r="E409" s="44" t="s">
+      <c r="D409" s="43">
+        <v>2</v>
+      </c>
+      <c r="E409" s="43" t="s">
+        <v>627</v>
+      </c>
+      <c r="F409" s="43"/>
+      <c r="G409" s="43"/>
+      <c r="H409" s="43"/>
+      <c r="I409" s="43" t="s">
         <v>628</v>
-      </c>
-      <c r="F409" s="44"/>
-      <c r="G409" s="44"/>
-      <c r="H409" s="44"/>
-      <c r="I409" s="44" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="410" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -13829,23 +13903,23 @@
         <f t="shared" si="15"/>
         <v>10200023</v>
       </c>
-      <c r="B410" s="44">
+      <c r="B410" s="43">
         <v>102000</v>
       </c>
-      <c r="C410" s="44">
+      <c r="C410" s="43">
         <v>23</v>
       </c>
-      <c r="D410" s="44">
+      <c r="D410" s="43">
         <v>2</v>
       </c>
-      <c r="E410" s="44" t="s">
+      <c r="E410" s="43" t="s">
+        <v>629</v>
+      </c>
+      <c r="F410" s="43"/>
+      <c r="G410" s="43"/>
+      <c r="H410" s="43"/>
+      <c r="I410" s="43" t="s">
         <v>630</v>
-      </c>
-      <c r="F410" s="44"/>
-      <c r="G410" s="44"/>
-      <c r="H410" s="44"/>
-      <c r="I410" s="44" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="411" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -13853,23 +13927,23 @@
         <f t="shared" si="15"/>
         <v>10200024</v>
       </c>
-      <c r="B411" s="44">
+      <c r="B411" s="43">
         <v>102000</v>
       </c>
-      <c r="C411" s="44">
+      <c r="C411" s="43">
         <v>24</v>
       </c>
-      <c r="D411" s="44">
+      <c r="D411" s="43">
         <v>2</v>
       </c>
-      <c r="E411" s="44" t="s">
+      <c r="E411" s="43" t="s">
         <v>631</v>
       </c>
-      <c r="F411" s="44"/>
-      <c r="G411" s="44"/>
-      <c r="H411" s="44"/>
-      <c r="I411" s="44" t="s">
-        <v>432</v>
+      <c r="F411" s="43"/>
+      <c r="G411" s="43"/>
+      <c r="H411" s="43"/>
+      <c r="I411" s="43" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="412" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -13877,81 +13951,441 @@
         <f t="shared" si="15"/>
         <v>10200025</v>
       </c>
-      <c r="B412" s="44">
+      <c r="B412" s="43">
         <v>102000</v>
       </c>
-      <c r="C412" s="44">
+      <c r="C412" s="43">
         <v>25</v>
       </c>
-      <c r="D412" s="44">
+      <c r="D412" s="43">
         <v>2</v>
       </c>
-      <c r="E412" s="44" t="s">
-        <v>632</v>
-      </c>
-      <c r="F412" s="44"/>
-      <c r="G412" s="44"/>
-      <c r="H412" s="44"/>
-      <c r="I412" s="44" t="s">
-        <v>434</v>
+      <c r="E412" s="43" t="s">
+        <v>633</v>
+      </c>
+      <c r="F412" s="43"/>
+      <c r="G412" s="43"/>
+      <c r="H412" s="43"/>
+      <c r="I412" s="43" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="413" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A413" s="43">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="A413:A429" si="16">B413*100+C413</f>
         <v>10200026</v>
       </c>
-      <c r="B413" s="44">
+      <c r="B413" s="43">
         <v>102000</v>
       </c>
-      <c r="C413" s="44">
+      <c r="C413" s="43">
         <v>26</v>
       </c>
-      <c r="D413" s="44">
-        <v>2</v>
-      </c>
-      <c r="E413" s="44" t="s">
-        <v>633</v>
-      </c>
-      <c r="F413" s="44"/>
-      <c r="G413" s="44"/>
-      <c r="H413" s="44"/>
-      <c r="I413" s="44" t="s">
-        <v>436</v>
+      <c r="D413" s="43">
+        <v>1</v>
+      </c>
+      <c r="E413" s="43" t="s">
+        <v>635</v>
+      </c>
+      <c r="F413" s="43"/>
+      <c r="G413" s="43"/>
+      <c r="H413" s="43"/>
+      <c r="I413" s="43" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="414" s="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A414" s="43">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>10200027</v>
       </c>
-      <c r="B414" s="44">
+      <c r="B414" s="43">
         <v>102000</v>
       </c>
-      <c r="C414" s="44">
+      <c r="C414" s="43">
         <v>27</v>
       </c>
-      <c r="D414" s="44">
+      <c r="D414" s="43">
+        <v>1</v>
+      </c>
+      <c r="E414" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="F414" s="43"/>
+      <c r="G414" s="43"/>
+      <c r="H414" s="43"/>
+      <c r="I414" s="43" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="415" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A415" s="43">
+        <f t="shared" si="16"/>
+        <v>10200028</v>
+      </c>
+      <c r="B415" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C415" s="43">
+        <v>28</v>
+      </c>
+      <c r="D415" s="43">
+        <v>1</v>
+      </c>
+      <c r="E415" s="43" t="s">
+        <v>639</v>
+      </c>
+      <c r="F415" s="43"/>
+      <c r="G415" s="43"/>
+      <c r="H415" s="43"/>
+      <c r="I415" s="43" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="416" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A416" s="43">
+        <f t="shared" si="16"/>
+        <v>10200029</v>
+      </c>
+      <c r="B416" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C416" s="43">
+        <v>29</v>
+      </c>
+      <c r="D416" s="43">
+        <v>1</v>
+      </c>
+      <c r="E416" s="43" t="s">
+        <v>641</v>
+      </c>
+      <c r="F416" s="43"/>
+      <c r="G416" s="43"/>
+      <c r="H416" s="43"/>
+      <c r="I416" s="43" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="417" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A417" s="43">
+        <f t="shared" si="16"/>
+        <v>10200030</v>
+      </c>
+      <c r="B417" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C417" s="43">
+        <v>30</v>
+      </c>
+      <c r="D417" s="43">
+        <v>1</v>
+      </c>
+      <c r="E417" s="43" t="s">
+        <v>643</v>
+      </c>
+      <c r="F417" s="43"/>
+      <c r="G417" s="43"/>
+      <c r="H417" s="43"/>
+      <c r="I417" s="43" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="418" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A418" s="43">
+        <f t="shared" si="16"/>
+        <v>10200031</v>
+      </c>
+      <c r="B418" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C418" s="43">
+        <v>31</v>
+      </c>
+      <c r="D418" s="43">
+        <v>1</v>
+      </c>
+      <c r="E418" s="43" t="s">
+        <v>645</v>
+      </c>
+      <c r="F418" s="43"/>
+      <c r="G418" s="43"/>
+      <c r="H418" s="43"/>
+      <c r="I418" s="43" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="419" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A419" s="43">
+        <f t="shared" si="16"/>
+        <v>10200032</v>
+      </c>
+      <c r="B419" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C419" s="43">
+        <v>32</v>
+      </c>
+      <c r="D419" s="43">
+        <v>1</v>
+      </c>
+      <c r="E419" s="43" t="s">
+        <v>647</v>
+      </c>
+      <c r="F419" s="43"/>
+      <c r="G419" s="43"/>
+      <c r="H419" s="43"/>
+      <c r="I419" s="43" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="420" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A420" s="43">
+        <f t="shared" si="16"/>
+        <v>10200033</v>
+      </c>
+      <c r="B420" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C420" s="43">
+        <v>33</v>
+      </c>
+      <c r="D420" s="43">
+        <v>1</v>
+      </c>
+      <c r="E420" s="43" t="s">
+        <v>649</v>
+      </c>
+      <c r="F420" s="43"/>
+      <c r="G420" s="43"/>
+      <c r="H420" s="43"/>
+      <c r="I420" s="43" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="421" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A421" s="43">
+        <f t="shared" si="16"/>
+        <v>10200034</v>
+      </c>
+      <c r="B421" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C421" s="43">
+        <v>34</v>
+      </c>
+      <c r="D421" s="43">
         <v>2</v>
       </c>
-      <c r="E414" s="44" t="s">
-        <v>634</v>
-      </c>
-      <c r="F414" s="44"/>
-      <c r="G414" s="44"/>
-      <c r="H414" s="44"/>
-      <c r="I414" s="44" t="s">
+      <c r="E421" s="43" t="s">
+        <v>651</v>
+      </c>
+      <c r="F421" s="43"/>
+      <c r="G421" s="43"/>
+      <c r="H421" s="43"/>
+      <c r="I421" s="43" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="422" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A422" s="43">
+        <f t="shared" si="16"/>
+        <v>10200035</v>
+      </c>
+      <c r="B422" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C422" s="43">
+        <v>35</v>
+      </c>
+      <c r="D422" s="43">
+        <v>2</v>
+      </c>
+      <c r="E422" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="F422" s="43"/>
+      <c r="G422" s="43"/>
+      <c r="H422" s="43"/>
+      <c r="I422" s="43" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="423" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A423" s="43">
+        <f t="shared" si="16"/>
+        <v>10200036</v>
+      </c>
+      <c r="B423" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C423" s="43">
+        <v>36</v>
+      </c>
+      <c r="D423" s="43">
+        <v>2</v>
+      </c>
+      <c r="E423" s="43" t="s">
+        <v>653</v>
+      </c>
+      <c r="F423" s="43"/>
+      <c r="G423" s="43"/>
+      <c r="H423" s="43"/>
+      <c r="I423" s="43" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="424" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A424" s="43">
+        <f t="shared" si="16"/>
+        <v>10200037</v>
+      </c>
+      <c r="B424" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C424" s="43">
+        <v>37</v>
+      </c>
+      <c r="D424" s="43">
+        <v>2</v>
+      </c>
+      <c r="E424" s="43" t="s">
+        <v>654</v>
+      </c>
+      <c r="F424" s="43"/>
+      <c r="G424" s="43"/>
+      <c r="H424" s="43"/>
+      <c r="I424" s="43" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="425" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A425" s="43">
+        <f t="shared" si="16"/>
+        <v>10200038</v>
+      </c>
+      <c r="B425" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C425" s="43">
+        <v>38</v>
+      </c>
+      <c r="D425" s="43">
+        <v>2</v>
+      </c>
+      <c r="E425" s="43" t="s">
+        <v>655</v>
+      </c>
+      <c r="F425" s="43"/>
+      <c r="G425" s="43"/>
+      <c r="H425" s="43"/>
+      <c r="I425" s="43" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="415" s="1" customFormat="1" ht="16.5"/>
-    <row r="416" s="1" customFormat="1" ht="16.5"/>
-    <row r="417" s="1" customFormat="1" ht="16.5"/>
-    <row r="418" s="1" customFormat="1" ht="16.5"/>
-    <row r="419" s="1" customFormat="1" ht="16.5"/>
-    <row r="420" s="1" customFormat="1" ht="16.5"/>
-    <row r="421" s="1" customFormat="1" ht="16.5"/>
-    <row r="422" s="1" customFormat="1" ht="16.5"/>
+    <row r="426" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A426" s="43">
+        <f t="shared" si="16"/>
+        <v>10200039</v>
+      </c>
+      <c r="B426" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C426" s="43">
+        <v>39</v>
+      </c>
+      <c r="D426" s="43">
+        <v>2</v>
+      </c>
+      <c r="E426" s="43" t="s">
+        <v>656</v>
+      </c>
+      <c r="F426" s="43"/>
+      <c r="G426" s="43"/>
+      <c r="H426" s="43"/>
+      <c r="I426" s="43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="427" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A427" s="43">
+        <f t="shared" si="16"/>
+        <v>10200040</v>
+      </c>
+      <c r="B427" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C427" s="43">
+        <v>40</v>
+      </c>
+      <c r="D427" s="43">
+        <v>2</v>
+      </c>
+      <c r="E427" s="43" t="s">
+        <v>657</v>
+      </c>
+      <c r="F427" s="43"/>
+      <c r="G427" s="43"/>
+      <c r="H427" s="43"/>
+      <c r="I427" s="43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="428" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A428" s="43">
+        <f t="shared" si="16"/>
+        <v>10200041</v>
+      </c>
+      <c r="B428" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C428" s="43">
+        <v>41</v>
+      </c>
+      <c r="D428" s="43">
+        <v>1</v>
+      </c>
+      <c r="E428" s="43" t="s">
+        <v>658</v>
+      </c>
+      <c r="F428" s="43"/>
+      <c r="G428" s="43"/>
+      <c r="H428" s="43">
+        <v>5</v>
+      </c>
+      <c r="I428" s="43" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="429" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A429" s="43">
+        <f t="shared" si="16"/>
+        <v>10200042</v>
+      </c>
+      <c r="B429" s="43">
+        <v>102000</v>
+      </c>
+      <c r="C429" s="43">
+        <v>42</v>
+      </c>
+      <c r="D429" s="43">
+        <v>1</v>
+      </c>
+      <c r="E429" s="43" t="s">
+        <v>660</v>
+      </c>
+      <c r="F429" s="43"/>
+      <c r="G429" s="43"/>
+      <c r="H429" s="43">
+        <v>5</v>
+      </c>
+      <c r="I429" s="43" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="430" s="1" customFormat="1" ht="16.5"/>
+    <row r="431" s="1" customFormat="1" ht="16.5"/>
+    <row r="432" s="1" customFormat="1" ht="16.5"/>
+    <row r="433" s="1" customFormat="1" ht="16.5"/>
   </sheetData>
   <conditionalFormatting sqref="F2:H2">
     <cfRule type="expression" dxfId="0" priority="2">

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -13886,7 +13886,7 @@
         <v>22</v>
       </c>
       <c r="D409" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E409" s="43" t="s">
         <v>627</v>
@@ -13910,7 +13910,7 @@
         <v>23</v>
       </c>
       <c r="D410" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E410" s="43" t="s">
         <v>629</v>
@@ -13934,7 +13934,7 @@
         <v>24</v>
       </c>
       <c r="D411" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E411" s="43" t="s">
         <v>631</v>
@@ -13958,7 +13958,7 @@
         <v>25</v>
       </c>
       <c r="D412" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E412" s="43" t="s">
         <v>633</v>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="683">
   <si>
     <t>图标</t>
   </si>
@@ -2101,6 +2101,69 @@
   </si>
   <si>
     <t>哈迪斯百搭</t>
+  </si>
+  <si>
+    <t>emzz_icon_1.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_2.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_3.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_4.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_5.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_6.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_7.png</t>
+  </si>
+  <si>
+    <t>药水</t>
+  </si>
+  <si>
+    <t>emzz_icon_8.png</t>
+  </si>
+  <si>
+    <t>蜡烛</t>
+  </si>
+  <si>
+    <t>emzz_icon_9.png</t>
+  </si>
+  <si>
+    <t>戒指</t>
+  </si>
+  <si>
+    <t>emzz_icon_10.png</t>
+  </si>
+  <si>
+    <t>三叉戟</t>
+  </si>
+  <si>
+    <t>emzz_icon_11.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_12.png</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>emzz_icon_13.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_14.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_15.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_16.png</t>
   </si>
 </sst>
 </file>
@@ -2113,7 +2176,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2148,6 +2211,16 @@
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -2298,7 +2371,18 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2308,19 +2392,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2396,6 +2469,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2757,138 +2836,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3019,6 +3098,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -3345,7 +3436,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N433"/>
+  <dimension ref="A1:N445"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -8942,7 +9033,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
       <c r="H211" s="33"/>
-      <c r="I211" s="44" t="s">
+      <c r="I211" s="48" t="s">
         <v>300</v>
       </c>
     </row>
@@ -14382,10 +14473,390 @@
         <v>661</v>
       </c>
     </row>
-    <row r="430" s="1" customFormat="1" ht="16.5"/>
-    <row r="431" s="1" customFormat="1" ht="16.5"/>
-    <row r="432" s="1" customFormat="1" ht="16.5"/>
-    <row r="433" s="1" customFormat="1" ht="16.5"/>
+    <row r="430" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A430" s="44">
+        <f t="shared" ref="A430:A439" si="17">B430*100+C430</f>
+        <v>10380001</v>
+      </c>
+      <c r="B430" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C430" s="45">
+        <v>1</v>
+      </c>
+      <c r="D430" s="45">
+        <v>0</v>
+      </c>
+      <c r="E430" s="45" t="s">
+        <v>662</v>
+      </c>
+      <c r="F430" s="45"/>
+      <c r="G430" s="45"/>
+      <c r="H430" s="45"/>
+      <c r="I430" s="45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="431" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A431" s="44">
+        <f t="shared" si="17"/>
+        <v>10380002</v>
+      </c>
+      <c r="B431" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C431" s="45">
+        <v>2</v>
+      </c>
+      <c r="D431" s="45">
+        <v>0</v>
+      </c>
+      <c r="E431" s="45" t="s">
+        <v>663</v>
+      </c>
+      <c r="F431" s="45"/>
+      <c r="G431" s="45"/>
+      <c r="H431" s="45"/>
+      <c r="I431" s="45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="432" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A432" s="44">
+        <f t="shared" si="17"/>
+        <v>10380003</v>
+      </c>
+      <c r="B432" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C432" s="45">
+        <v>3</v>
+      </c>
+      <c r="D432" s="45">
+        <v>0</v>
+      </c>
+      <c r="E432" s="45" t="s">
+        <v>664</v>
+      </c>
+      <c r="F432" s="45"/>
+      <c r="G432" s="45"/>
+      <c r="H432" s="45"/>
+      <c r="I432" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="433" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A433" s="44">
+        <f t="shared" si="17"/>
+        <v>10380004</v>
+      </c>
+      <c r="B433" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C433" s="45">
+        <v>4</v>
+      </c>
+      <c r="D433" s="45">
+        <v>0</v>
+      </c>
+      <c r="E433" s="45" t="s">
+        <v>665</v>
+      </c>
+      <c r="F433" s="45"/>
+      <c r="G433" s="45"/>
+      <c r="H433" s="45"/>
+      <c r="I433" s="45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="434" ht="16.5" spans="1:9">
+      <c r="A434" s="44">
+        <f t="shared" si="17"/>
+        <v>10380005</v>
+      </c>
+      <c r="B434" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C434" s="45">
+        <v>5</v>
+      </c>
+      <c r="D434" s="45">
+        <v>0</v>
+      </c>
+      <c r="E434" s="45" t="s">
+        <v>666</v>
+      </c>
+      <c r="F434" s="46"/>
+      <c r="G434" s="46"/>
+      <c r="H434" s="46"/>
+      <c r="I434" s="45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="435" ht="16.5" spans="1:9">
+      <c r="A435" s="44">
+        <f t="shared" si="17"/>
+        <v>10380006</v>
+      </c>
+      <c r="B435" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C435" s="45">
+        <v>6</v>
+      </c>
+      <c r="D435" s="45">
+        <v>0</v>
+      </c>
+      <c r="E435" s="45" t="s">
+        <v>667</v>
+      </c>
+      <c r="F435" s="46"/>
+      <c r="G435" s="46"/>
+      <c r="H435" s="46"/>
+      <c r="I435" s="45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="436" ht="16.5" spans="1:9">
+      <c r="A436" s="44">
+        <f t="shared" si="17"/>
+        <v>10380007</v>
+      </c>
+      <c r="B436" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C436" s="45">
+        <v>7</v>
+      </c>
+      <c r="D436" s="45">
+        <v>0</v>
+      </c>
+      <c r="E436" s="45" t="s">
+        <v>668</v>
+      </c>
+      <c r="F436" s="46"/>
+      <c r="G436" s="46"/>
+      <c r="H436" s="46"/>
+      <c r="I436" s="45" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="437" ht="16.5" spans="1:9">
+      <c r="A437" s="44">
+        <f t="shared" si="17"/>
+        <v>10380008</v>
+      </c>
+      <c r="B437" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C437" s="45">
+        <v>8</v>
+      </c>
+      <c r="D437" s="45">
+        <v>0</v>
+      </c>
+      <c r="E437" s="45" t="s">
+        <v>670</v>
+      </c>
+      <c r="F437" s="46"/>
+      <c r="G437" s="46"/>
+      <c r="H437" s="46"/>
+      <c r="I437" s="45" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="438" ht="16.5" spans="1:9">
+      <c r="A438" s="44">
+        <f t="shared" si="17"/>
+        <v>10380009</v>
+      </c>
+      <c r="B438" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C438" s="45">
+        <v>9</v>
+      </c>
+      <c r="D438" s="45">
+        <v>0</v>
+      </c>
+      <c r="E438" s="45" t="s">
+        <v>672</v>
+      </c>
+      <c r="F438" s="46"/>
+      <c r="G438" s="46"/>
+      <c r="H438" s="46"/>
+      <c r="I438" s="45" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="439" ht="16.5" spans="1:9">
+      <c r="A439" s="44">
+        <f t="shared" si="17"/>
+        <v>10380010</v>
+      </c>
+      <c r="B439" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C439" s="45">
+        <v>10</v>
+      </c>
+      <c r="D439" s="45">
+        <v>0</v>
+      </c>
+      <c r="E439" s="45" t="s">
+        <v>674</v>
+      </c>
+      <c r="F439" s="46"/>
+      <c r="G439" s="46"/>
+      <c r="H439" s="46"/>
+      <c r="I439" s="45" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="440" ht="16.5" spans="1:9">
+      <c r="A440" s="44">
+        <f t="shared" ref="A440:A445" si="18">B440*100+C440</f>
+        <v>10380011</v>
+      </c>
+      <c r="B440" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C440" s="45">
+        <v>11</v>
+      </c>
+      <c r="D440" s="46">
+        <v>1</v>
+      </c>
+      <c r="E440" s="45" t="s">
+        <v>676</v>
+      </c>
+      <c r="F440" s="46"/>
+      <c r="G440" s="46"/>
+      <c r="H440" s="46"/>
+      <c r="I440" s="45" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="441" ht="16.5" spans="1:9">
+      <c r="A441" s="44">
+        <f t="shared" si="18"/>
+        <v>10380012</v>
+      </c>
+      <c r="B441" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C441" s="45">
+        <v>12</v>
+      </c>
+      <c r="D441" s="46">
+        <v>2</v>
+      </c>
+      <c r="E441" s="45" t="s">
+        <v>677</v>
+      </c>
+      <c r="F441" s="46"/>
+      <c r="G441" s="46"/>
+      <c r="H441" s="46"/>
+      <c r="I441" s="45" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="442" ht="17.25" spans="1:9">
+      <c r="A442" s="44">
+        <f t="shared" si="18"/>
+        <v>10380013</v>
+      </c>
+      <c r="B442" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C442" s="45">
+        <v>13</v>
+      </c>
+      <c r="D442" s="46">
+        <v>2</v>
+      </c>
+      <c r="E442" s="45" t="s">
+        <v>679</v>
+      </c>
+      <c r="F442" s="46"/>
+      <c r="G442" s="46"/>
+      <c r="H442" s="46"/>
+      <c r="I442" s="47" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="443" ht="16.5" spans="1:9">
+      <c r="A443" s="44">
+        <f t="shared" si="18"/>
+        <v>10380014</v>
+      </c>
+      <c r="B443" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C443" s="45">
+        <v>14</v>
+      </c>
+      <c r="D443" s="46">
+        <v>2</v>
+      </c>
+      <c r="E443" s="45" t="s">
+        <v>680</v>
+      </c>
+      <c r="F443" s="46"/>
+      <c r="G443" s="46"/>
+      <c r="H443" s="46"/>
+      <c r="I443" s="45" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="444" ht="16.5" spans="1:9">
+      <c r="A444" s="44">
+        <f t="shared" si="18"/>
+        <v>10380015</v>
+      </c>
+      <c r="B444" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C444" s="45">
+        <v>15</v>
+      </c>
+      <c r="D444" s="46">
+        <v>2</v>
+      </c>
+      <c r="E444" s="45" t="s">
+        <v>681</v>
+      </c>
+      <c r="F444" s="46"/>
+      <c r="G444" s="46"/>
+      <c r="H444" s="46"/>
+      <c r="I444" s="45" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="445" ht="16.5" spans="1:9">
+      <c r="A445" s="44">
+        <f t="shared" si="18"/>
+        <v>10380016</v>
+      </c>
+      <c r="B445" s="45">
+        <v>103800</v>
+      </c>
+      <c r="C445" s="45">
+        <v>16</v>
+      </c>
+      <c r="D445" s="46">
+        <v>2</v>
+      </c>
+      <c r="E445" s="45" t="s">
+        <v>682</v>
+      </c>
+      <c r="F445" s="46"/>
+      <c r="G445" s="46"/>
+      <c r="H445" s="46"/>
+      <c r="I445" s="45" t="s">
+        <v>438</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F2:H2">
     <cfRule type="expression" dxfId="0" priority="2">

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="676">
   <si>
     <t>图标</t>
   </si>
@@ -1875,214 +1875,181 @@
     <t>hhsc_icon_9.png</t>
   </si>
   <si>
-    <t>zsvshds_icon_1.png</t>
+    <t>hds_tb_101.png</t>
   </si>
   <si>
     <t>蓝10</t>
   </si>
   <si>
-    <t>zsvshds_icon_2.png</t>
+    <t>hds_tb_102.png</t>
   </si>
   <si>
     <t>红10</t>
   </si>
   <si>
-    <t>zsvshds_icon_3.png</t>
+    <t>hds_tb_103.png</t>
   </si>
   <si>
     <t>蓝J</t>
   </si>
   <si>
-    <t>zsvshds_icon_4.png</t>
+    <t>hds_tb_104.png</t>
   </si>
   <si>
     <t>红J</t>
   </si>
   <si>
-    <t>zsvshds_icon_5.png</t>
+    <t>hds_tb_105.png</t>
   </si>
   <si>
     <t>蓝Q</t>
   </si>
   <si>
-    <t>zsvshds_icon_6.png</t>
+    <t>hds_tb_106.png</t>
   </si>
   <si>
     <t>红Q</t>
   </si>
   <si>
-    <t>zsvshds_icon_7.png</t>
+    <t>hds_tb_107.png</t>
   </si>
   <si>
     <t>蓝K</t>
   </si>
   <si>
-    <t>zsvshds_icon_8.png</t>
+    <t>hds_tb_108.png</t>
   </si>
   <si>
     <t>红K</t>
   </si>
   <si>
-    <t>zsvshds_icon_9.png</t>
+    <t>hds_tb_109.png</t>
   </si>
   <si>
     <t>蓝A</t>
   </si>
   <si>
-    <t>zsvshds_icon_10.png</t>
+    <t>hds_tb_110.png</t>
   </si>
   <si>
     <t>红A</t>
   </si>
   <si>
-    <t>zsvshds_icon_11.png</t>
+    <t>hds_tb_111.png</t>
   </si>
   <si>
     <t>金杯</t>
   </si>
   <si>
-    <t>zsvshds_icon_12.png</t>
+    <t>hds_tb_112.png</t>
   </si>
   <si>
     <t>血杯</t>
   </si>
   <si>
-    <t>zsvshds_icon_13.png</t>
+    <t>hds_tb_113.png</t>
   </si>
   <si>
     <t>蓝戒指</t>
   </si>
   <si>
-    <t>zsvshds_icon_14.png</t>
+    <t>hds_tb_114.png</t>
   </si>
   <si>
     <t>红戒指</t>
   </si>
   <si>
-    <t>zsvshds_icon_15.png</t>
+    <t>hds_tb_115.png</t>
   </si>
   <si>
     <t>金甲</t>
   </si>
   <si>
-    <t>zsvshds_icon_16.png</t>
+    <t>hds_tb_116.png</t>
   </si>
   <si>
     <t>玄甲</t>
   </si>
   <si>
-    <t>zsvshds_icon_17.png</t>
+    <t>hds_tb_117.png</t>
   </si>
   <si>
     <t>天马</t>
   </si>
   <si>
-    <t>zsvshds_icon_18.png</t>
+    <t>hds_tb_118.png</t>
   </si>
   <si>
     <t>狼</t>
   </si>
   <si>
-    <t>zsvshds_icon_19.png</t>
+    <t>hds_tb_119.png</t>
   </si>
   <si>
     <t>宙斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_20.png</t>
+    <t>hds_tb_120.png</t>
   </si>
   <si>
     <t>哈迪斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_21.png</t>
-  </si>
-  <si>
-    <t>zsvshds_icon_22.png</t>
+    <t>hds_tb_201.png</t>
+  </si>
+  <si>
+    <t>hds_tb_202.png</t>
   </si>
   <si>
     <t>vs1-普通模式</t>
   </si>
   <si>
-    <t>zsvshds_icon_23.png</t>
-  </si>
-  <si>
     <t>vs2-普通模式</t>
   </si>
   <si>
-    <t>zsvshds_icon_24.png</t>
-  </si>
-  <si>
     <t>vs3-普通模式</t>
   </si>
   <si>
-    <t>zsvshds_icon_25.png</t>
-  </si>
-  <si>
     <t>vs4-普通模式</t>
   </si>
   <si>
-    <t>zsvshds_icon_26.png</t>
-  </si>
-  <si>
     <t>vs1-宙斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_27.png</t>
-  </si>
-  <si>
     <t>vs2-宙斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_28.png</t>
-  </si>
-  <si>
     <t>vs3-宙斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_29.png</t>
-  </si>
-  <si>
     <t>vs4-宙斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_30.png</t>
-  </si>
-  <si>
     <t>vs1-哈迪斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_31.png</t>
-  </si>
-  <si>
     <t>vs2-哈迪斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_32.png</t>
-  </si>
-  <si>
     <t>vs3-哈迪斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_33.png</t>
-  </si>
-  <si>
     <t>vs4-哈迪斯</t>
   </si>
   <si>
-    <t>zsvshds_icon_34.png</t>
-  </si>
-  <si>
-    <t>zsvshds_icon_35.png</t>
-  </si>
-  <si>
-    <t>zsvshds_icon_36.png</t>
-  </si>
-  <si>
-    <t>zsvshds_icon_37.png</t>
-  </si>
-  <si>
-    <t>zsvshds_icon_38.png</t>
+    <t>hds_tb_401.png</t>
+  </si>
+  <si>
+    <t>hds_tb_121.png</t>
+  </si>
+  <si>
+    <t>hds_tb_122.png</t>
+  </si>
+  <si>
+    <t>hds_tb_123.png</t>
+  </si>
+  <si>
+    <t>hds_tb_124.png</t>
   </si>
   <si>
     <t>zsvshds_icon_39.png</t>
@@ -2164,6 +2131,18 @@
   </si>
   <si>
     <t>emzz_icon_16.png</t>
+  </si>
+  <si>
+    <t>emzz_icon_17.png</t>
+  </si>
+  <si>
+    <t>用于触发免费游戏</t>
+  </si>
+  <si>
+    <t>emzz_icon_18.png</t>
+  </si>
+  <si>
+    <t>用于收集金币</t>
   </si>
 </sst>
 </file>
@@ -2369,8 +2348,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2382,18 +2361,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2469,12 +2448,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2842,7 +2815,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2866,16 +2839,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2884,90 +2857,90 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3103,13 +3076,7 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -3436,7 +3403,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N445"/>
+  <dimension ref="A1:N447"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -9033,7 +9000,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
       <c r="H211" s="33"/>
-      <c r="I211" s="48" t="s">
+      <c r="I211" s="46" t="s">
         <v>300</v>
       </c>
     </row>
@@ -14004,13 +13971,13 @@
         <v>1</v>
       </c>
       <c r="E410" s="43" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F410" s="43"/>
       <c r="G410" s="43"/>
       <c r="H410" s="43"/>
       <c r="I410" s="43" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="411" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14028,13 +13995,13 @@
         <v>1</v>
       </c>
       <c r="E411" s="43" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="F411" s="43"/>
       <c r="G411" s="43"/>
       <c r="H411" s="43"/>
       <c r="I411" s="43" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="412" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14052,13 +14019,13 @@
         <v>1</v>
       </c>
       <c r="E412" s="43" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="F412" s="43"/>
       <c r="G412" s="43"/>
       <c r="H412" s="43"/>
       <c r="I412" s="43" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="413" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14076,13 +14043,13 @@
         <v>1</v>
       </c>
       <c r="E413" s="43" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F413" s="43"/>
       <c r="G413" s="43"/>
       <c r="H413" s="43"/>
       <c r="I413" s="43" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="414" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14100,13 +14067,13 @@
         <v>1</v>
       </c>
       <c r="E414" s="43" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="F414" s="43"/>
       <c r="G414" s="43"/>
       <c r="H414" s="43"/>
       <c r="I414" s="43" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="415" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14124,13 +14091,13 @@
         <v>1</v>
       </c>
       <c r="E415" s="43" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="F415" s="43"/>
       <c r="G415" s="43"/>
       <c r="H415" s="43"/>
       <c r="I415" s="43" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
     </row>
     <row r="416" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14148,13 +14115,13 @@
         <v>1</v>
       </c>
       <c r="E416" s="43" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="F416" s="43"/>
       <c r="G416" s="43"/>
       <c r="H416" s="43"/>
       <c r="I416" s="43" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="417" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14172,13 +14139,13 @@
         <v>1</v>
       </c>
       <c r="E417" s="43" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="F417" s="43"/>
       <c r="G417" s="43"/>
       <c r="H417" s="43"/>
       <c r="I417" s="43" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
     </row>
     <row r="418" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14196,13 +14163,13 @@
         <v>1</v>
       </c>
       <c r="E418" s="43" t="s">
-        <v>645</v>
+        <v>627</v>
       </c>
       <c r="F418" s="43"/>
       <c r="G418" s="43"/>
       <c r="H418" s="43"/>
       <c r="I418" s="43" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
     </row>
     <row r="419" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14220,13 +14187,13 @@
         <v>1</v>
       </c>
       <c r="E419" s="43" t="s">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="F419" s="43"/>
       <c r="G419" s="43"/>
       <c r="H419" s="43"/>
       <c r="I419" s="43" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
     </row>
     <row r="420" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14244,13 +14211,13 @@
         <v>1</v>
       </c>
       <c r="E420" s="43" t="s">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="F420" s="43"/>
       <c r="G420" s="43"/>
       <c r="H420" s="43"/>
       <c r="I420" s="43" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
     </row>
     <row r="421" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14268,7 +14235,7 @@
         <v>2</v>
       </c>
       <c r="E421" s="43" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="F421" s="43"/>
       <c r="G421" s="43"/>
@@ -14292,7 +14259,7 @@
         <v>2</v>
       </c>
       <c r="E422" s="43" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="F422" s="43"/>
       <c r="G422" s="43"/>
@@ -14316,7 +14283,7 @@
         <v>2</v>
       </c>
       <c r="E423" s="43" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="F423" s="43"/>
       <c r="G423" s="43"/>
@@ -14340,7 +14307,7 @@
         <v>2</v>
       </c>
       <c r="E424" s="43" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="F424" s="43"/>
       <c r="G424" s="43"/>
@@ -14364,7 +14331,7 @@
         <v>2</v>
       </c>
       <c r="E425" s="43" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="F425" s="43"/>
       <c r="G425" s="43"/>
@@ -14388,7 +14355,7 @@
         <v>2</v>
       </c>
       <c r="E426" s="43" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="F426" s="43"/>
       <c r="G426" s="43"/>
@@ -14412,7 +14379,7 @@
         <v>2</v>
       </c>
       <c r="E427" s="43" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="F427" s="43"/>
       <c r="G427" s="43"/>
@@ -14436,7 +14403,7 @@
         <v>1</v>
       </c>
       <c r="E428" s="43" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="F428" s="43"/>
       <c r="G428" s="43"/>
@@ -14444,7 +14411,7 @@
         <v>5</v>
       </c>
       <c r="I428" s="43" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="429" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14462,7 +14429,7 @@
         <v>1</v>
       </c>
       <c r="E429" s="43" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="F429" s="43"/>
       <c r="G429" s="43"/>
@@ -14470,7 +14437,7 @@
         <v>5</v>
       </c>
       <c r="I429" s="43" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
     </row>
     <row r="430" s="1" customFormat="1" ht="16.5" spans="1:9">
@@ -14478,22 +14445,22 @@
         <f t="shared" ref="A430:A439" si="17">B430*100+C430</f>
         <v>10380001</v>
       </c>
-      <c r="B430" s="45">
+      <c r="B430" s="44">
         <v>103800</v>
       </c>
-      <c r="C430" s="45">
+      <c r="C430" s="44">
         <v>1</v>
       </c>
-      <c r="D430" s="45">
-        <v>0</v>
-      </c>
-      <c r="E430" s="45" t="s">
-        <v>662</v>
-      </c>
-      <c r="F430" s="45"/>
-      <c r="G430" s="45"/>
-      <c r="H430" s="45"/>
-      <c r="I430" s="45">
+      <c r="D430" s="44">
+        <v>0</v>
+      </c>
+      <c r="E430" s="44" t="s">
+        <v>651</v>
+      </c>
+      <c r="F430" s="44"/>
+      <c r="G430" s="44"/>
+      <c r="H430" s="44"/>
+      <c r="I430" s="44">
         <v>9</v>
       </c>
     </row>
@@ -14502,22 +14469,22 @@
         <f t="shared" si="17"/>
         <v>10380002</v>
       </c>
-      <c r="B431" s="45">
+      <c r="B431" s="44">
         <v>103800</v>
       </c>
-      <c r="C431" s="45">
+      <c r="C431" s="44">
         <v>2</v>
       </c>
-      <c r="D431" s="45">
-        <v>0</v>
-      </c>
-      <c r="E431" s="45" t="s">
-        <v>663</v>
-      </c>
-      <c r="F431" s="45"/>
-      <c r="G431" s="45"/>
-      <c r="H431" s="45"/>
-      <c r="I431" s="45">
+      <c r="D431" s="44">
+        <v>0</v>
+      </c>
+      <c r="E431" s="44" t="s">
+        <v>652</v>
+      </c>
+      <c r="F431" s="44"/>
+      <c r="G431" s="44"/>
+      <c r="H431" s="44"/>
+      <c r="I431" s="44">
         <v>10</v>
       </c>
     </row>
@@ -14526,22 +14493,22 @@
         <f t="shared" si="17"/>
         <v>10380003</v>
       </c>
-      <c r="B432" s="45">
+      <c r="B432" s="44">
         <v>103800</v>
       </c>
-      <c r="C432" s="45">
+      <c r="C432" s="44">
         <v>3</v>
       </c>
-      <c r="D432" s="45">
-        <v>0</v>
-      </c>
-      <c r="E432" s="45" t="s">
-        <v>664</v>
-      </c>
-      <c r="F432" s="45"/>
-      <c r="G432" s="45"/>
-      <c r="H432" s="45"/>
-      <c r="I432" s="45" t="s">
+      <c r="D432" s="44">
+        <v>0</v>
+      </c>
+      <c r="E432" s="44" t="s">
+        <v>653</v>
+      </c>
+      <c r="F432" s="44"/>
+      <c r="G432" s="44"/>
+      <c r="H432" s="44"/>
+      <c r="I432" s="44" t="s">
         <v>20</v>
       </c>
     </row>
@@ -14550,22 +14517,22 @@
         <f t="shared" si="17"/>
         <v>10380004</v>
       </c>
-      <c r="B433" s="45">
+      <c r="B433" s="44">
         <v>103800</v>
       </c>
-      <c r="C433" s="45">
+      <c r="C433" s="44">
         <v>4</v>
       </c>
-      <c r="D433" s="45">
-        <v>0</v>
-      </c>
-      <c r="E433" s="45" t="s">
-        <v>665</v>
-      </c>
-      <c r="F433" s="45"/>
-      <c r="G433" s="45"/>
-      <c r="H433" s="45"/>
-      <c r="I433" s="45" t="s">
+      <c r="D433" s="44">
+        <v>0</v>
+      </c>
+      <c r="E433" s="44" t="s">
+        <v>654</v>
+      </c>
+      <c r="F433" s="44"/>
+      <c r="G433" s="44"/>
+      <c r="H433" s="44"/>
+      <c r="I433" s="44" t="s">
         <v>22</v>
       </c>
     </row>
@@ -14574,22 +14541,22 @@
         <f t="shared" si="17"/>
         <v>10380005</v>
       </c>
-      <c r="B434" s="45">
+      <c r="B434" s="44">
         <v>103800</v>
       </c>
-      <c r="C434" s="45">
+      <c r="C434" s="44">
         <v>5</v>
       </c>
-      <c r="D434" s="45">
-        <v>0</v>
-      </c>
-      <c r="E434" s="45" t="s">
-        <v>666</v>
-      </c>
-      <c r="F434" s="46"/>
-      <c r="G434" s="46"/>
-      <c r="H434" s="46"/>
-      <c r="I434" s="45" t="s">
+      <c r="D434" s="44">
+        <v>0</v>
+      </c>
+      <c r="E434" s="44" t="s">
+        <v>655</v>
+      </c>
+      <c r="F434" s="44"/>
+      <c r="G434" s="44"/>
+      <c r="H434" s="44"/>
+      <c r="I434" s="44" t="s">
         <v>24</v>
       </c>
     </row>
@@ -14598,22 +14565,22 @@
         <f t="shared" si="17"/>
         <v>10380006</v>
       </c>
-      <c r="B435" s="45">
+      <c r="B435" s="44">
         <v>103800</v>
       </c>
-      <c r="C435" s="45">
+      <c r="C435" s="44">
         <v>6</v>
       </c>
-      <c r="D435" s="45">
-        <v>0</v>
-      </c>
-      <c r="E435" s="45" t="s">
-        <v>667</v>
-      </c>
-      <c r="F435" s="46"/>
-      <c r="G435" s="46"/>
-      <c r="H435" s="46"/>
-      <c r="I435" s="45" t="s">
+      <c r="D435" s="44">
+        <v>0</v>
+      </c>
+      <c r="E435" s="44" t="s">
+        <v>656</v>
+      </c>
+      <c r="F435" s="44"/>
+      <c r="G435" s="44"/>
+      <c r="H435" s="44"/>
+      <c r="I435" s="44" t="s">
         <v>26</v>
       </c>
     </row>
@@ -14622,23 +14589,23 @@
         <f t="shared" si="17"/>
         <v>10380007</v>
       </c>
-      <c r="B436" s="45">
+      <c r="B436" s="44">
         <v>103800</v>
       </c>
-      <c r="C436" s="45">
+      <c r="C436" s="44">
         <v>7</v>
       </c>
-      <c r="D436" s="45">
-        <v>0</v>
-      </c>
-      <c r="E436" s="45" t="s">
-        <v>668</v>
-      </c>
-      <c r="F436" s="46"/>
-      <c r="G436" s="46"/>
-      <c r="H436" s="46"/>
-      <c r="I436" s="45" t="s">
-        <v>669</v>
+      <c r="D436" s="44">
+        <v>0</v>
+      </c>
+      <c r="E436" s="44" t="s">
+        <v>657</v>
+      </c>
+      <c r="F436" s="44"/>
+      <c r="G436" s="44"/>
+      <c r="H436" s="44"/>
+      <c r="I436" s="44" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="437" ht="16.5" spans="1:9">
@@ -14646,23 +14613,23 @@
         <f t="shared" si="17"/>
         <v>10380008</v>
       </c>
-      <c r="B437" s="45">
+      <c r="B437" s="44">
         <v>103800</v>
       </c>
-      <c r="C437" s="45">
+      <c r="C437" s="44">
         <v>8</v>
       </c>
-      <c r="D437" s="45">
-        <v>0</v>
-      </c>
-      <c r="E437" s="45" t="s">
-        <v>670</v>
-      </c>
-      <c r="F437" s="46"/>
-      <c r="G437" s="46"/>
-      <c r="H437" s="46"/>
-      <c r="I437" s="45" t="s">
-        <v>671</v>
+      <c r="D437" s="44">
+        <v>0</v>
+      </c>
+      <c r="E437" s="44" t="s">
+        <v>659</v>
+      </c>
+      <c r="F437" s="44"/>
+      <c r="G437" s="44"/>
+      <c r="H437" s="44"/>
+      <c r="I437" s="44" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="438" ht="16.5" spans="1:9">
@@ -14670,23 +14637,23 @@
         <f t="shared" si="17"/>
         <v>10380009</v>
       </c>
-      <c r="B438" s="45">
+      <c r="B438" s="44">
         <v>103800</v>
       </c>
-      <c r="C438" s="45">
+      <c r="C438" s="44">
         <v>9</v>
       </c>
-      <c r="D438" s="45">
-        <v>0</v>
-      </c>
-      <c r="E438" s="45" t="s">
-        <v>672</v>
-      </c>
-      <c r="F438" s="46"/>
-      <c r="G438" s="46"/>
-      <c r="H438" s="46"/>
-      <c r="I438" s="45" t="s">
-        <v>673</v>
+      <c r="D438" s="44">
+        <v>0</v>
+      </c>
+      <c r="E438" s="44" t="s">
+        <v>661</v>
+      </c>
+      <c r="F438" s="44"/>
+      <c r="G438" s="44"/>
+      <c r="H438" s="44"/>
+      <c r="I438" s="44" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="439" ht="16.5" spans="1:9">
@@ -14694,46 +14661,46 @@
         <f t="shared" si="17"/>
         <v>10380010</v>
       </c>
-      <c r="B439" s="45">
+      <c r="B439" s="44">
         <v>103800</v>
       </c>
-      <c r="C439" s="45">
+      <c r="C439" s="44">
         <v>10</v>
       </c>
-      <c r="D439" s="45">
-        <v>0</v>
-      </c>
-      <c r="E439" s="45" t="s">
-        <v>674</v>
-      </c>
-      <c r="F439" s="46"/>
-      <c r="G439" s="46"/>
-      <c r="H439" s="46"/>
-      <c r="I439" s="45" t="s">
-        <v>675</v>
+      <c r="D439" s="44">
+        <v>0</v>
+      </c>
+      <c r="E439" s="44" t="s">
+        <v>663</v>
+      </c>
+      <c r="F439" s="44"/>
+      <c r="G439" s="44"/>
+      <c r="H439" s="44"/>
+      <c r="I439" s="44" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="440" ht="16.5" spans="1:9">
       <c r="A440" s="44">
-        <f t="shared" ref="A440:A445" si="18">B440*100+C440</f>
+        <f t="shared" ref="A440:A447" si="18">B440*100+C440</f>
         <v>10380011</v>
       </c>
-      <c r="B440" s="45">
+      <c r="B440" s="44">
         <v>103800</v>
       </c>
-      <c r="C440" s="45">
+      <c r="C440" s="44">
         <v>11</v>
       </c>
-      <c r="D440" s="46">
+      <c r="D440" s="44">
         <v>1</v>
       </c>
-      <c r="E440" s="45" t="s">
-        <v>676</v>
-      </c>
-      <c r="F440" s="46"/>
-      <c r="G440" s="46"/>
-      <c r="H440" s="46"/>
-      <c r="I440" s="45" t="s">
+      <c r="E440" s="44" t="s">
+        <v>665</v>
+      </c>
+      <c r="F440" s="44"/>
+      <c r="G440" s="44"/>
+      <c r="H440" s="44"/>
+      <c r="I440" s="44" t="s">
         <v>247</v>
       </c>
     </row>
@@ -14742,23 +14709,23 @@
         <f t="shared" si="18"/>
         <v>10380012</v>
       </c>
-      <c r="B441" s="45">
+      <c r="B441" s="44">
         <v>103800</v>
       </c>
-      <c r="C441" s="45">
+      <c r="C441" s="44">
         <v>12</v>
       </c>
-      <c r="D441" s="46">
+      <c r="D441" s="44">
         <v>2</v>
       </c>
-      <c r="E441" s="45" t="s">
-        <v>677</v>
-      </c>
-      <c r="F441" s="46"/>
-      <c r="G441" s="46"/>
-      <c r="H441" s="46"/>
-      <c r="I441" s="45" t="s">
-        <v>678</v>
+      <c r="E441" s="44" t="s">
+        <v>666</v>
+      </c>
+      <c r="F441" s="44"/>
+      <c r="G441" s="44"/>
+      <c r="H441" s="44"/>
+      <c r="I441" s="44" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="442" ht="17.25" spans="1:9">
@@ -14766,22 +14733,22 @@
         <f t="shared" si="18"/>
         <v>10380013</v>
       </c>
-      <c r="B442" s="45">
+      <c r="B442" s="44">
         <v>103800</v>
       </c>
-      <c r="C442" s="45">
+      <c r="C442" s="44">
         <v>13</v>
       </c>
-      <c r="D442" s="46">
+      <c r="D442" s="44">
         <v>2</v>
       </c>
-      <c r="E442" s="45" t="s">
-        <v>679</v>
-      </c>
-      <c r="F442" s="46"/>
-      <c r="G442" s="46"/>
-      <c r="H442" s="46"/>
-      <c r="I442" s="47" t="s">
+      <c r="E442" s="44" t="s">
+        <v>668</v>
+      </c>
+      <c r="F442" s="44"/>
+      <c r="G442" s="44"/>
+      <c r="H442" s="44"/>
+      <c r="I442" s="45" t="s">
         <v>432</v>
       </c>
     </row>
@@ -14790,22 +14757,22 @@
         <f t="shared" si="18"/>
         <v>10380014</v>
       </c>
-      <c r="B443" s="45">
+      <c r="B443" s="44">
         <v>103800</v>
       </c>
-      <c r="C443" s="45">
+      <c r="C443" s="44">
         <v>14</v>
       </c>
-      <c r="D443" s="46">
+      <c r="D443" s="44">
         <v>2</v>
       </c>
-      <c r="E443" s="45" t="s">
-        <v>680</v>
-      </c>
-      <c r="F443" s="46"/>
-      <c r="G443" s="46"/>
-      <c r="H443" s="46"/>
-      <c r="I443" s="45" t="s">
+      <c r="E443" s="44" t="s">
+        <v>669</v>
+      </c>
+      <c r="F443" s="44"/>
+      <c r="G443" s="44"/>
+      <c r="H443" s="44"/>
+      <c r="I443" s="44" t="s">
         <v>434</v>
       </c>
     </row>
@@ -14814,22 +14781,22 @@
         <f t="shared" si="18"/>
         <v>10380015</v>
       </c>
-      <c r="B444" s="45">
+      <c r="B444" s="44">
         <v>103800</v>
       </c>
-      <c r="C444" s="45">
+      <c r="C444" s="44">
         <v>15</v>
       </c>
-      <c r="D444" s="46">
+      <c r="D444" s="44">
         <v>2</v>
       </c>
-      <c r="E444" s="45" t="s">
-        <v>681</v>
-      </c>
-      <c r="F444" s="46"/>
-      <c r="G444" s="46"/>
-      <c r="H444" s="46"/>
-      <c r="I444" s="45" t="s">
+      <c r="E444" s="44" t="s">
+        <v>670</v>
+      </c>
+      <c r="F444" s="44"/>
+      <c r="G444" s="44"/>
+      <c r="H444" s="44"/>
+      <c r="I444" s="44" t="s">
         <v>436</v>
       </c>
     </row>
@@ -14838,23 +14805,71 @@
         <f t="shared" si="18"/>
         <v>10380016</v>
       </c>
-      <c r="B445" s="45">
+      <c r="B445" s="44">
         <v>103800</v>
       </c>
-      <c r="C445" s="45">
+      <c r="C445" s="44">
         <v>16</v>
       </c>
-      <c r="D445" s="46">
+      <c r="D445" s="44">
         <v>2</v>
       </c>
-      <c r="E445" s="45" t="s">
-        <v>682</v>
-      </c>
-      <c r="F445" s="46"/>
-      <c r="G445" s="46"/>
-      <c r="H445" s="46"/>
-      <c r="I445" s="45" t="s">
+      <c r="E445" s="44" t="s">
+        <v>671</v>
+      </c>
+      <c r="F445" s="44"/>
+      <c r="G445" s="44"/>
+      <c r="H445" s="44"/>
+      <c r="I445" s="44" t="s">
         <v>438</v>
+      </c>
+    </row>
+    <row r="446" ht="16.5" spans="1:9">
+      <c r="A446" s="44">
+        <f t="shared" si="18"/>
+        <v>10380017</v>
+      </c>
+      <c r="B446" s="44">
+        <v>103800</v>
+      </c>
+      <c r="C446" s="44">
+        <v>17</v>
+      </c>
+      <c r="D446" s="44">
+        <v>1</v>
+      </c>
+      <c r="E446" s="44" t="s">
+        <v>672</v>
+      </c>
+      <c r="F446" s="44"/>
+      <c r="G446" s="44"/>
+      <c r="H446" s="44"/>
+      <c r="I446" s="27" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="447" ht="16.5" spans="1:9">
+      <c r="A447" s="44">
+        <f t="shared" si="18"/>
+        <v>10380018</v>
+      </c>
+      <c r="B447" s="44">
+        <v>103800</v>
+      </c>
+      <c r="C447" s="44">
+        <v>18</v>
+      </c>
+      <c r="D447" s="44">
+        <v>1</v>
+      </c>
+      <c r="E447" s="44" t="s">
+        <v>674</v>
+      </c>
+      <c r="F447" s="44"/>
+      <c r="G447" s="44"/>
+      <c r="H447" s="44"/>
+      <c r="I447" s="27" t="s">
+        <v>675</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="702">
   <si>
     <t>图标</t>
   </si>
@@ -2143,6 +2143,84 @@
   </si>
   <si>
     <t>用于收集金币</t>
+  </si>
+  <si>
+    <t>xcs_icon_1.png</t>
+  </si>
+  <si>
+    <t>xcs_icon_2.png</t>
+  </si>
+  <si>
+    <t>xcs_icon_3.png</t>
+  </si>
+  <si>
+    <t>xcs_icon_4.png</t>
+  </si>
+  <si>
+    <t>xcs_icon_5.png</t>
+  </si>
+  <si>
+    <t>符号1</t>
+  </si>
+  <si>
+    <t>xcs_icon_6.png</t>
+  </si>
+  <si>
+    <t>符号2</t>
+  </si>
+  <si>
+    <t>xcs_icon_7.png</t>
+  </si>
+  <si>
+    <t>符号3</t>
+  </si>
+  <si>
+    <t>xcs_icon_8.png</t>
+  </si>
+  <si>
+    <t>符号4</t>
+  </si>
+  <si>
+    <t>xcs_icon_9.png</t>
+  </si>
+  <si>
+    <t>xcs_icon_10.png</t>
+  </si>
+  <si>
+    <t>xcs_icon_11.png</t>
+  </si>
+  <si>
+    <t>xcs_icon_12.png</t>
+  </si>
+  <si>
+    <t>xcs_icon_13.png</t>
+  </si>
+  <si>
+    <t>xcs_icon_14.png</t>
+  </si>
+  <si>
+    <t>sbjn_icon_1.png</t>
+  </si>
+  <si>
+    <t>sbjn_icon_2.png</t>
+  </si>
+  <si>
+    <t>sbjn_icon_3.png</t>
+  </si>
+  <si>
+    <t>sbjn_icon_4.png</t>
+  </si>
+  <si>
+    <t>sbjn_icon_5.png</t>
+  </si>
+  <si>
+    <t>宝箱</t>
+  </si>
+  <si>
+    <t>sbjn_icon_6.png</t>
+  </si>
+  <si>
+    <t>sbjn_icon_7.png</t>
   </si>
 </sst>
 </file>
@@ -2348,13 +2426,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -2453,6 +2531,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2514,12 +2598,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2815,7 +2893,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2839,16 +2917,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2857,28 +2935,28 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2940,7 +3018,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3077,6 +3155,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -3403,7 +3490,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N447"/>
+  <dimension ref="A1:N468"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -9000,7 +9087,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
       <c r="H211" s="33"/>
-      <c r="I211" s="46" t="s">
+      <c r="I211" s="49" t="s">
         <v>300</v>
       </c>
     </row>
@@ -14870,6 +14957,489 @@
       <c r="H447" s="44"/>
       <c r="I447" s="27" t="s">
         <v>675</v>
+      </c>
+    </row>
+    <row r="448" ht="16.5" spans="1:9">
+      <c r="A448" s="46">
+        <v>10270001</v>
+      </c>
+      <c r="B448" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C448" s="46">
+        <v>1</v>
+      </c>
+      <c r="D448" s="46">
+        <v>0</v>
+      </c>
+      <c r="E448" s="46" t="s">
+        <v>676</v>
+      </c>
+      <c r="F448" s="46"/>
+      <c r="G448" s="46"/>
+      <c r="H448" s="46"/>
+      <c r="I448" s="47" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="449" ht="16.5" spans="1:9">
+      <c r="A449" s="46">
+        <v>10270002</v>
+      </c>
+      <c r="B449" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C449" s="46">
+        <v>2</v>
+      </c>
+      <c r="D449" s="46">
+        <v>0</v>
+      </c>
+      <c r="E449" s="46" t="s">
+        <v>677</v>
+      </c>
+      <c r="F449" s="46"/>
+      <c r="G449" s="46"/>
+      <c r="H449" s="46"/>
+      <c r="I449" s="47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="450" ht="16.5" spans="1:9">
+      <c r="A450" s="46">
+        <v>10270003</v>
+      </c>
+      <c r="B450" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C450" s="46">
+        <v>3</v>
+      </c>
+      <c r="D450" s="46">
+        <v>0</v>
+      </c>
+      <c r="E450" s="46" t="s">
+        <v>678</v>
+      </c>
+      <c r="F450" s="46"/>
+      <c r="G450" s="46"/>
+      <c r="H450" s="46"/>
+      <c r="I450" s="47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="451" ht="16.5" spans="1:9">
+      <c r="A451" s="46">
+        <v>10270004</v>
+      </c>
+      <c r="B451" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C451" s="46">
+        <v>4</v>
+      </c>
+      <c r="D451" s="46">
+        <v>0</v>
+      </c>
+      <c r="E451" s="46" t="s">
+        <v>679</v>
+      </c>
+      <c r="F451" s="46"/>
+      <c r="G451" s="46"/>
+      <c r="H451" s="46"/>
+      <c r="I451" s="47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="452" ht="16.5" spans="1:9">
+      <c r="A452" s="46">
+        <v>10270005</v>
+      </c>
+      <c r="B452" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C452" s="46">
+        <v>5</v>
+      </c>
+      <c r="D452" s="46">
+        <v>0</v>
+      </c>
+      <c r="E452" s="46" t="s">
+        <v>680</v>
+      </c>
+      <c r="F452" s="46"/>
+      <c r="G452" s="46"/>
+      <c r="H452" s="46"/>
+      <c r="I452" s="47" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="453" ht="16.5" spans="1:9">
+      <c r="A453" s="46">
+        <v>10270006</v>
+      </c>
+      <c r="B453" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C453" s="46">
+        <v>6</v>
+      </c>
+      <c r="D453" s="46">
+        <v>0</v>
+      </c>
+      <c r="E453" s="46" t="s">
+        <v>682</v>
+      </c>
+      <c r="F453" s="46"/>
+      <c r="G453" s="46"/>
+      <c r="H453" s="46"/>
+      <c r="I453" s="47" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="454" ht="16.5" spans="1:9">
+      <c r="A454" s="46">
+        <v>10270007</v>
+      </c>
+      <c r="B454" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C454" s="46">
+        <v>7</v>
+      </c>
+      <c r="D454" s="46">
+        <v>0</v>
+      </c>
+      <c r="E454" s="46" t="s">
+        <v>684</v>
+      </c>
+      <c r="F454" s="46"/>
+      <c r="G454" s="46"/>
+      <c r="H454" s="46"/>
+      <c r="I454" s="47" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="455" ht="16.5" spans="1:9">
+      <c r="A455" s="46">
+        <v>10270008</v>
+      </c>
+      <c r="B455" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C455" s="46">
+        <v>8</v>
+      </c>
+      <c r="D455" s="46">
+        <v>0</v>
+      </c>
+      <c r="E455" s="46" t="s">
+        <v>686</v>
+      </c>
+      <c r="F455" s="46"/>
+      <c r="G455" s="46"/>
+      <c r="H455" s="46"/>
+      <c r="I455" s="47" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="456" ht="16.5" spans="1:9">
+      <c r="A456" s="46">
+        <v>10270009</v>
+      </c>
+      <c r="B456" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C456" s="46">
+        <v>9</v>
+      </c>
+      <c r="D456" s="46">
+        <v>1</v>
+      </c>
+      <c r="E456" s="46" t="s">
+        <v>688</v>
+      </c>
+      <c r="F456" s="46"/>
+      <c r="G456" s="46"/>
+      <c r="H456" s="46"/>
+      <c r="I456" s="47" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="457" ht="16.5" spans="1:9">
+      <c r="A457" s="46">
+        <v>10270010</v>
+      </c>
+      <c r="B457" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C457" s="46">
+        <v>10</v>
+      </c>
+      <c r="D457" s="46">
+        <v>2</v>
+      </c>
+      <c r="E457" s="46" t="s">
+        <v>689</v>
+      </c>
+      <c r="F457" s="46"/>
+      <c r="G457" s="46"/>
+      <c r="H457" s="46"/>
+      <c r="I457" s="47" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="458" ht="16.5" spans="1:9">
+      <c r="A458" s="46">
+        <v>10270011</v>
+      </c>
+      <c r="B458" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C458" s="46">
+        <v>11</v>
+      </c>
+      <c r="D458" s="46">
+        <v>2</v>
+      </c>
+      <c r="E458" s="46" t="s">
+        <v>690</v>
+      </c>
+      <c r="F458" s="46"/>
+      <c r="G458" s="46"/>
+      <c r="H458" s="46"/>
+      <c r="I458" s="47" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="459" ht="16.5" spans="1:9">
+      <c r="A459" s="46">
+        <v>10270012</v>
+      </c>
+      <c r="B459" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C459" s="46">
+        <v>12</v>
+      </c>
+      <c r="D459" s="46">
+        <v>2</v>
+      </c>
+      <c r="E459" s="46" t="s">
+        <v>691</v>
+      </c>
+      <c r="F459" s="46"/>
+      <c r="G459" s="46"/>
+      <c r="H459" s="46"/>
+      <c r="I459" s="47" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="460" ht="16.5" spans="1:9">
+      <c r="A460" s="46">
+        <v>10270013</v>
+      </c>
+      <c r="B460" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C460" s="46">
+        <v>13</v>
+      </c>
+      <c r="D460" s="46">
+        <v>2</v>
+      </c>
+      <c r="E460" s="46" t="s">
+        <v>692</v>
+      </c>
+      <c r="F460" s="46"/>
+      <c r="G460" s="46"/>
+      <c r="H460" s="46"/>
+      <c r="I460" s="47" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="461" ht="16.5" spans="1:9">
+      <c r="A461" s="46">
+        <v>10270014</v>
+      </c>
+      <c r="B461" s="46">
+        <v>102700</v>
+      </c>
+      <c r="C461" s="46">
+        <v>14</v>
+      </c>
+      <c r="D461" s="46">
+        <v>2</v>
+      </c>
+      <c r="E461" s="46" t="s">
+        <v>693</v>
+      </c>
+      <c r="F461" s="46"/>
+      <c r="G461" s="46"/>
+      <c r="H461" s="46"/>
+      <c r="I461" s="47" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="462" ht="16.5" spans="1:9">
+      <c r="A462" s="48">
+        <v>10370001</v>
+      </c>
+      <c r="B462" s="48">
+        <v>103700</v>
+      </c>
+      <c r="C462" s="48">
+        <v>1</v>
+      </c>
+      <c r="D462" s="48">
+        <v>0</v>
+      </c>
+      <c r="E462" s="48" t="s">
+        <v>694</v>
+      </c>
+      <c r="F462" s="48"/>
+      <c r="G462" s="48"/>
+      <c r="H462" s="48"/>
+      <c r="I462" s="43" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="463" ht="16.5" spans="1:9">
+      <c r="A463" s="48">
+        <v>10370002</v>
+      </c>
+      <c r="B463" s="48">
+        <v>103700</v>
+      </c>
+      <c r="C463" s="48">
+        <v>2</v>
+      </c>
+      <c r="D463" s="48">
+        <v>0</v>
+      </c>
+      <c r="E463" s="48" t="s">
+        <v>695</v>
+      </c>
+      <c r="F463" s="48"/>
+      <c r="G463" s="48"/>
+      <c r="H463" s="48"/>
+      <c r="I463" s="43" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="464" ht="16.5" spans="1:9">
+      <c r="A464" s="48">
+        <v>10370003</v>
+      </c>
+      <c r="B464" s="48">
+        <v>103700</v>
+      </c>
+      <c r="C464" s="48">
+        <v>3</v>
+      </c>
+      <c r="D464" s="48">
+        <v>0</v>
+      </c>
+      <c r="E464" s="48" t="s">
+        <v>696</v>
+      </c>
+      <c r="F464" s="48"/>
+      <c r="G464" s="48"/>
+      <c r="H464" s="48"/>
+      <c r="I464" s="43" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="465" ht="16.5" spans="1:9">
+      <c r="A465" s="48">
+        <v>10370004</v>
+      </c>
+      <c r="B465" s="48">
+        <v>103700</v>
+      </c>
+      <c r="C465" s="48">
+        <v>4</v>
+      </c>
+      <c r="D465" s="48">
+        <v>0</v>
+      </c>
+      <c r="E465" s="48" t="s">
+        <v>697</v>
+      </c>
+      <c r="F465" s="48"/>
+      <c r="G465" s="48"/>
+      <c r="H465" s="48"/>
+      <c r="I465" s="43" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="466" ht="16.5" spans="1:9">
+      <c r="A466" s="48">
+        <v>10370005</v>
+      </c>
+      <c r="B466" s="48">
+        <v>103700</v>
+      </c>
+      <c r="C466" s="48">
+        <v>5</v>
+      </c>
+      <c r="D466" s="48">
+        <v>0</v>
+      </c>
+      <c r="E466" s="48" t="s">
+        <v>698</v>
+      </c>
+      <c r="F466" s="48"/>
+      <c r="G466" s="48"/>
+      <c r="H466" s="48"/>
+      <c r="I466" s="43" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="467" ht="16.5" spans="1:9">
+      <c r="A467" s="48">
+        <v>10370006</v>
+      </c>
+      <c r="B467" s="48">
+        <v>103700</v>
+      </c>
+      <c r="C467" s="48">
+        <v>6</v>
+      </c>
+      <c r="D467" s="48">
+        <v>0</v>
+      </c>
+      <c r="E467" s="48" t="s">
+        <v>700</v>
+      </c>
+      <c r="F467" s="48"/>
+      <c r="G467" s="48"/>
+      <c r="H467" s="48"/>
+      <c r="I467" s="43" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="468" ht="16.5" spans="1:9">
+      <c r="A468" s="48">
+        <v>10370007</v>
+      </c>
+      <c r="B468" s="48">
+        <v>103700</v>
+      </c>
+      <c r="C468" s="48">
+        <v>7</v>
+      </c>
+      <c r="D468" s="48">
+        <v>1</v>
+      </c>
+      <c r="E468" s="48" t="s">
+        <v>701</v>
+      </c>
+      <c r="F468" s="48"/>
+      <c r="G468" s="48"/>
+      <c r="H468" s="48"/>
+      <c r="I468" s="43" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="729">
   <si>
     <t>图标</t>
   </si>
@@ -2221,6 +2221,87 @@
   </si>
   <si>
     <t>sbjn_icon_7.png</t>
+  </si>
+  <si>
+    <t>sbjn_icon_8.png</t>
+  </si>
+  <si>
+    <t>隐藏符号，用于触发福牛模式</t>
+  </si>
+  <si>
+    <t>ljr_icon_1.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_2.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_3.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_4.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_5.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_6.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_7.png</t>
+  </si>
+  <si>
+    <t>警车</t>
+  </si>
+  <si>
+    <t>ljr_icon_8.png</t>
+  </si>
+  <si>
+    <t>飞机</t>
+  </si>
+  <si>
+    <t>ljr_icon_9.png</t>
+  </si>
+  <si>
+    <t>毒气瓶</t>
+  </si>
+  <si>
+    <t>ljr_icon_10.png</t>
+  </si>
+  <si>
+    <t>墨镜</t>
+  </si>
+  <si>
+    <t>ljr_icon_11.png</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>ljr_icon_12.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_13.png</t>
+  </si>
+  <si>
+    <t>bonus</t>
+  </si>
+  <si>
+    <t>ljr_icon_14.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_15.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_16.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_17.png</t>
+  </si>
+  <si>
+    <t>ljr_icon_18.png</t>
+  </si>
+  <si>
+    <t>wild1，用于触发扩列，前端还是显示wild符号</t>
   </si>
 </sst>
 </file>
@@ -3490,7 +3571,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N468"/>
+  <dimension ref="A1:N487"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -15440,6 +15521,443 @@
       <c r="H468" s="48"/>
       <c r="I468" s="43" t="s">
         <v>247</v>
+      </c>
+    </row>
+    <row r="469" ht="16.5" spans="1:9">
+      <c r="A469" s="48">
+        <v>10370008</v>
+      </c>
+      <c r="B469" s="48">
+        <v>103700</v>
+      </c>
+      <c r="C469" s="48">
+        <v>8</v>
+      </c>
+      <c r="D469" s="48">
+        <v>2</v>
+      </c>
+      <c r="E469" s="48" t="s">
+        <v>702</v>
+      </c>
+      <c r="F469" s="48"/>
+      <c r="G469" s="48"/>
+      <c r="H469" s="48"/>
+      <c r="I469" s="43" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="470" ht="16.5" spans="1:9">
+      <c r="A470" s="34">
+        <v>10310001</v>
+      </c>
+      <c r="B470" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C470" s="34">
+        <v>1</v>
+      </c>
+      <c r="D470" s="34">
+        <v>0</v>
+      </c>
+      <c r="E470" s="34" t="s">
+        <v>704</v>
+      </c>
+      <c r="F470" s="34"/>
+      <c r="G470" s="34"/>
+      <c r="H470" s="34"/>
+      <c r="I470" s="34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="471" ht="16.5" spans="1:9">
+      <c r="A471" s="34">
+        <v>10310002</v>
+      </c>
+      <c r="B471" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C471" s="34">
+        <v>2</v>
+      </c>
+      <c r="D471" s="34">
+        <v>0</v>
+      </c>
+      <c r="E471" s="34" t="s">
+        <v>705</v>
+      </c>
+      <c r="F471" s="34"/>
+      <c r="G471" s="34"/>
+      <c r="H471" s="34"/>
+      <c r="I471" s="34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="472" ht="16.5" spans="1:9">
+      <c r="A472" s="34">
+        <v>10310003</v>
+      </c>
+      <c r="B472" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C472" s="34">
+        <v>3</v>
+      </c>
+      <c r="D472" s="34">
+        <v>0</v>
+      </c>
+      <c r="E472" s="34" t="s">
+        <v>706</v>
+      </c>
+      <c r="F472" s="34"/>
+      <c r="G472" s="34"/>
+      <c r="H472" s="34"/>
+      <c r="I472" s="34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="473" ht="16.5" spans="1:9">
+      <c r="A473" s="34">
+        <v>10310004</v>
+      </c>
+      <c r="B473" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C473" s="34">
+        <v>4</v>
+      </c>
+      <c r="D473" s="34">
+        <v>0</v>
+      </c>
+      <c r="E473" s="34" t="s">
+        <v>707</v>
+      </c>
+      <c r="F473" s="34"/>
+      <c r="G473" s="34"/>
+      <c r="H473" s="34"/>
+      <c r="I473" s="34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="474" ht="16.5" spans="1:9">
+      <c r="A474" s="34">
+        <v>10310005</v>
+      </c>
+      <c r="B474" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C474" s="34">
+        <v>5</v>
+      </c>
+      <c r="D474" s="34">
+        <v>0</v>
+      </c>
+      <c r="E474" s="34" t="s">
+        <v>708</v>
+      </c>
+      <c r="F474" s="34"/>
+      <c r="G474" s="34"/>
+      <c r="H474" s="34"/>
+      <c r="I474" s="34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="475" ht="16.5" spans="1:9">
+      <c r="A475" s="34">
+        <v>10310006</v>
+      </c>
+      <c r="B475" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C475" s="34">
+        <v>6</v>
+      </c>
+      <c r="D475" s="34">
+        <v>0</v>
+      </c>
+      <c r="E475" s="34" t="s">
+        <v>709</v>
+      </c>
+      <c r="F475" s="34"/>
+      <c r="G475" s="34"/>
+      <c r="H475" s="34"/>
+      <c r="I475" s="34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="476" ht="16.5" spans="1:9">
+      <c r="A476" s="34">
+        <v>10310007</v>
+      </c>
+      <c r="B476" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C476" s="34">
+        <v>7</v>
+      </c>
+      <c r="D476" s="34">
+        <v>0</v>
+      </c>
+      <c r="E476" s="34" t="s">
+        <v>710</v>
+      </c>
+      <c r="F476" s="34"/>
+      <c r="G476" s="34"/>
+      <c r="H476" s="34"/>
+      <c r="I476" s="34" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="477" ht="16.5" spans="1:9">
+      <c r="A477" s="34">
+        <v>10310008</v>
+      </c>
+      <c r="B477" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C477" s="34">
+        <v>8</v>
+      </c>
+      <c r="D477" s="34">
+        <v>0</v>
+      </c>
+      <c r="E477" s="34" t="s">
+        <v>712</v>
+      </c>
+      <c r="F477" s="34"/>
+      <c r="G477" s="34"/>
+      <c r="H477" s="34"/>
+      <c r="I477" s="34" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="478" ht="16.5" spans="1:9">
+      <c r="A478" s="34">
+        <v>10310009</v>
+      </c>
+      <c r="B478" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C478" s="34">
+        <v>9</v>
+      </c>
+      <c r="D478" s="34">
+        <v>0</v>
+      </c>
+      <c r="E478" s="34" t="s">
+        <v>714</v>
+      </c>
+      <c r="F478" s="34"/>
+      <c r="G478" s="34"/>
+      <c r="H478" s="34"/>
+      <c r="I478" s="34" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="479" ht="16.5" spans="1:9">
+      <c r="A479" s="34">
+        <v>10310010</v>
+      </c>
+      <c r="B479" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C479" s="34">
+        <v>10</v>
+      </c>
+      <c r="D479" s="34">
+        <v>0</v>
+      </c>
+      <c r="E479" s="34" t="s">
+        <v>716</v>
+      </c>
+      <c r="F479" s="34"/>
+      <c r="G479" s="34"/>
+      <c r="H479" s="34"/>
+      <c r="I479" s="34" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="480" ht="16.5" spans="1:9">
+      <c r="A480" s="34">
+        <v>10310011</v>
+      </c>
+      <c r="B480" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C480" s="34">
+        <v>11</v>
+      </c>
+      <c r="D480" s="34">
+        <v>1</v>
+      </c>
+      <c r="E480" s="34" t="s">
+        <v>718</v>
+      </c>
+      <c r="F480" s="34"/>
+      <c r="G480" s="34"/>
+      <c r="H480" s="34"/>
+      <c r="I480" s="34" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="481" ht="16.5" spans="1:9">
+      <c r="A481" s="34">
+        <v>10310012</v>
+      </c>
+      <c r="B481" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C481" s="34">
+        <v>12</v>
+      </c>
+      <c r="D481" s="34">
+        <v>2</v>
+      </c>
+      <c r="E481" s="34" t="s">
+        <v>720</v>
+      </c>
+      <c r="F481" s="34"/>
+      <c r="G481" s="34"/>
+      <c r="H481" s="34"/>
+      <c r="I481" s="34" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="482" ht="16.5" spans="1:9">
+      <c r="A482" s="34">
+        <v>10310013</v>
+      </c>
+      <c r="B482" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C482" s="34">
+        <v>13</v>
+      </c>
+      <c r="D482" s="34">
+        <v>2</v>
+      </c>
+      <c r="E482" s="34" t="s">
+        <v>721</v>
+      </c>
+      <c r="F482" s="34"/>
+      <c r="G482" s="34"/>
+      <c r="H482" s="34"/>
+      <c r="I482" s="34" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="483" ht="16.5" spans="1:9">
+      <c r="A483" s="34">
+        <v>10310014</v>
+      </c>
+      <c r="B483" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C483" s="34">
+        <v>14</v>
+      </c>
+      <c r="D483" s="34">
+        <v>2</v>
+      </c>
+      <c r="E483" s="34" t="s">
+        <v>723</v>
+      </c>
+      <c r="F483" s="34"/>
+      <c r="G483" s="34"/>
+      <c r="H483" s="34"/>
+      <c r="I483" s="34" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="484" ht="16.5" spans="1:9">
+      <c r="A484" s="34">
+        <v>10310015</v>
+      </c>
+      <c r="B484" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C484" s="34">
+        <v>15</v>
+      </c>
+      <c r="D484" s="34">
+        <v>2</v>
+      </c>
+      <c r="E484" s="34" t="s">
+        <v>724</v>
+      </c>
+      <c r="F484" s="34"/>
+      <c r="G484" s="34"/>
+      <c r="H484" s="34"/>
+      <c r="I484" s="34" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="485" ht="16.5" spans="1:9">
+      <c r="A485" s="34">
+        <v>10310016</v>
+      </c>
+      <c r="B485" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C485" s="34">
+        <v>16</v>
+      </c>
+      <c r="D485" s="34">
+        <v>2</v>
+      </c>
+      <c r="E485" s="34" t="s">
+        <v>725</v>
+      </c>
+      <c r="F485" s="34"/>
+      <c r="G485" s="34"/>
+      <c r="H485" s="34"/>
+      <c r="I485" s="34" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="486" ht="16.5" spans="1:9">
+      <c r="A486" s="34">
+        <v>10310017</v>
+      </c>
+      <c r="B486" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C486" s="34">
+        <v>17</v>
+      </c>
+      <c r="D486" s="34">
+        <v>2</v>
+      </c>
+      <c r="E486" s="34" t="s">
+        <v>726</v>
+      </c>
+      <c r="F486" s="34"/>
+      <c r="G486" s="34"/>
+      <c r="H486" s="34"/>
+      <c r="I486" s="34" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="487" ht="16.5" spans="1:9">
+      <c r="A487" s="34">
+        <v>10310018</v>
+      </c>
+      <c r="B487" s="34">
+        <v>103100</v>
+      </c>
+      <c r="C487" s="34">
+        <v>18</v>
+      </c>
+      <c r="D487" s="34">
+        <v>1</v>
+      </c>
+      <c r="E487" s="34" t="s">
+        <v>727</v>
+      </c>
+      <c r="F487" s="34"/>
+      <c r="G487" s="34"/>
+      <c r="H487" s="34"/>
+      <c r="I487" s="34" t="s">
+        <v>728</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="770">
   <si>
     <t>图标</t>
   </si>
@@ -2302,6 +2302,129 @@
   </si>
   <si>
     <t>wild1，用于触发扩列，前端还是显示wild符号</t>
+  </si>
+  <si>
+    <t>pjl_icon_1.png</t>
+  </si>
+  <si>
+    <t>pjl_icon_2.png</t>
+  </si>
+  <si>
+    <t>pjl_icon_3.png</t>
+  </si>
+  <si>
+    <t>pjl_icon_4.png</t>
+  </si>
+  <si>
+    <t>pjl_icon_5.png</t>
+  </si>
+  <si>
+    <t>烧饼摊</t>
+  </si>
+  <si>
+    <t>pjl_icon_6.png</t>
+  </si>
+  <si>
+    <t>酒罐</t>
+  </si>
+  <si>
+    <t>pjl_icon_7.png</t>
+  </si>
+  <si>
+    <t>王婆</t>
+  </si>
+  <si>
+    <t>pjl_icon_8.png</t>
+  </si>
+  <si>
+    <t>武大郎</t>
+  </si>
+  <si>
+    <t>pjl_icon_9.png</t>
+  </si>
+  <si>
+    <t>西门庆</t>
+  </si>
+  <si>
+    <t>pjl_icon_10.png</t>
+  </si>
+  <si>
+    <t>武松</t>
+  </si>
+  <si>
+    <t>pjl_icon_11.png</t>
+  </si>
+  <si>
+    <t>wild潘金莲</t>
+  </si>
+  <si>
+    <t>pjl_icon_12.png</t>
+  </si>
+  <si>
+    <t>pjl_icon_13.png</t>
+  </si>
+  <si>
+    <t>pjl_icon_14.png</t>
+  </si>
+  <si>
+    <t>pjl_icon_15.png</t>
+  </si>
+  <si>
+    <t>pjl_icon_16.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_1.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_2.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_3.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_4.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_5.png</t>
+  </si>
+  <si>
+    <t>黄鸟</t>
+  </si>
+  <si>
+    <t>fndxn_icon_6.png</t>
+  </si>
+  <si>
+    <t>黑鸟</t>
+  </si>
+  <si>
+    <t>fndxn_icon_7.png</t>
+  </si>
+  <si>
+    <t>蓝鸟</t>
+  </si>
+  <si>
+    <t>fndxn_icon_8.png</t>
+  </si>
+  <si>
+    <t>绿猪</t>
+  </si>
+  <si>
+    <t>fndxn_icon_9.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_10.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_11.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_12.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_13.png</t>
+  </si>
+  <si>
+    <t>fndxn_icon_14.png</t>
   </si>
 </sst>
 </file>
@@ -2515,6 +2638,11 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2525,13 +2653,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2613,6 +2736,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2974,7 +3103,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2998,16 +3127,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3016,90 +3145,90 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3245,6 +3374,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -3571,7 +3703,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N487"/>
+  <dimension ref="A1:N517"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -9168,7 +9300,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
       <c r="H211" s="33"/>
-      <c r="I211" s="49" t="s">
+      <c r="I211" s="50" t="s">
         <v>300</v>
       </c>
     </row>
@@ -15958,6 +16090,696 @@
       <c r="H487" s="34"/>
       <c r="I487" s="34" t="s">
         <v>728</v>
+      </c>
+    </row>
+    <row r="488" ht="16.5" spans="1:9">
+      <c r="A488" s="49">
+        <v>10400001</v>
+      </c>
+      <c r="B488" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C488" s="49">
+        <v>1</v>
+      </c>
+      <c r="D488" s="49">
+        <v>0</v>
+      </c>
+      <c r="E488" s="49" t="s">
+        <v>729</v>
+      </c>
+      <c r="F488" s="49"/>
+      <c r="G488" s="49"/>
+      <c r="H488" s="49"/>
+      <c r="I488" s="49" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="489" ht="16.5" spans="1:9">
+      <c r="A489" s="49">
+        <v>10400002</v>
+      </c>
+      <c r="B489" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C489" s="49">
+        <v>2</v>
+      </c>
+      <c r="D489" s="49">
+        <v>0</v>
+      </c>
+      <c r="E489" s="49" t="s">
+        <v>730</v>
+      </c>
+      <c r="F489" s="49"/>
+      <c r="G489" s="49"/>
+      <c r="H489" s="49"/>
+      <c r="I489" s="49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="490" ht="16.5" spans="1:9">
+      <c r="A490" s="49">
+        <v>10400003</v>
+      </c>
+      <c r="B490" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C490" s="49">
+        <v>3</v>
+      </c>
+      <c r="D490" s="49">
+        <v>0</v>
+      </c>
+      <c r="E490" s="49" t="s">
+        <v>731</v>
+      </c>
+      <c r="F490" s="49"/>
+      <c r="G490" s="49"/>
+      <c r="H490" s="49"/>
+      <c r="I490" s="49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="491" ht="16.5" spans="1:9">
+      <c r="A491" s="49">
+        <v>10400004</v>
+      </c>
+      <c r="B491" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C491" s="49">
+        <v>4</v>
+      </c>
+      <c r="D491" s="49">
+        <v>0</v>
+      </c>
+      <c r="E491" s="49" t="s">
+        <v>732</v>
+      </c>
+      <c r="F491" s="49"/>
+      <c r="G491" s="49"/>
+      <c r="H491" s="49"/>
+      <c r="I491" s="49" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="492" ht="16.5" spans="1:9">
+      <c r="A492" s="49">
+        <v>10400005</v>
+      </c>
+      <c r="B492" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C492" s="49">
+        <v>5</v>
+      </c>
+      <c r="D492" s="49">
+        <v>0</v>
+      </c>
+      <c r="E492" s="49" t="s">
+        <v>733</v>
+      </c>
+      <c r="F492" s="49"/>
+      <c r="G492" s="49"/>
+      <c r="H492" s="49"/>
+      <c r="I492" s="49" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="493" ht="16.5" spans="1:9">
+      <c r="A493" s="49">
+        <v>10400006</v>
+      </c>
+      <c r="B493" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C493" s="49">
+        <v>6</v>
+      </c>
+      <c r="D493" s="49">
+        <v>0</v>
+      </c>
+      <c r="E493" s="49" t="s">
+        <v>735</v>
+      </c>
+      <c r="F493" s="49"/>
+      <c r="G493" s="49"/>
+      <c r="H493" s="49"/>
+      <c r="I493" s="49" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="494" ht="16.5" spans="1:9">
+      <c r="A494" s="49">
+        <v>10400007</v>
+      </c>
+      <c r="B494" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C494" s="49">
+        <v>7</v>
+      </c>
+      <c r="D494" s="49">
+        <v>0</v>
+      </c>
+      <c r="E494" s="49" t="s">
+        <v>737</v>
+      </c>
+      <c r="F494" s="49"/>
+      <c r="G494" s="49"/>
+      <c r="H494" s="49"/>
+      <c r="I494" s="49" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="495" ht="16.5" spans="1:9">
+      <c r="A495" s="49">
+        <v>10400008</v>
+      </c>
+      <c r="B495" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C495" s="49">
+        <v>8</v>
+      </c>
+      <c r="D495" s="49">
+        <v>0</v>
+      </c>
+      <c r="E495" s="49" t="s">
+        <v>739</v>
+      </c>
+      <c r="F495" s="49"/>
+      <c r="G495" s="49"/>
+      <c r="H495" s="49"/>
+      <c r="I495" s="49" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="496" ht="16.5" spans="1:9">
+      <c r="A496" s="49">
+        <v>10400009</v>
+      </c>
+      <c r="B496" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C496" s="49">
+        <v>9</v>
+      </c>
+      <c r="D496" s="49">
+        <v>0</v>
+      </c>
+      <c r="E496" s="49" t="s">
+        <v>741</v>
+      </c>
+      <c r="F496" s="49"/>
+      <c r="G496" s="49"/>
+      <c r="H496" s="49"/>
+      <c r="I496" s="49" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="497" ht="16.5" spans="1:9">
+      <c r="A497" s="49">
+        <v>10400010</v>
+      </c>
+      <c r="B497" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C497" s="49">
+        <v>10</v>
+      </c>
+      <c r="D497" s="49">
+        <v>0</v>
+      </c>
+      <c r="E497" s="49" t="s">
+        <v>743</v>
+      </c>
+      <c r="F497" s="49"/>
+      <c r="G497" s="49"/>
+      <c r="H497" s="49"/>
+      <c r="I497" s="49" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="498" ht="16.5" spans="1:9">
+      <c r="A498" s="49">
+        <v>10400011</v>
+      </c>
+      <c r="B498" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C498" s="49">
+        <v>11</v>
+      </c>
+      <c r="D498" s="49">
+        <v>1</v>
+      </c>
+      <c r="E498" s="49" t="s">
+        <v>745</v>
+      </c>
+      <c r="F498" s="49"/>
+      <c r="G498" s="49"/>
+      <c r="H498" s="49"/>
+      <c r="I498" s="49" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="499" ht="16.5" spans="1:9">
+      <c r="A499" s="49">
+        <v>10400012</v>
+      </c>
+      <c r="B499" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C499" s="49">
+        <v>12</v>
+      </c>
+      <c r="D499" s="49">
+        <v>2</v>
+      </c>
+      <c r="E499" s="49" t="s">
+        <v>747</v>
+      </c>
+      <c r="F499" s="49"/>
+      <c r="G499" s="49"/>
+      <c r="H499" s="49"/>
+      <c r="I499" s="49" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="500" ht="16.5" spans="1:9">
+      <c r="A500" s="49">
+        <v>10400013</v>
+      </c>
+      <c r="B500" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C500" s="49">
+        <v>13</v>
+      </c>
+      <c r="D500" s="49">
+        <v>2</v>
+      </c>
+      <c r="E500" s="49" t="s">
+        <v>748</v>
+      </c>
+      <c r="F500" s="49"/>
+      <c r="G500" s="49"/>
+      <c r="H500" s="49"/>
+      <c r="I500" s="49" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="501" ht="16.5" spans="1:9">
+      <c r="A501" s="49">
+        <v>10400014</v>
+      </c>
+      <c r="B501" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C501" s="49">
+        <v>14</v>
+      </c>
+      <c r="D501" s="49">
+        <v>2</v>
+      </c>
+      <c r="E501" s="49" t="s">
+        <v>749</v>
+      </c>
+      <c r="F501" s="49"/>
+      <c r="G501" s="49"/>
+      <c r="H501" s="49"/>
+      <c r="I501" s="49" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="502" ht="16.5" spans="1:9">
+      <c r="A502" s="49">
+        <v>10400015</v>
+      </c>
+      <c r="B502" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C502" s="49">
+        <v>15</v>
+      </c>
+      <c r="D502" s="49">
+        <v>2</v>
+      </c>
+      <c r="E502" s="49" t="s">
+        <v>750</v>
+      </c>
+      <c r="F502" s="49"/>
+      <c r="G502" s="49"/>
+      <c r="H502" s="49"/>
+      <c r="I502" s="49" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="503" ht="16.5" spans="1:9">
+      <c r="A503" s="49">
+        <v>10400016</v>
+      </c>
+      <c r="B503" s="49">
+        <v>104000</v>
+      </c>
+      <c r="C503" s="49">
+        <v>16</v>
+      </c>
+      <c r="D503" s="49">
+        <v>2</v>
+      </c>
+      <c r="E503" s="49" t="s">
+        <v>751</v>
+      </c>
+      <c r="F503" s="49"/>
+      <c r="G503" s="49"/>
+      <c r="H503" s="49"/>
+      <c r="I503" s="49" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="504" ht="16.5" spans="1:9">
+      <c r="A504" s="25">
+        <v>10390001</v>
+      </c>
+      <c r="B504" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C504" s="25">
+        <v>1</v>
+      </c>
+      <c r="D504" s="25">
+        <v>0</v>
+      </c>
+      <c r="E504" s="25" t="s">
+        <v>752</v>
+      </c>
+      <c r="F504" s="25"/>
+      <c r="G504" s="25"/>
+      <c r="H504" s="25"/>
+      <c r="I504" s="25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="505" ht="16.5" spans="1:9">
+      <c r="A505" s="25">
+        <v>10390002</v>
+      </c>
+      <c r="B505" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C505" s="25">
+        <v>2</v>
+      </c>
+      <c r="D505" s="25">
+        <v>0</v>
+      </c>
+      <c r="E505" s="25" t="s">
+        <v>753</v>
+      </c>
+      <c r="F505" s="25"/>
+      <c r="G505" s="25"/>
+      <c r="H505" s="25"/>
+      <c r="I505" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="506" ht="16.5" spans="1:9">
+      <c r="A506" s="25">
+        <v>10390003</v>
+      </c>
+      <c r="B506" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C506" s="25">
+        <v>3</v>
+      </c>
+      <c r="D506" s="25">
+        <v>0</v>
+      </c>
+      <c r="E506" s="25" t="s">
+        <v>754</v>
+      </c>
+      <c r="F506" s="25"/>
+      <c r="G506" s="25"/>
+      <c r="H506" s="25"/>
+      <c r="I506" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="507" ht="16.5" spans="1:9">
+      <c r="A507" s="25">
+        <v>10390004</v>
+      </c>
+      <c r="B507" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C507" s="25">
+        <v>4</v>
+      </c>
+      <c r="D507" s="25">
+        <v>0</v>
+      </c>
+      <c r="E507" s="25" t="s">
+        <v>755</v>
+      </c>
+      <c r="F507" s="25"/>
+      <c r="G507" s="25"/>
+      <c r="H507" s="25"/>
+      <c r="I507" s="25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="508" ht="16.5" spans="1:9">
+      <c r="A508" s="25">
+        <v>10390005</v>
+      </c>
+      <c r="B508" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C508" s="25">
+        <v>5</v>
+      </c>
+      <c r="D508" s="25">
+        <v>0</v>
+      </c>
+      <c r="E508" s="25" t="s">
+        <v>756</v>
+      </c>
+      <c r="F508" s="25"/>
+      <c r="G508" s="25"/>
+      <c r="H508" s="25"/>
+      <c r="I508" s="25" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="509" ht="16.5" spans="1:9">
+      <c r="A509" s="25">
+        <v>10390006</v>
+      </c>
+      <c r="B509" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C509" s="25">
+        <v>6</v>
+      </c>
+      <c r="D509" s="25">
+        <v>0</v>
+      </c>
+      <c r="E509" s="25" t="s">
+        <v>758</v>
+      </c>
+      <c r="F509" s="25"/>
+      <c r="G509" s="25"/>
+      <c r="H509" s="25"/>
+      <c r="I509" s="25" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="510" ht="16.5" spans="1:9">
+      <c r="A510" s="25">
+        <v>10390007</v>
+      </c>
+      <c r="B510" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C510" s="25">
+        <v>7</v>
+      </c>
+      <c r="D510" s="25">
+        <v>0</v>
+      </c>
+      <c r="E510" s="25" t="s">
+        <v>760</v>
+      </c>
+      <c r="F510" s="25"/>
+      <c r="G510" s="25"/>
+      <c r="H510" s="25"/>
+      <c r="I510" s="25" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="511" ht="16.5" spans="1:9">
+      <c r="A511" s="25">
+        <v>10390008</v>
+      </c>
+      <c r="B511" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C511" s="25">
+        <v>8</v>
+      </c>
+      <c r="D511" s="25">
+        <v>0</v>
+      </c>
+      <c r="E511" s="25" t="s">
+        <v>762</v>
+      </c>
+      <c r="F511" s="25"/>
+      <c r="G511" s="25"/>
+      <c r="H511" s="25"/>
+      <c r="I511" s="25" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="512" ht="16.5" spans="1:9">
+      <c r="A512" s="25">
+        <v>10390009</v>
+      </c>
+      <c r="B512" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C512" s="25">
+        <v>9</v>
+      </c>
+      <c r="D512" s="25">
+        <v>1</v>
+      </c>
+      <c r="E512" s="25" t="s">
+        <v>764</v>
+      </c>
+      <c r="F512" s="25"/>
+      <c r="G512" s="25"/>
+      <c r="H512" s="25"/>
+      <c r="I512" s="25" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="513" ht="16.5" spans="1:9">
+      <c r="A513" s="25">
+        <v>10390010</v>
+      </c>
+      <c r="B513" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C513" s="25">
+        <v>10</v>
+      </c>
+      <c r="D513" s="25">
+        <v>2</v>
+      </c>
+      <c r="E513" s="25" t="s">
+        <v>765</v>
+      </c>
+      <c r="F513" s="25"/>
+      <c r="G513" s="25"/>
+      <c r="H513" s="25"/>
+      <c r="I513" s="25" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="514" ht="16.5" spans="1:9">
+      <c r="A514" s="25">
+        <v>10390011</v>
+      </c>
+      <c r="B514" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C514" s="25">
+        <v>11</v>
+      </c>
+      <c r="D514" s="25">
+        <v>2</v>
+      </c>
+      <c r="E514" s="25" t="s">
+        <v>766</v>
+      </c>
+      <c r="F514" s="25"/>
+      <c r="G514" s="25"/>
+      <c r="H514" s="25"/>
+      <c r="I514" s="25" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="515" ht="16.5" spans="1:9">
+      <c r="A515" s="25">
+        <v>10390012</v>
+      </c>
+      <c r="B515" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C515" s="25">
+        <v>12</v>
+      </c>
+      <c r="D515" s="25">
+        <v>2</v>
+      </c>
+      <c r="E515" s="25" t="s">
+        <v>767</v>
+      </c>
+      <c r="F515" s="25"/>
+      <c r="G515" s="25"/>
+      <c r="H515" s="25"/>
+      <c r="I515" s="25" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="516" ht="16.5" spans="1:9">
+      <c r="A516" s="25">
+        <v>10390013</v>
+      </c>
+      <c r="B516" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C516" s="25">
+        <v>13</v>
+      </c>
+      <c r="D516" s="25">
+        <v>2</v>
+      </c>
+      <c r="E516" s="25" t="s">
+        <v>768</v>
+      </c>
+      <c r="F516" s="25"/>
+      <c r="G516" s="25"/>
+      <c r="H516" s="25"/>
+      <c r="I516" s="25" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="517" ht="16.5" spans="1:9">
+      <c r="A517" s="25">
+        <v>10390014</v>
+      </c>
+      <c r="B517" s="25">
+        <v>103900</v>
+      </c>
+      <c r="C517" s="25">
+        <v>14</v>
+      </c>
+      <c r="D517" s="25">
+        <v>2</v>
+      </c>
+      <c r="E517" s="25" t="s">
+        <v>769</v>
+      </c>
+      <c r="F517" s="25"/>
+      <c r="G517" s="25"/>
+      <c r="H517" s="25"/>
+      <c r="I517" s="25" t="s">
+        <v>438</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1075">
   <si>
     <t>图标</t>
   </si>
@@ -3259,6 +3259,87 @@
   </si>
   <si>
     <t>黄金梅西消除后变成wild</t>
+  </si>
+  <si>
+    <t>ly__icon_1.png</t>
+  </si>
+  <si>
+    <t>ly__icon_2.png</t>
+  </si>
+  <si>
+    <t>ly__icon_3.png</t>
+  </si>
+  <si>
+    <t>ly__icon_4.png</t>
+  </si>
+  <si>
+    <t>ly__icon_5.png</t>
+  </si>
+  <si>
+    <t>ly__icon_6.png</t>
+  </si>
+  <si>
+    <t>ly__icon_7.png</t>
+  </si>
+  <si>
+    <t>匕首</t>
+  </si>
+  <si>
+    <t>ly__icon_8.png</t>
+  </si>
+  <si>
+    <t>ly__icon_9.png</t>
+  </si>
+  <si>
+    <t>狼爪</t>
+  </si>
+  <si>
+    <t>ly__icon_10.png</t>
+  </si>
+  <si>
+    <t>ly__icon_11.png</t>
+  </si>
+  <si>
+    <t>十字架</t>
+  </si>
+  <si>
+    <t>ly__icon_12.png</t>
+  </si>
+  <si>
+    <t>手枪</t>
+  </si>
+  <si>
+    <t>ly__icon_13.png</t>
+  </si>
+  <si>
+    <t>ly__icon_14.png</t>
+  </si>
+  <si>
+    <t>ly__icon_15.png</t>
+  </si>
+  <si>
+    <t>ly__icon_16.png</t>
+  </si>
+  <si>
+    <t>ly__icon_17.png</t>
+  </si>
+  <si>
+    <t>ly__icon_18.png</t>
+  </si>
+  <si>
+    <t>ly__icon_19.png</t>
+  </si>
+  <si>
+    <t>ly__icon_20.png</t>
+  </si>
+  <si>
+    <t>隐藏符号，用于触发免费游戏</t>
+  </si>
+  <si>
+    <t>ly__icon_21.png</t>
+  </si>
+  <si>
+    <t>ly__icon_22.png</t>
   </si>
 </sst>
 </file>
@@ -3471,18 +3552,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4068,7 +4149,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4220,6 +4301,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -10143,7 +10227,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
       <c r="H211" s="33"/>
-      <c r="I211" s="51" t="s">
+      <c r="I211" s="52" t="s">
         <v>302</v>
       </c>
     </row>
@@ -20996,28 +21080,512 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="649" s="1" customFormat="1" ht="16.5"/>
-    <row r="650" s="1" customFormat="1" ht="16.5"/>
-    <row r="651" s="1" customFormat="1" ht="16.5"/>
-    <row r="652" s="1" customFormat="1" ht="16.5"/>
-    <row r="653" s="1" customFormat="1" ht="16.5"/>
-    <row r="654" s="1" customFormat="1" ht="16.5"/>
-    <row r="655" s="1" customFormat="1" ht="16.5"/>
-    <row r="656" s="1" customFormat="1" ht="16.5"/>
-    <row r="657" s="1" customFormat="1" ht="16.5"/>
-    <row r="658" s="1" customFormat="1" ht="16.5"/>
-    <row r="659" s="1" customFormat="1" ht="16.5"/>
-    <row r="660" s="1" customFormat="1" ht="16.5"/>
-    <row r="661" s="1" customFormat="1" ht="16.5"/>
-    <row r="662" s="1" customFormat="1" ht="16.5"/>
-    <row r="663" s="1" customFormat="1" ht="16.5"/>
-    <row r="664" s="1" customFormat="1" ht="16.5"/>
-    <row r="665" s="1" customFormat="1" ht="16.5"/>
-    <row r="666" s="1" customFormat="1" ht="16.5"/>
-    <row r="667" s="1" customFormat="1" ht="16.5"/>
-    <row r="668" s="1" customFormat="1" ht="16.5"/>
-    <row r="669" s="1" customFormat="1" ht="16.5"/>
-    <row r="670" s="1" customFormat="1" ht="16.5"/>
+    <row r="649" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A649" s="51">
+        <v>10150001</v>
+      </c>
+      <c r="B649" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C649" s="51">
+        <v>1</v>
+      </c>
+      <c r="D649" s="51">
+        <v>0</v>
+      </c>
+      <c r="E649" s="51" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F649" s="51"/>
+      <c r="G649" s="51"/>
+      <c r="H649" s="51"/>
+      <c r="I649" s="51">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="650" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A650" s="51">
+        <v>10150002</v>
+      </c>
+      <c r="B650" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C650" s="51">
+        <v>2</v>
+      </c>
+      <c r="D650" s="51">
+        <v>0</v>
+      </c>
+      <c r="E650" s="51" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F650" s="51"/>
+      <c r="G650" s="51"/>
+      <c r="H650" s="51"/>
+      <c r="I650" s="51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="651" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A651" s="51">
+        <v>10150003</v>
+      </c>
+      <c r="B651" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C651" s="51">
+        <v>3</v>
+      </c>
+      <c r="D651" s="51">
+        <v>0</v>
+      </c>
+      <c r="E651" s="51" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F651" s="51"/>
+      <c r="G651" s="51"/>
+      <c r="H651" s="51"/>
+      <c r="I651" s="51" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="652" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A652" s="51">
+        <v>10150004</v>
+      </c>
+      <c r="B652" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C652" s="51">
+        <v>4</v>
+      </c>
+      <c r="D652" s="51">
+        <v>0</v>
+      </c>
+      <c r="E652" s="51" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F652" s="51"/>
+      <c r="G652" s="51"/>
+      <c r="H652" s="51"/>
+      <c r="I652" s="51" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="653" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A653" s="51">
+        <v>10150005</v>
+      </c>
+      <c r="B653" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C653" s="51">
+        <v>5</v>
+      </c>
+      <c r="D653" s="51">
+        <v>0</v>
+      </c>
+      <c r="E653" s="51" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F653" s="51"/>
+      <c r="G653" s="51"/>
+      <c r="H653" s="51"/>
+      <c r="I653" s="51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="654" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A654" s="51">
+        <v>10150006</v>
+      </c>
+      <c r="B654" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C654" s="51">
+        <v>6</v>
+      </c>
+      <c r="D654" s="51">
+        <v>0</v>
+      </c>
+      <c r="E654" s="51" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F654" s="51"/>
+      <c r="G654" s="51"/>
+      <c r="H654" s="51"/>
+      <c r="I654" s="51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="655" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A655" s="51">
+        <v>10150007</v>
+      </c>
+      <c r="B655" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C655" s="51">
+        <v>7</v>
+      </c>
+      <c r="D655" s="51">
+        <v>0</v>
+      </c>
+      <c r="E655" s="51" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F655" s="51"/>
+      <c r="G655" s="51"/>
+      <c r="H655" s="51"/>
+      <c r="I655" s="51" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="656" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A656" s="51">
+        <v>10150008</v>
+      </c>
+      <c r="B656" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C656" s="51">
+        <v>8</v>
+      </c>
+      <c r="D656" s="51">
+        <v>0</v>
+      </c>
+      <c r="E656" s="51" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F656" s="51"/>
+      <c r="G656" s="51"/>
+      <c r="H656" s="51"/>
+      <c r="I656" s="51" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="657" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A657" s="51">
+        <v>10150009</v>
+      </c>
+      <c r="B657" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C657" s="51">
+        <v>9</v>
+      </c>
+      <c r="D657" s="51">
+        <v>0</v>
+      </c>
+      <c r="E657" s="51" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F657" s="51"/>
+      <c r="G657" s="51"/>
+      <c r="H657" s="51"/>
+      <c r="I657" s="51" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="658" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A658" s="51">
+        <v>10150010</v>
+      </c>
+      <c r="B658" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C658" s="51">
+        <v>10</v>
+      </c>
+      <c r="D658" s="51">
+        <v>0</v>
+      </c>
+      <c r="E658" s="51" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F658" s="51"/>
+      <c r="G658" s="51"/>
+      <c r="H658" s="51"/>
+      <c r="I658" s="51" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="659" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A659" s="51">
+        <v>10150011</v>
+      </c>
+      <c r="B659" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C659" s="51">
+        <v>11</v>
+      </c>
+      <c r="D659" s="51">
+        <v>0</v>
+      </c>
+      <c r="E659" s="51" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F659" s="51"/>
+      <c r="G659" s="51"/>
+      <c r="H659" s="51"/>
+      <c r="I659" s="51" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="660" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A660" s="51">
+        <v>10150012</v>
+      </c>
+      <c r="B660" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C660" s="51">
+        <v>12</v>
+      </c>
+      <c r="D660" s="51">
+        <v>0</v>
+      </c>
+      <c r="E660" s="51" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F660" s="51"/>
+      <c r="G660" s="51"/>
+      <c r="H660" s="51"/>
+      <c r="I660" s="51" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="661" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A661" s="51">
+        <v>10150013</v>
+      </c>
+      <c r="B661" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C661" s="51">
+        <v>13</v>
+      </c>
+      <c r="D661" s="51">
+        <v>1</v>
+      </c>
+      <c r="E661" s="51" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F661" s="51"/>
+      <c r="G661" s="51"/>
+      <c r="H661" s="51"/>
+      <c r="I661" s="51" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="662" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A662" s="51">
+        <v>10150014</v>
+      </c>
+      <c r="B662" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C662" s="51">
+        <v>14</v>
+      </c>
+      <c r="D662" s="51">
+        <v>2</v>
+      </c>
+      <c r="E662" s="51" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F662" s="51"/>
+      <c r="G662" s="51"/>
+      <c r="H662" s="51"/>
+      <c r="I662" s="51" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="663" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A663" s="51">
+        <v>10150015</v>
+      </c>
+      <c r="B663" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C663" s="51">
+        <v>15</v>
+      </c>
+      <c r="D663" s="51">
+        <v>2</v>
+      </c>
+      <c r="E663" s="51" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F663" s="51"/>
+      <c r="G663" s="51"/>
+      <c r="H663" s="51"/>
+      <c r="I663" s="51" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="664" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A664" s="51">
+        <v>10150016</v>
+      </c>
+      <c r="B664" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C664" s="51">
+        <v>16</v>
+      </c>
+      <c r="D664" s="51">
+        <v>2</v>
+      </c>
+      <c r="E664" s="51" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F664" s="51"/>
+      <c r="G664" s="51"/>
+      <c r="H664" s="51"/>
+      <c r="I664" s="51" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="665" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A665" s="51">
+        <v>10150017</v>
+      </c>
+      <c r="B665" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C665" s="51">
+        <v>17</v>
+      </c>
+      <c r="D665" s="51">
+        <v>2</v>
+      </c>
+      <c r="E665" s="51" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F665" s="51"/>
+      <c r="G665" s="51"/>
+      <c r="H665" s="51"/>
+      <c r="I665" s="51" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="666" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A666" s="51">
+        <v>10150018</v>
+      </c>
+      <c r="B666" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C666" s="51">
+        <v>18</v>
+      </c>
+      <c r="D666" s="51">
+        <v>2</v>
+      </c>
+      <c r="E666" s="51" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F666" s="51"/>
+      <c r="G666" s="51"/>
+      <c r="H666" s="51"/>
+      <c r="I666" s="51" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="667" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A667" s="51">
+        <v>10150019</v>
+      </c>
+      <c r="B667" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C667" s="51">
+        <v>19</v>
+      </c>
+      <c r="D667" s="51">
+        <v>2</v>
+      </c>
+      <c r="E667" s="51" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F667" s="51"/>
+      <c r="G667" s="51"/>
+      <c r="H667" s="51"/>
+      <c r="I667" s="51" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="668" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A668" s="51">
+        <v>10150020</v>
+      </c>
+      <c r="B668" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C668" s="51">
+        <v>20</v>
+      </c>
+      <c r="D668" s="51">
+        <v>2</v>
+      </c>
+      <c r="E668" s="51" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F668" s="51"/>
+      <c r="G668" s="51"/>
+      <c r="H668" s="51"/>
+      <c r="I668" s="51" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="669" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A669" s="51">
+        <v>10150021</v>
+      </c>
+      <c r="B669" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C669" s="51">
+        <v>21</v>
+      </c>
+      <c r="D669" s="51">
+        <v>2</v>
+      </c>
+      <c r="E669" s="51" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F669" s="51"/>
+      <c r="G669" s="51"/>
+      <c r="H669" s="51"/>
+      <c r="I669" s="51" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="670" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A670" s="51">
+        <v>10150022</v>
+      </c>
+      <c r="B670" s="51">
+        <v>101500</v>
+      </c>
+      <c r="C670" s="51">
+        <v>22</v>
+      </c>
+      <c r="D670" s="51">
+        <v>2</v>
+      </c>
+      <c r="E670" s="51" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F670" s="51"/>
+      <c r="G670" s="51"/>
+      <c r="H670" s="51"/>
+      <c r="I670" s="51" t="s">
+        <v>1072</v>
+      </c>
+    </row>
     <row r="671" s="1" customFormat="1" ht="16.5"/>
     <row r="672" s="1" customFormat="1" ht="16.5"/>
     <row r="673" s="1" customFormat="1" ht="16.5"/>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="1092">
   <si>
     <t>图标</t>
   </si>
@@ -3340,6 +3340,57 @@
   </si>
   <si>
     <t>ly__icon_22.png</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_1.png</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_2.png</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_3.png</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_4.png</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_5.png</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_6.png</t>
+  </si>
+  <si>
+    <t>图案1</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_7.png</t>
+  </si>
+  <si>
+    <t>图案2</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_8.png</t>
+  </si>
+  <si>
+    <t>图案3</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_9.png</t>
+  </si>
+  <si>
+    <t>图案4</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_10.png</t>
+  </si>
+  <si>
+    <t>图案5</t>
+  </si>
+  <si>
+    <t>dbhjc__icon_11.png</t>
+  </si>
+  <si>
+    <t>图案6</t>
   </si>
 </sst>
 </file>
@@ -3558,12 +3609,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4149,7 +4200,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4301,9 +4352,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
@@ -10227,7 +10275,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="31"/>
       <c r="H211" s="33"/>
-      <c r="I211" s="52" t="s">
+      <c r="I211" s="51" t="s">
         <v>302</v>
       </c>
     </row>
@@ -21081,522 +21129,731 @@
       </c>
     </row>
     <row r="649" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A649" s="51">
+      <c r="A649" s="43">
         <v>10150001</v>
       </c>
-      <c r="B649" s="51">
+      <c r="B649" s="43">
         <v>101500</v>
       </c>
-      <c r="C649" s="51">
+      <c r="C649" s="43">
         <v>1</v>
       </c>
-      <c r="D649" s="51">
-        <v>0</v>
-      </c>
-      <c r="E649" s="51" t="s">
+      <c r="D649" s="43">
+        <v>0</v>
+      </c>
+      <c r="E649" s="43" t="s">
         <v>1048</v>
       </c>
-      <c r="F649" s="51"/>
-      <c r="G649" s="51"/>
-      <c r="H649" s="51"/>
-      <c r="I649" s="51">
+      <c r="F649" s="43"/>
+      <c r="G649" s="43"/>
+      <c r="H649" s="43"/>
+      <c r="I649" s="43">
         <v>9</v>
       </c>
     </row>
     <row r="650" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A650" s="51">
+      <c r="A650" s="43">
         <v>10150002</v>
       </c>
-      <c r="B650" s="51">
+      <c r="B650" s="43">
         <v>101500</v>
       </c>
-      <c r="C650" s="51">
+      <c r="C650" s="43">
         <v>2</v>
       </c>
-      <c r="D650" s="51">
-        <v>0</v>
-      </c>
-      <c r="E650" s="51" t="s">
+      <c r="D650" s="43">
+        <v>0</v>
+      </c>
+      <c r="E650" s="43" t="s">
         <v>1049</v>
       </c>
-      <c r="F650" s="51"/>
-      <c r="G650" s="51"/>
-      <c r="H650" s="51"/>
-      <c r="I650" s="51">
+      <c r="F650" s="43"/>
+      <c r="G650" s="43"/>
+      <c r="H650" s="43"/>
+      <c r="I650" s="43">
         <v>10</v>
       </c>
     </row>
     <row r="651" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A651" s="51">
+      <c r="A651" s="43">
         <v>10150003</v>
       </c>
-      <c r="B651" s="51">
+      <c r="B651" s="43">
         <v>101500</v>
       </c>
-      <c r="C651" s="51">
+      <c r="C651" s="43">
         <v>3</v>
       </c>
-      <c r="D651" s="51">
-        <v>0</v>
-      </c>
-      <c r="E651" s="51" t="s">
+      <c r="D651" s="43">
+        <v>0</v>
+      </c>
+      <c r="E651" s="43" t="s">
         <v>1050</v>
       </c>
-      <c r="F651" s="51"/>
-      <c r="G651" s="51"/>
-      <c r="H651" s="51"/>
-      <c r="I651" s="51" t="s">
+      <c r="F651" s="43"/>
+      <c r="G651" s="43"/>
+      <c r="H651" s="43"/>
+      <c r="I651" s="43" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="652" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A652" s="51">
+      <c r="A652" s="43">
         <v>10150004</v>
       </c>
-      <c r="B652" s="51">
+      <c r="B652" s="43">
         <v>101500</v>
       </c>
-      <c r="C652" s="51">
+      <c r="C652" s="43">
         <v>4</v>
       </c>
-      <c r="D652" s="51">
-        <v>0</v>
-      </c>
-      <c r="E652" s="51" t="s">
+      <c r="D652" s="43">
+        <v>0</v>
+      </c>
+      <c r="E652" s="43" t="s">
         <v>1051</v>
       </c>
-      <c r="F652" s="51"/>
-      <c r="G652" s="51"/>
-      <c r="H652" s="51"/>
-      <c r="I652" s="51" t="s">
+      <c r="F652" s="43"/>
+      <c r="G652" s="43"/>
+      <c r="H652" s="43"/>
+      <c r="I652" s="43" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="653" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A653" s="51">
+      <c r="A653" s="43">
         <v>10150005</v>
       </c>
-      <c r="B653" s="51">
+      <c r="B653" s="43">
         <v>101500</v>
       </c>
-      <c r="C653" s="51">
+      <c r="C653" s="43">
         <v>5</v>
       </c>
-      <c r="D653" s="51">
-        <v>0</v>
-      </c>
-      <c r="E653" s="51" t="s">
+      <c r="D653" s="43">
+        <v>0</v>
+      </c>
+      <c r="E653" s="43" t="s">
         <v>1052</v>
       </c>
-      <c r="F653" s="51"/>
-      <c r="G653" s="51"/>
-      <c r="H653" s="51"/>
-      <c r="I653" s="51" t="s">
+      <c r="F653" s="43"/>
+      <c r="G653" s="43"/>
+      <c r="H653" s="43"/>
+      <c r="I653" s="43" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="654" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A654" s="51">
+      <c r="A654" s="43">
         <v>10150006</v>
       </c>
-      <c r="B654" s="51">
+      <c r="B654" s="43">
         <v>101500</v>
       </c>
-      <c r="C654" s="51">
+      <c r="C654" s="43">
         <v>6</v>
       </c>
-      <c r="D654" s="51">
-        <v>0</v>
-      </c>
-      <c r="E654" s="51" t="s">
+      <c r="D654" s="43">
+        <v>0</v>
+      </c>
+      <c r="E654" s="43" t="s">
         <v>1053</v>
       </c>
-      <c r="F654" s="51"/>
-      <c r="G654" s="51"/>
-      <c r="H654" s="51"/>
-      <c r="I654" s="51" t="s">
+      <c r="F654" s="43"/>
+      <c r="G654" s="43"/>
+      <c r="H654" s="43"/>
+      <c r="I654" s="43" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="655" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A655" s="51">
+      <c r="A655" s="43">
         <v>10150007</v>
       </c>
-      <c r="B655" s="51">
+      <c r="B655" s="43">
         <v>101500</v>
       </c>
-      <c r="C655" s="51">
+      <c r="C655" s="43">
         <v>7</v>
       </c>
-      <c r="D655" s="51">
-        <v>0</v>
-      </c>
-      <c r="E655" s="51" t="s">
+      <c r="D655" s="43">
+        <v>0</v>
+      </c>
+      <c r="E655" s="43" t="s">
         <v>1054</v>
       </c>
-      <c r="F655" s="51"/>
-      <c r="G655" s="51"/>
-      <c r="H655" s="51"/>
-      <c r="I655" s="51" t="s">
+      <c r="F655" s="43"/>
+      <c r="G655" s="43"/>
+      <c r="H655" s="43"/>
+      <c r="I655" s="43" t="s">
         <v>1055</v>
       </c>
     </row>
     <row r="656" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A656" s="51">
+      <c r="A656" s="43">
         <v>10150008</v>
       </c>
-      <c r="B656" s="51">
+      <c r="B656" s="43">
         <v>101500</v>
       </c>
-      <c r="C656" s="51">
+      <c r="C656" s="43">
         <v>8</v>
       </c>
-      <c r="D656" s="51">
-        <v>0</v>
-      </c>
-      <c r="E656" s="51" t="s">
+      <c r="D656" s="43">
+        <v>0</v>
+      </c>
+      <c r="E656" s="43" t="s">
         <v>1056</v>
       </c>
-      <c r="F656" s="51"/>
-      <c r="G656" s="51"/>
-      <c r="H656" s="51"/>
-      <c r="I656" s="51" t="s">
+      <c r="F656" s="43"/>
+      <c r="G656" s="43"/>
+      <c r="H656" s="43"/>
+      <c r="I656" s="43" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="657" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A657" s="51">
+      <c r="A657" s="43">
         <v>10150009</v>
       </c>
-      <c r="B657" s="51">
+      <c r="B657" s="43">
         <v>101500</v>
       </c>
-      <c r="C657" s="51">
+      <c r="C657" s="43">
         <v>9</v>
       </c>
-      <c r="D657" s="51">
-        <v>0</v>
-      </c>
-      <c r="E657" s="51" t="s">
+      <c r="D657" s="43">
+        <v>0</v>
+      </c>
+      <c r="E657" s="43" t="s">
         <v>1057</v>
       </c>
-      <c r="F657" s="51"/>
-      <c r="G657" s="51"/>
-      <c r="H657" s="51"/>
-      <c r="I657" s="51" t="s">
+      <c r="F657" s="43"/>
+      <c r="G657" s="43"/>
+      <c r="H657" s="43"/>
+      <c r="I657" s="43" t="s">
         <v>1058</v>
       </c>
     </row>
     <row r="658" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A658" s="51">
+      <c r="A658" s="43">
         <v>10150010</v>
       </c>
-      <c r="B658" s="51">
+      <c r="B658" s="43">
         <v>101500</v>
       </c>
-      <c r="C658" s="51">
+      <c r="C658" s="43">
         <v>10</v>
       </c>
-      <c r="D658" s="51">
-        <v>0</v>
-      </c>
-      <c r="E658" s="51" t="s">
+      <c r="D658" s="43">
+        <v>0</v>
+      </c>
+      <c r="E658" s="43" t="s">
         <v>1059</v>
       </c>
-      <c r="F658" s="51"/>
-      <c r="G658" s="51"/>
-      <c r="H658" s="51"/>
-      <c r="I658" s="51" t="s">
+      <c r="F658" s="43"/>
+      <c r="G658" s="43"/>
+      <c r="H658" s="43"/>
+      <c r="I658" s="43" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="659" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A659" s="51">
+      <c r="A659" s="43">
         <v>10150011</v>
       </c>
-      <c r="B659" s="51">
+      <c r="B659" s="43">
         <v>101500</v>
       </c>
-      <c r="C659" s="51">
+      <c r="C659" s="43">
         <v>11</v>
       </c>
-      <c r="D659" s="51">
-        <v>0</v>
-      </c>
-      <c r="E659" s="51" t="s">
+      <c r="D659" s="43">
+        <v>0</v>
+      </c>
+      <c r="E659" s="43" t="s">
         <v>1060</v>
       </c>
-      <c r="F659" s="51"/>
-      <c r="G659" s="51"/>
-      <c r="H659" s="51"/>
-      <c r="I659" s="51" t="s">
+      <c r="F659" s="43"/>
+      <c r="G659" s="43"/>
+      <c r="H659" s="43"/>
+      <c r="I659" s="43" t="s">
         <v>1061</v>
       </c>
     </row>
     <row r="660" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A660" s="51">
+      <c r="A660" s="43">
         <v>10150012</v>
       </c>
-      <c r="B660" s="51">
+      <c r="B660" s="43">
         <v>101500</v>
       </c>
-      <c r="C660" s="51">
+      <c r="C660" s="43">
         <v>12</v>
       </c>
-      <c r="D660" s="51">
-        <v>0</v>
-      </c>
-      <c r="E660" s="51" t="s">
+      <c r="D660" s="43">
+        <v>0</v>
+      </c>
+      <c r="E660" s="43" t="s">
         <v>1062</v>
       </c>
-      <c r="F660" s="51"/>
-      <c r="G660" s="51"/>
-      <c r="H660" s="51"/>
-      <c r="I660" s="51" t="s">
+      <c r="F660" s="43"/>
+      <c r="G660" s="43"/>
+      <c r="H660" s="43"/>
+      <c r="I660" s="43" t="s">
         <v>1063</v>
       </c>
     </row>
     <row r="661" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A661" s="51">
+      <c r="A661" s="43">
         <v>10150013</v>
       </c>
-      <c r="B661" s="51">
+      <c r="B661" s="43">
         <v>101500</v>
       </c>
-      <c r="C661" s="51">
+      <c r="C661" s="43">
         <v>13</v>
       </c>
-      <c r="D661" s="51">
+      <c r="D661" s="43">
         <v>1</v>
       </c>
-      <c r="E661" s="51" t="s">
+      <c r="E661" s="43" t="s">
         <v>1064</v>
       </c>
-      <c r="F661" s="51"/>
-      <c r="G661" s="51"/>
-      <c r="H661" s="51"/>
-      <c r="I661" s="51" t="s">
+      <c r="F661" s="43"/>
+      <c r="G661" s="43"/>
+      <c r="H661" s="43"/>
+      <c r="I661" s="43" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="662" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A662" s="51">
+      <c r="A662" s="43">
         <v>10150014</v>
       </c>
-      <c r="B662" s="51">
+      <c r="B662" s="43">
         <v>101500</v>
       </c>
-      <c r="C662" s="51">
+      <c r="C662" s="43">
         <v>14</v>
       </c>
-      <c r="D662" s="51">
+      <c r="D662" s="43">
         <v>2</v>
       </c>
-      <c r="E662" s="51" t="s">
+      <c r="E662" s="43" t="s">
         <v>1065</v>
       </c>
-      <c r="F662" s="51"/>
-      <c r="G662" s="51"/>
-      <c r="H662" s="51"/>
-      <c r="I662" s="51" t="s">
+      <c r="F662" s="43"/>
+      <c r="G662" s="43"/>
+      <c r="H662" s="43"/>
+      <c r="I662" s="43" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="663" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A663" s="51">
+      <c r="A663" s="43">
         <v>10150015</v>
       </c>
-      <c r="B663" s="51">
+      <c r="B663" s="43">
         <v>101500</v>
       </c>
-      <c r="C663" s="51">
+      <c r="C663" s="43">
         <v>15</v>
       </c>
-      <c r="D663" s="51">
+      <c r="D663" s="43">
         <v>2</v>
       </c>
-      <c r="E663" s="51" t="s">
+      <c r="E663" s="43" t="s">
         <v>1066</v>
       </c>
-      <c r="F663" s="51"/>
-      <c r="G663" s="51"/>
-      <c r="H663" s="51"/>
-      <c r="I663" s="51" t="s">
+      <c r="F663" s="43"/>
+      <c r="G663" s="43"/>
+      <c r="H663" s="43"/>
+      <c r="I663" s="43" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="664" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A664" s="51">
+      <c r="A664" s="43">
         <v>10150016</v>
       </c>
-      <c r="B664" s="51">
+      <c r="B664" s="43">
         <v>101500</v>
       </c>
-      <c r="C664" s="51">
+      <c r="C664" s="43">
         <v>16</v>
       </c>
-      <c r="D664" s="51">
+      <c r="D664" s="43">
         <v>2</v>
       </c>
-      <c r="E664" s="51" t="s">
+      <c r="E664" s="43" t="s">
         <v>1067</v>
       </c>
-      <c r="F664" s="51"/>
-      <c r="G664" s="51"/>
-      <c r="H664" s="51"/>
-      <c r="I664" s="51" t="s">
+      <c r="F664" s="43"/>
+      <c r="G664" s="43"/>
+      <c r="H664" s="43"/>
+      <c r="I664" s="43" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="665" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A665" s="51">
+      <c r="A665" s="43">
         <v>10150017</v>
       </c>
-      <c r="B665" s="51">
+      <c r="B665" s="43">
         <v>101500</v>
       </c>
-      <c r="C665" s="51">
+      <c r="C665" s="43">
         <v>17</v>
       </c>
-      <c r="D665" s="51">
+      <c r="D665" s="43">
         <v>2</v>
       </c>
-      <c r="E665" s="51" t="s">
+      <c r="E665" s="43" t="s">
         <v>1068</v>
       </c>
-      <c r="F665" s="51"/>
-      <c r="G665" s="51"/>
-      <c r="H665" s="51"/>
-      <c r="I665" s="51" t="s">
+      <c r="F665" s="43"/>
+      <c r="G665" s="43"/>
+      <c r="H665" s="43"/>
+      <c r="I665" s="43" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="666" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A666" s="51">
+      <c r="A666" s="43">
         <v>10150018</v>
       </c>
-      <c r="B666" s="51">
+      <c r="B666" s="43">
         <v>101500</v>
       </c>
-      <c r="C666" s="51">
+      <c r="C666" s="43">
         <v>18</v>
       </c>
-      <c r="D666" s="51">
+      <c r="D666" s="43">
         <v>2</v>
       </c>
-      <c r="E666" s="51" t="s">
+      <c r="E666" s="43" t="s">
         <v>1069</v>
       </c>
-      <c r="F666" s="51"/>
-      <c r="G666" s="51"/>
-      <c r="H666" s="51"/>
-      <c r="I666" s="51" t="s">
+      <c r="F666" s="43"/>
+      <c r="G666" s="43"/>
+      <c r="H666" s="43"/>
+      <c r="I666" s="43" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="667" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A667" s="51">
+      <c r="A667" s="43">
         <v>10150019</v>
       </c>
-      <c r="B667" s="51">
+      <c r="B667" s="43">
         <v>101500</v>
       </c>
-      <c r="C667" s="51">
+      <c r="C667" s="43">
         <v>19</v>
       </c>
-      <c r="D667" s="51">
+      <c r="D667" s="43">
         <v>2</v>
       </c>
-      <c r="E667" s="51" t="s">
+      <c r="E667" s="43" t="s">
         <v>1070</v>
       </c>
-      <c r="F667" s="51"/>
-      <c r="G667" s="51"/>
-      <c r="H667" s="51"/>
-      <c r="I667" s="51" t="s">
+      <c r="F667" s="43"/>
+      <c r="G667" s="43"/>
+      <c r="H667" s="43"/>
+      <c r="I667" s="43" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="668" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A668" s="51">
+      <c r="A668" s="43">
         <v>10150020</v>
       </c>
-      <c r="B668" s="51">
+      <c r="B668" s="43">
         <v>101500</v>
       </c>
-      <c r="C668" s="51">
+      <c r="C668" s="43">
         <v>20</v>
       </c>
-      <c r="D668" s="51">
+      <c r="D668" s="43">
         <v>2</v>
       </c>
-      <c r="E668" s="51" t="s">
+      <c r="E668" s="43" t="s">
         <v>1071</v>
       </c>
-      <c r="F668" s="51"/>
-      <c r="G668" s="51"/>
-      <c r="H668" s="51"/>
-      <c r="I668" s="51" t="s">
+      <c r="F668" s="43"/>
+      <c r="G668" s="43"/>
+      <c r="H668" s="43"/>
+      <c r="I668" s="43" t="s">
         <v>1072</v>
       </c>
     </row>
     <row r="669" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A669" s="51">
+      <c r="A669" s="43">
         <v>10150021</v>
       </c>
-      <c r="B669" s="51">
+      <c r="B669" s="43">
         <v>101500</v>
       </c>
-      <c r="C669" s="51">
+      <c r="C669" s="43">
         <v>21</v>
       </c>
-      <c r="D669" s="51">
+      <c r="D669" s="43">
         <v>2</v>
       </c>
-      <c r="E669" s="51" t="s">
+      <c r="E669" s="43" t="s">
         <v>1073</v>
       </c>
-      <c r="F669" s="51"/>
-      <c r="G669" s="51"/>
-      <c r="H669" s="51"/>
-      <c r="I669" s="51" t="s">
+      <c r="F669" s="43"/>
+      <c r="G669" s="43"/>
+      <c r="H669" s="43"/>
+      <c r="I669" s="43" t="s">
         <v>1072</v>
       </c>
     </row>
     <row r="670" s="1" customFormat="1" ht="16.5" spans="1:9">
-      <c r="A670" s="51">
+      <c r="A670" s="43">
         <v>10150022</v>
       </c>
-      <c r="B670" s="51">
+      <c r="B670" s="43">
         <v>101500</v>
       </c>
-      <c r="C670" s="51">
+      <c r="C670" s="43">
         <v>22</v>
       </c>
-      <c r="D670" s="51">
+      <c r="D670" s="43">
         <v>2</v>
       </c>
-      <c r="E670" s="51" t="s">
+      <c r="E670" s="43" t="s">
         <v>1074</v>
       </c>
-      <c r="F670" s="51"/>
-      <c r="G670" s="51"/>
-      <c r="H670" s="51"/>
-      <c r="I670" s="51" t="s">
+      <c r="F670" s="43"/>
+      <c r="G670" s="43"/>
+      <c r="H670" s="43"/>
+      <c r="I670" s="43" t="s">
         <v>1072</v>
       </c>
     </row>
-    <row r="671" s="1" customFormat="1" ht="16.5"/>
-    <row r="672" s="1" customFormat="1" ht="16.5"/>
-    <row r="673" s="1" customFormat="1" ht="16.5"/>
-    <row r="674" s="1" customFormat="1" ht="16.5"/>
-    <row r="675" s="1" customFormat="1" ht="16.5"/>
-    <row r="676" s="1" customFormat="1" ht="16.5"/>
-    <row r="677" s="1" customFormat="1" ht="16.5"/>
-    <row r="678" s="1" customFormat="1" ht="16.5"/>
-    <row r="679" s="1" customFormat="1" ht="16.5"/>
-    <row r="680" s="1" customFormat="1" ht="16.5"/>
-    <row r="681" s="1" customFormat="1" ht="16.5"/>
+    <row r="671" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A671" s="1">
+        <v>10260001</v>
+      </c>
+      <c r="B671" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C671" s="1">
+        <v>1</v>
+      </c>
+      <c r="D671" s="1">
+        <v>0</v>
+      </c>
+      <c r="E671" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I671" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="672" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A672" s="1">
+        <v>10260002</v>
+      </c>
+      <c r="B672" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C672" s="1">
+        <v>2</v>
+      </c>
+      <c r="D672" s="1">
+        <v>0</v>
+      </c>
+      <c r="E672" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I672" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="673" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A673" s="1">
+        <v>10260003</v>
+      </c>
+      <c r="B673" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C673" s="1">
+        <v>3</v>
+      </c>
+      <c r="D673" s="1">
+        <v>0</v>
+      </c>
+      <c r="E673" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I673" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="674" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A674" s="1">
+        <v>10260004</v>
+      </c>
+      <c r="B674" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C674" s="1">
+        <v>4</v>
+      </c>
+      <c r="D674" s="1">
+        <v>0</v>
+      </c>
+      <c r="E674" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I674" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="675" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A675" s="1">
+        <v>10260005</v>
+      </c>
+      <c r="B675" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C675" s="1">
+        <v>5</v>
+      </c>
+      <c r="D675" s="1">
+        <v>0</v>
+      </c>
+      <c r="E675" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I675" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="676" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A676" s="1">
+        <v>10260006</v>
+      </c>
+      <c r="B676" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C676" s="1">
+        <v>6</v>
+      </c>
+      <c r="D676" s="1">
+        <v>0</v>
+      </c>
+      <c r="E676" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I676" s="1" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="677" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A677" s="1">
+        <v>10260007</v>
+      </c>
+      <c r="B677" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C677" s="1">
+        <v>7</v>
+      </c>
+      <c r="D677" s="1">
+        <v>0</v>
+      </c>
+      <c r="E677" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I677" s="1" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="678" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A678" s="1">
+        <v>10260008</v>
+      </c>
+      <c r="B678" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C678" s="1">
+        <v>8</v>
+      </c>
+      <c r="D678" s="1">
+        <v>0</v>
+      </c>
+      <c r="E678" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="I678" s="1" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="679" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A679" s="1">
+        <v>10260009</v>
+      </c>
+      <c r="B679" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C679" s="1">
+        <v>9</v>
+      </c>
+      <c r="D679" s="1">
+        <v>0</v>
+      </c>
+      <c r="E679" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I679" s="1" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="680" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A680" s="1">
+        <v>10260010</v>
+      </c>
+      <c r="B680" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C680" s="1">
+        <v>10</v>
+      </c>
+      <c r="D680" s="1">
+        <v>0</v>
+      </c>
+      <c r="E680" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="I680" s="1" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="681" s="1" customFormat="1" ht="16.5" spans="1:9">
+      <c r="A681" s="1">
+        <v>10260011</v>
+      </c>
+      <c r="B681" s="1">
+        <v>102600</v>
+      </c>
+      <c r="C681" s="1">
+        <v>11</v>
+      </c>
+      <c r="D681" s="1">
+        <v>0</v>
+      </c>
+      <c r="E681" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="I681" s="1" t="s">
+        <v>1091</v>
+      </c>
+    </row>
     <row r="682" s="1" customFormat="1" ht="16.5"/>
     <row r="683" s="1" customFormat="1" ht="16.5"/>
     <row r="684" s="1" customFormat="1" ht="16.5"/>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -19046,7 +19046,7 @@
         <v>30</v>
       </c>
       <c r="D547" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E547" s="50" t="s">
         <v>817</v>
@@ -19346,7 +19346,7 @@
         <v>42</v>
       </c>
       <c r="D559" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E559" s="50" t="s">
         <v>836</v>
@@ -19646,7 +19646,7 @@
         <v>54</v>
       </c>
       <c r="D571" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E571" s="50" t="s">
         <v>855</v>
@@ -22900,7 +22900,7 @@
         <v>29</v>
       </c>
       <c r="D699" s="51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E699" s="51" t="s">
         <v>1115</v>
@@ -23200,7 +23200,7 @@
         <v>41</v>
       </c>
       <c r="D711" s="51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E711" s="51" t="s">
         <v>1133</v>
@@ -23500,7 +23500,7 @@
         <v>53</v>
       </c>
       <c r="D723" s="51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E723" s="51" t="s">
         <v>1151</v>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -13248,7 +13248,7 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="28">
-        <f>B292*100+C292</f>
+        <f t="shared" si="11"/>
         <v>10360009</v>
       </c>
       <c r="B292" s="28">
@@ -28736,7 +28736,7 @@
         <v>10510001</v>
       </c>
       <c r="B915" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C915" s="57">
         <v>1</v>
@@ -28757,7 +28757,7 @@
         <v>10510002</v>
       </c>
       <c r="B916" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C916" s="57">
         <v>2</v>
@@ -28778,7 +28778,7 @@
         <v>10510003</v>
       </c>
       <c r="B917" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C917" s="57">
         <v>3</v>
@@ -28799,7 +28799,7 @@
         <v>10510004</v>
       </c>
       <c r="B918" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C918" s="57">
         <v>4</v>
@@ -28820,7 +28820,7 @@
         <v>10510005</v>
       </c>
       <c r="B919" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C919" s="57">
         <v>5</v>
@@ -28841,7 +28841,7 @@
         <v>10510006</v>
       </c>
       <c r="B920" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C920" s="57">
         <v>6</v>
@@ -28862,7 +28862,7 @@
         <v>10510007</v>
       </c>
       <c r="B921" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C921" s="57">
         <v>7</v>
@@ -28883,7 +28883,7 @@
         <v>10510008</v>
       </c>
       <c r="B922" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C922" s="57">
         <v>8</v>
@@ -28904,7 +28904,7 @@
         <v>10510009</v>
       </c>
       <c r="B923" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C923" s="57">
         <v>9</v>
@@ -28925,7 +28925,7 @@
         <v>10510010</v>
       </c>
       <c r="B924" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C924" s="57">
         <v>10</v>
@@ -28946,7 +28946,7 @@
         <v>10510011</v>
       </c>
       <c r="B925" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C925" s="57">
         <v>11</v>
@@ -28967,7 +28967,7 @@
         <v>10510012</v>
       </c>
       <c r="B926" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C926" s="57">
         <v>12</v>
@@ -28988,7 +28988,7 @@
         <v>10510013</v>
       </c>
       <c r="B927" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C927" s="57">
         <v>13</v>
@@ -29009,7 +29009,7 @@
         <v>10510014</v>
       </c>
       <c r="B928" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C928" s="57">
         <v>14</v>
@@ -29030,7 +29030,7 @@
         <v>10510015</v>
       </c>
       <c r="B929" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C929" s="57">
         <v>15</v>
@@ -29051,7 +29051,7 @@
         <v>10510016</v>
       </c>
       <c r="B930" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C930" s="57">
         <v>16</v>
@@ -29072,7 +29072,7 @@
         <v>10510017</v>
       </c>
       <c r="B931" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C931" s="57">
         <v>17</v>
@@ -29093,7 +29093,7 @@
         <v>10510018</v>
       </c>
       <c r="B932" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C932" s="57">
         <v>18</v>
@@ -29114,7 +29114,7 @@
         <v>10510019</v>
       </c>
       <c r="B933" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C933" s="57">
         <v>19</v>
@@ -29135,7 +29135,7 @@
         <v>10510020</v>
       </c>
       <c r="B934" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C934" s="57">
         <v>20</v>
@@ -29156,7 +29156,7 @@
         <v>10510021</v>
       </c>
       <c r="B935" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C935" s="57">
         <v>21</v>
@@ -29177,7 +29177,7 @@
         <v>10510022</v>
       </c>
       <c r="B936" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C936" s="57">
         <v>22</v>
@@ -29198,7 +29198,7 @@
         <v>10510023</v>
       </c>
       <c r="B937" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C937" s="57">
         <v>23</v>
@@ -29219,7 +29219,7 @@
         <v>10510024</v>
       </c>
       <c r="B938" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C938" s="57">
         <v>24</v>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -13248,7 +13248,7 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="28">
-        <f t="shared" si="11"/>
+        <f>B292*100+C292</f>
         <v>10360009</v>
       </c>
       <c r="B292" s="28">
@@ -28736,7 +28736,7 @@
         <v>10510001</v>
       </c>
       <c r="B915" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C915" s="57">
         <v>1</v>
@@ -28757,7 +28757,7 @@
         <v>10510002</v>
       </c>
       <c r="B916" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C916" s="57">
         <v>2</v>
@@ -28778,7 +28778,7 @@
         <v>10510003</v>
       </c>
       <c r="B917" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C917" s="57">
         <v>3</v>
@@ -28799,7 +28799,7 @@
         <v>10510004</v>
       </c>
       <c r="B918" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C918" s="57">
         <v>4</v>
@@ -28820,7 +28820,7 @@
         <v>10510005</v>
       </c>
       <c r="B919" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C919" s="57">
         <v>5</v>
@@ -28841,7 +28841,7 @@
         <v>10510006</v>
       </c>
       <c r="B920" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C920" s="57">
         <v>6</v>
@@ -28862,7 +28862,7 @@
         <v>10510007</v>
       </c>
       <c r="B921" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C921" s="57">
         <v>7</v>
@@ -28883,7 +28883,7 @@
         <v>10510008</v>
       </c>
       <c r="B922" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C922" s="57">
         <v>8</v>
@@ -28904,7 +28904,7 @@
         <v>10510009</v>
       </c>
       <c r="B923" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C923" s="57">
         <v>9</v>
@@ -28925,7 +28925,7 @@
         <v>10510010</v>
       </c>
       <c r="B924" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C924" s="57">
         <v>10</v>
@@ -28946,7 +28946,7 @@
         <v>10510011</v>
       </c>
       <c r="B925" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C925" s="57">
         <v>11</v>
@@ -28967,7 +28967,7 @@
         <v>10510012</v>
       </c>
       <c r="B926" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C926" s="57">
         <v>12</v>
@@ -28988,7 +28988,7 @@
         <v>10510013</v>
       </c>
       <c r="B927" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C927" s="57">
         <v>13</v>
@@ -29009,7 +29009,7 @@
         <v>10510014</v>
       </c>
       <c r="B928" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C928" s="57">
         <v>14</v>
@@ -29030,7 +29030,7 @@
         <v>10510015</v>
       </c>
       <c r="B929" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C929" s="57">
         <v>15</v>
@@ -29051,7 +29051,7 @@
         <v>10510016</v>
       </c>
       <c r="B930" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C930" s="57">
         <v>16</v>
@@ -29072,7 +29072,7 @@
         <v>10510017</v>
       </c>
       <c r="B931" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C931" s="57">
         <v>17</v>
@@ -29093,7 +29093,7 @@
         <v>10510018</v>
       </c>
       <c r="B932" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C932" s="57">
         <v>18</v>
@@ -29114,7 +29114,7 @@
         <v>10510019</v>
       </c>
       <c r="B933" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C933" s="57">
         <v>19</v>
@@ -29135,7 +29135,7 @@
         <v>10510020</v>
       </c>
       <c r="B934" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C934" s="57">
         <v>20</v>
@@ -29156,7 +29156,7 @@
         <v>10510021</v>
       </c>
       <c r="B935" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C935" s="57">
         <v>21</v>
@@ -29177,7 +29177,7 @@
         <v>10510022</v>
       </c>
       <c r="B936" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C936" s="57">
         <v>22</v>
@@ -29198,7 +29198,7 @@
         <v>10510023</v>
       </c>
       <c r="B937" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C937" s="57">
         <v>23</v>
@@ -29219,7 +29219,7 @@
         <v>10510024</v>
       </c>
       <c r="B938" s="57">
-        <v>105100</v>
+        <v>105001</v>
       </c>
       <c r="C938" s="57">
         <v>24</v>

--- a/slots/resources/sample/BaseElement.xlsx
+++ b/slots/resources/sample/BaseElement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21000" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseElement" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="1429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="1526">
   <si>
     <t>图标</t>
   </si>
@@ -4402,6 +4402,297 @@
   </si>
   <si>
     <t>透明图标</t>
+  </si>
+  <si>
+    <t>图标1</t>
+  </si>
+  <si>
+    <t>图标2</t>
+  </si>
+  <si>
+    <t>图标3</t>
+  </si>
+  <si>
+    <t>图标4</t>
+  </si>
+  <si>
+    <t>图标5</t>
+  </si>
+  <si>
+    <t>图标1*2</t>
+  </si>
+  <si>
+    <t>图标2*2</t>
+  </si>
+  <si>
+    <t>图标3*2</t>
+  </si>
+  <si>
+    <t>图标4*2</t>
+  </si>
+  <si>
+    <t>图标5*2</t>
+  </si>
+  <si>
+    <t>Wild*2</t>
+  </si>
+  <si>
+    <t>图标1*3</t>
+  </si>
+  <si>
+    <t>图标2*3</t>
+  </si>
+  <si>
+    <t>图标3*3</t>
+  </si>
+  <si>
+    <t>图标4*3</t>
+  </si>
+  <si>
+    <t>图标5*3</t>
+  </si>
+  <si>
+    <t>Wild*3</t>
+  </si>
+  <si>
+    <t>图标1*4</t>
+  </si>
+  <si>
+    <t>图标2*4</t>
+  </si>
+  <si>
+    <t>图标3*4</t>
+  </si>
+  <si>
+    <t>图标4*4</t>
+  </si>
+  <si>
+    <t>图标5*4</t>
+  </si>
+  <si>
+    <t>Wild*4</t>
+  </si>
+  <si>
+    <t>11_1</t>
+  </si>
+  <si>
+    <t>金框10*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框J*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框Q*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框K*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框A*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标1*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标2*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标3*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标4*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>金框图标5*1 消除后变为Wild</t>
+  </si>
+  <si>
+    <t>27_1</t>
+  </si>
+  <si>
+    <t>金框10*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框J*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框Q*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框K*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框A*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标1*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标2*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标3*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标4*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>金框图标5*2 消除后变为Wild*2</t>
+  </si>
+  <si>
+    <t>38_1</t>
+  </si>
+  <si>
+    <t>金框10*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框J*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框Q*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框K*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框A*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标1*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标2*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标3*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标4*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>金框图标5*3 消除后变为Wild*3</t>
+  </si>
+  <si>
+    <t>49_1</t>
+  </si>
+  <si>
+    <t>金框10*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框J*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框Q*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框K*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框A*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标1*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标2*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标3*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标4*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>金框图标5*4 消除后变为Wild*4</t>
+  </si>
+  <si>
+    <t>97_100|98_80|99_60|100_40|101_20|102_10|103_8|104_6|105_3|106_1</t>
+  </si>
+  <si>
+    <t>107_100|108_80|109_60|110_40|111_20|112_10|113_8|114_6|115_3|116_1</t>
+  </si>
+  <si>
+    <t>55_1</t>
+  </si>
+  <si>
+    <t>二条</t>
+  </si>
+  <si>
+    <t>二筒</t>
+  </si>
+  <si>
+    <t>三筒</t>
+  </si>
+  <si>
+    <t>五条</t>
+  </si>
+  <si>
+    <t>五筒</t>
+  </si>
+  <si>
+    <t>10_1</t>
+  </si>
+  <si>
+    <t>黄金_二条|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>黄金_二筒|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>黄金_三筒|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>黄金_五条|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>黄金_五筒|消除后变为Wild百搭</t>
+  </si>
+  <si>
+    <t>金框_J|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_Q|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_K|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_A|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_图案1|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_图案2|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_图案3|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>金框_图案4|消除后变为wild百搭</t>
+  </si>
+  <si>
+    <t>橙色小熊</t>
+  </si>
+  <si>
+    <t>紫色小熊</t>
+  </si>
+  <si>
+    <t>红色小熊</t>
+  </si>
+  <si>
+    <t>绿色星星</t>
+  </si>
+  <si>
+    <t>紫色软糖</t>
+  </si>
+  <si>
+    <t>橙色爱心</t>
+  </si>
+  <si>
+    <t>粉色糖果</t>
+  </si>
+  <si>
+    <t>奖池图标</t>
   </si>
 </sst>
 </file>
@@ -4414,7 +4705,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4467,6 +4758,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -4615,24 +4912,24 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -5092,16 +5389,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5110,120 +5404,123 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5403,6 +5700,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -5728,7 +6046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N938"/>
+  <dimension ref="A1:N1191"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="12.625"/>
@@ -11326,7 +11644,7 @@
       <c r="F211" s="31"/>
       <c r="G211" s="32"/>
       <c r="H211" s="34"/>
-      <c r="I211" s="60" t="s">
+      <c r="I211" s="67" t="s">
         <v>302</v>
       </c>
     </row>
@@ -13248,7 +13566,7 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="28">
-        <f>B292*100+C292</f>
+        <f t="shared" si="11"/>
         <v>10360009</v>
       </c>
       <c r="B292" s="28">
@@ -28736,7 +29054,7 @@
         <v>10510001</v>
       </c>
       <c r="B915" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C915" s="57">
         <v>1</v>
@@ -28757,7 +29075,7 @@
         <v>10510002</v>
       </c>
       <c r="B916" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C916" s="57">
         <v>2</v>
@@ -28778,7 +29096,7 @@
         <v>10510003</v>
       </c>
       <c r="B917" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C917" s="57">
         <v>3</v>
@@ -28799,7 +29117,7 @@
         <v>10510004</v>
       </c>
       <c r="B918" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C918" s="57">
         <v>4</v>
@@ -28820,7 +29138,7 @@
         <v>10510005</v>
       </c>
       <c r="B919" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C919" s="57">
         <v>5</v>
@@ -28841,7 +29159,7 @@
         <v>10510006</v>
       </c>
       <c r="B920" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C920" s="57">
         <v>6</v>
@@ -28862,7 +29180,7 @@
         <v>10510007</v>
       </c>
       <c r="B921" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C921" s="57">
         <v>7</v>
@@ -28883,7 +29201,7 @@
         <v>10510008</v>
       </c>
       <c r="B922" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C922" s="57">
         <v>8</v>
@@ -28904,7 +29222,7 @@
         <v>10510009</v>
       </c>
       <c r="B923" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C923" s="57">
         <v>9</v>
@@ -28925,7 +29243,7 @@
         <v>10510010</v>
       </c>
       <c r="B924" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C924" s="57">
         <v>10</v>
@@ -28946,7 +29264,7 @@
         <v>10510011</v>
       </c>
       <c r="B925" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C925" s="57">
         <v>11</v>
@@ -28967,7 +29285,7 @@
         <v>10510012</v>
       </c>
       <c r="B926" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C926" s="57">
         <v>12</v>
@@ -28988,7 +29306,7 @@
         <v>10510013</v>
       </c>
       <c r="B927" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C927" s="57">
         <v>13</v>
@@ -29009,7 +29327,7 @@
         <v>10510014</v>
       </c>
       <c r="B928" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C928" s="57">
         <v>14</v>
@@ -29030,7 +29348,7 @@
         <v>10510015</v>
       </c>
       <c r="B929" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C929" s="57">
         <v>15</v>
@@ -29051,7 +29369,7 @@
         <v>10510016</v>
       </c>
       <c r="B930" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C930" s="57">
         <v>16</v>
@@ -29072,7 +29390,7 @@
         <v>10510017</v>
       </c>
       <c r="B931" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C931" s="57">
         <v>17</v>
@@ -29093,7 +29411,7 @@
         <v>10510018</v>
       </c>
       <c r="B932" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C932" s="57">
         <v>18</v>
@@ -29114,7 +29432,7 @@
         <v>10510019</v>
       </c>
       <c r="B933" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C933" s="57">
         <v>19</v>
@@ -29135,7 +29453,7 @@
         <v>10510020</v>
       </c>
       <c r="B934" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C934" s="57">
         <v>20</v>
@@ -29156,7 +29474,7 @@
         <v>10510021</v>
       </c>
       <c r="B935" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C935" s="57">
         <v>21</v>
@@ -29177,7 +29495,7 @@
         <v>10510022</v>
       </c>
       <c r="B936" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C936" s="57">
         <v>22</v>
@@ -29198,7 +29516,7 @@
         <v>10510023</v>
       </c>
       <c r="B937" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C937" s="57">
         <v>23</v>
@@ -29219,7 +29537,7 @@
         <v>10510024</v>
       </c>
       <c r="B938" s="57">
-        <v>105001</v>
+        <v>105100</v>
       </c>
       <c r="C938" s="57">
         <v>24</v>
@@ -29233,6 +29551,5695 @@
       <c r="H938" s="57"/>
       <c r="I938" s="59" t="s">
         <v>1428</v>
+      </c>
+    </row>
+    <row r="939" spans="1:9">
+      <c r="A939" s="60">
+        <v>10540001</v>
+      </c>
+      <c r="B939" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C939" s="60">
+        <v>1</v>
+      </c>
+      <c r="D939" s="60">
+        <v>0</v>
+      </c>
+      <c r="E939" s="60"/>
+      <c r="F939" s="60"/>
+      <c r="G939" s="60"/>
+      <c r="H939" s="60"/>
+      <c r="I939" s="61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="940" spans="1:9">
+      <c r="A940" s="60">
+        <v>10540002</v>
+      </c>
+      <c r="B940" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C940" s="60">
+        <v>2</v>
+      </c>
+      <c r="D940" s="60"/>
+      <c r="E940" s="60"/>
+      <c r="F940" s="60"/>
+      <c r="G940" s="60"/>
+      <c r="H940" s="60"/>
+      <c r="I940" s="60" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="941" spans="1:9">
+      <c r="A941" s="60">
+        <v>10540003</v>
+      </c>
+      <c r="B941" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C941" s="60">
+        <v>3</v>
+      </c>
+      <c r="D941" s="60"/>
+      <c r="E941" s="60"/>
+      <c r="F941" s="60"/>
+      <c r="G941" s="60"/>
+      <c r="H941" s="60"/>
+      <c r="I941" s="60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="942" spans="1:9">
+      <c r="A942" s="60">
+        <v>10540004</v>
+      </c>
+      <c r="B942" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C942" s="60">
+        <v>4</v>
+      </c>
+      <c r="D942" s="60"/>
+      <c r="E942" s="60"/>
+      <c r="F942" s="60"/>
+      <c r="G942" s="60"/>
+      <c r="H942" s="60"/>
+      <c r="I942" s="60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="943" spans="1:9">
+      <c r="A943" s="60">
+        <v>10540005</v>
+      </c>
+      <c r="B943" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C943" s="60">
+        <v>5</v>
+      </c>
+      <c r="D943" s="60"/>
+      <c r="E943" s="60"/>
+      <c r="F943" s="60"/>
+      <c r="G943" s="60"/>
+      <c r="H943" s="60"/>
+      <c r="I943" s="60" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="944" spans="1:9">
+      <c r="A944" s="60">
+        <v>10540006</v>
+      </c>
+      <c r="B944" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C944" s="60">
+        <v>6</v>
+      </c>
+      <c r="D944" s="60"/>
+      <c r="E944" s="60"/>
+      <c r="F944" s="60"/>
+      <c r="G944" s="60"/>
+      <c r="H944" s="60"/>
+      <c r="I944" s="60" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="945" spans="1:9">
+      <c r="A945" s="60">
+        <v>10540007</v>
+      </c>
+      <c r="B945" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C945" s="60">
+        <v>7</v>
+      </c>
+      <c r="D945" s="60"/>
+      <c r="E945" s="60"/>
+      <c r="F945" s="60"/>
+      <c r="G945" s="60"/>
+      <c r="H945" s="60"/>
+      <c r="I945" s="60" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="946" spans="1:9">
+      <c r="A946" s="60">
+        <v>10540008</v>
+      </c>
+      <c r="B946" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C946" s="60">
+        <v>8</v>
+      </c>
+      <c r="D946" s="60"/>
+      <c r="E946" s="60"/>
+      <c r="F946" s="60"/>
+      <c r="G946" s="60"/>
+      <c r="H946" s="60"/>
+      <c r="I946" s="60" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="947" spans="1:9">
+      <c r="A947" s="60">
+        <v>10540009</v>
+      </c>
+      <c r="B947" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C947" s="60">
+        <v>9</v>
+      </c>
+      <c r="D947" s="60"/>
+      <c r="E947" s="60"/>
+      <c r="F947" s="60"/>
+      <c r="G947" s="60"/>
+      <c r="H947" s="60"/>
+      <c r="I947" s="60" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="948" spans="1:9">
+      <c r="A948" s="60">
+        <v>10540010</v>
+      </c>
+      <c r="B948" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C948" s="60">
+        <v>10</v>
+      </c>
+      <c r="D948" s="60"/>
+      <c r="E948" s="60"/>
+      <c r="F948" s="60"/>
+      <c r="G948" s="60"/>
+      <c r="H948" s="60"/>
+      <c r="I948" s="60" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="949" spans="1:9">
+      <c r="A949" s="60">
+        <v>10540011</v>
+      </c>
+      <c r="B949" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C949" s="60">
+        <v>11</v>
+      </c>
+      <c r="D949" s="60"/>
+      <c r="E949" s="60"/>
+      <c r="F949" s="60"/>
+      <c r="G949" s="60"/>
+      <c r="H949" s="60"/>
+      <c r="I949" s="60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9">
+      <c r="A950" s="60">
+        <v>10540012</v>
+      </c>
+      <c r="B950" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C950" s="60">
+        <v>12</v>
+      </c>
+      <c r="D950" s="60"/>
+      <c r="E950" s="60"/>
+      <c r="F950" s="60"/>
+      <c r="G950" s="60"/>
+      <c r="H950" s="60"/>
+      <c r="I950" s="60" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="951" spans="1:9">
+      <c r="A951" s="60">
+        <v>10540013</v>
+      </c>
+      <c r="B951" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C951" s="60">
+        <v>13</v>
+      </c>
+      <c r="D951" s="60"/>
+      <c r="E951" s="60"/>
+      <c r="F951" s="60"/>
+      <c r="G951" s="60"/>
+      <c r="H951" s="60"/>
+      <c r="I951" s="60" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9">
+      <c r="A952" s="60">
+        <v>10540014</v>
+      </c>
+      <c r="B952" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C952" s="60">
+        <v>14</v>
+      </c>
+      <c r="D952" s="60"/>
+      <c r="E952" s="60"/>
+      <c r="F952" s="60"/>
+      <c r="G952" s="60"/>
+      <c r="H952" s="60"/>
+      <c r="I952" s="60" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="953" spans="1:9">
+      <c r="A953" s="60">
+        <v>10540015</v>
+      </c>
+      <c r="B953" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C953" s="60">
+        <v>15</v>
+      </c>
+      <c r="D953" s="60"/>
+      <c r="E953" s="60"/>
+      <c r="F953" s="60"/>
+      <c r="G953" s="60"/>
+      <c r="H953" s="60"/>
+      <c r="I953" s="60" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9">
+      <c r="A954" s="60">
+        <v>10540016</v>
+      </c>
+      <c r="B954" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C954" s="60">
+        <v>16</v>
+      </c>
+      <c r="D954" s="60"/>
+      <c r="E954" s="60"/>
+      <c r="F954" s="60"/>
+      <c r="G954" s="60"/>
+      <c r="H954" s="60"/>
+      <c r="I954" s="60" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="955" spans="1:9">
+      <c r="A955" s="60">
+        <v>10540017</v>
+      </c>
+      <c r="B955" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C955" s="60">
+        <v>17</v>
+      </c>
+      <c r="D955" s="60"/>
+      <c r="E955" s="60"/>
+      <c r="F955" s="60"/>
+      <c r="G955" s="60"/>
+      <c r="H955" s="60">
+        <v>2</v>
+      </c>
+      <c r="I955" s="61" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9">
+      <c r="A956" s="60">
+        <v>10540018</v>
+      </c>
+      <c r="B956" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C956" s="60">
+        <v>18</v>
+      </c>
+      <c r="D956" s="60"/>
+      <c r="E956" s="60"/>
+      <c r="F956" s="60"/>
+      <c r="G956" s="60"/>
+      <c r="H956" s="60">
+        <v>2</v>
+      </c>
+      <c r="I956" s="60" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="957" spans="1:9">
+      <c r="A957" s="60">
+        <v>10540019</v>
+      </c>
+      <c r="B957" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C957" s="60">
+        <v>19</v>
+      </c>
+      <c r="D957" s="60"/>
+      <c r="E957" s="60"/>
+      <c r="F957" s="60"/>
+      <c r="G957" s="60"/>
+      <c r="H957" s="60">
+        <v>2</v>
+      </c>
+      <c r="I957" s="60" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9">
+      <c r="A958" s="60">
+        <v>10540020</v>
+      </c>
+      <c r="B958" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C958" s="60">
+        <v>20</v>
+      </c>
+      <c r="D958" s="60"/>
+      <c r="E958" s="60"/>
+      <c r="F958" s="60"/>
+      <c r="G958" s="60"/>
+      <c r="H958" s="60">
+        <v>2</v>
+      </c>
+      <c r="I958" s="60" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="959" spans="1:9">
+      <c r="A959" s="60">
+        <v>10540021</v>
+      </c>
+      <c r="B959" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C959" s="60">
+        <v>21</v>
+      </c>
+      <c r="D959" s="60"/>
+      <c r="E959" s="60"/>
+      <c r="F959" s="60"/>
+      <c r="G959" s="60"/>
+      <c r="H959" s="60">
+        <v>2</v>
+      </c>
+      <c r="I959" s="60" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9">
+      <c r="A960" s="60">
+        <v>10540022</v>
+      </c>
+      <c r="B960" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C960" s="60">
+        <v>22</v>
+      </c>
+      <c r="D960" s="60"/>
+      <c r="E960" s="60"/>
+      <c r="F960" s="60"/>
+      <c r="G960" s="60"/>
+      <c r="H960" s="60">
+        <v>2</v>
+      </c>
+      <c r="I960" s="60" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="961" spans="1:9">
+      <c r="A961" s="60">
+        <v>10540023</v>
+      </c>
+      <c r="B961" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C961" s="60">
+        <v>23</v>
+      </c>
+      <c r="D961" s="60"/>
+      <c r="E961" s="60"/>
+      <c r="F961" s="60"/>
+      <c r="G961" s="60"/>
+      <c r="H961" s="60">
+        <v>2</v>
+      </c>
+      <c r="I961" s="60" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9">
+      <c r="A962" s="60">
+        <v>10540024</v>
+      </c>
+      <c r="B962" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C962" s="60">
+        <v>24</v>
+      </c>
+      <c r="D962" s="60"/>
+      <c r="E962" s="60"/>
+      <c r="F962" s="60"/>
+      <c r="G962" s="60"/>
+      <c r="H962" s="60">
+        <v>2</v>
+      </c>
+      <c r="I962" s="60" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="963" spans="1:9">
+      <c r="A963" s="60">
+        <v>10540025</v>
+      </c>
+      <c r="B963" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C963" s="60">
+        <v>25</v>
+      </c>
+      <c r="D963" s="60"/>
+      <c r="E963" s="60"/>
+      <c r="F963" s="60"/>
+      <c r="G963" s="60"/>
+      <c r="H963" s="60">
+        <v>2</v>
+      </c>
+      <c r="I963" s="60" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9">
+      <c r="A964" s="60">
+        <v>10540026</v>
+      </c>
+      <c r="B964" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C964" s="60">
+        <v>26</v>
+      </c>
+      <c r="D964" s="60"/>
+      <c r="E964" s="60"/>
+      <c r="F964" s="60"/>
+      <c r="G964" s="60"/>
+      <c r="H964" s="60">
+        <v>2</v>
+      </c>
+      <c r="I964" s="60" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="965" spans="1:9">
+      <c r="A965" s="60">
+        <v>10540027</v>
+      </c>
+      <c r="B965" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C965" s="60">
+        <v>27</v>
+      </c>
+      <c r="D965" s="60"/>
+      <c r="E965" s="60"/>
+      <c r="F965" s="60"/>
+      <c r="G965" s="60"/>
+      <c r="H965" s="60">
+        <v>2</v>
+      </c>
+      <c r="I965" s="60" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9">
+      <c r="A966" s="60">
+        <v>10540028</v>
+      </c>
+      <c r="B966" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C966" s="60">
+        <v>28</v>
+      </c>
+      <c r="D966" s="60"/>
+      <c r="E966" s="60"/>
+      <c r="F966" s="60"/>
+      <c r="G966" s="60"/>
+      <c r="H966" s="60">
+        <v>3</v>
+      </c>
+      <c r="I966" s="61" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="967" spans="1:9">
+      <c r="A967" s="60">
+        <v>10540029</v>
+      </c>
+      <c r="B967" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C967" s="60">
+        <v>29</v>
+      </c>
+      <c r="D967" s="60"/>
+      <c r="E967" s="60"/>
+      <c r="F967" s="60"/>
+      <c r="G967" s="60"/>
+      <c r="H967" s="60">
+        <v>3</v>
+      </c>
+      <c r="I967" s="60" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9">
+      <c r="A968" s="60">
+        <v>10540030</v>
+      </c>
+      <c r="B968" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C968" s="60">
+        <v>30</v>
+      </c>
+      <c r="D968" s="60"/>
+      <c r="E968" s="60"/>
+      <c r="F968" s="60"/>
+      <c r="G968" s="60"/>
+      <c r="H968" s="60">
+        <v>3</v>
+      </c>
+      <c r="I968" s="60" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="969" spans="1:9">
+      <c r="A969" s="60">
+        <v>10540031</v>
+      </c>
+      <c r="B969" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C969" s="60">
+        <v>31</v>
+      </c>
+      <c r="D969" s="60"/>
+      <c r="E969" s="60"/>
+      <c r="F969" s="60"/>
+      <c r="G969" s="60"/>
+      <c r="H969" s="60">
+        <v>3</v>
+      </c>
+      <c r="I969" s="60" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9">
+      <c r="A970" s="60">
+        <v>10540032</v>
+      </c>
+      <c r="B970" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C970" s="60">
+        <v>32</v>
+      </c>
+      <c r="D970" s="60"/>
+      <c r="E970" s="60"/>
+      <c r="F970" s="60"/>
+      <c r="G970" s="60"/>
+      <c r="H970" s="60">
+        <v>3</v>
+      </c>
+      <c r="I970" s="60" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="971" spans="1:9">
+      <c r="A971" s="60">
+        <v>10540033</v>
+      </c>
+      <c r="B971" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C971" s="60">
+        <v>33</v>
+      </c>
+      <c r="D971" s="60"/>
+      <c r="E971" s="60"/>
+      <c r="F971" s="60"/>
+      <c r="G971" s="60"/>
+      <c r="H971" s="60">
+        <v>3</v>
+      </c>
+      <c r="I971" s="60" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9">
+      <c r="A972" s="60">
+        <v>10540034</v>
+      </c>
+      <c r="B972" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C972" s="60">
+        <v>34</v>
+      </c>
+      <c r="D972" s="60"/>
+      <c r="E972" s="60"/>
+      <c r="F972" s="60"/>
+      <c r="G972" s="60"/>
+      <c r="H972" s="60">
+        <v>3</v>
+      </c>
+      <c r="I972" s="60" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="973" spans="1:9">
+      <c r="A973" s="60">
+        <v>10540035</v>
+      </c>
+      <c r="B973" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C973" s="60">
+        <v>35</v>
+      </c>
+      <c r="D973" s="60"/>
+      <c r="E973" s="60"/>
+      <c r="F973" s="60"/>
+      <c r="G973" s="60"/>
+      <c r="H973" s="60">
+        <v>3</v>
+      </c>
+      <c r="I973" s="60" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9">
+      <c r="A974" s="60">
+        <v>10540036</v>
+      </c>
+      <c r="B974" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C974" s="60">
+        <v>36</v>
+      </c>
+      <c r="D974" s="60"/>
+      <c r="E974" s="60"/>
+      <c r="F974" s="60"/>
+      <c r="G974" s="60"/>
+      <c r="H974" s="60">
+        <v>3</v>
+      </c>
+      <c r="I974" s="60" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="975" spans="1:9">
+      <c r="A975" s="60">
+        <v>10540037</v>
+      </c>
+      <c r="B975" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C975" s="60">
+        <v>37</v>
+      </c>
+      <c r="D975" s="60"/>
+      <c r="E975" s="60"/>
+      <c r="F975" s="60"/>
+      <c r="G975" s="60"/>
+      <c r="H975" s="60">
+        <v>3</v>
+      </c>
+      <c r="I975" s="60" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9">
+      <c r="A976" s="60">
+        <v>10540038</v>
+      </c>
+      <c r="B976" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C976" s="60">
+        <v>38</v>
+      </c>
+      <c r="D976" s="60"/>
+      <c r="E976" s="60"/>
+      <c r="F976" s="60"/>
+      <c r="G976" s="60"/>
+      <c r="H976" s="60">
+        <v>3</v>
+      </c>
+      <c r="I976" s="60" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="977" spans="1:9">
+      <c r="A977" s="60">
+        <v>10540039</v>
+      </c>
+      <c r="B977" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C977" s="60">
+        <v>39</v>
+      </c>
+      <c r="D977" s="60"/>
+      <c r="E977" s="60"/>
+      <c r="F977" s="60"/>
+      <c r="G977" s="60"/>
+      <c r="H977" s="60">
+        <v>4</v>
+      </c>
+      <c r="I977" s="61" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9">
+      <c r="A978" s="60">
+        <v>10540040</v>
+      </c>
+      <c r="B978" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C978" s="60">
+        <v>40</v>
+      </c>
+      <c r="D978" s="60"/>
+      <c r="E978" s="60"/>
+      <c r="F978" s="60"/>
+      <c r="G978" s="60"/>
+      <c r="H978" s="60">
+        <v>4</v>
+      </c>
+      <c r="I978" s="60" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="979" spans="1:9">
+      <c r="A979" s="60">
+        <v>10540041</v>
+      </c>
+      <c r="B979" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C979" s="60">
+        <v>41</v>
+      </c>
+      <c r="D979" s="60"/>
+      <c r="E979" s="60"/>
+      <c r="F979" s="60"/>
+      <c r="G979" s="60"/>
+      <c r="H979" s="60">
+        <v>4</v>
+      </c>
+      <c r="I979" s="60" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="980" spans="1:9">
+      <c r="A980" s="60">
+        <v>10540042</v>
+      </c>
+      <c r="B980" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C980" s="60">
+        <v>42</v>
+      </c>
+      <c r="D980" s="60"/>
+      <c r="E980" s="60"/>
+      <c r="F980" s="60"/>
+      <c r="G980" s="60"/>
+      <c r="H980" s="60">
+        <v>4</v>
+      </c>
+      <c r="I980" s="60" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="981" spans="1:9">
+      <c r="A981" s="60">
+        <v>10540043</v>
+      </c>
+      <c r="B981" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C981" s="60">
+        <v>43</v>
+      </c>
+      <c r="D981" s="60"/>
+      <c r="E981" s="60"/>
+      <c r="F981" s="60"/>
+      <c r="G981" s="60"/>
+      <c r="H981" s="60">
+        <v>4</v>
+      </c>
+      <c r="I981" s="60" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="982" spans="1:9">
+      <c r="A982" s="60">
+        <v>10540044</v>
+      </c>
+      <c r="B982" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C982" s="60">
+        <v>44</v>
+      </c>
+      <c r="D982" s="60"/>
+      <c r="E982" s="60"/>
+      <c r="F982" s="60"/>
+      <c r="G982" s="60"/>
+      <c r="H982" s="60">
+        <v>4</v>
+      </c>
+      <c r="I982" s="60" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="983" spans="1:9">
+      <c r="A983" s="60">
+        <v>10540045</v>
+      </c>
+      <c r="B983" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C983" s="60">
+        <v>45</v>
+      </c>
+      <c r="D983" s="60"/>
+      <c r="E983" s="60"/>
+      <c r="F983" s="60"/>
+      <c r="G983" s="60"/>
+      <c r="H983" s="60">
+        <v>4</v>
+      </c>
+      <c r="I983" s="60" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="984" spans="1:9">
+      <c r="A984" s="60">
+        <v>10540046</v>
+      </c>
+      <c r="B984" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C984" s="60">
+        <v>46</v>
+      </c>
+      <c r="D984" s="60"/>
+      <c r="E984" s="60"/>
+      <c r="F984" s="60"/>
+      <c r="G984" s="60"/>
+      <c r="H984" s="60">
+        <v>4</v>
+      </c>
+      <c r="I984" s="60" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="985" spans="1:9">
+      <c r="A985" s="60">
+        <v>10540047</v>
+      </c>
+      <c r="B985" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C985" s="60">
+        <v>47</v>
+      </c>
+      <c r="D985" s="60"/>
+      <c r="E985" s="60"/>
+      <c r="F985" s="60"/>
+      <c r="G985" s="60"/>
+      <c r="H985" s="60">
+        <v>4</v>
+      </c>
+      <c r="I985" s="60" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="986" spans="1:9">
+      <c r="A986" s="60">
+        <v>10540048</v>
+      </c>
+      <c r="B986" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C986" s="60">
+        <v>48</v>
+      </c>
+      <c r="D986" s="60"/>
+      <c r="E986" s="60"/>
+      <c r="F986" s="60"/>
+      <c r="G986" s="60"/>
+      <c r="H986" s="60">
+        <v>4</v>
+      </c>
+      <c r="I986" s="60" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="987" spans="1:9">
+      <c r="A987" s="60">
+        <v>10540049</v>
+      </c>
+      <c r="B987" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C987" s="60">
+        <v>49</v>
+      </c>
+      <c r="D987" s="60"/>
+      <c r="E987" s="60"/>
+      <c r="F987" s="60"/>
+      <c r="G987" s="60"/>
+      <c r="H987" s="60">
+        <v>4</v>
+      </c>
+      <c r="I987" s="60" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="988" spans="1:9">
+      <c r="A988" s="60">
+        <v>10540050</v>
+      </c>
+      <c r="B988" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C988" s="60">
+        <v>50</v>
+      </c>
+      <c r="D988" s="60"/>
+      <c r="E988" s="60"/>
+      <c r="F988" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G988" s="60"/>
+      <c r="H988" s="60"/>
+      <c r="I988" s="60" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="989" spans="1:9">
+      <c r="A989" s="60">
+        <v>10540051</v>
+      </c>
+      <c r="B989" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C989" s="60">
+        <v>51</v>
+      </c>
+      <c r="D989" s="60"/>
+      <c r="E989" s="60"/>
+      <c r="F989" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G989" s="60"/>
+      <c r="H989" s="60"/>
+      <c r="I989" s="60" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="990" spans="1:9">
+      <c r="A990" s="60">
+        <v>10540052</v>
+      </c>
+      <c r="B990" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C990" s="60">
+        <v>52</v>
+      </c>
+      <c r="D990" s="60"/>
+      <c r="E990" s="60"/>
+      <c r="F990" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G990" s="60"/>
+      <c r="H990" s="60"/>
+      <c r="I990" s="60" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="991" spans="1:9">
+      <c r="A991" s="60">
+        <v>10540053</v>
+      </c>
+      <c r="B991" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C991" s="60">
+        <v>53</v>
+      </c>
+      <c r="D991" s="60"/>
+      <c r="E991" s="60"/>
+      <c r="F991" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G991" s="60"/>
+      <c r="H991" s="60"/>
+      <c r="I991" s="60" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="992" spans="1:9">
+      <c r="A992" s="60">
+        <v>10540054</v>
+      </c>
+      <c r="B992" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C992" s="60">
+        <v>54</v>
+      </c>
+      <c r="D992" s="60"/>
+      <c r="E992" s="60"/>
+      <c r="F992" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G992" s="60"/>
+      <c r="H992" s="60"/>
+      <c r="I992" s="60" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="993" spans="1:9">
+      <c r="A993" s="60">
+        <v>10540055</v>
+      </c>
+      <c r="B993" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C993" s="60">
+        <v>55</v>
+      </c>
+      <c r="D993" s="60"/>
+      <c r="E993" s="60"/>
+      <c r="F993" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G993" s="60"/>
+      <c r="H993" s="60"/>
+      <c r="I993" s="60" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="994" spans="1:9">
+      <c r="A994" s="60">
+        <v>10540056</v>
+      </c>
+      <c r="B994" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C994" s="60">
+        <v>56</v>
+      </c>
+      <c r="D994" s="60"/>
+      <c r="E994" s="60"/>
+      <c r="F994" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G994" s="60"/>
+      <c r="H994" s="60"/>
+      <c r="I994" s="60" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="995" spans="1:9">
+      <c r="A995" s="60">
+        <v>10540057</v>
+      </c>
+      <c r="B995" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C995" s="60">
+        <v>57</v>
+      </c>
+      <c r="D995" s="60"/>
+      <c r="E995" s="60"/>
+      <c r="F995" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G995" s="60"/>
+      <c r="H995" s="60"/>
+      <c r="I995" s="60" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="996" spans="1:9">
+      <c r="A996" s="60">
+        <v>10540058</v>
+      </c>
+      <c r="B996" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C996" s="60">
+        <v>58</v>
+      </c>
+      <c r="D996" s="60"/>
+      <c r="E996" s="60"/>
+      <c r="F996" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G996" s="60"/>
+      <c r="H996" s="60"/>
+      <c r="I996" s="60" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="997" spans="1:9">
+      <c r="A997" s="60">
+        <v>10540059</v>
+      </c>
+      <c r="B997" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C997" s="60">
+        <v>59</v>
+      </c>
+      <c r="D997" s="60"/>
+      <c r="E997" s="60"/>
+      <c r="F997" s="60" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G997" s="60"/>
+      <c r="H997" s="60"/>
+      <c r="I997" s="60" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="998" spans="1:9">
+      <c r="A998" s="60">
+        <v>10540060</v>
+      </c>
+      <c r="B998" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C998" s="60">
+        <v>60</v>
+      </c>
+      <c r="D998" s="60"/>
+      <c r="E998" s="60"/>
+      <c r="F998" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G998" s="60"/>
+      <c r="H998" s="60">
+        <v>2</v>
+      </c>
+      <c r="I998" s="60" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="999" spans="1:9">
+      <c r="A999" s="60">
+        <v>10540061</v>
+      </c>
+      <c r="B999" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C999" s="60">
+        <v>61</v>
+      </c>
+      <c r="D999" s="60"/>
+      <c r="E999" s="60"/>
+      <c r="F999" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G999" s="60"/>
+      <c r="H999" s="60">
+        <v>2</v>
+      </c>
+      <c r="I999" s="60" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:9">
+      <c r="A1000" s="60">
+        <v>10540062</v>
+      </c>
+      <c r="B1000" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1000" s="60">
+        <v>62</v>
+      </c>
+      <c r="D1000" s="60"/>
+      <c r="E1000" s="60"/>
+      <c r="F1000" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1000" s="60"/>
+      <c r="H1000" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1000" s="60" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:9">
+      <c r="A1001" s="60">
+        <v>10540063</v>
+      </c>
+      <c r="B1001" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1001" s="60">
+        <v>63</v>
+      </c>
+      <c r="D1001" s="60"/>
+      <c r="E1001" s="60"/>
+      <c r="F1001" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1001" s="60"/>
+      <c r="H1001" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1001" s="60" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:9">
+      <c r="A1002" s="60">
+        <v>10540064</v>
+      </c>
+      <c r="B1002" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1002" s="60">
+        <v>64</v>
+      </c>
+      <c r="D1002" s="60"/>
+      <c r="E1002" s="60"/>
+      <c r="F1002" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1002" s="60"/>
+      <c r="H1002" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1002" s="60" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:9">
+      <c r="A1003" s="60">
+        <v>10540065</v>
+      </c>
+      <c r="B1003" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1003" s="60">
+        <v>65</v>
+      </c>
+      <c r="D1003" s="60"/>
+      <c r="E1003" s="60"/>
+      <c r="F1003" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1003" s="60"/>
+      <c r="H1003" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1003" s="60" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:9">
+      <c r="A1004" s="60">
+        <v>10540066</v>
+      </c>
+      <c r="B1004" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1004" s="60">
+        <v>66</v>
+      </c>
+      <c r="D1004" s="60"/>
+      <c r="E1004" s="60"/>
+      <c r="F1004" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1004" s="60"/>
+      <c r="H1004" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1004" s="60" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:9">
+      <c r="A1005" s="60">
+        <v>10540067</v>
+      </c>
+      <c r="B1005" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1005" s="60">
+        <v>67</v>
+      </c>
+      <c r="D1005" s="60"/>
+      <c r="E1005" s="60"/>
+      <c r="F1005" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1005" s="60"/>
+      <c r="H1005" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1005" s="60" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:9">
+      <c r="A1006" s="60">
+        <v>10540068</v>
+      </c>
+      <c r="B1006" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1006" s="60">
+        <v>68</v>
+      </c>
+      <c r="D1006" s="60"/>
+      <c r="E1006" s="60"/>
+      <c r="F1006" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1006" s="60"/>
+      <c r="H1006" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1006" s="60" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:9">
+      <c r="A1007" s="60">
+        <v>10540069</v>
+      </c>
+      <c r="B1007" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1007" s="60">
+        <v>69</v>
+      </c>
+      <c r="D1007" s="60"/>
+      <c r="E1007" s="60"/>
+      <c r="F1007" s="60" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1007" s="60"/>
+      <c r="H1007" s="60">
+        <v>2</v>
+      </c>
+      <c r="I1007" s="60" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:9">
+      <c r="A1008" s="60">
+        <v>10540070</v>
+      </c>
+      <c r="B1008" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1008" s="60">
+        <v>70</v>
+      </c>
+      <c r="D1008" s="60"/>
+      <c r="E1008" s="60"/>
+      <c r="F1008" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1008" s="60"/>
+      <c r="H1008" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1008" s="60" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:9">
+      <c r="A1009" s="60">
+        <v>10540071</v>
+      </c>
+      <c r="B1009" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1009" s="60">
+        <v>71</v>
+      </c>
+      <c r="D1009" s="60"/>
+      <c r="E1009" s="60"/>
+      <c r="F1009" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1009" s="60"/>
+      <c r="H1009" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1009" s="60" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:9">
+      <c r="A1010" s="60">
+        <v>10540072</v>
+      </c>
+      <c r="B1010" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1010" s="60">
+        <v>72</v>
+      </c>
+      <c r="D1010" s="60"/>
+      <c r="E1010" s="60"/>
+      <c r="F1010" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1010" s="60"/>
+      <c r="H1010" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1010" s="60" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:9">
+      <c r="A1011" s="60">
+        <v>10540073</v>
+      </c>
+      <c r="B1011" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1011" s="60">
+        <v>73</v>
+      </c>
+      <c r="D1011" s="60"/>
+      <c r="E1011" s="60"/>
+      <c r="F1011" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1011" s="60"/>
+      <c r="H1011" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1011" s="60" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:9">
+      <c r="A1012" s="60">
+        <v>10540074</v>
+      </c>
+      <c r="B1012" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1012" s="60">
+        <v>74</v>
+      </c>
+      <c r="D1012" s="60"/>
+      <c r="E1012" s="60"/>
+      <c r="F1012" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1012" s="60"/>
+      <c r="H1012" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1012" s="60" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:9">
+      <c r="A1013" s="60">
+        <v>10540075</v>
+      </c>
+      <c r="B1013" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1013" s="60">
+        <v>75</v>
+      </c>
+      <c r="D1013" s="60"/>
+      <c r="E1013" s="60"/>
+      <c r="F1013" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1013" s="60"/>
+      <c r="H1013" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1013" s="60" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:9">
+      <c r="A1014" s="60">
+        <v>10540076</v>
+      </c>
+      <c r="B1014" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1014" s="60">
+        <v>76</v>
+      </c>
+      <c r="D1014" s="60"/>
+      <c r="E1014" s="60"/>
+      <c r="F1014" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1014" s="60"/>
+      <c r="H1014" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1014" s="60" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:9">
+      <c r="A1015" s="60">
+        <v>10540077</v>
+      </c>
+      <c r="B1015" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1015" s="60">
+        <v>77</v>
+      </c>
+      <c r="D1015" s="60"/>
+      <c r="E1015" s="60"/>
+      <c r="F1015" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1015" s="60"/>
+      <c r="H1015" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1015" s="60" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:9">
+      <c r="A1016" s="60">
+        <v>10540078</v>
+      </c>
+      <c r="B1016" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1016" s="60">
+        <v>78</v>
+      </c>
+      <c r="D1016" s="60"/>
+      <c r="E1016" s="60"/>
+      <c r="F1016" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1016" s="60"/>
+      <c r="H1016" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1016" s="60" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:9">
+      <c r="A1017" s="60">
+        <v>10540079</v>
+      </c>
+      <c r="B1017" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1017" s="60">
+        <v>79</v>
+      </c>
+      <c r="D1017" s="60"/>
+      <c r="E1017" s="60"/>
+      <c r="F1017" s="60" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G1017" s="60"/>
+      <c r="H1017" s="60">
+        <v>3</v>
+      </c>
+      <c r="I1017" s="60" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:9">
+      <c r="A1018" s="60">
+        <v>10540080</v>
+      </c>
+      <c r="B1018" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1018" s="60">
+        <v>80</v>
+      </c>
+      <c r="D1018" s="60"/>
+      <c r="E1018" s="60"/>
+      <c r="F1018" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1018" s="60"/>
+      <c r="H1018" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1018" s="60" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:9">
+      <c r="A1019" s="60">
+        <v>10540081</v>
+      </c>
+      <c r="B1019" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1019" s="60">
+        <v>81</v>
+      </c>
+      <c r="D1019" s="60"/>
+      <c r="E1019" s="60"/>
+      <c r="F1019" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1019" s="60"/>
+      <c r="H1019" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1019" s="60" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:9">
+      <c r="A1020" s="60">
+        <v>10540082</v>
+      </c>
+      <c r="B1020" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1020" s="60">
+        <v>82</v>
+      </c>
+      <c r="D1020" s="60"/>
+      <c r="E1020" s="60"/>
+      <c r="F1020" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1020" s="60"/>
+      <c r="H1020" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1020" s="60" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:9">
+      <c r="A1021" s="60">
+        <v>10540083</v>
+      </c>
+      <c r="B1021" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1021" s="60">
+        <v>83</v>
+      </c>
+      <c r="D1021" s="60"/>
+      <c r="E1021" s="60"/>
+      <c r="F1021" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1021" s="60"/>
+      <c r="H1021" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1021" s="60" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:9">
+      <c r="A1022" s="60">
+        <v>10540084</v>
+      </c>
+      <c r="B1022" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1022" s="60">
+        <v>84</v>
+      </c>
+      <c r="D1022" s="60"/>
+      <c r="E1022" s="60"/>
+      <c r="F1022" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1022" s="60"/>
+      <c r="H1022" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1022" s="60" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:9">
+      <c r="A1023" s="60">
+        <v>10540085</v>
+      </c>
+      <c r="B1023" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1023" s="60">
+        <v>85</v>
+      </c>
+      <c r="D1023" s="60"/>
+      <c r="E1023" s="60"/>
+      <c r="F1023" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1023" s="60"/>
+      <c r="H1023" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1023" s="60" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:9">
+      <c r="A1024" s="60">
+        <v>10540086</v>
+      </c>
+      <c r="B1024" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1024" s="60">
+        <v>86</v>
+      </c>
+      <c r="D1024" s="60"/>
+      <c r="E1024" s="60"/>
+      <c r="F1024" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1024" s="60"/>
+      <c r="H1024" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1024" s="60" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:9">
+      <c r="A1025" s="60">
+        <v>10540087</v>
+      </c>
+      <c r="B1025" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1025" s="60">
+        <v>87</v>
+      </c>
+      <c r="D1025" s="60"/>
+      <c r="E1025" s="60"/>
+      <c r="F1025" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1025" s="60"/>
+      <c r="H1025" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1025" s="60" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:9">
+      <c r="A1026" s="60">
+        <v>10540088</v>
+      </c>
+      <c r="B1026" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1026" s="60">
+        <v>88</v>
+      </c>
+      <c r="D1026" s="60"/>
+      <c r="E1026" s="60"/>
+      <c r="F1026" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1026" s="60"/>
+      <c r="H1026" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1026" s="60" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:9">
+      <c r="A1027" s="60">
+        <v>10540089</v>
+      </c>
+      <c r="B1027" s="60">
+        <v>105400</v>
+      </c>
+      <c r="C1027" s="60">
+        <v>89</v>
+      </c>
+      <c r="D1027" s="60"/>
+      <c r="E1027" s="60"/>
+      <c r="F1027" s="60" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1027" s="60"/>
+      <c r="H1027" s="60">
+        <v>4</v>
+      </c>
+      <c r="I1027" s="60" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:9">
+      <c r="A1028" s="28">
+        <v>10080001</v>
+      </c>
+      <c r="B1028" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1028" s="28">
+        <v>1</v>
+      </c>
+      <c r="D1028" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1028" s="28"/>
+      <c r="F1028" s="28"/>
+      <c r="G1028" s="28"/>
+      <c r="H1028" s="28"/>
+      <c r="I1028" s="62">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:9">
+      <c r="A1029" s="28">
+        <v>10080002</v>
+      </c>
+      <c r="B1029" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1029" s="28">
+        <v>2</v>
+      </c>
+      <c r="D1029" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1029" s="28"/>
+      <c r="F1029" s="28"/>
+      <c r="G1029" s="28"/>
+      <c r="H1029" s="28"/>
+      <c r="I1029" s="28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:9">
+      <c r="A1030" s="28">
+        <v>10080003</v>
+      </c>
+      <c r="B1030" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1030" s="28">
+        <v>3</v>
+      </c>
+      <c r="D1030" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1030" s="28"/>
+      <c r="F1030" s="28"/>
+      <c r="G1030" s="28"/>
+      <c r="H1030" s="28"/>
+      <c r="I1030" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:9">
+      <c r="A1031" s="28">
+        <v>10080004</v>
+      </c>
+      <c r="B1031" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1031" s="28">
+        <v>4</v>
+      </c>
+      <c r="D1031" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1031" s="28"/>
+      <c r="F1031" s="28"/>
+      <c r="G1031" s="28"/>
+      <c r="H1031" s="28"/>
+      <c r="I1031" s="28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:9">
+      <c r="A1032" s="28">
+        <v>10080005</v>
+      </c>
+      <c r="B1032" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1032" s="28">
+        <v>5</v>
+      </c>
+      <c r="D1032" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1032" s="28"/>
+      <c r="F1032" s="28"/>
+      <c r="G1032" s="28"/>
+      <c r="H1032" s="28"/>
+      <c r="I1032" s="28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:9">
+      <c r="A1033" s="28">
+        <v>10080006</v>
+      </c>
+      <c r="B1033" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1033" s="28">
+        <v>6</v>
+      </c>
+      <c r="D1033" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1033" s="28"/>
+      <c r="F1033" s="28"/>
+      <c r="G1033" s="28"/>
+      <c r="H1033" s="28"/>
+      <c r="I1033" s="28" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:9">
+      <c r="A1034" s="28">
+        <v>10080007</v>
+      </c>
+      <c r="B1034" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1034" s="28">
+        <v>7</v>
+      </c>
+      <c r="D1034" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1034" s="28"/>
+      <c r="F1034" s="28"/>
+      <c r="G1034" s="28"/>
+      <c r="H1034" s="28"/>
+      <c r="I1034" s="28" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:9">
+      <c r="A1035" s="28">
+        <v>10080008</v>
+      </c>
+      <c r="B1035" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1035" s="28">
+        <v>8</v>
+      </c>
+      <c r="D1035" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1035" s="28"/>
+      <c r="F1035" s="28"/>
+      <c r="G1035" s="28"/>
+      <c r="H1035" s="28"/>
+      <c r="I1035" s="28" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:9">
+      <c r="A1036" s="28">
+        <v>10080009</v>
+      </c>
+      <c r="B1036" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1036" s="28">
+        <v>9</v>
+      </c>
+      <c r="D1036" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1036" s="28"/>
+      <c r="F1036" s="28"/>
+      <c r="G1036" s="28"/>
+      <c r="H1036" s="28"/>
+      <c r="I1036" s="28" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:9">
+      <c r="A1037" s="28">
+        <v>10080010</v>
+      </c>
+      <c r="B1037" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1037" s="28">
+        <v>10</v>
+      </c>
+      <c r="D1037" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1037" s="28"/>
+      <c r="F1037" s="28"/>
+      <c r="G1037" s="28"/>
+      <c r="H1037" s="28"/>
+      <c r="I1037" s="28" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:9">
+      <c r="A1038" s="28">
+        <v>10080011</v>
+      </c>
+      <c r="B1038" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1038" s="28">
+        <v>11</v>
+      </c>
+      <c r="D1038" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1038" s="28"/>
+      <c r="F1038" s="28"/>
+      <c r="G1038" s="28"/>
+      <c r="H1038" s="28"/>
+      <c r="I1038" s="28" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:9">
+      <c r="A1039" s="28">
+        <v>10080012</v>
+      </c>
+      <c r="B1039" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1039" s="28">
+        <v>12</v>
+      </c>
+      <c r="D1039" s="28">
+        <v>1</v>
+      </c>
+      <c r="E1039" s="28"/>
+      <c r="F1039" s="28"/>
+      <c r="G1039" s="28"/>
+      <c r="H1039" s="28"/>
+      <c r="I1039" s="28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:9">
+      <c r="A1040" s="28">
+        <v>10080013</v>
+      </c>
+      <c r="B1040" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1040" s="28">
+        <v>13</v>
+      </c>
+      <c r="D1040" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1040" s="28"/>
+      <c r="F1040" s="28"/>
+      <c r="G1040" s="28"/>
+      <c r="H1040" s="28"/>
+      <c r="I1040" s="28" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:9">
+      <c r="A1041" s="28">
+        <v>10080014</v>
+      </c>
+      <c r="B1041" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1041" s="28">
+        <v>14</v>
+      </c>
+      <c r="D1041" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1041" s="28"/>
+      <c r="F1041" s="28"/>
+      <c r="G1041" s="28"/>
+      <c r="H1041" s="28"/>
+      <c r="I1041" s="63" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:9">
+      <c r="A1042" s="28">
+        <v>10080015</v>
+      </c>
+      <c r="B1042" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1042" s="28">
+        <v>15</v>
+      </c>
+      <c r="D1042" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1042" s="28"/>
+      <c r="F1042" s="28"/>
+      <c r="G1042" s="28"/>
+      <c r="H1042" s="28"/>
+      <c r="I1042" s="63" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:9">
+      <c r="A1043" s="28">
+        <v>10080016</v>
+      </c>
+      <c r="B1043" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1043" s="28">
+        <v>16</v>
+      </c>
+      <c r="D1043" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1043" s="28"/>
+      <c r="F1043" s="28"/>
+      <c r="G1043" s="28"/>
+      <c r="H1043" s="28"/>
+      <c r="I1043" s="63" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:9">
+      <c r="A1044" s="28">
+        <v>10080017</v>
+      </c>
+      <c r="B1044" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1044" s="28">
+        <v>17</v>
+      </c>
+      <c r="D1044" s="28">
+        <v>2</v>
+      </c>
+      <c r="E1044" s="28"/>
+      <c r="F1044" s="28"/>
+      <c r="G1044" s="28"/>
+      <c r="H1044" s="28"/>
+      <c r="I1044" s="63" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:9">
+      <c r="A1045" s="28">
+        <v>10080018</v>
+      </c>
+      <c r="B1045" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1045" s="28">
+        <v>18</v>
+      </c>
+      <c r="D1045" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1045" s="28"/>
+      <c r="F1045" s="28"/>
+      <c r="G1045" s="28"/>
+      <c r="H1045" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1045" s="45" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:9">
+      <c r="A1046" s="28">
+        <v>10080019</v>
+      </c>
+      <c r="B1046" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1046" s="28">
+        <v>19</v>
+      </c>
+      <c r="D1046" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1046" s="28"/>
+      <c r="F1046" s="28"/>
+      <c r="G1046" s="28"/>
+      <c r="H1046" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1046" s="45" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:9">
+      <c r="A1047" s="28">
+        <v>10080020</v>
+      </c>
+      <c r="B1047" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1047" s="28">
+        <v>20</v>
+      </c>
+      <c r="D1047" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1047" s="28"/>
+      <c r="F1047" s="28"/>
+      <c r="G1047" s="28"/>
+      <c r="H1047" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1047" s="45" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:9">
+      <c r="A1048" s="28">
+        <v>10080021</v>
+      </c>
+      <c r="B1048" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1048" s="28">
+        <v>21</v>
+      </c>
+      <c r="D1048" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1048" s="28"/>
+      <c r="F1048" s="28"/>
+      <c r="G1048" s="28"/>
+      <c r="H1048" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1048" s="45" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:9">
+      <c r="A1049" s="28">
+        <v>10080022</v>
+      </c>
+      <c r="B1049" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1049" s="28">
+        <v>22</v>
+      </c>
+      <c r="D1049" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1049" s="28"/>
+      <c r="F1049" s="28"/>
+      <c r="G1049" s="28"/>
+      <c r="H1049" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1049" s="45" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:9">
+      <c r="A1050" s="28">
+        <v>10080023</v>
+      </c>
+      <c r="B1050" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1050" s="28">
+        <v>23</v>
+      </c>
+      <c r="D1050" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1050" s="28"/>
+      <c r="F1050" s="28"/>
+      <c r="G1050" s="28"/>
+      <c r="H1050" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1050" s="45" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:9">
+      <c r="A1051" s="28">
+        <v>10080024</v>
+      </c>
+      <c r="B1051" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1051" s="28">
+        <v>24</v>
+      </c>
+      <c r="D1051" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1051" s="28"/>
+      <c r="F1051" s="28"/>
+      <c r="G1051" s="28"/>
+      <c r="H1051" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1051" s="45" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:9">
+      <c r="A1052" s="28">
+        <v>10080025</v>
+      </c>
+      <c r="B1052" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1052" s="28">
+        <v>25</v>
+      </c>
+      <c r="D1052" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1052" s="28"/>
+      <c r="F1052" s="28"/>
+      <c r="G1052" s="28"/>
+      <c r="H1052" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1052" s="45" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:9">
+      <c r="A1053" s="28">
+        <v>10080026</v>
+      </c>
+      <c r="B1053" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1053" s="28">
+        <v>26</v>
+      </c>
+      <c r="D1053" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1053" s="28"/>
+      <c r="F1053" s="28"/>
+      <c r="G1053" s="28"/>
+      <c r="H1053" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1053" s="45" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:9">
+      <c r="A1054" s="28">
+        <v>10080027</v>
+      </c>
+      <c r="B1054" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1054" s="28">
+        <v>27</v>
+      </c>
+      <c r="D1054" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1054" s="28"/>
+      <c r="F1054" s="28"/>
+      <c r="G1054" s="28"/>
+      <c r="H1054" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1054" s="45" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:9">
+      <c r="A1055" s="28">
+        <v>10080028</v>
+      </c>
+      <c r="B1055" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1055" s="28">
+        <v>28</v>
+      </c>
+      <c r="D1055" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1055" s="28"/>
+      <c r="F1055" s="28"/>
+      <c r="G1055" s="28"/>
+      <c r="H1055" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1055" s="45" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:9">
+      <c r="A1056" s="28">
+        <v>10080029</v>
+      </c>
+      <c r="B1056" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1056" s="28">
+        <v>29</v>
+      </c>
+      <c r="D1056" s="28">
+        <v>1</v>
+      </c>
+      <c r="E1056" s="28"/>
+      <c r="F1056" s="28"/>
+      <c r="G1056" s="28"/>
+      <c r="H1056" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1056" s="45" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:9">
+      <c r="A1057" s="28">
+        <v>10080030</v>
+      </c>
+      <c r="B1057" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1057" s="28">
+        <v>30</v>
+      </c>
+      <c r="D1057" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1057" s="28"/>
+      <c r="F1057" s="28"/>
+      <c r="G1057" s="28"/>
+      <c r="H1057" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1057" s="45" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:9">
+      <c r="A1058" s="28">
+        <v>10080031</v>
+      </c>
+      <c r="B1058" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1058" s="28">
+        <v>31</v>
+      </c>
+      <c r="D1058" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1058" s="28"/>
+      <c r="F1058" s="28"/>
+      <c r="G1058" s="28"/>
+      <c r="H1058" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1058" s="45" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:9">
+      <c r="A1059" s="28">
+        <v>10080032</v>
+      </c>
+      <c r="B1059" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1059" s="28">
+        <v>32</v>
+      </c>
+      <c r="D1059" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1059" s="28"/>
+      <c r="F1059" s="28"/>
+      <c r="G1059" s="28"/>
+      <c r="H1059" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1059" s="45" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:9">
+      <c r="A1060" s="28">
+        <v>10080033</v>
+      </c>
+      <c r="B1060" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1060" s="28">
+        <v>33</v>
+      </c>
+      <c r="D1060" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1060" s="28"/>
+      <c r="F1060" s="28"/>
+      <c r="G1060" s="28"/>
+      <c r="H1060" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1060" s="45" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:9">
+      <c r="A1061" s="28">
+        <v>10080034</v>
+      </c>
+      <c r="B1061" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1061" s="28">
+        <v>34</v>
+      </c>
+      <c r="D1061" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1061" s="28"/>
+      <c r="F1061" s="28"/>
+      <c r="G1061" s="28"/>
+      <c r="H1061" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1061" s="45" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:9">
+      <c r="A1062" s="28">
+        <v>10080035</v>
+      </c>
+      <c r="B1062" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1062" s="28">
+        <v>35</v>
+      </c>
+      <c r="D1062" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1062" s="28"/>
+      <c r="F1062" s="28"/>
+      <c r="G1062" s="28"/>
+      <c r="H1062" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1062" s="45" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:9">
+      <c r="A1063" s="28">
+        <v>10080036</v>
+      </c>
+      <c r="B1063" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1063" s="28">
+        <v>36</v>
+      </c>
+      <c r="D1063" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1063" s="28"/>
+      <c r="F1063" s="28"/>
+      <c r="G1063" s="28"/>
+      <c r="H1063" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1063" s="45" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:9">
+      <c r="A1064" s="28">
+        <v>10080037</v>
+      </c>
+      <c r="B1064" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1064" s="28">
+        <v>37</v>
+      </c>
+      <c r="D1064" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1064" s="28"/>
+      <c r="F1064" s="28"/>
+      <c r="G1064" s="28"/>
+      <c r="H1064" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1064" s="45" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:9">
+      <c r="A1065" s="28">
+        <v>10080038</v>
+      </c>
+      <c r="B1065" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1065" s="28">
+        <v>38</v>
+      </c>
+      <c r="D1065" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1065" s="28"/>
+      <c r="F1065" s="28"/>
+      <c r="G1065" s="28"/>
+      <c r="H1065" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1065" s="45" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:9">
+      <c r="A1066" s="28">
+        <v>10080039</v>
+      </c>
+      <c r="B1066" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1066" s="28">
+        <v>39</v>
+      </c>
+      <c r="D1066" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1066" s="28"/>
+      <c r="F1066" s="28"/>
+      <c r="G1066" s="28"/>
+      <c r="H1066" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1066" s="45" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:9">
+      <c r="A1067" s="28">
+        <v>10080040</v>
+      </c>
+      <c r="B1067" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1067" s="28">
+        <v>40</v>
+      </c>
+      <c r="D1067" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1067" s="28"/>
+      <c r="F1067" s="28"/>
+      <c r="G1067" s="28"/>
+      <c r="H1067" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1067" s="45" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:9">
+      <c r="A1068" s="28">
+        <v>10080041</v>
+      </c>
+      <c r="B1068" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1068" s="28">
+        <v>41</v>
+      </c>
+      <c r="D1068" s="28">
+        <v>1</v>
+      </c>
+      <c r="E1068" s="28"/>
+      <c r="F1068" s="28"/>
+      <c r="G1068" s="28"/>
+      <c r="H1068" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1068" s="45" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:9">
+      <c r="A1069" s="28">
+        <v>10080042</v>
+      </c>
+      <c r="B1069" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1069" s="28">
+        <v>42</v>
+      </c>
+      <c r="D1069" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1069" s="28"/>
+      <c r="F1069" s="28"/>
+      <c r="G1069" s="28"/>
+      <c r="H1069" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1069" s="45" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:9">
+      <c r="A1070" s="28">
+        <v>10080043</v>
+      </c>
+      <c r="B1070" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1070" s="28">
+        <v>43</v>
+      </c>
+      <c r="D1070" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1070" s="28"/>
+      <c r="F1070" s="28"/>
+      <c r="G1070" s="28"/>
+      <c r="H1070" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1070" s="45" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:9">
+      <c r="A1071" s="28">
+        <v>10080044</v>
+      </c>
+      <c r="B1071" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1071" s="28">
+        <v>44</v>
+      </c>
+      <c r="D1071" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1071" s="28"/>
+      <c r="F1071" s="28"/>
+      <c r="G1071" s="28"/>
+      <c r="H1071" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1071" s="45" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:9">
+      <c r="A1072" s="28">
+        <v>10080045</v>
+      </c>
+      <c r="B1072" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1072" s="28">
+        <v>45</v>
+      </c>
+      <c r="D1072" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1072" s="28"/>
+      <c r="F1072" s="28"/>
+      <c r="G1072" s="28"/>
+      <c r="H1072" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1072" s="45" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:9">
+      <c r="A1073" s="28">
+        <v>10080046</v>
+      </c>
+      <c r="B1073" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1073" s="28">
+        <v>46</v>
+      </c>
+      <c r="D1073" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1073" s="28"/>
+      <c r="F1073" s="28"/>
+      <c r="G1073" s="28"/>
+      <c r="H1073" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1073" s="45" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:9">
+      <c r="A1074" s="28">
+        <v>10080047</v>
+      </c>
+      <c r="B1074" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1074" s="28">
+        <v>47</v>
+      </c>
+      <c r="D1074" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1074" s="28"/>
+      <c r="F1074" s="28"/>
+      <c r="G1074" s="28"/>
+      <c r="H1074" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1074" s="45" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:9">
+      <c r="A1075" s="28">
+        <v>10080048</v>
+      </c>
+      <c r="B1075" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1075" s="28">
+        <v>48</v>
+      </c>
+      <c r="D1075" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1075" s="28"/>
+      <c r="F1075" s="28"/>
+      <c r="G1075" s="28"/>
+      <c r="H1075" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1075" s="45" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:9">
+      <c r="A1076" s="28">
+        <v>10080049</v>
+      </c>
+      <c r="B1076" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1076" s="28">
+        <v>49</v>
+      </c>
+      <c r="D1076" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1076" s="28"/>
+      <c r="F1076" s="28"/>
+      <c r="G1076" s="28"/>
+      <c r="H1076" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1076" s="45" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:9">
+      <c r="A1077" s="28">
+        <v>10080050</v>
+      </c>
+      <c r="B1077" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1077" s="28">
+        <v>50</v>
+      </c>
+      <c r="D1077" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1077" s="28"/>
+      <c r="F1077" s="28"/>
+      <c r="G1077" s="28"/>
+      <c r="H1077" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1077" s="45" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:9">
+      <c r="A1078" s="28">
+        <v>10080051</v>
+      </c>
+      <c r="B1078" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1078" s="28">
+        <v>51</v>
+      </c>
+      <c r="D1078" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1078" s="28"/>
+      <c r="F1078" s="28"/>
+      <c r="G1078" s="28"/>
+      <c r="H1078" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1078" s="45" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:9">
+      <c r="A1079" s="28">
+        <v>10080052</v>
+      </c>
+      <c r="B1079" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1079" s="28">
+        <v>52</v>
+      </c>
+      <c r="D1079" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1079" s="28"/>
+      <c r="F1079" s="28"/>
+      <c r="G1079" s="28"/>
+      <c r="H1079" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1079" s="45" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:9">
+      <c r="A1080" s="28">
+        <v>10080053</v>
+      </c>
+      <c r="B1080" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1080" s="28">
+        <v>53</v>
+      </c>
+      <c r="D1080" s="28">
+        <v>1</v>
+      </c>
+      <c r="E1080" s="28"/>
+      <c r="F1080" s="28"/>
+      <c r="G1080" s="28"/>
+      <c r="H1080" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1080" s="45" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:9">
+      <c r="A1081" s="28">
+        <v>10080054</v>
+      </c>
+      <c r="B1081" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1081" s="28">
+        <v>54</v>
+      </c>
+      <c r="D1081" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1081" s="28"/>
+      <c r="F1081" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1081" s="28"/>
+      <c r="H1081" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1081" s="45" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:9">
+      <c r="A1082" s="28">
+        <v>10080055</v>
+      </c>
+      <c r="B1082" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1082" s="28">
+        <v>55</v>
+      </c>
+      <c r="D1082" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1082" s="28"/>
+      <c r="F1082" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1082" s="28"/>
+      <c r="H1082" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1082" s="45" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:9">
+      <c r="A1083" s="28">
+        <v>10080056</v>
+      </c>
+      <c r="B1083" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1083" s="28">
+        <v>56</v>
+      </c>
+      <c r="D1083" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1083" s="28"/>
+      <c r="F1083" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1083" s="28"/>
+      <c r="H1083" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1083" s="45" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:9">
+      <c r="A1084" s="28">
+        <v>10080057</v>
+      </c>
+      <c r="B1084" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1084" s="28">
+        <v>57</v>
+      </c>
+      <c r="D1084" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1084" s="28"/>
+      <c r="F1084" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1084" s="28"/>
+      <c r="H1084" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1084" s="45" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:9">
+      <c r="A1085" s="28">
+        <v>10080058</v>
+      </c>
+      <c r="B1085" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1085" s="28">
+        <v>58</v>
+      </c>
+      <c r="D1085" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1085" s="28"/>
+      <c r="F1085" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1085" s="28"/>
+      <c r="H1085" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1085" s="45" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:9">
+      <c r="A1086" s="28">
+        <v>10080059</v>
+      </c>
+      <c r="B1086" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1086" s="28">
+        <v>59</v>
+      </c>
+      <c r="D1086" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1086" s="28"/>
+      <c r="F1086" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1086" s="28"/>
+      <c r="H1086" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1086" s="45" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:9">
+      <c r="A1087" s="28">
+        <v>10080060</v>
+      </c>
+      <c r="B1087" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1087" s="28">
+        <v>60</v>
+      </c>
+      <c r="D1087" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1087" s="28"/>
+      <c r="F1087" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1087" s="28"/>
+      <c r="H1087" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1087" s="45" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:9">
+      <c r="A1088" s="28">
+        <v>10080061</v>
+      </c>
+      <c r="B1088" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1088" s="28">
+        <v>61</v>
+      </c>
+      <c r="D1088" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1088" s="28"/>
+      <c r="F1088" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1088" s="28"/>
+      <c r="H1088" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1088" s="45" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:9">
+      <c r="A1089" s="28">
+        <v>10080062</v>
+      </c>
+      <c r="B1089" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1089" s="28">
+        <v>62</v>
+      </c>
+      <c r="D1089" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1089" s="28"/>
+      <c r="F1089" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1089" s="28"/>
+      <c r="H1089" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1089" s="45" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:9">
+      <c r="A1090" s="28">
+        <v>10080063</v>
+      </c>
+      <c r="B1090" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1090" s="28">
+        <v>63</v>
+      </c>
+      <c r="D1090" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1090" s="28"/>
+      <c r="F1090" s="28" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G1090" s="28"/>
+      <c r="H1090" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1090" s="45" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:9">
+      <c r="A1091" s="28">
+        <v>10080064</v>
+      </c>
+      <c r="B1091" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1091" s="28">
+        <v>64</v>
+      </c>
+      <c r="D1091" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1091" s="28"/>
+      <c r="F1091" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1091" s="28"/>
+      <c r="H1091" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1091" s="45" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:9">
+      <c r="A1092" s="28">
+        <v>10080065</v>
+      </c>
+      <c r="B1092" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1092" s="28">
+        <v>65</v>
+      </c>
+      <c r="D1092" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1092" s="28"/>
+      <c r="F1092" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1092" s="28"/>
+      <c r="H1092" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1092" s="45" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:9">
+      <c r="A1093" s="28">
+        <v>10080066</v>
+      </c>
+      <c r="B1093" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1093" s="28">
+        <v>66</v>
+      </c>
+      <c r="D1093" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1093" s="28"/>
+      <c r="F1093" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1093" s="28"/>
+      <c r="H1093" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1093" s="45" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:9">
+      <c r="A1094" s="28">
+        <v>10080067</v>
+      </c>
+      <c r="B1094" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1094" s="28">
+        <v>67</v>
+      </c>
+      <c r="D1094" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1094" s="28"/>
+      <c r="F1094" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1094" s="28"/>
+      <c r="H1094" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1094" s="45" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:9">
+      <c r="A1095" s="28">
+        <v>10080068</v>
+      </c>
+      <c r="B1095" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1095" s="28">
+        <v>68</v>
+      </c>
+      <c r="D1095" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1095" s="28"/>
+      <c r="F1095" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1095" s="28"/>
+      <c r="H1095" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1095" s="45" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:9">
+      <c r="A1096" s="28">
+        <v>10080069</v>
+      </c>
+      <c r="B1096" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1096" s="28">
+        <v>69</v>
+      </c>
+      <c r="D1096" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1096" s="28"/>
+      <c r="F1096" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1096" s="28"/>
+      <c r="H1096" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1096" s="45" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:9">
+      <c r="A1097" s="28">
+        <v>10080070</v>
+      </c>
+      <c r="B1097" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1097" s="28">
+        <v>70</v>
+      </c>
+      <c r="D1097" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1097" s="28"/>
+      <c r="F1097" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1097" s="28"/>
+      <c r="H1097" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1097" s="45" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:9">
+      <c r="A1098" s="28">
+        <v>10080071</v>
+      </c>
+      <c r="B1098" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1098" s="28">
+        <v>71</v>
+      </c>
+      <c r="D1098" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1098" s="28"/>
+      <c r="F1098" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1098" s="28"/>
+      <c r="H1098" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1098" s="45" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:9">
+      <c r="A1099" s="28">
+        <v>10080072</v>
+      </c>
+      <c r="B1099" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1099" s="28">
+        <v>72</v>
+      </c>
+      <c r="D1099" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1099" s="28"/>
+      <c r="F1099" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1099" s="28"/>
+      <c r="H1099" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1099" s="45" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:9">
+      <c r="A1100" s="28">
+        <v>10080073</v>
+      </c>
+      <c r="B1100" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1100" s="28">
+        <v>73</v>
+      </c>
+      <c r="D1100" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1100" s="28"/>
+      <c r="F1100" s="28" t="s">
+        <v>1496</v>
+      </c>
+      <c r="G1100" s="28"/>
+      <c r="H1100" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1100" s="45" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:9">
+      <c r="A1101" s="28">
+        <v>10080074</v>
+      </c>
+      <c r="B1101" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1101" s="28">
+        <v>74</v>
+      </c>
+      <c r="D1101" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1101" s="28"/>
+      <c r="F1101" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1101" s="28"/>
+      <c r="H1101" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1101" s="45" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:9">
+      <c r="A1102" s="28">
+        <v>10080075</v>
+      </c>
+      <c r="B1102" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1102" s="28">
+        <v>75</v>
+      </c>
+      <c r="D1102" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1102" s="28"/>
+      <c r="F1102" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1102" s="28"/>
+      <c r="H1102" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1102" s="45" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:9">
+      <c r="A1103" s="28">
+        <v>10080076</v>
+      </c>
+      <c r="B1103" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1103" s="28">
+        <v>76</v>
+      </c>
+      <c r="D1103" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1103" s="28"/>
+      <c r="F1103" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1103" s="28"/>
+      <c r="H1103" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1103" s="45" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:9">
+      <c r="A1104" s="28">
+        <v>10080077</v>
+      </c>
+      <c r="B1104" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1104" s="28">
+        <v>77</v>
+      </c>
+      <c r="D1104" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1104" s="28"/>
+      <c r="F1104" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1104" s="28"/>
+      <c r="H1104" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1104" s="45" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:9">
+      <c r="A1105" s="28">
+        <v>10080078</v>
+      </c>
+      <c r="B1105" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1105" s="28">
+        <v>78</v>
+      </c>
+      <c r="D1105" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1105" s="28"/>
+      <c r="F1105" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1105" s="28"/>
+      <c r="H1105" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1105" s="45" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:9">
+      <c r="A1106" s="28">
+        <v>10080079</v>
+      </c>
+      <c r="B1106" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1106" s="28">
+        <v>79</v>
+      </c>
+      <c r="D1106" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1106" s="28"/>
+      <c r="F1106" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1106" s="28"/>
+      <c r="H1106" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1106" s="45" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:9">
+      <c r="A1107" s="28">
+        <v>10080080</v>
+      </c>
+      <c r="B1107" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1107" s="28">
+        <v>80</v>
+      </c>
+      <c r="D1107" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1107" s="28"/>
+      <c r="F1107" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1107" s="28"/>
+      <c r="H1107" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1107" s="45" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:9">
+      <c r="A1108" s="28">
+        <v>10080081</v>
+      </c>
+      <c r="B1108" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1108" s="28">
+        <v>81</v>
+      </c>
+      <c r="D1108" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1108" s="28"/>
+      <c r="F1108" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1108" s="28"/>
+      <c r="H1108" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1108" s="45" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:9">
+      <c r="A1109" s="28">
+        <v>10080082</v>
+      </c>
+      <c r="B1109" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1109" s="28">
+        <v>82</v>
+      </c>
+      <c r="D1109" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1109" s="28"/>
+      <c r="F1109" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1109" s="28"/>
+      <c r="H1109" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1109" s="45" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:9">
+      <c r="A1110" s="28">
+        <v>10080083</v>
+      </c>
+      <c r="B1110" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1110" s="28">
+        <v>83</v>
+      </c>
+      <c r="D1110" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1110" s="28"/>
+      <c r="F1110" s="28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G1110" s="28"/>
+      <c r="H1110" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1110" s="45" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:9">
+      <c r="A1111" s="28">
+        <v>10080084</v>
+      </c>
+      <c r="B1111" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1111" s="28">
+        <v>84</v>
+      </c>
+      <c r="D1111" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1111" s="28"/>
+      <c r="F1111" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1111" s="28"/>
+      <c r="H1111" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1111" s="45" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:9">
+      <c r="A1112" s="28">
+        <v>10080085</v>
+      </c>
+      <c r="B1112" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1112" s="28">
+        <v>85</v>
+      </c>
+      <c r="D1112" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1112" s="28"/>
+      <c r="F1112" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1112" s="28"/>
+      <c r="H1112" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1112" s="45" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:9">
+      <c r="A1113" s="28">
+        <v>10080086</v>
+      </c>
+      <c r="B1113" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1113" s="28">
+        <v>86</v>
+      </c>
+      <c r="D1113" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1113" s="28"/>
+      <c r="F1113" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1113" s="28"/>
+      <c r="H1113" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1113" s="45" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:9">
+      <c r="A1114" s="28">
+        <v>10080087</v>
+      </c>
+      <c r="B1114" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1114" s="28">
+        <v>87</v>
+      </c>
+      <c r="D1114" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1114" s="28"/>
+      <c r="F1114" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1114" s="28"/>
+      <c r="H1114" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1114" s="45" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:9">
+      <c r="A1115" s="28">
+        <v>10080088</v>
+      </c>
+      <c r="B1115" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1115" s="28">
+        <v>88</v>
+      </c>
+      <c r="D1115" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1115" s="28"/>
+      <c r="F1115" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1115" s="28"/>
+      <c r="H1115" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1115" s="45" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:9">
+      <c r="A1116" s="28">
+        <v>10080089</v>
+      </c>
+      <c r="B1116" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1116" s="28">
+        <v>89</v>
+      </c>
+      <c r="D1116" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1116" s="28"/>
+      <c r="F1116" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1116" s="28"/>
+      <c r="H1116" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1116" s="45" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:9">
+      <c r="A1117" s="28">
+        <v>10080090</v>
+      </c>
+      <c r="B1117" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1117" s="28">
+        <v>90</v>
+      </c>
+      <c r="D1117" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1117" s="28"/>
+      <c r="F1117" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1117" s="28"/>
+      <c r="H1117" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1117" s="45" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:9">
+      <c r="A1118" s="28">
+        <v>10080091</v>
+      </c>
+      <c r="B1118" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1118" s="28">
+        <v>91</v>
+      </c>
+      <c r="D1118" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1118" s="28"/>
+      <c r="F1118" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1118" s="28"/>
+      <c r="H1118" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1118" s="45" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:9">
+      <c r="A1119" s="28">
+        <v>10080092</v>
+      </c>
+      <c r="B1119" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1119" s="28">
+        <v>92</v>
+      </c>
+      <c r="D1119" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1119" s="28"/>
+      <c r="F1119" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1119" s="28"/>
+      <c r="H1119" s="64">
+        <v>2</v>
+      </c>
+      <c r="I1119" s="45" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:9">
+      <c r="A1120" s="28">
+        <v>10080093</v>
+      </c>
+      <c r="B1120" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1120" s="28">
+        <v>93</v>
+      </c>
+      <c r="D1120" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1120" s="28"/>
+      <c r="F1120" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1120" s="28"/>
+      <c r="H1120" s="28">
+        <v>2</v>
+      </c>
+      <c r="I1120" s="45" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:9">
+      <c r="A1121" s="28">
+        <v>10080094</v>
+      </c>
+      <c r="B1121" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1121" s="28">
+        <v>94</v>
+      </c>
+      <c r="D1121" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1121" s="28"/>
+      <c r="F1121" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1121" s="28"/>
+      <c r="H1121" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1121" s="45" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:9">
+      <c r="A1122" s="28">
+        <v>10080095</v>
+      </c>
+      <c r="B1122" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1122" s="28">
+        <v>95</v>
+      </c>
+      <c r="D1122" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1122" s="28"/>
+      <c r="F1122" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1122" s="28"/>
+      <c r="H1122" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1122" s="45" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:9">
+      <c r="A1123" s="28">
+        <v>10080096</v>
+      </c>
+      <c r="B1123" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1123" s="28">
+        <v>96</v>
+      </c>
+      <c r="D1123" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1123" s="28"/>
+      <c r="F1123" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1123" s="28"/>
+      <c r="H1123" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1123" s="45" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:9">
+      <c r="A1124" s="28">
+        <v>10080097</v>
+      </c>
+      <c r="B1124" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1124" s="28">
+        <v>97</v>
+      </c>
+      <c r="D1124" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1124" s="28"/>
+      <c r="F1124" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1124" s="28"/>
+      <c r="H1124" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1124" s="45" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:9">
+      <c r="A1125" s="28">
+        <v>10080098</v>
+      </c>
+      <c r="B1125" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1125" s="28">
+        <v>98</v>
+      </c>
+      <c r="D1125" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1125" s="28"/>
+      <c r="F1125" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1125" s="28"/>
+      <c r="H1125" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1125" s="45" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:9">
+      <c r="A1126" s="28">
+        <v>10080099</v>
+      </c>
+      <c r="B1126" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1126" s="28">
+        <v>99</v>
+      </c>
+      <c r="D1126" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1126" s="28"/>
+      <c r="F1126" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1126" s="28"/>
+      <c r="H1126" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1126" s="45" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:9">
+      <c r="A1127" s="28">
+        <v>10080100</v>
+      </c>
+      <c r="B1127" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1127" s="28">
+        <v>100</v>
+      </c>
+      <c r="D1127" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1127" s="28"/>
+      <c r="F1127" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1127" s="28"/>
+      <c r="H1127" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1127" s="45" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:9">
+      <c r="A1128" s="28">
+        <v>10080101</v>
+      </c>
+      <c r="B1128" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1128" s="28">
+        <v>101</v>
+      </c>
+      <c r="D1128" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1128" s="28"/>
+      <c r="F1128" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1128" s="28"/>
+      <c r="H1128" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1128" s="45" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:9">
+      <c r="A1129" s="28">
+        <v>10080102</v>
+      </c>
+      <c r="B1129" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1129" s="28">
+        <v>102</v>
+      </c>
+      <c r="D1129" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1129" s="28"/>
+      <c r="F1129" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1129" s="28"/>
+      <c r="H1129" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1129" s="45" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:9">
+      <c r="A1130" s="28">
+        <v>10080103</v>
+      </c>
+      <c r="B1130" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1130" s="28">
+        <v>103</v>
+      </c>
+      <c r="D1130" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1130" s="28"/>
+      <c r="F1130" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1130" s="28"/>
+      <c r="H1130" s="28">
+        <v>3</v>
+      </c>
+      <c r="I1130" s="45" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:9">
+      <c r="A1131" s="28">
+        <v>10080104</v>
+      </c>
+      <c r="B1131" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1131" s="28">
+        <v>104</v>
+      </c>
+      <c r="D1131" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1131" s="28"/>
+      <c r="F1131" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1131" s="28"/>
+      <c r="H1131" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1131" s="45" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:9">
+      <c r="A1132" s="28">
+        <v>10080105</v>
+      </c>
+      <c r="B1132" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1132" s="28">
+        <v>105</v>
+      </c>
+      <c r="D1132" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1132" s="28"/>
+      <c r="F1132" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1132" s="28"/>
+      <c r="H1132" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1132" s="45" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:9">
+      <c r="A1133" s="28">
+        <v>10080106</v>
+      </c>
+      <c r="B1133" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1133" s="28">
+        <v>106</v>
+      </c>
+      <c r="D1133" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1133" s="28"/>
+      <c r="F1133" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1133" s="28"/>
+      <c r="H1133" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1133" s="45" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:9">
+      <c r="A1134" s="28">
+        <v>10080107</v>
+      </c>
+      <c r="B1134" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1134" s="28">
+        <v>107</v>
+      </c>
+      <c r="D1134" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1134" s="28"/>
+      <c r="F1134" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1134" s="28"/>
+      <c r="H1134" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1134" s="45" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:9">
+      <c r="A1135" s="28">
+        <v>10080108</v>
+      </c>
+      <c r="B1135" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1135" s="28">
+        <v>108</v>
+      </c>
+      <c r="D1135" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1135" s="28"/>
+      <c r="F1135" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1135" s="28"/>
+      <c r="H1135" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1135" s="45" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:9">
+      <c r="A1136" s="28">
+        <v>10080109</v>
+      </c>
+      <c r="B1136" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1136" s="28">
+        <v>109</v>
+      </c>
+      <c r="D1136" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1136" s="28"/>
+      <c r="F1136" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1136" s="28"/>
+      <c r="H1136" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1136" s="45" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:9">
+      <c r="A1137" s="28">
+        <v>10080110</v>
+      </c>
+      <c r="B1137" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1137" s="28">
+        <v>110</v>
+      </c>
+      <c r="D1137" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1137" s="28"/>
+      <c r="F1137" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1137" s="28"/>
+      <c r="H1137" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1137" s="45" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:9">
+      <c r="A1138" s="28">
+        <v>10080111</v>
+      </c>
+      <c r="B1138" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1138" s="28">
+        <v>111</v>
+      </c>
+      <c r="D1138" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1138" s="28"/>
+      <c r="F1138" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1138" s="28"/>
+      <c r="H1138" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1138" s="45" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:9">
+      <c r="A1139" s="28">
+        <v>10080112</v>
+      </c>
+      <c r="B1139" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1139" s="28">
+        <v>112</v>
+      </c>
+      <c r="D1139" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1139" s="28"/>
+      <c r="F1139" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1139" s="28"/>
+      <c r="H1139" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1139" s="45" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:9">
+      <c r="A1140" s="28">
+        <v>10080113</v>
+      </c>
+      <c r="B1140" s="28">
+        <v>100800</v>
+      </c>
+      <c r="C1140" s="28">
+        <v>113</v>
+      </c>
+      <c r="D1140" s="28">
+        <v>0</v>
+      </c>
+      <c r="E1140" s="28"/>
+      <c r="F1140" s="28" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G1140" s="28"/>
+      <c r="H1140" s="28">
+        <v>4</v>
+      </c>
+      <c r="I1140" s="45" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:9">
+      <c r="A1141" s="65">
+        <v>10530001</v>
+      </c>
+      <c r="B1141" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1141" s="65">
+        <v>1</v>
+      </c>
+      <c r="D1141" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1141" s="65"/>
+      <c r="F1141" s="65"/>
+      <c r="G1141" s="65"/>
+      <c r="H1141" s="65"/>
+      <c r="I1141" s="65" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:9">
+      <c r="A1142" s="65">
+        <v>10530002</v>
+      </c>
+      <c r="B1142" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1142" s="65">
+        <v>2</v>
+      </c>
+      <c r="D1142" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1142" s="65"/>
+      <c r="F1142" s="65"/>
+      <c r="G1142" s="65"/>
+      <c r="H1142" s="65"/>
+      <c r="I1142" s="65" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:9">
+      <c r="A1143" s="65">
+        <v>10530003</v>
+      </c>
+      <c r="B1143" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1143" s="65">
+        <v>3</v>
+      </c>
+      <c r="D1143" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1143" s="65"/>
+      <c r="F1143" s="65"/>
+      <c r="G1143" s="65"/>
+      <c r="H1143" s="65"/>
+      <c r="I1143" s="65" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:9">
+      <c r="A1144" s="65">
+        <v>10530004</v>
+      </c>
+      <c r="B1144" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1144" s="65">
+        <v>4</v>
+      </c>
+      <c r="D1144" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1144" s="65"/>
+      <c r="F1144" s="65"/>
+      <c r="G1144" s="65"/>
+      <c r="H1144" s="65"/>
+      <c r="I1144" s="65" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:9">
+      <c r="A1145" s="65">
+        <v>10530005</v>
+      </c>
+      <c r="B1145" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1145" s="65">
+        <v>5</v>
+      </c>
+      <c r="D1145" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1145" s="65"/>
+      <c r="F1145" s="65"/>
+      <c r="G1145" s="65"/>
+      <c r="H1145" s="65"/>
+      <c r="I1145" s="65" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:9">
+      <c r="A1146" s="65">
+        <v>10530006</v>
+      </c>
+      <c r="B1146" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1146" s="65">
+        <v>6</v>
+      </c>
+      <c r="D1146" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1146" s="65"/>
+      <c r="F1146" s="65"/>
+      <c r="G1146" s="65"/>
+      <c r="H1146" s="65"/>
+      <c r="I1146" s="65" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:9">
+      <c r="A1147" s="65">
+        <v>10530007</v>
+      </c>
+      <c r="B1147" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1147" s="65">
+        <v>7</v>
+      </c>
+      <c r="D1147" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1147" s="65"/>
+      <c r="F1147" s="65"/>
+      <c r="G1147" s="65"/>
+      <c r="H1147" s="65"/>
+      <c r="I1147" s="65" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:9">
+      <c r="A1148" s="65">
+        <v>10530008</v>
+      </c>
+      <c r="B1148" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1148" s="65">
+        <v>8</v>
+      </c>
+      <c r="D1148" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1148" s="65"/>
+      <c r="F1148" s="65"/>
+      <c r="G1148" s="65"/>
+      <c r="H1148" s="65"/>
+      <c r="I1148" s="65" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:9">
+      <c r="A1149" s="65">
+        <v>10530009</v>
+      </c>
+      <c r="B1149" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1149" s="65">
+        <v>9</v>
+      </c>
+      <c r="D1149" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1149" s="65"/>
+      <c r="F1149" s="65"/>
+      <c r="G1149" s="65"/>
+      <c r="H1149" s="65"/>
+      <c r="I1149" s="65" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:9">
+      <c r="A1150" s="65">
+        <v>10530010</v>
+      </c>
+      <c r="B1150" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1150" s="65">
+        <v>10</v>
+      </c>
+      <c r="D1150" s="65">
+        <v>1</v>
+      </c>
+      <c r="E1150" s="65"/>
+      <c r="F1150" s="65"/>
+      <c r="G1150" s="65"/>
+      <c r="H1150" s="65"/>
+      <c r="I1150" s="65" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:9">
+      <c r="A1151" s="65">
+        <v>10530011</v>
+      </c>
+      <c r="B1151" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1151" s="65">
+        <v>11</v>
+      </c>
+      <c r="D1151" s="65">
+        <v>2</v>
+      </c>
+      <c r="E1151" s="65"/>
+      <c r="F1151" s="65"/>
+      <c r="G1151" s="65"/>
+      <c r="H1151" s="65"/>
+      <c r="I1151" s="65" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:9">
+      <c r="A1152" s="65">
+        <v>10530012</v>
+      </c>
+      <c r="B1152" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1152" s="65">
+        <v>12</v>
+      </c>
+      <c r="D1152" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1152" s="65"/>
+      <c r="F1152" s="65" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G1152" s="65"/>
+      <c r="H1152" s="65"/>
+      <c r="I1152" s="65" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:9">
+      <c r="A1153" s="65">
+        <v>10530013</v>
+      </c>
+      <c r="B1153" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1153" s="65">
+        <v>13</v>
+      </c>
+      <c r="D1153" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1153" s="65"/>
+      <c r="F1153" s="65" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G1153" s="65"/>
+      <c r="H1153" s="65"/>
+      <c r="I1153" s="65" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:9">
+      <c r="A1154" s="65">
+        <v>10530014</v>
+      </c>
+      <c r="B1154" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1154" s="65">
+        <v>14</v>
+      </c>
+      <c r="D1154" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1154" s="65"/>
+      <c r="F1154" s="65" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G1154" s="65"/>
+      <c r="H1154" s="65"/>
+      <c r="I1154" s="65" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:9">
+      <c r="A1155" s="65">
+        <v>10530015</v>
+      </c>
+      <c r="B1155" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1155" s="65">
+        <v>15</v>
+      </c>
+      <c r="D1155" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1155" s="65"/>
+      <c r="F1155" s="65" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G1155" s="65"/>
+      <c r="H1155" s="65"/>
+      <c r="I1155" s="65" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:9">
+      <c r="A1156" s="65">
+        <v>10530016</v>
+      </c>
+      <c r="B1156" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1156" s="65">
+        <v>16</v>
+      </c>
+      <c r="D1156" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1156" s="65"/>
+      <c r="F1156" s="65" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G1156" s="65"/>
+      <c r="H1156" s="65"/>
+      <c r="I1156" s="65" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:9">
+      <c r="A1157" s="65">
+        <v>10530017</v>
+      </c>
+      <c r="B1157" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1157" s="65">
+        <v>17</v>
+      </c>
+      <c r="D1157" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1157" s="65"/>
+      <c r="F1157" s="65" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G1157" s="65"/>
+      <c r="H1157" s="65"/>
+      <c r="I1157" s="65" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:9">
+      <c r="A1158" s="65">
+        <v>10530018</v>
+      </c>
+      <c r="B1158" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1158" s="65">
+        <v>18</v>
+      </c>
+      <c r="D1158" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1158" s="65"/>
+      <c r="F1158" s="65" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G1158" s="65"/>
+      <c r="H1158" s="65"/>
+      <c r="I1158" s="65" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:9">
+      <c r="A1159" s="65">
+        <v>10530019</v>
+      </c>
+      <c r="B1159" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1159" s="65">
+        <v>19</v>
+      </c>
+      <c r="D1159" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1159" s="65"/>
+      <c r="F1159" s="65" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G1159" s="65"/>
+      <c r="H1159" s="65"/>
+      <c r="I1159" s="65" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:9">
+      <c r="A1160" s="65">
+        <v>10530020</v>
+      </c>
+      <c r="B1160" s="65">
+        <v>105300</v>
+      </c>
+      <c r="C1160" s="65">
+        <v>20</v>
+      </c>
+      <c r="D1160" s="65">
+        <v>0</v>
+      </c>
+      <c r="E1160" s="65"/>
+      <c r="F1160" s="65" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G1160" s="65"/>
+      <c r="H1160" s="65"/>
+      <c r="I1160" s="65" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:9">
+      <c r="A1161" s="23">
+        <v>10570001</v>
+      </c>
+      <c r="B1161" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1161" s="23">
+        <v>1</v>
+      </c>
+      <c r="D1161" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1161" s="23"/>
+      <c r="F1161" s="23"/>
+      <c r="G1161" s="23"/>
+      <c r="H1161" s="23"/>
+      <c r="I1161" s="23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:9">
+      <c r="A1162" s="23">
+        <v>10570002</v>
+      </c>
+      <c r="B1162" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1162" s="23">
+        <v>2</v>
+      </c>
+      <c r="D1162" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1162" s="23"/>
+      <c r="F1162" s="23"/>
+      <c r="G1162" s="23"/>
+      <c r="H1162" s="23"/>
+      <c r="I1162" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:9">
+      <c r="A1163" s="23">
+        <v>10570003</v>
+      </c>
+      <c r="B1163" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1163" s="23">
+        <v>3</v>
+      </c>
+      <c r="D1163" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1163" s="23"/>
+      <c r="F1163" s="23"/>
+      <c r="G1163" s="23"/>
+      <c r="H1163" s="23"/>
+      <c r="I1163" s="23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:9">
+      <c r="A1164" s="23">
+        <v>10570004</v>
+      </c>
+      <c r="B1164" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1164" s="23">
+        <v>4</v>
+      </c>
+      <c r="D1164" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1164" s="23"/>
+      <c r="F1164" s="23"/>
+      <c r="G1164" s="23"/>
+      <c r="H1164" s="23"/>
+      <c r="I1164" s="23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:9">
+      <c r="A1165" s="23">
+        <v>10570005</v>
+      </c>
+      <c r="B1165" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1165" s="23">
+        <v>5</v>
+      </c>
+      <c r="D1165" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1165" s="23"/>
+      <c r="F1165" s="23"/>
+      <c r="G1165" s="23"/>
+      <c r="H1165" s="23"/>
+      <c r="I1165" s="23" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:9">
+      <c r="A1166" s="23">
+        <v>10570006</v>
+      </c>
+      <c r="B1166" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1166" s="23">
+        <v>6</v>
+      </c>
+      <c r="D1166" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1166" s="23"/>
+      <c r="F1166" s="23"/>
+      <c r="G1166" s="23"/>
+      <c r="H1166" s="23"/>
+      <c r="I1166" s="23" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:9">
+      <c r="A1167" s="23">
+        <v>10570007</v>
+      </c>
+      <c r="B1167" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1167" s="23">
+        <v>7</v>
+      </c>
+      <c r="D1167" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1167" s="23"/>
+      <c r="F1167" s="23"/>
+      <c r="G1167" s="23"/>
+      <c r="H1167" s="23"/>
+      <c r="I1167" s="23" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:9">
+      <c r="A1168" s="23">
+        <v>10570008</v>
+      </c>
+      <c r="B1168" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1168" s="23">
+        <v>8</v>
+      </c>
+      <c r="D1168" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1168" s="23"/>
+      <c r="F1168" s="23"/>
+      <c r="G1168" s="23"/>
+      <c r="H1168" s="23"/>
+      <c r="I1168" s="23" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:9">
+      <c r="A1169" s="23">
+        <v>10570009</v>
+      </c>
+      <c r="B1169" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1169" s="23">
+        <v>9</v>
+      </c>
+      <c r="D1169" s="23">
+        <v>1</v>
+      </c>
+      <c r="E1169" s="23"/>
+      <c r="F1169" s="23"/>
+      <c r="G1169" s="23"/>
+      <c r="H1169" s="23"/>
+      <c r="I1169" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:9">
+      <c r="A1170" s="23">
+        <v>10570010</v>
+      </c>
+      <c r="B1170" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1170" s="23">
+        <v>10</v>
+      </c>
+      <c r="D1170" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1170" s="23"/>
+      <c r="F1170" s="23"/>
+      <c r="G1170" s="23"/>
+      <c r="H1170" s="23"/>
+      <c r="I1170" s="23" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:9">
+      <c r="A1171" s="23">
+        <v>10570011</v>
+      </c>
+      <c r="B1171" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1171" s="23">
+        <v>11</v>
+      </c>
+      <c r="D1171" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1171" s="23"/>
+      <c r="F1171" s="23"/>
+      <c r="G1171" s="23"/>
+      <c r="H1171" s="23"/>
+      <c r="I1171" s="23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:9">
+      <c r="A1172" s="23">
+        <v>10570012</v>
+      </c>
+      <c r="B1172" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1172" s="23">
+        <v>12</v>
+      </c>
+      <c r="D1172" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1172" s="23"/>
+      <c r="F1172" s="23"/>
+      <c r="G1172" s="23"/>
+      <c r="H1172" s="23"/>
+      <c r="I1172" s="23" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:9">
+      <c r="A1173" s="23">
+        <v>10570013</v>
+      </c>
+      <c r="B1173" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1173" s="23">
+        <v>13</v>
+      </c>
+      <c r="D1173" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1173" s="23"/>
+      <c r="F1173" s="23"/>
+      <c r="G1173" s="23"/>
+      <c r="H1173" s="23"/>
+      <c r="I1173" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:9">
+      <c r="A1174" s="23">
+        <v>10570014</v>
+      </c>
+      <c r="B1174" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1174" s="23">
+        <v>14</v>
+      </c>
+      <c r="D1174" s="23">
+        <v>2</v>
+      </c>
+      <c r="E1174" s="23"/>
+      <c r="F1174" s="23"/>
+      <c r="G1174" s="23"/>
+      <c r="H1174" s="23"/>
+      <c r="I1174" s="23" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:9">
+      <c r="A1175" s="23">
+        <v>10570015</v>
+      </c>
+      <c r="B1175" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1175" s="23">
+        <v>15</v>
+      </c>
+      <c r="D1175" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1175" s="23"/>
+      <c r="F1175" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1175" s="23"/>
+      <c r="H1175" s="23"/>
+      <c r="I1175" s="23" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:9">
+      <c r="A1176" s="23">
+        <v>10570016</v>
+      </c>
+      <c r="B1176" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1176" s="23">
+        <v>16</v>
+      </c>
+      <c r="D1176" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1176" s="23"/>
+      <c r="F1176" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1176" s="23"/>
+      <c r="H1176" s="23"/>
+      <c r="I1176" s="23" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:9">
+      <c r="A1177" s="23">
+        <v>10570017</v>
+      </c>
+      <c r="B1177" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1177" s="23">
+        <v>17</v>
+      </c>
+      <c r="D1177" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1177" s="23"/>
+      <c r="F1177" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1177" s="23"/>
+      <c r="H1177" s="23"/>
+      <c r="I1177" s="23" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:9">
+      <c r="A1178" s="23">
+        <v>10570018</v>
+      </c>
+      <c r="B1178" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1178" s="23">
+        <v>18</v>
+      </c>
+      <c r="D1178" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1178" s="23"/>
+      <c r="F1178" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1178" s="23"/>
+      <c r="H1178" s="23"/>
+      <c r="I1178" s="23" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:9">
+      <c r="A1179" s="23">
+        <v>10570019</v>
+      </c>
+      <c r="B1179" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1179" s="23">
+        <v>19</v>
+      </c>
+      <c r="D1179" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1179" s="23"/>
+      <c r="F1179" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1179" s="23"/>
+      <c r="H1179" s="23"/>
+      <c r="I1179" s="23" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:9">
+      <c r="A1180" s="23">
+        <v>10570020</v>
+      </c>
+      <c r="B1180" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1180" s="23">
+        <v>20</v>
+      </c>
+      <c r="D1180" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1180" s="23"/>
+      <c r="F1180" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1180" s="23"/>
+      <c r="H1180" s="23"/>
+      <c r="I1180" s="23" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:9">
+      <c r="A1181" s="23">
+        <v>10570021</v>
+      </c>
+      <c r="B1181" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1181" s="23">
+        <v>21</v>
+      </c>
+      <c r="D1181" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1181" s="23"/>
+      <c r="F1181" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1181" s="23"/>
+      <c r="H1181" s="23"/>
+      <c r="I1181" s="23" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:9">
+      <c r="A1182" s="23">
+        <v>10570022</v>
+      </c>
+      <c r="B1182" s="23">
+        <v>105700</v>
+      </c>
+      <c r="C1182" s="23">
+        <v>22</v>
+      </c>
+      <c r="D1182" s="23">
+        <v>0</v>
+      </c>
+      <c r="E1182" s="23"/>
+      <c r="F1182" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1182" s="23"/>
+      <c r="H1182" s="23"/>
+      <c r="I1182" s="23" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:9">
+      <c r="A1183" s="43">
+        <v>10580001</v>
+      </c>
+      <c r="B1183" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1183" s="43">
+        <v>1</v>
+      </c>
+      <c r="D1183" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1183" s="43"/>
+      <c r="F1183" s="43"/>
+      <c r="G1183" s="43"/>
+      <c r="H1183" s="43"/>
+      <c r="I1183" s="43" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:9">
+      <c r="A1184" s="43">
+        <v>10580002</v>
+      </c>
+      <c r="B1184" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1184" s="43">
+        <v>2</v>
+      </c>
+      <c r="D1184" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1184" s="43"/>
+      <c r="F1184" s="43"/>
+      <c r="G1184" s="43"/>
+      <c r="H1184" s="43"/>
+      <c r="I1184" s="43" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:9">
+      <c r="A1185" s="43">
+        <v>10580003</v>
+      </c>
+      <c r="B1185" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1185" s="43">
+        <v>3</v>
+      </c>
+      <c r="D1185" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1185" s="43"/>
+      <c r="F1185" s="43"/>
+      <c r="G1185" s="43"/>
+      <c r="H1185" s="43"/>
+      <c r="I1185" s="43" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:9">
+      <c r="A1186" s="43">
+        <v>10580004</v>
+      </c>
+      <c r="B1186" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1186" s="43">
+        <v>4</v>
+      </c>
+      <c r="D1186" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1186" s="43"/>
+      <c r="F1186" s="43"/>
+      <c r="G1186" s="43"/>
+      <c r="H1186" s="43"/>
+      <c r="I1186" s="43" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:9">
+      <c r="A1187" s="43">
+        <v>10580005</v>
+      </c>
+      <c r="B1187" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1187" s="43">
+        <v>5</v>
+      </c>
+      <c r="D1187" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1187" s="43"/>
+      <c r="F1187" s="43"/>
+      <c r="G1187" s="43"/>
+      <c r="H1187" s="43"/>
+      <c r="I1187" s="43" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:9">
+      <c r="A1188" s="43">
+        <v>10580006</v>
+      </c>
+      <c r="B1188" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1188" s="43">
+        <v>6</v>
+      </c>
+      <c r="D1188" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1188" s="43"/>
+      <c r="F1188" s="43"/>
+      <c r="G1188" s="43"/>
+      <c r="H1188" s="43"/>
+      <c r="I1188" s="43" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:9">
+      <c r="A1189" s="43">
+        <v>10580007</v>
+      </c>
+      <c r="B1189" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1189" s="43">
+        <v>7</v>
+      </c>
+      <c r="D1189" s="43">
+        <v>0</v>
+      </c>
+      <c r="E1189" s="43"/>
+      <c r="F1189" s="43"/>
+      <c r="G1189" s="43"/>
+      <c r="H1189" s="43"/>
+      <c r="I1189" s="43" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:9">
+      <c r="A1190" s="43">
+        <v>10580008</v>
+      </c>
+      <c r="B1190" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1190" s="43">
+        <v>8</v>
+      </c>
+      <c r="D1190" s="43">
+        <v>2</v>
+      </c>
+      <c r="E1190" s="43"/>
+      <c r="F1190" s="43"/>
+      <c r="G1190" s="43"/>
+      <c r="H1190" s="43"/>
+      <c r="I1190" s="43" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="1191" ht="17.25" spans="1:9">
+      <c r="A1191" s="43">
+        <v>10580009</v>
+      </c>
+      <c r="B1191" s="43">
+        <v>105800</v>
+      </c>
+      <c r="C1191" s="43">
+        <v>9</v>
+      </c>
+      <c r="D1191" s="43">
+        <v>2</v>
+      </c>
+      <c r="E1191" s="43"/>
+      <c r="F1191" s="43"/>
+      <c r="G1191" s="43"/>
+      <c r="H1191" s="43"/>
+      <c r="I1191" s="66" t="s">
+        <v>1525</v>
       </c>
     </row>
   </sheetData>
